--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="693">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -220,7 +220,7 @@
     <t>1,1,1</t>
   </si>
   <si>
-    <t>27.00,0.00,28.48,39.00,0.00,28.48,39.00,0.00,17.00,27.00,0.00,17.00</t>
+    <t>27.00,0.00,29.00,39.00,0.00,29.00,39.00,0.00,17.00,27.00,0.00,17.00</t>
   </si>
   <si>
     <t>26.00,0.00,16.00,40.00,0.00,16.00,40.00,0.00,30.00,26.00,0.00,30.00</t>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>11,4.999971,15</t>
-  </si>
-  <si>
-    <t>34,4.999971,23</t>
   </si>
   <si>
     <t>24.0169582366943,5.809939,8.63291168212891</t>
@@ -3625,7 +3622,7 @@
         <v>15050</v>
       </c>
       <c r="Z5" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="50">
         <v>0</v>
@@ -5100,7 +5097,7 @@
         <v>15050</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E24" s="50">
         <v>62</v>
@@ -5184,7 +5181,7 @@
         <v>30813</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="50">
         <v>12</v>
@@ -5268,7 +5265,7 @@
         <v>30819</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" s="50">
         <v>17</v>
@@ -5280,7 +5277,7 @@
         <v>64</v>
       </c>
       <c r="H26" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I26" s="50" t="s">
         <v>79</v>
@@ -5289,10 +5286,10 @@
         <v>66</v>
       </c>
       <c r="K26" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="50" t="s">
         <v>111</v>
-      </c>
-      <c r="L26" s="50" t="s">
-        <v>112</v>
       </c>
       <c r="M26" s="50" t="s">
         <v>1</v>
@@ -5355,7 +5352,7 @@
         <v>30822</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E27" s="50">
         <v>14</v>
@@ -5439,7 +5436,7 @@
         <v>30837</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E28" s="50">
         <v>55</v>
@@ -5451,7 +5448,7 @@
         <v>98</v>
       </c>
       <c r="H28" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I28" s="50" t="s">
         <v>79</v>
@@ -5460,10 +5457,10 @@
         <v>66</v>
       </c>
       <c r="K28" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="L28" s="50" t="s">
         <v>116</v>
-      </c>
-      <c r="L28" s="50" t="s">
-        <v>117</v>
       </c>
       <c r="M28" s="50" t="s">
         <v>1</v>
@@ -5526,7 +5523,7 @@
         <v>30840</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E29" s="50">
         <v>54</v>
@@ -5538,7 +5535,7 @@
         <v>98</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I29" s="50" t="s">
         <v>79</v>
@@ -5613,7 +5610,7 @@
         <v>30862</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E30" s="50">
         <v>53</v>
@@ -5625,7 +5622,7 @@
         <v>64</v>
       </c>
       <c r="H30" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I30" s="50" t="s">
         <v>79</v>
@@ -5634,7 +5631,7 @@
         <v>66</v>
       </c>
       <c r="K30" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L30" s="50" t="s">
         <v>1</v>
@@ -5671,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y30" s="50">
         <v>0</v>
@@ -5700,7 +5697,7 @@
         <v>30927</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E31" s="50">
         <v>5</v>
@@ -5709,10 +5706,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" s="50" t="s">
         <v>125</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>126</v>
       </c>
       <c r="I31" s="50" t="s">
         <v>79</v>
@@ -5787,7 +5784,7 @@
         <v>30930</v>
       </c>
       <c r="D32" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="50">
         <v>6</v>
@@ -5799,7 +5796,7 @@
         <v>98</v>
       </c>
       <c r="H32" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I32" s="50" t="s">
         <v>79</v>
@@ -5808,13 +5805,13 @@
         <v>66</v>
       </c>
       <c r="K32" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M32" s="50" t="s">
         <v>129</v>
-      </c>
-      <c r="L32" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M32" s="50" t="s">
-        <v>130</v>
       </c>
       <c r="N32" s="50">
         <v>2</v>
@@ -5845,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y32" s="50">
         <v>0</v>
@@ -5874,7 +5871,7 @@
         <v>30947</v>
       </c>
       <c r="D33" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E33" s="50">
         <v>7</v>
@@ -5883,10 +5880,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>79</v>
@@ -5895,10 +5892,10 @@
         <v>66</v>
       </c>
       <c r="K33" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="L33" s="50" t="s">
         <v>134</v>
-      </c>
-      <c r="L33" s="50" t="s">
-        <v>135</v>
       </c>
       <c r="M33" s="50" t="s">
         <v>1</v>
@@ -5961,7 +5958,7 @@
         <v>34800</v>
       </c>
       <c r="D34" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E34" s="50">
         <v>7</v>
@@ -5970,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I34" s="50" t="s">
         <v>79</v>
@@ -5982,10 +5979,10 @@
         <v>66</v>
       </c>
       <c r="K34" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="L34" s="50" t="s">
         <v>134</v>
-      </c>
-      <c r="L34" s="50" t="s">
-        <v>135</v>
       </c>
       <c r="M34" s="50" t="s">
         <v>1</v>
@@ -6048,7 +6045,7 @@
         <v>30969</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E35" s="50">
         <v>18</v>
@@ -6060,7 +6057,7 @@
         <v>64</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>79</v>
@@ -6069,7 +6066,7 @@
         <v>66</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L35" s="50" t="s">
         <v>1</v>
@@ -6135,7 +6132,7 @@
         <v>34815</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" s="50">
         <v>59</v>
@@ -6219,7 +6216,7 @@
         <v>24849</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E37" s="50">
         <v>2</v>
@@ -6244,7 +6241,7 @@
       </c>
       <c r="O37" s="50"/>
       <c r="P37" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="50"/>
       <c r="R37" s="50"/>
@@ -6279,7 +6276,7 @@
         <v>24850</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E38" s="50">
         <v>2</v>
@@ -6304,7 +6301,7 @@
       </c>
       <c r="O38" s="50"/>
       <c r="P38" s="50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="50"/>
       <c r="R38" s="50"/>
@@ -6335,7 +6332,7 @@
         <v>24851</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E39" s="50">
         <v>2</v>
@@ -6360,7 +6357,7 @@
       </c>
       <c r="O39" s="50"/>
       <c r="P39" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="50"/>
       <c r="R39" s="50"/>
@@ -6395,7 +6392,7 @@
         <v>24852</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E40" s="50">
         <v>2</v>
@@ -6420,7 +6417,7 @@
       </c>
       <c r="O40" s="50"/>
       <c r="P40" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="50"/>
       <c r="R40" s="50"/>
@@ -6432,7 +6429,7 @@
       </c>
       <c r="W40" s="50"/>
       <c r="X40" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y40" s="50"/>
       <c r="Z40" s="50"/>
@@ -6453,7 +6450,7 @@
         <v>24865</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E41" s="50">
         <v>2</v>
@@ -6478,7 +6475,7 @@
       </c>
       <c r="O41" s="50"/>
       <c r="P41" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="50"/>
       <c r="R41" s="50"/>
@@ -6513,7 +6510,7 @@
         <v>24866</v>
       </c>
       <c r="D42" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E42" s="50">
         <v>2</v>
@@ -6538,7 +6535,7 @@
       </c>
       <c r="O42" s="50"/>
       <c r="P42" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="50"/>
       <c r="R42" s="50"/>
@@ -6569,7 +6566,7 @@
         <v>24867</v>
       </c>
       <c r="D43" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E43" s="50">
         <v>2</v>
@@ -6594,7 +6591,7 @@
       </c>
       <c r="O43" s="50"/>
       <c r="P43" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="50"/>
       <c r="R43" s="50"/>
@@ -6629,7 +6626,7 @@
         <v>24868</v>
       </c>
       <c r="D44" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E44" s="50">
         <v>2</v>
@@ -6654,7 +6651,7 @@
       </c>
       <c r="O44" s="50"/>
       <c r="P44" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q44" s="50"/>
       <c r="R44" s="50"/>
@@ -6666,7 +6663,7 @@
       </c>
       <c r="W44" s="50"/>
       <c r="X44" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y44" s="50"/>
       <c r="Z44" s="50"/>
@@ -6687,7 +6684,7 @@
         <v>33236</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E45" s="50">
         <v>12</v>
@@ -6771,7 +6768,7 @@
         <v>33240</v>
       </c>
       <c r="D46" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E46" s="50">
         <v>5</v>
@@ -6783,7 +6780,7 @@
         <v>84</v>
       </c>
       <c r="H46" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I46" s="50" t="s">
         <v>79</v>
@@ -6858,7 +6855,7 @@
         <v>33249</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="50">
         <v>28</v>
@@ -6870,7 +6867,7 @@
         <v>64</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I47" s="50" t="s">
         <v>79</v>
@@ -6882,7 +6879,7 @@
         <v>75</v>
       </c>
       <c r="L47" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M47" s="50" t="s">
         <v>1</v>
@@ -6945,7 +6942,7 @@
         <v>33339</v>
       </c>
       <c r="D48" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="50">
         <v>29</v>
@@ -6957,7 +6954,7 @@
         <v>64</v>
       </c>
       <c r="H48" s="50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I48" s="50" t="s">
         <v>79</v>
@@ -6966,13 +6963,13 @@
         <v>66</v>
       </c>
       <c r="K48" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="L48" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M48" s="50" t="s">
         <v>167</v>
-      </c>
-      <c r="L48" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M48" s="50" t="s">
-        <v>168</v>
       </c>
       <c r="N48" s="50">
         <v>3</v>
@@ -7032,7 +7029,7 @@
         <v>33390</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E49" s="50">
         <v>14</v>
@@ -7116,7 +7113,7 @@
         <v>34816</v>
       </c>
       <c r="D50" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E50" s="50">
         <v>3</v>
@@ -7128,7 +7125,7 @@
         <v>64</v>
       </c>
       <c r="H50" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I50" s="50" t="s">
         <v>79</v>
@@ -7137,7 +7134,7 @@
         <v>66</v>
       </c>
       <c r="K50" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L50" s="50" t="s">
         <v>1</v>
@@ -7174,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y50" s="50">
         <v>0</v>
@@ -7203,7 +7200,7 @@
         <v>34817</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E51" s="50">
         <v>16</v>
@@ -7212,10 +7209,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>79</v>
@@ -7224,7 +7221,7 @@
         <v>66</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L51" s="50">
         <v>34816</v>
@@ -7290,7 +7287,7 @@
         <v>34821</v>
       </c>
       <c r="D52" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E52" s="50">
         <v>16</v>
@@ -7299,10 +7296,10 @@
         <v>9</v>
       </c>
       <c r="G52" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I52" s="50" t="s">
         <v>79</v>
@@ -7311,13 +7308,13 @@
         <v>66</v>
       </c>
       <c r="K52" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="L52" s="50">
+        <v>0</v>
+      </c>
+      <c r="M52" s="50" t="s">
         <v>179</v>
-      </c>
-      <c r="L52" s="50">
-        <v>0</v>
-      </c>
-      <c r="M52" s="50" t="s">
-        <v>180</v>
       </c>
       <c r="N52" s="50">
         <v>3</v>
@@ -7377,7 +7374,7 @@
         <v>34850</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E53" s="50">
         <v>2</v>
@@ -7402,7 +7399,7 @@
       </c>
       <c r="O53" s="50"/>
       <c r="P53" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q53" s="50"/>
       <c r="R53" s="50"/>
@@ -7437,7 +7434,7 @@
         <v>34882</v>
       </c>
       <c r="D54" s="50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54" s="50">
         <v>2</v>
@@ -7456,7 +7453,7 @@
       </c>
       <c r="K54" s="50"/>
       <c r="L54" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M54" s="50"/>
       <c r="N54" s="50">
@@ -7464,7 +7461,7 @@
       </c>
       <c r="O54" s="50"/>
       <c r="P54" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q54" s="50"/>
       <c r="R54" s="50"/>
@@ -7476,7 +7473,7 @@
       </c>
       <c r="W54" s="50"/>
       <c r="X54" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y54" s="50"/>
       <c r="Z54" s="50"/>
@@ -7497,7 +7494,7 @@
         <v>34852</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" s="50">
         <v>2</v>
@@ -7522,7 +7519,7 @@
       </c>
       <c r="O55" s="50"/>
       <c r="P55" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q55" s="50"/>
       <c r="R55" s="50"/>
@@ -7553,7 +7550,7 @@
         <v>34853</v>
       </c>
       <c r="D56" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56" s="50">
         <v>2</v>
@@ -7572,7 +7569,7 @@
       </c>
       <c r="K56" s="50"/>
       <c r="L56" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M56" s="50"/>
       <c r="N56" s="50">
@@ -7580,7 +7577,7 @@
       </c>
       <c r="O56" s="50"/>
       <c r="P56" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q56" s="50"/>
       <c r="R56" s="50"/>
@@ -7592,7 +7589,7 @@
       </c>
       <c r="W56" s="50"/>
       <c r="X56" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y56" s="50"/>
       <c r="Z56" s="50"/>
@@ -7613,7 +7610,7 @@
         <v>34868</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E57" s="50">
         <v>2</v>
@@ -7638,7 +7635,7 @@
       </c>
       <c r="O57" s="50"/>
       <c r="P57" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="50"/>
       <c r="R57" s="50"/>
@@ -7673,7 +7670,7 @@
         <v>34869</v>
       </c>
       <c r="D58" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E58" s="50">
         <v>2</v>
@@ -7698,7 +7695,7 @@
       </c>
       <c r="O58" s="50"/>
       <c r="P58" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q58" s="50"/>
       <c r="R58" s="50"/>
@@ -7729,7 +7726,7 @@
         <v>44810</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E59" s="50">
         <v>12</v>
@@ -7813,7 +7810,7 @@
         <v>44815</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E60" s="50">
         <v>6</v>
@@ -7825,7 +7822,7 @@
         <v>64</v>
       </c>
       <c r="H60" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I60" s="50" t="s">
         <v>79</v>
@@ -7834,13 +7831,13 @@
         <v>66</v>
       </c>
       <c r="K60" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L60" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M60" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N60" s="50">
         <v>4</v>
@@ -7900,7 +7897,7 @@
         <v>44816</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E61" s="50">
         <v>7</v>
@@ -7912,7 +7909,7 @@
         <v>98</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I61" s="50" t="s">
         <v>79</v>
@@ -7921,10 +7918,10 @@
         <v>66</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L61" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M61" s="50" t="s">
         <v>1</v>
@@ -7987,7 +7984,7 @@
         <v>44817</v>
       </c>
       <c r="D62" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E62" s="50">
         <v>7</v>
@@ -7999,7 +7996,7 @@
         <v>98</v>
       </c>
       <c r="H62" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I62" s="50" t="s">
         <v>79</v>
@@ -8008,10 +8005,10 @@
         <v>66</v>
       </c>
       <c r="K62" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L62" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M62" s="50" t="s">
         <v>1</v>
@@ -8074,7 +8071,7 @@
         <v>44818</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E63" s="50">
         <v>7</v>
@@ -8086,7 +8083,7 @@
         <v>98</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I63" s="50" t="s">
         <v>79</v>
@@ -8095,10 +8092,10 @@
         <v>66</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L63" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M63" s="50" t="s">
         <v>1</v>
@@ -8161,7 +8158,7 @@
         <v>44819</v>
       </c>
       <c r="D64" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E64" s="50">
         <v>5</v>
@@ -8173,7 +8170,7 @@
         <v>98</v>
       </c>
       <c r="H64" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I64" s="50" t="s">
         <v>79</v>
@@ -8248,7 +8245,7 @@
         <v>44820</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E65" s="50">
         <v>5</v>
@@ -8260,7 +8257,7 @@
         <v>84</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I65" s="50" t="s">
         <v>79</v>
@@ -8269,7 +8266,7 @@
         <v>66</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L65" s="50" t="s">
         <v>1</v>
@@ -8335,7 +8332,7 @@
         <v>44823</v>
       </c>
       <c r="D66" s="50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E66" s="50">
         <v>16</v>
@@ -8347,7 +8344,7 @@
         <v>64</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>79</v>
@@ -8359,7 +8356,7 @@
         <v>80</v>
       </c>
       <c r="L66" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M66" s="50" t="s">
         <v>1</v>
@@ -8422,7 +8419,7 @@
         <v>44824</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E67" s="50">
         <v>3</v>
@@ -8434,7 +8431,7 @@
         <v>64</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I67" s="50" t="s">
         <v>79</v>
@@ -8509,7 +8506,7 @@
         <v>44825</v>
       </c>
       <c r="D68" s="50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E68" s="50">
         <v>4</v>
@@ -8518,10 +8515,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I68" s="50" t="s">
         <v>79</v>
@@ -8530,7 +8527,7 @@
         <v>66</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L68" s="50" t="s">
         <v>1</v>
@@ -8596,7 +8593,7 @@
         <v>44827</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E69" s="50">
         <v>20</v>
@@ -8608,7 +8605,7 @@
         <v>64</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>79</v>
@@ -8617,13 +8614,13 @@
         <v>66</v>
       </c>
       <c r="K69" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="L69" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="L69" s="50" t="s">
+      <c r="M69" s="50" t="s">
         <v>221</v>
-      </c>
-      <c r="M69" s="50" t="s">
-        <v>222</v>
       </c>
       <c r="N69" s="50">
         <v>4</v>
@@ -8683,7 +8680,7 @@
         <v>44828</v>
       </c>
       <c r="D70" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E70" s="50">
         <v>19</v>
@@ -8695,7 +8692,7 @@
         <v>64</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I70" s="50" t="s">
         <v>79</v>
@@ -8704,7 +8701,7 @@
         <v>66</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L70" s="50" t="s">
         <v>1</v>
@@ -8770,7 +8767,7 @@
         <v>44829</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E71" s="50">
         <v>16</v>
@@ -8782,7 +8779,7 @@
         <v>64</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I71" s="50" t="s">
         <v>79</v>
@@ -8791,10 +8788,10 @@
         <v>66</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L71" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M71" s="50" t="s">
         <v>1</v>
@@ -8857,7 +8854,7 @@
         <v>44831</v>
       </c>
       <c r="D72" s="50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E72" s="50">
         <v>14</v>
@@ -8878,7 +8875,7 @@
         <v>82</v>
       </c>
       <c r="L72" s="50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M72" s="50" t="s">
         <v>1</v>
@@ -8941,7 +8938,7 @@
         <v>44832</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E73" s="50">
         <v>4</v>
@@ -8950,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I73" s="50" t="s">
         <v>79</v>
@@ -8962,7 +8959,7 @@
         <v>66</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L73" s="50" t="s">
         <v>1</v>
@@ -9028,7 +9025,7 @@
         <v>44834</v>
       </c>
       <c r="D74" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E74" s="50">
         <v>2</v>
@@ -9053,7 +9050,7 @@
       </c>
       <c r="O74" s="50"/>
       <c r="P74" s="50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q74" s="50"/>
       <c r="R74" s="50"/>
@@ -9082,7 +9079,7 @@
         <v>44836</v>
       </c>
       <c r="D75" s="50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E75" s="50">
         <v>2</v>
@@ -9107,7 +9104,7 @@
       </c>
       <c r="O75" s="50"/>
       <c r="P75" s="50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="50"/>
       <c r="R75" s="50"/>
@@ -9136,7 +9133,7 @@
         <v>44837</v>
       </c>
       <c r="D76" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E76" s="50">
         <v>2</v>
@@ -9161,7 +9158,7 @@
       </c>
       <c r="O76" s="50"/>
       <c r="P76" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q76" s="50"/>
       <c r="R76" s="50"/>
@@ -9190,7 +9187,7 @@
         <v>34027</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E77" s="50">
         <v>3</v>
@@ -9208,7 +9205,7 @@
         <v>66</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L77" s="50" t="s">
         <v>1</v>
@@ -9274,7 +9271,7 @@
         <v>34057</v>
       </c>
       <c r="D78" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E78" s="50">
         <v>5</v>
@@ -9283,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I78" s="50" t="s">
         <v>79</v>
@@ -9358,7 +9355,7 @@
         <v>34063</v>
       </c>
       <c r="D79" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E79" s="50">
         <v>16</v>
@@ -9376,10 +9373,10 @@
         <v>66</v>
       </c>
       <c r="K79" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="L79" s="50" t="s">
         <v>244</v>
-      </c>
-      <c r="L79" s="50" t="s">
-        <v>245</v>
       </c>
       <c r="M79" s="50" t="s">
         <v>1</v>
@@ -9442,7 +9439,7 @@
         <v>34107</v>
       </c>
       <c r="D80" s="50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E80" s="50">
         <v>12</v>
@@ -9526,7 +9523,7 @@
         <v>34115</v>
       </c>
       <c r="D81" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E81" s="50">
         <v>28</v>
@@ -9547,7 +9544,7 @@
         <v>75</v>
       </c>
       <c r="L81" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M81" s="50" t="s">
         <v>1</v>
@@ -9610,7 +9607,7 @@
         <v>34147</v>
       </c>
       <c r="D82" s="50" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E82" s="50">
         <v>54</v>
@@ -9619,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I82" s="50" t="s">
         <v>79</v>
@@ -9694,7 +9691,7 @@
         <v>34177</v>
       </c>
       <c r="D83" s="50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E83" s="50">
         <v>4</v>
@@ -9712,7 +9709,7 @@
         <v>66</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L83" s="50" t="s">
         <v>1</v>
@@ -9778,7 +9775,7 @@
         <v>34198</v>
       </c>
       <c r="D84" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E84" s="50">
         <v>19</v>
@@ -9796,7 +9793,7 @@
         <v>66</v>
       </c>
       <c r="K84" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L84" s="50" t="s">
         <v>1</v>
@@ -9862,7 +9859,7 @@
         <v>34199</v>
       </c>
       <c r="D85" s="50" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E85" s="50">
         <v>5</v>
@@ -9946,7 +9943,7 @@
         <v>34202</v>
       </c>
       <c r="D86" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E86" s="50">
         <v>16</v>
@@ -9964,10 +9961,10 @@
         <v>66</v>
       </c>
       <c r="K86" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L86" s="50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M86" s="50" t="s">
         <v>1</v>
@@ -10030,7 +10027,7 @@
         <v>34205</v>
       </c>
       <c r="D87" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E87" s="50">
         <v>29</v>
@@ -10048,13 +10045,13 @@
         <v>66</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L87" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M87" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N87" s="50">
         <v>5</v>
@@ -10114,7 +10111,7 @@
         <v>34214</v>
       </c>
       <c r="D88" s="50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E88" s="50">
         <v>52</v>
@@ -10132,13 +10129,13 @@
         <v>66</v>
       </c>
       <c r="K88" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L88" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="L88" s="50" t="s">
+      <c r="M88" s="50" t="s">
         <v>259</v>
-      </c>
-      <c r="M88" s="50" t="s">
-        <v>260</v>
       </c>
       <c r="N88" s="50">
         <v>5</v>
@@ -10198,7 +10195,7 @@
         <v>34217</v>
       </c>
       <c r="D89" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E89" s="50">
         <v>4</v>
@@ -10207,7 +10204,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I89" s="50" t="s">
         <v>79</v>
@@ -10216,7 +10213,7 @@
         <v>66</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L89" s="50" t="s">
         <v>1</v>
@@ -10282,7 +10279,7 @@
         <v>34240</v>
       </c>
       <c r="D90" s="50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E90" s="50">
         <v>51</v>
@@ -10300,7 +10297,7 @@
         <v>66</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L90" s="50" t="s">
         <v>1</v>
@@ -10366,7 +10363,7 @@
         <v>34275</v>
       </c>
       <c r="D91" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E91" s="50">
         <v>16</v>
@@ -10384,10 +10381,10 @@
         <v>66</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L91" s="50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M91" s="50" t="s">
         <v>1</v>
@@ -10450,7 +10447,7 @@
         <v>34291</v>
       </c>
       <c r="D92" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E92" s="50">
         <v>20</v>
@@ -10468,13 +10465,13 @@
         <v>66</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L92" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="M92" s="50" t="s">
         <v>267</v>
-      </c>
-      <c r="M92" s="50" t="s">
-        <v>268</v>
       </c>
       <c r="N92" s="50">
         <v>5</v>
@@ -10534,7 +10531,7 @@
         <v>34301</v>
       </c>
       <c r="D93" s="50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E93" s="50">
         <v>51</v>
@@ -10552,7 +10549,7 @@
         <v>66</v>
       </c>
       <c r="K93" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L93" s="50" t="s">
         <v>1</v>
@@ -10618,7 +10615,7 @@
         <v>34334</v>
       </c>
       <c r="D94" s="50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E94" s="50">
         <v>52</v>
@@ -10636,13 +10633,13 @@
         <v>66</v>
       </c>
       <c r="K94" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L94" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="L94" s="50" t="s">
-        <v>273</v>
-      </c>
       <c r="M94" s="50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N94" s="50">
         <v>5</v>
@@ -10702,7 +10699,7 @@
         <v>34337</v>
       </c>
       <c r="D95" s="50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E95" s="50">
         <v>14</v>
@@ -10723,7 +10720,7 @@
         <v>82</v>
       </c>
       <c r="L95" s="50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M95" s="50" t="s">
         <v>1</v>
@@ -10786,7 +10783,7 @@
         <v>34586</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E96" s="50">
         <v>2</v>
@@ -10811,7 +10808,7 @@
       </c>
       <c r="O96" s="50"/>
       <c r="P96" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q96" s="50"/>
       <c r="R96" s="50"/>
@@ -10840,7 +10837,7 @@
         <v>34587</v>
       </c>
       <c r="D97" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E97" s="50">
         <v>2</v>
@@ -10865,7 +10862,7 @@
       </c>
       <c r="O97" s="50"/>
       <c r="P97" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q97" s="50"/>
       <c r="R97" s="50"/>
@@ -10894,7 +10891,7 @@
         <v>34589</v>
       </c>
       <c r="D98" s="50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E98" s="50">
         <v>4</v>
@@ -10903,7 +10900,7 @@
         <v>2</v>
       </c>
       <c r="G98" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I98" s="50" t="s">
         <v>79</v>
@@ -10912,7 +10909,7 @@
         <v>66</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L98" s="50" t="s">
         <v>1</v>
@@ -10978,7 +10975,7 @@
         <v>34590</v>
       </c>
       <c r="D99" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E99" s="50">
         <v>5</v>
@@ -10987,7 +10984,7 @@
         <v>3</v>
       </c>
       <c r="G99" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I99" s="50" t="s">
         <v>79</v>
@@ -10996,7 +10993,7 @@
         <v>66</v>
       </c>
       <c r="K99" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L99" s="50" t="s">
         <v>1</v>
@@ -11062,7 +11059,7 @@
         <v>34591</v>
       </c>
       <c r="D100" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E100" s="50">
         <v>5</v>
@@ -11080,7 +11077,7 @@
         <v>66</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L100" s="50" t="s">
         <v>1</v>
@@ -11146,7 +11143,7 @@
         <v>34696</v>
       </c>
       <c r="D101" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E101" s="50">
         <v>2</v>
@@ -11171,7 +11168,7 @@
       </c>
       <c r="O101" s="50"/>
       <c r="P101" s="50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q101" s="50"/>
       <c r="R101" s="50"/>
@@ -11197,7 +11194,7 @@
         <v>34699</v>
       </c>
       <c r="D102" s="50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E102" s="50">
         <v>56</v>
@@ -11215,7 +11212,7 @@
         <v>66</v>
       </c>
       <c r="K102" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L102" s="50" t="s">
         <v>1</v>
@@ -11281,7 +11278,7 @@
         <v>34701</v>
       </c>
       <c r="D103" s="50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E103" s="50">
         <v>56</v>
@@ -11299,7 +11296,7 @@
         <v>66</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L103" s="50" t="s">
         <v>1</v>
@@ -11365,7 +11362,7 @@
         <v>34700</v>
       </c>
       <c r="D104" s="50" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E104" s="50">
         <v>56</v>
@@ -11383,7 +11380,7 @@
         <v>66</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L104" s="50" t="s">
         <v>1</v>
@@ -11449,7 +11446,7 @@
         <v>34697</v>
       </c>
       <c r="D105" s="50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E105" s="50">
         <v>56</v>
@@ -11467,7 +11464,7 @@
         <v>66</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L105" s="50" t="s">
         <v>1</v>
@@ -11533,7 +11530,7 @@
         <v>34698</v>
       </c>
       <c r="D106" s="50" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E106" s="50">
         <v>56</v>
@@ -11551,7 +11548,7 @@
         <v>66</v>
       </c>
       <c r="K106" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L106" s="50" t="s">
         <v>1</v>
@@ -11617,7 +11614,7 @@
         <v>34713</v>
       </c>
       <c r="D107" s="50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E107" s="50">
         <v>56</v>
@@ -11635,7 +11632,7 @@
         <v>66</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L107" s="50" t="s">
         <v>1</v>
@@ -11701,7 +11698,7 @@
         <v>34702</v>
       </c>
       <c r="D108" s="50" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E108" s="50">
         <v>56</v>
@@ -11719,7 +11716,7 @@
         <v>66</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L108" s="50" t="s">
         <v>1</v>
@@ -11785,7 +11782,7 @@
         <v>34703</v>
       </c>
       <c r="D109" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E109" s="50">
         <v>56</v>
@@ -11803,7 +11800,7 @@
         <v>66</v>
       </c>
       <c r="K109" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L109" s="50" t="s">
         <v>1</v>
@@ -11869,7 +11866,7 @@
         <v>34704</v>
       </c>
       <c r="D110" s="50" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E110" s="50">
         <v>56</v>
@@ -11887,7 +11884,7 @@
         <v>66</v>
       </c>
       <c r="K110" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L110" s="50" t="s">
         <v>1</v>
@@ -11953,7 +11950,7 @@
         <v>34705</v>
       </c>
       <c r="D111" s="50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E111" s="50">
         <v>56</v>
@@ -11971,7 +11968,7 @@
         <v>66</v>
       </c>
       <c r="K111" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L111" s="50" t="s">
         <v>1</v>
@@ -12037,7 +12034,7 @@
         <v>34706</v>
       </c>
       <c r="D112" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E112" s="50">
         <v>56</v>
@@ -12055,7 +12052,7 @@
         <v>66</v>
       </c>
       <c r="K112" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L112" s="50" t="s">
         <v>1</v>
@@ -12121,7 +12118,7 @@
         <v>34707</v>
       </c>
       <c r="D113" s="50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E113" s="50">
         <v>56</v>
@@ -12139,7 +12136,7 @@
         <v>66</v>
       </c>
       <c r="K113" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L113" s="50" t="s">
         <v>1</v>
@@ -12205,7 +12202,7 @@
         <v>34708</v>
       </c>
       <c r="D114" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E114" s="50">
         <v>56</v>
@@ -12223,7 +12220,7 @@
         <v>66</v>
       </c>
       <c r="K114" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L114" s="50" t="s">
         <v>1</v>
@@ -12289,7 +12286,7 @@
         <v>34709</v>
       </c>
       <c r="D115" s="50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E115" s="50">
         <v>56</v>
@@ -12307,7 +12304,7 @@
         <v>66</v>
       </c>
       <c r="K115" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L115" s="50" t="s">
         <v>1</v>
@@ -12373,7 +12370,7 @@
         <v>34710</v>
       </c>
       <c r="D116" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E116" s="50">
         <v>56</v>
@@ -12391,7 +12388,7 @@
         <v>66</v>
       </c>
       <c r="K116" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L116" s="50" t="s">
         <v>1</v>
@@ -12457,7 +12454,7 @@
         <v>34711</v>
       </c>
       <c r="D117" s="50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E117" s="50">
         <v>56</v>
@@ -12475,7 +12472,7 @@
         <v>66</v>
       </c>
       <c r="K117" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L117" s="50" t="s">
         <v>1</v>
@@ -12541,7 +12538,7 @@
         <v>34712</v>
       </c>
       <c r="D118" s="50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E118" s="50">
         <v>56</v>
@@ -12559,7 +12556,7 @@
         <v>66</v>
       </c>
       <c r="K118" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L118" s="50" t="s">
         <v>1</v>
@@ -12625,7 +12622,7 @@
         <v>34714</v>
       </c>
       <c r="D119" s="50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E119" s="50">
         <v>56</v>
@@ -12643,7 +12640,7 @@
         <v>66</v>
       </c>
       <c r="K119" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L119" s="50" t="s">
         <v>1</v>
@@ -12709,7 +12706,7 @@
         <v>34715</v>
       </c>
       <c r="D120" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E120" s="50">
         <v>56</v>
@@ -12727,7 +12724,7 @@
         <v>66</v>
       </c>
       <c r="K120" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L120" s="50" t="s">
         <v>1</v>
@@ -12793,7 +12790,7 @@
         <v>34716</v>
       </c>
       <c r="D121" s="50" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E121" s="50">
         <v>56</v>
@@ -12811,7 +12808,7 @@
         <v>66</v>
       </c>
       <c r="K121" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L121" s="50" t="s">
         <v>1</v>
@@ -12877,7 +12874,7 @@
         <v>34717</v>
       </c>
       <c r="D122" s="50" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E122" s="50">
         <v>56</v>
@@ -12895,7 +12892,7 @@
         <v>66</v>
       </c>
       <c r="K122" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L122" s="50" t="s">
         <v>1</v>
@@ -12961,7 +12958,7 @@
         <v>34593</v>
       </c>
       <c r="D123" s="50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E123" s="50">
         <v>12</v>
@@ -13045,7 +13042,7 @@
         <v>34594</v>
       </c>
       <c r="D124" s="50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E124" s="50">
         <v>49</v>
@@ -13063,10 +13060,10 @@
         <v>66</v>
       </c>
       <c r="K124" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="L124" s="50" t="s">
         <v>311</v>
-      </c>
-      <c r="L124" s="50" t="s">
-        <v>312</v>
       </c>
       <c r="M124" s="50" t="s">
         <v>1</v>
@@ -13129,7 +13126,7 @@
         <v>34595</v>
       </c>
       <c r="D125" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E125" s="50">
         <v>48</v>
@@ -13138,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I125" s="50" t="s">
         <v>79</v>
@@ -13147,13 +13144,13 @@
         <v>66</v>
       </c>
       <c r="K125" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="L125" s="50" t="s">
         <v>314</v>
       </c>
-      <c r="L125" s="50" t="s">
+      <c r="M125" s="50" t="s">
         <v>315</v>
-      </c>
-      <c r="M125" s="50" t="s">
-        <v>316</v>
       </c>
       <c r="N125" s="50">
         <v>6</v>
@@ -13213,7 +13210,7 @@
         <v>34596</v>
       </c>
       <c r="D126" s="50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E126" s="50">
         <v>50</v>
@@ -13231,7 +13228,7 @@
         <v>66</v>
       </c>
       <c r="K126" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L126" s="50" t="s">
         <v>1</v>
@@ -13297,7 +13294,7 @@
         <v>34612</v>
       </c>
       <c r="D127" s="50" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E127" s="50">
         <v>5</v>
@@ -13315,7 +13312,7 @@
         <v>66</v>
       </c>
       <c r="K127" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L127" s="50" t="s">
         <v>1</v>
@@ -13381,7 +13378,7 @@
         <v>34613</v>
       </c>
       <c r="D128" s="50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E128" s="50">
         <v>5</v>
@@ -13390,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I128" s="50" t="s">
         <v>79</v>
@@ -13465,7 +13462,7 @@
         <v>34614</v>
       </c>
       <c r="D129" s="50" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E129" s="50">
         <v>4</v>
@@ -13474,7 +13471,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I129" s="50" t="s">
         <v>79</v>
@@ -13483,7 +13480,7 @@
         <v>66</v>
       </c>
       <c r="K129" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L129" s="50" t="s">
         <v>1</v>
@@ -13549,7 +13546,7 @@
         <v>34615</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E130" s="50">
         <v>44</v>
@@ -13633,7 +13630,7 @@
         <v>34616</v>
       </c>
       <c r="D131" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E131" s="50">
         <v>5</v>
@@ -13642,7 +13639,7 @@
         <v>3</v>
       </c>
       <c r="G131" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I131" s="50" t="s">
         <v>79</v>
@@ -13651,7 +13648,7 @@
         <v>66</v>
       </c>
       <c r="K131" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L131" s="50" t="s">
         <v>1</v>
@@ -13717,7 +13714,7 @@
         <v>34617</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E132" s="50">
         <v>3</v>
@@ -13735,7 +13732,7 @@
         <v>66</v>
       </c>
       <c r="K132" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L132" s="50" t="s">
         <v>1</v>
@@ -13801,7 +13798,7 @@
         <v>34618</v>
       </c>
       <c r="D133" s="50" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E133" s="50">
         <v>16</v>
@@ -13810,7 +13807,7 @@
         <v>9</v>
       </c>
       <c r="G133" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I133" s="50" t="s">
         <v>79</v>
@@ -13819,10 +13816,10 @@
         <v>66</v>
       </c>
       <c r="K133" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L133" s="50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M133" s="50" t="s">
         <v>1</v>
@@ -13885,7 +13882,7 @@
         <v>34619</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E134" s="50">
         <v>20</v>
@@ -13903,13 +13900,13 @@
         <v>66</v>
       </c>
       <c r="K134" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L134" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="M134" s="50" t="s">
         <v>329</v>
-      </c>
-      <c r="M134" s="50" t="s">
-        <v>330</v>
       </c>
       <c r="N134" s="50">
         <v>6</v>
@@ -13969,7 +13966,7 @@
         <v>34620</v>
       </c>
       <c r="D135" s="50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E135" s="50">
         <v>4</v>
@@ -13987,7 +13984,7 @@
         <v>66</v>
       </c>
       <c r="K135" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L135" s="50" t="s">
         <v>1</v>
@@ -14053,7 +14050,7 @@
         <v>34621</v>
       </c>
       <c r="D136" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E136" s="50">
         <v>54</v>
@@ -14137,7 +14134,7 @@
         <v>34629</v>
       </c>
       <c r="D137" s="50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E137" s="50">
         <v>4</v>
@@ -14155,7 +14152,7 @@
         <v>66</v>
       </c>
       <c r="K137" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L137" s="50" t="s">
         <v>1</v>
@@ -14221,7 +14218,7 @@
         <v>34630</v>
       </c>
       <c r="D138" s="50" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E138" s="50">
         <v>5</v>
@@ -14305,7 +14302,7 @@
         <v>34631</v>
       </c>
       <c r="D139" s="50" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E139" s="50">
         <v>19</v>
@@ -14323,7 +14320,7 @@
         <v>66</v>
       </c>
       <c r="K139" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L139" s="50" t="s">
         <v>1</v>
@@ -14389,7 +14386,7 @@
         <v>34633</v>
       </c>
       <c r="D140" s="50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E140" s="50">
         <v>43</v>
@@ -14410,7 +14407,7 @@
         <v>92</v>
       </c>
       <c r="L140" s="50" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M140" s="50" t="s">
         <v>1</v>
@@ -14473,7 +14470,7 @@
         <v>34634</v>
       </c>
       <c r="D141" s="50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E141" s="50">
         <v>5</v>
@@ -14491,7 +14488,7 @@
         <v>66</v>
       </c>
       <c r="K141" s="50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L141" s="50" t="s">
         <v>1</v>
@@ -14557,7 +14554,7 @@
         <v>34636</v>
       </c>
       <c r="D142" s="50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E142" s="50">
         <v>4</v>
@@ -14575,7 +14572,7 @@
         <v>66</v>
       </c>
       <c r="K142" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L142" s="50" t="s">
         <v>1</v>
@@ -14641,7 +14638,7 @@
         <v>34639</v>
       </c>
       <c r="D143" s="50" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E143" s="50">
         <v>16</v>
@@ -14659,10 +14656,10 @@
         <v>66</v>
       </c>
       <c r="K143" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="L143" s="50" t="s">
         <v>342</v>
-      </c>
-      <c r="L143" s="50" t="s">
-        <v>343</v>
       </c>
       <c r="M143" s="50" t="s">
         <v>1</v>
@@ -14725,7 +14722,7 @@
         <v>34640</v>
       </c>
       <c r="D144" s="50" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E144" s="50">
         <v>16</v>
@@ -14746,7 +14743,7 @@
         <v>80</v>
       </c>
       <c r="L144" s="50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M144" s="50" t="s">
         <v>1</v>
@@ -14809,7 +14806,7 @@
         <v>34641</v>
       </c>
       <c r="D145" s="50" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E145" s="50">
         <v>3</v>
@@ -14893,7 +14890,7 @@
         <v>34644</v>
       </c>
       <c r="D146" s="50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E146" s="50">
         <v>5</v>
@@ -14911,7 +14908,7 @@
         <v>66</v>
       </c>
       <c r="K146" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L146" s="50" t="s">
         <v>1</v>
@@ -14977,7 +14974,7 @@
         <v>34645</v>
       </c>
       <c r="D147" s="50" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E147" s="50">
         <v>3</v>
@@ -14995,7 +14992,7 @@
         <v>66</v>
       </c>
       <c r="K147" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L147" s="50" t="s">
         <v>1</v>
@@ -15061,7 +15058,7 @@
         <v>34649</v>
       </c>
       <c r="D148" s="50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E148" s="50">
         <v>5</v>
@@ -15079,7 +15076,7 @@
         <v>66</v>
       </c>
       <c r="K148" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L148" s="50" t="s">
         <v>1</v>
@@ -15145,7 +15142,7 @@
         <v>34676</v>
       </c>
       <c r="D149" s="50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E149" s="50">
         <v>16</v>
@@ -15154,7 +15151,7 @@
         <v>1</v>
       </c>
       <c r="G149" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I149" s="50" t="s">
         <v>79</v>
@@ -15163,10 +15160,10 @@
         <v>66</v>
       </c>
       <c r="K149" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L149" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M149" s="50" t="s">
         <v>1</v>
@@ -15229,7 +15226,7 @@
         <v>34686</v>
       </c>
       <c r="D150" s="50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E150" s="50">
         <v>18</v>
@@ -15247,7 +15244,7 @@
         <v>66</v>
       </c>
       <c r="K150" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L150" s="50" t="s">
         <v>1</v>
@@ -15313,7 +15310,7 @@
         <v>34688</v>
       </c>
       <c r="D151" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E151" s="50">
         <v>4</v>
@@ -15331,7 +15328,7 @@
         <v>66</v>
       </c>
       <c r="K151" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L151" s="50" t="s">
         <v>1</v>
@@ -15397,7 +15394,7 @@
         <v>34691</v>
       </c>
       <c r="D152" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E152" s="50">
         <v>5</v>
@@ -15415,7 +15412,7 @@
         <v>66</v>
       </c>
       <c r="K152" s="50" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L152" s="50" t="s">
         <v>1</v>
@@ -15481,7 +15478,7 @@
         <v>34692</v>
       </c>
       <c r="D153" s="50" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E153" s="50">
         <v>4</v>
@@ -15490,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="G153" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I153" s="50" t="s">
         <v>79</v>
@@ -15499,7 +15496,7 @@
         <v>66</v>
       </c>
       <c r="K153" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L153" s="50" t="s">
         <v>1</v>
@@ -15565,7 +15562,7 @@
         <v>34693</v>
       </c>
       <c r="D154" s="50" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E154" s="50">
         <v>13</v>
@@ -15586,7 +15583,7 @@
         <v>82</v>
       </c>
       <c r="L154" s="50" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M154" s="50" t="s">
         <v>1</v>
@@ -15649,7 +15646,7 @@
         <v>34694</v>
       </c>
       <c r="D155" s="50" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E155" s="50">
         <v>17</v>
@@ -15667,10 +15664,10 @@
         <v>66</v>
       </c>
       <c r="K155" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L155" s="50" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M155" s="50" t="s">
         <v>1</v>
@@ -15733,7 +15730,7 @@
         <v>34695</v>
       </c>
       <c r="D156" s="50" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E156" s="50">
         <v>5</v>
@@ -15751,7 +15748,7 @@
         <v>66</v>
       </c>
       <c r="K156" s="50" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L156" s="50" t="s">
         <v>1</v>
@@ -15817,7 +15814,7 @@
         <v>34718</v>
       </c>
       <c r="D157" s="50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E157" s="50">
         <v>30</v>
@@ -15826,7 +15823,7 @@
         <v>0</v>
       </c>
       <c r="G157" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I157" s="50" t="s">
         <v>79</v>
@@ -15835,10 +15832,10 @@
         <v>66</v>
       </c>
       <c r="K157" s="50" t="s">
+        <v>363</v>
+      </c>
+      <c r="L157" s="50" t="s">
         <v>364</v>
-      </c>
-      <c r="L157" s="50" t="s">
-        <v>365</v>
       </c>
       <c r="M157" s="50" t="s">
         <v>1</v>
@@ -15901,7 +15898,7 @@
         <v>34730</v>
       </c>
       <c r="D158" s="50" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E158" s="50">
         <v>2</v>
@@ -15926,7 +15923,7 @@
       </c>
       <c r="O158" s="50"/>
       <c r="P158" s="50" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q158" s="50"/>
       <c r="R158" s="50"/>
@@ -15952,7 +15949,7 @@
         <v>34732</v>
       </c>
       <c r="D159" s="50" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E159" s="50">
         <v>2</v>
@@ -15977,7 +15974,7 @@
       </c>
       <c r="O159" s="50"/>
       <c r="P159" s="50" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q159" s="50"/>
       <c r="R159" s="50"/>
@@ -16006,7 +16003,7 @@
         <v>34733</v>
       </c>
       <c r="D160" s="50" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E160" s="50">
         <v>2</v>
@@ -16031,7 +16028,7 @@
       </c>
       <c r="O160" s="50"/>
       <c r="P160" s="50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q160" s="50"/>
       <c r="R160" s="50"/>
@@ -16060,7 +16057,7 @@
         <v>34722</v>
       </c>
       <c r="D161" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E161" s="50">
         <v>31</v>
@@ -16078,7 +16075,7 @@
         <v>66</v>
       </c>
       <c r="K161" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L161" s="50" t="s">
         <v>1</v>
@@ -16144,7 +16141,7 @@
         <v>34734</v>
       </c>
       <c r="D162" s="50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E162" s="50">
         <v>57</v>
@@ -16162,13 +16159,13 @@
         <v>66</v>
       </c>
       <c r="K162" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="L162" s="50" t="s">
         <v>375</v>
       </c>
-      <c r="L162" s="50" t="s">
+      <c r="M162" s="50" t="s">
         <v>376</v>
-      </c>
-      <c r="M162" s="50" t="s">
-        <v>377</v>
       </c>
       <c r="N162" s="50">
         <v>6</v>
@@ -16228,7 +16225,7 @@
         <v>34735</v>
       </c>
       <c r="D163" s="50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E163" s="50">
         <v>32</v>
@@ -16246,7 +16243,7 @@
         <v>66</v>
       </c>
       <c r="K163" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L163" s="50" t="s">
         <v>1</v>
@@ -16312,7 +16309,7 @@
         <v>34736</v>
       </c>
       <c r="D164" s="50" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E164" s="50">
         <v>15</v>
@@ -16330,7 +16327,7 @@
         <v>66</v>
       </c>
       <c r="K164" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L164" s="50" t="s">
         <v>1</v>
@@ -16396,7 +16393,7 @@
         <v>34741</v>
       </c>
       <c r="D165" s="50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E165" s="50">
         <v>31</v>
@@ -16414,7 +16411,7 @@
         <v>66</v>
       </c>
       <c r="K165" s="50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L165" s="50" t="s">
         <v>1</v>
@@ -16480,7 +16477,7 @@
         <v>34745</v>
       </c>
       <c r="D166" s="50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E166" s="50">
         <v>31</v>
@@ -16489,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="G166" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I166" s="50" t="s">
         <v>79</v>
@@ -16498,7 +16495,7 @@
         <v>66</v>
       </c>
       <c r="K166" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L166" s="50" t="s">
         <v>1</v>
@@ -16564,7 +16561,7 @@
         <v>34746</v>
       </c>
       <c r="D167" s="50" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E167" s="50">
         <v>31</v>
@@ -16582,7 +16579,7 @@
         <v>66</v>
       </c>
       <c r="K167" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L167" s="50" t="s">
         <v>1</v>
@@ -16648,7 +16645,7 @@
         <v>34747</v>
       </c>
       <c r="D168" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E168" s="50">
         <v>31</v>
@@ -16666,7 +16663,7 @@
         <v>66</v>
       </c>
       <c r="K168" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L168" s="50" t="s">
         <v>1</v>
@@ -16732,7 +16729,7 @@
         <v>34748</v>
       </c>
       <c r="D169" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E169" s="50">
         <v>31</v>
@@ -16750,7 +16747,7 @@
         <v>66</v>
       </c>
       <c r="K169" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L169" s="50" t="s">
         <v>1</v>
@@ -16816,7 +16813,7 @@
         <v>34749</v>
       </c>
       <c r="D170" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E170" s="50">
         <v>31</v>
@@ -16834,7 +16831,7 @@
         <v>66</v>
       </c>
       <c r="K170" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L170" s="50" t="s">
         <v>1</v>
@@ -16900,7 +16897,7 @@
         <v>34750</v>
       </c>
       <c r="D171" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E171" s="50">
         <v>31</v>
@@ -16909,7 +16906,7 @@
         <v>2</v>
       </c>
       <c r="G171" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I171" s="50" t="s">
         <v>79</v>
@@ -16918,7 +16915,7 @@
         <v>66</v>
       </c>
       <c r="K171" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L171" s="50" t="s">
         <v>1</v>
@@ -16984,7 +16981,7 @@
         <v>34751</v>
       </c>
       <c r="D172" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E172" s="50">
         <v>31</v>
@@ -16993,7 +16990,7 @@
         <v>2</v>
       </c>
       <c r="G172" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I172" s="50" t="s">
         <v>79</v>
@@ -17002,7 +16999,7 @@
         <v>66</v>
       </c>
       <c r="K172" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L172" s="50" t="s">
         <v>1</v>
@@ -17068,7 +17065,7 @@
         <v>34752</v>
       </c>
       <c r="D173" s="50" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E173" s="50">
         <v>31</v>
@@ -17086,7 +17083,7 @@
         <v>66</v>
       </c>
       <c r="K173" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L173" s="50" t="s">
         <v>1</v>
@@ -17152,7 +17149,7 @@
         <v>34753</v>
       </c>
       <c r="D174" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E174" s="50">
         <v>31</v>
@@ -17170,7 +17167,7 @@
         <v>66</v>
       </c>
       <c r="K174" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L174" s="50" t="s">
         <v>1</v>
@@ -17236,7 +17233,7 @@
         <v>34754</v>
       </c>
       <c r="D175" s="50" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E175" s="50">
         <v>31</v>
@@ -17254,7 +17251,7 @@
         <v>66</v>
       </c>
       <c r="K175" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L175" s="50" t="s">
         <v>1</v>
@@ -17320,7 +17317,7 @@
         <v>34757</v>
       </c>
       <c r="D176" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E176" s="50">
         <v>31</v>
@@ -17329,7 +17326,7 @@
         <v>3</v>
       </c>
       <c r="G176" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I176" s="50" t="s">
         <v>79</v>
@@ -17338,7 +17335,7 @@
         <v>66</v>
       </c>
       <c r="K176" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L176" s="50" t="s">
         <v>1</v>
@@ -17404,7 +17401,7 @@
         <v>34759</v>
       </c>
       <c r="D177" s="50" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E177" s="50">
         <v>31</v>
@@ -17422,7 +17419,7 @@
         <v>66</v>
       </c>
       <c r="K177" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L177" s="50" t="s">
         <v>1</v>
@@ -17488,7 +17485,7 @@
         <v>34760</v>
       </c>
       <c r="D178" s="50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E178" s="50">
         <v>32</v>
@@ -17506,7 +17503,7 @@
         <v>66</v>
       </c>
       <c r="K178" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L178" s="50" t="s">
         <v>1</v>
@@ -17572,7 +17569,7 @@
         <v>34764</v>
       </c>
       <c r="D179" s="50" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E179" s="50">
         <v>32</v>
@@ -17581,7 +17578,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I179" s="50" t="s">
         <v>79</v>
@@ -17590,7 +17587,7 @@
         <v>66</v>
       </c>
       <c r="K179" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L179" s="50" t="s">
         <v>1</v>
@@ -17656,7 +17653,7 @@
         <v>34765</v>
       </c>
       <c r="D180" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E180" s="50">
         <v>57</v>
@@ -17674,13 +17671,13 @@
         <v>66</v>
       </c>
       <c r="K180" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L180" s="50" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M180" s="50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N180" s="50">
         <v>6</v>
@@ -17740,7 +17737,7 @@
         <v>34766</v>
       </c>
       <c r="D181" s="50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E181" s="50">
         <v>57</v>
@@ -17749,7 +17746,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I181" s="50" t="s">
         <v>65</v>
@@ -17758,13 +17755,13 @@
         <v>66</v>
       </c>
       <c r="K181" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L181" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M181" s="50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N181" s="50">
         <v>6</v>
@@ -17824,7 +17821,7 @@
         <v>34768</v>
       </c>
       <c r="D182" s="50" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E182" s="50">
         <v>31</v>
@@ -17833,7 +17830,7 @@
         <v>2</v>
       </c>
       <c r="G182" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I182" s="50" t="s">
         <v>79</v>
@@ -17842,7 +17839,7 @@
         <v>66</v>
       </c>
       <c r="K182" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L182" s="50" t="s">
         <v>1</v>
@@ -17908,7 +17905,7 @@
         <v>34769</v>
       </c>
       <c r="D183" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E183" s="50">
         <v>15</v>
@@ -17926,7 +17923,7 @@
         <v>66</v>
       </c>
       <c r="K183" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L183" s="50" t="s">
         <v>1</v>
@@ -17992,7 +17989,7 @@
         <v>34772</v>
       </c>
       <c r="D184" s="50" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E184" s="50">
         <v>15</v>
@@ -18010,7 +18007,7 @@
         <v>66</v>
       </c>
       <c r="K184" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L184" s="50" t="s">
         <v>1</v>
@@ -18076,7 +18073,7 @@
         <v>34773</v>
       </c>
       <c r="D185" s="50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E185" s="50">
         <v>15</v>
@@ -18094,7 +18091,7 @@
         <v>66</v>
       </c>
       <c r="K185" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L185" s="50" t="s">
         <v>1</v>
@@ -18160,7 +18157,7 @@
         <v>34774</v>
       </c>
       <c r="D186" s="50" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E186" s="50">
         <v>15</v>
@@ -18178,7 +18175,7 @@
         <v>66</v>
       </c>
       <c r="K186" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L186" s="50" t="s">
         <v>1</v>
@@ -18244,7 +18241,7 @@
         <v>74804</v>
       </c>
       <c r="D187" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E187" s="50">
         <v>12</v>
@@ -18328,7 +18325,7 @@
         <v>74805</v>
       </c>
       <c r="D188" s="50" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E188" s="50">
         <v>16</v>
@@ -18340,7 +18337,7 @@
         <v>98</v>
       </c>
       <c r="H188" s="50" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I188" s="50" t="s">
         <v>79</v>
@@ -18349,10 +18346,10 @@
         <v>66</v>
       </c>
       <c r="K188" s="50" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L188" s="50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M188" s="50" t="s">
         <v>1</v>
@@ -18415,7 +18412,7 @@
         <v>74806</v>
       </c>
       <c r="D189" s="50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E189" s="50">
         <v>5</v>
@@ -18427,7 +18424,7 @@
         <v>64</v>
       </c>
       <c r="H189" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I189" s="50" t="s">
         <v>79</v>
@@ -18436,7 +18433,7 @@
         <v>66</v>
       </c>
       <c r="K189" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L189" s="50" t="s">
         <v>1</v>
@@ -18502,7 +18499,7 @@
         <v>74807</v>
       </c>
       <c r="D190" s="50" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E190" s="50">
         <v>3</v>
@@ -18514,7 +18511,7 @@
         <v>64</v>
       </c>
       <c r="H190" s="50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I190" s="50" t="s">
         <v>79</v>
@@ -18523,7 +18520,7 @@
         <v>66</v>
       </c>
       <c r="K190" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L190" s="50" t="s">
         <v>1</v>
@@ -18589,7 +18586,7 @@
         <v>74808</v>
       </c>
       <c r="D191" s="50" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E191" s="50">
         <v>14</v>
@@ -18610,7 +18607,7 @@
         <v>82</v>
       </c>
       <c r="L191" s="50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M191" s="50" t="s">
         <v>1</v>
@@ -18673,7 +18670,7 @@
         <v>74809</v>
       </c>
       <c r="D192" s="50" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E192" s="50">
         <v>4</v>
@@ -18685,7 +18682,7 @@
         <v>84</v>
       </c>
       <c r="H192" s="50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I192" s="50" t="s">
         <v>79</v>
@@ -18694,7 +18691,7 @@
         <v>66</v>
       </c>
       <c r="K192" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L192" s="50" t="s">
         <v>1</v>
@@ -18760,7 +18757,7 @@
         <v>74810</v>
       </c>
       <c r="D193" s="50" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E193" s="50">
         <v>7</v>
@@ -18772,7 +18769,7 @@
         <v>98</v>
       </c>
       <c r="H193" s="50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I193" s="50" t="s">
         <v>79</v>
@@ -18781,10 +18778,10 @@
         <v>66</v>
       </c>
       <c r="K193" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L193" s="50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M193" s="50" t="s">
         <v>1</v>
@@ -18847,7 +18844,7 @@
         <v>74811</v>
       </c>
       <c r="D194" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E194" s="50">
         <v>7</v>
@@ -18859,7 +18856,7 @@
         <v>98</v>
       </c>
       <c r="H194" s="50" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I194" s="50" t="s">
         <v>79</v>
@@ -18868,10 +18865,10 @@
         <v>66</v>
       </c>
       <c r="K194" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L194" s="50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M194" s="50" t="s">
         <v>1</v>
@@ -18934,7 +18931,7 @@
         <v>74812</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E195" s="50">
         <v>7</v>
@@ -18946,7 +18943,7 @@
         <v>98</v>
       </c>
       <c r="H195" s="50" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I195" s="50" t="s">
         <v>79</v>
@@ -18955,10 +18952,10 @@
         <v>66</v>
       </c>
       <c r="K195" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L195" s="50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M195" s="50" t="s">
         <v>1</v>
@@ -19021,7 +19018,7 @@
         <v>74813</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E196" s="50">
         <v>6</v>
@@ -19030,10 +19027,10 @@
         <v>0</v>
       </c>
       <c r="G196" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H196" s="50" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I196" s="50" t="s">
         <v>79</v>
@@ -19042,13 +19039,13 @@
         <v>66</v>
       </c>
       <c r="K196" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L196" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M196" s="50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N196" s="50">
         <v>7</v>
@@ -19108,7 +19105,7 @@
         <v>74814</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E197" s="50">
         <v>16</v>
@@ -19120,7 +19117,7 @@
         <v>64</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I197" s="50" t="s">
         <v>79</v>
@@ -19129,10 +19126,10 @@
         <v>66</v>
       </c>
       <c r="K197" s="50" t="s">
+        <v>433</v>
+      </c>
+      <c r="L197" s="50" t="s">
         <v>434</v>
-      </c>
-      <c r="L197" s="50" t="s">
-        <v>435</v>
       </c>
       <c r="M197" s="50" t="s">
         <v>1</v>
@@ -19195,7 +19192,7 @@
         <v>74815</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E198" s="50">
         <v>5</v>
@@ -19207,7 +19204,7 @@
         <v>64</v>
       </c>
       <c r="H198" s="50" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I198" s="50" t="s">
         <v>79</v>
@@ -19216,7 +19213,7 @@
         <v>66</v>
       </c>
       <c r="K198" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L198" s="50" t="s">
         <v>1</v>
@@ -19282,7 +19279,7 @@
         <v>74816</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E199" s="50">
         <v>5</v>
@@ -19291,10 +19288,10 @@
         <v>1</v>
       </c>
       <c r="G199" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I199" s="50" t="s">
         <v>79</v>
@@ -19369,7 +19366,7 @@
         <v>74817</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E200" s="50">
         <v>53</v>
@@ -19381,7 +19378,7 @@
         <v>64</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I200" s="50" t="s">
         <v>79</v>
@@ -19390,7 +19387,7 @@
         <v>66</v>
       </c>
       <c r="K200" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L200" s="50" t="s">
         <v>1</v>
@@ -19456,7 +19453,7 @@
         <v>74818</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E201" s="50">
         <v>55</v>
@@ -19468,7 +19465,7 @@
         <v>84</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I201" s="50" t="s">
         <v>79</v>
@@ -19477,10 +19474,10 @@
         <v>66</v>
       </c>
       <c r="K201" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L201" s="50" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M201" s="50" t="s">
         <v>1</v>
@@ -19543,7 +19540,7 @@
         <v>74819</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E202" s="50">
         <v>5</v>
@@ -19555,7 +19552,7 @@
         <v>84</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>79</v>
@@ -19564,7 +19561,7 @@
         <v>66</v>
       </c>
       <c r="K202" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L202" s="50" t="s">
         <v>1</v>
@@ -19630,7 +19627,7 @@
         <v>74820</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E203" s="50">
         <v>3</v>
@@ -19642,7 +19639,7 @@
         <v>64</v>
       </c>
       <c r="H203" s="50" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I203" s="50" t="s">
         <v>79</v>
@@ -19651,7 +19648,7 @@
         <v>66</v>
       </c>
       <c r="K203" s="50" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L203" s="50" t="s">
         <v>1</v>
@@ -19717,7 +19714,7 @@
         <v>74821</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E204" s="50">
         <v>5</v>
@@ -19729,7 +19726,7 @@
         <v>84</v>
       </c>
       <c r="H204" s="50" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I204" s="50" t="s">
         <v>79</v>
@@ -19738,7 +19735,7 @@
         <v>66</v>
       </c>
       <c r="K204" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L204" s="50" t="s">
         <v>1</v>
@@ -19804,7 +19801,7 @@
         <v>74822</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E205" s="50">
         <v>4</v>
@@ -19816,7 +19813,7 @@
         <v>84</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>79</v>
@@ -19825,7 +19822,7 @@
         <v>66</v>
       </c>
       <c r="K205" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L205" s="50" t="s">
         <v>1</v>
@@ -19891,7 +19888,7 @@
         <v>74823</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E206" s="50">
         <v>50</v>
@@ -19903,7 +19900,7 @@
         <v>64</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I206" s="50" t="s">
         <v>79</v>
@@ -19912,7 +19909,7 @@
         <v>66</v>
       </c>
       <c r="K206" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L206" s="50" t="s">
         <v>1</v>
@@ -19978,7 +19975,7 @@
         <v>74824</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E207" s="50">
         <v>49</v>
@@ -19990,7 +19987,7 @@
         <v>64</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>79</v>
@@ -19999,10 +19996,10 @@
         <v>66</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L207" s="50" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M207" s="50" t="s">
         <v>1</v>
@@ -20065,7 +20062,7 @@
         <v>74825</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E208" s="50">
         <v>48</v>
@@ -20077,7 +20074,7 @@
         <v>84</v>
       </c>
       <c r="H208" s="50" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I208" s="50" t="s">
         <v>79</v>
@@ -20086,13 +20083,13 @@
         <v>66</v>
       </c>
       <c r="K208" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L208" s="50" t="s">
+        <v>460</v>
+      </c>
+      <c r="M208" s="50" t="s">
         <v>461</v>
-      </c>
-      <c r="M208" s="50" t="s">
-        <v>462</v>
       </c>
       <c r="N208" s="50">
         <v>7</v>
@@ -20152,7 +20149,7 @@
         <v>74826</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E209" s="50">
         <v>5</v>
@@ -20164,7 +20161,7 @@
         <v>98</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>79</v>
@@ -20173,7 +20170,7 @@
         <v>66</v>
       </c>
       <c r="K209" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L209" s="50" t="s">
         <v>1</v>
@@ -20239,7 +20236,7 @@
         <v>74827</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E210" s="50">
         <v>4</v>
@@ -20248,10 +20245,10 @@
         <v>2</v>
       </c>
       <c r="G210" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>79</v>
@@ -20260,7 +20257,7 @@
         <v>66</v>
       </c>
       <c r="K210" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L210" s="50" t="s">
         <v>1</v>
@@ -20326,7 +20323,7 @@
         <v>74828</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E211" s="50">
         <v>5</v>
@@ -20338,7 +20335,7 @@
         <v>84</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>79</v>
@@ -20347,7 +20344,7 @@
         <v>66</v>
       </c>
       <c r="K211" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L211" s="50" t="s">
         <v>1</v>
@@ -20413,7 +20410,7 @@
         <v>74829</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E212" s="50">
         <v>4</v>
@@ -20425,7 +20422,7 @@
         <v>84</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>79</v>
@@ -20434,7 +20431,7 @@
         <v>66</v>
       </c>
       <c r="K212" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L212" s="50" t="s">
         <v>1</v>
@@ -20500,7 +20497,7 @@
         <v>74830</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E213" s="50">
         <v>31</v>
@@ -20512,7 +20509,7 @@
         <v>84</v>
       </c>
       <c r="H213" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I213" s="50" t="s">
         <v>79</v>
@@ -20521,7 +20518,7 @@
         <v>66</v>
       </c>
       <c r="K213" s="50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L213" s="50" t="s">
         <v>1</v>
@@ -20587,7 +20584,7 @@
         <v>74831</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E214" s="50">
         <v>31</v>
@@ -20596,10 +20593,10 @@
         <v>1</v>
       </c>
       <c r="G214" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>79</v>
@@ -20608,7 +20605,7 @@
         <v>66</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L214" s="50" t="s">
         <v>1</v>
@@ -20674,7 +20671,7 @@
         <v>74832</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E215" s="50">
         <v>57</v>
@@ -20683,10 +20680,10 @@
         <v>1</v>
       </c>
       <c r="G215" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H215" s="50" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I215" s="50" t="s">
         <v>65</v>
@@ -20695,13 +20692,13 @@
         <v>66</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L215" s="50" t="s">
+        <v>476</v>
+      </c>
+      <c r="M215" s="50" t="s">
         <v>477</v>
-      </c>
-      <c r="M215" s="50" t="s">
-        <v>478</v>
       </c>
       <c r="N215" s="50">
         <v>7</v>
@@ -20761,7 +20758,7 @@
         <v>74833</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E216" s="50">
         <v>32</v>
@@ -20770,10 +20767,10 @@
         <v>1</v>
       </c>
       <c r="G216" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>79</v>
@@ -20782,7 +20779,7 @@
         <v>66</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L216" s="50" t="s">
         <v>1</v>
@@ -20848,7 +20845,7 @@
         <v>74834</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E217" s="50">
         <v>31</v>
@@ -20857,10 +20854,10 @@
         <v>2</v>
       </c>
       <c r="G217" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H217" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I217" s="50" t="s">
         <v>79</v>
@@ -20869,7 +20866,7 @@
         <v>66</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L217" s="50" t="s">
         <v>1</v>
@@ -20935,7 +20932,7 @@
         <v>74835</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E218" s="50">
         <v>31</v>
@@ -20947,7 +20944,7 @@
         <v>84</v>
       </c>
       <c r="H218" s="50" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I218" s="50" t="s">
         <v>79</v>
@@ -20956,7 +20953,7 @@
         <v>66</v>
       </c>
       <c r="K218" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L218" s="50" t="s">
         <v>1</v>
@@ -21022,7 +21019,7 @@
         <v>74836</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E219" s="50">
         <v>31</v>
@@ -21034,7 +21031,7 @@
         <v>64</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>79</v>
@@ -21043,7 +21040,7 @@
         <v>66</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -21109,7 +21106,7 @@
         <v>74837</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E220" s="50">
         <v>57</v>
@@ -21121,7 +21118,7 @@
         <v>64</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>65</v>
@@ -21130,13 +21127,13 @@
         <v>66</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L220" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M220" s="50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N220" s="50">
         <v>7</v>
@@ -21196,7 +21193,7 @@
         <v>74838</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E221" s="50">
         <v>32</v>
@@ -21208,7 +21205,7 @@
         <v>64</v>
       </c>
       <c r="H221" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I221" s="50" t="s">
         <v>79</v>
@@ -21217,7 +21214,7 @@
         <v>66</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -21283,7 +21280,7 @@
         <v>74839</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E222" s="50">
         <v>31</v>
@@ -21295,7 +21292,7 @@
         <v>64</v>
       </c>
       <c r="H222" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I222" s="50" t="s">
         <v>79</v>
@@ -21304,7 +21301,7 @@
         <v>66</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -21370,7 +21367,7 @@
         <v>74840</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E223" s="50">
         <v>31</v>
@@ -21382,7 +21379,7 @@
         <v>98</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>79</v>
@@ -21391,7 +21388,7 @@
         <v>66</v>
       </c>
       <c r="K223" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L223" s="50" t="s">
         <v>1</v>
@@ -21457,7 +21454,7 @@
         <v>74841</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E224" s="50">
         <v>31</v>
@@ -21466,10 +21463,10 @@
         <v>2</v>
       </c>
       <c r="G224" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>79</v>
@@ -21478,7 +21475,7 @@
         <v>66</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L224" s="50" t="s">
         <v>1</v>
@@ -21544,7 +21541,7 @@
         <v>74842</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E225" s="50">
         <v>31</v>
@@ -21553,10 +21550,10 @@
         <v>1</v>
       </c>
       <c r="G225" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>79</v>
@@ -21565,7 +21562,7 @@
         <v>66</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L225" s="50" t="s">
         <v>1</v>
@@ -21631,7 +21628,7 @@
         <v>74843</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E226" s="50">
         <v>31</v>
@@ -21643,7 +21640,7 @@
         <v>64</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>79</v>
@@ -21652,7 +21649,7 @@
         <v>66</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L226" s="50" t="s">
         <v>1</v>
@@ -21718,7 +21715,7 @@
         <v>74844</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E227" s="50">
         <v>31</v>
@@ -21730,7 +21727,7 @@
         <v>64</v>
       </c>
       <c r="H227" s="50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I227" s="50" t="s">
         <v>79</v>
@@ -21739,7 +21736,7 @@
         <v>66</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L227" s="50" t="s">
         <v>1</v>
@@ -21805,7 +21802,7 @@
         <v>74845</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E228" s="50">
         <v>15</v>
@@ -21817,7 +21814,7 @@
         <v>64</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>79</v>
@@ -21826,7 +21823,7 @@
         <v>66</v>
       </c>
       <c r="K228" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L228" s="50" t="s">
         <v>1</v>
@@ -21892,7 +21889,7 @@
         <v>74846</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E229" s="50">
         <v>15</v>
@@ -21904,7 +21901,7 @@
         <v>64</v>
       </c>
       <c r="H229" s="50" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I229" s="50" t="s">
         <v>79</v>
@@ -21913,7 +21910,7 @@
         <v>66</v>
       </c>
       <c r="K229" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L229" s="50" t="s">
         <v>1</v>
@@ -21979,7 +21976,7 @@
         <v>74847</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E230" s="50">
         <v>15</v>
@@ -21991,7 +21988,7 @@
         <v>64</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I230" s="50" t="s">
         <v>79</v>
@@ -22000,7 +21997,7 @@
         <v>66</v>
       </c>
       <c r="K230" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L230" s="50" t="s">
         <v>1</v>
@@ -22066,7 +22063,7 @@
         <v>74848</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E231" s="50">
         <v>15</v>
@@ -22078,7 +22075,7 @@
         <v>64</v>
       </c>
       <c r="H231" s="50" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I231" s="50" t="s">
         <v>79</v>
@@ -22087,7 +22084,7 @@
         <v>66</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -22153,7 +22150,7 @@
         <v>74849</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E232" s="50">
         <v>30</v>
@@ -22165,7 +22162,7 @@
         <v>84</v>
       </c>
       <c r="H232" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I232" s="50" t="s">
         <v>79</v>
@@ -22174,10 +22171,10 @@
         <v>66</v>
       </c>
       <c r="K232" s="50" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L232" s="50" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M232" s="50" t="s">
         <v>1</v>
@@ -22240,7 +22237,7 @@
         <v>74850</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E233" s="50">
         <v>2</v>
@@ -22265,7 +22262,7 @@
       </c>
       <c r="O233" s="50"/>
       <c r="P233" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q233" s="50"/>
       <c r="R233" s="50"/>
@@ -22294,7 +22291,7 @@
         <v>74851</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E234" s="50">
         <v>2</v>
@@ -22319,7 +22316,7 @@
       </c>
       <c r="O234" s="50"/>
       <c r="P234" s="50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q234" s="50"/>
       <c r="R234" s="50"/>
@@ -22348,7 +22345,7 @@
         <v>84928</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E235" s="50">
         <v>12</v>
@@ -22432,7 +22429,7 @@
         <v>84929</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E236" s="50">
         <v>30</v>
@@ -22444,7 +22441,7 @@
         <v>84</v>
       </c>
       <c r="H236" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I236" s="50" t="s">
         <v>79</v>
@@ -22453,10 +22450,10 @@
         <v>66</v>
       </c>
       <c r="K236" s="50" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L236" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M236" s="50" t="s">
         <v>1</v>
@@ -22519,7 +22516,7 @@
         <v>84930</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E237" s="50">
         <v>57</v>
@@ -22528,7 +22525,7 @@
         <v>1</v>
       </c>
       <c r="G237" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I237" s="50" t="s">
         <v>65</v>
@@ -22537,13 +22534,13 @@
         <v>66</v>
       </c>
       <c r="K237" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L237" s="50" t="s">
+        <v>523</v>
+      </c>
+      <c r="M237" s="50" t="s">
         <v>524</v>
-      </c>
-      <c r="M237" s="50" t="s">
-        <v>525</v>
       </c>
       <c r="N237" s="50">
         <v>8</v>
@@ -22603,7 +22600,7 @@
         <v>84931</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E238" s="50">
         <v>32</v>
@@ -22612,10 +22609,10 @@
         <v>1</v>
       </c>
       <c r="G238" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H238" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I238" s="50" t="s">
         <v>79</v>
@@ -22624,7 +22621,7 @@
         <v>66</v>
       </c>
       <c r="K238" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L238" s="50" t="s">
         <v>1</v>
@@ -22690,7 +22687,7 @@
         <v>84932</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E239" s="50">
         <v>57</v>
@@ -22708,13 +22705,13 @@
         <v>66</v>
       </c>
       <c r="K239" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L239" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M239" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N239" s="50">
         <v>8</v>
@@ -22774,7 +22771,7 @@
         <v>84933</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E240" s="50">
         <v>32</v>
@@ -22786,7 +22783,7 @@
         <v>64</v>
       </c>
       <c r="H240" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I240" s="50" t="s">
         <v>79</v>
@@ -22795,7 +22792,7 @@
         <v>66</v>
       </c>
       <c r="K240" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L240" s="50" t="s">
         <v>1</v>
@@ -22861,7 +22858,7 @@
         <v>84934</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E241" s="50">
         <v>31</v>
@@ -22870,10 +22867,10 @@
         <v>1</v>
       </c>
       <c r="G241" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H241" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I241" s="50" t="s">
         <v>79</v>
@@ -22882,7 +22879,7 @@
         <v>66</v>
       </c>
       <c r="K241" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L241" s="50" t="s">
         <v>1</v>
@@ -22948,7 +22945,7 @@
         <v>84935</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E242" s="50">
         <v>31</v>
@@ -22960,7 +22957,7 @@
         <v>64</v>
       </c>
       <c r="H242" s="50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I242" s="50" t="s">
         <v>79</v>
@@ -22969,7 +22966,7 @@
         <v>66</v>
       </c>
       <c r="K242" s="50" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L242" s="50" t="s">
         <v>1</v>
@@ -23035,7 +23032,7 @@
         <v>84936</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E243" s="50">
         <v>31</v>
@@ -23047,7 +23044,7 @@
         <v>64</v>
       </c>
       <c r="H243" s="50" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I243" s="50" t="s">
         <v>79</v>
@@ -23056,7 +23053,7 @@
         <v>66</v>
       </c>
       <c r="K243" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L243" s="50" t="s">
         <v>1</v>
@@ -23122,7 +23119,7 @@
         <v>84937</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E244" s="50">
         <v>31</v>
@@ -23131,10 +23128,10 @@
         <v>4</v>
       </c>
       <c r="G244" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H244" s="50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I244" s="50" t="s">
         <v>79</v>
@@ -23143,7 +23140,7 @@
         <v>66</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L244" s="50" t="s">
         <v>1</v>
@@ -23209,7 +23206,7 @@
         <v>84938</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E245" s="50">
         <v>31</v>
@@ -23221,7 +23218,7 @@
         <v>64</v>
       </c>
       <c r="H245" s="50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I245" s="50" t="s">
         <v>79</v>
@@ -23230,7 +23227,7 @@
         <v>66</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
@@ -23296,7 +23293,7 @@
         <v>84939</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E246" s="50">
         <v>15</v>
@@ -23308,7 +23305,7 @@
         <v>64</v>
       </c>
       <c r="H246" s="50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I246" s="50" t="s">
         <v>79</v>
@@ -23317,7 +23314,7 @@
         <v>66</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
@@ -23383,7 +23380,7 @@
         <v>84940</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E247" s="50">
         <v>15</v>
@@ -23395,7 +23392,7 @@
         <v>64</v>
       </c>
       <c r="H247" s="50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I247" s="50" t="s">
         <v>79</v>
@@ -23404,7 +23401,7 @@
         <v>66</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
@@ -23470,7 +23467,7 @@
         <v>84941</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E248" s="50">
         <v>16</v>
@@ -23482,7 +23479,7 @@
         <v>64</v>
       </c>
       <c r="H248" s="50" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I248" s="50" t="s">
         <v>79</v>
@@ -23491,10 +23488,10 @@
         <v>66</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L248" s="50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M248" s="50" t="s">
         <v>1</v>
@@ -23557,7 +23554,7 @@
         <v>84942</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E249" s="50">
         <v>52</v>
@@ -23575,13 +23572,13 @@
         <v>66</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L249" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="M249" s="50" t="s">
         <v>550</v>
-      </c>
-      <c r="M249" s="50" t="s">
-        <v>551</v>
       </c>
       <c r="N249" s="50">
         <v>8</v>
@@ -23641,7 +23638,7 @@
         <v>84943</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E250" s="50">
         <v>51</v>
@@ -23653,7 +23650,7 @@
         <v>64</v>
       </c>
       <c r="H250" s="50" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>79</v>
@@ -23662,7 +23659,7 @@
         <v>66</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
@@ -23728,7 +23725,7 @@
         <v>84944</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E251" s="50">
         <v>52</v>
@@ -23746,13 +23743,13 @@
         <v>66</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L251" s="50" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="M251" s="50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N251" s="50">
         <v>8</v>
@@ -23812,7 +23809,7 @@
         <v>84945</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E252" s="50">
         <v>51</v>
@@ -23824,7 +23821,7 @@
         <v>64</v>
       </c>
       <c r="H252" s="50" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I252" s="50" t="s">
         <v>79</v>
@@ -23833,7 +23830,7 @@
         <v>66</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L252" s="50" t="s">
         <v>1</v>
@@ -23899,7 +23896,7 @@
         <v>84946</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E253" s="50">
         <v>56</v>
@@ -23917,7 +23914,7 @@
         <v>66</v>
       </c>
       <c r="K253" s="50" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L253" s="50" t="s">
         <v>1</v>
@@ -23983,7 +23980,7 @@
         <v>84947</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E254" s="50">
         <v>56</v>
@@ -24001,7 +23998,7 @@
         <v>66</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -24067,7 +24064,7 @@
         <v>84948</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E255" s="50">
         <v>56</v>
@@ -24085,7 +24082,7 @@
         <v>66</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L255" s="50" t="s">
         <v>1</v>
@@ -24151,7 +24148,7 @@
         <v>84949</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E256" s="50">
         <v>56</v>
@@ -24169,7 +24166,7 @@
         <v>66</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L256" s="50" t="s">
         <v>1</v>
@@ -24235,7 +24232,7 @@
         <v>84950</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E257" s="50">
         <v>56</v>
@@ -24253,7 +24250,7 @@
         <v>66</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
@@ -24319,7 +24316,7 @@
         <v>84951</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E258" s="50">
         <v>56</v>
@@ -24337,7 +24334,7 @@
         <v>66</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L258" s="50" t="s">
         <v>1</v>
@@ -24403,7 +24400,7 @@
         <v>84952</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E259" s="50">
         <v>56</v>
@@ -24421,7 +24418,7 @@
         <v>66</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L259" s="50" t="s">
         <v>1</v>
@@ -24487,7 +24484,7 @@
         <v>84953</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E260" s="50">
         <v>56</v>
@@ -24505,7 +24502,7 @@
         <v>66</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L260" s="50" t="s">
         <v>1</v>
@@ -24571,7 +24568,7 @@
         <v>84954</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E261" s="50">
         <v>56</v>
@@ -24589,7 +24586,7 @@
         <v>66</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L261" s="50" t="s">
         <v>1</v>
@@ -24655,7 +24652,7 @@
         <v>84955</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E262" s="50">
         <v>56</v>
@@ -24673,7 +24670,7 @@
         <v>66</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L262" s="50" t="s">
         <v>1</v>
@@ -24739,7 +24736,7 @@
         <v>84956</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E263" s="50">
         <v>56</v>
@@ -24757,7 +24754,7 @@
         <v>66</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L263" s="50" t="s">
         <v>1</v>
@@ -24823,7 +24820,7 @@
         <v>84957</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E264" s="50">
         <v>56</v>
@@ -24841,7 +24838,7 @@
         <v>66</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L264" s="50" t="s">
         <v>1</v>
@@ -24907,7 +24904,7 @@
         <v>84958</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E265" s="50">
         <v>56</v>
@@ -24925,7 +24922,7 @@
         <v>66</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L265" s="50" t="s">
         <v>1</v>
@@ -24991,7 +24988,7 @@
         <v>84959</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E266" s="50">
         <v>56</v>
@@ -25009,7 +25006,7 @@
         <v>66</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -25075,7 +25072,7 @@
         <v>84960</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E267" s="50">
         <v>56</v>
@@ -25093,7 +25090,7 @@
         <v>66</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -25159,7 +25156,7 @@
         <v>84961</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E268" s="50">
         <v>56</v>
@@ -25177,7 +25174,7 @@
         <v>66</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -25243,7 +25240,7 @@
         <v>84962</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E269" s="50">
         <v>56</v>
@@ -25261,7 +25258,7 @@
         <v>66</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -25327,7 +25324,7 @@
         <v>84963</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E270" s="50">
         <v>56</v>
@@ -25345,7 +25342,7 @@
         <v>66</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
@@ -25411,7 +25408,7 @@
         <v>84964</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E271" s="50">
         <v>56</v>
@@ -25429,7 +25426,7 @@
         <v>66</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L271" s="50" t="s">
         <v>1</v>
@@ -25495,7 +25492,7 @@
         <v>84965</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E272" s="50">
         <v>56</v>
@@ -25513,7 +25510,7 @@
         <v>66</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L272" s="50" t="s">
         <v>1</v>
@@ -25579,7 +25576,7 @@
         <v>84966</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E273" s="50">
         <v>56</v>
@@ -25597,7 +25594,7 @@
         <v>66</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L273" s="50" t="s">
         <v>1</v>
@@ -25663,7 +25660,7 @@
         <v>84967</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E274" s="50">
         <v>56</v>
@@ -25681,7 +25678,7 @@
         <v>66</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L274" s="50" t="s">
         <v>1</v>
@@ -25747,7 +25744,7 @@
         <v>84968</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E275" s="50">
         <v>56</v>
@@ -25765,7 +25762,7 @@
         <v>66</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L275" s="50" t="s">
         <v>1</v>
@@ -25831,7 +25828,7 @@
         <v>84969</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E276" s="50">
         <v>45</v>
@@ -25843,7 +25840,7 @@
         <v>84</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>79</v>
@@ -25852,7 +25849,7 @@
         <v>66</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L276" s="50" t="s">
         <v>1</v>
@@ -25918,7 +25915,7 @@
         <v>84970</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E277" s="50">
         <v>46</v>
@@ -25927,10 +25924,10 @@
         <v>0</v>
       </c>
       <c r="G277" s="50" t="s">
+        <v>585</v>
+      </c>
+      <c r="H277" s="50" t="s">
         <v>586</v>
-      </c>
-      <c r="H277" s="50" t="s">
-        <v>587</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>79</v>
@@ -25939,7 +25936,7 @@
         <v>66</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L277" s="50" t="s">
         <v>1</v>
@@ -26005,7 +26002,7 @@
         <v>84971</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E278" s="50">
         <v>47</v>
@@ -26017,7 +26014,7 @@
         <v>98</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>79</v>
@@ -26026,13 +26023,13 @@
         <v>66</v>
       </c>
       <c r="K278" s="50" t="s">
+        <v>590</v>
+      </c>
+      <c r="L278" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M278" s="50" t="s">
         <v>591</v>
-      </c>
-      <c r="L278" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M278" s="50" t="s">
-        <v>592</v>
       </c>
       <c r="N278" s="50">
         <v>8</v>
@@ -26092,7 +26089,7 @@
         <v>84972</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E279" s="50">
         <v>46</v>
@@ -26101,10 +26098,10 @@
         <v>0</v>
       </c>
       <c r="G279" s="50" t="s">
+        <v>593</v>
+      </c>
+      <c r="H279" s="50" t="s">
         <v>594</v>
-      </c>
-      <c r="H279" s="50" t="s">
-        <v>595</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>79</v>
@@ -26113,7 +26110,7 @@
         <v>66</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -26179,7 +26176,7 @@
         <v>84973</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E280" s="50">
         <v>16</v>
@@ -26191,7 +26188,7 @@
         <v>64</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>79</v>
@@ -26200,10 +26197,10 @@
         <v>66</v>
       </c>
       <c r="K280" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L280" s="50" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="M280" s="50" t="s">
         <v>1</v>
@@ -26266,7 +26263,7 @@
         <v>84974</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E281" s="50">
         <v>46</v>
@@ -26278,7 +26275,7 @@
         <v>64</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>79</v>
@@ -26287,7 +26284,7 @@
         <v>66</v>
       </c>
       <c r="K281" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L281" s="50" t="s">
         <v>1</v>
@@ -26353,7 +26350,7 @@
         <v>84976</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E282" s="50">
         <v>2</v>
@@ -26378,7 +26375,7 @@
       </c>
       <c r="O282" s="50"/>
       <c r="P282" s="50" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q282" s="50"/>
       <c r="R282" s="50"/>
@@ -26404,7 +26401,7 @@
         <v>84977</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E283" s="50">
         <v>2</v>
@@ -26429,7 +26426,7 @@
       </c>
       <c r="O283" s="50"/>
       <c r="P283" s="50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q283" s="50"/>
       <c r="R283" s="50"/>
@@ -26455,7 +26452,7 @@
         <v>84978</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E284" s="50">
         <v>2</v>
@@ -26480,7 +26477,7 @@
       </c>
       <c r="O284" s="50"/>
       <c r="P284" s="50" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q284" s="50"/>
       <c r="R284" s="50"/>
@@ -26506,7 +26503,7 @@
         <v>84979</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E285" s="50">
         <v>48</v>
@@ -26518,7 +26515,7 @@
         <v>84</v>
       </c>
       <c r="H285" s="50" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I285" s="50" t="s">
         <v>79</v>
@@ -26527,13 +26524,13 @@
         <v>66</v>
       </c>
       <c r="K285" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L285" s="50" t="s">
+        <v>608</v>
+      </c>
+      <c r="M285" s="50" t="s">
         <v>609</v>
-      </c>
-      <c r="M285" s="50" t="s">
-        <v>610</v>
       </c>
       <c r="N285" s="50">
         <v>8</v>
@@ -26593,7 +26590,7 @@
         <v>84980</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E286" s="50">
         <v>49</v>
@@ -26605,7 +26602,7 @@
         <v>64</v>
       </c>
       <c r="H286" s="50" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I286" s="50" t="s">
         <v>79</v>
@@ -26614,10 +26611,10 @@
         <v>66</v>
       </c>
       <c r="K286" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L286" s="50" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M286" s="50" t="s">
         <v>1</v>
@@ -26680,7 +26677,7 @@
         <v>84981</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E287" s="50">
         <v>50</v>
@@ -26692,7 +26689,7 @@
         <v>64</v>
       </c>
       <c r="H287" s="50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I287" s="50" t="s">
         <v>79</v>
@@ -26701,7 +26698,7 @@
         <v>66</v>
       </c>
       <c r="K287" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L287" s="50" t="s">
         <v>1</v>
@@ -26767,7 +26764,7 @@
         <v>84982</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E288" s="50">
         <v>23</v>
@@ -26785,13 +26782,13 @@
         <v>66</v>
       </c>
       <c r="K288" s="50" t="s">
+        <v>616</v>
+      </c>
+      <c r="L288" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M288" s="50" t="s">
         <v>617</v>
-      </c>
-      <c r="L288" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M288" s="50" t="s">
-        <v>618</v>
       </c>
       <c r="N288" s="50">
         <v>8</v>
@@ -26851,7 +26848,7 @@
         <v>84983</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E289" s="50">
         <v>24</v>
@@ -26863,7 +26860,7 @@
         <v>64</v>
       </c>
       <c r="H289" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I289" s="50" t="s">
         <v>79</v>
@@ -26872,7 +26869,7 @@
         <v>66</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -26938,7 +26935,7 @@
         <v>84984</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E290" s="50">
         <v>25</v>
@@ -26950,7 +26947,7 @@
         <v>64</v>
       </c>
       <c r="H290" s="50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I290" s="50" t="s">
         <v>79</v>
@@ -26959,7 +26956,7 @@
         <v>66</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -27025,7 +27022,7 @@
         <v>330037</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E291" s="50">
         <v>5</v>
@@ -27037,7 +27034,7 @@
         <v>64</v>
       </c>
       <c r="H291" s="50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>79</v>
@@ -27112,7 +27109,7 @@
         <v>330038</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E292" s="50">
         <v>6</v>
@@ -27124,7 +27121,7 @@
         <v>98</v>
       </c>
       <c r="H292" s="50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I292" s="50" t="s">
         <v>79</v>
@@ -27133,13 +27130,13 @@
         <v>66</v>
       </c>
       <c r="K292" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L292" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M292" s="50" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N292" s="50">
         <v>33</v>
@@ -27199,7 +27196,7 @@
         <v>330039</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E293" s="50">
         <v>7</v>
@@ -27208,10 +27205,10 @@
         <v>0</v>
       </c>
       <c r="G293" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H293" s="50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I293" s="50" t="s">
         <v>79</v>
@@ -27220,10 +27217,10 @@
         <v>66</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L293" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M293" s="50" t="s">
         <v>1</v>
@@ -27286,7 +27283,7 @@
         <v>330040</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E294" s="50">
         <v>7</v>
@@ -27295,10 +27292,10 @@
         <v>0</v>
       </c>
       <c r="G294" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H294" s="50" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I294" s="50" t="s">
         <v>79</v>
@@ -27307,10 +27304,10 @@
         <v>66</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L294" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M294" s="50" t="s">
         <v>1</v>
@@ -27373,7 +27370,7 @@
         <v>330041</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E295" s="50">
         <v>7</v>
@@ -27382,10 +27379,10 @@
         <v>0</v>
       </c>
       <c r="G295" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>79</v>
@@ -27394,10 +27391,10 @@
         <v>66</v>
       </c>
       <c r="K295" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L295" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M295" s="50" t="s">
         <v>1</v>
@@ -27460,7 +27457,7 @@
         <v>330042</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E296" s="50">
         <v>20</v>
@@ -27472,7 +27469,7 @@
         <v>64</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>79</v>
@@ -27481,13 +27478,13 @@
         <v>66</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L296" s="50" t="s">
+        <v>637</v>
+      </c>
+      <c r="M296" s="50" t="s">
         <v>638</v>
-      </c>
-      <c r="M296" s="50" t="s">
-        <v>639</v>
       </c>
       <c r="N296" s="50">
         <v>33</v>
@@ -27547,7 +27544,7 @@
         <v>330043</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E297" s="50">
         <v>19</v>
@@ -27559,7 +27556,7 @@
         <v>64</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>79</v>
@@ -27568,7 +27565,7 @@
         <v>66</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L297" s="50" t="s">
         <v>1</v>
@@ -27634,7 +27631,7 @@
         <v>330044</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E298" s="50">
         <v>16</v>
@@ -27646,7 +27643,7 @@
         <v>64</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>79</v>
@@ -27655,10 +27652,10 @@
         <v>66</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L298" s="50" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M298" s="50" t="s">
         <v>1</v>
@@ -27721,7 +27718,7 @@
         <v>330045</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E299" s="50">
         <v>5</v>
@@ -27733,7 +27730,7 @@
         <v>84</v>
       </c>
       <c r="H299" s="50" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I299" s="50" t="s">
         <v>79</v>
@@ -27808,7 +27805,7 @@
         <v>330046</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E300" s="50">
         <v>16</v>
@@ -27820,7 +27817,7 @@
         <v>84</v>
       </c>
       <c r="H300" s="50" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I300" s="50" t="s">
         <v>79</v>
@@ -27829,10 +27826,10 @@
         <v>66</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L300" s="50" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M300" s="50" t="s">
         <v>1</v>
@@ -27895,7 +27892,7 @@
         <v>330047</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E301" s="50">
         <v>3</v>
@@ -27907,7 +27904,7 @@
         <v>64</v>
       </c>
       <c r="H301" s="50" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I301" s="50" t="s">
         <v>79</v>
@@ -27916,7 +27913,7 @@
         <v>66</v>
       </c>
       <c r="K301" s="50" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L301" s="50" t="s">
         <v>1</v>
@@ -27982,7 +27979,7 @@
         <v>330048</v>
       </c>
       <c r="D302" s="50" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E302" s="50">
         <v>5</v>
@@ -27994,7 +27991,7 @@
         <v>64</v>
       </c>
       <c r="H302" s="50" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>79</v>
@@ -28069,7 +28066,7 @@
         <v>330049</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E303" s="50">
         <v>43</v>
@@ -28081,7 +28078,7 @@
         <v>64</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>79</v>
@@ -28093,7 +28090,7 @@
         <v>92</v>
       </c>
       <c r="L303" s="50" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M303" s="50" t="s">
         <v>1</v>
@@ -28156,7 +28153,7 @@
         <v>330050</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E304" s="50">
         <v>44</v>
@@ -28168,7 +28165,7 @@
         <v>64</v>
       </c>
       <c r="H304" s="50" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I304" s="50" t="s">
         <v>79</v>
@@ -28243,7 +28240,7 @@
         <v>330051</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E305" s="50">
         <v>4</v>
@@ -28252,10 +28249,10 @@
         <v>1</v>
       </c>
       <c r="G305" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H305" s="50" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I305" s="50" t="s">
         <v>79</v>
@@ -28264,7 +28261,7 @@
         <v>66</v>
       </c>
       <c r="K305" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L305" s="50" t="s">
         <v>1</v>
@@ -28330,7 +28327,7 @@
         <v>330052</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E306" s="50">
         <v>4</v>
@@ -28339,10 +28336,10 @@
         <v>2</v>
       </c>
       <c r="G306" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H306" s="50" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I306" s="50" t="s">
         <v>79</v>
@@ -28351,7 +28348,7 @@
         <v>66</v>
       </c>
       <c r="K306" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L306" s="50" t="s">
         <v>1</v>
@@ -28417,7 +28414,7 @@
         <v>330053</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E307" s="50">
         <v>4</v>
@@ -28429,7 +28426,7 @@
         <v>64</v>
       </c>
       <c r="H307" s="50" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I307" s="50" t="s">
         <v>79</v>
@@ -28438,7 +28435,7 @@
         <v>66</v>
       </c>
       <c r="K307" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L307" s="50" t="s">
         <v>1</v>
@@ -28504,7 +28501,7 @@
         <v>330054</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E308" s="50">
         <v>5</v>
@@ -28516,7 +28513,7 @@
         <v>64</v>
       </c>
       <c r="H308" s="50" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I308" s="50" t="s">
         <v>79</v>
@@ -28591,7 +28588,7 @@
         <v>330055</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E309" s="50">
         <v>4</v>
@@ -28603,7 +28600,7 @@
         <v>84</v>
       </c>
       <c r="H309" s="50" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I309" s="50" t="s">
         <v>79</v>
@@ -28612,7 +28609,7 @@
         <v>66</v>
       </c>
       <c r="K309" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L309" s="50" t="s">
         <v>1</v>
@@ -28678,7 +28675,7 @@
         <v>330056</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E310" s="50">
         <v>54</v>
@@ -28687,10 +28684,10 @@
         <v>0</v>
       </c>
       <c r="G310" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H310" s="50" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I310" s="50" t="s">
         <v>79</v>
@@ -28765,7 +28762,7 @@
         <v>330058</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E311" s="50">
         <v>5</v>
@@ -28774,10 +28771,10 @@
         <v>1</v>
       </c>
       <c r="G311" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H311" s="50" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I311" s="50" t="s">
         <v>79</v>
@@ -28852,7 +28849,7 @@
         <v>330061</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E312" s="50">
         <v>39</v>
@@ -28864,7 +28861,7 @@
         <v>64</v>
       </c>
       <c r="H312" s="50" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I312" s="50" t="s">
         <v>79</v>
@@ -28873,7 +28870,7 @@
         <v>66</v>
       </c>
       <c r="K312" s="50" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L312" s="50" t="s">
         <v>1</v>
@@ -28939,7 +28936,7 @@
         <v>330062</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E313" s="50">
         <v>40</v>
@@ -28951,7 +28948,7 @@
         <v>64</v>
       </c>
       <c r="H313" s="50" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I313" s="50" t="s">
         <v>79</v>
@@ -28960,7 +28957,7 @@
         <v>66</v>
       </c>
       <c r="K313" s="50" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L313" s="50" t="s">
         <v>1</v>
@@ -29026,7 +29023,7 @@
         <v>330063</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E314" s="50">
         <v>28</v>
@@ -29038,7 +29035,7 @@
         <v>64</v>
       </c>
       <c r="H314" s="50" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I314" s="50" t="s">
         <v>79</v>
@@ -29113,7 +29110,7 @@
         <v>330064</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E315" s="50">
         <v>29</v>
@@ -29122,10 +29119,10 @@
         <v>0</v>
       </c>
       <c r="G315" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H315" s="50" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="I315" s="50" t="s">
         <v>79</v>
@@ -29134,7 +29131,7 @@
         <v>66</v>
       </c>
       <c r="K315" s="50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L315" s="50" t="s">
         <v>1</v>
@@ -29200,7 +29197,7 @@
         <v>330065</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E316" s="50">
         <v>5</v>
@@ -29212,7 +29209,7 @@
         <v>64</v>
       </c>
       <c r="H316" s="50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I316" s="50" t="s">
         <v>79</v>
@@ -29221,7 +29218,7 @@
         <v>66</v>
       </c>
       <c r="K316" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L316" s="50" t="s">
         <v>1</v>
@@ -29287,7 +29284,7 @@
         <v>330067</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E317" s="50">
         <v>4</v>
@@ -29299,7 +29296,7 @@
         <v>64</v>
       </c>
       <c r="H317" s="50" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I317" s="50" t="s">
         <v>79</v>
@@ -29308,7 +29305,7 @@
         <v>66</v>
       </c>
       <c r="K317" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L317" s="50" t="s">
         <v>1</v>
@@ -29374,7 +29371,7 @@
         <v>330068</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E318" s="50">
         <v>5</v>
@@ -29383,10 +29380,10 @@
         <v>1</v>
       </c>
       <c r="G318" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H318" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="I318" s="50" t="s">
         <v>79</v>
@@ -29461,7 +29458,7 @@
         <v>330069</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E319" s="50">
         <v>16</v>
@@ -29473,7 +29470,7 @@
         <v>64</v>
       </c>
       <c r="H319" s="50" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I319" s="50" t="s">
         <v>79</v>
@@ -29482,10 +29479,10 @@
         <v>66</v>
       </c>
       <c r="K319" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L319" s="50" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M319" s="50" t="s">
         <v>1</v>
@@ -29548,7 +29545,7 @@
         <v>330070</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E320" s="50">
         <v>3</v>
@@ -29560,7 +29557,7 @@
         <v>64</v>
       </c>
       <c r="H320" s="50" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I320" s="50" t="s">
         <v>79</v>
@@ -29569,7 +29566,7 @@
         <v>66</v>
       </c>
       <c r="K320" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L320" s="50" t="s">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -1875,15 +1875,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1904,6 +1911,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1912,9 +1927,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1929,8 +1943,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1944,47 +1958,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1999,14 +1982,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2019,8 +2003,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2035,7 +2035,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2047,97 +2119,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2155,13 +2149,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2173,49 +2185,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2226,6 +2226,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2247,17 +2256,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2277,13 +2286,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2303,26 +2316,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2331,148 +2331,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="6">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3529" uniqueCount="616">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_yellow.prefab</t>
-  </si>
-  <si>
-    <t>15034</t>
   </si>
   <si>
     <t>18,4.999971,36</t>
@@ -1896,21 +1893,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -1927,16 +1909,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1944,7 +1933,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1965,6 +1962,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -1973,24 +1985,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2005,22 +2009,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2035,7 +2032,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2047,7 +2122,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2059,85 +2140,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2149,25 +2152,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2185,37 +2188,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2234,15 +2231,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2271,17 +2259,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2301,6 +2283,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2316,13 +2309,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2331,145 +2328,145 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="7">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="7">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="6">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1">
@@ -3466,8 +3463,8 @@
       <c r="K10" t="s">
         <v>79</v>
       </c>
-      <c r="L10" t="s">
-        <v>80</v>
+      <c r="L10">
+        <v>15057</v>
       </c>
       <c r="M10" t="s">
         <v>1</v>
@@ -3526,7 +3523,7 @@
         <v>15053</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -3544,7 +3541,7 @@
         <v>62</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L11" t="s">
         <v>1</v>
@@ -3606,7 +3603,7 @@
         <v>15054</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>54</v>
@@ -3615,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s">
         <v>84</v>
-      </c>
-      <c r="H12" t="s">
-        <v>85</v>
       </c>
       <c r="I12" t="s">
         <v>78</v>
@@ -3627,7 +3624,7 @@
         <v>62</v>
       </c>
       <c r="K12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L12" t="s">
         <v>1</v>
@@ -3689,7 +3686,7 @@
         <v>15055</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>44</v>
@@ -3701,7 +3698,7 @@
         <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
         <v>78</v>
@@ -3710,7 +3707,7 @@
         <v>62</v>
       </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
         <v>1</v>
@@ -3772,7 +3769,7 @@
         <v>15057</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -3784,7 +3781,7 @@
         <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
         <v>78</v>
@@ -3793,55 +3790,55 @@
         <v>62</v>
       </c>
       <c r="K14" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
         <v>92</v>
-      </c>
-      <c r="L14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -3855,7 +3852,7 @@
         <v>15035</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -3864,10 +3861,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" t="s">
         <v>95</v>
-      </c>
-      <c r="H15" t="s">
-        <v>96</v>
       </c>
       <c r="I15" t="s">
         <v>78</v>
@@ -3876,7 +3873,7 @@
         <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L15" t="s">
         <v>1</v>
@@ -3924,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -3938,7 +3935,7 @@
         <v>15056</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16">
         <v>43</v>
@@ -3950,7 +3947,7 @@
         <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
         <v>78</v>
@@ -3959,55 +3956,55 @@
         <v>62</v>
       </c>
       <c r="K16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" t="s">
         <v>101</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
         <v>102</v>
-      </c>
-      <c r="M16" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16" t="s">
-        <v>1</v>
-      </c>
-      <c r="X16" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -4021,7 +4018,7 @@
         <v>15065</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17">
         <v>62</v>
@@ -4081,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z17" s="2">
         <v>0</v>
@@ -4101,7 +4098,7 @@
         <v>15059</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18">
         <v>62</v>
@@ -4161,13 +4158,13 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
         <v>106</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -4181,7 +4178,7 @@
         <v>15060</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19">
         <v>62</v>
@@ -4247,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -4261,7 +4258,7 @@
         <v>15061</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E20">
         <v>62</v>
@@ -4321,7 +4318,7 @@
         <v>64</v>
       </c>
       <c r="Y20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Z20" s="2">
         <v>0</v>
@@ -4341,7 +4338,7 @@
         <v>15044</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E21">
         <v>62</v>
@@ -4421,7 +4418,7 @@
         <v>15062</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22">
         <v>62</v>
@@ -4481,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z22" s="2">
         <v>0</v>
@@ -4501,7 +4498,7 @@
         <v>15063</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E23">
         <v>62</v>
@@ -4581,7 +4578,7 @@
         <v>15064</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E24">
         <v>62</v>
@@ -4641,7 +4638,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z24" s="2">
         <v>0</v>
@@ -4661,7 +4658,7 @@
         <v>15068</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>62</v>
@@ -4721,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z25" s="2">
         <v>0</v>
@@ -4741,7 +4738,7 @@
         <v>15069</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26">
         <v>62</v>
@@ -4801,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z26" s="2">
         <v>0</v>
@@ -4821,7 +4818,7 @@
         <v>15066</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E27">
         <v>62</v>
@@ -4887,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -4901,7 +4898,7 @@
         <v>15067</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28">
         <v>62</v>
@@ -4961,7 +4958,7 @@
         <v>69</v>
       </c>
       <c r="Y28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z28" s="2">
         <v>0</v>
@@ -4981,7 +4978,7 @@
         <v>15045</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29">
         <v>62</v>
@@ -5061,7 +5058,7 @@
         <v>30813</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30">
         <v>12</v>
@@ -5138,7 +5135,7 @@
         <v>30819</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31">
         <v>17</v>
@@ -5150,7 +5147,7 @@
         <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I31" t="s">
         <v>78</v>
@@ -5159,10 +5156,10 @@
         <v>62</v>
       </c>
       <c r="K31" t="s">
+        <v>124</v>
+      </c>
+      <c r="L31" t="s">
         <v>125</v>
-      </c>
-      <c r="L31" t="s">
-        <v>126</v>
       </c>
       <c r="M31" t="s">
         <v>1</v>
@@ -5218,7 +5215,7 @@
         <v>30822</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32">
         <v>14</v>
@@ -5236,7 +5233,7 @@
         <v>62</v>
       </c>
       <c r="K32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L32" t="s">
         <v>1</v>
@@ -5295,7 +5292,7 @@
         <v>30837</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33">
         <v>55</v>
@@ -5304,10 +5301,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I33" t="s">
         <v>78</v>
@@ -5316,10 +5313,10 @@
         <v>62</v>
       </c>
       <c r="K33" t="s">
+        <v>129</v>
+      </c>
+      <c r="L33" t="s">
         <v>130</v>
-      </c>
-      <c r="L33" t="s">
-        <v>131</v>
       </c>
       <c r="M33" t="s">
         <v>1</v>
@@ -5375,7 +5372,7 @@
         <v>30840</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E34">
         <v>54</v>
@@ -5384,10 +5381,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I34" t="s">
         <v>78</v>
@@ -5396,7 +5393,7 @@
         <v>62</v>
       </c>
       <c r="K34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L34" t="s">
         <v>1</v>
@@ -5455,7 +5452,7 @@
         <v>30862</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E35">
         <v>53</v>
@@ -5467,7 +5464,7 @@
         <v>60</v>
       </c>
       <c r="H35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I35" t="s">
         <v>78</v>
@@ -5476,7 +5473,7 @@
         <v>62</v>
       </c>
       <c r="K35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s">
         <v>1</v>
@@ -5512,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="X35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y35" t="s">
         <v>1</v>
@@ -5535,7 +5532,7 @@
         <v>30927</v>
       </c>
       <c r="D36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -5544,10 +5541,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
+        <v>138</v>
+      </c>
+      <c r="H36" t="s">
         <v>139</v>
-      </c>
-      <c r="H36" t="s">
-        <v>140</v>
       </c>
       <c r="I36" t="s">
         <v>78</v>
@@ -5556,7 +5553,7 @@
         <v>62</v>
       </c>
       <c r="K36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L36" t="s">
         <v>1</v>
@@ -5615,7 +5612,7 @@
         <v>30930</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -5624,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I37" t="s">
         <v>78</v>
@@ -5636,13 +5633,13 @@
         <v>62</v>
       </c>
       <c r="K37" t="s">
+        <v>142</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
         <v>143</v>
-      </c>
-      <c r="L37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M37" t="s">
-        <v>144</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -5672,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="X37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y37" t="s">
         <v>1</v>
@@ -5695,7 +5692,7 @@
         <v>30947</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -5704,10 +5701,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I38" t="s">
         <v>78</v>
@@ -5716,10 +5713,10 @@
         <v>62</v>
       </c>
       <c r="K38" t="s">
+        <v>147</v>
+      </c>
+      <c r="L38" t="s">
         <v>148</v>
-      </c>
-      <c r="L38" t="s">
-        <v>149</v>
       </c>
       <c r="M38" t="s">
         <v>1</v>
@@ -5775,7 +5772,7 @@
         <v>34800</v>
       </c>
       <c r="D39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -5784,10 +5781,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I39" t="s">
         <v>78</v>
@@ -5796,10 +5793,10 @@
         <v>62</v>
       </c>
       <c r="K39" t="s">
+        <v>147</v>
+      </c>
+      <c r="L39" t="s">
         <v>148</v>
-      </c>
-      <c r="L39" t="s">
-        <v>149</v>
       </c>
       <c r="M39" t="s">
         <v>1</v>
@@ -5855,7 +5852,7 @@
         <v>30969</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E40">
         <v>18</v>
@@ -5867,7 +5864,7 @@
         <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I40" t="s">
         <v>78</v>
@@ -5876,7 +5873,7 @@
         <v>62</v>
       </c>
       <c r="K40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s">
         <v>1</v>
@@ -5935,7 +5932,7 @@
         <v>34815</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41">
         <v>59</v>
@@ -6015,7 +6012,7 @@
         <v>24849</v>
       </c>
       <c r="D42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -6036,7 +6033,7 @@
         <v>2</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -6050,7 +6047,7 @@
         <v>24850</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -6071,7 +6068,7 @@
         <v>2</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -6085,7 +6082,7 @@
         <v>24851</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -6106,7 +6103,7 @@
         <v>2</v>
       </c>
       <c r="P44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:24">
@@ -6120,7 +6117,7 @@
         <v>24852</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -6141,10 +6138,10 @@
         <v>2</v>
       </c>
       <c r="P45" t="s">
+        <v>162</v>
+      </c>
+      <c r="X45" t="s">
         <v>163</v>
-      </c>
-      <c r="X45" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -6158,7 +6155,7 @@
         <v>24865</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -6179,7 +6176,7 @@
         <v>2</v>
       </c>
       <c r="P46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -6193,7 +6190,7 @@
         <v>24866</v>
       </c>
       <c r="D47" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E47">
         <v>2</v>
@@ -6214,7 +6211,7 @@
         <v>2</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -6228,7 +6225,7 @@
         <v>24867</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48">
         <v>2</v>
@@ -6249,7 +6246,7 @@
         <v>2</v>
       </c>
       <c r="P48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -6263,7 +6260,7 @@
         <v>24868</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -6284,10 +6281,10 @@
         <v>2</v>
       </c>
       <c r="P49" t="s">
+        <v>170</v>
+      </c>
+      <c r="X49" t="s">
         <v>171</v>
-      </c>
-      <c r="X49" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -6301,7 +6298,7 @@
         <v>33236</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E50">
         <v>12</v>
@@ -6378,7 +6375,7 @@
         <v>33240</v>
       </c>
       <c r="D51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E51">
         <v>5</v>
@@ -6387,10 +6384,10 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" t="s">
         <v>78</v>
@@ -6399,7 +6396,7 @@
         <v>62</v>
       </c>
       <c r="K51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L51" t="s">
         <v>1</v>
@@ -6458,7 +6455,7 @@
         <v>33249</v>
       </c>
       <c r="D52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E52">
         <v>28</v>
@@ -6470,7 +6467,7 @@
         <v>60</v>
       </c>
       <c r="H52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I52" t="s">
         <v>78</v>
@@ -6482,7 +6479,7 @@
         <v>75</v>
       </c>
       <c r="L52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M52" t="s">
         <v>1</v>
@@ -6538,7 +6535,7 @@
         <v>33339</v>
       </c>
       <c r="D53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E53">
         <v>29</v>
@@ -6550,7 +6547,7 @@
         <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I53" t="s">
         <v>78</v>
@@ -6559,13 +6556,13 @@
         <v>62</v>
       </c>
       <c r="K53" t="s">
+        <v>180</v>
+      </c>
+      <c r="L53" t="s">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
         <v>181</v>
-      </c>
-      <c r="L53" t="s">
-        <v>1</v>
-      </c>
-      <c r="M53" t="s">
-        <v>182</v>
       </c>
       <c r="N53">
         <v>3</v>
@@ -6618,7 +6615,7 @@
         <v>33390</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54">
         <v>14</v>
@@ -6636,7 +6633,7 @@
         <v>62</v>
       </c>
       <c r="K54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L54" t="s">
         <v>1</v>
@@ -6695,7 +6692,7 @@
         <v>34816</v>
       </c>
       <c r="D55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -6707,7 +6704,7 @@
         <v>60</v>
       </c>
       <c r="H55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I55" t="s">
         <v>78</v>
@@ -6716,7 +6713,7 @@
         <v>62</v>
       </c>
       <c r="K55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L55" t="s">
         <v>1</v>
@@ -6755,7 +6752,7 @@
         <v>1</v>
       </c>
       <c r="X55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y55" t="s">
         <v>1</v>
@@ -6778,7 +6775,7 @@
         <v>34817</v>
       </c>
       <c r="D56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56">
         <v>16</v>
@@ -6787,10 +6784,10 @@
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I56" t="s">
         <v>78</v>
@@ -6799,7 +6796,7 @@
         <v>62</v>
       </c>
       <c r="K56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L56">
         <v>34816</v>
@@ -6861,7 +6858,7 @@
         <v>34821</v>
       </c>
       <c r="D57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E57">
         <v>16</v>
@@ -6870,10 +6867,10 @@
         <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I57" t="s">
         <v>78</v>
@@ -6882,13 +6879,13 @@
         <v>62</v>
       </c>
       <c r="K57" t="s">
+        <v>192</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
         <v>193</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57" t="s">
-        <v>194</v>
       </c>
       <c r="N57">
         <v>3</v>
@@ -6944,7 +6941,7 @@
         <v>34850</v>
       </c>
       <c r="D58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -6965,7 +6962,7 @@
         <v>3</v>
       </c>
       <c r="P58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:24">
@@ -6979,7 +6976,7 @@
         <v>34882</v>
       </c>
       <c r="D59" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -6997,16 +6994,16 @@
         <v>62</v>
       </c>
       <c r="L59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N59">
         <v>3</v>
       </c>
       <c r="P59" t="s">
+        <v>197</v>
+      </c>
+      <c r="X59" t="s">
         <v>198</v>
-      </c>
-      <c r="X59" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -7020,7 +7017,7 @@
         <v>34852</v>
       </c>
       <c r="D60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -7041,7 +7038,7 @@
         <v>3</v>
       </c>
       <c r="P60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:24">
@@ -7055,7 +7052,7 @@
         <v>34853</v>
       </c>
       <c r="D61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -7073,16 +7070,16 @@
         <v>62</v>
       </c>
       <c r="L61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N61">
         <v>3</v>
       </c>
       <c r="P61" t="s">
+        <v>202</v>
+      </c>
+      <c r="X61" t="s">
         <v>203</v>
-      </c>
-      <c r="X61" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -7096,7 +7093,7 @@
         <v>34868</v>
       </c>
       <c r="D62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -7117,7 +7114,7 @@
         <v>3</v>
       </c>
       <c r="P62" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7131,7 +7128,7 @@
         <v>34869</v>
       </c>
       <c r="D63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -7152,7 +7149,7 @@
         <v>3</v>
       </c>
       <c r="P63" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:27">
@@ -7166,7 +7163,7 @@
         <v>44810</v>
       </c>
       <c r="D64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E64">
         <v>12</v>
@@ -7246,7 +7243,7 @@
         <v>44815</v>
       </c>
       <c r="D65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E65">
         <v>6</v>
@@ -7258,7 +7255,7 @@
         <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I65" t="s">
         <v>78</v>
@@ -7267,13 +7264,13 @@
         <v>62</v>
       </c>
       <c r="K65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L65" t="s">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N65">
         <v>4</v>
@@ -7326,7 +7323,7 @@
         <v>44816</v>
       </c>
       <c r="D66" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E66">
         <v>7</v>
@@ -7335,10 +7332,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I66" t="s">
         <v>78</v>
@@ -7347,10 +7344,10 @@
         <v>62</v>
       </c>
       <c r="K66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M66" t="s">
         <v>1</v>
@@ -7406,7 +7403,7 @@
         <v>44817</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E67">
         <v>7</v>
@@ -7415,10 +7412,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I67" t="s">
         <v>78</v>
@@ -7427,10 +7424,10 @@
         <v>62</v>
       </c>
       <c r="K67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M67" t="s">
         <v>1</v>
@@ -7486,7 +7483,7 @@
         <v>44818</v>
       </c>
       <c r="D68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -7495,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I68" t="s">
         <v>78</v>
@@ -7507,10 +7504,10 @@
         <v>62</v>
       </c>
       <c r="K68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M68" t="s">
         <v>1</v>
@@ -7566,7 +7563,7 @@
         <v>44819</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E69">
         <v>5</v>
@@ -7575,10 +7572,10 @@
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I69" t="s">
         <v>78</v>
@@ -7587,7 +7584,7 @@
         <v>62</v>
       </c>
       <c r="K69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L69" t="s">
         <v>1</v>
@@ -7649,7 +7646,7 @@
         <v>44820</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -7658,10 +7655,10 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I70" t="s">
         <v>78</v>
@@ -7670,7 +7667,7 @@
         <v>62</v>
       </c>
       <c r="K70" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L70" t="s">
         <v>1</v>
@@ -7732,7 +7729,7 @@
         <v>44823</v>
       </c>
       <c r="D71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E71">
         <v>16</v>
@@ -7744,7 +7741,7 @@
         <v>60</v>
       </c>
       <c r="H71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I71" t="s">
         <v>78</v>
@@ -7756,7 +7753,7 @@
         <v>79</v>
       </c>
       <c r="L71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M71" t="s">
         <v>1</v>
@@ -7812,7 +7809,7 @@
         <v>44824</v>
       </c>
       <c r="D72" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -7824,7 +7821,7 @@
         <v>60</v>
       </c>
       <c r="H72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I72" t="s">
         <v>78</v>
@@ -7833,7 +7830,7 @@
         <v>62</v>
       </c>
       <c r="K72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L72" t="s">
         <v>1</v>
@@ -7892,7 +7889,7 @@
         <v>44825</v>
       </c>
       <c r="D73" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E73">
         <v>4</v>
@@ -7901,10 +7898,10 @@
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I73" t="s">
         <v>78</v>
@@ -7913,7 +7910,7 @@
         <v>62</v>
       </c>
       <c r="K73" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L73" t="s">
         <v>1</v>
@@ -7975,7 +7972,7 @@
         <v>44827</v>
       </c>
       <c r="D74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E74">
         <v>20</v>
@@ -7987,7 +7984,7 @@
         <v>60</v>
       </c>
       <c r="H74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I74" t="s">
         <v>78</v>
@@ -7996,13 +7993,13 @@
         <v>62</v>
       </c>
       <c r="K74" t="s">
+        <v>233</v>
+      </c>
+      <c r="L74" t="s">
         <v>234</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>235</v>
-      </c>
-      <c r="M74" t="s">
-        <v>236</v>
       </c>
       <c r="N74">
         <v>4</v>
@@ -8055,7 +8052,7 @@
         <v>44828</v>
       </c>
       <c r="D75" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E75">
         <v>19</v>
@@ -8067,7 +8064,7 @@
         <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I75" t="s">
         <v>78</v>
@@ -8076,7 +8073,7 @@
         <v>62</v>
       </c>
       <c r="K75" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L75" t="s">
         <v>1</v>
@@ -8135,7 +8132,7 @@
         <v>44829</v>
       </c>
       <c r="D76" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E76">
         <v>16</v>
@@ -8147,7 +8144,7 @@
         <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I76" t="s">
         <v>78</v>
@@ -8156,10 +8153,10 @@
         <v>62</v>
       </c>
       <c r="K76" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M76" t="s">
         <v>1</v>
@@ -8215,7 +8212,7 @@
         <v>44831</v>
       </c>
       <c r="D77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E77">
         <v>14</v>
@@ -8233,10 +8230,10 @@
         <v>62</v>
       </c>
       <c r="K77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M77" t="s">
         <v>1</v>
@@ -8292,7 +8289,7 @@
         <v>44832</v>
       </c>
       <c r="D78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E78">
         <v>4</v>
@@ -8301,10 +8298,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H78" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I78" t="s">
         <v>78</v>
@@ -8313,7 +8310,7 @@
         <v>62</v>
       </c>
       <c r="K78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L78" t="s">
         <v>1</v>
@@ -8372,7 +8369,7 @@
         <v>44834</v>
       </c>
       <c r="D79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -8393,7 +8390,7 @@
         <v>4</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -8407,7 +8404,7 @@
         <v>44836</v>
       </c>
       <c r="D80" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E80">
         <v>2</v>
@@ -8428,7 +8425,7 @@
         <v>4</v>
       </c>
       <c r="P80" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -8442,7 +8439,7 @@
         <v>44837</v>
       </c>
       <c r="D81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E81">
         <v>2</v>
@@ -8463,7 +8460,7 @@
         <v>4</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -8477,7 +8474,7 @@
         <v>34027</v>
       </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -8495,7 +8492,7 @@
         <v>62</v>
       </c>
       <c r="K82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L82" t="s">
         <v>1</v>
@@ -8554,7 +8551,7 @@
         <v>34057</v>
       </c>
       <c r="D83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -8563,7 +8560,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I83" t="s">
         <v>78</v>
@@ -8572,7 +8569,7 @@
         <v>62</v>
       </c>
       <c r="K83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L83" t="s">
         <v>1</v>
@@ -8631,7 +8628,7 @@
         <v>34063</v>
       </c>
       <c r="D84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E84">
         <v>16</v>
@@ -8640,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I84" t="s">
         <v>78</v>
@@ -8649,10 +8646,10 @@
         <v>62</v>
       </c>
       <c r="K84" t="s">
+        <v>257</v>
+      </c>
+      <c r="L84" t="s">
         <v>258</v>
-      </c>
-      <c r="L84" t="s">
-        <v>259</v>
       </c>
       <c r="M84" t="s">
         <v>1</v>
@@ -8708,7 +8705,7 @@
         <v>34107</v>
       </c>
       <c r="D85" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E85">
         <v>12</v>
@@ -8785,7 +8782,7 @@
         <v>34115</v>
       </c>
       <c r="D86" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E86">
         <v>28</v>
@@ -8806,7 +8803,7 @@
         <v>75</v>
       </c>
       <c r="L86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M86" t="s">
         <v>1</v>
@@ -8862,7 +8859,7 @@
         <v>34147</v>
       </c>
       <c r="D87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E87">
         <v>54</v>
@@ -8871,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I87" t="s">
         <v>78</v>
@@ -8880,7 +8877,7 @@
         <v>62</v>
       </c>
       <c r="K87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L87" t="s">
         <v>1</v>
@@ -8939,7 +8936,7 @@
         <v>34177</v>
       </c>
       <c r="D88" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E88">
         <v>4</v>
@@ -8948,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I88" t="s">
         <v>78</v>
@@ -8957,7 +8954,7 @@
         <v>62</v>
       </c>
       <c r="K88" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L88" t="s">
         <v>1</v>
@@ -9016,7 +9013,7 @@
         <v>34198</v>
       </c>
       <c r="D89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E89">
         <v>19</v>
@@ -9034,7 +9031,7 @@
         <v>62</v>
       </c>
       <c r="K89" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L89" t="s">
         <v>1</v>
@@ -9093,7 +9090,7 @@
         <v>34199</v>
       </c>
       <c r="D90" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E90">
         <v>5</v>
@@ -9111,7 +9108,7 @@
         <v>62</v>
       </c>
       <c r="K90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L90" t="s">
         <v>1</v>
@@ -9170,7 +9167,7 @@
         <v>34202</v>
       </c>
       <c r="D91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E91">
         <v>16</v>
@@ -9188,10 +9185,10 @@
         <v>62</v>
       </c>
       <c r="K91" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M91" t="s">
         <v>1</v>
@@ -9247,7 +9244,7 @@
         <v>34205</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E92">
         <v>29</v>
@@ -9265,13 +9262,13 @@
         <v>62</v>
       </c>
       <c r="K92" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L92" t="s">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N92">
         <v>5</v>
@@ -9324,7 +9321,7 @@
         <v>34214</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E93">
         <v>52</v>
@@ -9342,13 +9339,13 @@
         <v>62</v>
       </c>
       <c r="K93" t="s">
+        <v>271</v>
+      </c>
+      <c r="L93" t="s">
         <v>272</v>
       </c>
-      <c r="L93" t="s">
+      <c r="M93" t="s">
         <v>273</v>
-      </c>
-      <c r="M93" t="s">
-        <v>274</v>
       </c>
       <c r="N93">
         <v>5</v>
@@ -9401,7 +9398,7 @@
         <v>34217</v>
       </c>
       <c r="D94" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E94">
         <v>4</v>
@@ -9410,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I94" t="s">
         <v>78</v>
@@ -9419,7 +9416,7 @@
         <v>62</v>
       </c>
       <c r="K94" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L94" t="s">
         <v>1</v>
@@ -9478,7 +9475,7 @@
         <v>34240</v>
       </c>
       <c r="D95" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E95">
         <v>51</v>
@@ -9496,7 +9493,7 @@
         <v>62</v>
       </c>
       <c r="K95" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L95" t="s">
         <v>1</v>
@@ -9555,7 +9552,7 @@
         <v>34275</v>
       </c>
       <c r="D96" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E96">
         <v>16</v>
@@ -9573,10 +9570,10 @@
         <v>62</v>
       </c>
       <c r="K96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L96" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M96" t="s">
         <v>1</v>
@@ -9632,7 +9629,7 @@
         <v>34291</v>
       </c>
       <c r="D97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E97">
         <v>20</v>
@@ -9650,13 +9647,13 @@
         <v>62</v>
       </c>
       <c r="K97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L97" t="s">
+        <v>280</v>
+      </c>
+      <c r="M97" t="s">
         <v>281</v>
-      </c>
-      <c r="M97" t="s">
-        <v>282</v>
       </c>
       <c r="N97">
         <v>5</v>
@@ -9709,7 +9706,7 @@
         <v>34301</v>
       </c>
       <c r="D98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E98">
         <v>51</v>
@@ -9727,7 +9724,7 @@
         <v>62</v>
       </c>
       <c r="K98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L98" t="s">
         <v>1</v>
@@ -9786,7 +9783,7 @@
         <v>34334</v>
       </c>
       <c r="D99" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E99">
         <v>52</v>
@@ -9804,13 +9801,13 @@
         <v>62</v>
       </c>
       <c r="K99" t="s">
+        <v>285</v>
+      </c>
+      <c r="L99" t="s">
         <v>286</v>
       </c>
-      <c r="L99" t="s">
-        <v>287</v>
-      </c>
       <c r="M99" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -9863,7 +9860,7 @@
         <v>34337</v>
       </c>
       <c r="D100" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E100">
         <v>14</v>
@@ -9881,10 +9878,10 @@
         <v>62</v>
       </c>
       <c r="K100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L100" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M100" t="s">
         <v>1</v>
@@ -9940,7 +9937,7 @@
         <v>34586</v>
       </c>
       <c r="D101" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -9961,7 +9958,7 @@
         <v>5</v>
       </c>
       <c r="P101" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -9975,7 +9972,7 @@
         <v>34587</v>
       </c>
       <c r="D102" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E102">
         <v>2</v>
@@ -9996,7 +9993,7 @@
         <v>5</v>
       </c>
       <c r="P102" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="103" spans="1:27">
@@ -10010,7 +10007,7 @@
         <v>34589</v>
       </c>
       <c r="D103" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E103">
         <v>4</v>
@@ -10019,7 +10016,7 @@
         <v>2</v>
       </c>
       <c r="G103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I103" t="s">
         <v>78</v>
@@ -10028,7 +10025,7 @@
         <v>62</v>
       </c>
       <c r="K103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L103" t="s">
         <v>1</v>
@@ -10090,7 +10087,7 @@
         <v>34590</v>
       </c>
       <c r="D104" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E104">
         <v>5</v>
@@ -10099,7 +10096,7 @@
         <v>3</v>
       </c>
       <c r="G104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I104" t="s">
         <v>78</v>
@@ -10108,7 +10105,7 @@
         <v>62</v>
       </c>
       <c r="K104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L104" t="s">
         <v>1</v>
@@ -10170,7 +10167,7 @@
         <v>34591</v>
       </c>
       <c r="D105" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E105">
         <v>5</v>
@@ -10179,7 +10176,7 @@
         <v>2</v>
       </c>
       <c r="G105" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I105" t="s">
         <v>78</v>
@@ -10188,7 +10185,7 @@
         <v>62</v>
       </c>
       <c r="K105" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L105" t="s">
         <v>1</v>
@@ -10250,7 +10247,7 @@
         <v>34696</v>
       </c>
       <c r="D106" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E106">
         <v>2</v>
@@ -10271,7 +10268,7 @@
         <v>5</v>
       </c>
       <c r="P106" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107" spans="1:27">
@@ -10285,7 +10282,7 @@
         <v>34699</v>
       </c>
       <c r="D107" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E107">
         <v>56</v>
@@ -10303,7 +10300,7 @@
         <v>62</v>
       </c>
       <c r="K107" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L107" t="s">
         <v>1</v>
@@ -10365,7 +10362,7 @@
         <v>34701</v>
       </c>
       <c r="D108" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E108">
         <v>56</v>
@@ -10383,7 +10380,7 @@
         <v>62</v>
       </c>
       <c r="K108" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L108" t="s">
         <v>1</v>
@@ -10445,7 +10442,7 @@
         <v>34700</v>
       </c>
       <c r="D109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E109">
         <v>56</v>
@@ -10463,7 +10460,7 @@
         <v>62</v>
       </c>
       <c r="K109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L109" t="s">
         <v>1</v>
@@ -10525,7 +10522,7 @@
         <v>34697</v>
       </c>
       <c r="D110" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E110">
         <v>56</v>
@@ -10543,7 +10540,7 @@
         <v>62</v>
       </c>
       <c r="K110" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L110" t="s">
         <v>1</v>
@@ -10605,7 +10602,7 @@
         <v>34698</v>
       </c>
       <c r="D111" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E111">
         <v>56</v>
@@ -10623,7 +10620,7 @@
         <v>62</v>
       </c>
       <c r="K111" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L111" t="s">
         <v>1</v>
@@ -10685,7 +10682,7 @@
         <v>34713</v>
       </c>
       <c r="D112" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E112">
         <v>56</v>
@@ -10703,7 +10700,7 @@
         <v>62</v>
       </c>
       <c r="K112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L112" t="s">
         <v>1</v>
@@ -10765,7 +10762,7 @@
         <v>34702</v>
       </c>
       <c r="D113" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E113">
         <v>56</v>
@@ -10783,7 +10780,7 @@
         <v>62</v>
       </c>
       <c r="K113" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L113" t="s">
         <v>1</v>
@@ -10845,7 +10842,7 @@
         <v>34703</v>
       </c>
       <c r="D114" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E114">
         <v>56</v>
@@ -10863,7 +10860,7 @@
         <v>62</v>
       </c>
       <c r="K114" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L114" t="s">
         <v>1</v>
@@ -10925,7 +10922,7 @@
         <v>34704</v>
       </c>
       <c r="D115" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E115">
         <v>56</v>
@@ -10943,7 +10940,7 @@
         <v>62</v>
       </c>
       <c r="K115" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L115" t="s">
         <v>1</v>
@@ -11005,7 +11002,7 @@
         <v>34705</v>
       </c>
       <c r="D116" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E116">
         <v>56</v>
@@ -11023,7 +11020,7 @@
         <v>62</v>
       </c>
       <c r="K116" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L116" t="s">
         <v>1</v>
@@ -11085,7 +11082,7 @@
         <v>34706</v>
       </c>
       <c r="D117" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E117">
         <v>56</v>
@@ -11103,7 +11100,7 @@
         <v>62</v>
       </c>
       <c r="K117" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L117" t="s">
         <v>1</v>
@@ -11165,7 +11162,7 @@
         <v>34707</v>
       </c>
       <c r="D118" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E118">
         <v>56</v>
@@ -11183,7 +11180,7 @@
         <v>62</v>
       </c>
       <c r="K118" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L118" t="s">
         <v>1</v>
@@ -11245,7 +11242,7 @@
         <v>34708</v>
       </c>
       <c r="D119" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E119">
         <v>56</v>
@@ -11263,7 +11260,7 @@
         <v>62</v>
       </c>
       <c r="K119" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L119" t="s">
         <v>1</v>
@@ -11325,7 +11322,7 @@
         <v>34709</v>
       </c>
       <c r="D120" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E120">
         <v>56</v>
@@ -11343,7 +11340,7 @@
         <v>62</v>
       </c>
       <c r="K120" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L120" t="s">
         <v>1</v>
@@ -11405,7 +11402,7 @@
         <v>34710</v>
       </c>
       <c r="D121" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E121">
         <v>56</v>
@@ -11423,7 +11420,7 @@
         <v>62</v>
       </c>
       <c r="K121" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L121" t="s">
         <v>1</v>
@@ -11485,7 +11482,7 @@
         <v>34711</v>
       </c>
       <c r="D122" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E122">
         <v>56</v>
@@ -11503,7 +11500,7 @@
         <v>62</v>
       </c>
       <c r="K122" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L122" t="s">
         <v>1</v>
@@ -11565,7 +11562,7 @@
         <v>34712</v>
       </c>
       <c r="D123" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E123">
         <v>56</v>
@@ -11583,7 +11580,7 @@
         <v>62</v>
       </c>
       <c r="K123" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L123" t="s">
         <v>1</v>
@@ -11645,7 +11642,7 @@
         <v>34714</v>
       </c>
       <c r="D124" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E124">
         <v>56</v>
@@ -11663,7 +11660,7 @@
         <v>62</v>
       </c>
       <c r="K124" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L124" t="s">
         <v>1</v>
@@ -11725,7 +11722,7 @@
         <v>34715</v>
       </c>
       <c r="D125" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E125">
         <v>56</v>
@@ -11743,7 +11740,7 @@
         <v>62</v>
       </c>
       <c r="K125" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L125" t="s">
         <v>1</v>
@@ -11805,7 +11802,7 @@
         <v>34716</v>
       </c>
       <c r="D126" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E126">
         <v>56</v>
@@ -11823,7 +11820,7 @@
         <v>62</v>
       </c>
       <c r="K126" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L126" t="s">
         <v>1</v>
@@ -11885,7 +11882,7 @@
         <v>34717</v>
       </c>
       <c r="D127" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E127">
         <v>56</v>
@@ -11903,7 +11900,7 @@
         <v>62</v>
       </c>
       <c r="K127" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L127" t="s">
         <v>1</v>
@@ -11965,7 +11962,7 @@
         <v>34593</v>
       </c>
       <c r="D128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E128">
         <v>12</v>
@@ -12045,7 +12042,7 @@
         <v>34594</v>
       </c>
       <c r="D129" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E129">
         <v>49</v>
@@ -12054,7 +12051,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I129" t="s">
         <v>78</v>
@@ -12063,10 +12060,10 @@
         <v>62</v>
       </c>
       <c r="K129" t="s">
+        <v>324</v>
+      </c>
+      <c r="L129" t="s">
         <v>325</v>
-      </c>
-      <c r="L129" t="s">
-        <v>326</v>
       </c>
       <c r="M129" t="s">
         <v>1</v>
@@ -12125,7 +12122,7 @@
         <v>34595</v>
       </c>
       <c r="D130" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E130">
         <v>48</v>
@@ -12134,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I130" t="s">
         <v>78</v>
@@ -12143,13 +12140,13 @@
         <v>62</v>
       </c>
       <c r="K130" t="s">
+        <v>327</v>
+      </c>
+      <c r="L130" t="s">
         <v>328</v>
       </c>
-      <c r="L130" t="s">
+      <c r="M130" t="s">
         <v>329</v>
-      </c>
-      <c r="M130" t="s">
-        <v>330</v>
       </c>
       <c r="N130">
         <v>6</v>
@@ -12205,7 +12202,7 @@
         <v>34596</v>
       </c>
       <c r="D131" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E131">
         <v>50</v>
@@ -12223,7 +12220,7 @@
         <v>62</v>
       </c>
       <c r="K131" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L131" t="s">
         <v>1</v>
@@ -12285,7 +12282,7 @@
         <v>34612</v>
       </c>
       <c r="D132" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E132">
         <v>5</v>
@@ -12303,7 +12300,7 @@
         <v>62</v>
       </c>
       <c r="K132" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L132" t="s">
         <v>1</v>
@@ -12365,7 +12362,7 @@
         <v>34613</v>
       </c>
       <c r="D133" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E133">
         <v>5</v>
@@ -12374,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I133" t="s">
         <v>78</v>
@@ -12383,7 +12380,7 @@
         <v>62</v>
       </c>
       <c r="K133" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L133" t="s">
         <v>1</v>
@@ -12445,7 +12442,7 @@
         <v>34614</v>
       </c>
       <c r="D134" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E134">
         <v>4</v>
@@ -12454,7 +12451,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I134" t="s">
         <v>78</v>
@@ -12463,7 +12460,7 @@
         <v>62</v>
       </c>
       <c r="K134" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L134" t="s">
         <v>1</v>
@@ -12525,7 +12522,7 @@
         <v>34615</v>
       </c>
       <c r="D135" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E135">
         <v>44</v>
@@ -12543,7 +12540,7 @@
         <v>62</v>
       </c>
       <c r="K135" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L135" t="s">
         <v>1</v>
@@ -12605,7 +12602,7 @@
         <v>34616</v>
       </c>
       <c r="D136" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -12614,7 +12611,7 @@
         <v>3</v>
       </c>
       <c r="G136" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I136" t="s">
         <v>78</v>
@@ -12623,7 +12620,7 @@
         <v>62</v>
       </c>
       <c r="K136" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L136" t="s">
         <v>1</v>
@@ -12685,7 +12682,7 @@
         <v>34617</v>
       </c>
       <c r="D137" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -12703,7 +12700,7 @@
         <v>62</v>
       </c>
       <c r="K137" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L137" t="s">
         <v>1</v>
@@ -12765,7 +12762,7 @@
         <v>34618</v>
       </c>
       <c r="D138" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E138">
         <v>16</v>
@@ -12774,7 +12771,7 @@
         <v>9</v>
       </c>
       <c r="G138" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I138" t="s">
         <v>78</v>
@@ -12783,10 +12780,10 @@
         <v>62</v>
       </c>
       <c r="K138" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L138" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M138" t="s">
         <v>1</v>
@@ -12845,7 +12842,7 @@
         <v>34619</v>
       </c>
       <c r="D139" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E139">
         <v>20</v>
@@ -12863,13 +12860,13 @@
         <v>62</v>
       </c>
       <c r="K139" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L139" t="s">
+        <v>342</v>
+      </c>
+      <c r="M139" t="s">
         <v>343</v>
-      </c>
-      <c r="M139" t="s">
-        <v>344</v>
       </c>
       <c r="N139">
         <v>6</v>
@@ -12925,7 +12922,7 @@
         <v>34620</v>
       </c>
       <c r="D140" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E140">
         <v>4</v>
@@ -12943,7 +12940,7 @@
         <v>62</v>
       </c>
       <c r="K140" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L140" t="s">
         <v>1</v>
@@ -13005,7 +13002,7 @@
         <v>34621</v>
       </c>
       <c r="D141" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E141">
         <v>54</v>
@@ -13023,7 +13020,7 @@
         <v>62</v>
       </c>
       <c r="K141" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L141" t="s">
         <v>1</v>
@@ -13085,7 +13082,7 @@
         <v>34629</v>
       </c>
       <c r="D142" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E142">
         <v>4</v>
@@ -13094,7 +13091,7 @@
         <v>2</v>
       </c>
       <c r="G142" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I142" t="s">
         <v>78</v>
@@ -13103,7 +13100,7 @@
         <v>62</v>
       </c>
       <c r="K142" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L142" t="s">
         <v>1</v>
@@ -13165,7 +13162,7 @@
         <v>34630</v>
       </c>
       <c r="D143" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E143">
         <v>5</v>
@@ -13174,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I143" t="s">
         <v>78</v>
@@ -13183,7 +13180,7 @@
         <v>62</v>
       </c>
       <c r="K143" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L143" t="s">
         <v>1</v>
@@ -13245,7 +13242,7 @@
         <v>34631</v>
       </c>
       <c r="D144" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E144">
         <v>19</v>
@@ -13263,7 +13260,7 @@
         <v>62</v>
       </c>
       <c r="K144" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L144" t="s">
         <v>1</v>
@@ -13325,7 +13322,7 @@
         <v>34633</v>
       </c>
       <c r="D145" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E145">
         <v>43</v>
@@ -13334,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I145" t="s">
         <v>78</v>
@@ -13343,10 +13340,10 @@
         <v>62</v>
       </c>
       <c r="K145" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L145" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M145" t="s">
         <v>1</v>
@@ -13405,7 +13402,7 @@
         <v>34634</v>
       </c>
       <c r="D146" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -13414,7 +13411,7 @@
         <v>4</v>
       </c>
       <c r="G146" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I146" t="s">
         <v>78</v>
@@ -13423,7 +13420,7 @@
         <v>62</v>
       </c>
       <c r="K146" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L146" t="s">
         <v>1</v>
@@ -13485,7 +13482,7 @@
         <v>34636</v>
       </c>
       <c r="D147" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E147">
         <v>4</v>
@@ -13494,7 +13491,7 @@
         <v>3</v>
       </c>
       <c r="G147" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I147" t="s">
         <v>78</v>
@@ -13503,7 +13500,7 @@
         <v>62</v>
       </c>
       <c r="K147" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L147" t="s">
         <v>1</v>
@@ -13565,7 +13562,7 @@
         <v>34639</v>
       </c>
       <c r="D148" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E148">
         <v>16</v>
@@ -13583,10 +13580,10 @@
         <v>62</v>
       </c>
       <c r="K148" t="s">
+        <v>355</v>
+      </c>
+      <c r="L148" t="s">
         <v>356</v>
-      </c>
-      <c r="L148" t="s">
-        <v>357</v>
       </c>
       <c r="M148" t="s">
         <v>1</v>
@@ -13645,7 +13642,7 @@
         <v>34640</v>
       </c>
       <c r="D149" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E149">
         <v>16</v>
@@ -13654,7 +13651,7 @@
         <v>2</v>
       </c>
       <c r="G149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I149" t="s">
         <v>78</v>
@@ -13666,7 +13663,7 @@
         <v>79</v>
       </c>
       <c r="L149" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M149" t="s">
         <v>1</v>
@@ -13725,7 +13722,7 @@
         <v>34641</v>
       </c>
       <c r="D150" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -13743,7 +13740,7 @@
         <v>62</v>
       </c>
       <c r="K150" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L150" t="s">
         <v>1</v>
@@ -13805,7 +13802,7 @@
         <v>34644</v>
       </c>
       <c r="D151" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E151">
         <v>5</v>
@@ -13814,7 +13811,7 @@
         <v>2</v>
       </c>
       <c r="G151" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I151" t="s">
         <v>78</v>
@@ -13823,7 +13820,7 @@
         <v>62</v>
       </c>
       <c r="K151" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L151" t="s">
         <v>1</v>
@@ -13885,7 +13882,7 @@
         <v>34645</v>
       </c>
       <c r="D152" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E152">
         <v>3</v>
@@ -13903,7 +13900,7 @@
         <v>62</v>
       </c>
       <c r="K152" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L152" t="s">
         <v>1</v>
@@ -13965,7 +13962,7 @@
         <v>34649</v>
       </c>
       <c r="D153" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E153">
         <v>5</v>
@@ -13974,7 +13971,7 @@
         <v>2</v>
       </c>
       <c r="G153" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I153" t="s">
         <v>78</v>
@@ -13983,7 +13980,7 @@
         <v>62</v>
       </c>
       <c r="K153" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L153" t="s">
         <v>1</v>
@@ -14045,7 +14042,7 @@
         <v>34676</v>
       </c>
       <c r="D154" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E154">
         <v>16</v>
@@ -14054,7 +14051,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I154" t="s">
         <v>78</v>
@@ -14063,10 +14060,10 @@
         <v>62</v>
       </c>
       <c r="K154" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L154" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M154" t="s">
         <v>1</v>
@@ -14125,7 +14122,7 @@
         <v>34686</v>
       </c>
       <c r="D155" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E155">
         <v>18</v>
@@ -14143,7 +14140,7 @@
         <v>62</v>
       </c>
       <c r="K155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L155" t="s">
         <v>1</v>
@@ -14205,7 +14202,7 @@
         <v>34688</v>
       </c>
       <c r="D156" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E156">
         <v>4</v>
@@ -14214,7 +14211,7 @@
         <v>3</v>
       </c>
       <c r="G156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I156" t="s">
         <v>78</v>
@@ -14223,7 +14220,7 @@
         <v>62</v>
       </c>
       <c r="K156" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L156" t="s">
         <v>1</v>
@@ -14285,7 +14282,7 @@
         <v>34691</v>
       </c>
       <c r="D157" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E157">
         <v>5</v>
@@ -14294,7 +14291,7 @@
         <v>5</v>
       </c>
       <c r="G157" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I157" t="s">
         <v>78</v>
@@ -14303,7 +14300,7 @@
         <v>62</v>
       </c>
       <c r="K157" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L157" t="s">
         <v>1</v>
@@ -14365,7 +14362,7 @@
         <v>34692</v>
       </c>
       <c r="D158" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E158">
         <v>4</v>
@@ -14374,7 +14371,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I158" t="s">
         <v>78</v>
@@ -14383,7 +14380,7 @@
         <v>62</v>
       </c>
       <c r="K158" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L158" t="s">
         <v>1</v>
@@ -14445,7 +14442,7 @@
         <v>34693</v>
       </c>
       <c r="D159" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E159">
         <v>13</v>
@@ -14463,10 +14460,10 @@
         <v>62</v>
       </c>
       <c r="K159" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L159" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M159" t="s">
         <v>1</v>
@@ -14525,7 +14522,7 @@
         <v>34694</v>
       </c>
       <c r="D160" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E160">
         <v>17</v>
@@ -14543,10 +14540,10 @@
         <v>62</v>
       </c>
       <c r="K160" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L160" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M160" t="s">
         <v>1</v>
@@ -14605,7 +14602,7 @@
         <v>34695</v>
       </c>
       <c r="D161" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E161">
         <v>5</v>
@@ -14614,7 +14611,7 @@
         <v>6</v>
       </c>
       <c r="G161" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I161" t="s">
         <v>78</v>
@@ -14623,7 +14620,7 @@
         <v>62</v>
       </c>
       <c r="K161" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L161" t="s">
         <v>1</v>
@@ -14685,7 +14682,7 @@
         <v>34718</v>
       </c>
       <c r="D162" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E162">
         <v>30</v>
@@ -14694,7 +14691,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I162" t="s">
         <v>78</v>
@@ -14703,10 +14700,10 @@
         <v>62</v>
       </c>
       <c r="K162" t="s">
+        <v>377</v>
+      </c>
+      <c r="L162" t="s">
         <v>378</v>
-      </c>
-      <c r="L162" t="s">
-        <v>379</v>
       </c>
       <c r="M162" t="s">
         <v>1</v>
@@ -14765,7 +14762,7 @@
         <v>34730</v>
       </c>
       <c r="D163" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -14786,7 +14783,7 @@
         <v>6</v>
       </c>
       <c r="P163" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -14800,7 +14797,7 @@
         <v>34732</v>
       </c>
       <c r="D164" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E164">
         <v>2</v>
@@ -14821,7 +14818,7 @@
         <v>6</v>
       </c>
       <c r="P164" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -14835,7 +14832,7 @@
         <v>34733</v>
       </c>
       <c r="D165" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E165">
         <v>2</v>
@@ -14856,7 +14853,7 @@
         <v>6</v>
       </c>
       <c r="P165" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:27">
@@ -14870,7 +14867,7 @@
         <v>34722</v>
       </c>
       <c r="D166" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E166">
         <v>31</v>
@@ -14888,7 +14885,7 @@
         <v>62</v>
       </c>
       <c r="K166" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L166" t="s">
         <v>1</v>
@@ -14950,7 +14947,7 @@
         <v>34734</v>
       </c>
       <c r="D167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E167">
         <v>57</v>
@@ -14968,13 +14965,13 @@
         <v>62</v>
       </c>
       <c r="K167" t="s">
+        <v>388</v>
+      </c>
+      <c r="L167" t="s">
         <v>389</v>
       </c>
-      <c r="L167" t="s">
+      <c r="M167" t="s">
         <v>390</v>
-      </c>
-      <c r="M167" t="s">
-        <v>391</v>
       </c>
       <c r="N167">
         <v>6</v>
@@ -15030,7 +15027,7 @@
         <v>34735</v>
       </c>
       <c r="D168" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E168">
         <v>32</v>
@@ -15048,7 +15045,7 @@
         <v>62</v>
       </c>
       <c r="K168" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L168" t="s">
         <v>1</v>
@@ -15110,7 +15107,7 @@
         <v>34736</v>
       </c>
       <c r="D169" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E169">
         <v>15</v>
@@ -15128,7 +15125,7 @@
         <v>62</v>
       </c>
       <c r="K169" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L169" t="s">
         <v>1</v>
@@ -15190,7 +15187,7 @@
         <v>34741</v>
       </c>
       <c r="D170" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E170">
         <v>31</v>
@@ -15199,7 +15196,7 @@
         <v>4</v>
       </c>
       <c r="G170" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I170" t="s">
         <v>78</v>
@@ -15208,7 +15205,7 @@
         <v>62</v>
       </c>
       <c r="K170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L170" t="s">
         <v>1</v>
@@ -15270,7 +15267,7 @@
         <v>34745</v>
       </c>
       <c r="D171" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E171">
         <v>31</v>
@@ -15279,7 +15276,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I171" t="s">
         <v>78</v>
@@ -15288,7 +15285,7 @@
         <v>62</v>
       </c>
       <c r="K171" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L171" t="s">
         <v>1</v>
@@ -15350,7 +15347,7 @@
         <v>34746</v>
       </c>
       <c r="D172" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E172">
         <v>31</v>
@@ -15359,7 +15356,7 @@
         <v>3</v>
       </c>
       <c r="G172" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I172" t="s">
         <v>78</v>
@@ -15368,7 +15365,7 @@
         <v>62</v>
       </c>
       <c r="K172" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L172" t="s">
         <v>1</v>
@@ -15430,7 +15427,7 @@
         <v>34747</v>
       </c>
       <c r="D173" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E173">
         <v>31</v>
@@ -15448,7 +15445,7 @@
         <v>62</v>
       </c>
       <c r="K173" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L173" t="s">
         <v>1</v>
@@ -15510,7 +15507,7 @@
         <v>34748</v>
       </c>
       <c r="D174" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E174">
         <v>31</v>
@@ -15528,7 +15525,7 @@
         <v>62</v>
       </c>
       <c r="K174" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L174" t="s">
         <v>1</v>
@@ -15590,7 +15587,7 @@
         <v>34749</v>
       </c>
       <c r="D175" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E175">
         <v>31</v>
@@ -15599,7 +15596,7 @@
         <v>3</v>
       </c>
       <c r="G175" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I175" t="s">
         <v>78</v>
@@ -15608,7 +15605,7 @@
         <v>62</v>
       </c>
       <c r="K175" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L175" t="s">
         <v>1</v>
@@ -15670,7 +15667,7 @@
         <v>34750</v>
       </c>
       <c r="D176" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E176">
         <v>31</v>
@@ -15679,7 +15676,7 @@
         <v>2</v>
       </c>
       <c r="G176" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I176" t="s">
         <v>78</v>
@@ -15688,7 +15685,7 @@
         <v>62</v>
       </c>
       <c r="K176" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L176" t="s">
         <v>1</v>
@@ -15750,7 +15747,7 @@
         <v>34751</v>
       </c>
       <c r="D177" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E177">
         <v>31</v>
@@ -15759,7 +15756,7 @@
         <v>2</v>
       </c>
       <c r="G177" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I177" t="s">
         <v>78</v>
@@ -15768,7 +15765,7 @@
         <v>62</v>
       </c>
       <c r="K177" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L177" t="s">
         <v>1</v>
@@ -15830,7 +15827,7 @@
         <v>34752</v>
       </c>
       <c r="D178" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E178">
         <v>31</v>
@@ -15848,7 +15845,7 @@
         <v>62</v>
       </c>
       <c r="K178" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L178" t="s">
         <v>1</v>
@@ -15910,7 +15907,7 @@
         <v>34753</v>
       </c>
       <c r="D179" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E179">
         <v>31</v>
@@ -15928,7 +15925,7 @@
         <v>62</v>
       </c>
       <c r="K179" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L179" t="s">
         <v>1</v>
@@ -15990,7 +15987,7 @@
         <v>34754</v>
       </c>
       <c r="D180" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E180">
         <v>31</v>
@@ -16008,7 +16005,7 @@
         <v>62</v>
       </c>
       <c r="K180" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L180" t="s">
         <v>1</v>
@@ -16070,7 +16067,7 @@
         <v>34757</v>
       </c>
       <c r="D181" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E181">
         <v>31</v>
@@ -16079,7 +16076,7 @@
         <v>3</v>
       </c>
       <c r="G181" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I181" t="s">
         <v>78</v>
@@ -16088,7 +16085,7 @@
         <v>62</v>
       </c>
       <c r="K181" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L181" t="s">
         <v>1</v>
@@ -16150,7 +16147,7 @@
         <v>34759</v>
       </c>
       <c r="D182" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E182">
         <v>31</v>
@@ -16159,7 +16156,7 @@
         <v>3</v>
       </c>
       <c r="G182" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I182" t="s">
         <v>78</v>
@@ -16168,7 +16165,7 @@
         <v>62</v>
       </c>
       <c r="K182" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L182" t="s">
         <v>1</v>
@@ -16230,7 +16227,7 @@
         <v>34760</v>
       </c>
       <c r="D183" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E183">
         <v>32</v>
@@ -16248,7 +16245,7 @@
         <v>62</v>
       </c>
       <c r="K183" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L183" t="s">
         <v>1</v>
@@ -16310,7 +16307,7 @@
         <v>34764</v>
       </c>
       <c r="D184" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E184">
         <v>32</v>
@@ -16319,7 +16316,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I184" t="s">
         <v>78</v>
@@ -16328,7 +16325,7 @@
         <v>62</v>
       </c>
       <c r="K184" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L184" t="s">
         <v>1</v>
@@ -16390,7 +16387,7 @@
         <v>34765</v>
       </c>
       <c r="D185" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E185">
         <v>57</v>
@@ -16408,13 +16405,13 @@
         <v>62</v>
       </c>
       <c r="K185" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L185" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M185" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N185">
         <v>6</v>
@@ -16470,7 +16467,7 @@
         <v>34766</v>
       </c>
       <c r="D186" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E186">
         <v>57</v>
@@ -16479,7 +16476,7 @@
         <v>1</v>
       </c>
       <c r="G186" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I186" t="s">
         <v>61</v>
@@ -16488,13 +16485,13 @@
         <v>62</v>
       </c>
       <c r="K186" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L186" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M186" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N186">
         <v>6</v>
@@ -16550,7 +16547,7 @@
         <v>34768</v>
       </c>
       <c r="D187" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E187">
         <v>31</v>
@@ -16559,7 +16556,7 @@
         <v>2</v>
       </c>
       <c r="G187" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I187" t="s">
         <v>78</v>
@@ -16568,7 +16565,7 @@
         <v>62</v>
       </c>
       <c r="K187" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L187" t="s">
         <v>1</v>
@@ -16630,7 +16627,7 @@
         <v>34769</v>
       </c>
       <c r="D188" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E188">
         <v>15</v>
@@ -16648,7 +16645,7 @@
         <v>62</v>
       </c>
       <c r="K188" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L188" t="s">
         <v>1</v>
@@ -16710,7 +16707,7 @@
         <v>34772</v>
       </c>
       <c r="D189" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E189">
         <v>15</v>
@@ -16728,7 +16725,7 @@
         <v>62</v>
       </c>
       <c r="K189" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L189" t="s">
         <v>1</v>
@@ -16790,7 +16787,7 @@
         <v>34773</v>
       </c>
       <c r="D190" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E190">
         <v>15</v>
@@ -16808,7 +16805,7 @@
         <v>62</v>
       </c>
       <c r="K190" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L190" t="s">
         <v>1</v>
@@ -16870,7 +16867,7 @@
         <v>34774</v>
       </c>
       <c r="D191" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E191">
         <v>15</v>
@@ -16888,7 +16885,7 @@
         <v>62</v>
       </c>
       <c r="K191" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L191" t="s">
         <v>1</v>
@@ -16950,7 +16947,7 @@
         <v>74852</v>
       </c>
       <c r="D192" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E192">
         <v>12</v>
@@ -17030,7 +17027,7 @@
         <v>74854</v>
       </c>
       <c r="D193" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E193">
         <v>5</v>
@@ -17039,10 +17036,10 @@
         <v>1</v>
       </c>
       <c r="G193" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H193" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I193" t="s">
         <v>78</v>
@@ -17051,7 +17048,7 @@
         <v>62</v>
       </c>
       <c r="K193" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L193" t="s">
         <v>1</v>
@@ -17078,7 +17075,7 @@
         <v>0</v>
       </c>
       <c r="T193" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U193">
         <v>0</v>
@@ -17113,7 +17110,7 @@
         <v>74856</v>
       </c>
       <c r="D194" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E194">
         <v>2</v>
@@ -17134,7 +17131,7 @@
         <v>7</v>
       </c>
       <c r="P194" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="195" spans="1:27">
@@ -17148,7 +17145,7 @@
         <v>74857</v>
       </c>
       <c r="D195" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E195">
         <v>6</v>
@@ -17157,10 +17154,10 @@
         <v>0</v>
       </c>
       <c r="G195" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H195" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I195" t="s">
         <v>78</v>
@@ -17169,13 +17166,13 @@
         <v>62</v>
       </c>
       <c r="K195" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L195" t="s">
         <v>1</v>
       </c>
       <c r="M195" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N195">
         <v>7</v>
@@ -17228,7 +17225,7 @@
         <v>74858</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E196">
         <v>7</v>
@@ -17237,10 +17234,10 @@
         <v>0</v>
       </c>
       <c r="G196" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I196" t="s">
         <v>78</v>
@@ -17249,10 +17246,10 @@
         <v>62</v>
       </c>
       <c r="K196" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L196" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M196" t="s">
         <v>1</v>
@@ -17308,7 +17305,7 @@
         <v>74859</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E197">
         <v>7</v>
@@ -17317,10 +17314,10 @@
         <v>0</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H197" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I197" t="s">
         <v>78</v>
@@ -17329,10 +17326,10 @@
         <v>62</v>
       </c>
       <c r="K197" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L197" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M197" t="s">
         <v>1</v>
@@ -17388,7 +17385,7 @@
         <v>74860</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E198">
         <v>7</v>
@@ -17397,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="G198" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H198" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I198" t="s">
         <v>78</v>
@@ -17409,10 +17406,10 @@
         <v>62</v>
       </c>
       <c r="K198" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L198" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M198" t="s">
         <v>1</v>
@@ -17468,7 +17465,7 @@
         <v>84928</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E199">
         <v>12</v>
@@ -17548,7 +17545,7 @@
         <v>84929</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E200">
         <v>30</v>
@@ -17557,10 +17554,10 @@
         <v>0</v>
       </c>
       <c r="G200" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H200" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I200" t="s">
         <v>78</v>
@@ -17569,10 +17566,10 @@
         <v>62</v>
       </c>
       <c r="K200" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L200" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M200" t="s">
         <v>1</v>
@@ -17628,7 +17625,7 @@
         <v>84930</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E201">
         <v>57</v>
@@ -17637,7 +17634,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I201" t="s">
         <v>61</v>
@@ -17646,13 +17643,13 @@
         <v>62</v>
       </c>
       <c r="K201" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L201" t="s">
+        <v>444</v>
+      </c>
+      <c r="M201" t="s">
         <v>445</v>
-      </c>
-      <c r="M201" t="s">
-        <v>446</v>
       </c>
       <c r="N201">
         <v>8</v>
@@ -17705,7 +17702,7 @@
         <v>84931</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E202">
         <v>32</v>
@@ -17714,10 +17711,10 @@
         <v>1</v>
       </c>
       <c r="G202" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H202" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I202" t="s">
         <v>78</v>
@@ -17726,7 +17723,7 @@
         <v>62</v>
       </c>
       <c r="K202" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L202" t="s">
         <v>1</v>
@@ -17785,7 +17782,7 @@
         <v>84932</v>
       </c>
       <c r="D203" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E203">
         <v>57</v>
@@ -17803,13 +17800,13 @@
         <v>62</v>
       </c>
       <c r="K203" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L203" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M203" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N203">
         <v>8</v>
@@ -17862,7 +17859,7 @@
         <v>84933</v>
       </c>
       <c r="D204" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E204">
         <v>32</v>
@@ -17874,7 +17871,7 @@
         <v>60</v>
       </c>
       <c r="H204" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I204" t="s">
         <v>78</v>
@@ -17883,7 +17880,7 @@
         <v>62</v>
       </c>
       <c r="K204" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L204" t="s">
         <v>1</v>
@@ -17942,7 +17939,7 @@
         <v>84934</v>
       </c>
       <c r="D205" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E205">
         <v>31</v>
@@ -17951,10 +17948,10 @@
         <v>1</v>
       </c>
       <c r="G205" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H205" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I205" t="s">
         <v>78</v>
@@ -17963,7 +17960,7 @@
         <v>62</v>
       </c>
       <c r="K205" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L205" t="s">
         <v>1</v>
@@ -18022,7 +18019,7 @@
         <v>84935</v>
       </c>
       <c r="D206" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E206">
         <v>31</v>
@@ -18034,7 +18031,7 @@
         <v>60</v>
       </c>
       <c r="H206" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I206" t="s">
         <v>78</v>
@@ -18043,7 +18040,7 @@
         <v>62</v>
       </c>
       <c r="K206" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L206" t="s">
         <v>1</v>
@@ -18102,7 +18099,7 @@
         <v>84936</v>
       </c>
       <c r="D207" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E207">
         <v>31</v>
@@ -18114,7 +18111,7 @@
         <v>60</v>
       </c>
       <c r="H207" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I207" t="s">
         <v>78</v>
@@ -18123,7 +18120,7 @@
         <v>62</v>
       </c>
       <c r="K207" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L207" t="s">
         <v>1</v>
@@ -18182,7 +18179,7 @@
         <v>84937</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E208">
         <v>31</v>
@@ -18191,10 +18188,10 @@
         <v>4</v>
       </c>
       <c r="G208" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H208" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I208" t="s">
         <v>78</v>
@@ -18203,7 +18200,7 @@
         <v>62</v>
       </c>
       <c r="K208" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L208" t="s">
         <v>1</v>
@@ -18262,7 +18259,7 @@
         <v>84938</v>
       </c>
       <c r="D209" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E209">
         <v>31</v>
@@ -18274,7 +18271,7 @@
         <v>60</v>
       </c>
       <c r="H209" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I209" t="s">
         <v>78</v>
@@ -18283,7 +18280,7 @@
         <v>62</v>
       </c>
       <c r="K209" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L209" t="s">
         <v>1</v>
@@ -18342,7 +18339,7 @@
         <v>84939</v>
       </c>
       <c r="D210" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E210">
         <v>15</v>
@@ -18354,7 +18351,7 @@
         <v>60</v>
       </c>
       <c r="H210" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I210" t="s">
         <v>78</v>
@@ -18363,7 +18360,7 @@
         <v>62</v>
       </c>
       <c r="K210" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L210" t="s">
         <v>1</v>
@@ -18422,7 +18419,7 @@
         <v>84940</v>
       </c>
       <c r="D211" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E211">
         <v>15</v>
@@ -18434,7 +18431,7 @@
         <v>60</v>
       </c>
       <c r="H211" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I211" t="s">
         <v>78</v>
@@ -18443,7 +18440,7 @@
         <v>62</v>
       </c>
       <c r="K211" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L211" t="s">
         <v>1</v>
@@ -18502,7 +18499,7 @@
         <v>84941</v>
       </c>
       <c r="D212" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E212">
         <v>16</v>
@@ -18514,7 +18511,7 @@
         <v>60</v>
       </c>
       <c r="H212" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I212" t="s">
         <v>78</v>
@@ -18523,10 +18520,10 @@
         <v>62</v>
       </c>
       <c r="K212" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L212" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M212" t="s">
         <v>1</v>
@@ -18582,7 +18579,7 @@
         <v>84942</v>
       </c>
       <c r="D213" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E213">
         <v>52</v>
@@ -18600,13 +18597,13 @@
         <v>62</v>
       </c>
       <c r="K213" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L213" t="s">
+        <v>470</v>
+      </c>
+      <c r="M213" t="s">
         <v>471</v>
-      </c>
-      <c r="M213" t="s">
-        <v>472</v>
       </c>
       <c r="N213">
         <v>8</v>
@@ -18659,7 +18656,7 @@
         <v>84943</v>
       </c>
       <c r="D214" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E214">
         <v>51</v>
@@ -18671,7 +18668,7 @@
         <v>60</v>
       </c>
       <c r="H214" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I214" t="s">
         <v>78</v>
@@ -18680,7 +18677,7 @@
         <v>62</v>
       </c>
       <c r="K214" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L214" t="s">
         <v>1</v>
@@ -18739,7 +18736,7 @@
         <v>84944</v>
       </c>
       <c r="D215" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E215">
         <v>52</v>
@@ -18757,13 +18754,13 @@
         <v>62</v>
       </c>
       <c r="K215" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L215" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M215" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N215">
         <v>8</v>
@@ -18816,7 +18813,7 @@
         <v>84945</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E216">
         <v>51</v>
@@ -18828,7 +18825,7 @@
         <v>60</v>
       </c>
       <c r="H216" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I216" t="s">
         <v>78</v>
@@ -18837,7 +18834,7 @@
         <v>62</v>
       </c>
       <c r="K216" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L216" t="s">
         <v>1</v>
@@ -18896,7 +18893,7 @@
         <v>84946</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E217">
         <v>56</v>
@@ -18914,7 +18911,7 @@
         <v>62</v>
       </c>
       <c r="K217" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L217" t="s">
         <v>1</v>
@@ -18973,7 +18970,7 @@
         <v>84947</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E218">
         <v>56</v>
@@ -18991,7 +18988,7 @@
         <v>62</v>
       </c>
       <c r="K218" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L218" t="s">
         <v>1</v>
@@ -19050,7 +19047,7 @@
         <v>84948</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E219">
         <v>56</v>
@@ -19068,7 +19065,7 @@
         <v>62</v>
       </c>
       <c r="K219" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L219" t="s">
         <v>1</v>
@@ -19127,7 +19124,7 @@
         <v>84949</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E220">
         <v>56</v>
@@ -19145,7 +19142,7 @@
         <v>62</v>
       </c>
       <c r="K220" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L220" t="s">
         <v>1</v>
@@ -19204,7 +19201,7 @@
         <v>84950</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E221">
         <v>56</v>
@@ -19222,7 +19219,7 @@
         <v>62</v>
       </c>
       <c r="K221" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L221" t="s">
         <v>1</v>
@@ -19281,7 +19278,7 @@
         <v>84951</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E222">
         <v>56</v>
@@ -19299,7 +19296,7 @@
         <v>62</v>
       </c>
       <c r="K222" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L222" t="s">
         <v>1</v>
@@ -19358,7 +19355,7 @@
         <v>84952</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E223">
         <v>56</v>
@@ -19376,7 +19373,7 @@
         <v>62</v>
       </c>
       <c r="K223" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L223" t="s">
         <v>1</v>
@@ -19435,7 +19432,7 @@
         <v>84953</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E224">
         <v>56</v>
@@ -19453,7 +19450,7 @@
         <v>62</v>
       </c>
       <c r="K224" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L224" t="s">
         <v>1</v>
@@ -19512,7 +19509,7 @@
         <v>84954</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E225">
         <v>56</v>
@@ -19530,7 +19527,7 @@
         <v>62</v>
       </c>
       <c r="K225" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L225" t="s">
         <v>1</v>
@@ -19589,7 +19586,7 @@
         <v>84955</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E226">
         <v>56</v>
@@ -19607,7 +19604,7 @@
         <v>62</v>
       </c>
       <c r="K226" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L226" t="s">
         <v>1</v>
@@ -19666,7 +19663,7 @@
         <v>84956</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E227">
         <v>56</v>
@@ -19684,7 +19681,7 @@
         <v>62</v>
       </c>
       <c r="K227" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L227" t="s">
         <v>1</v>
@@ -19743,7 +19740,7 @@
         <v>84957</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E228">
         <v>56</v>
@@ -19761,7 +19758,7 @@
         <v>62</v>
       </c>
       <c r="K228" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L228" t="s">
         <v>1</v>
@@ -19820,7 +19817,7 @@
         <v>84958</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E229">
         <v>56</v>
@@ -19838,7 +19835,7 @@
         <v>62</v>
       </c>
       <c r="K229" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L229" t="s">
         <v>1</v>
@@ -19897,7 +19894,7 @@
         <v>84959</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E230">
         <v>56</v>
@@ -19915,7 +19912,7 @@
         <v>62</v>
       </c>
       <c r="K230" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L230" t="s">
         <v>1</v>
@@ -19974,7 +19971,7 @@
         <v>84960</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E231">
         <v>56</v>
@@ -19992,7 +19989,7 @@
         <v>62</v>
       </c>
       <c r="K231" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L231" t="s">
         <v>1</v>
@@ -20051,7 +20048,7 @@
         <v>84961</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E232">
         <v>56</v>
@@ -20069,7 +20066,7 @@
         <v>62</v>
       </c>
       <c r="K232" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L232" t="s">
         <v>1</v>
@@ -20128,7 +20125,7 @@
         <v>84962</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E233">
         <v>56</v>
@@ -20146,7 +20143,7 @@
         <v>62</v>
       </c>
       <c r="K233" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L233" t="s">
         <v>1</v>
@@ -20205,7 +20202,7 @@
         <v>84963</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E234">
         <v>56</v>
@@ -20223,7 +20220,7 @@
         <v>62</v>
       </c>
       <c r="K234" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L234" t="s">
         <v>1</v>
@@ -20282,7 +20279,7 @@
         <v>84964</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E235">
         <v>56</v>
@@ -20300,7 +20297,7 @@
         <v>62</v>
       </c>
       <c r="K235" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L235" t="s">
         <v>1</v>
@@ -20359,7 +20356,7 @@
         <v>84965</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E236">
         <v>56</v>
@@ -20377,7 +20374,7 @@
         <v>62</v>
       </c>
       <c r="K236" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L236" t="s">
         <v>1</v>
@@ -20436,7 +20433,7 @@
         <v>84966</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E237">
         <v>56</v>
@@ -20454,7 +20451,7 @@
         <v>62</v>
       </c>
       <c r="K237" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L237" t="s">
         <v>1</v>
@@ -20513,7 +20510,7 @@
         <v>84967</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E238">
         <v>56</v>
@@ -20531,7 +20528,7 @@
         <v>62</v>
       </c>
       <c r="K238" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L238" t="s">
         <v>1</v>
@@ -20590,7 +20587,7 @@
         <v>84968</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E239">
         <v>56</v>
@@ -20608,7 +20605,7 @@
         <v>62</v>
       </c>
       <c r="K239" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L239" t="s">
         <v>1</v>
@@ -20667,7 +20664,7 @@
         <v>84969</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E240">
         <v>45</v>
@@ -20676,10 +20673,10 @@
         <v>0</v>
       </c>
       <c r="G240" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H240" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I240" t="s">
         <v>78</v>
@@ -20688,7 +20685,7 @@
         <v>62</v>
       </c>
       <c r="K240" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L240" t="s">
         <v>1</v>
@@ -20747,7 +20744,7 @@
         <v>84970</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E241">
         <v>46</v>
@@ -20756,10 +20753,10 @@
         <v>0</v>
       </c>
       <c r="G241" t="s">
+        <v>506</v>
+      </c>
+      <c r="H241" t="s">
         <v>507</v>
-      </c>
-      <c r="H241" t="s">
-        <v>508</v>
       </c>
       <c r="I241" t="s">
         <v>78</v>
@@ -20768,7 +20765,7 @@
         <v>62</v>
       </c>
       <c r="K241" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L241" t="s">
         <v>1</v>
@@ -20827,7 +20824,7 @@
         <v>84971</v>
       </c>
       <c r="D242" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E242">
         <v>47</v>
@@ -20836,10 +20833,10 @@
         <v>0</v>
       </c>
       <c r="G242" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H242" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I242" t="s">
         <v>78</v>
@@ -20848,13 +20845,13 @@
         <v>62</v>
       </c>
       <c r="K242" t="s">
+        <v>511</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1</v>
+      </c>
+      <c r="M242" t="s">
         <v>512</v>
-      </c>
-      <c r="L242" t="s">
-        <v>1</v>
-      </c>
-      <c r="M242" t="s">
-        <v>513</v>
       </c>
       <c r="N242">
         <v>8</v>
@@ -20907,7 +20904,7 @@
         <v>84972</v>
       </c>
       <c r="D243" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E243">
         <v>46</v>
@@ -20916,10 +20913,10 @@
         <v>0</v>
       </c>
       <c r="G243" t="s">
+        <v>514</v>
+      </c>
+      <c r="H243" t="s">
         <v>515</v>
-      </c>
-      <c r="H243" t="s">
-        <v>516</v>
       </c>
       <c r="I243" t="s">
         <v>78</v>
@@ -20928,7 +20925,7 @@
         <v>62</v>
       </c>
       <c r="K243" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L243" t="s">
         <v>1</v>
@@ -20987,7 +20984,7 @@
         <v>84973</v>
       </c>
       <c r="D244" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E244">
         <v>16</v>
@@ -20999,7 +20996,7 @@
         <v>60</v>
       </c>
       <c r="H244" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I244" t="s">
         <v>78</v>
@@ -21008,10 +21005,10 @@
         <v>62</v>
       </c>
       <c r="K244" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L244" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M244" t="s">
         <v>1</v>
@@ -21067,7 +21064,7 @@
         <v>84974</v>
       </c>
       <c r="D245" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E245">
         <v>46</v>
@@ -21079,7 +21076,7 @@
         <v>60</v>
       </c>
       <c r="H245" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I245" t="s">
         <v>78</v>
@@ -21088,7 +21085,7 @@
         <v>62</v>
       </c>
       <c r="K245" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L245" t="s">
         <v>1</v>
@@ -21147,7 +21144,7 @@
         <v>84976</v>
       </c>
       <c r="D246" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E246">
         <v>2</v>
@@ -21168,7 +21165,7 @@
         <v>8</v>
       </c>
       <c r="P246" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -21182,7 +21179,7 @@
         <v>84977</v>
       </c>
       <c r="D247" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E247">
         <v>2</v>
@@ -21203,7 +21200,7 @@
         <v>8</v>
       </c>
       <c r="P247" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -21217,7 +21214,7 @@
         <v>84978</v>
       </c>
       <c r="D248" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E248">
         <v>2</v>
@@ -21238,7 +21235,7 @@
         <v>8</v>
       </c>
       <c r="P248" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="249" spans="1:27">
@@ -21252,7 +21249,7 @@
         <v>84979</v>
       </c>
       <c r="D249" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E249">
         <v>48</v>
@@ -21261,10 +21258,10 @@
         <v>0</v>
       </c>
       <c r="G249" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H249" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I249" t="s">
         <v>78</v>
@@ -21273,13 +21270,13 @@
         <v>62</v>
       </c>
       <c r="K249" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L249" t="s">
+        <v>529</v>
+      </c>
+      <c r="M249" t="s">
         <v>530</v>
-      </c>
-      <c r="M249" t="s">
-        <v>531</v>
       </c>
       <c r="N249">
         <v>8</v>
@@ -21332,7 +21329,7 @@
         <v>84980</v>
       </c>
       <c r="D250" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E250">
         <v>49</v>
@@ -21344,7 +21341,7 @@
         <v>60</v>
       </c>
       <c r="H250" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I250" t="s">
         <v>78</v>
@@ -21353,10 +21350,10 @@
         <v>62</v>
       </c>
       <c r="K250" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L250" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="M250" t="s">
         <v>1</v>
@@ -21412,7 +21409,7 @@
         <v>84981</v>
       </c>
       <c r="D251" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E251">
         <v>50</v>
@@ -21424,7 +21421,7 @@
         <v>60</v>
       </c>
       <c r="H251" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I251" t="s">
         <v>78</v>
@@ -21433,7 +21430,7 @@
         <v>62</v>
       </c>
       <c r="K251" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L251" t="s">
         <v>1</v>
@@ -21492,7 +21489,7 @@
         <v>84982</v>
       </c>
       <c r="D252" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E252">
         <v>23</v>
@@ -21510,13 +21507,13 @@
         <v>62</v>
       </c>
       <c r="K252" t="s">
+        <v>537</v>
+      </c>
+      <c r="L252" t="s">
+        <v>1</v>
+      </c>
+      <c r="M252" t="s">
         <v>538</v>
-      </c>
-      <c r="L252" t="s">
-        <v>1</v>
-      </c>
-      <c r="M252" t="s">
-        <v>539</v>
       </c>
       <c r="N252">
         <v>8</v>
@@ -21572,7 +21569,7 @@
         <v>84983</v>
       </c>
       <c r="D253" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E253">
         <v>24</v>
@@ -21584,7 +21581,7 @@
         <v>60</v>
       </c>
       <c r="H253" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I253" t="s">
         <v>78</v>
@@ -21593,7 +21590,7 @@
         <v>62</v>
       </c>
       <c r="K253" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L253" t="s">
         <v>1</v>
@@ -21655,7 +21652,7 @@
         <v>84984</v>
       </c>
       <c r="D254" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E254">
         <v>25</v>
@@ -21667,7 +21664,7 @@
         <v>60</v>
       </c>
       <c r="H254" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I254" t="s">
         <v>78</v>
@@ -21676,7 +21673,7 @@
         <v>62</v>
       </c>
       <c r="K254" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L254" t="s">
         <v>1</v>
@@ -21738,7 +21735,7 @@
         <v>330037</v>
       </c>
       <c r="D255" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E255">
         <v>5</v>
@@ -21750,7 +21747,7 @@
         <v>60</v>
       </c>
       <c r="H255" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I255" t="s">
         <v>78</v>
@@ -21759,7 +21756,7 @@
         <v>62</v>
       </c>
       <c r="K255" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L255" t="s">
         <v>1</v>
@@ -21821,7 +21818,7 @@
         <v>330038</v>
       </c>
       <c r="D256" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E256">
         <v>6</v>
@@ -21830,10 +21827,10 @@
         <v>0</v>
       </c>
       <c r="G256" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H256" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I256" t="s">
         <v>78</v>
@@ -21842,13 +21839,13 @@
         <v>62</v>
       </c>
       <c r="K256" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L256" t="s">
         <v>1</v>
       </c>
       <c r="M256" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N256">
         <v>33</v>
@@ -21901,7 +21898,7 @@
         <v>330039</v>
       </c>
       <c r="D257" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E257">
         <v>7</v>
@@ -21910,10 +21907,10 @@
         <v>0</v>
       </c>
       <c r="G257" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H257" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I257" t="s">
         <v>78</v>
@@ -21922,10 +21919,10 @@
         <v>62</v>
       </c>
       <c r="K257" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L257" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M257" t="s">
         <v>1</v>
@@ -21981,7 +21978,7 @@
         <v>330040</v>
       </c>
       <c r="D258" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E258">
         <v>7</v>
@@ -21990,10 +21987,10 @@
         <v>0</v>
       </c>
       <c r="G258" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H258" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I258" t="s">
         <v>78</v>
@@ -22002,10 +21999,10 @@
         <v>62</v>
       </c>
       <c r="K258" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L258" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M258" t="s">
         <v>1</v>
@@ -22061,7 +22058,7 @@
         <v>330041</v>
       </c>
       <c r="D259" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E259">
         <v>7</v>
@@ -22070,10 +22067,10 @@
         <v>0</v>
       </c>
       <c r="G259" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H259" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I259" t="s">
         <v>78</v>
@@ -22082,10 +22079,10 @@
         <v>62</v>
       </c>
       <c r="K259" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L259" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M259" t="s">
         <v>1</v>
@@ -22141,7 +22138,7 @@
         <v>330042</v>
       </c>
       <c r="D260" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E260">
         <v>20</v>
@@ -22153,7 +22150,7 @@
         <v>60</v>
       </c>
       <c r="H260" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I260" t="s">
         <v>78</v>
@@ -22162,13 +22159,13 @@
         <v>62</v>
       </c>
       <c r="K260" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L260" t="s">
+        <v>558</v>
+      </c>
+      <c r="M260" t="s">
         <v>559</v>
-      </c>
-      <c r="M260" t="s">
-        <v>560</v>
       </c>
       <c r="N260">
         <v>33</v>
@@ -22221,7 +22218,7 @@
         <v>330043</v>
       </c>
       <c r="D261" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E261">
         <v>19</v>
@@ -22233,7 +22230,7 @@
         <v>60</v>
       </c>
       <c r="H261" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I261" t="s">
         <v>78</v>
@@ -22242,7 +22239,7 @@
         <v>62</v>
       </c>
       <c r="K261" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L261" t="s">
         <v>1</v>
@@ -22301,7 +22298,7 @@
         <v>330044</v>
       </c>
       <c r="D262" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E262">
         <v>16</v>
@@ -22313,7 +22310,7 @@
         <v>60</v>
       </c>
       <c r="H262" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I262" t="s">
         <v>78</v>
@@ -22322,10 +22319,10 @@
         <v>62</v>
       </c>
       <c r="K262" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L262" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="M262" t="s">
         <v>1</v>
@@ -22381,7 +22378,7 @@
         <v>330045</v>
       </c>
       <c r="D263" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E263">
         <v>5</v>
@@ -22390,10 +22387,10 @@
         <v>1</v>
       </c>
       <c r="G263" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H263" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I263" t="s">
         <v>78</v>
@@ -22402,7 +22399,7 @@
         <v>62</v>
       </c>
       <c r="K263" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L263" t="s">
         <v>1</v>
@@ -22464,7 +22461,7 @@
         <v>330046</v>
       </c>
       <c r="D264" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E264">
         <v>16</v>
@@ -22473,10 +22470,10 @@
         <v>6</v>
       </c>
       <c r="G264" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H264" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I264" t="s">
         <v>78</v>
@@ -22485,10 +22482,10 @@
         <v>62</v>
       </c>
       <c r="K264" t="s">
+        <v>569</v>
+      </c>
+      <c r="L264" t="s">
         <v>570</v>
-      </c>
-      <c r="L264" t="s">
-        <v>571</v>
       </c>
       <c r="M264" t="s">
         <v>1</v>
@@ -22544,7 +22541,7 @@
         <v>330047</v>
       </c>
       <c r="D265" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E265">
         <v>3</v>
@@ -22556,7 +22553,7 @@
         <v>60</v>
       </c>
       <c r="H265" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I265" t="s">
         <v>78</v>
@@ -22565,7 +22562,7 @@
         <v>62</v>
       </c>
       <c r="K265" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L265" t="s">
         <v>1</v>
@@ -22624,7 +22621,7 @@
         <v>330048</v>
       </c>
       <c r="D266" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E266">
         <v>5</v>
@@ -22636,7 +22633,7 @@
         <v>60</v>
       </c>
       <c r="H266" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I266" t="s">
         <v>78</v>
@@ -22645,7 +22642,7 @@
         <v>62</v>
       </c>
       <c r="K266" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L266" t="s">
         <v>1</v>
@@ -22707,7 +22704,7 @@
         <v>330049</v>
       </c>
       <c r="D267" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E267">
         <v>43</v>
@@ -22719,7 +22716,7 @@
         <v>60</v>
       </c>
       <c r="H267" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="I267" t="s">
         <v>78</v>
@@ -22728,10 +22725,10 @@
         <v>62</v>
       </c>
       <c r="K267" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L267" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M267" t="s">
         <v>1</v>
@@ -22787,7 +22784,7 @@
         <v>330050</v>
       </c>
       <c r="D268" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E268">
         <v>44</v>
@@ -22799,7 +22796,7 @@
         <v>60</v>
       </c>
       <c r="H268" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I268" t="s">
         <v>78</v>
@@ -22808,7 +22805,7 @@
         <v>62</v>
       </c>
       <c r="K268" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L268" t="s">
         <v>1</v>
@@ -22867,7 +22864,7 @@
         <v>330051</v>
       </c>
       <c r="D269" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E269">
         <v>4</v>
@@ -22876,10 +22873,10 @@
         <v>1</v>
       </c>
       <c r="G269" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H269" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I269" t="s">
         <v>78</v>
@@ -22888,7 +22885,7 @@
         <v>62</v>
       </c>
       <c r="K269" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L269" t="s">
         <v>1</v>
@@ -22950,7 +22947,7 @@
         <v>330052</v>
       </c>
       <c r="D270" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E270">
         <v>4</v>
@@ -22959,10 +22956,10 @@
         <v>2</v>
       </c>
       <c r="G270" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H270" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I270" t="s">
         <v>78</v>
@@ -22971,7 +22968,7 @@
         <v>62</v>
       </c>
       <c r="K270" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L270" t="s">
         <v>1</v>
@@ -23033,7 +23030,7 @@
         <v>330053</v>
       </c>
       <c r="D271" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E271">
         <v>4</v>
@@ -23045,7 +23042,7 @@
         <v>60</v>
       </c>
       <c r="H271" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I271" t="s">
         <v>78</v>
@@ -23054,7 +23051,7 @@
         <v>62</v>
       </c>
       <c r="K271" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L271" t="s">
         <v>1</v>
@@ -23116,7 +23113,7 @@
         <v>330054</v>
       </c>
       <c r="D272" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E272">
         <v>5</v>
@@ -23128,7 +23125,7 @@
         <v>60</v>
       </c>
       <c r="H272" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I272" t="s">
         <v>78</v>
@@ -23137,7 +23134,7 @@
         <v>62</v>
       </c>
       <c r="K272" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L272" t="s">
         <v>1</v>
@@ -23199,7 +23196,7 @@
         <v>330055</v>
       </c>
       <c r="D273" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E273">
         <v>4</v>
@@ -23208,10 +23205,10 @@
         <v>1</v>
       </c>
       <c r="G273" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H273" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I273" t="s">
         <v>78</v>
@@ -23220,7 +23217,7 @@
         <v>62</v>
       </c>
       <c r="K273" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L273" t="s">
         <v>1</v>
@@ -23282,7 +23279,7 @@
         <v>330056</v>
       </c>
       <c r="D274" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E274">
         <v>54</v>
@@ -23291,10 +23288,10 @@
         <v>0</v>
       </c>
       <c r="G274" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H274" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="I274" t="s">
         <v>78</v>
@@ -23303,7 +23300,7 @@
         <v>62</v>
       </c>
       <c r="K274" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L274" t="s">
         <v>1</v>
@@ -23365,7 +23362,7 @@
         <v>330058</v>
       </c>
       <c r="D275" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E275">
         <v>5</v>
@@ -23374,10 +23371,10 @@
         <v>1</v>
       </c>
       <c r="G275" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H275" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I275" t="s">
         <v>78</v>
@@ -23386,7 +23383,7 @@
         <v>62</v>
       </c>
       <c r="K275" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L275" t="s">
         <v>1</v>
@@ -23448,7 +23445,7 @@
         <v>330061</v>
       </c>
       <c r="D276" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E276">
         <v>39</v>
@@ -23460,7 +23457,7 @@
         <v>60</v>
       </c>
       <c r="H276" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I276" t="s">
         <v>78</v>
@@ -23469,7 +23466,7 @@
         <v>62</v>
       </c>
       <c r="K276" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="L276" t="s">
         <v>1</v>
@@ -23531,7 +23528,7 @@
         <v>330062</v>
       </c>
       <c r="D277" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E277">
         <v>40</v>
@@ -23543,7 +23540,7 @@
         <v>60</v>
       </c>
       <c r="H277" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I277" t="s">
         <v>78</v>
@@ -23552,7 +23549,7 @@
         <v>62</v>
       </c>
       <c r="K277" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L277" t="s">
         <v>1</v>
@@ -23614,7 +23611,7 @@
         <v>330063</v>
       </c>
       <c r="D278" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E278">
         <v>28</v>
@@ -23626,7 +23623,7 @@
         <v>60</v>
       </c>
       <c r="H278" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I278" t="s">
         <v>78</v>
@@ -23697,7 +23694,7 @@
         <v>330064</v>
       </c>
       <c r="D279" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E279">
         <v>29</v>
@@ -23706,10 +23703,10 @@
         <v>0</v>
       </c>
       <c r="G279" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H279" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I279" t="s">
         <v>78</v>
@@ -23718,7 +23715,7 @@
         <v>62</v>
       </c>
       <c r="K279" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L279" t="s">
         <v>1</v>
@@ -23780,7 +23777,7 @@
         <v>330065</v>
       </c>
       <c r="D280" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E280">
         <v>5</v>
@@ -23792,7 +23789,7 @@
         <v>60</v>
       </c>
       <c r="H280" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I280" t="s">
         <v>78</v>
@@ -23801,7 +23798,7 @@
         <v>62</v>
       </c>
       <c r="K280" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L280" t="s">
         <v>1</v>
@@ -23863,7 +23860,7 @@
         <v>330067</v>
       </c>
       <c r="D281" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E281">
         <v>4</v>
@@ -23875,7 +23872,7 @@
         <v>60</v>
       </c>
       <c r="H281" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I281" t="s">
         <v>78</v>
@@ -23884,7 +23881,7 @@
         <v>62</v>
       </c>
       <c r="K281" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L281" t="s">
         <v>1</v>
@@ -23946,7 +23943,7 @@
         <v>330068</v>
       </c>
       <c r="D282" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E282">
         <v>5</v>
@@ -23955,10 +23952,10 @@
         <v>1</v>
       </c>
       <c r="G282" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H282" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I282" t="s">
         <v>78</v>
@@ -23967,7 +23964,7 @@
         <v>62</v>
       </c>
       <c r="K282" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L282" t="s">
         <v>1</v>
@@ -24029,7 +24026,7 @@
         <v>330069</v>
       </c>
       <c r="D283" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E283">
         <v>16</v>
@@ -24041,7 +24038,7 @@
         <v>60</v>
       </c>
       <c r="H283" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I283" t="s">
         <v>78</v>
@@ -24050,10 +24047,10 @@
         <v>62</v>
       </c>
       <c r="K283" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L283" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M283" t="s">
         <v>1</v>
@@ -24109,7 +24106,7 @@
         <v>330070</v>
       </c>
       <c r="D284" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E284">
         <v>3</v>
@@ -24121,7 +24118,7 @@
         <v>60</v>
       </c>
       <c r="H284" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I284" t="s">
         <v>78</v>
@@ -24130,7 +24127,7 @@
         <v>62</v>
       </c>
       <c r="K284" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L284" t="s">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -10,7 +10,7 @@
     <sheet name="doll_map_puzzle_new_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'doll_map_puzzle_new_v8'!$C$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'doll_map_puzzle_new_v8'!$C$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1291,52 +1291,94 @@
     <t>48,5.9997,84</t>
   </si>
   <si>
-    <t>119.050003051758,7.999978,14.7399997711182</t>
-  </si>
-  <si>
-    <t>84,-0.04387474,20</t>
-  </si>
-  <si>
-    <t>81.75,8,22.25_81.75,8,17.75_86.25,8,17.75_86.25,8,22.25</t>
+    <t>112,7.999978,54</t>
+  </si>
+  <si>
+    <t>123,8.003199,60</t>
+  </si>
+  <si>
+    <t>120.75,8,62.25_120.75,8,57.75_125.25,8,57.75_125.25,8,62.25</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>85.2012634277344,-0.04387474,29.0751438140869</t>
-  </si>
-  <si>
-    <t>85.20,0.00,29.08,106.76,0.00,29.08,106.76,0.00,7.07,85.20,0.00,7.07</t>
-  </si>
-  <si>
-    <t>157.699996948242,7.999978,22.7000007629395</t>
-  </si>
-  <si>
-    <t>156.2,8,20.7_159.2,8,20.7_159.2,8,24.7_156.2,8,24.7</t>
+    <t>146,7.999978,61</t>
+  </si>
+  <si>
+    <t>144.5,8,59_147.5,8,59_147.5,8,63_144.5,8,63</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
   </si>
   <si>
-    <t>145,8.003199,66</t>
-  </si>
-  <si>
-    <t>146,8,65_146,8,67_144,8,67_144,8,65</t>
+    <t>q</t>
+  </si>
+  <si>
+    <t>121,8.003199,86</t>
+  </si>
+  <si>
+    <t>122,8,85_122,8,87_120,8,87_120,8,85</t>
   </si>
   <si>
     <t>74857</t>
   </si>
   <si>
-    <t>147,8.003199,66</t>
-  </si>
-  <si>
-    <t>148,8,65_148,8,67_146,8,67_146,8,65</t>
-  </si>
-  <si>
-    <t>149,8.003199,66</t>
-  </si>
-  <si>
-    <t>150,8,65_150,8,67_148,8,67_148,8,65</t>
+    <t>123,8.003199,86</t>
+  </si>
+  <si>
+    <t>124,8,85_124,8,87_122,8,87_122,8,85</t>
+  </si>
+  <si>
+    <t>125,8.003199,86</t>
+  </si>
+  <si>
+    <t>126,8,85_126,8,87_124,8,87_124,8,85</t>
+  </si>
+  <si>
+    <t>129.307510375977,7.999978,74.7048797607422</t>
+  </si>
+  <si>
+    <t>129.31,0.00,74.70,158.54,0.00,74.70,158.54,0.00,45.38,129.31,0.00,45.38</t>
+  </si>
+  <si>
+    <t>97,7.999978,86.1221466064453</t>
+  </si>
+  <si>
+    <t>98.5,8,87.62215_95.5,8,87.62215_95.5,8,84.62215_98.5,8,84.62215</t>
+  </si>
+  <si>
+    <t>74864</t>
+  </si>
+  <si>
+    <t>74865</t>
+  </si>
+  <si>
+    <t>135,7.999978,86</t>
+  </si>
+  <si>
+    <t>136.5,8,87.5_133.5,8,87.5_133.5,8,84.5_136.5,8,84.5</t>
+  </si>
+  <si>
+    <t>109.819999694824,7.999978,93</t>
+  </si>
+  <si>
+    <t>111.82,8,94_107.82,8,94_107.82,8,92_111.82,8,92</t>
+  </si>
+  <si>
+    <t>74863</t>
+  </si>
+  <si>
+    <t>77.1564254760742,7.999978,98</t>
+  </si>
+  <si>
+    <t>78.65643,8,96_78.65643,8,100_75.65643,8,100_75.65643,8,96</t>
+  </si>
+  <si>
+    <t>87.1449661254883,7.822312,117.04264831543</t>
+  </si>
+  <si>
+    <t>87.14,0.00,117.04,116.84,0.00,117.04,116.84,0.00,94.90,87.14,0.00,94.90</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -2959,7 +3001,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA284"/>
+  <dimension ref="A1:AA289"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -17677,47 +17719,78 @@
         <v>58</v>
       </c>
       <c r="C194" s="50">
-        <v>74856</v>
+        <v>74857</v>
       </c>
       <c r="D194" s="50" t="s">
         <v>428</v>
       </c>
       <c r="E194" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F194" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" s="50" t="s">
-        <v>60</v>
+        <v>95</v>
+      </c>
+      <c r="H194" s="50" t="s">
+        <v>429</v>
       </c>
       <c r="I194" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J194" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K194" s="50"/>
-      <c r="L194" s="50"/>
-      <c r="M194" s="50"/>
+      <c r="K194" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="L194" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M194" s="50" t="s">
+        <v>430</v>
+      </c>
       <c r="N194" s="50">
         <v>7</v>
       </c>
-      <c r="O194" s="50"/>
-      <c r="P194" s="50" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q194" s="50"/>
-      <c r="R194" s="50"/>
-      <c r="S194" s="50"/>
-      <c r="T194" s="50"/>
-      <c r="U194" s="50"/>
-      <c r="V194" s="50"/>
-      <c r="W194" s="50"/>
-      <c r="X194" s="50"/>
-      <c r="Y194" s="50"/>
-      <c r="Z194" s="52"/>
-      <c r="AA194" s="50"/>
+      <c r="O194" s="50">
+        <v>0</v>
+      </c>
+      <c r="P194" s="50"/>
+      <c r="Q194" s="50">
+        <v>0</v>
+      </c>
+      <c r="R194" s="50">
+        <v>0</v>
+      </c>
+      <c r="S194" s="50">
+        <v>0</v>
+      </c>
+      <c r="T194" s="50">
+        <v>0</v>
+      </c>
+      <c r="U194" s="50">
+        <v>0</v>
+      </c>
+      <c r="V194" s="50">
+        <v>0</v>
+      </c>
+      <c r="W194" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X194" s="50" t="s">
+        <v>431</v>
+      </c>
+      <c r="Y194" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z194" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="50">
@@ -17727,22 +17800,22 @@
         <v>58</v>
       </c>
       <c r="C195" s="50">
-        <v>74857</v>
+        <v>74858</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E195" s="50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F195" s="50">
         <v>0</v>
       </c>
       <c r="G195" s="50" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="H195" s="50" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I195" s="50" t="s">
         <v>78</v>
@@ -17751,13 +17824,13 @@
         <v>62</v>
       </c>
       <c r="K195" s="50" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L195" s="50" t="s">
-        <v>1</v>
+        <v>434</v>
       </c>
       <c r="M195" s="50" t="s">
-        <v>432</v>
+        <v>1</v>
       </c>
       <c r="N195" s="50">
         <v>7</v>
@@ -17788,7 +17861,7 @@
         <v>1</v>
       </c>
       <c r="X195" s="50" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="Y195" s="50" t="s">
         <v>1</v>
@@ -17808,10 +17881,10 @@
         <v>58</v>
       </c>
       <c r="C196" s="50">
-        <v>74858</v>
+        <v>74859</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E196" s="50">
         <v>7</v>
@@ -17823,7 +17896,7 @@
         <v>139</v>
       </c>
       <c r="H196" s="50" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I196" s="50" t="s">
         <v>78</v>
@@ -17835,7 +17908,7 @@
         <v>148</v>
       </c>
       <c r="L196" s="50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M196" s="50" t="s">
         <v>1</v>
@@ -17889,10 +17962,10 @@
         <v>58</v>
       </c>
       <c r="C197" s="50">
-        <v>74859</v>
+        <v>74860</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E197" s="50">
         <v>7</v>
@@ -17904,7 +17977,7 @@
         <v>139</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I197" s="50" t="s">
         <v>78</v>
@@ -17916,7 +17989,7 @@
         <v>148</v>
       </c>
       <c r="L197" s="50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M197" s="50" t="s">
         <v>1</v>
@@ -17970,77 +18043,50 @@
         <v>58</v>
       </c>
       <c r="C198" s="50">
-        <v>74860</v>
+        <v>74862</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E198" s="50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F198" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H198" s="50" t="s">
-        <v>439</v>
+        <v>60</v>
       </c>
       <c r="I198" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J198" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K198" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="L198" s="50" t="s">
-        <v>435</v>
-      </c>
-      <c r="M198" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K198" s="50"/>
+      <c r="L198" s="50"/>
+      <c r="M198" s="50"/>
       <c r="N198" s="50">
         <v>7</v>
       </c>
-      <c r="O198" s="50">
-        <v>0</v>
-      </c>
-      <c r="P198" s="50"/>
-      <c r="Q198" s="50">
-        <v>0</v>
-      </c>
-      <c r="R198" s="50">
-        <v>0</v>
-      </c>
-      <c r="S198" s="50">
-        <v>0</v>
-      </c>
-      <c r="T198" s="50">
-        <v>0</v>
-      </c>
-      <c r="U198" s="50">
-        <v>0</v>
-      </c>
-      <c r="V198" s="50">
-        <v>0</v>
-      </c>
+      <c r="O198" s="50"/>
+      <c r="P198" s="50" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q198" s="50"/>
+      <c r="R198" s="50"/>
+      <c r="S198" s="50"/>
+      <c r="T198" s="50"/>
+      <c r="U198" s="50"/>
+      <c r="V198" s="50"/>
       <c r="W198" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X198" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y198" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z198" s="52">
-        <v>0</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="X198" s="50"/>
+      <c r="Y198" s="50"/>
+      <c r="Z198" s="52"/>
       <c r="AA198" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="199">
@@ -18051,44 +18097,45 @@
         <v>58</v>
       </c>
       <c r="C199" s="50">
-        <v>84928</v>
+        <v>74863</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E199" s="50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F199" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H199" s="50" t="s">
+        <v>442</v>
+      </c>
       <c r="I199" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J199" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K199" s="50" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="L199" s="50" t="s">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="M199" s="50" t="s">
-        <v>1</v>
+        <v>444</v>
       </c>
       <c r="N199" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O199" s="50">
         <v>0</v>
       </c>
-      <c r="P199" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P199" s="50"/>
       <c r="Q199" s="50">
         <v>0</v>
       </c>
@@ -18131,22 +18178,22 @@
         <v>58</v>
       </c>
       <c r="C200" s="50">
-        <v>84929</v>
+        <v>74864</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E200" s="50">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F200" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="I200" s="50" t="s">
         <v>78</v>
@@ -18155,16 +18202,16 @@
         <v>62</v>
       </c>
       <c r="K200" s="50" t="s">
-        <v>378</v>
+        <v>239</v>
       </c>
       <c r="L200" s="50" t="s">
-        <v>443</v>
+        <v>1</v>
       </c>
       <c r="M200" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N200" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O200" s="50">
         <v>0</v>
@@ -18212,37 +18259,40 @@
         <v>58</v>
       </c>
       <c r="C201" s="50">
-        <v>84930</v>
+        <v>74865</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E201" s="50">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F201" s="50">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G201" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
+      </c>
+      <c r="H201" s="50" t="s">
+        <v>448</v>
       </c>
       <c r="I201" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J201" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K201" s="50" t="s">
-        <v>389</v>
+        <v>193</v>
       </c>
       <c r="L201" s="50" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M201" s="50" t="s">
-        <v>446</v>
+        <v>1</v>
       </c>
       <c r="N201" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O201" s="50">
         <v>0</v>
@@ -18270,7 +18320,7 @@
         <v>1</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="Y201" s="50" t="s">
         <v>1</v>
@@ -18290,13 +18340,13 @@
         <v>58</v>
       </c>
       <c r="C202" s="50">
-        <v>84931</v>
+        <v>74866</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E202" s="50">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F202" s="50">
         <v>1</v>
@@ -18305,7 +18355,7 @@
         <v>139</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>78</v>
@@ -18314,7 +18364,7 @@
         <v>62</v>
       </c>
       <c r="K202" s="50" t="s">
-        <v>393</v>
+        <v>231</v>
       </c>
       <c r="L202" s="50" t="s">
         <v>1</v>
@@ -18323,12 +18373,14 @@
         <v>1</v>
       </c>
       <c r="N202" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O202" s="50">
         <v>0</v>
       </c>
-      <c r="P202" s="50"/>
+      <c r="P202" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q202" s="50">
         <v>0</v>
       </c>
@@ -18336,7 +18388,7 @@
         <v>0</v>
       </c>
       <c r="S202" s="50">
-        <v>0</v>
+        <v>70002</v>
       </c>
       <c r="T202" s="50">
         <v>0</v>
@@ -18371,13 +18423,13 @@
         <v>58</v>
       </c>
       <c r="C203" s="50">
-        <v>84932</v>
+        <v>74867</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E203" s="50">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F203" s="50">
         <v>1</v>
@@ -18391,54 +18443,32 @@
       <c r="J203" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K203" s="50" t="s">
-        <v>389</v>
-      </c>
+      <c r="K203" s="50"/>
       <c r="L203" s="50" t="s">
-        <v>450</v>
-      </c>
-      <c r="M203" s="50" t="s">
-        <v>446</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M203" s="50"/>
       <c r="N203" s="50">
-        <v>8</v>
-      </c>
-      <c r="O203" s="50">
-        <v>0</v>
-      </c>
-      <c r="P203" s="50"/>
-      <c r="Q203" s="50">
-        <v>0</v>
-      </c>
-      <c r="R203" s="50">
-        <v>0</v>
-      </c>
-      <c r="S203" s="50">
-        <v>0</v>
-      </c>
-      <c r="T203" s="50">
-        <v>0</v>
-      </c>
-      <c r="U203" s="50">
-        <v>0</v>
-      </c>
-      <c r="V203" s="50">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O203" s="50"/>
+      <c r="P203" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q203" s="50"/>
+      <c r="R203" s="50"/>
+      <c r="S203" s="50"/>
+      <c r="T203" s="50"/>
+      <c r="U203" s="50"/>
+      <c r="V203" s="50"/>
       <c r="W203" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X203" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y203" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z203" s="52">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="X203" s="50"/>
+      <c r="Y203" s="50"/>
+      <c r="Z203" s="52"/>
       <c r="AA203" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="204">
@@ -18449,31 +18479,28 @@
         <v>58</v>
       </c>
       <c r="C204" s="50">
-        <v>84933</v>
+        <v>84928</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E204" s="50">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F204" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H204" s="50" t="s">
-        <v>452</v>
-      </c>
       <c r="I204" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J204" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K204" s="50" t="s">
-        <v>393</v>
+        <v>75</v>
       </c>
       <c r="L204" s="50" t="s">
         <v>1</v>
@@ -18487,7 +18514,9 @@
       <c r="O204" s="50">
         <v>0</v>
       </c>
-      <c r="P204" s="50"/>
+      <c r="P204" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q204" s="50">
         <v>0</v>
       </c>
@@ -18530,22 +18559,22 @@
         <v>58</v>
       </c>
       <c r="C205" s="50">
-        <v>84934</v>
+        <v>84929</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E205" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F205" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205" s="50" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -18554,10 +18583,10 @@
         <v>62</v>
       </c>
       <c r="K205" s="50" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="L205" s="50" t="s">
-        <v>1</v>
+        <v>457</v>
       </c>
       <c r="M205" s="50" t="s">
         <v>1</v>
@@ -18611,37 +18640,34 @@
         <v>58</v>
       </c>
       <c r="C206" s="50">
-        <v>84935</v>
+        <v>84930</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E206" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F206" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G206" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H206" s="50" t="s">
-        <v>456</v>
+        <v>139</v>
       </c>
       <c r="I206" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J206" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="L206" s="50" t="s">
-        <v>1</v>
+        <v>459</v>
       </c>
       <c r="M206" s="50" t="s">
-        <v>1</v>
+        <v>460</v>
       </c>
       <c r="N206" s="50">
         <v>8</v>
@@ -18692,22 +18718,22 @@
         <v>58</v>
       </c>
       <c r="C207" s="50">
-        <v>84936</v>
+        <v>84931</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E207" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F207" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G207" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -18716,7 +18742,7 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="L207" s="50" t="s">
         <v>1</v>
@@ -18747,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="V207" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W207" s="50" t="s">
         <v>1</v>
@@ -18773,37 +18799,34 @@
         <v>58</v>
       </c>
       <c r="C208" s="50">
-        <v>84937</v>
+        <v>84932</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E208" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F208" s="50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G208" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H208" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I208" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J208" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K208" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="L208" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="M208" s="50" t="s">
         <v>460</v>
-      </c>
-      <c r="I208" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J208" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K208" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="L208" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M208" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N208" s="50">
         <v>8</v>
@@ -18828,7 +18851,7 @@
         <v>0</v>
       </c>
       <c r="V208" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W208" s="50" t="s">
         <v>1</v>
@@ -18854,22 +18877,22 @@
         <v>58</v>
       </c>
       <c r="C209" s="50">
-        <v>84938</v>
+        <v>84933</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E209" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F209" s="50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G209" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -18878,7 +18901,7 @@
         <v>62</v>
       </c>
       <c r="K209" s="50" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L209" s="50" t="s">
         <v>1</v>
@@ -18935,22 +18958,22 @@
         <v>58</v>
       </c>
       <c r="C210" s="50">
-        <v>84939</v>
+        <v>84934</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E210" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F210" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -18959,7 +18982,7 @@
         <v>62</v>
       </c>
       <c r="K210" s="50" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L210" s="50" t="s">
         <v>1</v>
@@ -19016,22 +19039,22 @@
         <v>58</v>
       </c>
       <c r="C211" s="50">
-        <v>84940</v>
+        <v>84935</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E211" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F211" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G211" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19040,7 +19063,7 @@
         <v>62</v>
       </c>
       <c r="K211" s="50" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="L211" s="50" t="s">
         <v>1</v>
@@ -19097,22 +19120,22 @@
         <v>58</v>
       </c>
       <c r="C212" s="50">
-        <v>84941</v>
+        <v>84936</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E212" s="50">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F212" s="50">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G212" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19121,10 +19144,10 @@
         <v>62</v>
       </c>
       <c r="K212" s="50" t="s">
-        <v>193</v>
+        <v>401</v>
       </c>
       <c r="L212" s="50" t="s">
-        <v>469</v>
+        <v>1</v>
       </c>
       <c r="M212" s="50" t="s">
         <v>1</v>
@@ -19152,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="V212" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W212" s="50" t="s">
         <v>1</v>
@@ -19178,34 +19201,37 @@
         <v>58</v>
       </c>
       <c r="C213" s="50">
-        <v>84942</v>
+        <v>84937</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E213" s="50">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F213" s="50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G213" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
+      </c>
+      <c r="H213" s="50" t="s">
+        <v>474</v>
       </c>
       <c r="I213" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J213" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K213" s="50" t="s">
-        <v>286</v>
+        <v>397</v>
       </c>
       <c r="L213" s="50" t="s">
-        <v>471</v>
+        <v>1</v>
       </c>
       <c r="M213" s="50" t="s">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="N213" s="50">
         <v>8</v>
@@ -19230,7 +19256,7 @@
         <v>0</v>
       </c>
       <c r="V213" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W213" s="50" t="s">
         <v>1</v>
@@ -19256,22 +19282,22 @@
         <v>58</v>
       </c>
       <c r="C214" s="50">
-        <v>84943</v>
+        <v>84938</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E214" s="50">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F214" s="50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G214" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19280,7 +19306,7 @@
         <v>62</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>277</v>
+        <v>387</v>
       </c>
       <c r="L214" s="50" t="s">
         <v>1</v>
@@ -19337,34 +19363,37 @@
         <v>58</v>
       </c>
       <c r="C215" s="50">
-        <v>84944</v>
+        <v>84939</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E215" s="50">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F215" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G215" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H215" s="50" t="s">
+        <v>478</v>
+      </c>
       <c r="I215" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J215" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="L215" s="50" t="s">
-        <v>476</v>
+        <v>1</v>
       </c>
       <c r="M215" s="50" t="s">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="N215" s="50">
         <v>8</v>
@@ -19415,22 +19444,22 @@
         <v>58</v>
       </c>
       <c r="C216" s="50">
-        <v>84945</v>
+        <v>84940</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E216" s="50">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="F216" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G216" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -19439,7 +19468,7 @@
         <v>62</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>284</v>
+        <v>395</v>
       </c>
       <c r="L216" s="50" t="s">
         <v>1</v>
@@ -19496,31 +19525,34 @@
         <v>58</v>
       </c>
       <c r="C217" s="50">
-        <v>84946</v>
+        <v>84941</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E217" s="50">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F217" s="50">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G217" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H217" s="50" t="s">
+        <v>482</v>
+      </c>
       <c r="I217" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J217" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>480</v>
+        <v>193</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>1</v>
+        <v>483</v>
       </c>
       <c r="M217" s="50" t="s">
         <v>1</v>
@@ -19574,16 +19606,16 @@
         <v>58</v>
       </c>
       <c r="C218" s="50">
-        <v>84947</v>
+        <v>84942</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E218" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F218" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G218" s="50" t="s">
         <v>60</v>
@@ -19595,13 +19627,13 @@
         <v>62</v>
       </c>
       <c r="K218" s="50" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="L218" s="50" t="s">
-        <v>1</v>
+        <v>485</v>
       </c>
       <c r="M218" s="50" t="s">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="N218" s="50">
         <v>8</v>
@@ -19652,28 +19684,31 @@
         <v>58</v>
       </c>
       <c r="C219" s="50">
-        <v>84948</v>
+        <v>84943</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E219" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F219" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G219" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H219" s="50" t="s">
+        <v>488</v>
+      </c>
       <c r="I219" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J219" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -19730,16 +19765,16 @@
         <v>58</v>
       </c>
       <c r="C220" s="50">
-        <v>84949</v>
+        <v>84944</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E220" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F220" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G220" s="50" t="s">
         <v>60</v>
@@ -19751,13 +19786,13 @@
         <v>62</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="L220" s="50" t="s">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="M220" s="50" t="s">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="N220" s="50">
         <v>8</v>
@@ -19808,28 +19843,31 @@
         <v>58</v>
       </c>
       <c r="C221" s="50">
-        <v>84950</v>
+        <v>84945</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E221" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F221" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G221" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H221" s="50" t="s">
+        <v>492</v>
+      </c>
       <c r="I221" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J221" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -19886,16 +19924,16 @@
         <v>58</v>
       </c>
       <c r="C222" s="50">
-        <v>84951</v>
+        <v>84946</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E222" s="50">
         <v>56</v>
       </c>
       <c r="F222" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" s="50" t="s">
         <v>60</v>
@@ -19907,7 +19945,7 @@
         <v>62</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>302</v>
+        <v>494</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -19964,10 +20002,10 @@
         <v>58</v>
       </c>
       <c r="C223" s="50">
-        <v>84952</v>
+        <v>84947</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E223" s="50">
         <v>56</v>
@@ -20042,10 +20080,10 @@
         <v>58</v>
       </c>
       <c r="C224" s="50">
-        <v>84953</v>
+        <v>84948</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E224" s="50">
         <v>56</v>
@@ -20120,10 +20158,10 @@
         <v>58</v>
       </c>
       <c r="C225" s="50">
-        <v>84954</v>
+        <v>84949</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="E225" s="50">
         <v>56</v>
@@ -20198,10 +20236,10 @@
         <v>58</v>
       </c>
       <c r="C226" s="50">
-        <v>84955</v>
+        <v>84950</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E226" s="50">
         <v>56</v>
@@ -20276,10 +20314,10 @@
         <v>58</v>
       </c>
       <c r="C227" s="50">
-        <v>84956</v>
+        <v>84951</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E227" s="50">
         <v>56</v>
@@ -20354,10 +20392,10 @@
         <v>58</v>
       </c>
       <c r="C228" s="50">
-        <v>84957</v>
+        <v>84952</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="E228" s="50">
         <v>56</v>
@@ -20432,10 +20470,10 @@
         <v>58</v>
       </c>
       <c r="C229" s="50">
-        <v>84958</v>
+        <v>84953</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E229" s="50">
         <v>56</v>
@@ -20510,10 +20548,10 @@
         <v>58</v>
       </c>
       <c r="C230" s="50">
-        <v>84959</v>
+        <v>84954</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E230" s="50">
         <v>56</v>
@@ -20588,10 +20626,10 @@
         <v>58</v>
       </c>
       <c r="C231" s="50">
-        <v>84960</v>
+        <v>84955</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E231" s="50">
         <v>56</v>
@@ -20666,10 +20704,10 @@
         <v>58</v>
       </c>
       <c r="C232" s="50">
-        <v>84961</v>
+        <v>84956</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="E232" s="50">
         <v>56</v>
@@ -20744,10 +20782,10 @@
         <v>58</v>
       </c>
       <c r="C233" s="50">
-        <v>84962</v>
+        <v>84957</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E233" s="50">
         <v>56</v>
@@ -20822,10 +20860,10 @@
         <v>58</v>
       </c>
       <c r="C234" s="50">
-        <v>84963</v>
+        <v>84958</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="E234" s="50">
         <v>56</v>
@@ -20900,10 +20938,10 @@
         <v>58</v>
       </c>
       <c r="C235" s="50">
-        <v>84964</v>
+        <v>84959</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E235" s="50">
         <v>56</v>
@@ -20978,10 +21016,10 @@
         <v>58</v>
       </c>
       <c r="C236" s="50">
-        <v>84965</v>
+        <v>84960</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E236" s="50">
         <v>56</v>
@@ -21056,10 +21094,10 @@
         <v>58</v>
       </c>
       <c r="C237" s="50">
-        <v>84966</v>
+        <v>84961</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E237" s="50">
         <v>56</v>
@@ -21134,10 +21172,10 @@
         <v>58</v>
       </c>
       <c r="C238" s="50">
-        <v>84967</v>
+        <v>84962</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E238" s="50">
         <v>56</v>
@@ -21212,10 +21250,10 @@
         <v>58</v>
       </c>
       <c r="C239" s="50">
-        <v>84968</v>
+        <v>84963</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E239" s="50">
         <v>56</v>
@@ -21290,31 +21328,28 @@
         <v>58</v>
       </c>
       <c r="C240" s="50">
-        <v>84969</v>
+        <v>84964</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="E240" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F240" s="50">
         <v>0</v>
       </c>
       <c r="G240" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="H240" s="50" t="s">
-        <v>504</v>
+        <v>60</v>
       </c>
       <c r="I240" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J240" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K240" s="50" t="s">
-        <v>505</v>
+        <v>302</v>
       </c>
       <c r="L240" s="50" t="s">
         <v>1</v>
@@ -21371,31 +21406,28 @@
         <v>58</v>
       </c>
       <c r="C241" s="50">
-        <v>84970</v>
+        <v>84965</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="E241" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F241" s="50">
         <v>0</v>
       </c>
       <c r="G241" s="50" t="s">
-        <v>507</v>
-      </c>
-      <c r="H241" s="50" t="s">
-        <v>508</v>
+        <v>60</v>
       </c>
       <c r="I241" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J241" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K241" s="50" t="s">
-        <v>509</v>
+        <v>302</v>
       </c>
       <c r="L241" s="50" t="s">
         <v>1</v>
@@ -21452,37 +21484,34 @@
         <v>58</v>
       </c>
       <c r="C242" s="50">
-        <v>84971</v>
+        <v>84966</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E242" s="50">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F242" s="50">
         <v>0</v>
       </c>
       <c r="G242" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="H242" s="50" t="s">
-        <v>511</v>
+        <v>60</v>
       </c>
       <c r="I242" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J242" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K242" s="50" t="s">
-        <v>512</v>
+        <v>302</v>
       </c>
       <c r="L242" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M242" s="50" t="s">
-        <v>513</v>
+        <v>1</v>
       </c>
       <c r="N242" s="50">
         <v>8</v>
@@ -21533,31 +21562,28 @@
         <v>58</v>
       </c>
       <c r="C243" s="50">
-        <v>84972</v>
+        <v>84967</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E243" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F243" s="50">
         <v>0</v>
       </c>
       <c r="G243" s="50" t="s">
-        <v>515</v>
-      </c>
-      <c r="H243" s="50" t="s">
-        <v>516</v>
+        <v>60</v>
       </c>
       <c r="I243" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J243" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K243" s="50" t="s">
-        <v>509</v>
+        <v>302</v>
       </c>
       <c r="L243" s="50" t="s">
         <v>1</v>
@@ -21614,34 +21640,31 @@
         <v>58</v>
       </c>
       <c r="C244" s="50">
-        <v>84973</v>
+        <v>84968</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E244" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F244" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G244" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H244" s="50" t="s">
-        <v>518</v>
-      </c>
       <c r="I244" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J244" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="L244" s="50" t="s">
-        <v>519</v>
+        <v>1</v>
       </c>
       <c r="M244" s="50" t="s">
         <v>1</v>
@@ -21695,22 +21718,22 @@
         <v>58</v>
       </c>
       <c r="C245" s="50">
-        <v>84974</v>
+        <v>84969</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E245" s="50">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F245" s="50">
         <v>0</v>
       </c>
       <c r="G245" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H245" s="50" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="I245" s="50" t="s">
         <v>78</v>
@@ -21719,7 +21742,7 @@
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
@@ -21776,47 +21799,78 @@
         <v>58</v>
       </c>
       <c r="C246" s="50">
-        <v>84976</v>
+        <v>84970</v>
       </c>
       <c r="D246" s="50" t="s">
+        <v>520</v>
+      </c>
+      <c r="E246" s="50">
+        <v>46</v>
+      </c>
+      <c r="F246" s="50">
+        <v>0</v>
+      </c>
+      <c r="G246" s="50" t="s">
+        <v>521</v>
+      </c>
+      <c r="H246" s="50" t="s">
         <v>522</v>
       </c>
-      <c r="E246" s="50">
-        <v>2</v>
-      </c>
-      <c r="F246" s="50">
-        <v>2</v>
-      </c>
-      <c r="G246" s="50" t="s">
-        <v>60</v>
-      </c>
       <c r="I246" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J246" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K246" s="50"/>
-      <c r="L246" s="50"/>
-      <c r="M246" s="50"/>
+      <c r="K246" s="50" t="s">
+        <v>523</v>
+      </c>
+      <c r="L246" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M246" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N246" s="50">
         <v>8</v>
       </c>
-      <c r="O246" s="50"/>
-      <c r="P246" s="50" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q246" s="50"/>
-      <c r="R246" s="50"/>
-      <c r="S246" s="50"/>
-      <c r="T246" s="50"/>
-      <c r="U246" s="50"/>
-      <c r="V246" s="50"/>
-      <c r="W246" s="50"/>
-      <c r="X246" s="50"/>
-      <c r="Y246" s="50"/>
-      <c r="Z246" s="52"/>
-      <c r="AA246" s="50"/>
+      <c r="O246" s="50">
+        <v>0</v>
+      </c>
+      <c r="P246" s="50"/>
+      <c r="Q246" s="50">
+        <v>0</v>
+      </c>
+      <c r="R246" s="50">
+        <v>0</v>
+      </c>
+      <c r="S246" s="50">
+        <v>0</v>
+      </c>
+      <c r="T246" s="50">
+        <v>0</v>
+      </c>
+      <c r="U246" s="50">
+        <v>0</v>
+      </c>
+      <c r="V246" s="50">
+        <v>0</v>
+      </c>
+      <c r="W246" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X246" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y246" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z246" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA246" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="50">
@@ -21826,47 +21880,78 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>84977</v>
+        <v>84971</v>
       </c>
       <c r="D247" s="50" t="s">
         <v>524</v>
       </c>
       <c r="E247" s="50">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F247" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>60</v>
+        <v>95</v>
+      </c>
+      <c r="H247" s="50" t="s">
+        <v>525</v>
       </c>
       <c r="I247" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J247" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K247" s="50"/>
-      <c r="L247" s="50"/>
-      <c r="M247" s="50"/>
+      <c r="K247" s="50" t="s">
+        <v>526</v>
+      </c>
+      <c r="L247" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M247" s="50" t="s">
+        <v>527</v>
+      </c>
       <c r="N247" s="50">
         <v>8</v>
       </c>
-      <c r="O247" s="50"/>
-      <c r="P247" s="50" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q247" s="50"/>
-      <c r="R247" s="50"/>
-      <c r="S247" s="50"/>
-      <c r="T247" s="50"/>
-      <c r="U247" s="50"/>
-      <c r="V247" s="50"/>
-      <c r="W247" s="50"/>
-      <c r="X247" s="50"/>
-      <c r="Y247" s="50"/>
-      <c r="Z247" s="52"/>
-      <c r="AA247" s="50"/>
+      <c r="O247" s="50">
+        <v>0</v>
+      </c>
+      <c r="P247" s="50"/>
+      <c r="Q247" s="50">
+        <v>0</v>
+      </c>
+      <c r="R247" s="50">
+        <v>0</v>
+      </c>
+      <c r="S247" s="50">
+        <v>0</v>
+      </c>
+      <c r="T247" s="50">
+        <v>0</v>
+      </c>
+      <c r="U247" s="50">
+        <v>0</v>
+      </c>
+      <c r="V247" s="50">
+        <v>0</v>
+      </c>
+      <c r="W247" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X247" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y247" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z247" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA247" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="50">
@@ -21876,47 +21961,78 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>84978</v>
+        <v>84972</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E248" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F248" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G248" s="50" t="s">
-        <v>60</v>
+        <v>529</v>
+      </c>
+      <c r="H248" s="50" t="s">
+        <v>530</v>
       </c>
       <c r="I248" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J248" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K248" s="50"/>
-      <c r="L248" s="50"/>
-      <c r="M248" s="50"/>
+      <c r="K248" s="50" t="s">
+        <v>523</v>
+      </c>
+      <c r="L248" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M248" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N248" s="50">
         <v>8</v>
       </c>
-      <c r="O248" s="50"/>
-      <c r="P248" s="50" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q248" s="50"/>
-      <c r="R248" s="50"/>
-      <c r="S248" s="50"/>
-      <c r="T248" s="50"/>
-      <c r="U248" s="50"/>
-      <c r="V248" s="50"/>
-      <c r="W248" s="50"/>
-      <c r="X248" s="50"/>
-      <c r="Y248" s="50"/>
-      <c r="Z248" s="52"/>
-      <c r="AA248" s="50"/>
+      <c r="O248" s="50">
+        <v>0</v>
+      </c>
+      <c r="P248" s="50"/>
+      <c r="Q248" s="50">
+        <v>0</v>
+      </c>
+      <c r="R248" s="50">
+        <v>0</v>
+      </c>
+      <c r="S248" s="50">
+        <v>0</v>
+      </c>
+      <c r="T248" s="50">
+        <v>0</v>
+      </c>
+      <c r="U248" s="50">
+        <v>0</v>
+      </c>
+      <c r="V248" s="50">
+        <v>0</v>
+      </c>
+      <c r="W248" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X248" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y248" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z248" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA248" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="50">
@@ -21926,22 +22042,22 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>84979</v>
+        <v>84973</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E249" s="50">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F249" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G249" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H249" s="50" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I249" s="50" t="s">
         <v>78</v>
@@ -21950,13 +22066,13 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>328</v>
+        <v>193</v>
       </c>
       <c r="L249" s="50" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="M249" s="50" t="s">
-        <v>531</v>
+        <v>1</v>
       </c>
       <c r="N249" s="50">
         <v>8</v>
@@ -22007,13 +22123,13 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>84980</v>
+        <v>84974</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E250" s="50">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F250" s="50">
         <v>0</v>
@@ -22022,7 +22138,7 @@
         <v>60</v>
       </c>
       <c r="H250" s="50" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>78</v>
@@ -22031,10 +22147,10 @@
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>325</v>
+        <v>523</v>
       </c>
       <c r="L250" s="50" t="s">
-        <v>534</v>
+        <v>1</v>
       </c>
       <c r="M250" s="50" t="s">
         <v>1</v>
@@ -22088,78 +22204,47 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>84981</v>
+        <v>84976</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E251" s="50">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F251" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G251" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H251" s="50" t="s">
-        <v>536</v>
-      </c>
       <c r="I251" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J251" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K251" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="L251" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M251" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K251" s="50"/>
+      <c r="L251" s="50"/>
+      <c r="M251" s="50"/>
       <c r="N251" s="50">
         <v>8</v>
       </c>
-      <c r="O251" s="50">
-        <v>0</v>
-      </c>
-      <c r="P251" s="50"/>
-      <c r="Q251" s="50">
-        <v>0</v>
-      </c>
-      <c r="R251" s="50">
-        <v>0</v>
-      </c>
-      <c r="S251" s="50">
-        <v>0</v>
-      </c>
-      <c r="T251" s="50">
-        <v>0</v>
-      </c>
-      <c r="U251" s="50">
-        <v>0</v>
-      </c>
-      <c r="V251" s="50">
-        <v>0</v>
-      </c>
-      <c r="W251" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X251" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y251" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z251" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA251" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O251" s="50"/>
+      <c r="P251" s="50" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q251" s="50"/>
+      <c r="R251" s="50"/>
+      <c r="S251" s="50"/>
+      <c r="T251" s="50"/>
+      <c r="U251" s="50"/>
+      <c r="V251" s="50"/>
+      <c r="W251" s="50"/>
+      <c r="X251" s="50"/>
+      <c r="Y251" s="50"/>
+      <c r="Z251" s="52"/>
+      <c r="AA251" s="50"/>
     </row>
     <row r="252">
       <c r="A252" s="50">
@@ -22169,16 +22254,16 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>84982</v>
+        <v>84977</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E252" s="50">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F252" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G252" s="50" t="s">
         <v>60</v>
@@ -22189,57 +22274,27 @@
       <c r="J252" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K252" s="50" t="s">
-        <v>538</v>
-      </c>
-      <c r="L252" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M252" s="50" t="s">
-        <v>539</v>
-      </c>
+      <c r="K252" s="50"/>
+      <c r="L252" s="50"/>
+      <c r="M252" s="50"/>
       <c r="N252" s="50">
         <v>8</v>
       </c>
-      <c r="O252" s="50">
-        <v>0</v>
-      </c>
+      <c r="O252" s="50"/>
       <c r="P252" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q252" s="50">
-        <v>0</v>
-      </c>
-      <c r="R252" s="50">
-        <v>0</v>
-      </c>
-      <c r="S252" s="50">
-        <v>0</v>
-      </c>
-      <c r="T252" s="50">
-        <v>0</v>
-      </c>
-      <c r="U252" s="50">
-        <v>0</v>
-      </c>
-      <c r="V252" s="50">
-        <v>0</v>
-      </c>
-      <c r="W252" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X252" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y252" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z252" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA252" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="Q252" s="50"/>
+      <c r="R252" s="50"/>
+      <c r="S252" s="50"/>
+      <c r="T252" s="50"/>
+      <c r="U252" s="50"/>
+      <c r="V252" s="50"/>
+      <c r="W252" s="50"/>
+      <c r="X252" s="50"/>
+      <c r="Y252" s="50"/>
+      <c r="Z252" s="52"/>
+      <c r="AA252" s="50"/>
     </row>
     <row r="253">
       <c r="A253" s="50">
@@ -22249,80 +22304,47 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>84983</v>
+        <v>84978</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E253" s="50">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F253" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G253" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H253" s="50" t="s">
-        <v>540</v>
-      </c>
       <c r="I253" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J253" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K253" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="L253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M253" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K253" s="50"/>
+      <c r="L253" s="50"/>
+      <c r="M253" s="50"/>
       <c r="N253" s="50">
         <v>8</v>
       </c>
-      <c r="O253" s="50">
-        <v>0</v>
-      </c>
+      <c r="O253" s="50"/>
       <c r="P253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q253" s="50">
-        <v>0</v>
-      </c>
-      <c r="R253" s="50">
-        <v>0</v>
-      </c>
-      <c r="S253" s="50">
-        <v>0</v>
-      </c>
-      <c r="T253" s="50">
-        <v>0</v>
-      </c>
-      <c r="U253" s="50">
-        <v>0</v>
-      </c>
-      <c r="V253" s="50">
-        <v>0</v>
-      </c>
-      <c r="W253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z253" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA253" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="Q253" s="50"/>
+      <c r="R253" s="50"/>
+      <c r="S253" s="50"/>
+      <c r="T253" s="50"/>
+      <c r="U253" s="50"/>
+      <c r="V253" s="50"/>
+      <c r="W253" s="50"/>
+      <c r="X253" s="50"/>
+      <c r="Y253" s="50"/>
+      <c r="Z253" s="52"/>
+      <c r="AA253" s="50"/>
     </row>
     <row r="254">
       <c r="A254" s="50">
@@ -22332,19 +22354,19 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>84984</v>
+        <v>84979</v>
       </c>
       <c r="D254" s="50" t="s">
         <v>542</v>
       </c>
       <c r="E254" s="50">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F254" s="50">
         <v>0</v>
       </c>
       <c r="G254" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H254" s="50" t="s">
         <v>543</v>
@@ -22356,13 +22378,13 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="L254" s="50" t="s">
         <v>544</v>
       </c>
-      <c r="L254" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M254" s="50" t="s">
-        <v>1</v>
+        <v>545</v>
       </c>
       <c r="N254" s="50">
         <v>8</v>
@@ -22370,9 +22392,7 @@
       <c r="O254" s="50">
         <v>0</v>
       </c>
-      <c r="P254" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P254" s="50"/>
       <c r="Q254" s="50">
         <v>0</v>
       </c>
@@ -22415,22 +22435,22 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>330037</v>
+        <v>84980</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E255" s="50">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="F255" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H255" s="50" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22439,23 +22459,21 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="L255" s="50" t="s">
-        <v>1</v>
+        <v>548</v>
       </c>
       <c r="M255" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N255" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O255" s="50">
         <v>0</v>
       </c>
-      <c r="P255" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P255" s="50"/>
       <c r="Q255" s="50">
         <v>0</v>
       </c>
@@ -22465,8 +22483,8 @@
       <c r="S255" s="50">
         <v>0</v>
       </c>
-      <c r="T255" s="50" t="s">
-        <v>61</v>
+      <c r="T255" s="50">
+        <v>0</v>
       </c>
       <c r="U255" s="50">
         <v>0</v>
@@ -22498,22 +22516,22 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>330038</v>
+        <v>84981</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E256" s="50">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F256" s="50">
         <v>0</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -22522,16 +22540,16 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>143</v>
+        <v>332</v>
       </c>
       <c r="L256" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M256" s="50" t="s">
-        <v>549</v>
+        <v>1</v>
       </c>
       <c r="N256" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O256" s="50">
         <v>0</v>
@@ -22579,45 +22597,44 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>330039</v>
+        <v>84982</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E257" s="50">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H257" s="50" t="s">
-        <v>551</v>
+        <v>60</v>
       </c>
       <c r="I257" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J257" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>148</v>
+        <v>552</v>
       </c>
       <c r="L257" s="50" t="s">
-        <v>552</v>
+        <v>1</v>
       </c>
       <c r="M257" s="50" t="s">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="N257" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O257" s="50">
         <v>0</v>
       </c>
-      <c r="P257" s="50"/>
+      <c r="P257" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q257" s="50">
         <v>0</v>
       </c>
@@ -22660,19 +22677,19 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>330040</v>
+        <v>84983</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E258" s="50">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F258" s="50">
         <v>0</v>
       </c>
       <c r="G258" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H258" s="50" t="s">
         <v>554</v>
@@ -22684,21 +22701,23 @@
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>148</v>
+        <v>555</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>552</v>
+        <v>1</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N258" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O258" s="50">
         <v>0</v>
       </c>
-      <c r="P258" s="50"/>
+      <c r="P258" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q258" s="50">
         <v>0</v>
       </c>
@@ -22741,22 +22760,22 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>330041</v>
+        <v>84984</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E259" s="50">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F259" s="50">
         <v>0</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -22765,21 +22784,23 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>148</v>
+        <v>558</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>552</v>
+        <v>1</v>
       </c>
       <c r="M259" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N259" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O259" s="50">
         <v>0</v>
       </c>
-      <c r="P259" s="50"/>
+      <c r="P259" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q259" s="50">
         <v>0</v>
       </c>
@@ -22822,13 +22843,13 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>330042</v>
+        <v>330037</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E260" s="50">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F260" s="50">
         <v>1</v>
@@ -22837,7 +22858,7 @@
         <v>60</v>
       </c>
       <c r="H260" s="50" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -22846,13 +22867,13 @@
         <v>62</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>234</v>
+        <v>97</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>559</v>
+        <v>1</v>
       </c>
       <c r="M260" s="50" t="s">
-        <v>560</v>
+        <v>1</v>
       </c>
       <c r="N260" s="50">
         <v>33</v>
@@ -22860,7 +22881,9 @@
       <c r="O260" s="50">
         <v>0</v>
       </c>
-      <c r="P260" s="50"/>
+      <c r="P260" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q260" s="50">
         <v>0</v>
       </c>
@@ -22870,8 +22893,8 @@
       <c r="S260" s="50">
         <v>0</v>
       </c>
-      <c r="T260" s="50">
-        <v>0</v>
+      <c r="T260" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U260" s="50">
         <v>0</v>
@@ -22903,19 +22926,19 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>330043</v>
+        <v>330038</v>
       </c>
       <c r="D261" s="50" t="s">
         <v>561</v>
       </c>
       <c r="E261" s="50">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F261" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H261" s="50" t="s">
         <v>562</v>
@@ -22927,13 +22950,13 @@
         <v>62</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
       <c r="L261" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M261" s="50" t="s">
-        <v>1</v>
+        <v>563</v>
       </c>
       <c r="N261" s="50">
         <v>33</v>
@@ -22984,22 +23007,22 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>330044</v>
+        <v>330039</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E262" s="50">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F262" s="50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H262" s="50" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I262" s="50" t="s">
         <v>78</v>
@@ -23008,10 +23031,10 @@
         <v>62</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M262" s="50" t="s">
         <v>1</v>
@@ -23065,22 +23088,22 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>330045</v>
+        <v>330040</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E263" s="50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F263" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23089,10 +23112,10 @@
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>1</v>
+        <v>566</v>
       </c>
       <c r="M263" s="50" t="s">
         <v>1</v>
@@ -23103,9 +23126,7 @@
       <c r="O263" s="50">
         <v>0</v>
       </c>
-      <c r="P263" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P263" s="50"/>
       <c r="Q263" s="50">
         <v>0</v>
       </c>
@@ -23115,8 +23136,8 @@
       <c r="S263" s="50">
         <v>0</v>
       </c>
-      <c r="T263" s="50" t="s">
-        <v>61</v>
+      <c r="T263" s="50">
+        <v>0</v>
       </c>
       <c r="U263" s="50">
         <v>0</v>
@@ -23148,22 +23169,22 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>330046</v>
+        <v>330041</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E264" s="50">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F264" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G264" s="50" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23172,10 +23193,10 @@
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>570</v>
+        <v>148</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
@@ -23229,22 +23250,22 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>330047</v>
+        <v>330042</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E265" s="50">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F265" s="50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23253,13 +23274,13 @@
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="L265" s="50" t="s">
+        <v>573</v>
+      </c>
+      <c r="M265" s="50" t="s">
         <v>574</v>
-      </c>
-      <c r="L265" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M265" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N265" s="50">
         <v>33</v>
@@ -23310,13 +23331,13 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>330048</v>
+        <v>330043</v>
       </c>
       <c r="D266" s="50" t="s">
         <v>575</v>
       </c>
       <c r="E266" s="50">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F266" s="50">
         <v>1</v>
@@ -23334,7 +23355,7 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -23348,9 +23369,7 @@
       <c r="O266" s="50">
         <v>0</v>
       </c>
-      <c r="P266" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P266" s="50"/>
       <c r="Q266" s="50">
         <v>0</v>
       </c>
@@ -23360,8 +23379,8 @@
       <c r="S266" s="50">
         <v>0</v>
       </c>
-      <c r="T266" s="50" t="s">
-        <v>61</v>
+      <c r="T266" s="50">
+        <v>0</v>
       </c>
       <c r="U266" s="50">
         <v>0</v>
@@ -23393,16 +23412,16 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>330049</v>
+        <v>330044</v>
       </c>
       <c r="D267" s="50" t="s">
         <v>577</v>
       </c>
       <c r="E267" s="50">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="F267" s="50">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
@@ -23417,7 +23436,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>579</v>
@@ -23474,19 +23493,19 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>330050</v>
+        <v>330045</v>
       </c>
       <c r="D268" s="50" t="s">
         <v>580</v>
       </c>
       <c r="E268" s="50">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F268" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H268" s="50" t="s">
         <v>581</v>
@@ -23498,7 +23517,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23512,7 +23531,9 @@
       <c r="O268" s="50">
         <v>0</v>
       </c>
-      <c r="P268" s="50"/>
+      <c r="P268" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q268" s="50">
         <v>0</v>
       </c>
@@ -23522,8 +23543,8 @@
       <c r="S268" s="50">
         <v>0</v>
       </c>
-      <c r="T268" s="50">
-        <v>0</v>
+      <c r="T268" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U268" s="50">
         <v>0</v>
@@ -23555,19 +23576,19 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>330051</v>
+        <v>330046</v>
       </c>
       <c r="D269" s="50" t="s">
         <v>582</v>
       </c>
       <c r="E269" s="50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F269" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G269" s="50" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="H269" s="50" t="s">
         <v>583</v>
@@ -23579,10 +23600,10 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>231</v>
+        <v>584</v>
       </c>
       <c r="L269" s="50" t="s">
-        <v>1</v>
+        <v>585</v>
       </c>
       <c r="M269" s="50" t="s">
         <v>1</v>
@@ -23593,9 +23614,7 @@
       <c r="O269" s="50">
         <v>0</v>
       </c>
-      <c r="P269" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P269" s="50"/>
       <c r="Q269" s="50">
         <v>0</v>
       </c>
@@ -23638,22 +23657,22 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>330052</v>
+        <v>330047</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E270" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F270" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23662,7 +23681,7 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>295</v>
+        <v>588</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
@@ -23676,9 +23695,7 @@
       <c r="O270" s="50">
         <v>0</v>
       </c>
-      <c r="P270" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P270" s="50"/>
       <c r="Q270" s="50">
         <v>0</v>
       </c>
@@ -23721,22 +23738,22 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>330053</v>
+        <v>330048</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E271" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F271" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G271" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -23745,7 +23762,7 @@
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="L271" s="50" t="s">
         <v>1</v>
@@ -23771,8 +23788,8 @@
       <c r="S271" s="50">
         <v>0</v>
       </c>
-      <c r="T271" s="50">
-        <v>0</v>
+      <c r="T271" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U271" s="50">
         <v>0</v>
@@ -23804,22 +23821,22 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>330054</v>
+        <v>330049</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E272" s="50">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F272" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G272" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23828,10 +23845,10 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -23842,9 +23859,7 @@
       <c r="O272" s="50">
         <v>0</v>
       </c>
-      <c r="P272" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P272" s="50"/>
       <c r="Q272" s="50">
         <v>0</v>
       </c>
@@ -23854,8 +23869,8 @@
       <c r="S272" s="50">
         <v>0</v>
       </c>
-      <c r="T272" s="50" t="s">
-        <v>61</v>
+      <c r="T272" s="50">
+        <v>0</v>
       </c>
       <c r="U272" s="50">
         <v>0</v>
@@ -23887,22 +23902,22 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>330055</v>
+        <v>330050</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E273" s="50">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F273" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -23911,7 +23926,7 @@
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="L273" s="50" t="s">
         <v>1</v>
@@ -23925,9 +23940,7 @@
       <c r="O273" s="50">
         <v>0</v>
       </c>
-      <c r="P273" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P273" s="50"/>
       <c r="Q273" s="50">
         <v>0</v>
       </c>
@@ -23970,22 +23983,22 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>330056</v>
+        <v>330051</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E274" s="50">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F274" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" s="50" t="s">
         <v>139</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -23994,7 +24007,7 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>86</v>
+        <v>231</v>
       </c>
       <c r="L274" s="50" t="s">
         <v>1</v>
@@ -24053,22 +24066,22 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>330058</v>
+        <v>330052</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E275" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F275" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G275" s="50" t="s">
         <v>139</v>
       </c>
       <c r="H275" s="50" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="I275" s="50" t="s">
         <v>78</v>
@@ -24077,7 +24090,7 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>97</v>
+        <v>295</v>
       </c>
       <c r="L275" s="50" t="s">
         <v>1</v>
@@ -24103,8 +24116,8 @@
       <c r="S275" s="50">
         <v>0</v>
       </c>
-      <c r="T275" s="50" t="s">
-        <v>61</v>
+      <c r="T275" s="50">
+        <v>0</v>
       </c>
       <c r="U275" s="50">
         <v>0</v>
@@ -24136,22 +24149,22 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>330061</v>
+        <v>330053</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E276" s="50">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F276" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24160,7 +24173,7 @@
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>598</v>
+        <v>247</v>
       </c>
       <c r="L276" s="50" t="s">
         <v>1</v>
@@ -24219,22 +24232,22 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>330062</v>
+        <v>330054</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E277" s="50">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F277" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H277" s="50" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>78</v>
@@ -24243,7 +24256,7 @@
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>601</v>
+        <v>97</v>
       </c>
       <c r="L277" s="50" t="s">
         <v>1</v>
@@ -24269,8 +24282,8 @@
       <c r="S277" s="50">
         <v>0</v>
       </c>
-      <c r="T277" s="50">
-        <v>0</v>
+      <c r="T277" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U277" s="50">
         <v>0</v>
@@ -24302,22 +24315,22 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>330063</v>
+        <v>330055</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E278" s="50">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F278" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24326,10 +24339,10 @@
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
@@ -24385,13 +24398,13 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>330064</v>
+        <v>330056</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E279" s="50">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F279" s="50">
         <v>0</v>
@@ -24400,7 +24413,7 @@
         <v>139</v>
       </c>
       <c r="H279" s="50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>78</v>
@@ -24409,13 +24422,13 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M279" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N279" s="50">
         <v>33</v>
@@ -24468,22 +24481,22 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>330065</v>
+        <v>330058</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E280" s="50">
         <v>5</v>
       </c>
       <c r="F280" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G280" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>78</v>
@@ -24492,7 +24505,7 @@
         <v>62</v>
       </c>
       <c r="K280" s="50" t="s">
-        <v>298</v>
+        <v>97</v>
       </c>
       <c r="L280" s="50" t="s">
         <v>1</v>
@@ -24551,22 +24564,22 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>330067</v>
+        <v>330061</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E281" s="50">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F281" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G281" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>78</v>
@@ -24575,7 +24588,7 @@
         <v>62</v>
       </c>
       <c r="K281" s="50" t="s">
-        <v>231</v>
+        <v>612</v>
       </c>
       <c r="L281" s="50" t="s">
         <v>1</v>
@@ -24634,22 +24647,22 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>330068</v>
+        <v>330062</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E282" s="50">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F282" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G282" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H282" s="50" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I282" s="50" t="s">
         <v>78</v>
@@ -24658,7 +24671,7 @@
         <v>62</v>
       </c>
       <c r="K282" s="50" t="s">
-        <v>97</v>
+        <v>615</v>
       </c>
       <c r="L282" s="50" t="s">
         <v>1</v>
@@ -24684,8 +24697,8 @@
       <c r="S282" s="50">
         <v>0</v>
       </c>
-      <c r="T282" s="50" t="s">
-        <v>61</v>
+      <c r="T282" s="50">
+        <v>0</v>
       </c>
       <c r="U282" s="50">
         <v>0</v>
@@ -24717,22 +24730,22 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>330069</v>
+        <v>330063</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E283" s="50">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F283" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G283" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H283" s="50" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I283" s="50" t="s">
         <v>78</v>
@@ -24741,10 +24754,10 @@
         <v>62</v>
       </c>
       <c r="K283" s="50" t="s">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="L283" s="50" t="s">
-        <v>614</v>
+        <v>61</v>
       </c>
       <c r="M283" s="50" t="s">
         <v>1</v>
@@ -24755,7 +24768,9 @@
       <c r="O283" s="50">
         <v>0</v>
       </c>
-      <c r="P283" s="50"/>
+      <c r="P283" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q283" s="50">
         <v>0</v>
       </c>
@@ -24798,22 +24813,22 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>330070</v>
+        <v>330064</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E284" s="50">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F284" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="I284" s="50" t="s">
         <v>78</v>
@@ -24822,13 +24837,13 @@
         <v>62</v>
       </c>
       <c r="K284" s="50" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="L284" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M284" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N284" s="50">
         <v>33</v>
@@ -24836,7 +24851,9 @@
       <c r="O284" s="50">
         <v>0</v>
       </c>
-      <c r="P284" s="50"/>
+      <c r="P284" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q284" s="50">
         <v>0</v>
       </c>
@@ -24868,6 +24885,417 @@
         <v>0</v>
       </c>
       <c r="AA284" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="50">
+        <v>280</v>
+      </c>
+      <c r="B285" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C285" s="50">
+        <v>330065</v>
+      </c>
+      <c r="D285" s="50" t="s">
+        <v>620</v>
+      </c>
+      <c r="E285" s="50">
+        <v>5</v>
+      </c>
+      <c r="F285" s="50">
+        <v>2</v>
+      </c>
+      <c r="G285" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H285" s="50" t="s">
+        <v>621</v>
+      </c>
+      <c r="I285" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J285" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K285" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="L285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N285" s="50">
+        <v>33</v>
+      </c>
+      <c r="O285" s="50">
+        <v>0</v>
+      </c>
+      <c r="P285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q285" s="50">
+        <v>0</v>
+      </c>
+      <c r="R285" s="50">
+        <v>0</v>
+      </c>
+      <c r="S285" s="50">
+        <v>0</v>
+      </c>
+      <c r="T285" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U285" s="50">
+        <v>0</v>
+      </c>
+      <c r="V285" s="50">
+        <v>0</v>
+      </c>
+      <c r="W285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y285" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z285" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA285" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="50">
+        <v>281</v>
+      </c>
+      <c r="B286" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C286" s="50">
+        <v>330067</v>
+      </c>
+      <c r="D286" s="50" t="s">
+        <v>622</v>
+      </c>
+      <c r="E286" s="50">
+        <v>4</v>
+      </c>
+      <c r="F286" s="50">
+        <v>1</v>
+      </c>
+      <c r="G286" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H286" s="50" t="s">
+        <v>623</v>
+      </c>
+      <c r="I286" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J286" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K286" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="L286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N286" s="50">
+        <v>33</v>
+      </c>
+      <c r="O286" s="50">
+        <v>0</v>
+      </c>
+      <c r="P286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q286" s="50">
+        <v>0</v>
+      </c>
+      <c r="R286" s="50">
+        <v>0</v>
+      </c>
+      <c r="S286" s="50">
+        <v>0</v>
+      </c>
+      <c r="T286" s="50">
+        <v>0</v>
+      </c>
+      <c r="U286" s="50">
+        <v>0</v>
+      </c>
+      <c r="V286" s="50">
+        <v>0</v>
+      </c>
+      <c r="W286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y286" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z286" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA286" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="50">
+        <v>282</v>
+      </c>
+      <c r="B287" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C287" s="50">
+        <v>330068</v>
+      </c>
+      <c r="D287" s="50" t="s">
+        <v>624</v>
+      </c>
+      <c r="E287" s="50">
+        <v>5</v>
+      </c>
+      <c r="F287" s="50">
+        <v>1</v>
+      </c>
+      <c r="G287" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H287" s="50" t="s">
+        <v>625</v>
+      </c>
+      <c r="I287" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J287" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K287" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="L287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N287" s="50">
+        <v>33</v>
+      </c>
+      <c r="O287" s="50">
+        <v>0</v>
+      </c>
+      <c r="P287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q287" s="50">
+        <v>0</v>
+      </c>
+      <c r="R287" s="50">
+        <v>0</v>
+      </c>
+      <c r="S287" s="50">
+        <v>0</v>
+      </c>
+      <c r="T287" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U287" s="50">
+        <v>0</v>
+      </c>
+      <c r="V287" s="50">
+        <v>0</v>
+      </c>
+      <c r="W287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y287" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z287" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA287" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="50">
+        <v>283</v>
+      </c>
+      <c r="B288" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C288" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D288" s="50" t="s">
+        <v>626</v>
+      </c>
+      <c r="E288" s="50">
+        <v>16</v>
+      </c>
+      <c r="F288" s="50">
+        <v>1</v>
+      </c>
+      <c r="G288" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H288" s="50" t="s">
+        <v>627</v>
+      </c>
+      <c r="I288" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J288" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K288" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="L288" s="50" t="s">
+        <v>628</v>
+      </c>
+      <c r="M288" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N288" s="50">
+        <v>33</v>
+      </c>
+      <c r="O288" s="50">
+        <v>0</v>
+      </c>
+      <c r="P288" s="50"/>
+      <c r="Q288" s="50">
+        <v>0</v>
+      </c>
+      <c r="R288" s="50">
+        <v>0</v>
+      </c>
+      <c r="S288" s="50">
+        <v>0</v>
+      </c>
+      <c r="T288" s="50">
+        <v>0</v>
+      </c>
+      <c r="U288" s="50">
+        <v>0</v>
+      </c>
+      <c r="V288" s="50">
+        <v>0</v>
+      </c>
+      <c r="W288" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X288" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y288" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z288" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA288" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="50">
+        <v>284</v>
+      </c>
+      <c r="B289" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C289" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D289" s="50" t="s">
+        <v>629</v>
+      </c>
+      <c r="E289" s="50">
+        <v>3</v>
+      </c>
+      <c r="F289" s="50">
+        <v>1</v>
+      </c>
+      <c r="G289" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H289" s="50" t="s">
+        <v>630</v>
+      </c>
+      <c r="I289" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J289" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K289" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="L289" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M289" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N289" s="50">
+        <v>33</v>
+      </c>
+      <c r="O289" s="50">
+        <v>0</v>
+      </c>
+      <c r="P289" s="50"/>
+      <c r="Q289" s="50">
+        <v>0</v>
+      </c>
+      <c r="R289" s="50">
+        <v>0</v>
+      </c>
+      <c r="S289" s="50">
+        <v>0</v>
+      </c>
+      <c r="T289" s="50">
+        <v>0</v>
+      </c>
+      <c r="U289" s="50">
+        <v>0</v>
+      </c>
+      <c r="V289" s="50">
+        <v>0</v>
+      </c>
+      <c r="W289" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X289" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y289" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z289" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA289" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -1294,19 +1294,19 @@
     <t>112,7.999978,54</t>
   </si>
   <si>
-    <t>123,8.003199,60</t>
-  </si>
-  <si>
-    <t>120.75,8,62.25_120.75,8,57.75_125.25,8,57.75_125.25,8,62.25</t>
+    <t>115,7.999978,66</t>
+  </si>
+  <si>
+    <t>112.75,8,68.25_112.75,8,63.75_117.25,8,63.75_117.25,8,68.25</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>146,7.999978,61</t>
-  </si>
-  <si>
-    <t>144.5,8,59_147.5,8,59_147.5,8,63_144.5,8,63</t>
+    <t>130,8.003199,66</t>
+  </si>
+  <si>
+    <t>128.5,8,64_131.5,8,64_131.5,8,68_128.5,8,68</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1315,31 +1315,31 @@
     <t>q</t>
   </si>
   <si>
+    <t>117,7.999978,86</t>
+  </si>
+  <si>
+    <t>118,8,85_118,8,87_116,8,87_116,8,85</t>
+  </si>
+  <si>
+    <t>74857</t>
+  </si>
+  <si>
+    <t>119,8.003199,86</t>
+  </si>
+  <si>
+    <t>120,8,85_120,8,87_118,8,87_118,8,85</t>
+  </si>
+  <si>
     <t>121,8.003199,86</t>
   </si>
   <si>
     <t>122,8,85_122,8,87_120,8,87_120,8,85</t>
   </si>
   <si>
-    <t>74857</t>
-  </si>
-  <si>
-    <t>123,8.003199,86</t>
-  </si>
-  <si>
-    <t>124,8,85_124,8,87_122,8,87_122,8,85</t>
-  </si>
-  <si>
-    <t>125,8.003199,86</t>
-  </si>
-  <si>
-    <t>126,8,85_126,8,87_124,8,87_124,8,85</t>
-  </si>
-  <si>
     <t>129.307510375977,7.999978,74.7048797607422</t>
   </si>
   <si>
-    <t>129.31,0.00,74.70,158.54,0.00,74.70,158.54,0.00,45.38,129.31,0.00,45.38</t>
+    <t>117.00,0.00,77.00,145.00,0.00,77.00,145.00,0.00,55.00,117.00,0.00,55.00</t>
   </si>
   <si>
     <t>97,7.999978,86.1221466064453</t>
@@ -1354,31 +1354,31 @@
     <t>74865</t>
   </si>
   <si>
-    <t>135,7.999978,86</t>
-  </si>
-  <si>
-    <t>136.5,8,87.5_133.5,8,87.5_133.5,8,84.5_136.5,8,84.5</t>
-  </si>
-  <si>
-    <t>109.819999694824,7.999978,93</t>
-  </si>
-  <si>
-    <t>111.82,8,94_107.82,8,94_107.82,8,92_111.82,8,92</t>
+    <t>130,7.999978,86</t>
+  </si>
+  <si>
+    <t>131.5,8,87.5_128.5,8,87.5_128.5,8,84.5_131.5,8,84.5</t>
+  </si>
+  <si>
+    <t>104,7.999978,93</t>
+  </si>
+  <si>
+    <t>106,8,94_102,8,94_102,8,92_106,8,92</t>
   </si>
   <si>
     <t>74863</t>
   </si>
   <si>
-    <t>77.1564254760742,7.999978,98</t>
-  </si>
-  <si>
-    <t>78.65643,8,96_78.65643,8,100_75.65643,8,100_75.65643,8,96</t>
+    <t>81,7.999978,98</t>
+  </si>
+  <si>
+    <t>82.5,8,96_82.5,8,100_79.5,8,100_79.5,8,96</t>
   </si>
   <si>
     <t>87.1449661254883,7.822312,117.04264831543</t>
   </si>
   <si>
-    <t>87.14,0.00,117.04,116.84,0.00,117.04,116.84,0.00,94.90,87.14,0.00,94.90</t>
+    <t>87.14,0.00,117.04,113.00,0.00,117.04,113.00,0.00,94.90,87.14,0.00,94.90</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1291,10 +1291,10 @@
     <t>48,5.9997,84</t>
   </si>
   <si>
-    <t>112,7.999978,54</t>
-  </si>
-  <si>
-    <t>115,7.999978,66</t>
+    <t>110,7.999978,54</t>
+  </si>
+  <si>
+    <t>115,8.002208,66</t>
   </si>
   <si>
     <t>112.75,8,68.25_112.75,8,63.75_117.25,8,63.75_117.25,8,68.25</t>
@@ -1303,7 +1303,7 @@
     <t>70201</t>
   </si>
   <si>
-    <t>130,8.003199,66</t>
+    <t>130,8.002208,66</t>
   </si>
   <si>
     <t>128.5,8,64_131.5,8,64_131.5,8,68_128.5,8,68</t>
@@ -1315,7 +1315,7 @@
     <t>q</t>
   </si>
   <si>
-    <t>117,7.999978,86</t>
+    <t>117,8.003199,86</t>
   </si>
   <si>
     <t>118,8,85_118,8,87_116,8,87_116,8,85</t>
@@ -1375,12 +1375,90 @@
     <t>82.5,8,96_82.5,8,100_79.5,8,100_79.5,8,96</t>
   </si>
   <si>
-    <t>87.1449661254883,7.822312,117.04264831543</t>
+    <t>87.1449661254883,7.999978,117.04264831543</t>
   </si>
   <si>
     <t>87.14,0.00,117.04,113.00,0.00,117.04,113.00,0.00,94.90,87.14,0.00,94.90</t>
   </si>
   <si>
+    <t>58,7.999978,104</t>
+  </si>
+  <si>
+    <t>60.25,8,105.5_55.75,8,105.5_55.75,8,102.5_60.25,8,102.5</t>
+  </si>
+  <si>
+    <t>70308</t>
+  </si>
+  <si>
+    <t>57.7461738586426,7.999978,97</t>
+  </si>
+  <si>
+    <t>59.74617,8,98.5_55.74617,8,98.5_55.74617,8,95.5_59.74617,8,95.5</t>
+  </si>
+  <si>
+    <t>63,9.211463,84</t>
+  </si>
+  <si>
+    <t>62,8,86_62,8,82_64,8,82_64,8,86</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
+  </si>
+  <si>
+    <t>74871</t>
+  </si>
+  <si>
+    <t>98,7.999978,69</t>
+  </si>
+  <si>
+    <t>99,9.000299,70_97,9.000299,70_97,9.000299,68_99,9.000299,68</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
+  </si>
+  <si>
+    <t>90,7.999978,70</t>
+  </si>
+  <si>
+    <t>87.75,8,72.25_87.75,8,67.75_92.25,8,67.75_92.25,8,72.25</t>
+  </si>
+  <si>
+    <t>74876</t>
+  </si>
+  <si>
+    <t>70301</t>
+  </si>
+  <si>
+    <t>58,7.999978,77</t>
+  </si>
+  <si>
+    <t>60.25,7.999999,79.25_55.75,7.999999,79.25_55.75,7.999999,74.75_60.25,7.999999,74.75</t>
+  </si>
+  <si>
+    <t>70302</t>
+  </si>
+  <si>
+    <t>111,8.003199,124</t>
+  </si>
+  <si>
+    <t>116,7.999999,126_109,7.999999,126_109,7.999999,122_116,7.999999,122</t>
+  </si>
+  <si>
+    <t>74875</t>
+  </si>
+  <si>
+    <t>58,7.999978,70</t>
+  </si>
+  <si>
+    <t>59,7.999999,71_57,7.999999,71_57,7.999999,69_59,7.999999,69</t>
+  </si>
+  <si>
+    <t>58,7.999978,56.6089134216309</t>
+  </si>
+  <si>
+    <t>59.5,8,54.60891_59.5,8,58.60891_56.5,8,58.60891_56.5,8,54.60891</t>
+  </si>
+  <si>
     <t>37,-8.769137E-05,28</t>
   </si>
   <si>
@@ -1771,9 +1849,6 @@
     <t>52,0.003075539,39_52,0.003075539,35_54,0.003075539,35_54,0.003075539,39</t>
   </si>
   <si>
-    <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
-  </si>
-  <si>
     <t>330047</t>
   </si>
   <si>
@@ -1781,9 +1856,6 @@
   </si>
   <si>
     <t>76.22073,0.003075539,26_74.22073,0.003075539,26_74.22073,0.003075539,24_76.22073,0.003075539,24</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
     <t>48,0.003195092,30</t>
@@ -3001,7 +3073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA289"/>
+  <dimension ref="A1:AA298"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -18479,28 +18551,31 @@
         <v>58</v>
       </c>
       <c r="C204" s="50">
-        <v>84928</v>
+        <v>74868</v>
       </c>
       <c r="D204" s="50" t="s">
         <v>454</v>
       </c>
       <c r="E204" s="50">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F204" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G204" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H204" s="50" t="s">
+        <v>455</v>
+      </c>
       <c r="I204" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J204" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K204" s="50" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="L204" s="50" t="s">
         <v>1</v>
@@ -18509,7 +18584,7 @@
         <v>1</v>
       </c>
       <c r="N204" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O204" s="50">
         <v>0</v>
@@ -18526,11 +18601,11 @@
       <c r="S204" s="50">
         <v>0</v>
       </c>
-      <c r="T204" s="50">
-        <v>0</v>
+      <c r="T204" s="50" t="s">
+        <v>456</v>
       </c>
       <c r="U204" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V204" s="50">
         <v>0</v>
@@ -18559,22 +18634,22 @@
         <v>58</v>
       </c>
       <c r="C205" s="50">
-        <v>84929</v>
+        <v>74869</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E205" s="50">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F205" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -18583,21 +18658,23 @@
         <v>62</v>
       </c>
       <c r="K205" s="50" t="s">
-        <v>378</v>
+        <v>295</v>
       </c>
       <c r="L205" s="50" t="s">
-        <v>457</v>
+        <v>1</v>
       </c>
       <c r="M205" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N205" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O205" s="50">
         <v>0</v>
       </c>
-      <c r="P205" s="50"/>
+      <c r="P205" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q205" s="50">
         <v>0</v>
       </c>
@@ -18605,7 +18682,7 @@
         <v>0</v>
       </c>
       <c r="S205" s="50">
-        <v>0</v>
+        <v>70004</v>
       </c>
       <c r="T205" s="50">
         <v>0</v>
@@ -18640,37 +18717,40 @@
         <v>58</v>
       </c>
       <c r="C206" s="50">
-        <v>84930</v>
+        <v>74870</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E206" s="50">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F206" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G206" s="50" t="s">
-        <v>139</v>
+        <v>84</v>
+      </c>
+      <c r="H206" s="50" t="s">
+        <v>460</v>
       </c>
       <c r="I206" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J206" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
-        <v>389</v>
+        <v>461</v>
       </c>
       <c r="L206" s="50" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M206" s="50" t="s">
-        <v>460</v>
+        <v>1</v>
       </c>
       <c r="N206" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O206" s="50">
         <v>0</v>
@@ -18718,22 +18798,22 @@
         <v>58</v>
       </c>
       <c r="C207" s="50">
-        <v>84931</v>
+        <v>74871</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E207" s="50">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F207" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G207" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -18742,7 +18822,7 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="L207" s="50" t="s">
         <v>1</v>
@@ -18751,7 +18831,7 @@
         <v>1</v>
       </c>
       <c r="N207" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O207" s="50">
         <v>0</v>
@@ -18799,42 +18879,47 @@
         <v>58</v>
       </c>
       <c r="C208" s="50">
-        <v>84932</v>
+        <v>74872</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E208" s="50">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F208" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G208" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="H208" s="50" t="s">
+        <v>467</v>
       </c>
       <c r="I208" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J208" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K208" s="50" t="s">
-        <v>389</v>
+        <v>298</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M208" s="50" t="s">
-        <v>460</v>
+        <v>1</v>
       </c>
       <c r="N208" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O208" s="50">
         <v>0</v>
       </c>
-      <c r="P208" s="50"/>
+      <c r="P208" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q208" s="50">
         <v>0</v>
       </c>
@@ -18844,8 +18929,8 @@
       <c r="S208" s="50">
         <v>0</v>
       </c>
-      <c r="T208" s="50">
-        <v>0</v>
+      <c r="T208" s="50" t="s">
+        <v>469</v>
       </c>
       <c r="U208" s="50">
         <v>0</v>
@@ -18877,22 +18962,22 @@
         <v>58</v>
       </c>
       <c r="C209" s="50">
-        <v>84933</v>
+        <v>74873</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E209" s="50">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F209" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G209" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -18901,7 +18986,7 @@
         <v>62</v>
       </c>
       <c r="K209" s="50" t="s">
-        <v>393</v>
+        <v>223</v>
       </c>
       <c r="L209" s="50" t="s">
         <v>1</v>
@@ -18910,12 +18995,14 @@
         <v>1</v>
       </c>
       <c r="N209" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O209" s="50">
         <v>0</v>
       </c>
-      <c r="P209" s="50"/>
+      <c r="P209" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q209" s="50">
         <v>0</v>
       </c>
@@ -18925,8 +19012,8 @@
       <c r="S209" s="50">
         <v>0</v>
       </c>
-      <c r="T209" s="50">
-        <v>0</v>
+      <c r="T209" s="50" t="s">
+        <v>472</v>
       </c>
       <c r="U209" s="50">
         <v>0</v>
@@ -18958,22 +19045,22 @@
         <v>58</v>
       </c>
       <c r="C210" s="50">
-        <v>84934</v>
+        <v>74874</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E210" s="50">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F210" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G210" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -18982,16 +19069,16 @@
         <v>62</v>
       </c>
       <c r="K210" s="50" t="s">
-        <v>399</v>
+        <v>101</v>
       </c>
       <c r="L210" s="50" t="s">
-        <v>1</v>
+        <v>475</v>
       </c>
       <c r="M210" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N210" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O210" s="50">
         <v>0</v>
@@ -19039,22 +19126,22 @@
         <v>58</v>
       </c>
       <c r="C211" s="50">
-        <v>84935</v>
+        <v>74875</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E211" s="50">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F211" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G211" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19063,7 +19150,7 @@
         <v>62</v>
       </c>
       <c r="K211" s="50" t="s">
-        <v>404</v>
+        <v>89</v>
       </c>
       <c r="L211" s="50" t="s">
         <v>1</v>
@@ -19072,7 +19159,7 @@
         <v>1</v>
       </c>
       <c r="N211" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O211" s="50">
         <v>0</v>
@@ -19120,22 +19207,22 @@
         <v>58</v>
       </c>
       <c r="C212" s="50">
-        <v>84936</v>
+        <v>74876</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E212" s="50">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F212" s="50">
         <v>3</v>
       </c>
       <c r="G212" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19144,7 +19231,7 @@
         <v>62</v>
       </c>
       <c r="K212" s="50" t="s">
-        <v>401</v>
+        <v>247</v>
       </c>
       <c r="L212" s="50" t="s">
         <v>1</v>
@@ -19153,12 +19240,14 @@
         <v>1</v>
       </c>
       <c r="N212" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O212" s="50">
         <v>0</v>
       </c>
-      <c r="P212" s="50"/>
+      <c r="P212" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q212" s="50">
         <v>0</v>
       </c>
@@ -19166,7 +19255,7 @@
         <v>0</v>
       </c>
       <c r="S212" s="50">
-        <v>0</v>
+        <v>70003</v>
       </c>
       <c r="T212" s="50">
         <v>0</v>
@@ -19175,7 +19264,7 @@
         <v>0</v>
       </c>
       <c r="V212" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W212" s="50" t="s">
         <v>1</v>
@@ -19201,31 +19290,28 @@
         <v>58</v>
       </c>
       <c r="C213" s="50">
-        <v>84937</v>
+        <v>84928</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E213" s="50">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F213" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G213" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H213" s="50" t="s">
-        <v>474</v>
+        <v>60</v>
       </c>
       <c r="I213" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J213" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K213" s="50" t="s">
-        <v>397</v>
+        <v>75</v>
       </c>
       <c r="L213" s="50" t="s">
         <v>1</v>
@@ -19239,7 +19325,9 @@
       <c r="O213" s="50">
         <v>0</v>
       </c>
-      <c r="P213" s="50"/>
+      <c r="P213" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q213" s="50">
         <v>0</v>
       </c>
@@ -19256,7 +19344,7 @@
         <v>0</v>
       </c>
       <c r="V213" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W213" s="50" t="s">
         <v>1</v>
@@ -19282,22 +19370,22 @@
         <v>58</v>
       </c>
       <c r="C214" s="50">
-        <v>84938</v>
+        <v>84929</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E214" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F214" s="50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G214" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19306,10 +19394,10 @@
         <v>62</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>1</v>
+        <v>483</v>
       </c>
       <c r="M214" s="50" t="s">
         <v>1</v>
@@ -19363,37 +19451,34 @@
         <v>58</v>
       </c>
       <c r="C215" s="50">
-        <v>84939</v>
+        <v>84930</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E215" s="50">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F215" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H215" s="50" t="s">
-        <v>478</v>
+        <v>139</v>
       </c>
       <c r="I215" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J215" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="L215" s="50" t="s">
-        <v>1</v>
+        <v>485</v>
       </c>
       <c r="M215" s="50" t="s">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="N215" s="50">
         <v>8</v>
@@ -19444,22 +19529,22 @@
         <v>58</v>
       </c>
       <c r="C216" s="50">
-        <v>84940</v>
+        <v>84931</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E216" s="50">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F216" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -19468,7 +19553,7 @@
         <v>62</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L216" s="50" t="s">
         <v>1</v>
@@ -19525,37 +19610,34 @@
         <v>58</v>
       </c>
       <c r="C217" s="50">
-        <v>84941</v>
+        <v>84932</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E217" s="50">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="F217" s="50">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G217" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H217" s="50" t="s">
-        <v>482</v>
-      </c>
       <c r="I217" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J217" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>193</v>
+        <v>389</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="N217" s="50">
         <v>8</v>
@@ -19606,34 +19688,37 @@
         <v>58</v>
       </c>
       <c r="C218" s="50">
-        <v>84942</v>
+        <v>84933</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E218" s="50">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F218" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G218" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H218" s="50" t="s">
+        <v>492</v>
+      </c>
       <c r="I218" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J218" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K218" s="50" t="s">
-        <v>286</v>
+        <v>393</v>
       </c>
       <c r="L218" s="50" t="s">
-        <v>485</v>
+        <v>1</v>
       </c>
       <c r="M218" s="50" t="s">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="N218" s="50">
         <v>8</v>
@@ -19684,22 +19769,22 @@
         <v>58</v>
       </c>
       <c r="C219" s="50">
-        <v>84943</v>
+        <v>84934</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E219" s="50">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F219" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G219" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>78</v>
@@ -19708,7 +19793,7 @@
         <v>62</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>277</v>
+        <v>399</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -19765,34 +19850,37 @@
         <v>58</v>
       </c>
       <c r="C220" s="50">
-        <v>84944</v>
+        <v>84935</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E220" s="50">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F220" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G220" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H220" s="50" t="s">
+        <v>496</v>
+      </c>
       <c r="I220" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J220" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>272</v>
+        <v>404</v>
       </c>
       <c r="L220" s="50" t="s">
-        <v>490</v>
+        <v>1</v>
       </c>
       <c r="M220" s="50" t="s">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="N220" s="50">
         <v>8</v>
@@ -19843,22 +19931,22 @@
         <v>58</v>
       </c>
       <c r="C221" s="50">
-        <v>84945</v>
+        <v>84936</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E221" s="50">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F221" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G221" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H221" s="50" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="I221" s="50" t="s">
         <v>78</v>
@@ -19867,7 +19955,7 @@
         <v>62</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>284</v>
+        <v>401</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -19898,7 +19986,7 @@
         <v>0</v>
       </c>
       <c r="V221" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W221" s="50" t="s">
         <v>1</v>
@@ -19924,28 +20012,31 @@
         <v>58</v>
       </c>
       <c r="C222" s="50">
-        <v>84946</v>
+        <v>84937</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E222" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F222" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G222" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
+      </c>
+      <c r="H222" s="50" t="s">
+        <v>500</v>
       </c>
       <c r="I222" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J222" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>494</v>
+        <v>397</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -19976,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="V222" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W222" s="50" t="s">
         <v>1</v>
@@ -20002,28 +20093,31 @@
         <v>58</v>
       </c>
       <c r="C223" s="50">
-        <v>84947</v>
+        <v>84938</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E223" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F223" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G223" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H223" s="50" t="s">
+        <v>502</v>
+      </c>
       <c r="I223" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J223" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K223" s="50" t="s">
-        <v>302</v>
+        <v>387</v>
       </c>
       <c r="L223" s="50" t="s">
         <v>1</v>
@@ -20080,13 +20174,13 @@
         <v>58</v>
       </c>
       <c r="C224" s="50">
-        <v>84948</v>
+        <v>84939</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E224" s="50">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F224" s="50">
         <v>0</v>
@@ -20094,14 +20188,17 @@
       <c r="G224" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H224" s="50" t="s">
+        <v>504</v>
+      </c>
       <c r="I224" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J224" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="L224" s="50" t="s">
         <v>1</v>
@@ -20158,13 +20255,13 @@
         <v>58</v>
       </c>
       <c r="C225" s="50">
-        <v>84949</v>
+        <v>84940</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E225" s="50">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F225" s="50">
         <v>0</v>
@@ -20172,14 +20269,17 @@
       <c r="G225" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H225" s="50" t="s">
+        <v>506</v>
+      </c>
       <c r="I225" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J225" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="L225" s="50" t="s">
         <v>1</v>
@@ -20236,31 +20336,34 @@
         <v>58</v>
       </c>
       <c r="C226" s="50">
-        <v>84950</v>
+        <v>84941</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E226" s="50">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F226" s="50">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G226" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H226" s="50" t="s">
+        <v>508</v>
+      </c>
       <c r="I226" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J226" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>302</v>
+        <v>193</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>1</v>
+        <v>509</v>
       </c>
       <c r="M226" s="50" t="s">
         <v>1</v>
@@ -20314,16 +20417,16 @@
         <v>58</v>
       </c>
       <c r="C227" s="50">
-        <v>84951</v>
+        <v>84942</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="E227" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F227" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G227" s="50" t="s">
         <v>60</v>
@@ -20335,13 +20438,13 @@
         <v>62</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>1</v>
+        <v>511</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="N227" s="50">
         <v>8</v>
@@ -20392,28 +20495,31 @@
         <v>58</v>
       </c>
       <c r="C228" s="50">
-        <v>84952</v>
+        <v>84943</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="E228" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F228" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G228" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H228" s="50" t="s">
+        <v>514</v>
+      </c>
       <c r="I228" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J228" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K228" s="50" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="L228" s="50" t="s">
         <v>1</v>
@@ -20470,16 +20576,16 @@
         <v>58</v>
       </c>
       <c r="C229" s="50">
-        <v>84953</v>
+        <v>84944</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="E229" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F229" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G229" s="50" t="s">
         <v>60</v>
@@ -20491,13 +20597,13 @@
         <v>62</v>
       </c>
       <c r="K229" s="50" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>1</v>
+        <v>516</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="N229" s="50">
         <v>8</v>
@@ -20548,28 +20654,31 @@
         <v>58</v>
       </c>
       <c r="C230" s="50">
-        <v>84954</v>
+        <v>84945</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="E230" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F230" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G230" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H230" s="50" t="s">
+        <v>518</v>
+      </c>
       <c r="I230" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J230" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K230" s="50" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="L230" s="50" t="s">
         <v>1</v>
@@ -20626,16 +20735,16 @@
         <v>58</v>
       </c>
       <c r="C231" s="50">
-        <v>84955</v>
+        <v>84946</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E231" s="50">
         <v>56</v>
       </c>
       <c r="F231" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" s="50" t="s">
         <v>60</v>
@@ -20647,7 +20756,7 @@
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>302</v>
+        <v>520</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -20704,10 +20813,10 @@
         <v>58</v>
       </c>
       <c r="C232" s="50">
-        <v>84956</v>
+        <v>84947</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="E232" s="50">
         <v>56</v>
@@ -20782,10 +20891,10 @@
         <v>58</v>
       </c>
       <c r="C233" s="50">
-        <v>84957</v>
+        <v>84948</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="E233" s="50">
         <v>56</v>
@@ -20860,10 +20969,10 @@
         <v>58</v>
       </c>
       <c r="C234" s="50">
-        <v>84958</v>
+        <v>84949</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="E234" s="50">
         <v>56</v>
@@ -20938,10 +21047,10 @@
         <v>58</v>
       </c>
       <c r="C235" s="50">
-        <v>84959</v>
+        <v>84950</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="E235" s="50">
         <v>56</v>
@@ -21016,10 +21125,10 @@
         <v>58</v>
       </c>
       <c r="C236" s="50">
-        <v>84960</v>
+        <v>84951</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="E236" s="50">
         <v>56</v>
@@ -21094,10 +21203,10 @@
         <v>58</v>
       </c>
       <c r="C237" s="50">
-        <v>84961</v>
+        <v>84952</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="E237" s="50">
         <v>56</v>
@@ -21172,10 +21281,10 @@
         <v>58</v>
       </c>
       <c r="C238" s="50">
-        <v>84962</v>
+        <v>84953</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="E238" s="50">
         <v>56</v>
@@ -21250,10 +21359,10 @@
         <v>58</v>
       </c>
       <c r="C239" s="50">
-        <v>84963</v>
+        <v>84954</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="E239" s="50">
         <v>56</v>
@@ -21328,10 +21437,10 @@
         <v>58</v>
       </c>
       <c r="C240" s="50">
-        <v>84964</v>
+        <v>84955</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="E240" s="50">
         <v>56</v>
@@ -21406,10 +21515,10 @@
         <v>58</v>
       </c>
       <c r="C241" s="50">
-        <v>84965</v>
+        <v>84956</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="E241" s="50">
         <v>56</v>
@@ -21484,10 +21593,10 @@
         <v>58</v>
       </c>
       <c r="C242" s="50">
-        <v>84966</v>
+        <v>84957</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="E242" s="50">
         <v>56</v>
@@ -21562,10 +21671,10 @@
         <v>58</v>
       </c>
       <c r="C243" s="50">
-        <v>84967</v>
+        <v>84958</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="E243" s="50">
         <v>56</v>
@@ -21640,10 +21749,10 @@
         <v>58</v>
       </c>
       <c r="C244" s="50">
-        <v>84968</v>
+        <v>84959</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="E244" s="50">
         <v>56</v>
@@ -21718,31 +21827,28 @@
         <v>58</v>
       </c>
       <c r="C245" s="50">
-        <v>84969</v>
+        <v>84960</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="E245" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F245" s="50">
         <v>0</v>
       </c>
       <c r="G245" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="H245" s="50" t="s">
-        <v>518</v>
+        <v>60</v>
       </c>
       <c r="I245" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J245" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>519</v>
+        <v>302</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
@@ -21799,31 +21905,28 @@
         <v>58</v>
       </c>
       <c r="C246" s="50">
-        <v>84970</v>
+        <v>84961</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="E246" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F246" s="50">
         <v>0</v>
       </c>
       <c r="G246" s="50" t="s">
-        <v>521</v>
-      </c>
-      <c r="H246" s="50" t="s">
-        <v>522</v>
+        <v>60</v>
       </c>
       <c r="I246" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J246" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>523</v>
+        <v>302</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
@@ -21880,37 +21983,34 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>84971</v>
+        <v>84962</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="E247" s="50">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F247" s="50">
         <v>0</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="H247" s="50" t="s">
-        <v>525</v>
+        <v>60</v>
       </c>
       <c r="I247" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J247" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>526</v>
+        <v>302</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M247" s="50" t="s">
-        <v>527</v>
+        <v>1</v>
       </c>
       <c r="N247" s="50">
         <v>8</v>
@@ -21961,31 +22061,28 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>84972</v>
+        <v>84963</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E248" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F248" s="50">
         <v>0</v>
       </c>
       <c r="G248" s="50" t="s">
-        <v>529</v>
-      </c>
-      <c r="H248" s="50" t="s">
-        <v>530</v>
+        <v>60</v>
       </c>
       <c r="I248" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J248" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>523</v>
+        <v>302</v>
       </c>
       <c r="L248" s="50" t="s">
         <v>1</v>
@@ -22042,34 +22139,31 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>84973</v>
+        <v>84964</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="E249" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F249" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G249" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H249" s="50" t="s">
-        <v>532</v>
-      </c>
       <c r="I249" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J249" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="L249" s="50" t="s">
-        <v>533</v>
+        <v>1</v>
       </c>
       <c r="M249" s="50" t="s">
         <v>1</v>
@@ -22123,13 +22217,13 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>84974</v>
+        <v>84965</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E250" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F250" s="50">
         <v>0</v>
@@ -22137,17 +22231,14 @@
       <c r="G250" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H250" s="50" t="s">
-        <v>535</v>
-      </c>
       <c r="I250" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J250" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>523</v>
+        <v>302</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
@@ -22204,16 +22295,16 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>84976</v>
+        <v>84966</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E251" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F251" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G251" s="50" t="s">
         <v>60</v>
@@ -22224,27 +22315,55 @@
       <c r="J251" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K251" s="50"/>
-      <c r="L251" s="50"/>
-      <c r="M251" s="50"/>
+      <c r="K251" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="L251" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M251" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N251" s="50">
         <v>8</v>
       </c>
-      <c r="O251" s="50"/>
-      <c r="P251" s="50" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q251" s="50"/>
-      <c r="R251" s="50"/>
-      <c r="S251" s="50"/>
-      <c r="T251" s="50"/>
-      <c r="U251" s="50"/>
-      <c r="V251" s="50"/>
-      <c r="W251" s="50"/>
-      <c r="X251" s="50"/>
-      <c r="Y251" s="50"/>
-      <c r="Z251" s="52"/>
-      <c r="AA251" s="50"/>
+      <c r="O251" s="50">
+        <v>0</v>
+      </c>
+      <c r="P251" s="50"/>
+      <c r="Q251" s="50">
+        <v>0</v>
+      </c>
+      <c r="R251" s="50">
+        <v>0</v>
+      </c>
+      <c r="S251" s="50">
+        <v>0</v>
+      </c>
+      <c r="T251" s="50">
+        <v>0</v>
+      </c>
+      <c r="U251" s="50">
+        <v>0</v>
+      </c>
+      <c r="V251" s="50">
+        <v>0</v>
+      </c>
+      <c r="W251" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X251" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y251" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z251" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA251" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="50">
@@ -22254,16 +22373,16 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>84977</v>
+        <v>84967</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E252" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F252" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G252" s="50" t="s">
         <v>60</v>
@@ -22274,27 +22393,55 @@
       <c r="J252" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K252" s="50"/>
-      <c r="L252" s="50"/>
-      <c r="M252" s="50"/>
+      <c r="K252" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="L252" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M252" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N252" s="50">
         <v>8</v>
       </c>
-      <c r="O252" s="50"/>
-      <c r="P252" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="Q252" s="50"/>
-      <c r="R252" s="50"/>
-      <c r="S252" s="50"/>
-      <c r="T252" s="50"/>
-      <c r="U252" s="50"/>
-      <c r="V252" s="50"/>
-      <c r="W252" s="50"/>
-      <c r="X252" s="50"/>
-      <c r="Y252" s="50"/>
-      <c r="Z252" s="52"/>
-      <c r="AA252" s="50"/>
+      <c r="O252" s="50">
+        <v>0</v>
+      </c>
+      <c r="P252" s="50"/>
+      <c r="Q252" s="50">
+        <v>0</v>
+      </c>
+      <c r="R252" s="50">
+        <v>0</v>
+      </c>
+      <c r="S252" s="50">
+        <v>0</v>
+      </c>
+      <c r="T252" s="50">
+        <v>0</v>
+      </c>
+      <c r="U252" s="50">
+        <v>0</v>
+      </c>
+      <c r="V252" s="50">
+        <v>0</v>
+      </c>
+      <c r="W252" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X252" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y252" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z252" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA252" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="50">
@@ -22304,16 +22451,16 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>84978</v>
+        <v>84968</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E253" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F253" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G253" s="50" t="s">
         <v>60</v>
@@ -22324,27 +22471,55 @@
       <c r="J253" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K253" s="50"/>
-      <c r="L253" s="50"/>
-      <c r="M253" s="50"/>
+      <c r="K253" s="50" t="s">
+        <v>302</v>
+      </c>
+      <c r="L253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M253" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N253" s="50">
         <v>8</v>
       </c>
-      <c r="O253" s="50"/>
-      <c r="P253" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="Q253" s="50"/>
-      <c r="R253" s="50"/>
-      <c r="S253" s="50"/>
-      <c r="T253" s="50"/>
-      <c r="U253" s="50"/>
-      <c r="V253" s="50"/>
-      <c r="W253" s="50"/>
-      <c r="X253" s="50"/>
-      <c r="Y253" s="50"/>
-      <c r="Z253" s="52"/>
-      <c r="AA253" s="50"/>
+      <c r="O253" s="50">
+        <v>0</v>
+      </c>
+      <c r="P253" s="50"/>
+      <c r="Q253" s="50">
+        <v>0</v>
+      </c>
+      <c r="R253" s="50">
+        <v>0</v>
+      </c>
+      <c r="S253" s="50">
+        <v>0</v>
+      </c>
+      <c r="T253" s="50">
+        <v>0</v>
+      </c>
+      <c r="U253" s="50">
+        <v>0</v>
+      </c>
+      <c r="V253" s="50">
+        <v>0</v>
+      </c>
+      <c r="W253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z253" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA253" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="50">
@@ -22354,13 +22529,13 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>84979</v>
+        <v>84969</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E254" s="50">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F254" s="50">
         <v>0</v>
@@ -22369,7 +22544,7 @@
         <v>84</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -22378,13 +22553,13 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>328</v>
+        <v>545</v>
       </c>
       <c r="L254" s="50" t="s">
-        <v>544</v>
+        <v>1</v>
       </c>
       <c r="M254" s="50" t="s">
-        <v>545</v>
+        <v>1</v>
       </c>
       <c r="N254" s="50">
         <v>8</v>
@@ -22435,22 +22610,22 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>84980</v>
+        <v>84970</v>
       </c>
       <c r="D255" s="50" t="s">
         <v>546</v>
       </c>
       <c r="E255" s="50">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F255" s="50">
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
-        <v>60</v>
+        <v>547</v>
       </c>
       <c r="H255" s="50" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22459,10 +22634,10 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>325</v>
+        <v>549</v>
       </c>
       <c r="L255" s="50" t="s">
-        <v>548</v>
+        <v>1</v>
       </c>
       <c r="M255" s="50" t="s">
         <v>1</v>
@@ -22516,22 +22691,22 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>84981</v>
+        <v>84971</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E256" s="50">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F256" s="50">
         <v>0</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -22540,13 +22715,13 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>332</v>
+        <v>552</v>
       </c>
       <c r="L256" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M256" s="50" t="s">
-        <v>1</v>
+        <v>553</v>
       </c>
       <c r="N256" s="50">
         <v>8</v>
@@ -22597,34 +22772,37 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>84982</v>
+        <v>84972</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E257" s="50">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
-        <v>60</v>
+        <v>555</v>
+      </c>
+      <c r="H257" s="50" t="s">
+        <v>556</v>
       </c>
       <c r="I257" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J257" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M257" s="50" t="s">
-        <v>553</v>
+        <v>1</v>
       </c>
       <c r="N257" s="50">
         <v>8</v>
@@ -22632,9 +22810,7 @@
       <c r="O257" s="50">
         <v>0</v>
       </c>
-      <c r="P257" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P257" s="50"/>
       <c r="Q257" s="50">
         <v>0</v>
       </c>
@@ -22677,22 +22853,22 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>84983</v>
+        <v>84973</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E258" s="50">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F258" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G258" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -22701,10 +22877,10 @@
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>555</v>
+        <v>193</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>1</v>
+        <v>559</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -22715,9 +22891,7 @@
       <c r="O258" s="50">
         <v>0</v>
       </c>
-      <c r="P258" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P258" s="50"/>
       <c r="Q258" s="50">
         <v>0</v>
       </c>
@@ -22760,13 +22934,13 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>84984</v>
+        <v>84974</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E259" s="50">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F259" s="50">
         <v>0</v>
@@ -22775,7 +22949,7 @@
         <v>60</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -22784,7 +22958,7 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="L259" s="50" t="s">
         <v>1</v>
@@ -22798,9 +22972,7 @@
       <c r="O259" s="50">
         <v>0</v>
       </c>
-      <c r="P259" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P259" s="50"/>
       <c r="Q259" s="50">
         <v>0</v>
       </c>
@@ -22843,80 +23015,47 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>330037</v>
+        <v>84976</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E260" s="50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F260" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G260" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H260" s="50" t="s">
-        <v>560</v>
-      </c>
       <c r="I260" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J260" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K260" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="L260" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M260" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K260" s="50"/>
+      <c r="L260" s="50"/>
+      <c r="M260" s="50"/>
       <c r="N260" s="50">
-        <v>33</v>
-      </c>
-      <c r="O260" s="50">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O260" s="50"/>
       <c r="P260" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q260" s="50">
-        <v>0</v>
-      </c>
-      <c r="R260" s="50">
-        <v>0</v>
-      </c>
-      <c r="S260" s="50">
-        <v>0</v>
-      </c>
-      <c r="T260" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="U260" s="50">
-        <v>0</v>
-      </c>
-      <c r="V260" s="50">
-        <v>0</v>
-      </c>
-      <c r="W260" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X260" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y260" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z260" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA260" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="Q260" s="50"/>
+      <c r="R260" s="50"/>
+      <c r="S260" s="50"/>
+      <c r="T260" s="50"/>
+      <c r="U260" s="50"/>
+      <c r="V260" s="50"/>
+      <c r="W260" s="50"/>
+      <c r="X260" s="50"/>
+      <c r="Y260" s="50"/>
+      <c r="Z260" s="52"/>
+      <c r="AA260" s="50"/>
     </row>
     <row r="261">
       <c r="A261" s="50">
@@ -22926,78 +23065,47 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>330038</v>
+        <v>84977</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E261" s="50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F261" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="H261" s="50" t="s">
-        <v>562</v>
+        <v>60</v>
       </c>
       <c r="I261" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J261" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K261" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="L261" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M261" s="50" t="s">
-        <v>563</v>
-      </c>
+      <c r="K261" s="50"/>
+      <c r="L261" s="50"/>
+      <c r="M261" s="50"/>
       <c r="N261" s="50">
-        <v>33</v>
-      </c>
-      <c r="O261" s="50">
-        <v>0</v>
-      </c>
-      <c r="P261" s="50"/>
-      <c r="Q261" s="50">
-        <v>0</v>
-      </c>
-      <c r="R261" s="50">
-        <v>0</v>
-      </c>
-      <c r="S261" s="50">
-        <v>0</v>
-      </c>
-      <c r="T261" s="50">
-        <v>0</v>
-      </c>
-      <c r="U261" s="50">
-        <v>0</v>
-      </c>
-      <c r="V261" s="50">
-        <v>0</v>
-      </c>
-      <c r="W261" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X261" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y261" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z261" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA261" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O261" s="50"/>
+      <c r="P261" s="50" t="s">
+        <v>565</v>
+      </c>
+      <c r="Q261" s="50"/>
+      <c r="R261" s="50"/>
+      <c r="S261" s="50"/>
+      <c r="T261" s="50"/>
+      <c r="U261" s="50"/>
+      <c r="V261" s="50"/>
+      <c r="W261" s="50"/>
+      <c r="X261" s="50"/>
+      <c r="Y261" s="50"/>
+      <c r="Z261" s="52"/>
+      <c r="AA261" s="50"/>
     </row>
     <row r="262">
       <c r="A262" s="50">
@@ -23007,78 +23115,47 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>330039</v>
+        <v>84978</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E262" s="50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F262" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H262" s="50" t="s">
-        <v>565</v>
+        <v>60</v>
       </c>
       <c r="I262" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J262" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K262" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="L262" s="50" t="s">
-        <v>566</v>
-      </c>
-      <c r="M262" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K262" s="50"/>
+      <c r="L262" s="50"/>
+      <c r="M262" s="50"/>
       <c r="N262" s="50">
-        <v>33</v>
-      </c>
-      <c r="O262" s="50">
-        <v>0</v>
-      </c>
-      <c r="P262" s="50"/>
-      <c r="Q262" s="50">
-        <v>0</v>
-      </c>
-      <c r="R262" s="50">
-        <v>0</v>
-      </c>
-      <c r="S262" s="50">
-        <v>0</v>
-      </c>
-      <c r="T262" s="50">
-        <v>0</v>
-      </c>
-      <c r="U262" s="50">
-        <v>0</v>
-      </c>
-      <c r="V262" s="50">
-        <v>0</v>
-      </c>
-      <c r="W262" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X262" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y262" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z262" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA262" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O262" s="50"/>
+      <c r="P262" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q262" s="50"/>
+      <c r="R262" s="50"/>
+      <c r="S262" s="50"/>
+      <c r="T262" s="50"/>
+      <c r="U262" s="50"/>
+      <c r="V262" s="50"/>
+      <c r="W262" s="50"/>
+      <c r="X262" s="50"/>
+      <c r="Y262" s="50"/>
+      <c r="Z262" s="52"/>
+      <c r="AA262" s="50"/>
     </row>
     <row r="263">
       <c r="A263" s="50">
@@ -23088,22 +23165,22 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>330040</v>
+        <v>84979</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E263" s="50">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="F263" s="50">
         <v>0</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23112,16 +23189,16 @@
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>148</v>
+        <v>328</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>1</v>
+        <v>571</v>
       </c>
       <c r="N263" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O263" s="50">
         <v>0</v>
@@ -23169,22 +23246,22 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>330041</v>
+        <v>84980</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E264" s="50">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="F264" s="50">
         <v>0</v>
       </c>
       <c r="G264" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23193,16 +23270,16 @@
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>148</v>
+        <v>325</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N264" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O264" s="50">
         <v>0</v>
@@ -23250,22 +23327,22 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>330042</v>
+        <v>84981</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E265" s="50">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F265" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23274,16 +23351,16 @@
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>574</v>
+        <v>1</v>
       </c>
       <c r="N265" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O265" s="50">
         <v>0</v>
@@ -23331,45 +23408,44 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>330043</v>
+        <v>84982</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E266" s="50">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F266" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G266" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H266" s="50" t="s">
-        <v>576</v>
-      </c>
       <c r="I266" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J266" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>239</v>
+        <v>578</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M266" s="50" t="s">
-        <v>1</v>
+        <v>579</v>
       </c>
       <c r="N266" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O266" s="50">
         <v>0</v>
       </c>
-      <c r="P266" s="50"/>
+      <c r="P266" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q266" s="50">
         <v>0</v>
       </c>
@@ -23412,22 +23488,22 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>330044</v>
+        <v>84983</v>
       </c>
       <c r="D267" s="50" t="s">
         <v>577</v>
       </c>
       <c r="E267" s="50">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F267" s="50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23436,21 +23512,23 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>193</v>
+        <v>581</v>
       </c>
       <c r="L267" s="50" t="s">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="M267" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N267" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O267" s="50">
         <v>0</v>
       </c>
-      <c r="P267" s="50"/>
+      <c r="P267" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q267" s="50">
         <v>0</v>
       </c>
@@ -23493,22 +23571,22 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>330045</v>
+        <v>84984</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E268" s="50">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F268" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G268" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23517,7 +23595,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>97</v>
+        <v>584</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23526,7 +23604,7 @@
         <v>1</v>
       </c>
       <c r="N268" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O268" s="50">
         <v>0</v>
@@ -23543,8 +23621,8 @@
       <c r="S268" s="50">
         <v>0</v>
       </c>
-      <c r="T268" s="50" t="s">
-        <v>61</v>
+      <c r="T268" s="50">
+        <v>0</v>
       </c>
       <c r="U268" s="50">
         <v>0</v>
@@ -23576,22 +23654,22 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>330046</v>
+        <v>330037</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E269" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F269" s="50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G269" s="50" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -23600,10 +23678,10 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>584</v>
+        <v>97</v>
       </c>
       <c r="L269" s="50" t="s">
-        <v>585</v>
+        <v>1</v>
       </c>
       <c r="M269" s="50" t="s">
         <v>1</v>
@@ -23614,7 +23692,9 @@
       <c r="O269" s="50">
         <v>0</v>
       </c>
-      <c r="P269" s="50"/>
+      <c r="P269" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q269" s="50">
         <v>0</v>
       </c>
@@ -23624,8 +23704,8 @@
       <c r="S269" s="50">
         <v>0</v>
       </c>
-      <c r="T269" s="50">
-        <v>0</v>
+      <c r="T269" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U269" s="50">
         <v>0</v>
@@ -23657,22 +23737,22 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>330047</v>
+        <v>330038</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E270" s="50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F270" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23681,13 +23761,13 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>588</v>
+        <v>143</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M270" s="50" t="s">
-        <v>1</v>
+        <v>589</v>
       </c>
       <c r="N270" s="50">
         <v>33</v>
@@ -23738,22 +23818,22 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>330048</v>
+        <v>330039</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E271" s="50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F271" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G271" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -23762,10 +23842,10 @@
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="M271" s="50" t="s">
         <v>1</v>
@@ -23776,9 +23856,7 @@
       <c r="O271" s="50">
         <v>0</v>
       </c>
-      <c r="P271" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P271" s="50"/>
       <c r="Q271" s="50">
         <v>0</v>
       </c>
@@ -23788,8 +23866,8 @@
       <c r="S271" s="50">
         <v>0</v>
       </c>
-      <c r="T271" s="50" t="s">
-        <v>61</v>
+      <c r="T271" s="50">
+        <v>0</v>
       </c>
       <c r="U271" s="50">
         <v>0</v>
@@ -23821,22 +23899,22 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>330049</v>
+        <v>330040</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E272" s="50">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="F272" s="50">
         <v>0</v>
       </c>
       <c r="G272" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23845,10 +23923,10 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -23902,22 +23980,22 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>330050</v>
+        <v>330041</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E273" s="50">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="F273" s="50">
         <v>0</v>
       </c>
       <c r="G273" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -23926,10 +24004,10 @@
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="M273" s="50" t="s">
         <v>1</v>
@@ -23983,22 +24061,22 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>330051</v>
+        <v>330042</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E274" s="50">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F274" s="50">
         <v>1</v>
       </c>
       <c r="G274" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24007,13 +24085,13 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>1</v>
+        <v>599</v>
       </c>
       <c r="M274" s="50" t="s">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="N274" s="50">
         <v>33</v>
@@ -24021,9 +24099,7 @@
       <c r="O274" s="50">
         <v>0</v>
       </c>
-      <c r="P274" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P274" s="50"/>
       <c r="Q274" s="50">
         <v>0</v>
       </c>
@@ -24066,22 +24142,22 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>330052</v>
+        <v>330043</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E275" s="50">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F275" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G275" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H275" s="50" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="I275" s="50" t="s">
         <v>78</v>
@@ -24090,7 +24166,7 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="L275" s="50" t="s">
         <v>1</v>
@@ -24104,9 +24180,7 @@
       <c r="O275" s="50">
         <v>0</v>
       </c>
-      <c r="P275" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P275" s="50"/>
       <c r="Q275" s="50">
         <v>0</v>
       </c>
@@ -24149,22 +24223,22 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>330053</v>
+        <v>330044</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E276" s="50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F276" s="50">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24173,10 +24247,10 @@
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="L276" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="M276" s="50" t="s">
         <v>1</v>
@@ -24187,9 +24261,7 @@
       <c r="O276" s="50">
         <v>0</v>
       </c>
-      <c r="P276" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P276" s="50"/>
       <c r="Q276" s="50">
         <v>0</v>
       </c>
@@ -24232,10 +24304,10 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>330054</v>
+        <v>330045</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E277" s="50">
         <v>5</v>
@@ -24244,10 +24316,10 @@
         <v>1</v>
       </c>
       <c r="G277" s="50" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H277" s="50" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>78</v>
@@ -24315,22 +24387,22 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>330055</v>
+        <v>330046</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E278" s="50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F278" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G278" s="50" t="s">
         <v>84</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24339,10 +24411,10 @@
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>231</v>
+        <v>461</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>1</v>
+        <v>610</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
@@ -24353,9 +24425,7 @@
       <c r="O278" s="50">
         <v>0</v>
       </c>
-      <c r="P278" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P278" s="50"/>
       <c r="Q278" s="50">
         <v>0</v>
       </c>
@@ -24398,22 +24468,22 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>330056</v>
+        <v>330047</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="E279" s="50">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F279" s="50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G279" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H279" s="50" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>78</v>
@@ -24422,7 +24492,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>86</v>
+        <v>465</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24436,9 +24506,7 @@
       <c r="O279" s="50">
         <v>0</v>
       </c>
-      <c r="P279" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P279" s="50"/>
       <c r="Q279" s="50">
         <v>0</v>
       </c>
@@ -24481,10 +24549,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>330058</v>
+        <v>330048</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E280" s="50">
         <v>5</v>
@@ -24493,10 +24561,10 @@
         <v>1</v>
       </c>
       <c r="G280" s="50" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>78</v>
@@ -24564,13 +24632,13 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>330061</v>
+        <v>330049</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E281" s="50">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F281" s="50">
         <v>0</v>
@@ -24579,7 +24647,7 @@
         <v>60</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>78</v>
@@ -24588,10 +24656,10 @@
         <v>62</v>
       </c>
       <c r="K281" s="50" t="s">
-        <v>612</v>
+        <v>101</v>
       </c>
       <c r="L281" s="50" t="s">
-        <v>1</v>
+        <v>617</v>
       </c>
       <c r="M281" s="50" t="s">
         <v>1</v>
@@ -24602,9 +24670,7 @@
       <c r="O281" s="50">
         <v>0</v>
       </c>
-      <c r="P281" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P281" s="50"/>
       <c r="Q281" s="50">
         <v>0</v>
       </c>
@@ -24647,13 +24713,13 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>330062</v>
+        <v>330050</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E282" s="50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F282" s="50">
         <v>0</v>
@@ -24662,7 +24728,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="50" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="I282" s="50" t="s">
         <v>78</v>
@@ -24671,7 +24737,7 @@
         <v>62</v>
       </c>
       <c r="K282" s="50" t="s">
-        <v>615</v>
+        <v>89</v>
       </c>
       <c r="L282" s="50" t="s">
         <v>1</v>
@@ -24685,9 +24751,7 @@
       <c r="O282" s="50">
         <v>0</v>
       </c>
-      <c r="P282" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P282" s="50"/>
       <c r="Q282" s="50">
         <v>0</v>
       </c>
@@ -24730,22 +24794,22 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>330063</v>
+        <v>330051</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E283" s="50">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F283" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G283" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H283" s="50" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I283" s="50" t="s">
         <v>78</v>
@@ -24754,10 +24818,10 @@
         <v>62</v>
       </c>
       <c r="K283" s="50" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="L283" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M283" s="50" t="s">
         <v>1</v>
@@ -24813,22 +24877,22 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>330064</v>
+        <v>330052</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E284" s="50">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F284" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G284" s="50" t="s">
         <v>139</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I284" s="50" t="s">
         <v>78</v>
@@ -24837,13 +24901,13 @@
         <v>62</v>
       </c>
       <c r="K284" s="50" t="s">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="L284" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M284" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N284" s="50">
         <v>33</v>
@@ -24896,22 +24960,22 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>330065</v>
+        <v>330053</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E285" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F285" s="50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G285" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H285" s="50" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I285" s="50" t="s">
         <v>78</v>
@@ -24920,7 +24984,7 @@
         <v>62</v>
       </c>
       <c r="K285" s="50" t="s">
-        <v>298</v>
+        <v>247</v>
       </c>
       <c r="L285" s="50" t="s">
         <v>1</v>
@@ -24946,8 +25010,8 @@
       <c r="S285" s="50">
         <v>0</v>
       </c>
-      <c r="T285" s="50" t="s">
-        <v>61</v>
+      <c r="T285" s="50">
+        <v>0</v>
       </c>
       <c r="U285" s="50">
         <v>0</v>
@@ -24979,13 +25043,13 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>330067</v>
+        <v>330054</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E286" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F286" s="50">
         <v>1</v>
@@ -24994,7 +25058,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="50" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="I286" s="50" t="s">
         <v>78</v>
@@ -25003,7 +25067,7 @@
         <v>62</v>
       </c>
       <c r="K286" s="50" t="s">
-        <v>231</v>
+        <v>97</v>
       </c>
       <c r="L286" s="50" t="s">
         <v>1</v>
@@ -25029,8 +25093,8 @@
       <c r="S286" s="50">
         <v>0</v>
       </c>
-      <c r="T286" s="50">
-        <v>0</v>
+      <c r="T286" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U286" s="50">
         <v>0</v>
@@ -25062,22 +25126,22 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>330068</v>
+        <v>330055</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E287" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F287" s="50">
         <v>1</v>
       </c>
       <c r="G287" s="50" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="H287" s="50" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I287" s="50" t="s">
         <v>78</v>
@@ -25086,7 +25150,7 @@
         <v>62</v>
       </c>
       <c r="K287" s="50" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="L287" s="50" t="s">
         <v>1</v>
@@ -25112,8 +25176,8 @@
       <c r="S287" s="50">
         <v>0</v>
       </c>
-      <c r="T287" s="50" t="s">
-        <v>61</v>
+      <c r="T287" s="50">
+        <v>0</v>
       </c>
       <c r="U287" s="50">
         <v>0</v>
@@ -25145,22 +25209,22 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>330069</v>
+        <v>330056</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E288" s="50">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F288" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G288" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H288" s="50" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="I288" s="50" t="s">
         <v>78</v>
@@ -25169,10 +25233,10 @@
         <v>62</v>
       </c>
       <c r="K288" s="50" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="L288" s="50" t="s">
-        <v>628</v>
+        <v>1</v>
       </c>
       <c r="M288" s="50" t="s">
         <v>1</v>
@@ -25183,7 +25247,9 @@
       <c r="O288" s="50">
         <v>0</v>
       </c>
-      <c r="P288" s="50"/>
+      <c r="P288" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q288" s="50">
         <v>0</v>
       </c>
@@ -25226,22 +25292,22 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>330070</v>
+        <v>330058</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E289" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F289" s="50">
         <v>1</v>
       </c>
       <c r="G289" s="50" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="H289" s="50" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I289" s="50" t="s">
         <v>78</v>
@@ -25250,7 +25316,7 @@
         <v>62</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -25264,7 +25330,9 @@
       <c r="O289" s="50">
         <v>0</v>
       </c>
-      <c r="P289" s="50"/>
+      <c r="P289" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q289" s="50">
         <v>0</v>
       </c>
@@ -25274,8 +25342,8 @@
       <c r="S289" s="50">
         <v>0</v>
       </c>
-      <c r="T289" s="50">
-        <v>0</v>
+      <c r="T289" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U289" s="50">
         <v>0</v>
@@ -25296,6 +25364,749 @@
         <v>0</v>
       </c>
       <c r="AA289" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="50">
+        <v>285</v>
+      </c>
+      <c r="B290" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C290" s="50">
+        <v>330061</v>
+      </c>
+      <c r="D290" s="50" t="s">
+        <v>634</v>
+      </c>
+      <c r="E290" s="50">
+        <v>39</v>
+      </c>
+      <c r="F290" s="50">
+        <v>0</v>
+      </c>
+      <c r="G290" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H290" s="50" t="s">
+        <v>635</v>
+      </c>
+      <c r="I290" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J290" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K290" s="50" t="s">
+        <v>636</v>
+      </c>
+      <c r="L290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N290" s="50">
+        <v>33</v>
+      </c>
+      <c r="O290" s="50">
+        <v>0</v>
+      </c>
+      <c r="P290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q290" s="50">
+        <v>0</v>
+      </c>
+      <c r="R290" s="50">
+        <v>0</v>
+      </c>
+      <c r="S290" s="50">
+        <v>0</v>
+      </c>
+      <c r="T290" s="50">
+        <v>0</v>
+      </c>
+      <c r="U290" s="50">
+        <v>0</v>
+      </c>
+      <c r="V290" s="50">
+        <v>0</v>
+      </c>
+      <c r="W290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y290" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z290" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA290" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="50">
+        <v>286</v>
+      </c>
+      <c r="B291" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C291" s="50">
+        <v>330062</v>
+      </c>
+      <c r="D291" s="50" t="s">
+        <v>637</v>
+      </c>
+      <c r="E291" s="50">
+        <v>40</v>
+      </c>
+      <c r="F291" s="50">
+        <v>0</v>
+      </c>
+      <c r="G291" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H291" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="I291" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J291" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K291" s="50" t="s">
+        <v>639</v>
+      </c>
+      <c r="L291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N291" s="50">
+        <v>33</v>
+      </c>
+      <c r="O291" s="50">
+        <v>0</v>
+      </c>
+      <c r="P291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q291" s="50">
+        <v>0</v>
+      </c>
+      <c r="R291" s="50">
+        <v>0</v>
+      </c>
+      <c r="S291" s="50">
+        <v>0</v>
+      </c>
+      <c r="T291" s="50">
+        <v>0</v>
+      </c>
+      <c r="U291" s="50">
+        <v>0</v>
+      </c>
+      <c r="V291" s="50">
+        <v>0</v>
+      </c>
+      <c r="W291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y291" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z291" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA291" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="50">
+        <v>287</v>
+      </c>
+      <c r="B292" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C292" s="50">
+        <v>330063</v>
+      </c>
+      <c r="D292" s="50" t="s">
+        <v>640</v>
+      </c>
+      <c r="E292" s="50">
+        <v>28</v>
+      </c>
+      <c r="F292" s="50">
+        <v>0</v>
+      </c>
+      <c r="G292" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H292" s="50" t="s">
+        <v>641</v>
+      </c>
+      <c r="I292" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J292" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K292" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L292" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M292" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N292" s="50">
+        <v>33</v>
+      </c>
+      <c r="O292" s="50">
+        <v>0</v>
+      </c>
+      <c r="P292" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q292" s="50">
+        <v>0</v>
+      </c>
+      <c r="R292" s="50">
+        <v>0</v>
+      </c>
+      <c r="S292" s="50">
+        <v>0</v>
+      </c>
+      <c r="T292" s="50">
+        <v>0</v>
+      </c>
+      <c r="U292" s="50">
+        <v>0</v>
+      </c>
+      <c r="V292" s="50">
+        <v>0</v>
+      </c>
+      <c r="W292" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X292" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y292" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z292" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA292" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="50">
+        <v>288</v>
+      </c>
+      <c r="B293" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C293" s="50">
+        <v>330064</v>
+      </c>
+      <c r="D293" s="50" t="s">
+        <v>642</v>
+      </c>
+      <c r="E293" s="50">
+        <v>29</v>
+      </c>
+      <c r="F293" s="50">
+        <v>0</v>
+      </c>
+      <c r="G293" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H293" s="50" t="s">
+        <v>643</v>
+      </c>
+      <c r="I293" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J293" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K293" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="L293" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M293" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N293" s="50">
+        <v>33</v>
+      </c>
+      <c r="O293" s="50">
+        <v>0</v>
+      </c>
+      <c r="P293" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q293" s="50">
+        <v>0</v>
+      </c>
+      <c r="R293" s="50">
+        <v>0</v>
+      </c>
+      <c r="S293" s="50">
+        <v>0</v>
+      </c>
+      <c r="T293" s="50">
+        <v>0</v>
+      </c>
+      <c r="U293" s="50">
+        <v>0</v>
+      </c>
+      <c r="V293" s="50">
+        <v>0</v>
+      </c>
+      <c r="W293" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X293" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y293" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z293" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA293" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="50">
+        <v>289</v>
+      </c>
+      <c r="B294" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C294" s="50">
+        <v>330065</v>
+      </c>
+      <c r="D294" s="50" t="s">
+        <v>644</v>
+      </c>
+      <c r="E294" s="50">
+        <v>5</v>
+      </c>
+      <c r="F294" s="50">
+        <v>2</v>
+      </c>
+      <c r="G294" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H294" s="50" t="s">
+        <v>645</v>
+      </c>
+      <c r="I294" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J294" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K294" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="L294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N294" s="50">
+        <v>33</v>
+      </c>
+      <c r="O294" s="50">
+        <v>0</v>
+      </c>
+      <c r="P294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q294" s="50">
+        <v>0</v>
+      </c>
+      <c r="R294" s="50">
+        <v>0</v>
+      </c>
+      <c r="S294" s="50">
+        <v>0</v>
+      </c>
+      <c r="T294" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U294" s="50">
+        <v>0</v>
+      </c>
+      <c r="V294" s="50">
+        <v>0</v>
+      </c>
+      <c r="W294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y294" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z294" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA294" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="50">
+        <v>290</v>
+      </c>
+      <c r="B295" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C295" s="50">
+        <v>330067</v>
+      </c>
+      <c r="D295" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="E295" s="50">
+        <v>4</v>
+      </c>
+      <c r="F295" s="50">
+        <v>1</v>
+      </c>
+      <c r="G295" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H295" s="50" t="s">
+        <v>647</v>
+      </c>
+      <c r="I295" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J295" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K295" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="L295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N295" s="50">
+        <v>33</v>
+      </c>
+      <c r="O295" s="50">
+        <v>0</v>
+      </c>
+      <c r="P295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q295" s="50">
+        <v>0</v>
+      </c>
+      <c r="R295" s="50">
+        <v>0</v>
+      </c>
+      <c r="S295" s="50">
+        <v>0</v>
+      </c>
+      <c r="T295" s="50">
+        <v>0</v>
+      </c>
+      <c r="U295" s="50">
+        <v>0</v>
+      </c>
+      <c r="V295" s="50">
+        <v>0</v>
+      </c>
+      <c r="W295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y295" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z295" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA295" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="50">
+        <v>291</v>
+      </c>
+      <c r="B296" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C296" s="50">
+        <v>330068</v>
+      </c>
+      <c r="D296" s="50" t="s">
+        <v>648</v>
+      </c>
+      <c r="E296" s="50">
+        <v>5</v>
+      </c>
+      <c r="F296" s="50">
+        <v>1</v>
+      </c>
+      <c r="G296" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H296" s="50" t="s">
+        <v>649</v>
+      </c>
+      <c r="I296" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J296" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K296" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="L296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N296" s="50">
+        <v>33</v>
+      </c>
+      <c r="O296" s="50">
+        <v>0</v>
+      </c>
+      <c r="P296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q296" s="50">
+        <v>0</v>
+      </c>
+      <c r="R296" s="50">
+        <v>0</v>
+      </c>
+      <c r="S296" s="50">
+        <v>0</v>
+      </c>
+      <c r="T296" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U296" s="50">
+        <v>0</v>
+      </c>
+      <c r="V296" s="50">
+        <v>0</v>
+      </c>
+      <c r="W296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y296" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z296" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA296" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="50">
+        <v>292</v>
+      </c>
+      <c r="B297" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C297" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D297" s="50" t="s">
+        <v>650</v>
+      </c>
+      <c r="E297" s="50">
+        <v>16</v>
+      </c>
+      <c r="F297" s="50">
+        <v>1</v>
+      </c>
+      <c r="G297" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H297" s="50" t="s">
+        <v>651</v>
+      </c>
+      <c r="I297" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J297" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K297" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="L297" s="50" t="s">
+        <v>652</v>
+      </c>
+      <c r="M297" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N297" s="50">
+        <v>33</v>
+      </c>
+      <c r="O297" s="50">
+        <v>0</v>
+      </c>
+      <c r="P297" s="50"/>
+      <c r="Q297" s="50">
+        <v>0</v>
+      </c>
+      <c r="R297" s="50">
+        <v>0</v>
+      </c>
+      <c r="S297" s="50">
+        <v>0</v>
+      </c>
+      <c r="T297" s="50">
+        <v>0</v>
+      </c>
+      <c r="U297" s="50">
+        <v>0</v>
+      </c>
+      <c r="V297" s="50">
+        <v>0</v>
+      </c>
+      <c r="W297" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X297" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y297" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z297" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA297" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="50">
+        <v>293</v>
+      </c>
+      <c r="B298" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C298" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D298" s="50" t="s">
+        <v>653</v>
+      </c>
+      <c r="E298" s="50">
+        <v>3</v>
+      </c>
+      <c r="F298" s="50">
+        <v>1</v>
+      </c>
+      <c r="G298" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H298" s="50" t="s">
+        <v>654</v>
+      </c>
+      <c r="I298" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J298" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K298" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="L298" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M298" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N298" s="50">
+        <v>33</v>
+      </c>
+      <c r="O298" s="50">
+        <v>0</v>
+      </c>
+      <c r="P298" s="50"/>
+      <c r="Q298" s="50">
+        <v>0</v>
+      </c>
+      <c r="R298" s="50">
+        <v>0</v>
+      </c>
+      <c r="S298" s="50">
+        <v>0</v>
+      </c>
+      <c r="T298" s="50">
+        <v>0</v>
+      </c>
+      <c r="U298" s="50">
+        <v>0</v>
+      </c>
+      <c r="V298" s="50">
+        <v>0</v>
+      </c>
+      <c r="W298" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X298" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y298" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z298" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA298" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -226,6 +226,9 @@
     <t>9.00,0.00,25.00,19.00,0.00,25.00,19.00,0.00,12.00,9.00,0.00,12.00</t>
   </si>
   <si>
+    <t>10001_1</t>
+  </si>
+  <si>
     <t>8.27194023132324,4.999971,25.0142784118652</t>
   </si>
   <si>
@@ -235,9 +238,6 @@
     <t>8.27,0.00,26.00,20.00,0.00,26.00,20.00,0.00,10.91,8.27,0.00,10.91</t>
   </si>
   <si>
-    <t>10001_1</t>
-  </si>
-  <si>
     <t>0,15066</t>
   </si>
   <si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_yellow.prefab</t>
-  </si>
-  <si>
-    <t>15034</t>
   </si>
   <si>
     <t>18,4.999971,36</t>
@@ -3586,7 +3583,9 @@
       <c r="T7" s="50"/>
       <c r="U7" s="50"/>
       <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
+      <c r="W7" s="50" t="s">
+        <v>69</v>
+      </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="50"/>
       <c r="Z7" s="52"/>
@@ -3603,7 +3602,7 @@
         <v>15025</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" s="50">
         <v>2</v>
@@ -3622,7 +3621,7 @@
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M8" s="50"/>
       <c r="N8" s="50">
@@ -3630,7 +3629,7 @@
       </c>
       <c r="O8" s="50"/>
       <c r="P8" s="50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="50"/>
       <c r="R8" s="50"/>
@@ -3639,7 +3638,7 @@
       <c r="U8" s="50"/>
       <c r="V8" s="50"/>
       <c r="W8" s="50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="50"/>
@@ -3763,7 +3762,7 @@
         <v>79</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="M10" s="50" t="s">
         <v>1</v>
@@ -3822,7 +3821,7 @@
         <v>15053</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" s="50">
         <v>14</v>
@@ -3840,7 +3839,7 @@
         <v>62</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L11" s="50" t="s">
         <v>1</v>
@@ -3902,7 +3901,7 @@
         <v>15054</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" s="50">
         <v>54</v>
@@ -3911,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="50" t="s">
         <v>84</v>
-      </c>
-      <c r="H12" s="50" t="s">
-        <v>85</v>
       </c>
       <c r="I12" s="50" t="s">
         <v>78</v>
@@ -3923,7 +3922,7 @@
         <v>62</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L12" s="50" t="s">
         <v>1</v>
@@ -3985,7 +3984,7 @@
         <v>15055</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13" s="50">
         <v>44</v>
@@ -3997,7 +3996,7 @@
         <v>60</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I13" s="50" t="s">
         <v>78</v>
@@ -4006,7 +4005,7 @@
         <v>62</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L13" s="50" t="s">
         <v>1</v>
@@ -4068,7 +4067,7 @@
         <v>15057</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="50">
         <v>3</v>
@@ -4080,7 +4079,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="50" t="s">
         <v>78</v>
@@ -4089,55 +4088,55 @@
         <v>62</v>
       </c>
       <c r="K14" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="50">
+        <v>1</v>
+      </c>
+      <c r="O14" s="50">
+        <v>0</v>
+      </c>
+      <c r="P14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="50">
+        <v>0</v>
+      </c>
+      <c r="R14" s="50">
+        <v>0</v>
+      </c>
+      <c r="S14" s="50">
+        <v>0</v>
+      </c>
+      <c r="T14" s="50">
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <v>0</v>
+      </c>
+      <c r="W14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="50" t="s">
         <v>92</v>
-      </c>
-      <c r="L14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="N14" s="50">
-        <v>1</v>
-      </c>
-      <c r="O14" s="50">
-        <v>0</v>
-      </c>
-      <c r="P14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="50">
-        <v>0</v>
-      </c>
-      <c r="R14" s="50">
-        <v>0</v>
-      </c>
-      <c r="S14" s="50">
-        <v>0</v>
-      </c>
-      <c r="T14" s="50">
-        <v>0</v>
-      </c>
-      <c r="U14" s="50">
-        <v>0</v>
-      </c>
-      <c r="V14" s="50">
-        <v>0</v>
-      </c>
-      <c r="W14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -4151,7 +4150,7 @@
         <v>15035</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="50">
         <v>5</v>
@@ -4160,10 +4159,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="50" t="s">
         <v>95</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>96</v>
       </c>
       <c r="I15" s="50" t="s">
         <v>78</v>
@@ -4172,7 +4171,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L15" s="50" t="s">
         <v>1</v>
@@ -4220,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -4234,7 +4233,7 @@
         <v>15056</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="50">
         <v>43</v>
@@ -4246,7 +4245,7 @@
         <v>60</v>
       </c>
       <c r="H16" s="50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I16" s="50" t="s">
         <v>78</v>
@@ -4255,55 +4254,55 @@
         <v>62</v>
       </c>
       <c r="K16" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="L16" s="50" t="s">
+      <c r="M16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="50">
+        <v>1</v>
+      </c>
+      <c r="O16" s="50">
+        <v>0</v>
+      </c>
+      <c r="P16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="50">
+        <v>0</v>
+      </c>
+      <c r="R16" s="50">
+        <v>0</v>
+      </c>
+      <c r="S16" s="50">
+        <v>0</v>
+      </c>
+      <c r="T16" s="50">
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <v>0</v>
+      </c>
+      <c r="W16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="50" t="s">
         <v>102</v>
-      </c>
-      <c r="M16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="50">
-        <v>1</v>
-      </c>
-      <c r="O16" s="50">
-        <v>0</v>
-      </c>
-      <c r="P16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="50">
-        <v>0</v>
-      </c>
-      <c r="R16" s="50">
-        <v>0</v>
-      </c>
-      <c r="S16" s="50">
-        <v>0</v>
-      </c>
-      <c r="T16" s="50">
-        <v>0</v>
-      </c>
-      <c r="U16" s="50">
-        <v>0</v>
-      </c>
-      <c r="V16" s="50">
-        <v>0</v>
-      </c>
-      <c r="W16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="50" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17">
@@ -4317,7 +4316,7 @@
         <v>15065</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="50">
         <v>62</v>
@@ -4377,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="Y17" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z17" s="52">
         <v>0</v>
@@ -4397,7 +4396,7 @@
         <v>15059</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" s="50">
         <v>62</v>
@@ -4457,13 +4456,13 @@
         <v>1</v>
       </c>
       <c r="Y18" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z18" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="50" t="s">
         <v>106</v>
-      </c>
-      <c r="Z18" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="50" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19">
@@ -4477,7 +4476,7 @@
         <v>15060</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19" s="50">
         <v>62</v>
@@ -4543,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20">
@@ -4557,7 +4556,7 @@
         <v>15061</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E20" s="50">
         <v>62</v>
@@ -4617,7 +4616,7 @@
         <v>64</v>
       </c>
       <c r="Y20" s="50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Z20" s="52">
         <v>0</v>
@@ -4637,7 +4636,7 @@
         <v>15044</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E21" s="50">
         <v>62</v>
@@ -4717,7 +4716,7 @@
         <v>15062</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="50">
         <v>62</v>
@@ -4777,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="Y22" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z22" s="52">
         <v>0</v>
@@ -4797,7 +4796,7 @@
         <v>15063</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E23" s="50">
         <v>62</v>
@@ -4857,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="Y23" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z23" s="52">
         <v>0</v>
@@ -4877,7 +4876,7 @@
         <v>15064</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E24" s="50">
         <v>62</v>
@@ -4937,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="Y24" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z24" s="52">
         <v>0</v>
@@ -4957,7 +4956,7 @@
         <v>15068</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="50">
         <v>62</v>
@@ -5017,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="Y25" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z25" s="52">
         <v>0</v>
@@ -5037,7 +5036,7 @@
         <v>15069</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" s="50">
         <v>62</v>
@@ -5097,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="Y26" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z26" s="52">
         <v>0</v>
@@ -5117,7 +5116,7 @@
         <v>15066</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E27" s="50">
         <v>62</v>
@@ -5183,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
@@ -5197,7 +5196,7 @@
         <v>15067</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" s="50">
         <v>62</v>
@@ -5254,10 +5253,10 @@
         <v>1</v>
       </c>
       <c r="X28" s="50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Y28" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z28" s="52">
         <v>0</v>
@@ -5277,7 +5276,7 @@
         <v>15045</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" s="50">
         <v>62</v>
@@ -5357,7 +5356,7 @@
         <v>30813</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="50">
         <v>12</v>
@@ -5435,7 +5434,7 @@
         <v>30819</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" s="50">
         <v>17</v>
@@ -5447,7 +5446,7 @@
         <v>60</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I31" s="50" t="s">
         <v>78</v>
@@ -5456,10 +5455,10 @@
         <v>62</v>
       </c>
       <c r="K31" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="L31" s="50" t="s">
         <v>125</v>
-      </c>
-      <c r="L31" s="50" t="s">
-        <v>126</v>
       </c>
       <c r="M31" s="50" t="s">
         <v>1</v>
@@ -5516,7 +5515,7 @@
         <v>30822</v>
       </c>
       <c r="D32" s="50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="50">
         <v>14</v>
@@ -5534,7 +5533,7 @@
         <v>62</v>
       </c>
       <c r="K32" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L32" s="50" t="s">
         <v>1</v>
@@ -5594,7 +5593,7 @@
         <v>30837</v>
       </c>
       <c r="D33" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" s="50">
         <v>55</v>
@@ -5603,10 +5602,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>78</v>
@@ -5615,10 +5614,10 @@
         <v>62</v>
       </c>
       <c r="K33" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="L33" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="L33" s="50" t="s">
-        <v>131</v>
       </c>
       <c r="M33" s="50" t="s">
         <v>1</v>
@@ -5675,7 +5674,7 @@
         <v>30840</v>
       </c>
       <c r="D34" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E34" s="50">
         <v>54</v>
@@ -5684,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H34" s="50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I34" s="50" t="s">
         <v>78</v>
@@ -5696,7 +5695,7 @@
         <v>62</v>
       </c>
       <c r="K34" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L34" s="50" t="s">
         <v>1</v>
@@ -5756,7 +5755,7 @@
         <v>30862</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E35" s="50">
         <v>53</v>
@@ -5768,7 +5767,7 @@
         <v>60</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>78</v>
@@ -5777,7 +5776,7 @@
         <v>62</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L35" s="50" t="s">
         <v>1</v>
@@ -5814,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="X35" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y35" s="50" t="s">
         <v>1</v>
@@ -5837,7 +5836,7 @@
         <v>30927</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E36" s="50">
         <v>5</v>
@@ -5846,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H36" s="50" t="s">
         <v>139</v>
-      </c>
-      <c r="H36" s="50" t="s">
-        <v>140</v>
       </c>
       <c r="I36" s="50" t="s">
         <v>78</v>
@@ -5858,7 +5857,7 @@
         <v>62</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L36" s="50" t="s">
         <v>1</v>
@@ -5918,7 +5917,7 @@
         <v>30930</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E37" s="50">
         <v>6</v>
@@ -5927,10 +5926,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I37" s="50" t="s">
         <v>78</v>
@@ -5939,13 +5938,13 @@
         <v>62</v>
       </c>
       <c r="K37" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L37" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" s="50" t="s">
         <v>143</v>
-      </c>
-      <c r="L37" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M37" s="50" t="s">
-        <v>144</v>
       </c>
       <c r="N37" s="50">
         <v>2</v>
@@ -5976,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="X37" s="50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y37" s="50" t="s">
         <v>1</v>
@@ -5999,7 +5998,7 @@
         <v>30947</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" s="50">
         <v>7</v>
@@ -6008,10 +6007,10 @@
         <v>0</v>
       </c>
       <c r="G38" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H38" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I38" s="50" t="s">
         <v>78</v>
@@ -6020,10 +6019,10 @@
         <v>62</v>
       </c>
       <c r="K38" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L38" s="50" t="s">
         <v>148</v>
-      </c>
-      <c r="L38" s="50" t="s">
-        <v>149</v>
       </c>
       <c r="M38" s="50" t="s">
         <v>1</v>
@@ -6080,7 +6079,7 @@
         <v>34800</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E39" s="50">
         <v>7</v>
@@ -6089,10 +6088,10 @@
         <v>0</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I39" s="50" t="s">
         <v>78</v>
@@ -6101,10 +6100,10 @@
         <v>62</v>
       </c>
       <c r="K39" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L39" s="50" t="s">
         <v>148</v>
-      </c>
-      <c r="L39" s="50" t="s">
-        <v>149</v>
       </c>
       <c r="M39" s="50" t="s">
         <v>1</v>
@@ -6161,7 +6160,7 @@
         <v>30969</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E40" s="50">
         <v>18</v>
@@ -6173,7 +6172,7 @@
         <v>60</v>
       </c>
       <c r="H40" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I40" s="50" t="s">
         <v>78</v>
@@ -6182,7 +6181,7 @@
         <v>62</v>
       </c>
       <c r="K40" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L40" s="50" t="s">
         <v>1</v>
@@ -6242,7 +6241,7 @@
         <v>34815</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E41" s="50">
         <v>59</v>
@@ -6322,7 +6321,7 @@
         <v>24849</v>
       </c>
       <c r="D42" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E42" s="50">
         <v>2</v>
@@ -6347,7 +6346,7 @@
       </c>
       <c r="O42" s="50"/>
       <c r="P42" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="50"/>
       <c r="R42" s="50"/>
@@ -6372,7 +6371,7 @@
         <v>24850</v>
       </c>
       <c r="D43" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E43" s="50">
         <v>2</v>
@@ -6397,7 +6396,7 @@
       </c>
       <c r="O43" s="50"/>
       <c r="P43" s="50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="50"/>
       <c r="R43" s="50"/>
@@ -6422,7 +6421,7 @@
         <v>24851</v>
       </c>
       <c r="D44" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="50">
         <v>2</v>
@@ -6447,7 +6446,7 @@
       </c>
       <c r="O44" s="50"/>
       <c r="P44" s="50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="50"/>
       <c r="R44" s="50"/>
@@ -6472,7 +6471,7 @@
         <v>24852</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E45" s="50">
         <v>2</v>
@@ -6497,7 +6496,7 @@
       </c>
       <c r="O45" s="50"/>
       <c r="P45" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="50"/>
       <c r="R45" s="50"/>
@@ -6507,7 +6506,7 @@
       <c r="V45" s="50"/>
       <c r="W45" s="50"/>
       <c r="X45" s="50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y45" s="50"/>
       <c r="Z45" s="52"/>
@@ -6524,7 +6523,7 @@
         <v>24865</v>
       </c>
       <c r="D46" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E46" s="50">
         <v>2</v>
@@ -6549,7 +6548,7 @@
       </c>
       <c r="O46" s="50"/>
       <c r="P46" s="50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="50"/>
       <c r="R46" s="50"/>
@@ -6574,7 +6573,7 @@
         <v>24866</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E47" s="50">
         <v>2</v>
@@ -6599,7 +6598,7 @@
       </c>
       <c r="O47" s="50"/>
       <c r="P47" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="50"/>
       <c r="R47" s="50"/>
@@ -6624,7 +6623,7 @@
         <v>24867</v>
       </c>
       <c r="D48" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48" s="50">
         <v>2</v>
@@ -6649,7 +6648,7 @@
       </c>
       <c r="O48" s="50"/>
       <c r="P48" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q48" s="50"/>
       <c r="R48" s="50"/>
@@ -6674,7 +6673,7 @@
         <v>24868</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E49" s="50">
         <v>2</v>
@@ -6699,7 +6698,7 @@
       </c>
       <c r="O49" s="50"/>
       <c r="P49" s="50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q49" s="50"/>
       <c r="R49" s="50"/>
@@ -6709,7 +6708,7 @@
       <c r="V49" s="50"/>
       <c r="W49" s="50"/>
       <c r="X49" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y49" s="50"/>
       <c r="Z49" s="52"/>
@@ -6726,7 +6725,7 @@
         <v>33236</v>
       </c>
       <c r="D50" s="50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E50" s="50">
         <v>12</v>
@@ -6804,7 +6803,7 @@
         <v>33240</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E51" s="50">
         <v>5</v>
@@ -6813,10 +6812,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>78</v>
@@ -6825,7 +6824,7 @@
         <v>62</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L51" s="50" t="s">
         <v>1</v>
@@ -6885,7 +6884,7 @@
         <v>33249</v>
       </c>
       <c r="D52" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E52" s="50">
         <v>28</v>
@@ -6897,7 +6896,7 @@
         <v>60</v>
       </c>
       <c r="H52" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I52" s="50" t="s">
         <v>78</v>
@@ -6909,7 +6908,7 @@
         <v>75</v>
       </c>
       <c r="L52" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M52" s="50" t="s">
         <v>1</v>
@@ -6966,7 +6965,7 @@
         <v>33339</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E53" s="50">
         <v>29</v>
@@ -6978,7 +6977,7 @@
         <v>60</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I53" s="50" t="s">
         <v>78</v>
@@ -6987,13 +6986,13 @@
         <v>62</v>
       </c>
       <c r="K53" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="L53" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M53" s="50" t="s">
         <v>181</v>
-      </c>
-      <c r="L53" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M53" s="50" t="s">
-        <v>182</v>
       </c>
       <c r="N53" s="50">
         <v>3</v>
@@ -7047,7 +7046,7 @@
         <v>33390</v>
       </c>
       <c r="D54" s="50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54" s="50">
         <v>14</v>
@@ -7065,7 +7064,7 @@
         <v>62</v>
       </c>
       <c r="K54" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L54" s="50" t="s">
         <v>1</v>
@@ -7125,7 +7124,7 @@
         <v>34816</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E55" s="50">
         <v>3</v>
@@ -7137,7 +7136,7 @@
         <v>60</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I55" s="50" t="s">
         <v>78</v>
@@ -7146,7 +7145,7 @@
         <v>62</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L55" s="50" t="s">
         <v>1</v>
@@ -7185,7 +7184,7 @@
         <v>1</v>
       </c>
       <c r="X55" s="50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y55" s="50" t="s">
         <v>1</v>
@@ -7208,7 +7207,7 @@
         <v>34817</v>
       </c>
       <c r="D56" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E56" s="50">
         <v>16</v>
@@ -7217,10 +7216,10 @@
         <v>5</v>
       </c>
       <c r="G56" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H56" s="50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I56" s="50" t="s">
         <v>78</v>
@@ -7229,7 +7228,7 @@
         <v>62</v>
       </c>
       <c r="K56" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L56" s="50">
         <v>34816</v>
@@ -7291,7 +7290,7 @@
         <v>34821</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E57" s="50">
         <v>16</v>
@@ -7300,10 +7299,10 @@
         <v>9</v>
       </c>
       <c r="G57" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I57" s="50" t="s">
         <v>78</v>
@@ -7312,13 +7311,13 @@
         <v>62</v>
       </c>
       <c r="K57" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L57" s="50">
+        <v>0</v>
+      </c>
+      <c r="M57" s="50" t="s">
         <v>193</v>
-      </c>
-      <c r="L57" s="50">
-        <v>0</v>
-      </c>
-      <c r="M57" s="50" t="s">
-        <v>194</v>
       </c>
       <c r="N57" s="50">
         <v>3</v>
@@ -7374,7 +7373,7 @@
         <v>34850</v>
       </c>
       <c r="D58" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E58" s="50">
         <v>2</v>
@@ -7399,7 +7398,7 @@
       </c>
       <c r="O58" s="50"/>
       <c r="P58" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="50"/>
       <c r="R58" s="50"/>
@@ -7424,7 +7423,7 @@
         <v>34882</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E59" s="50">
         <v>2</v>
@@ -7443,7 +7442,7 @@
       </c>
       <c r="K59" s="50"/>
       <c r="L59" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M59" s="50"/>
       <c r="N59" s="50">
@@ -7451,7 +7450,7 @@
       </c>
       <c r="O59" s="50"/>
       <c r="P59" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q59" s="50"/>
       <c r="R59" s="50"/>
@@ -7461,7 +7460,7 @@
       <c r="V59" s="50"/>
       <c r="W59" s="50"/>
       <c r="X59" s="50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y59" s="50"/>
       <c r="Z59" s="52"/>
@@ -7478,7 +7477,7 @@
         <v>34852</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E60" s="50">
         <v>2</v>
@@ -7503,7 +7502,7 @@
       </c>
       <c r="O60" s="50"/>
       <c r="P60" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q60" s="50"/>
       <c r="R60" s="50"/>
@@ -7528,7 +7527,7 @@
         <v>34853</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E61" s="50">
         <v>2</v>
@@ -7547,7 +7546,7 @@
       </c>
       <c r="K61" s="50"/>
       <c r="L61" s="50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M61" s="50"/>
       <c r="N61" s="50">
@@ -7555,7 +7554,7 @@
       </c>
       <c r="O61" s="50"/>
       <c r="P61" s="50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q61" s="50"/>
       <c r="R61" s="50"/>
@@ -7565,7 +7564,7 @@
       <c r="V61" s="50"/>
       <c r="W61" s="50"/>
       <c r="X61" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y61" s="50"/>
       <c r="Z61" s="52"/>
@@ -7582,7 +7581,7 @@
         <v>34868</v>
       </c>
       <c r="D62" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E62" s="50">
         <v>2</v>
@@ -7607,7 +7606,7 @@
       </c>
       <c r="O62" s="50"/>
       <c r="P62" s="50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q62" s="50"/>
       <c r="R62" s="50"/>
@@ -7632,7 +7631,7 @@
         <v>34869</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="50">
         <v>2</v>
@@ -7657,7 +7656,7 @@
       </c>
       <c r="O63" s="50"/>
       <c r="P63" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q63" s="50"/>
       <c r="R63" s="50"/>
@@ -7682,7 +7681,7 @@
         <v>44810</v>
       </c>
       <c r="D64" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E64" s="50">
         <v>12</v>
@@ -7762,7 +7761,7 @@
         <v>44815</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E65" s="50">
         <v>6</v>
@@ -7774,7 +7773,7 @@
         <v>60</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I65" s="50" t="s">
         <v>78</v>
@@ -7783,13 +7782,13 @@
         <v>62</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L65" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M65" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N65" s="50">
         <v>4</v>
@@ -7843,7 +7842,7 @@
         <v>44816</v>
       </c>
       <c r="D66" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E66" s="50">
         <v>7</v>
@@ -7852,10 +7851,10 @@
         <v>0</v>
       </c>
       <c r="G66" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H66" s="50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I66" s="50" t="s">
         <v>78</v>
@@ -7864,10 +7863,10 @@
         <v>62</v>
       </c>
       <c r="K66" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L66" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M66" s="50" t="s">
         <v>1</v>
@@ -7924,7 +7923,7 @@
         <v>44817</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E67" s="50">
         <v>7</v>
@@ -7933,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I67" s="50" t="s">
         <v>78</v>
@@ -7945,10 +7944,10 @@
         <v>62</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L67" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M67" s="50" t="s">
         <v>1</v>
@@ -8005,7 +8004,7 @@
         <v>44818</v>
       </c>
       <c r="D68" s="50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E68" s="50">
         <v>7</v>
@@ -8014,10 +8013,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H68" s="50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I68" s="50" t="s">
         <v>78</v>
@@ -8026,10 +8025,10 @@
         <v>62</v>
       </c>
       <c r="K68" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L68" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M68" s="50" t="s">
         <v>1</v>
@@ -8086,7 +8085,7 @@
         <v>44819</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E69" s="50">
         <v>5</v>
@@ -8095,10 +8094,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I69" s="50" t="s">
         <v>78</v>
@@ -8107,7 +8106,7 @@
         <v>62</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L69" s="50" t="s">
         <v>1</v>
@@ -8169,7 +8168,7 @@
         <v>44820</v>
       </c>
       <c r="D70" s="50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E70" s="50">
         <v>5</v>
@@ -8178,10 +8177,10 @@
         <v>3</v>
       </c>
       <c r="G70" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H70" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I70" s="50" t="s">
         <v>78</v>
@@ -8190,7 +8189,7 @@
         <v>62</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L70" s="50" t="s">
         <v>1</v>
@@ -8252,7 +8251,7 @@
         <v>44823</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E71" s="50">
         <v>16</v>
@@ -8264,7 +8263,7 @@
         <v>60</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I71" s="50" t="s">
         <v>78</v>
@@ -8276,7 +8275,7 @@
         <v>79</v>
       </c>
       <c r="L71" s="50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M71" s="50" t="s">
         <v>1</v>
@@ -8333,7 +8332,7 @@
         <v>44824</v>
       </c>
       <c r="D72" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E72" s="50">
         <v>3</v>
@@ -8345,7 +8344,7 @@
         <v>60</v>
       </c>
       <c r="H72" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I72" s="50" t="s">
         <v>78</v>
@@ -8354,7 +8353,7 @@
         <v>62</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L72" s="50" t="s">
         <v>1</v>
@@ -8414,7 +8413,7 @@
         <v>44825</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E73" s="50">
         <v>4</v>
@@ -8423,10 +8422,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I73" s="50" t="s">
         <v>78</v>
@@ -8435,7 +8434,7 @@
         <v>62</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L73" s="50" t="s">
         <v>1</v>
@@ -8497,7 +8496,7 @@
         <v>44827</v>
       </c>
       <c r="D74" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E74" s="50">
         <v>20</v>
@@ -8509,7 +8508,7 @@
         <v>60</v>
       </c>
       <c r="H74" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I74" s="50" t="s">
         <v>78</v>
@@ -8518,13 +8517,13 @@
         <v>62</v>
       </c>
       <c r="K74" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="L74" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="L74" s="50" t="s">
+      <c r="M74" s="50" t="s">
         <v>235</v>
-      </c>
-      <c r="M74" s="50" t="s">
-        <v>236</v>
       </c>
       <c r="N74" s="50">
         <v>4</v>
@@ -8578,7 +8577,7 @@
         <v>44828</v>
       </c>
       <c r="D75" s="50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E75" s="50">
         <v>19</v>
@@ -8590,7 +8589,7 @@
         <v>60</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I75" s="50" t="s">
         <v>78</v>
@@ -8599,7 +8598,7 @@
         <v>62</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L75" s="50" t="s">
         <v>1</v>
@@ -8659,7 +8658,7 @@
         <v>44829</v>
       </c>
       <c r="D76" s="50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E76" s="50">
         <v>16</v>
@@ -8671,7 +8670,7 @@
         <v>60</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I76" s="50" t="s">
         <v>78</v>
@@ -8680,10 +8679,10 @@
         <v>62</v>
       </c>
       <c r="K76" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L76" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M76" s="50" t="s">
         <v>1</v>
@@ -8740,7 +8739,7 @@
         <v>44831</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E77" s="50">
         <v>14</v>
@@ -8758,10 +8757,10 @@
         <v>62</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L77" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M77" s="50" t="s">
         <v>1</v>
@@ -8818,7 +8817,7 @@
         <v>44832</v>
       </c>
       <c r="D78" s="50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E78" s="50">
         <v>4</v>
@@ -8827,10 +8826,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H78" s="50" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I78" s="50" t="s">
         <v>78</v>
@@ -8839,7 +8838,7 @@
         <v>62</v>
       </c>
       <c r="K78" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L78" s="50" t="s">
         <v>1</v>
@@ -8899,7 +8898,7 @@
         <v>44834</v>
       </c>
       <c r="D79" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E79" s="50">
         <v>2</v>
@@ -8924,7 +8923,7 @@
       </c>
       <c r="O79" s="50"/>
       <c r="P79" s="50" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="50"/>
       <c r="R79" s="50"/>
@@ -8949,7 +8948,7 @@
         <v>44836</v>
       </c>
       <c r="D80" s="50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E80" s="50">
         <v>2</v>
@@ -8974,7 +8973,7 @@
       </c>
       <c r="O80" s="50"/>
       <c r="P80" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q80" s="50"/>
       <c r="R80" s="50"/>
@@ -8999,7 +8998,7 @@
         <v>44837</v>
       </c>
       <c r="D81" s="50" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E81" s="50">
         <v>2</v>
@@ -9024,7 +9023,7 @@
       </c>
       <c r="O81" s="50"/>
       <c r="P81" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q81" s="50"/>
       <c r="R81" s="50"/>
@@ -9049,7 +9048,7 @@
         <v>34027</v>
       </c>
       <c r="D82" s="50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E82" s="50">
         <v>3</v>
@@ -9067,7 +9066,7 @@
         <v>62</v>
       </c>
       <c r="K82" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L82" s="50" t="s">
         <v>1</v>
@@ -9127,7 +9126,7 @@
         <v>34057</v>
       </c>
       <c r="D83" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E83" s="50">
         <v>5</v>
@@ -9136,7 +9135,7 @@
         <v>1</v>
       </c>
       <c r="G83" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I83" s="50" t="s">
         <v>78</v>
@@ -9145,7 +9144,7 @@
         <v>62</v>
       </c>
       <c r="K83" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L83" s="50" t="s">
         <v>1</v>
@@ -9205,7 +9204,7 @@
         <v>34063</v>
       </c>
       <c r="D84" s="50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E84" s="50">
         <v>16</v>
@@ -9214,7 +9213,7 @@
         <v>1</v>
       </c>
       <c r="G84" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I84" s="50" t="s">
         <v>78</v>
@@ -9223,10 +9222,10 @@
         <v>62</v>
       </c>
       <c r="K84" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L84" s="50" t="s">
         <v>258</v>
-      </c>
-      <c r="L84" s="50" t="s">
-        <v>259</v>
       </c>
       <c r="M84" s="50" t="s">
         <v>1</v>
@@ -9283,7 +9282,7 @@
         <v>34107</v>
       </c>
       <c r="D85" s="50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E85" s="50">
         <v>12</v>
@@ -9361,7 +9360,7 @@
         <v>34115</v>
       </c>
       <c r="D86" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E86" s="50">
         <v>28</v>
@@ -9382,7 +9381,7 @@
         <v>75</v>
       </c>
       <c r="L86" s="50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M86" s="50" t="s">
         <v>1</v>
@@ -9439,7 +9438,7 @@
         <v>34147</v>
       </c>
       <c r="D87" s="50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E87" s="50">
         <v>54</v>
@@ -9448,7 +9447,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I87" s="50" t="s">
         <v>78</v>
@@ -9457,7 +9456,7 @@
         <v>62</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L87" s="50" t="s">
         <v>1</v>
@@ -9517,7 +9516,7 @@
         <v>34177</v>
       </c>
       <c r="D88" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E88" s="50">
         <v>4</v>
@@ -9526,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I88" s="50" t="s">
         <v>78</v>
@@ -9535,7 +9534,7 @@
         <v>62</v>
       </c>
       <c r="K88" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L88" s="50" t="s">
         <v>1</v>
@@ -9595,7 +9594,7 @@
         <v>34198</v>
       </c>
       <c r="D89" s="50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E89" s="50">
         <v>19</v>
@@ -9613,7 +9612,7 @@
         <v>62</v>
       </c>
       <c r="K89" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L89" s="50" t="s">
         <v>1</v>
@@ -9673,7 +9672,7 @@
         <v>34199</v>
       </c>
       <c r="D90" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E90" s="50">
         <v>5</v>
@@ -9691,7 +9690,7 @@
         <v>62</v>
       </c>
       <c r="K90" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L90" s="50" t="s">
         <v>1</v>
@@ -9751,7 +9750,7 @@
         <v>34202</v>
       </c>
       <c r="D91" s="50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E91" s="50">
         <v>16</v>
@@ -9769,10 +9768,10 @@
         <v>62</v>
       </c>
       <c r="K91" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L91" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M91" s="50" t="s">
         <v>1</v>
@@ -9829,7 +9828,7 @@
         <v>34205</v>
       </c>
       <c r="D92" s="50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E92" s="50">
         <v>29</v>
@@ -9847,13 +9846,13 @@
         <v>62</v>
       </c>
       <c r="K92" s="50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L92" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M92" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N92" s="50">
         <v>5</v>
@@ -9907,7 +9906,7 @@
         <v>34214</v>
       </c>
       <c r="D93" s="50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E93" s="50">
         <v>52</v>
@@ -9925,13 +9924,13 @@
         <v>62</v>
       </c>
       <c r="K93" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L93" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="L93" s="50" t="s">
+      <c r="M93" s="50" t="s">
         <v>273</v>
-      </c>
-      <c r="M93" s="50" t="s">
-        <v>274</v>
       </c>
       <c r="N93" s="50">
         <v>5</v>
@@ -9985,7 +9984,7 @@
         <v>34217</v>
       </c>
       <c r="D94" s="50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E94" s="50">
         <v>4</v>
@@ -9994,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I94" s="50" t="s">
         <v>78</v>
@@ -10003,7 +10002,7 @@
         <v>62</v>
       </c>
       <c r="K94" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L94" s="50" t="s">
         <v>1</v>
@@ -10063,7 +10062,7 @@
         <v>34240</v>
       </c>
       <c r="D95" s="50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E95" s="50">
         <v>51</v>
@@ -10081,7 +10080,7 @@
         <v>62</v>
       </c>
       <c r="K95" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L95" s="50" t="s">
         <v>1</v>
@@ -10141,7 +10140,7 @@
         <v>34275</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E96" s="50">
         <v>16</v>
@@ -10159,10 +10158,10 @@
         <v>62</v>
       </c>
       <c r="K96" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L96" s="50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M96" s="50" t="s">
         <v>1</v>
@@ -10219,7 +10218,7 @@
         <v>34291</v>
       </c>
       <c r="D97" s="50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E97" s="50">
         <v>20</v>
@@ -10237,13 +10236,13 @@
         <v>62</v>
       </c>
       <c r="K97" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L97" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="M97" s="50" t="s">
         <v>281</v>
-      </c>
-      <c r="M97" s="50" t="s">
-        <v>282</v>
       </c>
       <c r="N97" s="50">
         <v>5</v>
@@ -10297,7 +10296,7 @@
         <v>34301</v>
       </c>
       <c r="D98" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E98" s="50">
         <v>51</v>
@@ -10315,7 +10314,7 @@
         <v>62</v>
       </c>
       <c r="K98" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L98" s="50" t="s">
         <v>1</v>
@@ -10375,7 +10374,7 @@
         <v>34334</v>
       </c>
       <c r="D99" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E99" s="50">
         <v>52</v>
@@ -10393,13 +10392,13 @@
         <v>62</v>
       </c>
       <c r="K99" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="L99" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="L99" s="50" t="s">
-        <v>287</v>
-      </c>
       <c r="M99" s="50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N99" s="50">
         <v>5</v>
@@ -10453,7 +10452,7 @@
         <v>34337</v>
       </c>
       <c r="D100" s="50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E100" s="50">
         <v>14</v>
@@ -10471,10 +10470,10 @@
         <v>62</v>
       </c>
       <c r="K100" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L100" s="50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M100" s="50" t="s">
         <v>1</v>
@@ -10531,7 +10530,7 @@
         <v>34586</v>
       </c>
       <c r="D101" s="50" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E101" s="50">
         <v>2</v>
@@ -10556,7 +10555,7 @@
       </c>
       <c r="O101" s="50"/>
       <c r="P101" s="50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q101" s="50"/>
       <c r="R101" s="50"/>
@@ -10581,7 +10580,7 @@
         <v>34587</v>
       </c>
       <c r="D102" s="50" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E102" s="50">
         <v>2</v>
@@ -10606,7 +10605,7 @@
       </c>
       <c r="O102" s="50"/>
       <c r="P102" s="50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q102" s="50"/>
       <c r="R102" s="50"/>
@@ -10631,7 +10630,7 @@
         <v>34589</v>
       </c>
       <c r="D103" s="50" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E103" s="50">
         <v>4</v>
@@ -10640,7 +10639,7 @@
         <v>2</v>
       </c>
       <c r="G103" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I103" s="50" t="s">
         <v>78</v>
@@ -10649,7 +10648,7 @@
         <v>62</v>
       </c>
       <c r="K103" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L103" s="50" t="s">
         <v>1</v>
@@ -10711,7 +10710,7 @@
         <v>34590</v>
       </c>
       <c r="D104" s="50" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E104" s="50">
         <v>5</v>
@@ -10720,7 +10719,7 @@
         <v>3</v>
       </c>
       <c r="G104" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I104" s="50" t="s">
         <v>78</v>
@@ -10729,7 +10728,7 @@
         <v>62</v>
       </c>
       <c r="K104" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L104" s="50" t="s">
         <v>1</v>
@@ -10791,7 +10790,7 @@
         <v>34591</v>
       </c>
       <c r="D105" s="50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E105" s="50">
         <v>5</v>
@@ -10800,7 +10799,7 @@
         <v>2</v>
       </c>
       <c r="G105" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I105" s="50" t="s">
         <v>78</v>
@@ -10809,7 +10808,7 @@
         <v>62</v>
       </c>
       <c r="K105" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L105" s="50" t="s">
         <v>1</v>
@@ -10871,7 +10870,7 @@
         <v>34696</v>
       </c>
       <c r="D106" s="50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E106" s="50">
         <v>2</v>
@@ -10896,7 +10895,7 @@
       </c>
       <c r="O106" s="50"/>
       <c r="P106" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q106" s="50"/>
       <c r="R106" s="50"/>
@@ -10921,7 +10920,7 @@
         <v>34699</v>
       </c>
       <c r="D107" s="50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E107" s="50">
         <v>56</v>
@@ -10939,7 +10938,7 @@
         <v>62</v>
       </c>
       <c r="K107" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L107" s="50" t="s">
         <v>1</v>
@@ -11001,7 +11000,7 @@
         <v>34701</v>
       </c>
       <c r="D108" s="50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E108" s="50">
         <v>56</v>
@@ -11019,7 +11018,7 @@
         <v>62</v>
       </c>
       <c r="K108" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L108" s="50" t="s">
         <v>1</v>
@@ -11081,7 +11080,7 @@
         <v>34700</v>
       </c>
       <c r="D109" s="50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E109" s="50">
         <v>56</v>
@@ -11099,7 +11098,7 @@
         <v>62</v>
       </c>
       <c r="K109" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L109" s="50" t="s">
         <v>1</v>
@@ -11161,7 +11160,7 @@
         <v>34697</v>
       </c>
       <c r="D110" s="50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E110" s="50">
         <v>56</v>
@@ -11179,7 +11178,7 @@
         <v>62</v>
       </c>
       <c r="K110" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L110" s="50" t="s">
         <v>1</v>
@@ -11241,7 +11240,7 @@
         <v>34698</v>
       </c>
       <c r="D111" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E111" s="50">
         <v>56</v>
@@ -11259,7 +11258,7 @@
         <v>62</v>
       </c>
       <c r="K111" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L111" s="50" t="s">
         <v>1</v>
@@ -11321,7 +11320,7 @@
         <v>34713</v>
       </c>
       <c r="D112" s="50" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E112" s="50">
         <v>56</v>
@@ -11339,7 +11338,7 @@
         <v>62</v>
       </c>
       <c r="K112" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L112" s="50" t="s">
         <v>1</v>
@@ -11401,7 +11400,7 @@
         <v>34702</v>
       </c>
       <c r="D113" s="50" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E113" s="50">
         <v>56</v>
@@ -11419,7 +11418,7 @@
         <v>62</v>
       </c>
       <c r="K113" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L113" s="50" t="s">
         <v>1</v>
@@ -11481,7 +11480,7 @@
         <v>34703</v>
       </c>
       <c r="D114" s="50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E114" s="50">
         <v>56</v>
@@ -11499,7 +11498,7 @@
         <v>62</v>
       </c>
       <c r="K114" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L114" s="50" t="s">
         <v>1</v>
@@ -11561,7 +11560,7 @@
         <v>34704</v>
       </c>
       <c r="D115" s="50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E115" s="50">
         <v>56</v>
@@ -11579,7 +11578,7 @@
         <v>62</v>
       </c>
       <c r="K115" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L115" s="50" t="s">
         <v>1</v>
@@ -11641,7 +11640,7 @@
         <v>34705</v>
       </c>
       <c r="D116" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E116" s="50">
         <v>56</v>
@@ -11659,7 +11658,7 @@
         <v>62</v>
       </c>
       <c r="K116" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L116" s="50" t="s">
         <v>1</v>
@@ -11721,7 +11720,7 @@
         <v>34706</v>
       </c>
       <c r="D117" s="50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E117" s="50">
         <v>56</v>
@@ -11739,7 +11738,7 @@
         <v>62</v>
       </c>
       <c r="K117" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L117" s="50" t="s">
         <v>1</v>
@@ -11801,7 +11800,7 @@
         <v>34707</v>
       </c>
       <c r="D118" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E118" s="50">
         <v>56</v>
@@ -11819,7 +11818,7 @@
         <v>62</v>
       </c>
       <c r="K118" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L118" s="50" t="s">
         <v>1</v>
@@ -11881,7 +11880,7 @@
         <v>34708</v>
       </c>
       <c r="D119" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E119" s="50">
         <v>56</v>
@@ -11899,7 +11898,7 @@
         <v>62</v>
       </c>
       <c r="K119" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L119" s="50" t="s">
         <v>1</v>
@@ -11961,7 +11960,7 @@
         <v>34709</v>
       </c>
       <c r="D120" s="50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E120" s="50">
         <v>56</v>
@@ -11979,7 +11978,7 @@
         <v>62</v>
       </c>
       <c r="K120" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L120" s="50" t="s">
         <v>1</v>
@@ -12041,7 +12040,7 @@
         <v>34710</v>
       </c>
       <c r="D121" s="50" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E121" s="50">
         <v>56</v>
@@ -12059,7 +12058,7 @@
         <v>62</v>
       </c>
       <c r="K121" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L121" s="50" t="s">
         <v>1</v>
@@ -12121,7 +12120,7 @@
         <v>34711</v>
       </c>
       <c r="D122" s="50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E122" s="50">
         <v>56</v>
@@ -12139,7 +12138,7 @@
         <v>62</v>
       </c>
       <c r="K122" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L122" s="50" t="s">
         <v>1</v>
@@ -12201,7 +12200,7 @@
         <v>34712</v>
       </c>
       <c r="D123" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E123" s="50">
         <v>56</v>
@@ -12219,7 +12218,7 @@
         <v>62</v>
       </c>
       <c r="K123" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L123" s="50" t="s">
         <v>1</v>
@@ -12281,7 +12280,7 @@
         <v>34714</v>
       </c>
       <c r="D124" s="50" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E124" s="50">
         <v>56</v>
@@ -12299,7 +12298,7 @@
         <v>62</v>
       </c>
       <c r="K124" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L124" s="50" t="s">
         <v>1</v>
@@ -12361,7 +12360,7 @@
         <v>34715</v>
       </c>
       <c r="D125" s="50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E125" s="50">
         <v>56</v>
@@ -12379,7 +12378,7 @@
         <v>62</v>
       </c>
       <c r="K125" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L125" s="50" t="s">
         <v>1</v>
@@ -12441,7 +12440,7 @@
         <v>34716</v>
       </c>
       <c r="D126" s="50" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E126" s="50">
         <v>56</v>
@@ -12459,7 +12458,7 @@
         <v>62</v>
       </c>
       <c r="K126" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L126" s="50" t="s">
         <v>1</v>
@@ -12521,7 +12520,7 @@
         <v>34717</v>
       </c>
       <c r="D127" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E127" s="50">
         <v>56</v>
@@ -12539,7 +12538,7 @@
         <v>62</v>
       </c>
       <c r="K127" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L127" s="50" t="s">
         <v>1</v>
@@ -12601,7 +12600,7 @@
         <v>34593</v>
       </c>
       <c r="D128" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E128" s="50">
         <v>12</v>
@@ -12681,7 +12680,7 @@
         <v>34594</v>
       </c>
       <c r="D129" s="50" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E129" s="50">
         <v>49</v>
@@ -12690,7 +12689,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I129" s="50" t="s">
         <v>78</v>
@@ -12699,10 +12698,10 @@
         <v>62</v>
       </c>
       <c r="K129" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="L129" s="50" t="s">
         <v>325</v>
-      </c>
-      <c r="L129" s="50" t="s">
-        <v>326</v>
       </c>
       <c r="M129" s="50" t="s">
         <v>1</v>
@@ -12761,7 +12760,7 @@
         <v>34595</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E130" s="50">
         <v>48</v>
@@ -12770,7 +12769,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I130" s="50" t="s">
         <v>78</v>
@@ -12779,13 +12778,13 @@
         <v>62</v>
       </c>
       <c r="K130" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="L130" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="L130" s="50" t="s">
+      <c r="M130" s="50" t="s">
         <v>329</v>
-      </c>
-      <c r="M130" s="50" t="s">
-        <v>330</v>
       </c>
       <c r="N130" s="50">
         <v>6</v>
@@ -12841,7 +12840,7 @@
         <v>34596</v>
       </c>
       <c r="D131" s="50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E131" s="50">
         <v>50</v>
@@ -12859,7 +12858,7 @@
         <v>62</v>
       </c>
       <c r="K131" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L131" s="50" t="s">
         <v>1</v>
@@ -12921,7 +12920,7 @@
         <v>34612</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E132" s="50">
         <v>5</v>
@@ -12939,7 +12938,7 @@
         <v>62</v>
       </c>
       <c r="K132" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L132" s="50" t="s">
         <v>1</v>
@@ -13001,7 +13000,7 @@
         <v>34613</v>
       </c>
       <c r="D133" s="50" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E133" s="50">
         <v>5</v>
@@ -13010,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I133" s="50" t="s">
         <v>78</v>
@@ -13019,7 +13018,7 @@
         <v>62</v>
       </c>
       <c r="K133" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L133" s="50" t="s">
         <v>1</v>
@@ -13081,7 +13080,7 @@
         <v>34614</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E134" s="50">
         <v>4</v>
@@ -13090,7 +13089,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I134" s="50" t="s">
         <v>78</v>
@@ -13099,7 +13098,7 @@
         <v>62</v>
       </c>
       <c r="K134" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L134" s="50" t="s">
         <v>1</v>
@@ -13161,7 +13160,7 @@
         <v>34615</v>
       </c>
       <c r="D135" s="50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E135" s="50">
         <v>44</v>
@@ -13179,7 +13178,7 @@
         <v>62</v>
       </c>
       <c r="K135" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L135" s="50" t="s">
         <v>1</v>
@@ -13241,7 +13240,7 @@
         <v>34616</v>
       </c>
       <c r="D136" s="50" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E136" s="50">
         <v>5</v>
@@ -13250,7 +13249,7 @@
         <v>3</v>
       </c>
       <c r="G136" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I136" s="50" t="s">
         <v>78</v>
@@ -13259,7 +13258,7 @@
         <v>62</v>
       </c>
       <c r="K136" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L136" s="50" t="s">
         <v>1</v>
@@ -13321,7 +13320,7 @@
         <v>34617</v>
       </c>
       <c r="D137" s="50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E137" s="50">
         <v>3</v>
@@ -13339,7 +13338,7 @@
         <v>62</v>
       </c>
       <c r="K137" s="50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L137" s="50" t="s">
         <v>1</v>
@@ -13401,7 +13400,7 @@
         <v>34618</v>
       </c>
       <c r="D138" s="50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E138" s="50">
         <v>16</v>
@@ -13410,7 +13409,7 @@
         <v>9</v>
       </c>
       <c r="G138" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I138" s="50" t="s">
         <v>78</v>
@@ -13419,10 +13418,10 @@
         <v>62</v>
       </c>
       <c r="K138" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L138" s="50" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M138" s="50" t="s">
         <v>1</v>
@@ -13481,7 +13480,7 @@
         <v>34619</v>
       </c>
       <c r="D139" s="50" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E139" s="50">
         <v>20</v>
@@ -13499,13 +13498,13 @@
         <v>62</v>
       </c>
       <c r="K139" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L139" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="M139" s="50" t="s">
         <v>343</v>
-      </c>
-      <c r="M139" s="50" t="s">
-        <v>344</v>
       </c>
       <c r="N139" s="50">
         <v>6</v>
@@ -13561,7 +13560,7 @@
         <v>34620</v>
       </c>
       <c r="D140" s="50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E140" s="50">
         <v>4</v>
@@ -13579,7 +13578,7 @@
         <v>62</v>
       </c>
       <c r="K140" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L140" s="50" t="s">
         <v>1</v>
@@ -13641,7 +13640,7 @@
         <v>34621</v>
       </c>
       <c r="D141" s="50" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E141" s="50">
         <v>54</v>
@@ -13659,7 +13658,7 @@
         <v>62</v>
       </c>
       <c r="K141" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L141" s="50" t="s">
         <v>1</v>
@@ -13721,7 +13720,7 @@
         <v>34629</v>
       </c>
       <c r="D142" s="50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E142" s="50">
         <v>4</v>
@@ -13730,7 +13729,7 @@
         <v>2</v>
       </c>
       <c r="G142" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I142" s="50" t="s">
         <v>78</v>
@@ -13739,7 +13738,7 @@
         <v>62</v>
       </c>
       <c r="K142" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L142" s="50" t="s">
         <v>1</v>
@@ -13801,7 +13800,7 @@
         <v>34630</v>
       </c>
       <c r="D143" s="50" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E143" s="50">
         <v>5</v>
@@ -13810,7 +13809,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I143" s="50" t="s">
         <v>78</v>
@@ -13819,7 +13818,7 @@
         <v>62</v>
       </c>
       <c r="K143" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L143" s="50" t="s">
         <v>1</v>
@@ -13881,7 +13880,7 @@
         <v>34631</v>
       </c>
       <c r="D144" s="50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E144" s="50">
         <v>19</v>
@@ -13899,7 +13898,7 @@
         <v>62</v>
       </c>
       <c r="K144" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L144" s="50" t="s">
         <v>1</v>
@@ -13961,7 +13960,7 @@
         <v>34633</v>
       </c>
       <c r="D145" s="50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E145" s="50">
         <v>43</v>
@@ -13970,7 +13969,7 @@
         <v>0</v>
       </c>
       <c r="G145" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I145" s="50" t="s">
         <v>78</v>
@@ -13979,10 +13978,10 @@
         <v>62</v>
       </c>
       <c r="K145" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L145" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M145" s="50" t="s">
         <v>1</v>
@@ -14041,7 +14040,7 @@
         <v>34634</v>
       </c>
       <c r="D146" s="50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E146" s="50">
         <v>5</v>
@@ -14050,7 +14049,7 @@
         <v>4</v>
       </c>
       <c r="G146" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I146" s="50" t="s">
         <v>78</v>
@@ -14059,7 +14058,7 @@
         <v>62</v>
       </c>
       <c r="K146" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L146" s="50" t="s">
         <v>1</v>
@@ -14121,7 +14120,7 @@
         <v>34636</v>
       </c>
       <c r="D147" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E147" s="50">
         <v>4</v>
@@ -14130,7 +14129,7 @@
         <v>3</v>
       </c>
       <c r="G147" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I147" s="50" t="s">
         <v>78</v>
@@ -14139,7 +14138,7 @@
         <v>62</v>
       </c>
       <c r="K147" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L147" s="50" t="s">
         <v>1</v>
@@ -14201,7 +14200,7 @@
         <v>34639</v>
       </c>
       <c r="D148" s="50" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E148" s="50">
         <v>16</v>
@@ -14219,10 +14218,10 @@
         <v>62</v>
       </c>
       <c r="K148" s="50" t="s">
+        <v>355</v>
+      </c>
+      <c r="L148" s="50" t="s">
         <v>356</v>
-      </c>
-      <c r="L148" s="50" t="s">
-        <v>357</v>
       </c>
       <c r="M148" s="50" t="s">
         <v>1</v>
@@ -14281,7 +14280,7 @@
         <v>34640</v>
       </c>
       <c r="D149" s="50" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E149" s="50">
         <v>16</v>
@@ -14290,7 +14289,7 @@
         <v>2</v>
       </c>
       <c r="G149" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I149" s="50" t="s">
         <v>78</v>
@@ -14302,7 +14301,7 @@
         <v>79</v>
       </c>
       <c r="L149" s="50" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M149" s="50" t="s">
         <v>1</v>
@@ -14361,7 +14360,7 @@
         <v>34641</v>
       </c>
       <c r="D150" s="50" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E150" s="50">
         <v>3</v>
@@ -14379,7 +14378,7 @@
         <v>62</v>
       </c>
       <c r="K150" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L150" s="50" t="s">
         <v>1</v>
@@ -14441,7 +14440,7 @@
         <v>34644</v>
       </c>
       <c r="D151" s="50" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E151" s="50">
         <v>5</v>
@@ -14450,7 +14449,7 @@
         <v>2</v>
       </c>
       <c r="G151" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I151" s="50" t="s">
         <v>78</v>
@@ -14459,7 +14458,7 @@
         <v>62</v>
       </c>
       <c r="K151" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L151" s="50" t="s">
         <v>1</v>
@@ -14521,7 +14520,7 @@
         <v>34645</v>
       </c>
       <c r="D152" s="50" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E152" s="50">
         <v>3</v>
@@ -14539,7 +14538,7 @@
         <v>62</v>
       </c>
       <c r="K152" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L152" s="50" t="s">
         <v>1</v>
@@ -14601,7 +14600,7 @@
         <v>34649</v>
       </c>
       <c r="D153" s="50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E153" s="50">
         <v>5</v>
@@ -14610,7 +14609,7 @@
         <v>2</v>
       </c>
       <c r="G153" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I153" s="50" t="s">
         <v>78</v>
@@ -14619,7 +14618,7 @@
         <v>62</v>
       </c>
       <c r="K153" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L153" s="50" t="s">
         <v>1</v>
@@ -14681,7 +14680,7 @@
         <v>34676</v>
       </c>
       <c r="D154" s="50" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E154" s="50">
         <v>16</v>
@@ -14690,7 +14689,7 @@
         <v>1</v>
       </c>
       <c r="G154" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I154" s="50" t="s">
         <v>78</v>
@@ -14699,10 +14698,10 @@
         <v>62</v>
       </c>
       <c r="K154" s="50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L154" s="50" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M154" s="50" t="s">
         <v>1</v>
@@ -14761,7 +14760,7 @@
         <v>34686</v>
       </c>
       <c r="D155" s="50" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E155" s="50">
         <v>18</v>
@@ -14779,7 +14778,7 @@
         <v>62</v>
       </c>
       <c r="K155" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L155" s="50" t="s">
         <v>1</v>
@@ -14841,7 +14840,7 @@
         <v>34688</v>
       </c>
       <c r="D156" s="50" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E156" s="50">
         <v>4</v>
@@ -14850,7 +14849,7 @@
         <v>3</v>
       </c>
       <c r="G156" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I156" s="50" t="s">
         <v>78</v>
@@ -14859,7 +14858,7 @@
         <v>62</v>
       </c>
       <c r="K156" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L156" s="50" t="s">
         <v>1</v>
@@ -14921,7 +14920,7 @@
         <v>34691</v>
       </c>
       <c r="D157" s="50" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E157" s="50">
         <v>5</v>
@@ -14930,7 +14929,7 @@
         <v>5</v>
       </c>
       <c r="G157" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I157" s="50" t="s">
         <v>78</v>
@@ -14939,7 +14938,7 @@
         <v>62</v>
       </c>
       <c r="K157" s="50" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L157" s="50" t="s">
         <v>1</v>
@@ -15001,7 +15000,7 @@
         <v>34692</v>
       </c>
       <c r="D158" s="50" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E158" s="50">
         <v>4</v>
@@ -15010,7 +15009,7 @@
         <v>0</v>
       </c>
       <c r="G158" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I158" s="50" t="s">
         <v>78</v>
@@ -15019,7 +15018,7 @@
         <v>62</v>
       </c>
       <c r="K158" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L158" s="50" t="s">
         <v>1</v>
@@ -15081,7 +15080,7 @@
         <v>34693</v>
       </c>
       <c r="D159" s="50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E159" s="50">
         <v>13</v>
@@ -15099,10 +15098,10 @@
         <v>62</v>
       </c>
       <c r="K159" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L159" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M159" s="50" t="s">
         <v>1</v>
@@ -15161,7 +15160,7 @@
         <v>34694</v>
       </c>
       <c r="D160" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E160" s="50">
         <v>17</v>
@@ -15179,10 +15178,10 @@
         <v>62</v>
       </c>
       <c r="K160" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L160" s="50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M160" s="50" t="s">
         <v>1</v>
@@ -15241,7 +15240,7 @@
         <v>34695</v>
       </c>
       <c r="D161" s="50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E161" s="50">
         <v>5</v>
@@ -15250,7 +15249,7 @@
         <v>6</v>
       </c>
       <c r="G161" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I161" s="50" t="s">
         <v>78</v>
@@ -15259,7 +15258,7 @@
         <v>62</v>
       </c>
       <c r="K161" s="50" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L161" s="50" t="s">
         <v>1</v>
@@ -15321,7 +15320,7 @@
         <v>34718</v>
       </c>
       <c r="D162" s="50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E162" s="50">
         <v>30</v>
@@ -15330,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="G162" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I162" s="50" t="s">
         <v>78</v>
@@ -15339,10 +15338,10 @@
         <v>62</v>
       </c>
       <c r="K162" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="L162" s="50" t="s">
         <v>378</v>
-      </c>
-      <c r="L162" s="50" t="s">
-        <v>379</v>
       </c>
       <c r="M162" s="50" t="s">
         <v>1</v>
@@ -15401,7 +15400,7 @@
         <v>34730</v>
       </c>
       <c r="D163" s="50" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E163" s="50">
         <v>2</v>
@@ -15426,7 +15425,7 @@
       </c>
       <c r="O163" s="50"/>
       <c r="P163" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q163" s="50"/>
       <c r="R163" s="50"/>
@@ -15451,7 +15450,7 @@
         <v>34732</v>
       </c>
       <c r="D164" s="50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E164" s="50">
         <v>2</v>
@@ -15476,7 +15475,7 @@
       </c>
       <c r="O164" s="50"/>
       <c r="P164" s="50" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q164" s="50"/>
       <c r="R164" s="50"/>
@@ -15501,7 +15500,7 @@
         <v>34733</v>
       </c>
       <c r="D165" s="50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E165" s="50">
         <v>2</v>
@@ -15526,7 +15525,7 @@
       </c>
       <c r="O165" s="50"/>
       <c r="P165" s="50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q165" s="50"/>
       <c r="R165" s="50"/>
@@ -15551,7 +15550,7 @@
         <v>34722</v>
       </c>
       <c r="D166" s="50" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E166" s="50">
         <v>31</v>
@@ -15569,7 +15568,7 @@
         <v>62</v>
       </c>
       <c r="K166" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L166" s="50" t="s">
         <v>1</v>
@@ -15631,7 +15630,7 @@
         <v>34734</v>
       </c>
       <c r="D167" s="50" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E167" s="50">
         <v>57</v>
@@ -15649,13 +15648,13 @@
         <v>62</v>
       </c>
       <c r="K167" s="50" t="s">
+        <v>388</v>
+      </c>
+      <c r="L167" s="50" t="s">
         <v>389</v>
       </c>
-      <c r="L167" s="50" t="s">
+      <c r="M167" s="50" t="s">
         <v>390</v>
-      </c>
-      <c r="M167" s="50" t="s">
-        <v>391</v>
       </c>
       <c r="N167" s="50">
         <v>6</v>
@@ -15711,7 +15710,7 @@
         <v>34735</v>
       </c>
       <c r="D168" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E168" s="50">
         <v>32</v>
@@ -15729,7 +15728,7 @@
         <v>62</v>
       </c>
       <c r="K168" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L168" s="50" t="s">
         <v>1</v>
@@ -15791,7 +15790,7 @@
         <v>34736</v>
       </c>
       <c r="D169" s="50" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E169" s="50">
         <v>15</v>
@@ -15809,7 +15808,7 @@
         <v>62</v>
       </c>
       <c r="K169" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L169" s="50" t="s">
         <v>1</v>
@@ -15871,7 +15870,7 @@
         <v>34741</v>
       </c>
       <c r="D170" s="50" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E170" s="50">
         <v>31</v>
@@ -15880,7 +15879,7 @@
         <v>4</v>
       </c>
       <c r="G170" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I170" s="50" t="s">
         <v>78</v>
@@ -15889,7 +15888,7 @@
         <v>62</v>
       </c>
       <c r="K170" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L170" s="50" t="s">
         <v>1</v>
@@ -15951,7 +15950,7 @@
         <v>34745</v>
       </c>
       <c r="D171" s="50" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E171" s="50">
         <v>31</v>
@@ -15960,7 +15959,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I171" s="50" t="s">
         <v>78</v>
@@ -15969,7 +15968,7 @@
         <v>62</v>
       </c>
       <c r="K171" s="50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L171" s="50" t="s">
         <v>1</v>
@@ -16031,7 +16030,7 @@
         <v>34746</v>
       </c>
       <c r="D172" s="50" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E172" s="50">
         <v>31</v>
@@ -16040,7 +16039,7 @@
         <v>3</v>
       </c>
       <c r="G172" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I172" s="50" t="s">
         <v>78</v>
@@ -16049,7 +16048,7 @@
         <v>62</v>
       </c>
       <c r="K172" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L172" s="50" t="s">
         <v>1</v>
@@ -16111,7 +16110,7 @@
         <v>34747</v>
       </c>
       <c r="D173" s="50" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E173" s="50">
         <v>31</v>
@@ -16129,7 +16128,7 @@
         <v>62</v>
       </c>
       <c r="K173" s="50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L173" s="50" t="s">
         <v>1</v>
@@ -16191,7 +16190,7 @@
         <v>34748</v>
       </c>
       <c r="D174" s="50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E174" s="50">
         <v>31</v>
@@ -16209,7 +16208,7 @@
         <v>62</v>
       </c>
       <c r="K174" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L174" s="50" t="s">
         <v>1</v>
@@ -16271,7 +16270,7 @@
         <v>34749</v>
       </c>
       <c r="D175" s="50" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E175" s="50">
         <v>31</v>
@@ -16280,7 +16279,7 @@
         <v>3</v>
       </c>
       <c r="G175" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I175" s="50" t="s">
         <v>78</v>
@@ -16289,7 +16288,7 @@
         <v>62</v>
       </c>
       <c r="K175" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L175" s="50" t="s">
         <v>1</v>
@@ -16351,7 +16350,7 @@
         <v>34750</v>
       </c>
       <c r="D176" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E176" s="50">
         <v>31</v>
@@ -16360,7 +16359,7 @@
         <v>2</v>
       </c>
       <c r="G176" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I176" s="50" t="s">
         <v>78</v>
@@ -16369,7 +16368,7 @@
         <v>62</v>
       </c>
       <c r="K176" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L176" s="50" t="s">
         <v>1</v>
@@ -16431,7 +16430,7 @@
         <v>34751</v>
       </c>
       <c r="D177" s="50" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E177" s="50">
         <v>31</v>
@@ -16440,7 +16439,7 @@
         <v>2</v>
       </c>
       <c r="G177" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I177" s="50" t="s">
         <v>78</v>
@@ -16449,7 +16448,7 @@
         <v>62</v>
       </c>
       <c r="K177" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L177" s="50" t="s">
         <v>1</v>
@@ -16511,7 +16510,7 @@
         <v>34752</v>
       </c>
       <c r="D178" s="50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E178" s="50">
         <v>31</v>
@@ -16529,7 +16528,7 @@
         <v>62</v>
       </c>
       <c r="K178" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L178" s="50" t="s">
         <v>1</v>
@@ -16591,7 +16590,7 @@
         <v>34753</v>
       </c>
       <c r="D179" s="50" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E179" s="50">
         <v>31</v>
@@ -16609,7 +16608,7 @@
         <v>62</v>
       </c>
       <c r="K179" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L179" s="50" t="s">
         <v>1</v>
@@ -16671,7 +16670,7 @@
         <v>34754</v>
       </c>
       <c r="D180" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E180" s="50">
         <v>31</v>
@@ -16689,7 +16688,7 @@
         <v>62</v>
       </c>
       <c r="K180" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L180" s="50" t="s">
         <v>1</v>
@@ -16751,7 +16750,7 @@
         <v>34757</v>
       </c>
       <c r="D181" s="50" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E181" s="50">
         <v>31</v>
@@ -16760,7 +16759,7 @@
         <v>3</v>
       </c>
       <c r="G181" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I181" s="50" t="s">
         <v>78</v>
@@ -16769,7 +16768,7 @@
         <v>62</v>
       </c>
       <c r="K181" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L181" s="50" t="s">
         <v>1</v>
@@ -16831,7 +16830,7 @@
         <v>34759</v>
       </c>
       <c r="D182" s="50" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E182" s="50">
         <v>31</v>
@@ -16840,7 +16839,7 @@
         <v>3</v>
       </c>
       <c r="G182" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I182" s="50" t="s">
         <v>78</v>
@@ -16849,7 +16848,7 @@
         <v>62</v>
       </c>
       <c r="K182" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L182" s="50" t="s">
         <v>1</v>
@@ -16911,7 +16910,7 @@
         <v>34760</v>
       </c>
       <c r="D183" s="50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E183" s="50">
         <v>32</v>
@@ -16929,7 +16928,7 @@
         <v>62</v>
       </c>
       <c r="K183" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L183" s="50" t="s">
         <v>1</v>
@@ -16991,7 +16990,7 @@
         <v>34764</v>
       </c>
       <c r="D184" s="50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E184" s="50">
         <v>32</v>
@@ -17000,7 +16999,7 @@
         <v>1</v>
       </c>
       <c r="G184" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I184" s="50" t="s">
         <v>78</v>
@@ -17009,7 +17008,7 @@
         <v>62</v>
       </c>
       <c r="K184" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L184" s="50" t="s">
         <v>1</v>
@@ -17071,7 +17070,7 @@
         <v>34765</v>
       </c>
       <c r="D185" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E185" s="50">
         <v>57</v>
@@ -17089,13 +17088,13 @@
         <v>62</v>
       </c>
       <c r="K185" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L185" s="50" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M185" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N185" s="50">
         <v>6</v>
@@ -17151,7 +17150,7 @@
         <v>34766</v>
       </c>
       <c r="D186" s="50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E186" s="50">
         <v>57</v>
@@ -17160,7 +17159,7 @@
         <v>1</v>
       </c>
       <c r="G186" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I186" s="50" t="s">
         <v>61</v>
@@ -17169,13 +17168,13 @@
         <v>62</v>
       </c>
       <c r="K186" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L186" s="50" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M186" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N186" s="50">
         <v>6</v>
@@ -17231,7 +17230,7 @@
         <v>34768</v>
       </c>
       <c r="D187" s="50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E187" s="50">
         <v>31</v>
@@ -17240,7 +17239,7 @@
         <v>2</v>
       </c>
       <c r="G187" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I187" s="50" t="s">
         <v>78</v>
@@ -17249,7 +17248,7 @@
         <v>62</v>
       </c>
       <c r="K187" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L187" s="50" t="s">
         <v>1</v>
@@ -17311,7 +17310,7 @@
         <v>34769</v>
       </c>
       <c r="D188" s="50" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E188" s="50">
         <v>15</v>
@@ -17329,7 +17328,7 @@
         <v>62</v>
       </c>
       <c r="K188" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L188" s="50" t="s">
         <v>1</v>
@@ -17391,7 +17390,7 @@
         <v>34772</v>
       </c>
       <c r="D189" s="50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E189" s="50">
         <v>15</v>
@@ -17409,7 +17408,7 @@
         <v>62</v>
       </c>
       <c r="K189" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L189" s="50" t="s">
         <v>1</v>
@@ -17471,7 +17470,7 @@
         <v>34773</v>
       </c>
       <c r="D190" s="50" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E190" s="50">
         <v>15</v>
@@ -17489,7 +17488,7 @@
         <v>62</v>
       </c>
       <c r="K190" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L190" s="50" t="s">
         <v>1</v>
@@ -17551,7 +17550,7 @@
         <v>34774</v>
       </c>
       <c r="D191" s="50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E191" s="50">
         <v>15</v>
@@ -17569,7 +17568,7 @@
         <v>62</v>
       </c>
       <c r="K191" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L191" s="50" t="s">
         <v>1</v>
@@ -17631,7 +17630,7 @@
         <v>74852</v>
       </c>
       <c r="D192" s="50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E192" s="50">
         <v>12</v>
@@ -17711,7 +17710,7 @@
         <v>74854</v>
       </c>
       <c r="D193" s="50" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E193" s="50">
         <v>5</v>
@@ -17720,10 +17719,10 @@
         <v>1</v>
       </c>
       <c r="G193" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H193" s="50" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I193" s="50" t="s">
         <v>78</v>
@@ -17732,7 +17731,7 @@
         <v>62</v>
       </c>
       <c r="K193" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L193" s="50" t="s">
         <v>1</v>
@@ -17759,7 +17758,7 @@
         <v>0</v>
       </c>
       <c r="T193" s="50" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U193" s="50">
         <v>0</v>
@@ -17794,7 +17793,7 @@
         <v>74857</v>
       </c>
       <c r="D194" s="50" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E194" s="50">
         <v>6</v>
@@ -17803,10 +17802,10 @@
         <v>0</v>
       </c>
       <c r="G194" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H194" s="50" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I194" s="50" t="s">
         <v>78</v>
@@ -17815,13 +17814,13 @@
         <v>62</v>
       </c>
       <c r="K194" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L194" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M194" s="50" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N194" s="50">
         <v>7</v>
@@ -17852,7 +17851,7 @@
         <v>1</v>
       </c>
       <c r="X194" s="50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y194" s="50" t="s">
         <v>1</v>
@@ -17875,7 +17874,7 @@
         <v>74858</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E195" s="50">
         <v>7</v>
@@ -17884,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="G195" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H195" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I195" s="50" t="s">
         <v>78</v>
@@ -17896,10 +17895,10 @@
         <v>62</v>
       </c>
       <c r="K195" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L195" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M195" s="50" t="s">
         <v>1</v>
@@ -17956,7 +17955,7 @@
         <v>74859</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E196" s="50">
         <v>7</v>
@@ -17965,10 +17964,10 @@
         <v>0</v>
       </c>
       <c r="G196" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" s="50" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I196" s="50" t="s">
         <v>78</v>
@@ -17977,10 +17976,10 @@
         <v>62</v>
       </c>
       <c r="K196" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L196" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M196" s="50" t="s">
         <v>1</v>
@@ -18037,7 +18036,7 @@
         <v>74860</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E197" s="50">
         <v>7</v>
@@ -18046,10 +18045,10 @@
         <v>0</v>
       </c>
       <c r="G197" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I197" s="50" t="s">
         <v>78</v>
@@ -18058,10 +18057,10 @@
         <v>62</v>
       </c>
       <c r="K197" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L197" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M197" s="50" t="s">
         <v>1</v>
@@ -18118,7 +18117,7 @@
         <v>74862</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E198" s="50">
         <v>2</v>
@@ -18143,7 +18142,7 @@
       </c>
       <c r="O198" s="50"/>
       <c r="P198" s="50" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q198" s="50"/>
       <c r="R198" s="50"/>
@@ -18172,7 +18171,7 @@
         <v>74863</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E199" s="50">
         <v>20</v>
@@ -18184,7 +18183,7 @@
         <v>60</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I199" s="50" t="s">
         <v>78</v>
@@ -18193,13 +18192,13 @@
         <v>62</v>
       </c>
       <c r="K199" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L199" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="M199" s="50" t="s">
         <v>443</v>
-      </c>
-      <c r="M199" s="50" t="s">
-        <v>444</v>
       </c>
       <c r="N199" s="50">
         <v>7</v>
@@ -18253,7 +18252,7 @@
         <v>74864</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E200" s="50">
         <v>19</v>
@@ -18265,7 +18264,7 @@
         <v>60</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I200" s="50" t="s">
         <v>78</v>
@@ -18274,7 +18273,7 @@
         <v>62</v>
       </c>
       <c r="K200" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L200" s="50" t="s">
         <v>1</v>
@@ -18334,7 +18333,7 @@
         <v>74865</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E201" s="50">
         <v>16</v>
@@ -18346,7 +18345,7 @@
         <v>60</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I201" s="50" t="s">
         <v>78</v>
@@ -18355,10 +18354,10 @@
         <v>62</v>
       </c>
       <c r="K201" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L201" s="50" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M201" s="50" t="s">
         <v>1</v>
@@ -18392,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Y201" s="50" t="s">
         <v>1</v>
@@ -18415,7 +18414,7 @@
         <v>74866</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E202" s="50">
         <v>4</v>
@@ -18424,10 +18423,10 @@
         <v>1</v>
       </c>
       <c r="G202" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>78</v>
@@ -18436,7 +18435,7 @@
         <v>62</v>
       </c>
       <c r="K202" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L202" s="50" t="s">
         <v>1</v>
@@ -18498,7 +18497,7 @@
         <v>74867</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E203" s="50">
         <v>2</v>
@@ -18525,7 +18524,7 @@
       </c>
       <c r="O203" s="50"/>
       <c r="P203" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q203" s="50"/>
       <c r="R203" s="50"/>
@@ -18534,7 +18533,7 @@
       <c r="U203" s="50"/>
       <c r="V203" s="50"/>
       <c r="W203" s="50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X203" s="50"/>
       <c r="Y203" s="50"/>
@@ -18554,7 +18553,7 @@
         <v>74868</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E204" s="50">
         <v>5</v>
@@ -18566,7 +18565,7 @@
         <v>60</v>
       </c>
       <c r="H204" s="50" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I204" s="50" t="s">
         <v>78</v>
@@ -18575,7 +18574,7 @@
         <v>62</v>
       </c>
       <c r="K204" s="50" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L204" s="50" t="s">
         <v>1</v>
@@ -18602,7 +18601,7 @@
         <v>0</v>
       </c>
       <c r="T204" s="50" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U204" s="50">
         <v>1</v>
@@ -18637,7 +18636,7 @@
         <v>74869</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E205" s="50">
         <v>4</v>
@@ -18649,7 +18648,7 @@
         <v>60</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -18658,7 +18657,7 @@
         <v>62</v>
       </c>
       <c r="K205" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L205" s="50" t="s">
         <v>1</v>
@@ -18720,7 +18719,7 @@
         <v>74870</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E206" s="50">
         <v>16</v>
@@ -18729,10 +18728,10 @@
         <v>6</v>
       </c>
       <c r="G206" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I206" s="50" t="s">
         <v>78</v>
@@ -18741,10 +18740,10 @@
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
+        <v>460</v>
+      </c>
+      <c r="L206" s="50" t="s">
         <v>461</v>
-      </c>
-      <c r="L206" s="50" t="s">
-        <v>462</v>
       </c>
       <c r="M206" s="50" t="s">
         <v>1</v>
@@ -18801,7 +18800,7 @@
         <v>74871</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E207" s="50">
         <v>3</v>
@@ -18813,7 +18812,7 @@
         <v>60</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -18822,7 +18821,7 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L207" s="50" t="s">
         <v>1</v>
@@ -18882,7 +18881,7 @@
         <v>74872</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E208" s="50">
         <v>5</v>
@@ -18891,10 +18890,10 @@
         <v>2</v>
       </c>
       <c r="G208" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H208" s="50" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I208" s="50" t="s">
         <v>78</v>
@@ -18903,10 +18902,10 @@
         <v>62</v>
       </c>
       <c r="K208" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M208" s="50" t="s">
         <v>1</v>
@@ -18930,7 +18929,7 @@
         <v>0</v>
       </c>
       <c r="T208" s="50" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="U208" s="50">
         <v>0</v>
@@ -18965,7 +18964,7 @@
         <v>74873</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E209" s="50">
         <v>5</v>
@@ -18977,7 +18976,7 @@
         <v>60</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -18986,7 +18985,7 @@
         <v>62</v>
       </c>
       <c r="K209" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L209" s="50" t="s">
         <v>1</v>
@@ -19013,7 +19012,7 @@
         <v>0</v>
       </c>
       <c r="T209" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="U209" s="50">
         <v>0</v>
@@ -19048,7 +19047,7 @@
         <v>74874</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E210" s="50">
         <v>43</v>
@@ -19060,7 +19059,7 @@
         <v>60</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -19069,10 +19068,10 @@
         <v>62</v>
       </c>
       <c r="K210" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L210" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M210" s="50" t="s">
         <v>1</v>
@@ -19129,7 +19128,7 @@
         <v>74875</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E211" s="50">
         <v>44</v>
@@ -19141,7 +19140,7 @@
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19150,7 +19149,7 @@
         <v>62</v>
       </c>
       <c r="K211" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L211" s="50" t="s">
         <v>1</v>
@@ -19210,7 +19209,7 @@
         <v>74876</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E212" s="50">
         <v>4</v>
@@ -19219,10 +19218,10 @@
         <v>3</v>
       </c>
       <c r="G212" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19231,7 +19230,7 @@
         <v>62</v>
       </c>
       <c r="K212" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L212" s="50" t="s">
         <v>1</v>
@@ -19293,7 +19292,7 @@
         <v>84928</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E213" s="50">
         <v>12</v>
@@ -19373,7 +19372,7 @@
         <v>84929</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E214" s="50">
         <v>30</v>
@@ -19382,10 +19381,10 @@
         <v>0</v>
       </c>
       <c r="G214" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19394,10 +19393,10 @@
         <v>62</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="M214" s="50" t="s">
         <v>1</v>
@@ -19454,7 +19453,7 @@
         <v>84930</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E215" s="50">
         <v>57</v>
@@ -19463,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="G215" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I215" s="50" t="s">
         <v>61</v>
@@ -19472,13 +19471,13 @@
         <v>62</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L215" s="50" t="s">
+        <v>484</v>
+      </c>
+      <c r="M215" s="50" t="s">
         <v>485</v>
-      </c>
-      <c r="M215" s="50" t="s">
-        <v>486</v>
       </c>
       <c r="N215" s="50">
         <v>8</v>
@@ -19532,7 +19531,7 @@
         <v>84931</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E216" s="50">
         <v>32</v>
@@ -19541,10 +19540,10 @@
         <v>1</v>
       </c>
       <c r="G216" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -19553,7 +19552,7 @@
         <v>62</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L216" s="50" t="s">
         <v>1</v>
@@ -19613,7 +19612,7 @@
         <v>84932</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E217" s="50">
         <v>57</v>
@@ -19631,13 +19630,13 @@
         <v>62</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N217" s="50">
         <v>8</v>
@@ -19691,7 +19690,7 @@
         <v>84933</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E218" s="50">
         <v>32</v>
@@ -19703,7 +19702,7 @@
         <v>60</v>
       </c>
       <c r="H218" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I218" s="50" t="s">
         <v>78</v>
@@ -19712,7 +19711,7 @@
         <v>62</v>
       </c>
       <c r="K218" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L218" s="50" t="s">
         <v>1</v>
@@ -19772,7 +19771,7 @@
         <v>84934</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E219" s="50">
         <v>31</v>
@@ -19781,10 +19780,10 @@
         <v>1</v>
       </c>
       <c r="G219" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>78</v>
@@ -19793,7 +19792,7 @@
         <v>62</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -19853,7 +19852,7 @@
         <v>84935</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E220" s="50">
         <v>31</v>
@@ -19865,7 +19864,7 @@
         <v>60</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>78</v>
@@ -19874,7 +19873,7 @@
         <v>62</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L220" s="50" t="s">
         <v>1</v>
@@ -19934,7 +19933,7 @@
         <v>84936</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E221" s="50">
         <v>31</v>
@@ -19946,7 +19945,7 @@
         <v>60</v>
       </c>
       <c r="H221" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I221" s="50" t="s">
         <v>78</v>
@@ -19955,7 +19954,7 @@
         <v>62</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -20015,7 +20014,7 @@
         <v>84937</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E222" s="50">
         <v>31</v>
@@ -20024,10 +20023,10 @@
         <v>4</v>
       </c>
       <c r="G222" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H222" s="50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I222" s="50" t="s">
         <v>78</v>
@@ -20036,7 +20035,7 @@
         <v>62</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -20096,7 +20095,7 @@
         <v>84938</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E223" s="50">
         <v>31</v>
@@ -20108,7 +20107,7 @@
         <v>60</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>78</v>
@@ -20117,7 +20116,7 @@
         <v>62</v>
       </c>
       <c r="K223" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L223" s="50" t="s">
         <v>1</v>
@@ -20177,7 +20176,7 @@
         <v>84939</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E224" s="50">
         <v>15</v>
@@ -20189,7 +20188,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20198,7 +20197,7 @@
         <v>62</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L224" s="50" t="s">
         <v>1</v>
@@ -20258,7 +20257,7 @@
         <v>84940</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E225" s="50">
         <v>15</v>
@@ -20270,7 +20269,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20279,7 +20278,7 @@
         <v>62</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L225" s="50" t="s">
         <v>1</v>
@@ -20339,7 +20338,7 @@
         <v>84941</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E226" s="50">
         <v>16</v>
@@ -20351,7 +20350,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20360,10 +20359,10 @@
         <v>62</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M226" s="50" t="s">
         <v>1</v>
@@ -20420,7 +20419,7 @@
         <v>84942</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E227" s="50">
         <v>52</v>
@@ -20438,13 +20437,13 @@
         <v>62</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L227" s="50" t="s">
+        <v>510</v>
+      </c>
+      <c r="M227" s="50" t="s">
         <v>511</v>
-      </c>
-      <c r="M227" s="50" t="s">
-        <v>512</v>
       </c>
       <c r="N227" s="50">
         <v>8</v>
@@ -20498,7 +20497,7 @@
         <v>84943</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E228" s="50">
         <v>51</v>
@@ -20510,7 +20509,7 @@
         <v>60</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>78</v>
@@ -20519,7 +20518,7 @@
         <v>62</v>
       </c>
       <c r="K228" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L228" s="50" t="s">
         <v>1</v>
@@ -20579,7 +20578,7 @@
         <v>84944</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E229" s="50">
         <v>52</v>
@@ -20597,13 +20596,13 @@
         <v>62</v>
       </c>
       <c r="K229" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N229" s="50">
         <v>8</v>
@@ -20657,7 +20656,7 @@
         <v>84945</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E230" s="50">
         <v>51</v>
@@ -20669,7 +20668,7 @@
         <v>60</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I230" s="50" t="s">
         <v>78</v>
@@ -20678,7 +20677,7 @@
         <v>62</v>
       </c>
       <c r="K230" s="50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L230" s="50" t="s">
         <v>1</v>
@@ -20738,7 +20737,7 @@
         <v>84946</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E231" s="50">
         <v>56</v>
@@ -20756,7 +20755,7 @@
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -20816,7 +20815,7 @@
         <v>84947</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E232" s="50">
         <v>56</v>
@@ -20834,7 +20833,7 @@
         <v>62</v>
       </c>
       <c r="K232" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L232" s="50" t="s">
         <v>1</v>
@@ -20894,7 +20893,7 @@
         <v>84948</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E233" s="50">
         <v>56</v>
@@ -20912,7 +20911,7 @@
         <v>62</v>
       </c>
       <c r="K233" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L233" s="50" t="s">
         <v>1</v>
@@ -20972,7 +20971,7 @@
         <v>84949</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E234" s="50">
         <v>56</v>
@@ -20990,7 +20989,7 @@
         <v>62</v>
       </c>
       <c r="K234" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L234" s="50" t="s">
         <v>1</v>
@@ -21050,7 +21049,7 @@
         <v>84950</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E235" s="50">
         <v>56</v>
@@ -21068,7 +21067,7 @@
         <v>62</v>
       </c>
       <c r="K235" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L235" s="50" t="s">
         <v>1</v>
@@ -21128,7 +21127,7 @@
         <v>84951</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E236" s="50">
         <v>56</v>
@@ -21146,7 +21145,7 @@
         <v>62</v>
       </c>
       <c r="K236" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L236" s="50" t="s">
         <v>1</v>
@@ -21206,7 +21205,7 @@
         <v>84952</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E237" s="50">
         <v>56</v>
@@ -21224,7 +21223,7 @@
         <v>62</v>
       </c>
       <c r="K237" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L237" s="50" t="s">
         <v>1</v>
@@ -21284,7 +21283,7 @@
         <v>84953</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E238" s="50">
         <v>56</v>
@@ -21302,7 +21301,7 @@
         <v>62</v>
       </c>
       <c r="K238" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L238" s="50" t="s">
         <v>1</v>
@@ -21362,7 +21361,7 @@
         <v>84954</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E239" s="50">
         <v>56</v>
@@ -21380,7 +21379,7 @@
         <v>62</v>
       </c>
       <c r="K239" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L239" s="50" t="s">
         <v>1</v>
@@ -21440,7 +21439,7 @@
         <v>84955</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E240" s="50">
         <v>56</v>
@@ -21458,7 +21457,7 @@
         <v>62</v>
       </c>
       <c r="K240" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L240" s="50" t="s">
         <v>1</v>
@@ -21518,7 +21517,7 @@
         <v>84956</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E241" s="50">
         <v>56</v>
@@ -21536,7 +21535,7 @@
         <v>62</v>
       </c>
       <c r="K241" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L241" s="50" t="s">
         <v>1</v>
@@ -21596,7 +21595,7 @@
         <v>84957</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E242" s="50">
         <v>56</v>
@@ -21614,7 +21613,7 @@
         <v>62</v>
       </c>
       <c r="K242" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L242" s="50" t="s">
         <v>1</v>
@@ -21674,7 +21673,7 @@
         <v>84958</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E243" s="50">
         <v>56</v>
@@ -21692,7 +21691,7 @@
         <v>62</v>
       </c>
       <c r="K243" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L243" s="50" t="s">
         <v>1</v>
@@ -21752,7 +21751,7 @@
         <v>84959</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E244" s="50">
         <v>56</v>
@@ -21770,7 +21769,7 @@
         <v>62</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L244" s="50" t="s">
         <v>1</v>
@@ -21830,7 +21829,7 @@
         <v>84960</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E245" s="50">
         <v>56</v>
@@ -21848,7 +21847,7 @@
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
@@ -21908,7 +21907,7 @@
         <v>84961</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E246" s="50">
         <v>56</v>
@@ -21926,7 +21925,7 @@
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
@@ -21986,7 +21985,7 @@
         <v>84962</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E247" s="50">
         <v>56</v>
@@ -22004,7 +22003,7 @@
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
@@ -22064,7 +22063,7 @@
         <v>84963</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E248" s="50">
         <v>56</v>
@@ -22082,7 +22081,7 @@
         <v>62</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L248" s="50" t="s">
         <v>1</v>
@@ -22142,7 +22141,7 @@
         <v>84964</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E249" s="50">
         <v>56</v>
@@ -22160,7 +22159,7 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22220,7 +22219,7 @@
         <v>84965</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E250" s="50">
         <v>56</v>
@@ -22238,7 +22237,7 @@
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
@@ -22298,7 +22297,7 @@
         <v>84966</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E251" s="50">
         <v>56</v>
@@ -22316,7 +22315,7 @@
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L251" s="50" t="s">
         <v>1</v>
@@ -22376,7 +22375,7 @@
         <v>84967</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E252" s="50">
         <v>56</v>
@@ -22394,7 +22393,7 @@
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L252" s="50" t="s">
         <v>1</v>
@@ -22454,7 +22453,7 @@
         <v>84968</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E253" s="50">
         <v>56</v>
@@ -22472,7 +22471,7 @@
         <v>62</v>
       </c>
       <c r="K253" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L253" s="50" t="s">
         <v>1</v>
@@ -22532,7 +22531,7 @@
         <v>84969</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E254" s="50">
         <v>45</v>
@@ -22541,10 +22540,10 @@
         <v>0</v>
       </c>
       <c r="G254" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -22553,7 +22552,7 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -22613,7 +22612,7 @@
         <v>84970</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E255" s="50">
         <v>46</v>
@@ -22622,10 +22621,10 @@
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
+        <v>546</v>
+      </c>
+      <c r="H255" s="50" t="s">
         <v>547</v>
-      </c>
-      <c r="H255" s="50" t="s">
-        <v>548</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22634,7 +22633,7 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L255" s="50" t="s">
         <v>1</v>
@@ -22694,7 +22693,7 @@
         <v>84971</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E256" s="50">
         <v>47</v>
@@ -22703,10 +22702,10 @@
         <v>0</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -22715,13 +22714,13 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
+        <v>551</v>
+      </c>
+      <c r="L256" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M256" s="50" t="s">
         <v>552</v>
-      </c>
-      <c r="L256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M256" s="50" t="s">
-        <v>553</v>
       </c>
       <c r="N256" s="50">
         <v>8</v>
@@ -22775,7 +22774,7 @@
         <v>84972</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E257" s="50">
         <v>46</v>
@@ -22784,10 +22783,10 @@
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
+        <v>554</v>
+      </c>
+      <c r="H257" s="50" t="s">
         <v>555</v>
-      </c>
-      <c r="H257" s="50" t="s">
-        <v>556</v>
       </c>
       <c r="I257" s="50" t="s">
         <v>78</v>
@@ -22796,7 +22795,7 @@
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
@@ -22856,7 +22855,7 @@
         <v>84973</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E258" s="50">
         <v>16</v>
@@ -22868,7 +22867,7 @@
         <v>60</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -22877,10 +22876,10 @@
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -22937,7 +22936,7 @@
         <v>84974</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E259" s="50">
         <v>46</v>
@@ -22949,7 +22948,7 @@
         <v>60</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -22958,7 +22957,7 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L259" s="50" t="s">
         <v>1</v>
@@ -23018,7 +23017,7 @@
         <v>84976</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E260" s="50">
         <v>2</v>
@@ -23043,7 +23042,7 @@
       </c>
       <c r="O260" s="50"/>
       <c r="P260" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Q260" s="50"/>
       <c r="R260" s="50"/>
@@ -23068,7 +23067,7 @@
         <v>84977</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E261" s="50">
         <v>2</v>
@@ -23093,7 +23092,7 @@
       </c>
       <c r="O261" s="50"/>
       <c r="P261" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q261" s="50"/>
       <c r="R261" s="50"/>
@@ -23118,7 +23117,7 @@
         <v>84978</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E262" s="50">
         <v>2</v>
@@ -23143,7 +23142,7 @@
       </c>
       <c r="O262" s="50"/>
       <c r="P262" s="50" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="Q262" s="50"/>
       <c r="R262" s="50"/>
@@ -23168,7 +23167,7 @@
         <v>84979</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E263" s="50">
         <v>48</v>
@@ -23177,10 +23176,10 @@
         <v>0</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23189,13 +23188,13 @@
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L263" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="M263" s="50" t="s">
         <v>570</v>
-      </c>
-      <c r="M263" s="50" t="s">
-        <v>571</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23249,7 +23248,7 @@
         <v>84980</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E264" s="50">
         <v>49</v>
@@ -23261,7 +23260,7 @@
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23270,10 +23269,10 @@
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
@@ -23330,7 +23329,7 @@
         <v>84981</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E265" s="50">
         <v>50</v>
@@ -23342,7 +23341,7 @@
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23351,7 +23350,7 @@
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L265" s="50" t="s">
         <v>1</v>
@@ -23411,7 +23410,7 @@
         <v>84982</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E266" s="50">
         <v>23</v>
@@ -23429,13 +23428,13 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
+        <v>577</v>
+      </c>
+      <c r="L266" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M266" s="50" t="s">
         <v>578</v>
-      </c>
-      <c r="L266" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M266" s="50" t="s">
-        <v>579</v>
       </c>
       <c r="N266" s="50">
         <v>8</v>
@@ -23491,7 +23490,7 @@
         <v>84983</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E267" s="50">
         <v>24</v>
@@ -23503,7 +23502,7 @@
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23512,7 +23511,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23574,7 +23573,7 @@
         <v>84984</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E268" s="50">
         <v>25</v>
@@ -23586,7 +23585,7 @@
         <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23595,7 +23594,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23657,7 +23656,7 @@
         <v>330037</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E269" s="50">
         <v>5</v>
@@ -23669,7 +23668,7 @@
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -23678,7 +23677,7 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -23740,7 +23739,7 @@
         <v>330038</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E270" s="50">
         <v>6</v>
@@ -23749,10 +23748,10 @@
         <v>0</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23761,13 +23760,13 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M270" s="50" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N270" s="50">
         <v>33</v>
@@ -23821,7 +23820,7 @@
         <v>330039</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E271" s="50">
         <v>7</v>
@@ -23830,10 +23829,10 @@
         <v>0</v>
       </c>
       <c r="G271" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -23842,10 +23841,10 @@
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M271" s="50" t="s">
         <v>1</v>
@@ -23902,7 +23901,7 @@
         <v>330040</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E272" s="50">
         <v>7</v>
@@ -23911,10 +23910,10 @@
         <v>0</v>
       </c>
       <c r="G272" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23923,10 +23922,10 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -23983,7 +23982,7 @@
         <v>330041</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E273" s="50">
         <v>7</v>
@@ -23992,10 +23991,10 @@
         <v>0</v>
       </c>
       <c r="G273" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -24004,10 +24003,10 @@
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M273" s="50" t="s">
         <v>1</v>
@@ -24064,7 +24063,7 @@
         <v>330042</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E274" s="50">
         <v>20</v>
@@ -24076,7 +24075,7 @@
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24085,13 +24084,13 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L274" s="50" t="s">
+        <v>598</v>
+      </c>
+      <c r="M274" s="50" t="s">
         <v>599</v>
-      </c>
-      <c r="M274" s="50" t="s">
-        <v>600</v>
       </c>
       <c r="N274" s="50">
         <v>33</v>
@@ -24145,7 +24144,7 @@
         <v>330043</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E275" s="50">
         <v>19</v>
@@ -24157,7 +24156,7 @@
         <v>60</v>
       </c>
       <c r="H275" s="50" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I275" s="50" t="s">
         <v>78</v>
@@ -24166,7 +24165,7 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L275" s="50" t="s">
         <v>1</v>
@@ -24226,7 +24225,7 @@
         <v>330044</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E276" s="50">
         <v>16</v>
@@ -24238,7 +24237,7 @@
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24247,10 +24246,10 @@
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L276" s="50" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="M276" s="50" t="s">
         <v>1</v>
@@ -24307,7 +24306,7 @@
         <v>330045</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E277" s="50">
         <v>5</v>
@@ -24316,10 +24315,10 @@
         <v>1</v>
       </c>
       <c r="G277" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H277" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>78</v>
@@ -24328,7 +24327,7 @@
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L277" s="50" t="s">
         <v>1</v>
@@ -24390,7 +24389,7 @@
         <v>330046</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E278" s="50">
         <v>16</v>
@@ -24399,10 +24398,10 @@
         <v>6</v>
       </c>
       <c r="G278" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24411,10 +24410,10 @@
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
@@ -24471,7 +24470,7 @@
         <v>330047</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E279" s="50">
         <v>3</v>
@@ -24483,7 +24482,7 @@
         <v>60</v>
       </c>
       <c r="H279" s="50" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>78</v>
@@ -24492,7 +24491,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24552,7 +24551,7 @@
         <v>330048</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E280" s="50">
         <v>5</v>
@@ -24564,7 +24563,7 @@
         <v>60</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>78</v>
@@ -24573,7 +24572,7 @@
         <v>62</v>
       </c>
       <c r="K280" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L280" s="50" t="s">
         <v>1</v>
@@ -24635,7 +24634,7 @@
         <v>330049</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E281" s="50">
         <v>43</v>
@@ -24647,7 +24646,7 @@
         <v>60</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>78</v>
@@ -24656,10 +24655,10 @@
         <v>62</v>
       </c>
       <c r="K281" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L281" s="50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M281" s="50" t="s">
         <v>1</v>
@@ -24716,7 +24715,7 @@
         <v>330050</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E282" s="50">
         <v>44</v>
@@ -24728,7 +24727,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I282" s="50" t="s">
         <v>78</v>
@@ -24737,7 +24736,7 @@
         <v>62</v>
       </c>
       <c r="K282" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L282" s="50" t="s">
         <v>1</v>
@@ -24797,7 +24796,7 @@
         <v>330051</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E283" s="50">
         <v>4</v>
@@ -24806,10 +24805,10 @@
         <v>1</v>
       </c>
       <c r="G283" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H283" s="50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I283" s="50" t="s">
         <v>78</v>
@@ -24818,7 +24817,7 @@
         <v>62</v>
       </c>
       <c r="K283" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L283" s="50" t="s">
         <v>1</v>
@@ -24880,7 +24879,7 @@
         <v>330052</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E284" s="50">
         <v>4</v>
@@ -24889,10 +24888,10 @@
         <v>2</v>
       </c>
       <c r="G284" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I284" s="50" t="s">
         <v>78</v>
@@ -24901,7 +24900,7 @@
         <v>62</v>
       </c>
       <c r="K284" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L284" s="50" t="s">
         <v>1</v>
@@ -24963,7 +24962,7 @@
         <v>330053</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E285" s="50">
         <v>4</v>
@@ -24975,7 +24974,7 @@
         <v>60</v>
       </c>
       <c r="H285" s="50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I285" s="50" t="s">
         <v>78</v>
@@ -24984,7 +24983,7 @@
         <v>62</v>
       </c>
       <c r="K285" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L285" s="50" t="s">
         <v>1</v>
@@ -25046,7 +25045,7 @@
         <v>330054</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E286" s="50">
         <v>5</v>
@@ -25058,7 +25057,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I286" s="50" t="s">
         <v>78</v>
@@ -25067,7 +25066,7 @@
         <v>62</v>
       </c>
       <c r="K286" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L286" s="50" t="s">
         <v>1</v>
@@ -25129,7 +25128,7 @@
         <v>330055</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E287" s="50">
         <v>4</v>
@@ -25138,10 +25137,10 @@
         <v>1</v>
       </c>
       <c r="G287" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H287" s="50" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I287" s="50" t="s">
         <v>78</v>
@@ -25150,7 +25149,7 @@
         <v>62</v>
       </c>
       <c r="K287" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L287" s="50" t="s">
         <v>1</v>
@@ -25212,7 +25211,7 @@
         <v>330056</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E288" s="50">
         <v>54</v>
@@ -25221,10 +25220,10 @@
         <v>0</v>
       </c>
       <c r="G288" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H288" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I288" s="50" t="s">
         <v>78</v>
@@ -25233,7 +25232,7 @@
         <v>62</v>
       </c>
       <c r="K288" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L288" s="50" t="s">
         <v>1</v>
@@ -25295,7 +25294,7 @@
         <v>330058</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E289" s="50">
         <v>5</v>
@@ -25304,10 +25303,10 @@
         <v>1</v>
       </c>
       <c r="G289" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H289" s="50" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I289" s="50" t="s">
         <v>78</v>
@@ -25316,7 +25315,7 @@
         <v>62</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -25378,7 +25377,7 @@
         <v>330061</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E290" s="50">
         <v>39</v>
@@ -25390,7 +25389,7 @@
         <v>60</v>
       </c>
       <c r="H290" s="50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I290" s="50" t="s">
         <v>78</v>
@@ -25399,7 +25398,7 @@
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -25461,7 +25460,7 @@
         <v>330062</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E291" s="50">
         <v>40</v>
@@ -25473,7 +25472,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="50" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>78</v>
@@ -25482,7 +25481,7 @@
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L291" s="50" t="s">
         <v>1</v>
@@ -25544,7 +25543,7 @@
         <v>330063</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E292" s="50">
         <v>28</v>
@@ -25556,7 +25555,7 @@
         <v>60</v>
       </c>
       <c r="H292" s="50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I292" s="50" t="s">
         <v>78</v>
@@ -25627,7 +25626,7 @@
         <v>330064</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E293" s="50">
         <v>29</v>
@@ -25636,10 +25635,10 @@
         <v>0</v>
       </c>
       <c r="G293" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H293" s="50" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="I293" s="50" t="s">
         <v>78</v>
@@ -25648,7 +25647,7 @@
         <v>62</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L293" s="50" t="s">
         <v>1</v>
@@ -25710,7 +25709,7 @@
         <v>330065</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E294" s="50">
         <v>5</v>
@@ -25722,7 +25721,7 @@
         <v>60</v>
       </c>
       <c r="H294" s="50" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I294" s="50" t="s">
         <v>78</v>
@@ -25731,7 +25730,7 @@
         <v>62</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L294" s="50" t="s">
         <v>1</v>
@@ -25793,7 +25792,7 @@
         <v>330067</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E295" s="50">
         <v>4</v>
@@ -25805,7 +25804,7 @@
         <v>60</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>78</v>
@@ -25814,7 +25813,7 @@
         <v>62</v>
       </c>
       <c r="K295" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L295" s="50" t="s">
         <v>1</v>
@@ -25876,7 +25875,7 @@
         <v>330068</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E296" s="50">
         <v>5</v>
@@ -25885,10 +25884,10 @@
         <v>1</v>
       </c>
       <c r="G296" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>78</v>
@@ -25897,7 +25896,7 @@
         <v>62</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L296" s="50" t="s">
         <v>1</v>
@@ -25959,7 +25958,7 @@
         <v>330069</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E297" s="50">
         <v>16</v>
@@ -25971,7 +25970,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -25980,10 +25979,10 @@
         <v>62</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L297" s="50" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M297" s="50" t="s">
         <v>1</v>
@@ -26040,7 +26039,7 @@
         <v>330070</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E298" s="50">
         <v>3</v>
@@ -26052,7 +26051,7 @@
         <v>60</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>
@@ -26061,7 +26060,7 @@
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L298" s="50" t="s">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1288,61 +1288,58 @@
     <t>48,5.9997,84</t>
   </si>
   <si>
-    <t>110,7.999978,54</t>
-  </si>
-  <si>
-    <t>115,8.002208,66</t>
-  </si>
-  <si>
-    <t>112.75,8,68.25_112.75,8,63.75_117.25,8,63.75_117.25,8,68.25</t>
+    <t>110,7.999978,48</t>
+  </si>
+  <si>
+    <t>115,8.002977,58.2436180114746</t>
+  </si>
+  <si>
+    <t>112.75,8,60.49362_112.75,8,55.99362_117.25,8,55.99362_117.25,8,60.49362</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>130,8.002208,66</t>
-  </si>
-  <si>
-    <t>128.5,8,64_131.5,8,64_131.5,8,68_128.5,8,68</t>
+    <t>132,8.003199,59</t>
+  </si>
+  <si>
+    <t>130.5,8,57_133.5,8,57_133.5,8,61_130.5,8,61</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
   </si>
   <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>117,8.003199,86</t>
-  </si>
-  <si>
-    <t>118,8,85_118,8,87_116,8,87_116,8,85</t>
+    <t>117,8.003199,79.8584136962891</t>
+  </si>
+  <si>
+    <t>118,8,78.85841_118,8,80.85841_116,8,80.85841_116,8,78.85841</t>
   </si>
   <si>
     <t>74857</t>
   </si>
   <si>
-    <t>119,8.003199,86</t>
-  </si>
-  <si>
-    <t>120,8,85_120,8,87_118,8,87_118,8,85</t>
-  </si>
-  <si>
-    <t>121,8.003199,86</t>
-  </si>
-  <si>
-    <t>122,8,85_122,8,87_120,8,87_120,8,85</t>
-  </si>
-  <si>
-    <t>129.307510375977,7.999978,74.7048797607422</t>
-  </si>
-  <si>
-    <t>117.00,0.00,77.00,145.00,0.00,77.00,145.00,0.00,55.00,117.00,0.00,55.00</t>
-  </si>
-  <si>
-    <t>97,7.999978,86.1221466064453</t>
-  </si>
-  <si>
-    <t>98.5,8,87.62215_95.5,8,87.62215_95.5,8,84.62215_98.5,8,84.62215</t>
+    <t>119,8.003199,79.8584136962891</t>
+  </si>
+  <si>
+    <t>120,8,78.85841_120,8,80.85841_118,8,80.85841_118,8,78.85841</t>
+  </si>
+  <si>
+    <t>121,8.003199,79.8584136962891</t>
+  </si>
+  <si>
+    <t>122,8,78.85841_122,8,80.85841_120,8,80.85841_120,8,78.85841</t>
+  </si>
+  <si>
+    <t>129.307510375977,7.999978,66.7048797607422</t>
+  </si>
+  <si>
+    <t>117.00,0.00,69.00,145.00,0.00,69.00,145.00,0.00,47.00,117.00,0.00,47.00</t>
+  </si>
+  <si>
+    <t>97,7.999978,77</t>
+  </si>
+  <si>
+    <t>98.5,8,78.5_95.5,8,78.5_95.5,8,75.5_98.5,8,75.5</t>
   </si>
   <si>
     <t>74864</t>
@@ -1351,52 +1348,52 @@
     <t>74865</t>
   </si>
   <si>
-    <t>130,7.999978,86</t>
-  </si>
-  <si>
-    <t>131.5,8,87.5_128.5,8,87.5_128.5,8,84.5_131.5,8,84.5</t>
-  </si>
-  <si>
-    <t>104,7.999978,93</t>
-  </si>
-  <si>
-    <t>106,8,94_102,8,94_102,8,92_106,8,92</t>
+    <t>130,7.999978,80</t>
+  </si>
+  <si>
+    <t>131.5,8,81.5_128.5,8,81.5_128.5,8,78.5_131.5,8,78.5</t>
+  </si>
+  <si>
+    <t>104,7.999978,85</t>
+  </si>
+  <si>
+    <t>106,8,86_102,8,86_102,8,84_106,8,84</t>
   </si>
   <si>
     <t>74863</t>
   </si>
   <si>
-    <t>81,7.999978,98</t>
-  </si>
-  <si>
-    <t>82.5,8,96_82.5,8,100_79.5,8,100_79.5,8,96</t>
-  </si>
-  <si>
-    <t>87.1449661254883,7.999978,117.04264831543</t>
-  </si>
-  <si>
-    <t>87.14,0.00,117.04,113.00,0.00,117.04,113.00,0.00,94.90,87.14,0.00,94.90</t>
-  </si>
-  <si>
-    <t>58,7.999978,104</t>
-  </si>
-  <si>
-    <t>60.25,8,105.5_55.75,8,105.5_55.75,8,102.5_60.25,8,102.5</t>
+    <t>81,7.999978,90</t>
+  </si>
+  <si>
+    <t>82.5,8,88_82.5,8,92_79.5,8,92_79.5,8,88</t>
+  </si>
+  <si>
+    <t>87.1449661254883,1.861901,110.072158813477</t>
+  </si>
+  <si>
+    <t>87.14,0.00,110.07,113.00,0.00,110.07,113.00,0.00,87.93,87.14,0.00,87.93</t>
+  </si>
+  <si>
+    <t>58,7.999978,95</t>
+  </si>
+  <si>
+    <t>60.25,8,96.5_55.75,8,96.5_55.75,8,93.5_60.25,8,93.5</t>
   </si>
   <si>
     <t>70308</t>
   </si>
   <si>
-    <t>57.7461738586426,7.999978,97</t>
-  </si>
-  <si>
-    <t>59.74617,8,98.5_55.74617,8,98.5_55.74617,8,95.5_59.74617,8,95.5</t>
-  </si>
-  <si>
-    <t>63,9.211463,84</t>
-  </si>
-  <si>
-    <t>62,8,86_62,8,82_64,8,82_64,8,86</t>
+    <t>57.7461738586426,7.999978,89</t>
+  </si>
+  <si>
+    <t>59.74617,8,90.5_55.74617,8,90.5_55.74617,8,87.5_59.74617,8,87.5</t>
+  </si>
+  <si>
+    <t>63,9.211463,76</t>
+  </si>
+  <si>
+    <t>62,8,78_62,8,74_64,8,74_64,8,78</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1405,19 +1402,19 @@
     <t>74871</t>
   </si>
   <si>
-    <t>98,7.999978,69</t>
-  </si>
-  <si>
-    <t>99,9.000299,70_97,9.000299,70_97,9.000299,68_99,9.000299,68</t>
+    <t>98,7.999978,62</t>
+  </si>
+  <si>
+    <t>99,9.000299,63_97,9.000299,63_97,9.000299,61_99,9.000299,61</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
-    <t>90,7.999978,70</t>
-  </si>
-  <si>
-    <t>87.75,8,72.25_87.75,8,67.75_92.25,8,67.75_92.25,8,72.25</t>
+    <t>91,7.999978,62</t>
+  </si>
+  <si>
+    <t>88.75,8,64.25_88.75,8,59.75_93.25,8,59.75_93.25,8,64.25</t>
   </si>
   <si>
     <t>74876</t>
@@ -1426,34 +1423,34 @@
     <t>70301</t>
   </si>
   <si>
-    <t>58,7.999978,77</t>
-  </si>
-  <si>
-    <t>60.25,7.999999,79.25_55.75,7.999999,79.25_55.75,7.999999,74.75_60.25,7.999999,74.75</t>
+    <t>58,7.999978,69</t>
+  </si>
+  <si>
+    <t>60.25,7.999999,71.25_55.75,7.999999,71.25_55.75,7.999999,66.75_60.25,7.999999,66.75</t>
   </si>
   <si>
     <t>70302</t>
   </si>
   <si>
-    <t>111,8.003199,124</t>
-  </si>
-  <si>
-    <t>116,7.999999,126_109,7.999999,126_109,7.999999,122_116,7.999999,122</t>
+    <t>109.408554077148,8.003199,121</t>
+  </si>
+  <si>
+    <t>114.4086,7.999999,123_107.4086,7.999999,123_107.4086,7.999999,119_114.4086,7.999999,119</t>
   </si>
   <si>
     <t>74875</t>
   </si>
   <si>
-    <t>58,7.999978,70</t>
-  </si>
-  <si>
-    <t>59,7.999999,71_57,7.999999,71_57,7.999999,69_59,7.999999,69</t>
-  </si>
-  <si>
-    <t>58,7.999978,56.6089134216309</t>
-  </si>
-  <si>
-    <t>59.5,8,54.60891_59.5,8,58.60891_56.5,8,58.60891_56.5,8,54.60891</t>
+    <t>58,7.999978,62</t>
+  </si>
+  <si>
+    <t>59,7.999999,63_57,7.999999,63_57,7.999999,61_59,7.999999,61</t>
+  </si>
+  <si>
+    <t>58,7.999978,48</t>
+  </si>
+  <si>
+    <t>59.5,8,46_59.5,8,50_56.5,8,50_56.5,8,46</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -17851,7 +17848,7 @@
         <v>1</v>
       </c>
       <c r="X194" s="50" t="s">
-        <v>430</v>
+        <v>64</v>
       </c>
       <c r="Y194" s="50" t="s">
         <v>1</v>
@@ -17874,7 +17871,7 @@
         <v>74858</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E195" s="50">
         <v>7</v>
@@ -17886,7 +17883,7 @@
         <v>138</v>
       </c>
       <c r="H195" s="50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I195" s="50" t="s">
         <v>78</v>
@@ -17898,7 +17895,7 @@
         <v>147</v>
       </c>
       <c r="L195" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M195" s="50" t="s">
         <v>1</v>
@@ -17955,7 +17952,7 @@
         <v>74859</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E196" s="50">
         <v>7</v>
@@ -17967,7 +17964,7 @@
         <v>138</v>
       </c>
       <c r="H196" s="50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I196" s="50" t="s">
         <v>78</v>
@@ -17979,7 +17976,7 @@
         <v>147</v>
       </c>
       <c r="L196" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M196" s="50" t="s">
         <v>1</v>
@@ -18036,7 +18033,7 @@
         <v>74860</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E197" s="50">
         <v>7</v>
@@ -18048,7 +18045,7 @@
         <v>138</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I197" s="50" t="s">
         <v>78</v>
@@ -18060,7 +18057,7 @@
         <v>147</v>
       </c>
       <c r="L197" s="50" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M197" s="50" t="s">
         <v>1</v>
@@ -18117,7 +18114,7 @@
         <v>74862</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E198" s="50">
         <v>2</v>
@@ -18142,7 +18139,7 @@
       </c>
       <c r="O198" s="50"/>
       <c r="P198" s="50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q198" s="50"/>
       <c r="R198" s="50"/>
@@ -18171,7 +18168,7 @@
         <v>74863</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E199" s="50">
         <v>20</v>
@@ -18183,7 +18180,7 @@
         <v>60</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I199" s="50" t="s">
         <v>78</v>
@@ -18195,10 +18192,10 @@
         <v>233</v>
       </c>
       <c r="L199" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="M199" s="50" t="s">
         <v>442</v>
-      </c>
-      <c r="M199" s="50" t="s">
-        <v>443</v>
       </c>
       <c r="N199" s="50">
         <v>7</v>
@@ -18252,7 +18249,7 @@
         <v>74864</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E200" s="50">
         <v>19</v>
@@ -18264,7 +18261,7 @@
         <v>60</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I200" s="50" t="s">
         <v>78</v>
@@ -18333,7 +18330,7 @@
         <v>74865</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E201" s="50">
         <v>16</v>
@@ -18345,7 +18342,7 @@
         <v>60</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I201" s="50" t="s">
         <v>78</v>
@@ -18357,7 +18354,7 @@
         <v>192</v>
       </c>
       <c r="L201" s="50" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M201" s="50" t="s">
         <v>1</v>
@@ -18414,7 +18411,7 @@
         <v>74866</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E202" s="50">
         <v>4</v>
@@ -18426,7 +18423,7 @@
         <v>138</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>78</v>
@@ -18497,7 +18494,7 @@
         <v>74867</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E203" s="50">
         <v>2</v>
@@ -18524,7 +18521,7 @@
       </c>
       <c r="O203" s="50"/>
       <c r="P203" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q203" s="50"/>
       <c r="R203" s="50"/>
@@ -18553,7 +18550,7 @@
         <v>74868</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E204" s="50">
         <v>5</v>
@@ -18565,7 +18562,7 @@
         <v>60</v>
       </c>
       <c r="H204" s="50" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I204" s="50" t="s">
         <v>78</v>
@@ -18601,7 +18598,7 @@
         <v>0</v>
       </c>
       <c r="T204" s="50" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="U204" s="50">
         <v>1</v>
@@ -18636,7 +18633,7 @@
         <v>74869</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E205" s="50">
         <v>4</v>
@@ -18648,7 +18645,7 @@
         <v>60</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -18719,7 +18716,7 @@
         <v>74870</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E206" s="50">
         <v>16</v>
@@ -18731,7 +18728,7 @@
         <v>83</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I206" s="50" t="s">
         <v>78</v>
@@ -18740,10 +18737,10 @@
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="L206" s="50" t="s">
         <v>460</v>
-      </c>
-      <c r="L206" s="50" t="s">
-        <v>461</v>
       </c>
       <c r="M206" s="50" t="s">
         <v>1</v>
@@ -18800,7 +18797,7 @@
         <v>74871</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E207" s="50">
         <v>3</v>
@@ -18812,7 +18809,7 @@
         <v>60</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -18821,7 +18818,7 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L207" s="50" t="s">
         <v>1</v>
@@ -18881,7 +18878,7 @@
         <v>74872</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E208" s="50">
         <v>5</v>
@@ -18893,7 +18890,7 @@
         <v>83</v>
       </c>
       <c r="H208" s="50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I208" s="50" t="s">
         <v>78</v>
@@ -18905,7 +18902,7 @@
         <v>297</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M208" s="50" t="s">
         <v>1</v>
@@ -18929,7 +18926,7 @@
         <v>0</v>
       </c>
       <c r="T208" s="50" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="U208" s="50">
         <v>0</v>
@@ -18964,7 +18961,7 @@
         <v>74873</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E209" s="50">
         <v>5</v>
@@ -18976,7 +18973,7 @@
         <v>60</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -19012,7 +19009,7 @@
         <v>0</v>
       </c>
       <c r="T209" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="U209" s="50">
         <v>0</v>
@@ -19047,7 +19044,7 @@
         <v>74874</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E210" s="50">
         <v>43</v>
@@ -19059,7 +19056,7 @@
         <v>60</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -19071,7 +19068,7 @@
         <v>100</v>
       </c>
       <c r="L210" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M210" s="50" t="s">
         <v>1</v>
@@ -19128,7 +19125,7 @@
         <v>74875</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E211" s="50">
         <v>44</v>
@@ -19140,7 +19137,7 @@
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19209,7 +19206,7 @@
         <v>74876</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E212" s="50">
         <v>4</v>
@@ -19221,7 +19218,7 @@
         <v>138</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19292,7 +19289,7 @@
         <v>84928</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E213" s="50">
         <v>12</v>
@@ -19372,7 +19369,7 @@
         <v>84929</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E214" s="50">
         <v>30</v>
@@ -19384,7 +19381,7 @@
         <v>83</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19396,7 +19393,7 @@
         <v>377</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M214" s="50" t="s">
         <v>1</v>
@@ -19453,7 +19450,7 @@
         <v>84930</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E215" s="50">
         <v>57</v>
@@ -19474,10 +19471,10 @@
         <v>388</v>
       </c>
       <c r="L215" s="50" t="s">
+        <v>483</v>
+      </c>
+      <c r="M215" s="50" t="s">
         <v>484</v>
-      </c>
-      <c r="M215" s="50" t="s">
-        <v>485</v>
       </c>
       <c r="N215" s="50">
         <v>8</v>
@@ -19531,7 +19528,7 @@
         <v>84931</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E216" s="50">
         <v>32</v>
@@ -19543,7 +19540,7 @@
         <v>138</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -19612,7 +19609,7 @@
         <v>84932</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E217" s="50">
         <v>57</v>
@@ -19633,10 +19630,10 @@
         <v>388</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N217" s="50">
         <v>8</v>
@@ -19690,7 +19687,7 @@
         <v>84933</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E218" s="50">
         <v>32</v>
@@ -19702,7 +19699,7 @@
         <v>60</v>
       </c>
       <c r="H218" s="50" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I218" s="50" t="s">
         <v>78</v>
@@ -19771,7 +19768,7 @@
         <v>84934</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E219" s="50">
         <v>31</v>
@@ -19783,7 +19780,7 @@
         <v>138</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>78</v>
@@ -19852,7 +19849,7 @@
         <v>84935</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E220" s="50">
         <v>31</v>
@@ -19864,7 +19861,7 @@
         <v>60</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>78</v>
@@ -19933,7 +19930,7 @@
         <v>84936</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E221" s="50">
         <v>31</v>
@@ -19945,7 +19942,7 @@
         <v>60</v>
       </c>
       <c r="H221" s="50" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I221" s="50" t="s">
         <v>78</v>
@@ -20014,7 +20011,7 @@
         <v>84937</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E222" s="50">
         <v>31</v>
@@ -20026,7 +20023,7 @@
         <v>138</v>
       </c>
       <c r="H222" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I222" s="50" t="s">
         <v>78</v>
@@ -20095,7 +20092,7 @@
         <v>84938</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E223" s="50">
         <v>31</v>
@@ -20107,7 +20104,7 @@
         <v>60</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>78</v>
@@ -20176,7 +20173,7 @@
         <v>84939</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E224" s="50">
         <v>15</v>
@@ -20188,7 +20185,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20257,7 +20254,7 @@
         <v>84940</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E225" s="50">
         <v>15</v>
@@ -20269,7 +20266,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20338,7 +20335,7 @@
         <v>84941</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E226" s="50">
         <v>16</v>
@@ -20350,7 +20347,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20362,7 +20359,7 @@
         <v>192</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M226" s="50" t="s">
         <v>1</v>
@@ -20419,7 +20416,7 @@
         <v>84942</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E227" s="50">
         <v>52</v>
@@ -20440,10 +20437,10 @@
         <v>285</v>
       </c>
       <c r="L227" s="50" t="s">
+        <v>509</v>
+      </c>
+      <c r="M227" s="50" t="s">
         <v>510</v>
-      </c>
-      <c r="M227" s="50" t="s">
-        <v>511</v>
       </c>
       <c r="N227" s="50">
         <v>8</v>
@@ -20497,7 +20494,7 @@
         <v>84943</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E228" s="50">
         <v>51</v>
@@ -20509,7 +20506,7 @@
         <v>60</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>78</v>
@@ -20578,7 +20575,7 @@
         <v>84944</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E229" s="50">
         <v>52</v>
@@ -20599,10 +20596,10 @@
         <v>271</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N229" s="50">
         <v>8</v>
@@ -20656,7 +20653,7 @@
         <v>84945</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E230" s="50">
         <v>51</v>
@@ -20668,7 +20665,7 @@
         <v>60</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I230" s="50" t="s">
         <v>78</v>
@@ -20737,7 +20734,7 @@
         <v>84946</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E231" s="50">
         <v>56</v>
@@ -20755,7 +20752,7 @@
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -20815,7 +20812,7 @@
         <v>84947</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E232" s="50">
         <v>56</v>
@@ -20893,7 +20890,7 @@
         <v>84948</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E233" s="50">
         <v>56</v>
@@ -20971,7 +20968,7 @@
         <v>84949</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E234" s="50">
         <v>56</v>
@@ -21049,7 +21046,7 @@
         <v>84950</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E235" s="50">
         <v>56</v>
@@ -21127,7 +21124,7 @@
         <v>84951</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E236" s="50">
         <v>56</v>
@@ -21205,7 +21202,7 @@
         <v>84952</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E237" s="50">
         <v>56</v>
@@ -21283,7 +21280,7 @@
         <v>84953</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E238" s="50">
         <v>56</v>
@@ -21361,7 +21358,7 @@
         <v>84954</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E239" s="50">
         <v>56</v>
@@ -21439,7 +21436,7 @@
         <v>84955</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E240" s="50">
         <v>56</v>
@@ -21517,7 +21514,7 @@
         <v>84956</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E241" s="50">
         <v>56</v>
@@ -21595,7 +21592,7 @@
         <v>84957</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E242" s="50">
         <v>56</v>
@@ -21673,7 +21670,7 @@
         <v>84958</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E243" s="50">
         <v>56</v>
@@ -21751,7 +21748,7 @@
         <v>84959</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E244" s="50">
         <v>56</v>
@@ -21829,7 +21826,7 @@
         <v>84960</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E245" s="50">
         <v>56</v>
@@ -21907,7 +21904,7 @@
         <v>84961</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E246" s="50">
         <v>56</v>
@@ -21985,7 +21982,7 @@
         <v>84962</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E247" s="50">
         <v>56</v>
@@ -22063,7 +22060,7 @@
         <v>84963</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E248" s="50">
         <v>56</v>
@@ -22141,7 +22138,7 @@
         <v>84964</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E249" s="50">
         <v>56</v>
@@ -22219,7 +22216,7 @@
         <v>84965</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E250" s="50">
         <v>56</v>
@@ -22297,7 +22294,7 @@
         <v>84966</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E251" s="50">
         <v>56</v>
@@ -22375,7 +22372,7 @@
         <v>84967</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E252" s="50">
         <v>56</v>
@@ -22453,7 +22450,7 @@
         <v>84968</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E253" s="50">
         <v>56</v>
@@ -22531,7 +22528,7 @@
         <v>84969</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E254" s="50">
         <v>45</v>
@@ -22543,7 +22540,7 @@
         <v>83</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -22552,7 +22549,7 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -22612,7 +22609,7 @@
         <v>84970</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E255" s="50">
         <v>46</v>
@@ -22621,10 +22618,10 @@
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="H255" s="50" t="s">
         <v>546</v>
-      </c>
-      <c r="H255" s="50" t="s">
-        <v>547</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22633,7 +22630,7 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L255" s="50" t="s">
         <v>1</v>
@@ -22693,7 +22690,7 @@
         <v>84971</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E256" s="50">
         <v>47</v>
@@ -22705,7 +22702,7 @@
         <v>94</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -22714,13 +22711,13 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
+        <v>550</v>
+      </c>
+      <c r="L256" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M256" s="50" t="s">
         <v>551</v>
-      </c>
-      <c r="L256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M256" s="50" t="s">
-        <v>552</v>
       </c>
       <c r="N256" s="50">
         <v>8</v>
@@ -22774,7 +22771,7 @@
         <v>84972</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E257" s="50">
         <v>46</v>
@@ -22783,10 +22780,10 @@
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
+        <v>553</v>
+      </c>
+      <c r="H257" s="50" t="s">
         <v>554</v>
-      </c>
-      <c r="H257" s="50" t="s">
-        <v>555</v>
       </c>
       <c r="I257" s="50" t="s">
         <v>78</v>
@@ -22795,7 +22792,7 @@
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
@@ -22855,7 +22852,7 @@
         <v>84973</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E258" s="50">
         <v>16</v>
@@ -22867,7 +22864,7 @@
         <v>60</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -22879,7 +22876,7 @@
         <v>192</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -22936,7 +22933,7 @@
         <v>84974</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E259" s="50">
         <v>46</v>
@@ -22948,7 +22945,7 @@
         <v>60</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -22957,7 +22954,7 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L259" s="50" t="s">
         <v>1</v>
@@ -23017,7 +23014,7 @@
         <v>84976</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E260" s="50">
         <v>2</v>
@@ -23042,7 +23039,7 @@
       </c>
       <c r="O260" s="50"/>
       <c r="P260" s="50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Q260" s="50"/>
       <c r="R260" s="50"/>
@@ -23067,7 +23064,7 @@
         <v>84977</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E261" s="50">
         <v>2</v>
@@ -23092,7 +23089,7 @@
       </c>
       <c r="O261" s="50"/>
       <c r="P261" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Q261" s="50"/>
       <c r="R261" s="50"/>
@@ -23117,7 +23114,7 @@
         <v>84978</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E262" s="50">
         <v>2</v>
@@ -23142,7 +23139,7 @@
       </c>
       <c r="O262" s="50"/>
       <c r="P262" s="50" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q262" s="50"/>
       <c r="R262" s="50"/>
@@ -23167,7 +23164,7 @@
         <v>84979</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E263" s="50">
         <v>48</v>
@@ -23179,7 +23176,7 @@
         <v>83</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23191,10 +23188,10 @@
         <v>327</v>
       </c>
       <c r="L263" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="M263" s="50" t="s">
         <v>569</v>
-      </c>
-      <c r="M263" s="50" t="s">
-        <v>570</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23248,7 +23245,7 @@
         <v>84980</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E264" s="50">
         <v>49</v>
@@ -23260,7 +23257,7 @@
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23272,7 +23269,7 @@
         <v>324</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
@@ -23329,7 +23326,7 @@
         <v>84981</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E265" s="50">
         <v>50</v>
@@ -23341,7 +23338,7 @@
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23410,7 +23407,7 @@
         <v>84982</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E266" s="50">
         <v>23</v>
@@ -23428,13 +23425,13 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
+        <v>576</v>
+      </c>
+      <c r="L266" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M266" s="50" t="s">
         <v>577</v>
-      </c>
-      <c r="L266" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M266" s="50" t="s">
-        <v>578</v>
       </c>
       <c r="N266" s="50">
         <v>8</v>
@@ -23490,7 +23487,7 @@
         <v>84983</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E267" s="50">
         <v>24</v>
@@ -23502,7 +23499,7 @@
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23511,7 +23508,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23573,7 +23570,7 @@
         <v>84984</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E268" s="50">
         <v>25</v>
@@ -23585,7 +23582,7 @@
         <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23594,7 +23591,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23656,7 +23653,7 @@
         <v>330037</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E269" s="50">
         <v>5</v>
@@ -23668,7 +23665,7 @@
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -23739,7 +23736,7 @@
         <v>330038</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E270" s="50">
         <v>6</v>
@@ -23751,7 +23748,7 @@
         <v>94</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23766,7 +23763,7 @@
         <v>1</v>
       </c>
       <c r="M270" s="50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N270" s="50">
         <v>33</v>
@@ -23820,7 +23817,7 @@
         <v>330039</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E271" s="50">
         <v>7</v>
@@ -23832,7 +23829,7 @@
         <v>138</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -23844,7 +23841,7 @@
         <v>147</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M271" s="50" t="s">
         <v>1</v>
@@ -23901,7 +23898,7 @@
         <v>330040</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E272" s="50">
         <v>7</v>
@@ -23913,7 +23910,7 @@
         <v>138</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23925,7 +23922,7 @@
         <v>147</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -23982,7 +23979,7 @@
         <v>330041</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E273" s="50">
         <v>7</v>
@@ -23994,7 +23991,7 @@
         <v>138</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -24006,7 +24003,7 @@
         <v>147</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M273" s="50" t="s">
         <v>1</v>
@@ -24063,7 +24060,7 @@
         <v>330042</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E274" s="50">
         <v>20</v>
@@ -24075,7 +24072,7 @@
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24087,10 +24084,10 @@
         <v>233</v>
       </c>
       <c r="L274" s="50" t="s">
+        <v>597</v>
+      </c>
+      <c r="M274" s="50" t="s">
         <v>598</v>
-      </c>
-      <c r="M274" s="50" t="s">
-        <v>599</v>
       </c>
       <c r="N274" s="50">
         <v>33</v>
@@ -24144,7 +24141,7 @@
         <v>330043</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E275" s="50">
         <v>19</v>
@@ -24156,7 +24153,7 @@
         <v>60</v>
       </c>
       <c r="H275" s="50" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="I275" s="50" t="s">
         <v>78</v>
@@ -24225,7 +24222,7 @@
         <v>330044</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E276" s="50">
         <v>16</v>
@@ -24237,7 +24234,7 @@
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24249,7 +24246,7 @@
         <v>192</v>
       </c>
       <c r="L276" s="50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M276" s="50" t="s">
         <v>1</v>
@@ -24306,7 +24303,7 @@
         <v>330045</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E277" s="50">
         <v>5</v>
@@ -24318,7 +24315,7 @@
         <v>83</v>
       </c>
       <c r="H277" s="50" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>78</v>
@@ -24389,7 +24386,7 @@
         <v>330046</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E278" s="50">
         <v>16</v>
@@ -24401,7 +24398,7 @@
         <v>83</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24410,10 +24407,10 @@
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
@@ -24470,7 +24467,7 @@
         <v>330047</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E279" s="50">
         <v>3</v>
@@ -24482,7 +24479,7 @@
         <v>60</v>
       </c>
       <c r="H279" s="50" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>78</v>
@@ -24491,7 +24488,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24551,7 +24548,7 @@
         <v>330048</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E280" s="50">
         <v>5</v>
@@ -24563,7 +24560,7 @@
         <v>60</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>78</v>
@@ -24634,7 +24631,7 @@
         <v>330049</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E281" s="50">
         <v>43</v>
@@ -24646,7 +24643,7 @@
         <v>60</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>78</v>
@@ -24658,7 +24655,7 @@
         <v>100</v>
       </c>
       <c r="L281" s="50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M281" s="50" t="s">
         <v>1</v>
@@ -24715,7 +24712,7 @@
         <v>330050</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E282" s="50">
         <v>44</v>
@@ -24727,7 +24724,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="50" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I282" s="50" t="s">
         <v>78</v>
@@ -24796,7 +24793,7 @@
         <v>330051</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E283" s="50">
         <v>4</v>
@@ -24808,7 +24805,7 @@
         <v>138</v>
       </c>
       <c r="H283" s="50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I283" s="50" t="s">
         <v>78</v>
@@ -24879,7 +24876,7 @@
         <v>330052</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E284" s="50">
         <v>4</v>
@@ -24891,7 +24888,7 @@
         <v>138</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I284" s="50" t="s">
         <v>78</v>
@@ -24962,7 +24959,7 @@
         <v>330053</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E285" s="50">
         <v>4</v>
@@ -24974,7 +24971,7 @@
         <v>60</v>
       </c>
       <c r="H285" s="50" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I285" s="50" t="s">
         <v>78</v>
@@ -25045,7 +25042,7 @@
         <v>330054</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E286" s="50">
         <v>5</v>
@@ -25057,7 +25054,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="50" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I286" s="50" t="s">
         <v>78</v>
@@ -25128,7 +25125,7 @@
         <v>330055</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E287" s="50">
         <v>4</v>
@@ -25140,7 +25137,7 @@
         <v>83</v>
       </c>
       <c r="H287" s="50" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I287" s="50" t="s">
         <v>78</v>
@@ -25211,7 +25208,7 @@
         <v>330056</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E288" s="50">
         <v>54</v>
@@ -25223,7 +25220,7 @@
         <v>138</v>
       </c>
       <c r="H288" s="50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I288" s="50" t="s">
         <v>78</v>
@@ -25294,7 +25291,7 @@
         <v>330058</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E289" s="50">
         <v>5</v>
@@ -25306,7 +25303,7 @@
         <v>138</v>
       </c>
       <c r="H289" s="50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I289" s="50" t="s">
         <v>78</v>
@@ -25377,7 +25374,7 @@
         <v>330061</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E290" s="50">
         <v>39</v>
@@ -25389,7 +25386,7 @@
         <v>60</v>
       </c>
       <c r="H290" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I290" s="50" t="s">
         <v>78</v>
@@ -25398,7 +25395,7 @@
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -25460,7 +25457,7 @@
         <v>330062</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E291" s="50">
         <v>40</v>
@@ -25472,7 +25469,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>78</v>
@@ -25481,7 +25478,7 @@
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L291" s="50" t="s">
         <v>1</v>
@@ -25543,7 +25540,7 @@
         <v>330063</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E292" s="50">
         <v>28</v>
@@ -25555,7 +25552,7 @@
         <v>60</v>
       </c>
       <c r="H292" s="50" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I292" s="50" t="s">
         <v>78</v>
@@ -25626,7 +25623,7 @@
         <v>330064</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E293" s="50">
         <v>29</v>
@@ -25638,7 +25635,7 @@
         <v>138</v>
       </c>
       <c r="H293" s="50" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I293" s="50" t="s">
         <v>78</v>
@@ -25709,7 +25706,7 @@
         <v>330065</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E294" s="50">
         <v>5</v>
@@ -25721,7 +25718,7 @@
         <v>60</v>
       </c>
       <c r="H294" s="50" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I294" s="50" t="s">
         <v>78</v>
@@ -25792,7 +25789,7 @@
         <v>330067</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E295" s="50">
         <v>4</v>
@@ -25804,7 +25801,7 @@
         <v>60</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>78</v>
@@ -25875,7 +25872,7 @@
         <v>330068</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E296" s="50">
         <v>5</v>
@@ -25887,7 +25884,7 @@
         <v>138</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>78</v>
@@ -25958,7 +25955,7 @@
         <v>330069</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E297" s="50">
         <v>16</v>
@@ -25970,7 +25967,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -25982,7 +25979,7 @@
         <v>257</v>
       </c>
       <c r="L297" s="50" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="M297" s="50" t="s">
         <v>1</v>
@@ -26039,7 +26036,7 @@
         <v>330070</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E298" s="50">
         <v>3</v>
@@ -26051,7 +26048,7 @@
         <v>60</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1309,6 +1309,9 @@
     <t>74858,74859,74860</t>
   </si>
   <si>
+    <t>70001_0</t>
+  </si>
+  <si>
     <t>117,8.003199,79.8584136962891</t>
   </si>
   <si>
@@ -1361,6 +1364,9 @@
   </si>
   <si>
     <t>74863</t>
+  </si>
+  <si>
+    <t>70001_1</t>
   </si>
   <si>
     <t>81,7.999978,90</t>
@@ -17848,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="X194" s="50" t="s">
-        <v>64</v>
+        <v>430</v>
       </c>
       <c r="Y194" s="50" t="s">
         <v>1</v>
@@ -17871,7 +17877,7 @@
         <v>74858</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E195" s="50">
         <v>7</v>
@@ -17883,7 +17889,7 @@
         <v>138</v>
       </c>
       <c r="H195" s="50" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I195" s="50" t="s">
         <v>78</v>
@@ -17895,7 +17901,7 @@
         <v>147</v>
       </c>
       <c r="L195" s="50" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M195" s="50" t="s">
         <v>1</v>
@@ -17952,7 +17958,7 @@
         <v>74859</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E196" s="50">
         <v>7</v>
@@ -17964,7 +17970,7 @@
         <v>138</v>
       </c>
       <c r="H196" s="50" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I196" s="50" t="s">
         <v>78</v>
@@ -17976,7 +17982,7 @@
         <v>147</v>
       </c>
       <c r="L196" s="50" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M196" s="50" t="s">
         <v>1</v>
@@ -18033,7 +18039,7 @@
         <v>74860</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E197" s="50">
         <v>7</v>
@@ -18045,7 +18051,7 @@
         <v>138</v>
       </c>
       <c r="H197" s="50" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I197" s="50" t="s">
         <v>78</v>
@@ -18057,7 +18063,7 @@
         <v>147</v>
       </c>
       <c r="L197" s="50" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M197" s="50" t="s">
         <v>1</v>
@@ -18114,7 +18120,7 @@
         <v>74862</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E198" s="50">
         <v>2</v>
@@ -18139,7 +18145,7 @@
       </c>
       <c r="O198" s="50"/>
       <c r="P198" s="50" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q198" s="50"/>
       <c r="R198" s="50"/>
@@ -18148,7 +18154,7 @@
       <c r="U198" s="50"/>
       <c r="V198" s="50"/>
       <c r="W198" s="50" t="s">
-        <v>64</v>
+        <v>430</v>
       </c>
       <c r="X198" s="50"/>
       <c r="Y198" s="50"/>
@@ -18168,7 +18174,7 @@
         <v>74863</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E199" s="50">
         <v>20</v>
@@ -18180,7 +18186,7 @@
         <v>60</v>
       </c>
       <c r="H199" s="50" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I199" s="50" t="s">
         <v>78</v>
@@ -18192,10 +18198,10 @@
         <v>233</v>
       </c>
       <c r="L199" s="50" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M199" s="50" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N199" s="50">
         <v>7</v>
@@ -18249,7 +18255,7 @@
         <v>74864</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E200" s="50">
         <v>19</v>
@@ -18261,7 +18267,7 @@
         <v>60</v>
       </c>
       <c r="H200" s="50" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I200" s="50" t="s">
         <v>78</v>
@@ -18330,7 +18336,7 @@
         <v>74865</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E201" s="50">
         <v>16</v>
@@ -18342,7 +18348,7 @@
         <v>60</v>
       </c>
       <c r="H201" s="50" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I201" s="50" t="s">
         <v>78</v>
@@ -18354,7 +18360,7 @@
         <v>192</v>
       </c>
       <c r="L201" s="50" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M201" s="50" t="s">
         <v>1</v>
@@ -18388,7 +18394,7 @@
         <v>1</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>69</v>
+        <v>449</v>
       </c>
       <c r="Y201" s="50" t="s">
         <v>1</v>
@@ -18411,7 +18417,7 @@
         <v>74866</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E202" s="50">
         <v>4</v>
@@ -18423,7 +18429,7 @@
         <v>138</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>78</v>
@@ -18494,7 +18500,7 @@
         <v>74867</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E203" s="50">
         <v>2</v>
@@ -18521,7 +18527,7 @@
       </c>
       <c r="O203" s="50"/>
       <c r="P203" s="50" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q203" s="50"/>
       <c r="R203" s="50"/>
@@ -18530,7 +18536,7 @@
       <c r="U203" s="50"/>
       <c r="V203" s="50"/>
       <c r="W203" s="50" t="s">
-        <v>69</v>
+        <v>449</v>
       </c>
       <c r="X203" s="50"/>
       <c r="Y203" s="50"/>
@@ -18550,7 +18556,7 @@
         <v>74868</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E204" s="50">
         <v>5</v>
@@ -18562,7 +18568,7 @@
         <v>60</v>
       </c>
       <c r="H204" s="50" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I204" s="50" t="s">
         <v>78</v>
@@ -18598,7 +18604,7 @@
         <v>0</v>
       </c>
       <c r="T204" s="50" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="U204" s="50">
         <v>1</v>
@@ -18633,7 +18639,7 @@
         <v>74869</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E205" s="50">
         <v>4</v>
@@ -18645,7 +18651,7 @@
         <v>60</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -18716,7 +18722,7 @@
         <v>74870</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E206" s="50">
         <v>16</v>
@@ -18728,7 +18734,7 @@
         <v>83</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I206" s="50" t="s">
         <v>78</v>
@@ -18737,10 +18743,10 @@
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L206" s="50" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M206" s="50" t="s">
         <v>1</v>
@@ -18797,7 +18803,7 @@
         <v>74871</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E207" s="50">
         <v>3</v>
@@ -18809,7 +18815,7 @@
         <v>60</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -18818,7 +18824,7 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L207" s="50" t="s">
         <v>1</v>
@@ -18878,7 +18884,7 @@
         <v>74872</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E208" s="50">
         <v>5</v>
@@ -18890,7 +18896,7 @@
         <v>83</v>
       </c>
       <c r="H208" s="50" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I208" s="50" t="s">
         <v>78</v>
@@ -18902,7 +18908,7 @@
         <v>297</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M208" s="50" t="s">
         <v>1</v>
@@ -18926,7 +18932,7 @@
         <v>0</v>
       </c>
       <c r="T208" s="50" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="U208" s="50">
         <v>0</v>
@@ -18961,7 +18967,7 @@
         <v>74873</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E209" s="50">
         <v>5</v>
@@ -18973,7 +18979,7 @@
         <v>60</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -19009,7 +19015,7 @@
         <v>0</v>
       </c>
       <c r="T209" s="50" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="U209" s="50">
         <v>0</v>
@@ -19044,7 +19050,7 @@
         <v>74874</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E210" s="50">
         <v>43</v>
@@ -19056,7 +19062,7 @@
         <v>60</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -19068,7 +19074,7 @@
         <v>100</v>
       </c>
       <c r="L210" s="50" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M210" s="50" t="s">
         <v>1</v>
@@ -19125,7 +19131,7 @@
         <v>74875</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E211" s="50">
         <v>44</v>
@@ -19137,7 +19143,7 @@
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19206,7 +19212,7 @@
         <v>74876</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E212" s="50">
         <v>4</v>
@@ -19218,7 +19224,7 @@
         <v>138</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19289,7 +19295,7 @@
         <v>84928</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E213" s="50">
         <v>12</v>
@@ -19369,7 +19375,7 @@
         <v>84929</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E214" s="50">
         <v>30</v>
@@ -19381,7 +19387,7 @@
         <v>83</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19393,7 +19399,7 @@
         <v>377</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M214" s="50" t="s">
         <v>1</v>
@@ -19450,7 +19456,7 @@
         <v>84930</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E215" s="50">
         <v>57</v>
@@ -19471,10 +19477,10 @@
         <v>388</v>
       </c>
       <c r="L215" s="50" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M215" s="50" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N215" s="50">
         <v>8</v>
@@ -19528,7 +19534,7 @@
         <v>84931</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E216" s="50">
         <v>32</v>
@@ -19540,7 +19546,7 @@
         <v>138</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -19609,7 +19615,7 @@
         <v>84932</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E217" s="50">
         <v>57</v>
@@ -19630,10 +19636,10 @@
         <v>388</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N217" s="50">
         <v>8</v>
@@ -19687,7 +19693,7 @@
         <v>84933</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E218" s="50">
         <v>32</v>
@@ -19699,7 +19705,7 @@
         <v>60</v>
       </c>
       <c r="H218" s="50" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I218" s="50" t="s">
         <v>78</v>
@@ -19768,7 +19774,7 @@
         <v>84934</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E219" s="50">
         <v>31</v>
@@ -19780,7 +19786,7 @@
         <v>138</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>78</v>
@@ -19849,7 +19855,7 @@
         <v>84935</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E220" s="50">
         <v>31</v>
@@ -19861,7 +19867,7 @@
         <v>60</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>78</v>
@@ -19930,7 +19936,7 @@
         <v>84936</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E221" s="50">
         <v>31</v>
@@ -19942,7 +19948,7 @@
         <v>60</v>
       </c>
       <c r="H221" s="50" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I221" s="50" t="s">
         <v>78</v>
@@ -20011,7 +20017,7 @@
         <v>84937</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E222" s="50">
         <v>31</v>
@@ -20023,7 +20029,7 @@
         <v>138</v>
       </c>
       <c r="H222" s="50" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I222" s="50" t="s">
         <v>78</v>
@@ -20092,7 +20098,7 @@
         <v>84938</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E223" s="50">
         <v>31</v>
@@ -20104,7 +20110,7 @@
         <v>60</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>78</v>
@@ -20173,7 +20179,7 @@
         <v>84939</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E224" s="50">
         <v>15</v>
@@ -20185,7 +20191,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20254,7 +20260,7 @@
         <v>84940</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E225" s="50">
         <v>15</v>
@@ -20266,7 +20272,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20335,7 +20341,7 @@
         <v>84941</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E226" s="50">
         <v>16</v>
@@ -20347,7 +20353,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20359,7 +20365,7 @@
         <v>192</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M226" s="50" t="s">
         <v>1</v>
@@ -20416,7 +20422,7 @@
         <v>84942</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E227" s="50">
         <v>52</v>
@@ -20437,10 +20443,10 @@
         <v>285</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N227" s="50">
         <v>8</v>
@@ -20494,7 +20500,7 @@
         <v>84943</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E228" s="50">
         <v>51</v>
@@ -20506,7 +20512,7 @@
         <v>60</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>78</v>
@@ -20575,7 +20581,7 @@
         <v>84944</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E229" s="50">
         <v>52</v>
@@ -20596,10 +20602,10 @@
         <v>271</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N229" s="50">
         <v>8</v>
@@ -20653,7 +20659,7 @@
         <v>84945</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E230" s="50">
         <v>51</v>
@@ -20665,7 +20671,7 @@
         <v>60</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I230" s="50" t="s">
         <v>78</v>
@@ -20734,7 +20740,7 @@
         <v>84946</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E231" s="50">
         <v>56</v>
@@ -20752,7 +20758,7 @@
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -20812,7 +20818,7 @@
         <v>84947</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E232" s="50">
         <v>56</v>
@@ -20890,7 +20896,7 @@
         <v>84948</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E233" s="50">
         <v>56</v>
@@ -20968,7 +20974,7 @@
         <v>84949</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E234" s="50">
         <v>56</v>
@@ -21046,7 +21052,7 @@
         <v>84950</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E235" s="50">
         <v>56</v>
@@ -21124,7 +21130,7 @@
         <v>84951</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E236" s="50">
         <v>56</v>
@@ -21202,7 +21208,7 @@
         <v>84952</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E237" s="50">
         <v>56</v>
@@ -21280,7 +21286,7 @@
         <v>84953</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E238" s="50">
         <v>56</v>
@@ -21358,7 +21364,7 @@
         <v>84954</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E239" s="50">
         <v>56</v>
@@ -21436,7 +21442,7 @@
         <v>84955</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E240" s="50">
         <v>56</v>
@@ -21514,7 +21520,7 @@
         <v>84956</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E241" s="50">
         <v>56</v>
@@ -21592,7 +21598,7 @@
         <v>84957</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E242" s="50">
         <v>56</v>
@@ -21670,7 +21676,7 @@
         <v>84958</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E243" s="50">
         <v>56</v>
@@ -21748,7 +21754,7 @@
         <v>84959</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E244" s="50">
         <v>56</v>
@@ -21826,7 +21832,7 @@
         <v>84960</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E245" s="50">
         <v>56</v>
@@ -21904,7 +21910,7 @@
         <v>84961</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E246" s="50">
         <v>56</v>
@@ -21982,7 +21988,7 @@
         <v>84962</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E247" s="50">
         <v>56</v>
@@ -22060,7 +22066,7 @@
         <v>84963</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E248" s="50">
         <v>56</v>
@@ -22138,7 +22144,7 @@
         <v>84964</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E249" s="50">
         <v>56</v>
@@ -22216,7 +22222,7 @@
         <v>84965</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E250" s="50">
         <v>56</v>
@@ -22294,7 +22300,7 @@
         <v>84966</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E251" s="50">
         <v>56</v>
@@ -22372,7 +22378,7 @@
         <v>84967</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E252" s="50">
         <v>56</v>
@@ -22450,7 +22456,7 @@
         <v>84968</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E253" s="50">
         <v>56</v>
@@ -22528,7 +22534,7 @@
         <v>84969</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E254" s="50">
         <v>45</v>
@@ -22540,7 +22546,7 @@
         <v>83</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -22549,7 +22555,7 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -22609,7 +22615,7 @@
         <v>84970</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E255" s="50">
         <v>46</v>
@@ -22618,10 +22624,10 @@
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H255" s="50" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22630,7 +22636,7 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L255" s="50" t="s">
         <v>1</v>
@@ -22690,7 +22696,7 @@
         <v>84971</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E256" s="50">
         <v>47</v>
@@ -22702,7 +22708,7 @@
         <v>94</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -22711,13 +22717,13 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L256" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M256" s="50" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N256" s="50">
         <v>8</v>
@@ -22771,7 +22777,7 @@
         <v>84972</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E257" s="50">
         <v>46</v>
@@ -22780,10 +22786,10 @@
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H257" s="50" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I257" s="50" t="s">
         <v>78</v>
@@ -22792,7 +22798,7 @@
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
@@ -22852,7 +22858,7 @@
         <v>84973</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E258" s="50">
         <v>16</v>
@@ -22864,7 +22870,7 @@
         <v>60</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -22876,7 +22882,7 @@
         <v>192</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -22933,7 +22939,7 @@
         <v>84974</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E259" s="50">
         <v>46</v>
@@ -22945,7 +22951,7 @@
         <v>60</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -22954,7 +22960,7 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L259" s="50" t="s">
         <v>1</v>
@@ -23014,7 +23020,7 @@
         <v>84976</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E260" s="50">
         <v>2</v>
@@ -23039,7 +23045,7 @@
       </c>
       <c r="O260" s="50"/>
       <c r="P260" s="50" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="Q260" s="50"/>
       <c r="R260" s="50"/>
@@ -23064,7 +23070,7 @@
         <v>84977</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E261" s="50">
         <v>2</v>
@@ -23089,7 +23095,7 @@
       </c>
       <c r="O261" s="50"/>
       <c r="P261" s="50" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="Q261" s="50"/>
       <c r="R261" s="50"/>
@@ -23114,7 +23120,7 @@
         <v>84978</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E262" s="50">
         <v>2</v>
@@ -23139,7 +23145,7 @@
       </c>
       <c r="O262" s="50"/>
       <c r="P262" s="50" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="Q262" s="50"/>
       <c r="R262" s="50"/>
@@ -23164,7 +23170,7 @@
         <v>84979</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E263" s="50">
         <v>48</v>
@@ -23176,7 +23182,7 @@
         <v>83</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23188,10 +23194,10 @@
         <v>327</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23245,7 +23251,7 @@
         <v>84980</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E264" s="50">
         <v>49</v>
@@ -23257,7 +23263,7 @@
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23269,7 +23275,7 @@
         <v>324</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
@@ -23326,7 +23332,7 @@
         <v>84981</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E265" s="50">
         <v>50</v>
@@ -23338,7 +23344,7 @@
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23407,7 +23413,7 @@
         <v>84982</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E266" s="50">
         <v>23</v>
@@ -23425,13 +23431,13 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M266" s="50" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N266" s="50">
         <v>8</v>
@@ -23487,7 +23493,7 @@
         <v>84983</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E267" s="50">
         <v>24</v>
@@ -23499,7 +23505,7 @@
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23508,7 +23514,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23570,7 +23576,7 @@
         <v>84984</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E268" s="50">
         <v>25</v>
@@ -23582,7 +23588,7 @@
         <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23591,7 +23597,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23653,7 +23659,7 @@
         <v>330037</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E269" s="50">
         <v>5</v>
@@ -23665,7 +23671,7 @@
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -23736,7 +23742,7 @@
         <v>330038</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E270" s="50">
         <v>6</v>
@@ -23748,7 +23754,7 @@
         <v>94</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23763,7 +23769,7 @@
         <v>1</v>
       </c>
       <c r="M270" s="50" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N270" s="50">
         <v>33</v>
@@ -23817,7 +23823,7 @@
         <v>330039</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E271" s="50">
         <v>7</v>
@@ -23829,7 +23835,7 @@
         <v>138</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -23841,7 +23847,7 @@
         <v>147</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M271" s="50" t="s">
         <v>1</v>
@@ -23898,7 +23904,7 @@
         <v>330040</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E272" s="50">
         <v>7</v>
@@ -23910,7 +23916,7 @@
         <v>138</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23922,7 +23928,7 @@
         <v>147</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -23979,7 +23985,7 @@
         <v>330041</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E273" s="50">
         <v>7</v>
@@ -23991,7 +23997,7 @@
         <v>138</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -24003,7 +24009,7 @@
         <v>147</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M273" s="50" t="s">
         <v>1</v>
@@ -24060,7 +24066,7 @@
         <v>330042</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E274" s="50">
         <v>20</v>
@@ -24072,7 +24078,7 @@
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24084,10 +24090,10 @@
         <v>233</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M274" s="50" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N274" s="50">
         <v>33</v>
@@ -24141,7 +24147,7 @@
         <v>330043</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E275" s="50">
         <v>19</v>
@@ -24153,7 +24159,7 @@
         <v>60</v>
       </c>
       <c r="H275" s="50" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I275" s="50" t="s">
         <v>78</v>
@@ -24222,7 +24228,7 @@
         <v>330044</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E276" s="50">
         <v>16</v>
@@ -24234,7 +24240,7 @@
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24246,7 +24252,7 @@
         <v>192</v>
       </c>
       <c r="L276" s="50" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M276" s="50" t="s">
         <v>1</v>
@@ -24303,7 +24309,7 @@
         <v>330045</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E277" s="50">
         <v>5</v>
@@ -24315,7 +24321,7 @@
         <v>83</v>
       </c>
       <c r="H277" s="50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I277" s="50" t="s">
         <v>78</v>
@@ -24386,7 +24392,7 @@
         <v>330046</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E278" s="50">
         <v>16</v>
@@ -24398,7 +24404,7 @@
         <v>83</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24407,10 +24413,10 @@
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
@@ -24467,7 +24473,7 @@
         <v>330047</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E279" s="50">
         <v>3</v>
@@ -24479,7 +24485,7 @@
         <v>60</v>
       </c>
       <c r="H279" s="50" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I279" s="50" t="s">
         <v>78</v>
@@ -24488,7 +24494,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24548,7 +24554,7 @@
         <v>330048</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E280" s="50">
         <v>5</v>
@@ -24560,7 +24566,7 @@
         <v>60</v>
       </c>
       <c r="H280" s="50" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I280" s="50" t="s">
         <v>78</v>
@@ -24631,7 +24637,7 @@
         <v>330049</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E281" s="50">
         <v>43</v>
@@ -24643,7 +24649,7 @@
         <v>60</v>
       </c>
       <c r="H281" s="50" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="I281" s="50" t="s">
         <v>78</v>
@@ -24655,7 +24661,7 @@
         <v>100</v>
       </c>
       <c r="L281" s="50" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M281" s="50" t="s">
         <v>1</v>
@@ -24712,7 +24718,7 @@
         <v>330050</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E282" s="50">
         <v>44</v>
@@ -24724,7 +24730,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="50" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I282" s="50" t="s">
         <v>78</v>
@@ -24793,7 +24799,7 @@
         <v>330051</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E283" s="50">
         <v>4</v>
@@ -24805,7 +24811,7 @@
         <v>138</v>
       </c>
       <c r="H283" s="50" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="I283" s="50" t="s">
         <v>78</v>
@@ -24876,7 +24882,7 @@
         <v>330052</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E284" s="50">
         <v>4</v>
@@ -24888,7 +24894,7 @@
         <v>138</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I284" s="50" t="s">
         <v>78</v>
@@ -24959,7 +24965,7 @@
         <v>330053</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E285" s="50">
         <v>4</v>
@@ -24971,7 +24977,7 @@
         <v>60</v>
       </c>
       <c r="H285" s="50" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="I285" s="50" t="s">
         <v>78</v>
@@ -25042,7 +25048,7 @@
         <v>330054</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E286" s="50">
         <v>5</v>
@@ -25054,7 +25060,7 @@
         <v>60</v>
       </c>
       <c r="H286" s="50" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="I286" s="50" t="s">
         <v>78</v>
@@ -25125,7 +25131,7 @@
         <v>330055</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E287" s="50">
         <v>4</v>
@@ -25137,7 +25143,7 @@
         <v>83</v>
       </c>
       <c r="H287" s="50" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="I287" s="50" t="s">
         <v>78</v>
@@ -25208,7 +25214,7 @@
         <v>330056</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E288" s="50">
         <v>54</v>
@@ -25220,7 +25226,7 @@
         <v>138</v>
       </c>
       <c r="H288" s="50" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="I288" s="50" t="s">
         <v>78</v>
@@ -25291,7 +25297,7 @@
         <v>330058</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E289" s="50">
         <v>5</v>
@@ -25303,7 +25309,7 @@
         <v>138</v>
       </c>
       <c r="H289" s="50" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I289" s="50" t="s">
         <v>78</v>
@@ -25374,7 +25380,7 @@
         <v>330061</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E290" s="50">
         <v>39</v>
@@ -25386,7 +25392,7 @@
         <v>60</v>
       </c>
       <c r="H290" s="50" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="I290" s="50" t="s">
         <v>78</v>
@@ -25395,7 +25401,7 @@
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -25457,7 +25463,7 @@
         <v>330062</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E291" s="50">
         <v>40</v>
@@ -25469,7 +25475,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="50" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>78</v>
@@ -25478,7 +25484,7 @@
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L291" s="50" t="s">
         <v>1</v>
@@ -25540,7 +25546,7 @@
         <v>330063</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E292" s="50">
         <v>28</v>
@@ -25552,7 +25558,7 @@
         <v>60</v>
       </c>
       <c r="H292" s="50" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I292" s="50" t="s">
         <v>78</v>
@@ -25623,7 +25629,7 @@
         <v>330064</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E293" s="50">
         <v>29</v>
@@ -25635,7 +25641,7 @@
         <v>138</v>
       </c>
       <c r="H293" s="50" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I293" s="50" t="s">
         <v>78</v>
@@ -25706,7 +25712,7 @@
         <v>330065</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E294" s="50">
         <v>5</v>
@@ -25718,7 +25724,7 @@
         <v>60</v>
       </c>
       <c r="H294" s="50" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I294" s="50" t="s">
         <v>78</v>
@@ -25789,7 +25795,7 @@
         <v>330067</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E295" s="50">
         <v>4</v>
@@ -25801,7 +25807,7 @@
         <v>60</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>78</v>
@@ -25872,7 +25878,7 @@
         <v>330068</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E296" s="50">
         <v>5</v>
@@ -25884,7 +25890,7 @@
         <v>138</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>78</v>
@@ -25955,7 +25961,7 @@
         <v>330069</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E297" s="50">
         <v>16</v>
@@ -25967,7 +25973,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -25979,7 +25985,7 @@
         <v>257</v>
       </c>
       <c r="L297" s="50" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M297" s="50" t="s">
         <v>1</v>
@@ -26036,7 +26042,7 @@
         <v>330070</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E298" s="50">
         <v>3</v>
@@ -26048,7 +26054,7 @@
         <v>60</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="761">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1288,22 +1288,22 @@
     <t>48,5.9997,84</t>
   </si>
   <si>
-    <t>110,7.999978,48</t>
-  </si>
-  <si>
-    <t>115,8.002977,58.2436180114746</t>
-  </si>
-  <si>
-    <t>112.75,8,60.49362_112.75,8,55.99362_117.25,8,55.99362_117.25,8,60.49362</t>
+    <t>110,7.999978,43</t>
+  </si>
+  <si>
+    <t>115,9.499898,52</t>
+  </si>
+  <si>
+    <t>112.75,8,54.25_112.75,8,49.75_117.25,8,49.75_117.25,8,54.25</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>132,8.003199,59</t>
-  </si>
-  <si>
-    <t>130.5,8,57_133.5,8,57_133.5,8,61_130.5,8,61</t>
+    <t>132,7.999978,52</t>
+  </si>
+  <si>
+    <t>130.5,8,50_133.5,8,50_133.5,8,54_130.5,8,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1312,37 +1312,37 @@
     <t>70001_0</t>
   </si>
   <si>
-    <t>117,8.003199,79.8584136962891</t>
-  </si>
-  <si>
-    <t>118,8,78.85841_118,8,80.85841_116,8,80.85841_116,8,78.85841</t>
+    <t>117,-0.04387474,73.8584136962891</t>
+  </si>
+  <si>
+    <t>118,8,72.85841_118,8,74.85841_116,8,74.85841_116,8,72.85841</t>
   </si>
   <si>
     <t>74857</t>
   </si>
   <si>
-    <t>119,8.003199,79.8584136962891</t>
-  </si>
-  <si>
-    <t>120,8,78.85841_120,8,80.85841_118,8,80.85841_118,8,78.85841</t>
-  </si>
-  <si>
-    <t>121,8.003199,79.8584136962891</t>
-  </si>
-  <si>
-    <t>122,8,78.85841_122,8,80.85841_120,8,80.85841_120,8,78.85841</t>
-  </si>
-  <si>
-    <t>129.307510375977,7.999978,66.7048797607422</t>
-  </si>
-  <si>
-    <t>117.00,0.00,69.00,145.00,0.00,69.00,145.00,0.00,47.00,117.00,0.00,47.00</t>
-  </si>
-  <si>
-    <t>97,7.999978,77</t>
-  </si>
-  <si>
-    <t>98.5,8,78.5_95.5,8,78.5_95.5,8,75.5_98.5,8,75.5</t>
+    <t>119,-0.04387474,73.8584136962891</t>
+  </si>
+  <si>
+    <t>120,8,72.85841_120,8,74.85841_118,8,74.85841_118,8,72.85841</t>
+  </si>
+  <si>
+    <t>121,-0.04387474,73.8584136962891</t>
+  </si>
+  <si>
+    <t>122,8,72.85841_122,8,74.85841_120,8,74.85841_120,8,72.85841</t>
+  </si>
+  <si>
+    <t>129.307510375977,8.003199,60.7048797607422</t>
+  </si>
+  <si>
+    <t>117.00,0.00,63.00,145.00,0.00,63.00,145.00,0.00,41.00,117.00,0.00,41.00</t>
+  </si>
+  <si>
+    <t>97,7.999978,71</t>
+  </si>
+  <si>
+    <t>98.5,8,72.5_95.5,8,72.5_95.5,8,69.5_98.5,8,69.5</t>
   </si>
   <si>
     <t>74864</t>
@@ -1351,16 +1351,16 @@
     <t>74865</t>
   </si>
   <si>
-    <t>130,7.999978,80</t>
-  </si>
-  <si>
-    <t>131.5,8,81.5_128.5,8,81.5_128.5,8,78.5_131.5,8,78.5</t>
-  </si>
-  <si>
-    <t>104,7.999978,85</t>
-  </si>
-  <si>
-    <t>106,8,86_102,8,86_102,8,84_106,8,84</t>
+    <t>130,3.049911,74</t>
+  </si>
+  <si>
+    <t>131.5,8,75.5_128.5,8,75.5_128.5,8,72.5_131.5,8,72.5</t>
+  </si>
+  <si>
+    <t>104,7.999978,79</t>
+  </si>
+  <si>
+    <t>106,8,80_102,8,80_102,8,78_106,8,78</t>
   </si>
   <si>
     <t>74863</t>
@@ -1369,37 +1369,37 @@
     <t>70001_1</t>
   </si>
   <si>
-    <t>81,7.999978,90</t>
-  </si>
-  <si>
-    <t>82.5,8,88_82.5,8,92_79.5,8,92_79.5,8,88</t>
-  </si>
-  <si>
-    <t>87.1449661254883,1.861901,110.072158813477</t>
-  </si>
-  <si>
-    <t>87.14,0.00,110.07,113.00,0.00,110.07,113.00,0.00,87.93,87.14,0.00,87.93</t>
-  </si>
-  <si>
-    <t>58,7.999978,95</t>
-  </si>
-  <si>
-    <t>60.25,8,96.5_55.75,8,96.5_55.75,8,93.5_60.25,8,93.5</t>
+    <t>81,8.384579,84</t>
+  </si>
+  <si>
+    <t>82.5,8,82_82.5,8,86_79.5,8,86_79.5,8,82</t>
+  </si>
+  <si>
+    <t>87.1449661254883,7.999978,103.072158813477</t>
+  </si>
+  <si>
+    <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
+  </si>
+  <si>
+    <t>58,7.999978,89</t>
+  </si>
+  <si>
+    <t>60.25,8,90.5_55.75,8,90.5_55.75,8,87.5_60.25,8,87.5</t>
   </si>
   <si>
     <t>70308</t>
   </si>
   <si>
-    <t>57.7461738586426,7.999978,89</t>
-  </si>
-  <si>
-    <t>59.74617,8,90.5_55.74617,8,90.5_55.74617,8,87.5_59.74617,8,87.5</t>
-  </si>
-  <si>
-    <t>63,9.211463,76</t>
-  </si>
-  <si>
-    <t>62,8,78_62,8,74_64,8,74_64,8,78</t>
+    <t>57.7461738586426,7.999978,84</t>
+  </si>
+  <si>
+    <t>59.74617,8,85.5_55.74617,8,85.5_55.74617,8,82.5_59.74617,8,82.5</t>
+  </si>
+  <si>
+    <t>63,9.699891,70</t>
+  </si>
+  <si>
+    <t>62,8,72_62,8,68_64,8,68_64,8,72</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1408,19 +1408,19 @@
     <t>74871</t>
   </si>
   <si>
-    <t>98,7.999978,62</t>
-  </si>
-  <si>
-    <t>99,9.000299,63_97,9.000299,63_97,9.000299,61_99,9.000299,61</t>
+    <t>98,6.143705,54</t>
+  </si>
+  <si>
+    <t>99,9.000299,55_97,9.000299,55_97,9.000299,53_99,9.000299,53</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
-    <t>91,7.999978,62</t>
-  </si>
-  <si>
-    <t>88.75,8,64.25_88.75,8,59.75_93.25,8,59.75_93.25,8,64.25</t>
+    <t>91,9.999871,56</t>
+  </si>
+  <si>
+    <t>88.75,8,58.25_88.75,8,53.75_93.25,8,53.75_93.25,8,58.25</t>
   </si>
   <si>
     <t>74876</t>
@@ -1429,34 +1429,361 @@
     <t>70301</t>
   </si>
   <si>
-    <t>58,7.999978,69</t>
-  </si>
-  <si>
-    <t>60.25,7.999999,71.25_55.75,7.999999,71.25_55.75,7.999999,66.75_60.25,7.999999,66.75</t>
+    <t>58,7.999978,63</t>
+  </si>
+  <si>
+    <t>60.25,8,65.25_55.75,8,65.25_55.75,8,60.75_60.25,8,60.75</t>
   </si>
   <si>
     <t>70302</t>
   </si>
   <si>
-    <t>109.408554077148,8.003199,121</t>
-  </si>
-  <si>
-    <t>114.4086,7.999999,123_107.4086,7.999999,123_107.4086,7.999999,119_114.4086,7.999999,119</t>
+    <t>109.408554077148,-0.04387474,114</t>
+  </si>
+  <si>
+    <t>114.4086,7.999999,116_107.4086,7.999999,116_107.4086,7.999999,112_114.4086,7.999999,112</t>
   </si>
   <si>
     <t>74875</t>
   </si>
   <si>
-    <t>58,7.999978,62</t>
-  </si>
-  <si>
-    <t>59,7.999999,63_57,7.999999,63_57,7.999999,61_59,7.999999,61</t>
-  </si>
-  <si>
-    <t>58,7.999978,48</t>
-  </si>
-  <si>
-    <t>59.5,8,46_59.5,8,50_56.5,8,50_56.5,8,46</t>
+    <t>58,7.999978,57</t>
+  </si>
+  <si>
+    <t>59,8,58_57,8,58_57,8,56_59,8,56</t>
+  </si>
+  <si>
+    <t>58,0,41</t>
+  </si>
+  <si>
+    <t>59.5,8,39_59.5,8,43_56.5,8,43_56.5,8,39</t>
+  </si>
+  <si>
+    <t>137,-0.04387474,133.983917236328</t>
+  </si>
+  <si>
+    <t>138.5,8,131.4839_138.5,8,136.4839_135.5,8,136.4839_135.5,8,131.4839</t>
+  </si>
+  <si>
+    <t>74878</t>
+  </si>
+  <si>
+    <t>88,7.999978,156</t>
+  </si>
+  <si>
+    <t>89,8,155_89,8,157_87,8,157_87,8,155</t>
+  </si>
+  <si>
+    <t>99,7.999978,156</t>
+  </si>
+  <si>
+    <t>100.5,8.013261,153.5_100.5,8.013261,158.5_97.5,8.013261,158.5_97.5,8.013261,153.5</t>
+  </si>
+  <si>
+    <t>102,7.999978,121</t>
+  </si>
+  <si>
+    <t>104,7.859674,122_100,7.859674,122_100,7.859674,120_104,7.859674,120</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_Door_01_purple.prefab</t>
+  </si>
+  <si>
+    <t>74881</t>
+  </si>
+  <si>
+    <t>102,7.999978,122</t>
+  </si>
+  <si>
+    <t>0,74995</t>
+  </si>
+  <si>
+    <t>102,7.999978,124</t>
+  </si>
+  <si>
+    <t>74880</t>
+  </si>
+  <si>
+    <t>122,-0.04387474,114</t>
+  </si>
+  <si>
+    <t>123,7.859674,115_121,7.859674,115_121,7.859674,113_123,7.859674,113</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/Key_Purple.prefab</t>
+  </si>
+  <si>
+    <t>112,-0.04387474,134</t>
+  </si>
+  <si>
+    <t>110.5,7.960799,136_110.5,7.960799,132_113.5,7.960799,132_113.5,7.960799,136</t>
+  </si>
+  <si>
+    <t>0,74996</t>
+  </si>
+  <si>
+    <t>105,7.999978,143</t>
+  </si>
+  <si>
+    <t>70001_2</t>
+  </si>
+  <si>
+    <t>74996</t>
+  </si>
+  <si>
+    <t>127,-0.04387474,134</t>
+  </si>
+  <si>
+    <t>129.25,8,131.75_129.25,8,136.25_124.75,8,136.25_124.75,8,131.75</t>
+  </si>
+  <si>
+    <t>142,7.999978,176</t>
+  </si>
+  <si>
+    <t>143.5,8.039689,178_140.5,8.039689,178_140.5,8.039689,174_143.5,8.039689,174</t>
+  </si>
+  <si>
+    <t>74887</t>
+  </si>
+  <si>
+    <t>74886</t>
+  </si>
+  <si>
+    <t>142,7.999978,185</t>
+  </si>
+  <si>
+    <t>144,8.039689,187_140,8.039689,187_140,8.039689,183_144,8.039689,183</t>
+  </si>
+  <si>
+    <t>74885</t>
+  </si>
+  <si>
+    <t>122,-0.04387474,134</t>
+  </si>
+  <si>
+    <t>123,8,135_121,8,135_121,8,133_123,8,133</t>
+  </si>
+  <si>
+    <t>119,10.00309,203</t>
+  </si>
+  <si>
+    <t>120,10,204.5_118,10,204.5_118,10,201.5_120,10,201.5</t>
+  </si>
+  <si>
+    <t>74889</t>
+  </si>
+  <si>
+    <t>112,8.003199,203</t>
+  </si>
+  <si>
+    <t>113.5,8,205_110.5,8,205_110.5,8,201_113.5,8,201</t>
+  </si>
+  <si>
+    <t>74888</t>
+  </si>
+  <si>
+    <t>112,7.999978,207</t>
+  </si>
+  <si>
+    <t>0,74998</t>
+  </si>
+  <si>
+    <t>112,7.999978,208</t>
+  </si>
+  <si>
+    <t>95.7563781738281,-0.04387474,203</t>
+  </si>
+  <si>
+    <t>97.75638,8.046697,204.5_93.75638,8.046697,204.5_93.75638,8.046697,201.5_97.75638,8.046697,201.5</t>
+  </si>
+  <si>
+    <t>96,-0.04387474,209</t>
+  </si>
+  <si>
+    <t>98.25,7.109542,211.25_93.75,7.109542,211.25_93.75,7.109542,206.75_98.25,7.109542,206.75</t>
+  </si>
+  <si>
+    <t>70309</t>
+  </si>
+  <si>
+    <t>73,7.999978,216</t>
+  </si>
+  <si>
+    <t>74.5,7.664845,213.75_74.5,7.664845,218.25_71.5,7.664845,218.25_71.5,7.664845,213.75</t>
+  </si>
+  <si>
+    <t>70304</t>
+  </si>
+  <si>
+    <t>115,9.499898,240</t>
+  </si>
+  <si>
+    <t>116,7.859674,238_116,7.859674,242_114,7.859674,242_114,7.859674,238</t>
+  </si>
+  <si>
+    <t>74894</t>
+  </si>
+  <si>
+    <t>70001_3</t>
+  </si>
+  <si>
+    <t>67,7.999978,216</t>
+  </si>
+  <si>
+    <t>68,7.859674,217_66,7.859674,217_66,7.859674,215_68,7.859674,215</t>
+  </si>
+  <si>
+    <t>133,7.999978,238.119369506836</t>
+  </si>
+  <si>
+    <t>131.5,8,240.1194_131.5,8,236.1194_134.5,8,236.1194_134.5,8,240.1194</t>
+  </si>
+  <si>
+    <t>100.981590270996,7.999978,172.904113769531</t>
+  </si>
+  <si>
+    <t>100.98,0.00,172.90,145.17,0.00,172.90,145.17,0.00,142.53,100.98,0.00,142.53</t>
+  </si>
+  <si>
+    <t>128,7.999978,296</t>
+  </si>
+  <si>
+    <t>126.5,8,294_129.5,8,294_129.5,8,298_126.5,8,298</t>
+  </si>
+  <si>
+    <t>74898,74899,74900</t>
+  </si>
+  <si>
+    <t>117.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>118.1416,8,273_118.1416,8,275_116.1416,8,275_116.1416,8,273</t>
+  </si>
+  <si>
+    <t>74897</t>
+  </si>
+  <si>
+    <t>119.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>120.1416,8,273_120.1416,8,275_118.1416,8,275_118.1416,8,273</t>
+  </si>
+  <si>
+    <t>121.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>122.1416,8,273_122.1416,8,275_120.1416,8,275_120.1416,8,273</t>
+  </si>
+  <si>
+    <t>135,7.999978,274</t>
+  </si>
+  <si>
+    <t>132.75,8,276.25_132.75,8,271.75_137.25,8,271.75_137.25,8,276.25</t>
+  </si>
+  <si>
+    <t>70306</t>
+  </si>
+  <si>
+    <t>116.034126281738,7.999978,253.618927001953</t>
+  </si>
+  <si>
+    <t>116.03,0.00,253.00,149.00,0.00,253.00,149.00,0.00,223.00,116.03,0.00,223.00</t>
+  </si>
+  <si>
+    <t>113,7.999978,294</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_TanHuangBan.prefab</t>
+  </si>
+  <si>
+    <t>74907</t>
+  </si>
+  <si>
+    <t>119,-0.04387474,293.976043701172</t>
+  </si>
+  <si>
+    <t>119,-0.04387474,298</t>
+  </si>
+  <si>
+    <t>74909</t>
+  </si>
+  <si>
+    <t>113,7.999978,297.976043701172</t>
+  </si>
+  <si>
+    <t>74.038444519043,14.99987,232</t>
+  </si>
+  <si>
+    <t>75.78844,14,230.5_75.78844,14,233.5_71.78844,14,233.5_71.78844,14,230.5</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGfasheqi.prefab</t>
+  </si>
+  <si>
+    <t>88.038444519043,14.99987,232</t>
+  </si>
+  <si>
+    <t>89.53844,14,233.5_86.53844,14,233.5_86.53844,14,230.5_89.53844,14,230.5</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGjingzi.prefab</t>
+  </si>
+  <si>
+    <t>88.038444519043,14.99987,244</t>
+  </si>
+  <si>
+    <t>89.53844,14,245.5_86.53844,14,245.5_86.53844,14,242.5_89.53844,14,242.5</t>
+  </si>
+  <si>
+    <t>74.038444519043,14.99987,253.25</t>
+  </si>
+  <si>
+    <t>72.53844,14,251_75.53844,14,251_75.53844,14,255_72.53844,14,255</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGJieshouqi.prefab</t>
+  </si>
+  <si>
+    <t>74983</t>
+  </si>
+  <si>
+    <t>78,14.99987,255</t>
+  </si>
+  <si>
+    <t>80,14,256_76,14,256_76,14,254_80,14,254</t>
+  </si>
+  <si>
+    <t>74981</t>
+  </si>
+  <si>
+    <t>74.038444519043,14.99987,244</t>
+  </si>
+  <si>
+    <t>75.53844,14,245.5_72.53844,14,245.5_72.53844,14,242.5_75.53844,14,242.5</t>
+  </si>
+  <si>
+    <t>62.2290153503418,14.99987,253.647537231445</t>
+  </si>
+  <si>
+    <t>62.23,0.00,253.65,97.86,0.00,253.65,97.86,0.00,222.24,62.23,0.00,222.24</t>
+  </si>
+  <si>
+    <t>143,7.999978,274</t>
+  </si>
+  <si>
+    <t>142,8,273_144,8,273_144,8,275_142,8,275</t>
+  </si>
+  <si>
+    <t>90.9580841064453,7.999978,221</t>
+  </si>
+  <si>
+    <t>92.95808,8,222.5_88.95808,8,222.5_88.95808,8,219.5_92.95808,8,219.5</t>
+  </si>
+  <si>
+    <t>74991</t>
+  </si>
+  <si>
+    <t>75,14.99987,266</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -1654,9 +1981,6 @@
     <t>66.25,-8.769137E-05,46.5_66.25,-8.769137E-05,43.5_70.25,-8.769137E-05,43.5_70.25,-8.769137E-05,46.5</t>
   </si>
   <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGfasheqi.prefab</t>
-  </si>
-  <si>
     <t>60,-8.769137E-05,45</t>
   </si>
   <si>
@@ -1666,16 +1990,10 @@
     <t>57.87868,-8.769137E-05,45_60,-8.769137E-05,42.87868_62.12132,-8.769137E-05,45_60,-8.769137E-05,47.12132</t>
   </si>
   <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGjingzi.prefab</t>
-  </si>
-  <si>
     <t>75,-8.769137E-05,49</t>
   </si>
   <si>
     <t>73.5,-8.769137E-05,46.75_76.5,-8.769137E-05,46.75_76.5,-8.769137E-05,50.75_73.5,-8.769137E-05,50.75</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGJieshouqi.prefab</t>
   </si>
   <si>
     <t>84973</t>
@@ -3073,7 +3391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA298"/>
+  <dimension ref="A1:AA342"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -19292,44 +19610,45 @@
         <v>58</v>
       </c>
       <c r="C213" s="50">
-        <v>84928</v>
+        <v>74877</v>
       </c>
       <c r="D213" s="50" t="s">
         <v>480</v>
       </c>
       <c r="E213" s="50">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F213" s="50">
         <v>0</v>
       </c>
       <c r="G213" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H213" s="50" t="s">
+        <v>481</v>
       </c>
       <c r="I213" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J213" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K213" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="L213" s="50" t="s">
+        <v>482</v>
+      </c>
+      <c r="M213" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="J213" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K213" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="L213" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M213" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="N213" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O213" s="50">
         <v>0</v>
       </c>
-      <c r="P213" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P213" s="50"/>
       <c r="Q213" s="50">
         <v>0</v>
       </c>
@@ -19372,22 +19691,22 @@
         <v>58</v>
       </c>
       <c r="C214" s="50">
-        <v>84929</v>
+        <v>74878</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E214" s="50">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F214" s="50">
         <v>0</v>
       </c>
       <c r="G214" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19396,16 +19715,16 @@
         <v>62</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>377</v>
+        <v>135</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>483</v>
+        <v>1</v>
       </c>
       <c r="M214" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N214" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O214" s="50">
         <v>0</v>
@@ -19415,7 +19734,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S214" s="50">
         <v>0</v>
@@ -19453,44 +19772,49 @@
         <v>58</v>
       </c>
       <c r="C215" s="50">
-        <v>84930</v>
+        <v>74879</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E215" s="50">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F215" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="50" t="s">
         <v>138</v>
       </c>
+      <c r="H215" s="50" t="s">
+        <v>486</v>
+      </c>
       <c r="I215" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J215" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>388</v>
+        <v>85</v>
       </c>
       <c r="L215" s="50" t="s">
-        <v>485</v>
+        <v>1</v>
       </c>
       <c r="M215" s="50" t="s">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="N215" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O215" s="50">
         <v>0</v>
       </c>
-      <c r="P215" s="50"/>
+      <c r="P215" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q215" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R215" s="50">
         <v>0</v>
@@ -19531,19 +19855,19 @@
         <v>58</v>
       </c>
       <c r="C216" s="50">
-        <v>84931</v>
+        <v>74880</v>
       </c>
       <c r="D216" s="50" t="s">
         <v>487</v>
       </c>
       <c r="E216" s="50">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F216" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G216" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H216" s="50" t="s">
         <v>488</v>
@@ -19555,16 +19879,16 @@
         <v>62</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>392</v>
+        <v>489</v>
       </c>
       <c r="L216" s="50" t="s">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="M216" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N216" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O216" s="50">
         <v>0</v>
@@ -19612,16 +19936,16 @@
         <v>58</v>
       </c>
       <c r="C217" s="50">
-        <v>84932</v>
+        <v>74994</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E217" s="50">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F217" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217" s="50" t="s">
         <v>60</v>
@@ -19633,21 +19957,23 @@
         <v>62</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>490</v>
+        <v>1</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>486</v>
+        <v>61</v>
       </c>
       <c r="N217" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O217" s="50">
         <v>0</v>
       </c>
-      <c r="P217" s="50"/>
+      <c r="P217" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q217" s="50">
         <v>0</v>
       </c>
@@ -19679,7 +20005,7 @@
         <v>0</v>
       </c>
       <c r="AA217" s="50" t="s">
-        <v>1</v>
+        <v>492</v>
       </c>
     </row>
     <row r="218">
@@ -19690,31 +20016,28 @@
         <v>58</v>
       </c>
       <c r="C218" s="50">
-        <v>84933</v>
+        <v>74995</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E218" s="50">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F218" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G218" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H218" s="50" t="s">
-        <v>492</v>
-      </c>
       <c r="I218" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J218" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K218" s="50" t="s">
-        <v>392</v>
+        <v>75</v>
       </c>
       <c r="L218" s="50" t="s">
         <v>1</v>
@@ -19723,12 +20046,14 @@
         <v>1</v>
       </c>
       <c r="N218" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O218" s="50">
         <v>0</v>
       </c>
-      <c r="P218" s="50"/>
+      <c r="P218" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q218" s="50">
         <v>0</v>
       </c>
@@ -19754,7 +20079,7 @@
         <v>1</v>
       </c>
       <c r="Y218" s="50" t="s">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="Z218" s="52">
         <v>0</v>
@@ -19771,22 +20096,22 @@
         <v>58</v>
       </c>
       <c r="C219" s="50">
-        <v>84934</v>
+        <v>74881</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E219" s="50">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F219" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G219" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H219" s="50" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I219" s="50" t="s">
         <v>78</v>
@@ -19795,7 +20120,7 @@
         <v>62</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>398</v>
+        <v>497</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -19804,7 +20129,7 @@
         <v>1</v>
       </c>
       <c r="N219" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O219" s="50">
         <v>0</v>
@@ -19852,22 +20177,22 @@
         <v>58</v>
       </c>
       <c r="C220" s="50">
-        <v>84935</v>
+        <v>74882</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E220" s="50">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F220" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>78</v>
@@ -19876,7 +20201,7 @@
         <v>62</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>403</v>
+        <v>230</v>
       </c>
       <c r="L220" s="50" t="s">
         <v>1</v>
@@ -19885,12 +20210,14 @@
         <v>1</v>
       </c>
       <c r="N220" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O220" s="50">
         <v>0</v>
       </c>
-      <c r="P220" s="50"/>
+      <c r="P220" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q220" s="50">
         <v>0</v>
       </c>
@@ -19898,7 +20225,7 @@
         <v>0</v>
       </c>
       <c r="S220" s="50">
-        <v>0</v>
+        <v>70005</v>
       </c>
       <c r="T220" s="50">
         <v>0</v>
@@ -19922,7 +20249,7 @@
         <v>0</v>
       </c>
       <c r="AA220" s="50" t="s">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221">
@@ -19933,13 +20260,13 @@
         <v>58</v>
       </c>
       <c r="C221" s="50">
-        <v>84936</v>
+        <v>74996</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E221" s="50">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="F221" s="50">
         <v>3</v>
@@ -19947,17 +20274,14 @@
       <c r="G221" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H221" s="50" t="s">
-        <v>498</v>
-      </c>
       <c r="I221" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J221" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -19966,12 +20290,14 @@
         <v>1</v>
       </c>
       <c r="N221" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O221" s="50">
         <v>0</v>
       </c>
-      <c r="P221" s="50"/>
+      <c r="P221" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q221" s="50">
         <v>0</v>
       </c>
@@ -19988,16 +20314,16 @@
         <v>0</v>
       </c>
       <c r="V221" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W221" s="50" t="s">
         <v>1</v>
       </c>
       <c r="X221" s="50" t="s">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="Y221" s="50" t="s">
-        <v>1</v>
+        <v>503</v>
       </c>
       <c r="Z221" s="52">
         <v>0</v>
@@ -20014,22 +20340,22 @@
         <v>58</v>
       </c>
       <c r="C222" s="50">
-        <v>84937</v>
+        <v>74884</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E222" s="50">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F222" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G222" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H222" s="50" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="I222" s="50" t="s">
         <v>78</v>
@@ -20038,7 +20364,7 @@
         <v>62</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>396</v>
+        <v>297</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -20047,12 +20373,14 @@
         <v>1</v>
       </c>
       <c r="N222" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O222" s="50">
         <v>0</v>
       </c>
-      <c r="P222" s="50"/>
+      <c r="P222" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q222" s="50">
         <v>0</v>
       </c>
@@ -20062,14 +20390,14 @@
       <c r="S222" s="50">
         <v>0</v>
       </c>
-      <c r="T222" s="50">
-        <v>0</v>
+      <c r="T222" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U222" s="50">
         <v>0</v>
       </c>
       <c r="V222" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W222" s="50" t="s">
         <v>1</v>
@@ -20095,22 +20423,22 @@
         <v>58</v>
       </c>
       <c r="C223" s="50">
-        <v>84938</v>
+        <v>74885</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="E223" s="50">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F223" s="50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G223" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>78</v>
@@ -20119,16 +20447,16 @@
         <v>62</v>
       </c>
       <c r="K223" s="50" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="L223" s="50" t="s">
-        <v>1</v>
+        <v>508</v>
       </c>
       <c r="M223" s="50" t="s">
-        <v>1</v>
+        <v>509</v>
       </c>
       <c r="N223" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O223" s="50">
         <v>0</v>
@@ -20176,13 +20504,13 @@
         <v>58</v>
       </c>
       <c r="C224" s="50">
-        <v>84939</v>
+        <v>74886</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="E224" s="50">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="F224" s="50">
         <v>0</v>
@@ -20191,7 +20519,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20200,16 +20528,16 @@
         <v>62</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="L224" s="50" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="M224" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N224" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O224" s="50">
         <v>0</v>
@@ -20257,13 +20585,13 @@
         <v>58</v>
       </c>
       <c r="C225" s="50">
-        <v>84940</v>
+        <v>74887</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E225" s="50">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F225" s="50">
         <v>0</v>
@@ -20272,7 +20600,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20281,7 +20609,7 @@
         <v>62</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="L225" s="50" t="s">
         <v>1</v>
@@ -20290,7 +20618,7 @@
         <v>1</v>
       </c>
       <c r="N225" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O225" s="50">
         <v>0</v>
@@ -20338,22 +20666,22 @@
         <v>58</v>
       </c>
       <c r="C226" s="50">
-        <v>84941</v>
+        <v>74888</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E226" s="50">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F226" s="50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G226" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20362,16 +20690,16 @@
         <v>62</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>509</v>
+        <v>1</v>
       </c>
       <c r="M226" s="50" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="N226" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O226" s="50">
         <v>0</v>
@@ -20419,37 +20747,40 @@
         <v>58</v>
       </c>
       <c r="C227" s="50">
-        <v>84942</v>
+        <v>74889</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E227" s="50">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F227" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G227" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H227" s="50" t="s">
+        <v>519</v>
+      </c>
       <c r="I227" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J227" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>512</v>
+        <v>1</v>
       </c>
       <c r="N227" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O227" s="50">
         <v>0</v>
@@ -20497,45 +20828,44 @@
         <v>58</v>
       </c>
       <c r="C228" s="50">
-        <v>84943</v>
+        <v>74997</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E228" s="50">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F228" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G228" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H228" s="50" t="s">
-        <v>514</v>
-      </c>
       <c r="I228" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J228" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K228" s="50" t="s">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="L228" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M228" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N228" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O228" s="50">
         <v>0</v>
       </c>
-      <c r="P228" s="50"/>
+      <c r="P228" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q228" s="50">
         <v>0</v>
       </c>
@@ -20567,7 +20897,7 @@
         <v>0</v>
       </c>
       <c r="AA228" s="50" t="s">
-        <v>1</v>
+        <v>522</v>
       </c>
     </row>
     <row r="229">
@@ -20578,16 +20908,16 @@
         <v>58</v>
       </c>
       <c r="C229" s="50">
-        <v>84944</v>
+        <v>74998</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E229" s="50">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F229" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G229" s="50" t="s">
         <v>60</v>
@@ -20599,21 +20929,23 @@
         <v>62</v>
       </c>
       <c r="K229" s="50" t="s">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>516</v>
+        <v>1</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>512</v>
+        <v>1</v>
       </c>
       <c r="N229" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O229" s="50">
         <v>0</v>
       </c>
-      <c r="P229" s="50"/>
+      <c r="P229" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q229" s="50">
         <v>0</v>
       </c>
@@ -20639,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="Y229" s="50" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="Z229" s="52">
         <v>0</v>
@@ -20656,22 +20988,22 @@
         <v>58</v>
       </c>
       <c r="C230" s="50">
-        <v>84945</v>
+        <v>74890</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="E230" s="50">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F230" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G230" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H230" s="50" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="I230" s="50" t="s">
         <v>78</v>
@@ -20680,7 +21012,7 @@
         <v>62</v>
       </c>
       <c r="K230" s="50" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="L230" s="50" t="s">
         <v>1</v>
@@ -20689,12 +21021,14 @@
         <v>1</v>
       </c>
       <c r="N230" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O230" s="50">
         <v>0</v>
       </c>
-      <c r="P230" s="50"/>
+      <c r="P230" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q230" s="50">
         <v>0</v>
       </c>
@@ -20702,7 +21036,7 @@
         <v>0</v>
       </c>
       <c r="S230" s="50">
-        <v>0</v>
+        <v>70006</v>
       </c>
       <c r="T230" s="50">
         <v>0</v>
@@ -20737,13 +21071,13 @@
         <v>58</v>
       </c>
       <c r="C231" s="50">
-        <v>84946</v>
+        <v>74891</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E231" s="50">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F231" s="50">
         <v>1</v>
@@ -20751,14 +21085,17 @@
       <c r="G231" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H231" s="50" t="s">
+        <v>527</v>
+      </c>
       <c r="I231" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J231" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>520</v>
+        <v>96</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -20767,12 +21104,14 @@
         <v>1</v>
       </c>
       <c r="N231" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O231" s="50">
         <v>0</v>
       </c>
-      <c r="P231" s="50"/>
+      <c r="P231" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q231" s="50">
         <v>0</v>
       </c>
@@ -20782,8 +21121,8 @@
       <c r="S231" s="50">
         <v>0</v>
       </c>
-      <c r="T231" s="50">
-        <v>0</v>
+      <c r="T231" s="50" t="s">
+        <v>528</v>
       </c>
       <c r="U231" s="50">
         <v>0</v>
@@ -20815,28 +21154,31 @@
         <v>58</v>
       </c>
       <c r="C232" s="50">
-        <v>84947</v>
+        <v>74892</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E232" s="50">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F232" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G232" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H232" s="50" t="s">
+        <v>530</v>
       </c>
       <c r="I232" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J232" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K232" s="50" t="s">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="L232" s="50" t="s">
         <v>1</v>
@@ -20845,12 +21187,14 @@
         <v>1</v>
       </c>
       <c r="N232" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O232" s="50">
         <v>0</v>
       </c>
-      <c r="P232" s="50"/>
+      <c r="P232" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q232" s="50">
         <v>0</v>
       </c>
@@ -20860,8 +21204,8 @@
       <c r="S232" s="50">
         <v>0</v>
       </c>
-      <c r="T232" s="50">
-        <v>0</v>
+      <c r="T232" s="50" t="s">
+        <v>531</v>
       </c>
       <c r="U232" s="50">
         <v>0</v>
@@ -20893,37 +21237,40 @@
         <v>58</v>
       </c>
       <c r="C233" s="50">
-        <v>84948</v>
+        <v>74893</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="E233" s="50">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F233" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G233" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H233" s="50" t="s">
+        <v>533</v>
       </c>
       <c r="I233" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J233" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K233" s="50" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="L233" s="50" t="s">
-        <v>1</v>
+        <v>534</v>
       </c>
       <c r="M233" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N233" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O233" s="50">
         <v>0</v>
@@ -20951,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="X233" s="50" t="s">
-        <v>1</v>
+        <v>535</v>
       </c>
       <c r="Y233" s="50" t="s">
         <v>1</v>
@@ -20971,28 +21318,31 @@
         <v>58</v>
       </c>
       <c r="C234" s="50">
-        <v>84949</v>
+        <v>74894</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="E234" s="50">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="F234" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G234" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H234" s="50" t="s">
+        <v>537</v>
+      </c>
       <c r="I234" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J234" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K234" s="50" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="L234" s="50" t="s">
         <v>1</v>
@@ -21001,7 +21351,7 @@
         <v>1</v>
       </c>
       <c r="N234" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O234" s="50">
         <v>0</v>
@@ -21049,28 +21399,31 @@
         <v>58</v>
       </c>
       <c r="C235" s="50">
-        <v>84950</v>
+        <v>74895</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="E235" s="50">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F235" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G235" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H235" s="50" t="s">
+        <v>539</v>
       </c>
       <c r="I235" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J235" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K235" s="50" t="s">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="L235" s="50" t="s">
         <v>1</v>
@@ -21079,12 +21432,14 @@
         <v>1</v>
       </c>
       <c r="N235" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O235" s="50">
         <v>0</v>
       </c>
-      <c r="P235" s="50"/>
+      <c r="P235" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q235" s="50">
         <v>0</v>
       </c>
@@ -21092,7 +21447,7 @@
         <v>0</v>
       </c>
       <c r="S235" s="50">
-        <v>0</v>
+        <v>70007</v>
       </c>
       <c r="T235" s="50">
         <v>0</v>
@@ -21127,16 +21482,16 @@
         <v>58</v>
       </c>
       <c r="C236" s="50">
-        <v>84951</v>
+        <v>74896</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="E236" s="50">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="F236" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" s="50" t="s">
         <v>60</v>
@@ -21147,54 +21502,32 @@
       <c r="J236" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K236" s="50" t="s">
-        <v>301</v>
-      </c>
+      <c r="K236" s="50"/>
       <c r="L236" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M236" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M236" s="50"/>
       <c r="N236" s="50">
-        <v>8</v>
-      </c>
-      <c r="O236" s="50">
-        <v>0</v>
-      </c>
-      <c r="P236" s="50"/>
-      <c r="Q236" s="50">
-        <v>0</v>
-      </c>
-      <c r="R236" s="50">
-        <v>0</v>
-      </c>
-      <c r="S236" s="50">
-        <v>0</v>
-      </c>
-      <c r="T236" s="50">
-        <v>0</v>
-      </c>
-      <c r="U236" s="50">
-        <v>0</v>
-      </c>
-      <c r="V236" s="50">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O236" s="50"/>
+      <c r="P236" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="Q236" s="50"/>
+      <c r="R236" s="50"/>
+      <c r="S236" s="50"/>
+      <c r="T236" s="50"/>
+      <c r="U236" s="50"/>
+      <c r="V236" s="50"/>
       <c r="W236" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X236" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y236" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z236" s="52">
-        <v>0</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="X236" s="50"/>
+      <c r="Y236" s="50"/>
+      <c r="Z236" s="52"/>
       <c r="AA236" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="237">
@@ -21205,37 +21538,40 @@
         <v>58</v>
       </c>
       <c r="C237" s="50">
-        <v>84952</v>
+        <v>74897</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="E237" s="50">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F237" s="50">
         <v>0</v>
       </c>
       <c r="G237" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
+      </c>
+      <c r="H237" s="50" t="s">
+        <v>543</v>
       </c>
       <c r="I237" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J237" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K237" s="50" t="s">
-        <v>301</v>
+        <v>142</v>
       </c>
       <c r="L237" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M237" s="50" t="s">
-        <v>1</v>
+        <v>544</v>
       </c>
       <c r="N237" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O237" s="50">
         <v>0</v>
@@ -21283,37 +21619,40 @@
         <v>58</v>
       </c>
       <c r="C238" s="50">
-        <v>84953</v>
+        <v>74898</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E238" s="50">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F238" s="50">
         <v>0</v>
       </c>
       <c r="G238" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H238" s="50" t="s">
+        <v>546</v>
       </c>
       <c r="I238" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J238" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K238" s="50" t="s">
-        <v>301</v>
+        <v>147</v>
       </c>
       <c r="L238" s="50" t="s">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="M238" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N238" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O238" s="50">
         <v>0</v>
@@ -21361,37 +21700,40 @@
         <v>58</v>
       </c>
       <c r="C239" s="50">
-        <v>84954</v>
+        <v>74899</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="E239" s="50">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F239" s="50">
         <v>0</v>
       </c>
       <c r="G239" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H239" s="50" t="s">
+        <v>549</v>
       </c>
       <c r="I239" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J239" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K239" s="50" t="s">
-        <v>301</v>
+        <v>147</v>
       </c>
       <c r="L239" s="50" t="s">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="M239" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N239" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O239" s="50">
         <v>0</v>
@@ -21439,37 +21781,40 @@
         <v>58</v>
       </c>
       <c r="C240" s="50">
-        <v>84955</v>
+        <v>74900</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="E240" s="50">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F240" s="50">
         <v>0</v>
       </c>
       <c r="G240" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H240" s="50" t="s">
+        <v>551</v>
       </c>
       <c r="I240" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J240" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K240" s="50" t="s">
-        <v>301</v>
+        <v>147</v>
       </c>
       <c r="L240" s="50" t="s">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="M240" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N240" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O240" s="50">
         <v>0</v>
@@ -21517,28 +21862,31 @@
         <v>58</v>
       </c>
       <c r="C241" s="50">
-        <v>84956</v>
+        <v>74901</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
       <c r="E241" s="50">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F241" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G241" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H241" s="50" t="s">
+        <v>553</v>
       </c>
       <c r="I241" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J241" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K241" s="50" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L241" s="50" t="s">
         <v>1</v>
@@ -21547,12 +21895,14 @@
         <v>1</v>
       </c>
       <c r="N241" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O241" s="50">
         <v>0</v>
       </c>
-      <c r="P241" s="50"/>
+      <c r="P241" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q241" s="50">
         <v>0</v>
       </c>
@@ -21562,8 +21912,8 @@
       <c r="S241" s="50">
         <v>0</v>
       </c>
-      <c r="T241" s="50">
-        <v>0</v>
+      <c r="T241" s="50" t="s">
+        <v>554</v>
       </c>
       <c r="U241" s="50">
         <v>0</v>
@@ -21595,16 +21945,16 @@
         <v>58</v>
       </c>
       <c r="C242" s="50">
-        <v>84957</v>
+        <v>74905</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="E242" s="50">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="F242" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" s="50" t="s">
         <v>60</v>
@@ -21615,54 +21965,32 @@
       <c r="J242" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K242" s="50" t="s">
-        <v>301</v>
-      </c>
+      <c r="K242" s="50"/>
       <c r="L242" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M242" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M242" s="50"/>
       <c r="N242" s="50">
-        <v>8</v>
-      </c>
-      <c r="O242" s="50">
-        <v>0</v>
-      </c>
-      <c r="P242" s="50"/>
-      <c r="Q242" s="50">
-        <v>0</v>
-      </c>
-      <c r="R242" s="50">
-        <v>0</v>
-      </c>
-      <c r="S242" s="50">
-        <v>0</v>
-      </c>
-      <c r="T242" s="50">
-        <v>0</v>
-      </c>
-      <c r="U242" s="50">
-        <v>0</v>
-      </c>
-      <c r="V242" s="50">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O242" s="50"/>
+      <c r="P242" s="50" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q242" s="50"/>
+      <c r="R242" s="50"/>
+      <c r="S242" s="50"/>
+      <c r="T242" s="50"/>
+      <c r="U242" s="50"/>
+      <c r="V242" s="50"/>
       <c r="W242" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X242" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y242" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z242" s="52">
-        <v>0</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="X242" s="50"/>
+      <c r="Y242" s="50"/>
+      <c r="Z242" s="52"/>
       <c r="AA242" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="243">
@@ -21673,19 +22001,19 @@
         <v>58</v>
       </c>
       <c r="C243" s="50">
-        <v>84958</v>
+        <v>74906</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="E243" s="50">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F243" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G243" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I243" s="50" t="s">
         <v>61</v>
@@ -21694,16 +22022,16 @@
         <v>62</v>
       </c>
       <c r="K243" s="50" t="s">
-        <v>301</v>
+        <v>558</v>
       </c>
       <c r="L243" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M243" s="50" t="s">
-        <v>1</v>
+        <v>559</v>
       </c>
       <c r="N243" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O243" s="50">
         <v>0</v>
@@ -21751,16 +22079,16 @@
         <v>58</v>
       </c>
       <c r="C244" s="50">
-        <v>84959</v>
+        <v>74907</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="E244" s="50">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F244" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G244" s="50" t="s">
         <v>60</v>
@@ -21772,7 +22100,7 @@
         <v>62</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>301</v>
+        <v>75</v>
       </c>
       <c r="L244" s="50" t="s">
         <v>1</v>
@@ -21781,7 +22109,7 @@
         <v>1</v>
       </c>
       <c r="N244" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O244" s="50">
         <v>0</v>
@@ -21829,19 +22157,19 @@
         <v>58</v>
       </c>
       <c r="C245" s="50">
-        <v>84960</v>
+        <v>74908</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="E245" s="50">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F245" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I245" s="50" t="s">
         <v>61</v>
@@ -21850,16 +22178,16 @@
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>301</v>
+        <v>558</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M245" s="50" t="s">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="N245" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O245" s="50">
         <v>0</v>
@@ -21907,16 +22235,16 @@
         <v>58</v>
       </c>
       <c r="C246" s="50">
-        <v>84961</v>
+        <v>74909</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="E246" s="50">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F246" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G246" s="50" t="s">
         <v>60</v>
@@ -21928,7 +22256,7 @@
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>301</v>
+        <v>75</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
@@ -21937,7 +22265,7 @@
         <v>1</v>
       </c>
       <c r="N246" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O246" s="50">
         <v>0</v>
@@ -21985,28 +22313,31 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>84962</v>
+        <v>74979</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="E247" s="50">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F247" s="50">
         <v>0</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H247" s="50" t="s">
+        <v>565</v>
       </c>
       <c r="I247" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J247" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>301</v>
+        <v>566</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
@@ -22015,7 +22346,7 @@
         <v>1</v>
       </c>
       <c r="N247" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O247" s="50">
         <v>0</v>
@@ -22063,13 +22394,13 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>84963</v>
+        <v>74982</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="E248" s="50">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F248" s="50">
         <v>0</v>
@@ -22077,14 +22408,17 @@
       <c r="G248" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H248" s="50" t="s">
+        <v>568</v>
+      </c>
       <c r="I248" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J248" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>301</v>
+        <v>569</v>
       </c>
       <c r="L248" s="50" t="s">
         <v>1</v>
@@ -22093,7 +22427,7 @@
         <v>1</v>
       </c>
       <c r="N248" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O248" s="50">
         <v>0</v>
@@ -22141,13 +22475,13 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>84964</v>
+        <v>74984</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="E249" s="50">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F249" s="50">
         <v>0</v>
@@ -22155,14 +22489,17 @@
       <c r="G249" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H249" s="50" t="s">
+        <v>571</v>
+      </c>
       <c r="I249" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J249" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>301</v>
+        <v>569</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22171,7 +22508,7 @@
         <v>1</v>
       </c>
       <c r="N249" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O249" s="50">
         <v>0</v>
@@ -22219,37 +22556,40 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>84965</v>
+        <v>74981</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="E250" s="50">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F250" s="50">
         <v>0</v>
       </c>
       <c r="G250" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
+      </c>
+      <c r="H250" s="50" t="s">
+        <v>573</v>
       </c>
       <c r="I250" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J250" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>301</v>
+        <v>574</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M250" s="50" t="s">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="N250" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O250" s="50">
         <v>0</v>
@@ -22297,37 +22637,40 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>84966</v>
+        <v>74983</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="E251" s="50">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F251" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G251" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H251" s="50" t="s">
+        <v>577</v>
+      </c>
       <c r="I251" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J251" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="L251" s="50" t="s">
-        <v>1</v>
+        <v>578</v>
       </c>
       <c r="M251" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N251" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O251" s="50">
         <v>0</v>
@@ -22375,13 +22718,13 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>84967</v>
+        <v>74985</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="E252" s="50">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F252" s="50">
         <v>0</v>
@@ -22389,14 +22732,17 @@
       <c r="G252" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H252" s="50" t="s">
+        <v>580</v>
+      </c>
       <c r="I252" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J252" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>301</v>
+        <v>569</v>
       </c>
       <c r="L252" s="50" t="s">
         <v>1</v>
@@ -22405,7 +22751,7 @@
         <v>1</v>
       </c>
       <c r="N252" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O252" s="50">
         <v>0</v>
@@ -22453,16 +22799,16 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>84968</v>
+        <v>74988</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>542</v>
+        <v>581</v>
       </c>
       <c r="E253" s="50">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="F253" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G253" s="50" t="s">
         <v>60</v>
@@ -22473,55 +22819,27 @@
       <c r="J253" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K253" s="50" t="s">
-        <v>301</v>
-      </c>
-      <c r="L253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M253" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K253" s="50"/>
+      <c r="L253" s="50"/>
+      <c r="M253" s="50"/>
       <c r="N253" s="50">
-        <v>8</v>
-      </c>
-      <c r="O253" s="50">
-        <v>0</v>
-      </c>
-      <c r="P253" s="50"/>
-      <c r="Q253" s="50">
-        <v>0</v>
-      </c>
-      <c r="R253" s="50">
-        <v>0</v>
-      </c>
-      <c r="S253" s="50">
-        <v>0</v>
-      </c>
-      <c r="T253" s="50">
-        <v>0</v>
-      </c>
-      <c r="U253" s="50">
-        <v>0</v>
-      </c>
-      <c r="V253" s="50">
-        <v>0</v>
-      </c>
-      <c r="W253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y253" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z253" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA253" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O253" s="50"/>
+      <c r="P253" s="50" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q253" s="50"/>
+      <c r="R253" s="50"/>
+      <c r="S253" s="50"/>
+      <c r="T253" s="50"/>
+      <c r="U253" s="50"/>
+      <c r="V253" s="50"/>
+      <c r="W253" s="50"/>
+      <c r="X253" s="50"/>
+      <c r="Y253" s="50"/>
+      <c r="Z253" s="52"/>
+      <c r="AA253" s="50"/>
     </row>
     <row r="254">
       <c r="A254" s="50">
@@ -22531,22 +22849,22 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>84969</v>
+        <v>74991</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="E254" s="50">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F254" s="50">
         <v>0</v>
       </c>
       <c r="G254" s="50" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -22555,7 +22873,7 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>545</v>
+        <v>153</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -22564,7 +22882,7 @@
         <v>1</v>
       </c>
       <c r="N254" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O254" s="50">
         <v>0</v>
@@ -22612,22 +22930,22 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>84970</v>
+        <v>74990</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>546</v>
+        <v>585</v>
       </c>
       <c r="E255" s="50">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F255" s="50">
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
-        <v>547</v>
+        <v>60</v>
       </c>
       <c r="H255" s="50" t="s">
-        <v>548</v>
+        <v>586</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22636,16 +22954,16 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>549</v>
+        <v>124</v>
       </c>
       <c r="L255" s="50" t="s">
-        <v>1</v>
+        <v>587</v>
       </c>
       <c r="M255" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N255" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O255" s="50">
         <v>0</v>
@@ -22693,45 +23011,44 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>84971</v>
+        <v>74989</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="E256" s="50">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F256" s="50">
         <v>0</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H256" s="50" t="s">
-        <v>551</v>
+        <v>60</v>
       </c>
       <c r="I256" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J256" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="L256" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M256" s="50" t="s">
-        <v>553</v>
+        <v>1</v>
       </c>
       <c r="N256" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O256" s="50">
         <v>0</v>
       </c>
-      <c r="P256" s="50"/>
+      <c r="P256" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q256" s="50">
         <v>0</v>
       </c>
@@ -22774,31 +23091,28 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>84972</v>
+        <v>84928</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="E257" s="50">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
-        <v>555</v>
-      </c>
-      <c r="H257" s="50" t="s">
-        <v>556</v>
+        <v>60</v>
       </c>
       <c r="I257" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J257" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>549</v>
+        <v>75</v>
       </c>
       <c r="L257" s="50" t="s">
         <v>1</v>
@@ -22812,7 +23126,9 @@
       <c r="O257" s="50">
         <v>0</v>
       </c>
-      <c r="P257" s="50"/>
+      <c r="P257" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q257" s="50">
         <v>0</v>
       </c>
@@ -22855,22 +23171,22 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>84973</v>
+        <v>84929</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>557</v>
+        <v>590</v>
       </c>
       <c r="E258" s="50">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F258" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G258" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -22879,10 +23195,10 @@
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>192</v>
+        <v>377</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -22936,37 +23252,34 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>84974</v>
+        <v>84930</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="E259" s="50">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F259" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H259" s="50" t="s">
-        <v>561</v>
+        <v>138</v>
       </c>
       <c r="I259" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J259" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>549</v>
+        <v>388</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>1</v>
+        <v>594</v>
       </c>
       <c r="M259" s="50" t="s">
-        <v>1</v>
+        <v>595</v>
       </c>
       <c r="N259" s="50">
         <v>8</v>
@@ -23017,47 +23330,78 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>84976</v>
+        <v>84931</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>562</v>
+        <v>596</v>
       </c>
       <c r="E260" s="50">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F260" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G260" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H260" s="50" t="s">
+        <v>597</v>
       </c>
       <c r="I260" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J260" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K260" s="50"/>
-      <c r="L260" s="50"/>
-      <c r="M260" s="50"/>
+      <c r="K260" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="L260" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M260" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N260" s="50">
         <v>8</v>
       </c>
-      <c r="O260" s="50"/>
-      <c r="P260" s="50" t="s">
-        <v>563</v>
-      </c>
-      <c r="Q260" s="50"/>
-      <c r="R260" s="50"/>
-      <c r="S260" s="50"/>
-      <c r="T260" s="50"/>
-      <c r="U260" s="50"/>
-      <c r="V260" s="50"/>
-      <c r="W260" s="50"/>
-      <c r="X260" s="50"/>
-      <c r="Y260" s="50"/>
-      <c r="Z260" s="52"/>
-      <c r="AA260" s="50"/>
+      <c r="O260" s="50">
+        <v>0</v>
+      </c>
+      <c r="P260" s="50"/>
+      <c r="Q260" s="50">
+        <v>0</v>
+      </c>
+      <c r="R260" s="50">
+        <v>0</v>
+      </c>
+      <c r="S260" s="50">
+        <v>0</v>
+      </c>
+      <c r="T260" s="50">
+        <v>0</v>
+      </c>
+      <c r="U260" s="50">
+        <v>0</v>
+      </c>
+      <c r="V260" s="50">
+        <v>0</v>
+      </c>
+      <c r="W260" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X260" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y260" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z260" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA260" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="50">
@@ -23067,16 +23411,16 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>84977</v>
+        <v>84932</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>564</v>
+        <v>598</v>
       </c>
       <c r="E261" s="50">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F261" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G261" s="50" t="s">
         <v>60</v>
@@ -23087,27 +23431,55 @@
       <c r="J261" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K261" s="50"/>
-      <c r="L261" s="50"/>
-      <c r="M261" s="50"/>
+      <c r="K261" s="50" t="s">
+        <v>388</v>
+      </c>
+      <c r="L261" s="50" t="s">
+        <v>599</v>
+      </c>
+      <c r="M261" s="50" t="s">
+        <v>595</v>
+      </c>
       <c r="N261" s="50">
         <v>8</v>
       </c>
-      <c r="O261" s="50"/>
-      <c r="P261" s="50" t="s">
-        <v>565</v>
-      </c>
-      <c r="Q261" s="50"/>
-      <c r="R261" s="50"/>
-      <c r="S261" s="50"/>
-      <c r="T261" s="50"/>
-      <c r="U261" s="50"/>
-      <c r="V261" s="50"/>
-      <c r="W261" s="50"/>
-      <c r="X261" s="50"/>
-      <c r="Y261" s="50"/>
-      <c r="Z261" s="52"/>
-      <c r="AA261" s="50"/>
+      <c r="O261" s="50">
+        <v>0</v>
+      </c>
+      <c r="P261" s="50"/>
+      <c r="Q261" s="50">
+        <v>0</v>
+      </c>
+      <c r="R261" s="50">
+        <v>0</v>
+      </c>
+      <c r="S261" s="50">
+        <v>0</v>
+      </c>
+      <c r="T261" s="50">
+        <v>0</v>
+      </c>
+      <c r="U261" s="50">
+        <v>0</v>
+      </c>
+      <c r="V261" s="50">
+        <v>0</v>
+      </c>
+      <c r="W261" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X261" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y261" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z261" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA261" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="50">
@@ -23117,47 +23489,78 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>84978</v>
+        <v>84933</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>566</v>
+        <v>600</v>
       </c>
       <c r="E262" s="50">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F262" s="50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G262" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H262" s="50" t="s">
+        <v>601</v>
+      </c>
       <c r="I262" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J262" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K262" s="50"/>
-      <c r="L262" s="50"/>
-      <c r="M262" s="50"/>
+      <c r="K262" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="L262" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M262" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N262" s="50">
         <v>8</v>
       </c>
-      <c r="O262" s="50"/>
-      <c r="P262" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q262" s="50"/>
-      <c r="R262" s="50"/>
-      <c r="S262" s="50"/>
-      <c r="T262" s="50"/>
-      <c r="U262" s="50"/>
-      <c r="V262" s="50"/>
-      <c r="W262" s="50"/>
-      <c r="X262" s="50"/>
-      <c r="Y262" s="50"/>
-      <c r="Z262" s="52"/>
-      <c r="AA262" s="50"/>
+      <c r="O262" s="50">
+        <v>0</v>
+      </c>
+      <c r="P262" s="50"/>
+      <c r="Q262" s="50">
+        <v>0</v>
+      </c>
+      <c r="R262" s="50">
+        <v>0</v>
+      </c>
+      <c r="S262" s="50">
+        <v>0</v>
+      </c>
+      <c r="T262" s="50">
+        <v>0</v>
+      </c>
+      <c r="U262" s="50">
+        <v>0</v>
+      </c>
+      <c r="V262" s="50">
+        <v>0</v>
+      </c>
+      <c r="W262" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X262" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y262" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z262" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA262" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="50">
@@ -23167,22 +23570,22 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>84979</v>
+        <v>84934</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>568</v>
+        <v>602</v>
       </c>
       <c r="E263" s="50">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F263" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H263" s="50" t="s">
-        <v>569</v>
+        <v>603</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>78</v>
@@ -23191,13 +23594,13 @@
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>327</v>
+        <v>398</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>570</v>
+        <v>1</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23248,22 +23651,22 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>84980</v>
+        <v>84935</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="E264" s="50">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F264" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G264" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23272,10 +23675,10 @@
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>324</v>
+        <v>403</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>574</v>
+        <v>1</v>
       </c>
       <c r="M264" s="50" t="s">
         <v>1</v>
@@ -23329,22 +23732,22 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>84981</v>
+        <v>84936</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="E265" s="50">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F265" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23353,7 +23756,7 @@
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>331</v>
+        <v>400</v>
       </c>
       <c r="L265" s="50" t="s">
         <v>1</v>
@@ -23384,7 +23787,7 @@
         <v>0</v>
       </c>
       <c r="V265" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W265" s="50" t="s">
         <v>1</v>
@@ -23410,34 +23813,37 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>84982</v>
+        <v>84937</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
       <c r="E266" s="50">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F266" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G266" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H266" s="50" t="s">
+        <v>609</v>
       </c>
       <c r="I266" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J266" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>578</v>
+        <v>396</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M266" s="50" t="s">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="N266" s="50">
         <v>8</v>
@@ -23445,9 +23851,7 @@
       <c r="O266" s="50">
         <v>0</v>
       </c>
-      <c r="P266" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P266" s="50"/>
       <c r="Q266" s="50">
         <v>0</v>
       </c>
@@ -23464,7 +23868,7 @@
         <v>0</v>
       </c>
       <c r="V266" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W266" s="50" t="s">
         <v>1</v>
@@ -23490,22 +23894,22 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>84983</v>
+        <v>84938</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="E267" s="50">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F267" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23514,7 +23918,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>581</v>
+        <v>386</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23528,9 +23932,7 @@
       <c r="O267" s="50">
         <v>0</v>
       </c>
-      <c r="P267" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P267" s="50"/>
       <c r="Q267" s="50">
         <v>0</v>
       </c>
@@ -23573,13 +23975,13 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>84984</v>
+        <v>84939</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="E268" s="50">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F268" s="50">
         <v>0</v>
@@ -23588,7 +23990,7 @@
         <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23597,7 +23999,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>584</v>
+        <v>394</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -23611,9 +24013,7 @@
       <c r="O268" s="50">
         <v>0</v>
       </c>
-      <c r="P268" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P268" s="50"/>
       <c r="Q268" s="50">
         <v>0</v>
       </c>
@@ -23656,22 +24056,22 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>330037</v>
+        <v>84940</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="E269" s="50">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F269" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G269" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -23680,7 +24080,7 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>96</v>
+        <v>394</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -23689,14 +24089,12 @@
         <v>1</v>
       </c>
       <c r="N269" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O269" s="50">
         <v>0</v>
       </c>
-      <c r="P269" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P269" s="50"/>
       <c r="Q269" s="50">
         <v>0</v>
       </c>
@@ -23706,8 +24104,8 @@
       <c r="S269" s="50">
         <v>0</v>
       </c>
-      <c r="T269" s="50" t="s">
-        <v>61</v>
+      <c r="T269" s="50">
+        <v>0</v>
       </c>
       <c r="U269" s="50">
         <v>0</v>
@@ -23739,22 +24137,22 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>330038</v>
+        <v>84941</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="E270" s="50">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F270" s="50">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -23763,16 +24161,16 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="L270" s="50" t="s">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="M270" s="50" t="s">
-        <v>589</v>
+        <v>1</v>
       </c>
       <c r="N270" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O270" s="50">
         <v>0</v>
@@ -23820,40 +24218,37 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>330039</v>
+        <v>84942</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="E271" s="50">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="F271" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G271" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H271" s="50" t="s">
-        <v>591</v>
+        <v>60</v>
       </c>
       <c r="I271" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J271" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>147</v>
+        <v>285</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="M271" s="50" t="s">
-        <v>1</v>
+        <v>621</v>
       </c>
       <c r="N271" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O271" s="50">
         <v>0</v>
@@ -23901,22 +24296,22 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>330040</v>
+        <v>84943</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="E272" s="50">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F272" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G272" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -23925,16 +24320,16 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>592</v>
+        <v>1</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N272" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O272" s="50">
         <v>0</v>
@@ -23982,40 +24377,37 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>330041</v>
+        <v>84944</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="E273" s="50">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="F273" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G273" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H273" s="50" t="s">
-        <v>596</v>
+        <v>60</v>
       </c>
       <c r="I273" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J273" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>147</v>
+        <v>271</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="M273" s="50" t="s">
-        <v>1</v>
+        <v>621</v>
       </c>
       <c r="N273" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O273" s="50">
         <v>0</v>
@@ -24063,22 +24455,22 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>330042</v>
+        <v>84945</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="E274" s="50">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F274" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G274" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24087,16 +24479,16 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>599</v>
+        <v>1</v>
       </c>
       <c r="M274" s="50" t="s">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="N274" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O274" s="50">
         <v>0</v>
@@ -24144,13 +24536,13 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>330043</v>
+        <v>84946</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="E275" s="50">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F275" s="50">
         <v>1</v>
@@ -24158,17 +24550,14 @@
       <c r="G275" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H275" s="50" t="s">
-        <v>602</v>
-      </c>
       <c r="I275" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J275" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>238</v>
+        <v>629</v>
       </c>
       <c r="L275" s="50" t="s">
         <v>1</v>
@@ -24177,7 +24566,7 @@
         <v>1</v>
       </c>
       <c r="N275" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O275" s="50">
         <v>0</v>
@@ -24225,40 +24614,37 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>330044</v>
+        <v>84947</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="E276" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F276" s="50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H276" s="50" t="s">
-        <v>604</v>
-      </c>
       <c r="I276" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J276" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="L276" s="50" t="s">
-        <v>605</v>
+        <v>1</v>
       </c>
       <c r="M276" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N276" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O276" s="50">
         <v>0</v>
@@ -24306,31 +24692,28 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>330045</v>
+        <v>84948</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="E277" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F277" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G277" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H277" s="50" t="s">
-        <v>607</v>
+        <v>60</v>
       </c>
       <c r="I277" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J277" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L277" s="50" t="s">
         <v>1</v>
@@ -24339,14 +24722,12 @@
         <v>1</v>
       </c>
       <c r="N277" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O277" s="50">
         <v>0</v>
       </c>
-      <c r="P277" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P277" s="50"/>
       <c r="Q277" s="50">
         <v>0</v>
       </c>
@@ -24356,8 +24737,8 @@
       <c r="S277" s="50">
         <v>0</v>
       </c>
-      <c r="T277" s="50" t="s">
-        <v>61</v>
+      <c r="T277" s="50">
+        <v>0</v>
       </c>
       <c r="U277" s="50">
         <v>0</v>
@@ -24389,40 +24770,37 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>330046</v>
+        <v>84949</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="E278" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F278" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G278" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H278" s="50" t="s">
-        <v>609</v>
+        <v>60</v>
       </c>
       <c r="I278" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J278" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>461</v>
+        <v>301</v>
       </c>
       <c r="L278" s="50" t="s">
-        <v>610</v>
+        <v>1</v>
       </c>
       <c r="M278" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N278" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O278" s="50">
         <v>0</v>
@@ -24470,31 +24848,28 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>330047</v>
+        <v>84950</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="E279" s="50">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F279" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G279" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H279" s="50" t="s">
-        <v>612</v>
-      </c>
       <c r="I279" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J279" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>465</v>
+        <v>301</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24503,7 +24878,7 @@
         <v>1</v>
       </c>
       <c r="N279" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O279" s="50">
         <v>0</v>
@@ -24551,31 +24926,28 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>330048</v>
+        <v>84951</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="E280" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F280" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G280" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H280" s="50" t="s">
-        <v>614</v>
-      </c>
       <c r="I280" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J280" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K280" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L280" s="50" t="s">
         <v>1</v>
@@ -24584,14 +24956,12 @@
         <v>1</v>
       </c>
       <c r="N280" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O280" s="50">
         <v>0</v>
       </c>
-      <c r="P280" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P280" s="50"/>
       <c r="Q280" s="50">
         <v>0</v>
       </c>
@@ -24601,8 +24971,8 @@
       <c r="S280" s="50">
         <v>0</v>
       </c>
-      <c r="T280" s="50" t="s">
-        <v>61</v>
+      <c r="T280" s="50">
+        <v>0</v>
       </c>
       <c r="U280" s="50">
         <v>0</v>
@@ -24634,13 +25004,13 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>330049</v>
+        <v>84952</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="E281" s="50">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F281" s="50">
         <v>0</v>
@@ -24648,26 +25018,23 @@
       <c r="G281" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H281" s="50" t="s">
-        <v>616</v>
-      </c>
       <c r="I281" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J281" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K281" s="50" t="s">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="L281" s="50" t="s">
-        <v>617</v>
+        <v>1</v>
       </c>
       <c r="M281" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N281" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O281" s="50">
         <v>0</v>
@@ -24715,13 +25082,13 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>330050</v>
+        <v>84953</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="E282" s="50">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F282" s="50">
         <v>0</v>
@@ -24729,17 +25096,14 @@
       <c r="G282" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H282" s="50" t="s">
-        <v>619</v>
-      </c>
       <c r="I282" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J282" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K282" s="50" t="s">
-        <v>88</v>
+        <v>301</v>
       </c>
       <c r="L282" s="50" t="s">
         <v>1</v>
@@ -24748,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="N282" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O282" s="50">
         <v>0</v>
@@ -24796,31 +25160,28 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>330051</v>
+        <v>84954</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="E283" s="50">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F283" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G283" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H283" s="50" t="s">
-        <v>621</v>
+        <v>60</v>
       </c>
       <c r="I283" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J283" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K283" s="50" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="L283" s="50" t="s">
         <v>1</v>
@@ -24829,14 +25190,12 @@
         <v>1</v>
       </c>
       <c r="N283" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O283" s="50">
         <v>0</v>
       </c>
-      <c r="P283" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P283" s="50"/>
       <c r="Q283" s="50">
         <v>0</v>
       </c>
@@ -24879,31 +25238,28 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>330052</v>
+        <v>84955</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="E284" s="50">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F284" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G284" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H284" s="50" t="s">
-        <v>623</v>
+        <v>60</v>
       </c>
       <c r="I284" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J284" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K284" s="50" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="L284" s="50" t="s">
         <v>1</v>
@@ -24912,14 +25268,12 @@
         <v>1</v>
       </c>
       <c r="N284" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O284" s="50">
         <v>0</v>
       </c>
-      <c r="P284" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P284" s="50"/>
       <c r="Q284" s="50">
         <v>0</v>
       </c>
@@ -24962,31 +25316,28 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>330053</v>
+        <v>84956</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="E285" s="50">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F285" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G285" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H285" s="50" t="s">
-        <v>625</v>
-      </c>
       <c r="I285" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J285" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K285" s="50" t="s">
-        <v>246</v>
+        <v>301</v>
       </c>
       <c r="L285" s="50" t="s">
         <v>1</v>
@@ -24995,14 +25346,12 @@
         <v>1</v>
       </c>
       <c r="N285" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O285" s="50">
         <v>0</v>
       </c>
-      <c r="P285" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P285" s="50"/>
       <c r="Q285" s="50">
         <v>0</v>
       </c>
@@ -25045,31 +25394,28 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>330054</v>
+        <v>84957</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="E286" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F286" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G286" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H286" s="50" t="s">
-        <v>627</v>
-      </c>
       <c r="I286" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J286" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K286" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L286" s="50" t="s">
         <v>1</v>
@@ -25078,14 +25424,12 @@
         <v>1</v>
       </c>
       <c r="N286" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O286" s="50">
         <v>0</v>
       </c>
-      <c r="P286" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P286" s="50"/>
       <c r="Q286" s="50">
         <v>0</v>
       </c>
@@ -25095,8 +25439,8 @@
       <c r="S286" s="50">
         <v>0</v>
       </c>
-      <c r="T286" s="50" t="s">
-        <v>61</v>
+      <c r="T286" s="50">
+        <v>0</v>
       </c>
       <c r="U286" s="50">
         <v>0</v>
@@ -25128,31 +25472,28 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>330055</v>
+        <v>84958</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="E287" s="50">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F287" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G287" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H287" s="50" t="s">
-        <v>629</v>
+        <v>60</v>
       </c>
       <c r="I287" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J287" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K287" s="50" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="L287" s="50" t="s">
         <v>1</v>
@@ -25161,14 +25502,12 @@
         <v>1</v>
       </c>
       <c r="N287" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O287" s="50">
         <v>0</v>
       </c>
-      <c r="P287" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P287" s="50"/>
       <c r="Q287" s="50">
         <v>0</v>
       </c>
@@ -25211,31 +25550,28 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>330056</v>
+        <v>84959</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="E288" s="50">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F288" s="50">
         <v>0</v>
       </c>
       <c r="G288" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H288" s="50" t="s">
-        <v>631</v>
+        <v>60</v>
       </c>
       <c r="I288" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J288" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K288" s="50" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="L288" s="50" t="s">
         <v>1</v>
@@ -25244,14 +25580,12 @@
         <v>1</v>
       </c>
       <c r="N288" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O288" s="50">
         <v>0</v>
       </c>
-      <c r="P288" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P288" s="50"/>
       <c r="Q288" s="50">
         <v>0</v>
       </c>
@@ -25294,31 +25628,28 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>330058</v>
+        <v>84960</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="E289" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F289" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G289" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H289" s="50" t="s">
-        <v>633</v>
+        <v>60</v>
       </c>
       <c r="I289" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J289" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -25327,14 +25658,12 @@
         <v>1</v>
       </c>
       <c r="N289" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O289" s="50">
         <v>0</v>
       </c>
-      <c r="P289" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P289" s="50"/>
       <c r="Q289" s="50">
         <v>0</v>
       </c>
@@ -25344,8 +25673,8 @@
       <c r="S289" s="50">
         <v>0</v>
       </c>
-      <c r="T289" s="50" t="s">
-        <v>61</v>
+      <c r="T289" s="50">
+        <v>0</v>
       </c>
       <c r="U289" s="50">
         <v>0</v>
@@ -25377,13 +25706,13 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>330061</v>
+        <v>84961</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="E290" s="50">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F290" s="50">
         <v>0</v>
@@ -25391,17 +25720,14 @@
       <c r="G290" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H290" s="50" t="s">
-        <v>635</v>
-      </c>
       <c r="I290" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J290" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>636</v>
+        <v>301</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -25410,14 +25736,12 @@
         <v>1</v>
       </c>
       <c r="N290" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O290" s="50">
         <v>0</v>
       </c>
-      <c r="P290" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P290" s="50"/>
       <c r="Q290" s="50">
         <v>0</v>
       </c>
@@ -25460,13 +25784,13 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>330062</v>
+        <v>84962</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="E291" s="50">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F291" s="50">
         <v>0</v>
@@ -25474,17 +25798,14 @@
       <c r="G291" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H291" s="50" t="s">
-        <v>638</v>
-      </c>
       <c r="I291" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J291" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>639</v>
+        <v>301</v>
       </c>
       <c r="L291" s="50" t="s">
         <v>1</v>
@@ -25493,14 +25814,12 @@
         <v>1</v>
       </c>
       <c r="N291" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O291" s="50">
         <v>0</v>
       </c>
-      <c r="P291" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P291" s="50"/>
       <c r="Q291" s="50">
         <v>0</v>
       </c>
@@ -25543,13 +25862,13 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>330063</v>
+        <v>84963</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="E292" s="50">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="F292" s="50">
         <v>0</v>
@@ -25557,33 +25876,28 @@
       <c r="G292" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H292" s="50" t="s">
-        <v>641</v>
-      </c>
       <c r="I292" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J292" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K292" s="50" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="L292" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M292" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N292" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O292" s="50">
         <v>0</v>
       </c>
-      <c r="P292" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P292" s="50"/>
       <c r="Q292" s="50">
         <v>0</v>
       </c>
@@ -25626,47 +25940,42 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>330064</v>
+        <v>84964</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E293" s="50">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F293" s="50">
         <v>0</v>
       </c>
       <c r="G293" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H293" s="50" t="s">
-        <v>643</v>
+        <v>60</v>
       </c>
       <c r="I293" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J293" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>180</v>
+        <v>301</v>
       </c>
       <c r="L293" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M293" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N293" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O293" s="50">
         <v>0</v>
       </c>
-      <c r="P293" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P293" s="50"/>
       <c r="Q293" s="50">
         <v>0</v>
       </c>
@@ -25709,31 +26018,28 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>330065</v>
+        <v>84965</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E294" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F294" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G294" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H294" s="50" t="s">
-        <v>645</v>
-      </c>
       <c r="I294" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J294" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L294" s="50" t="s">
         <v>1</v>
@@ -25742,14 +26048,12 @@
         <v>1</v>
       </c>
       <c r="N294" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O294" s="50">
         <v>0</v>
       </c>
-      <c r="P294" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P294" s="50"/>
       <c r="Q294" s="50">
         <v>0</v>
       </c>
@@ -25759,8 +26063,8 @@
       <c r="S294" s="50">
         <v>0</v>
       </c>
-      <c r="T294" s="50" t="s">
-        <v>61</v>
+      <c r="T294" s="50">
+        <v>0</v>
       </c>
       <c r="U294" s="50">
         <v>0</v>
@@ -25792,31 +26096,28 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>330067</v>
+        <v>84966</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E295" s="50">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F295" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G295" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H295" s="50" t="s">
-        <v>647</v>
-      </c>
       <c r="I295" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J295" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K295" s="50" t="s">
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="L295" s="50" t="s">
         <v>1</v>
@@ -25825,14 +26126,12 @@
         <v>1</v>
       </c>
       <c r="N295" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O295" s="50">
         <v>0</v>
       </c>
-      <c r="P295" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P295" s="50"/>
       <c r="Q295" s="50">
         <v>0</v>
       </c>
@@ -25875,31 +26174,28 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>330068</v>
+        <v>84967</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E296" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F296" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H296" s="50" t="s">
-        <v>649</v>
+        <v>60</v>
       </c>
       <c r="I296" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J296" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L296" s="50" t="s">
         <v>1</v>
@@ -25908,14 +26204,12 @@
         <v>1</v>
       </c>
       <c r="N296" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O296" s="50">
         <v>0</v>
       </c>
-      <c r="P296" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P296" s="50"/>
       <c r="Q296" s="50">
         <v>0</v>
       </c>
@@ -25925,8 +26219,8 @@
       <c r="S296" s="50">
         <v>0</v>
       </c>
-      <c r="T296" s="50" t="s">
-        <v>61</v>
+      <c r="T296" s="50">
+        <v>0</v>
       </c>
       <c r="U296" s="50">
         <v>0</v>
@@ -25958,40 +26252,37 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>330069</v>
+        <v>84968</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E297" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F297" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G297" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H297" s="50" t="s">
-        <v>651</v>
-      </c>
       <c r="I297" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J297" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="L297" s="50" t="s">
-        <v>652</v>
+        <v>1</v>
       </c>
       <c r="M297" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N297" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O297" s="50">
         <v>0</v>
@@ -26039,22 +26330,22 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>330070</v>
+        <v>84969</v>
       </c>
       <c r="D298" s="50" t="s">
+        <v>652</v>
+      </c>
+      <c r="E298" s="50">
+        <v>45</v>
+      </c>
+      <c r="F298" s="50">
+        <v>0</v>
+      </c>
+      <c r="G298" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H298" s="50" t="s">
         <v>653</v>
-      </c>
-      <c r="E298" s="50">
-        <v>3</v>
-      </c>
-      <c r="F298" s="50">
-        <v>1</v>
-      </c>
-      <c r="G298" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H298" s="50" t="s">
-        <v>654</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>
@@ -26063,7 +26354,7 @@
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>254</v>
+        <v>566</v>
       </c>
       <c r="L298" s="50" t="s">
         <v>1</v>
@@ -26072,7 +26363,7 @@
         <v>1</v>
       </c>
       <c r="N298" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O298" s="50">
         <v>0</v>
@@ -26109,6 +26400,3514 @@
         <v>0</v>
       </c>
       <c r="AA298" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="50">
+        <v>294</v>
+      </c>
+      <c r="B299" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C299" s="50">
+        <v>84970</v>
+      </c>
+      <c r="D299" s="50" t="s">
+        <v>654</v>
+      </c>
+      <c r="E299" s="50">
+        <v>46</v>
+      </c>
+      <c r="F299" s="50">
+        <v>0</v>
+      </c>
+      <c r="G299" s="50" t="s">
+        <v>655</v>
+      </c>
+      <c r="H299" s="50" t="s">
+        <v>656</v>
+      </c>
+      <c r="I299" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J299" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K299" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="L299" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M299" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N299" s="50">
+        <v>8</v>
+      </c>
+      <c r="O299" s="50">
+        <v>0</v>
+      </c>
+      <c r="P299" s="50"/>
+      <c r="Q299" s="50">
+        <v>0</v>
+      </c>
+      <c r="R299" s="50">
+        <v>0</v>
+      </c>
+      <c r="S299" s="50">
+        <v>0</v>
+      </c>
+      <c r="T299" s="50">
+        <v>0</v>
+      </c>
+      <c r="U299" s="50">
+        <v>0</v>
+      </c>
+      <c r="V299" s="50">
+        <v>0</v>
+      </c>
+      <c r="W299" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X299" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y299" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z299" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA299" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="50">
+        <v>295</v>
+      </c>
+      <c r="B300" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C300" s="50">
+        <v>84971</v>
+      </c>
+      <c r="D300" s="50" t="s">
+        <v>657</v>
+      </c>
+      <c r="E300" s="50">
+        <v>47</v>
+      </c>
+      <c r="F300" s="50">
+        <v>0</v>
+      </c>
+      <c r="G300" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H300" s="50" t="s">
+        <v>658</v>
+      </c>
+      <c r="I300" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J300" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K300" s="50" t="s">
+        <v>574</v>
+      </c>
+      <c r="L300" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M300" s="50" t="s">
+        <v>659</v>
+      </c>
+      <c r="N300" s="50">
+        <v>8</v>
+      </c>
+      <c r="O300" s="50">
+        <v>0</v>
+      </c>
+      <c r="P300" s="50"/>
+      <c r="Q300" s="50">
+        <v>0</v>
+      </c>
+      <c r="R300" s="50">
+        <v>0</v>
+      </c>
+      <c r="S300" s="50">
+        <v>0</v>
+      </c>
+      <c r="T300" s="50">
+        <v>0</v>
+      </c>
+      <c r="U300" s="50">
+        <v>0</v>
+      </c>
+      <c r="V300" s="50">
+        <v>0</v>
+      </c>
+      <c r="W300" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X300" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y300" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z300" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA300" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="50">
+        <v>296</v>
+      </c>
+      <c r="B301" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C301" s="50">
+        <v>84972</v>
+      </c>
+      <c r="D301" s="50" t="s">
+        <v>660</v>
+      </c>
+      <c r="E301" s="50">
+        <v>46</v>
+      </c>
+      <c r="F301" s="50">
+        <v>0</v>
+      </c>
+      <c r="G301" s="50" t="s">
+        <v>661</v>
+      </c>
+      <c r="H301" s="50" t="s">
+        <v>662</v>
+      </c>
+      <c r="I301" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J301" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K301" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="L301" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M301" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N301" s="50">
+        <v>8</v>
+      </c>
+      <c r="O301" s="50">
+        <v>0</v>
+      </c>
+      <c r="P301" s="50"/>
+      <c r="Q301" s="50">
+        <v>0</v>
+      </c>
+      <c r="R301" s="50">
+        <v>0</v>
+      </c>
+      <c r="S301" s="50">
+        <v>0</v>
+      </c>
+      <c r="T301" s="50">
+        <v>0</v>
+      </c>
+      <c r="U301" s="50">
+        <v>0</v>
+      </c>
+      <c r="V301" s="50">
+        <v>0</v>
+      </c>
+      <c r="W301" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X301" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y301" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z301" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA301" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="50">
+        <v>297</v>
+      </c>
+      <c r="B302" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C302" s="50">
+        <v>84973</v>
+      </c>
+      <c r="D302" s="50" t="s">
+        <v>663</v>
+      </c>
+      <c r="E302" s="50">
+        <v>16</v>
+      </c>
+      <c r="F302" s="50">
+        <v>7</v>
+      </c>
+      <c r="G302" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H302" s="50" t="s">
+        <v>664</v>
+      </c>
+      <c r="I302" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J302" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K302" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L302" s="50" t="s">
+        <v>665</v>
+      </c>
+      <c r="M302" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N302" s="50">
+        <v>8</v>
+      </c>
+      <c r="O302" s="50">
+        <v>0</v>
+      </c>
+      <c r="P302" s="50"/>
+      <c r="Q302" s="50">
+        <v>0</v>
+      </c>
+      <c r="R302" s="50">
+        <v>0</v>
+      </c>
+      <c r="S302" s="50">
+        <v>0</v>
+      </c>
+      <c r="T302" s="50">
+        <v>0</v>
+      </c>
+      <c r="U302" s="50">
+        <v>0</v>
+      </c>
+      <c r="V302" s="50">
+        <v>0</v>
+      </c>
+      <c r="W302" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X302" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y302" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z302" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA302" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="50">
+        <v>298</v>
+      </c>
+      <c r="B303" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C303" s="50">
+        <v>84974</v>
+      </c>
+      <c r="D303" s="50" t="s">
+        <v>666</v>
+      </c>
+      <c r="E303" s="50">
+        <v>46</v>
+      </c>
+      <c r="F303" s="50">
+        <v>0</v>
+      </c>
+      <c r="G303" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H303" s="50" t="s">
+        <v>667</v>
+      </c>
+      <c r="I303" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J303" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K303" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="L303" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M303" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N303" s="50">
+        <v>8</v>
+      </c>
+      <c r="O303" s="50">
+        <v>0</v>
+      </c>
+      <c r="P303" s="50"/>
+      <c r="Q303" s="50">
+        <v>0</v>
+      </c>
+      <c r="R303" s="50">
+        <v>0</v>
+      </c>
+      <c r="S303" s="50">
+        <v>0</v>
+      </c>
+      <c r="T303" s="50">
+        <v>0</v>
+      </c>
+      <c r="U303" s="50">
+        <v>0</v>
+      </c>
+      <c r="V303" s="50">
+        <v>0</v>
+      </c>
+      <c r="W303" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X303" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y303" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z303" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA303" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="50">
+        <v>299</v>
+      </c>
+      <c r="B304" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C304" s="50">
+        <v>84976</v>
+      </c>
+      <c r="D304" s="50" t="s">
+        <v>668</v>
+      </c>
+      <c r="E304" s="50">
+        <v>2</v>
+      </c>
+      <c r="F304" s="50">
+        <v>2</v>
+      </c>
+      <c r="G304" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I304" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J304" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K304" s="50"/>
+      <c r="L304" s="50"/>
+      <c r="M304" s="50"/>
+      <c r="N304" s="50">
+        <v>8</v>
+      </c>
+      <c r="O304" s="50"/>
+      <c r="P304" s="50" t="s">
+        <v>669</v>
+      </c>
+      <c r="Q304" s="50"/>
+      <c r="R304" s="50"/>
+      <c r="S304" s="50"/>
+      <c r="T304" s="50"/>
+      <c r="U304" s="50"/>
+      <c r="V304" s="50"/>
+      <c r="W304" s="50"/>
+      <c r="X304" s="50"/>
+      <c r="Y304" s="50"/>
+      <c r="Z304" s="52"/>
+      <c r="AA304" s="50"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="50">
+        <v>300</v>
+      </c>
+      <c r="B305" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C305" s="50">
+        <v>84977</v>
+      </c>
+      <c r="D305" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="E305" s="50">
+        <v>2</v>
+      </c>
+      <c r="F305" s="50">
+        <v>3</v>
+      </c>
+      <c r="G305" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I305" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J305" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K305" s="50"/>
+      <c r="L305" s="50"/>
+      <c r="M305" s="50"/>
+      <c r="N305" s="50">
+        <v>8</v>
+      </c>
+      <c r="O305" s="50"/>
+      <c r="P305" s="50" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q305" s="50"/>
+      <c r="R305" s="50"/>
+      <c r="S305" s="50"/>
+      <c r="T305" s="50"/>
+      <c r="U305" s="50"/>
+      <c r="V305" s="50"/>
+      <c r="W305" s="50"/>
+      <c r="X305" s="50"/>
+      <c r="Y305" s="50"/>
+      <c r="Z305" s="52"/>
+      <c r="AA305" s="50"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="50">
+        <v>301</v>
+      </c>
+      <c r="B306" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C306" s="50">
+        <v>84978</v>
+      </c>
+      <c r="D306" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="E306" s="50">
+        <v>2</v>
+      </c>
+      <c r="F306" s="50">
+        <v>4</v>
+      </c>
+      <c r="G306" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I306" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J306" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K306" s="50"/>
+      <c r="L306" s="50"/>
+      <c r="M306" s="50"/>
+      <c r="N306" s="50">
+        <v>8</v>
+      </c>
+      <c r="O306" s="50"/>
+      <c r="P306" s="50" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q306" s="50"/>
+      <c r="R306" s="50"/>
+      <c r="S306" s="50"/>
+      <c r="T306" s="50"/>
+      <c r="U306" s="50"/>
+      <c r="V306" s="50"/>
+      <c r="W306" s="50"/>
+      <c r="X306" s="50"/>
+      <c r="Y306" s="50"/>
+      <c r="Z306" s="52"/>
+      <c r="AA306" s="50"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="50">
+        <v>302</v>
+      </c>
+      <c r="B307" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C307" s="50">
+        <v>84979</v>
+      </c>
+      <c r="D307" s="50" t="s">
+        <v>674</v>
+      </c>
+      <c r="E307" s="50">
+        <v>48</v>
+      </c>
+      <c r="F307" s="50">
+        <v>0</v>
+      </c>
+      <c r="G307" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H307" s="50" t="s">
+        <v>675</v>
+      </c>
+      <c r="I307" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J307" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K307" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="L307" s="50" t="s">
+        <v>676</v>
+      </c>
+      <c r="M307" s="50" t="s">
+        <v>677</v>
+      </c>
+      <c r="N307" s="50">
+        <v>8</v>
+      </c>
+      <c r="O307" s="50">
+        <v>0</v>
+      </c>
+      <c r="P307" s="50"/>
+      <c r="Q307" s="50">
+        <v>0</v>
+      </c>
+      <c r="R307" s="50">
+        <v>0</v>
+      </c>
+      <c r="S307" s="50">
+        <v>0</v>
+      </c>
+      <c r="T307" s="50">
+        <v>0</v>
+      </c>
+      <c r="U307" s="50">
+        <v>0</v>
+      </c>
+      <c r="V307" s="50">
+        <v>0</v>
+      </c>
+      <c r="W307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z307" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA307" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="50">
+        <v>303</v>
+      </c>
+      <c r="B308" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C308" s="50">
+        <v>84980</v>
+      </c>
+      <c r="D308" s="50" t="s">
+        <v>678</v>
+      </c>
+      <c r="E308" s="50">
+        <v>49</v>
+      </c>
+      <c r="F308" s="50">
+        <v>0</v>
+      </c>
+      <c r="G308" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H308" s="50" t="s">
+        <v>679</v>
+      </c>
+      <c r="I308" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J308" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K308" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="L308" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="M308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N308" s="50">
+        <v>8</v>
+      </c>
+      <c r="O308" s="50">
+        <v>0</v>
+      </c>
+      <c r="P308" s="50"/>
+      <c r="Q308" s="50">
+        <v>0</v>
+      </c>
+      <c r="R308" s="50">
+        <v>0</v>
+      </c>
+      <c r="S308" s="50">
+        <v>0</v>
+      </c>
+      <c r="T308" s="50">
+        <v>0</v>
+      </c>
+      <c r="U308" s="50">
+        <v>0</v>
+      </c>
+      <c r="V308" s="50">
+        <v>0</v>
+      </c>
+      <c r="W308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z308" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="50">
+        <v>304</v>
+      </c>
+      <c r="B309" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C309" s="50">
+        <v>84981</v>
+      </c>
+      <c r="D309" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="E309" s="50">
+        <v>50</v>
+      </c>
+      <c r="F309" s="50">
+        <v>0</v>
+      </c>
+      <c r="G309" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H309" s="50" t="s">
+        <v>682</v>
+      </c>
+      <c r="I309" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J309" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K309" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="L309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N309" s="50">
+        <v>8</v>
+      </c>
+      <c r="O309" s="50">
+        <v>0</v>
+      </c>
+      <c r="P309" s="50"/>
+      <c r="Q309" s="50">
+        <v>0</v>
+      </c>
+      <c r="R309" s="50">
+        <v>0</v>
+      </c>
+      <c r="S309" s="50">
+        <v>0</v>
+      </c>
+      <c r="T309" s="50">
+        <v>0</v>
+      </c>
+      <c r="U309" s="50">
+        <v>0</v>
+      </c>
+      <c r="V309" s="50">
+        <v>0</v>
+      </c>
+      <c r="W309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z309" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="50">
+        <v>305</v>
+      </c>
+      <c r="B310" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C310" s="50">
+        <v>84982</v>
+      </c>
+      <c r="D310" s="50" t="s">
+        <v>683</v>
+      </c>
+      <c r="E310" s="50">
+        <v>23</v>
+      </c>
+      <c r="F310" s="50">
+        <v>0</v>
+      </c>
+      <c r="G310" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I310" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J310" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K310" s="50" t="s">
+        <v>684</v>
+      </c>
+      <c r="L310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M310" s="50" t="s">
+        <v>685</v>
+      </c>
+      <c r="N310" s="50">
+        <v>8</v>
+      </c>
+      <c r="O310" s="50">
+        <v>0</v>
+      </c>
+      <c r="P310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q310" s="50">
+        <v>0</v>
+      </c>
+      <c r="R310" s="50">
+        <v>0</v>
+      </c>
+      <c r="S310" s="50">
+        <v>0</v>
+      </c>
+      <c r="T310" s="50">
+        <v>0</v>
+      </c>
+      <c r="U310" s="50">
+        <v>0</v>
+      </c>
+      <c r="V310" s="50">
+        <v>0</v>
+      </c>
+      <c r="W310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z310" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA310" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="50">
+        <v>306</v>
+      </c>
+      <c r="B311" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C311" s="50">
+        <v>84983</v>
+      </c>
+      <c r="D311" s="50" t="s">
+        <v>683</v>
+      </c>
+      <c r="E311" s="50">
+        <v>24</v>
+      </c>
+      <c r="F311" s="50">
+        <v>0</v>
+      </c>
+      <c r="G311" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H311" s="50" t="s">
+        <v>686</v>
+      </c>
+      <c r="I311" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J311" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K311" s="50" t="s">
+        <v>687</v>
+      </c>
+      <c r="L311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N311" s="50">
+        <v>8</v>
+      </c>
+      <c r="O311" s="50">
+        <v>0</v>
+      </c>
+      <c r="P311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q311" s="50">
+        <v>0</v>
+      </c>
+      <c r="R311" s="50">
+        <v>0</v>
+      </c>
+      <c r="S311" s="50">
+        <v>0</v>
+      </c>
+      <c r="T311" s="50">
+        <v>0</v>
+      </c>
+      <c r="U311" s="50">
+        <v>0</v>
+      </c>
+      <c r="V311" s="50">
+        <v>0</v>
+      </c>
+      <c r="W311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y311" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z311" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA311" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="50">
+        <v>307</v>
+      </c>
+      <c r="B312" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C312" s="50">
+        <v>84984</v>
+      </c>
+      <c r="D312" s="50" t="s">
+        <v>688</v>
+      </c>
+      <c r="E312" s="50">
+        <v>25</v>
+      </c>
+      <c r="F312" s="50">
+        <v>0</v>
+      </c>
+      <c r="G312" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H312" s="50" t="s">
+        <v>689</v>
+      </c>
+      <c r="I312" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J312" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K312" s="50" t="s">
+        <v>690</v>
+      </c>
+      <c r="L312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N312" s="50">
+        <v>8</v>
+      </c>
+      <c r="O312" s="50">
+        <v>0</v>
+      </c>
+      <c r="P312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q312" s="50">
+        <v>0</v>
+      </c>
+      <c r="R312" s="50">
+        <v>0</v>
+      </c>
+      <c r="S312" s="50">
+        <v>0</v>
+      </c>
+      <c r="T312" s="50">
+        <v>0</v>
+      </c>
+      <c r="U312" s="50">
+        <v>0</v>
+      </c>
+      <c r="V312" s="50">
+        <v>0</v>
+      </c>
+      <c r="W312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y312" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z312" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA312" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="50">
+        <v>308</v>
+      </c>
+      <c r="B313" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C313" s="50">
+        <v>330037</v>
+      </c>
+      <c r="D313" s="50" t="s">
+        <v>691</v>
+      </c>
+      <c r="E313" s="50">
+        <v>5</v>
+      </c>
+      <c r="F313" s="50">
+        <v>1</v>
+      </c>
+      <c r="G313" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H313" s="50" t="s">
+        <v>692</v>
+      </c>
+      <c r="I313" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J313" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K313" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N313" s="50">
+        <v>33</v>
+      </c>
+      <c r="O313" s="50">
+        <v>0</v>
+      </c>
+      <c r="P313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q313" s="50">
+        <v>0</v>
+      </c>
+      <c r="R313" s="50">
+        <v>0</v>
+      </c>
+      <c r="S313" s="50">
+        <v>0</v>
+      </c>
+      <c r="T313" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U313" s="50">
+        <v>0</v>
+      </c>
+      <c r="V313" s="50">
+        <v>0</v>
+      </c>
+      <c r="W313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y313" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z313" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA313" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="50">
+        <v>309</v>
+      </c>
+      <c r="B314" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C314" s="50">
+        <v>330038</v>
+      </c>
+      <c r="D314" s="50" t="s">
+        <v>693</v>
+      </c>
+      <c r="E314" s="50">
+        <v>6</v>
+      </c>
+      <c r="F314" s="50">
+        <v>0</v>
+      </c>
+      <c r="G314" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H314" s="50" t="s">
+        <v>694</v>
+      </c>
+      <c r="I314" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J314" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K314" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L314" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M314" s="50" t="s">
+        <v>695</v>
+      </c>
+      <c r="N314" s="50">
+        <v>33</v>
+      </c>
+      <c r="O314" s="50">
+        <v>0</v>
+      </c>
+      <c r="P314" s="50"/>
+      <c r="Q314" s="50">
+        <v>0</v>
+      </c>
+      <c r="R314" s="50">
+        <v>0</v>
+      </c>
+      <c r="S314" s="50">
+        <v>0</v>
+      </c>
+      <c r="T314" s="50">
+        <v>0</v>
+      </c>
+      <c r="U314" s="50">
+        <v>0</v>
+      </c>
+      <c r="V314" s="50">
+        <v>0</v>
+      </c>
+      <c r="W314" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X314" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y314" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z314" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA314" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="50">
+        <v>310</v>
+      </c>
+      <c r="B315" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C315" s="50">
+        <v>330039</v>
+      </c>
+      <c r="D315" s="50" t="s">
+        <v>696</v>
+      </c>
+      <c r="E315" s="50">
+        <v>7</v>
+      </c>
+      <c r="F315" s="50">
+        <v>0</v>
+      </c>
+      <c r="G315" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H315" s="50" t="s">
+        <v>697</v>
+      </c>
+      <c r="I315" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J315" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K315" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L315" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="M315" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N315" s="50">
+        <v>33</v>
+      </c>
+      <c r="O315" s="50">
+        <v>0</v>
+      </c>
+      <c r="P315" s="50"/>
+      <c r="Q315" s="50">
+        <v>0</v>
+      </c>
+      <c r="R315" s="50">
+        <v>0</v>
+      </c>
+      <c r="S315" s="50">
+        <v>0</v>
+      </c>
+      <c r="T315" s="50">
+        <v>0</v>
+      </c>
+      <c r="U315" s="50">
+        <v>0</v>
+      </c>
+      <c r="V315" s="50">
+        <v>0</v>
+      </c>
+      <c r="W315" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X315" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y315" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z315" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA315" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="50">
+        <v>311</v>
+      </c>
+      <c r="B316" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C316" s="50">
+        <v>330040</v>
+      </c>
+      <c r="D316" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="E316" s="50">
+        <v>7</v>
+      </c>
+      <c r="F316" s="50">
+        <v>0</v>
+      </c>
+      <c r="G316" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H316" s="50" t="s">
+        <v>700</v>
+      </c>
+      <c r="I316" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J316" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K316" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L316" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="M316" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N316" s="50">
+        <v>33</v>
+      </c>
+      <c r="O316" s="50">
+        <v>0</v>
+      </c>
+      <c r="P316" s="50"/>
+      <c r="Q316" s="50">
+        <v>0</v>
+      </c>
+      <c r="R316" s="50">
+        <v>0</v>
+      </c>
+      <c r="S316" s="50">
+        <v>0</v>
+      </c>
+      <c r="T316" s="50">
+        <v>0</v>
+      </c>
+      <c r="U316" s="50">
+        <v>0</v>
+      </c>
+      <c r="V316" s="50">
+        <v>0</v>
+      </c>
+      <c r="W316" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X316" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y316" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z316" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA316" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="50">
+        <v>312</v>
+      </c>
+      <c r="B317" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C317" s="50">
+        <v>330041</v>
+      </c>
+      <c r="D317" s="50" t="s">
+        <v>701</v>
+      </c>
+      <c r="E317" s="50">
+        <v>7</v>
+      </c>
+      <c r="F317" s="50">
+        <v>0</v>
+      </c>
+      <c r="G317" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H317" s="50" t="s">
+        <v>702</v>
+      </c>
+      <c r="I317" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J317" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K317" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L317" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="M317" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N317" s="50">
+        <v>33</v>
+      </c>
+      <c r="O317" s="50">
+        <v>0</v>
+      </c>
+      <c r="P317" s="50"/>
+      <c r="Q317" s="50">
+        <v>0</v>
+      </c>
+      <c r="R317" s="50">
+        <v>0</v>
+      </c>
+      <c r="S317" s="50">
+        <v>0</v>
+      </c>
+      <c r="T317" s="50">
+        <v>0</v>
+      </c>
+      <c r="U317" s="50">
+        <v>0</v>
+      </c>
+      <c r="V317" s="50">
+        <v>0</v>
+      </c>
+      <c r="W317" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X317" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y317" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z317" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA317" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="50">
+        <v>313</v>
+      </c>
+      <c r="B318" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C318" s="50">
+        <v>330042</v>
+      </c>
+      <c r="D318" s="50" t="s">
+        <v>703</v>
+      </c>
+      <c r="E318" s="50">
+        <v>20</v>
+      </c>
+      <c r="F318" s="50">
+        <v>1</v>
+      </c>
+      <c r="G318" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H318" s="50" t="s">
+        <v>704</v>
+      </c>
+      <c r="I318" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J318" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K318" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="L318" s="50" t="s">
+        <v>705</v>
+      </c>
+      <c r="M318" s="50" t="s">
+        <v>706</v>
+      </c>
+      <c r="N318" s="50">
+        <v>33</v>
+      </c>
+      <c r="O318" s="50">
+        <v>0</v>
+      </c>
+      <c r="P318" s="50"/>
+      <c r="Q318" s="50">
+        <v>0</v>
+      </c>
+      <c r="R318" s="50">
+        <v>0</v>
+      </c>
+      <c r="S318" s="50">
+        <v>0</v>
+      </c>
+      <c r="T318" s="50">
+        <v>0</v>
+      </c>
+      <c r="U318" s="50">
+        <v>0</v>
+      </c>
+      <c r="V318" s="50">
+        <v>0</v>
+      </c>
+      <c r="W318" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X318" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y318" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z318" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA318" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="50">
+        <v>314</v>
+      </c>
+      <c r="B319" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C319" s="50">
+        <v>330043</v>
+      </c>
+      <c r="D319" s="50" t="s">
+        <v>707</v>
+      </c>
+      <c r="E319" s="50">
+        <v>19</v>
+      </c>
+      <c r="F319" s="50">
+        <v>1</v>
+      </c>
+      <c r="G319" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H319" s="50" t="s">
+        <v>708</v>
+      </c>
+      <c r="I319" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J319" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K319" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="L319" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M319" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N319" s="50">
+        <v>33</v>
+      </c>
+      <c r="O319" s="50">
+        <v>0</v>
+      </c>
+      <c r="P319" s="50"/>
+      <c r="Q319" s="50">
+        <v>0</v>
+      </c>
+      <c r="R319" s="50">
+        <v>0</v>
+      </c>
+      <c r="S319" s="50">
+        <v>0</v>
+      </c>
+      <c r="T319" s="50">
+        <v>0</v>
+      </c>
+      <c r="U319" s="50">
+        <v>0</v>
+      </c>
+      <c r="V319" s="50">
+        <v>0</v>
+      </c>
+      <c r="W319" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X319" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y319" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z319" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA319" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="50">
+        <v>315</v>
+      </c>
+      <c r="B320" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C320" s="50">
+        <v>330044</v>
+      </c>
+      <c r="D320" s="50" t="s">
+        <v>709</v>
+      </c>
+      <c r="E320" s="50">
+        <v>16</v>
+      </c>
+      <c r="F320" s="50">
+        <v>9</v>
+      </c>
+      <c r="G320" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H320" s="50" t="s">
+        <v>710</v>
+      </c>
+      <c r="I320" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J320" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K320" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L320" s="50" t="s">
+        <v>711</v>
+      </c>
+      <c r="M320" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N320" s="50">
+        <v>33</v>
+      </c>
+      <c r="O320" s="50">
+        <v>0</v>
+      </c>
+      <c r="P320" s="50"/>
+      <c r="Q320" s="50">
+        <v>0</v>
+      </c>
+      <c r="R320" s="50">
+        <v>0</v>
+      </c>
+      <c r="S320" s="50">
+        <v>0</v>
+      </c>
+      <c r="T320" s="50">
+        <v>0</v>
+      </c>
+      <c r="U320" s="50">
+        <v>0</v>
+      </c>
+      <c r="V320" s="50">
+        <v>0</v>
+      </c>
+      <c r="W320" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X320" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y320" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z320" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA320" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="50">
+        <v>316</v>
+      </c>
+      <c r="B321" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C321" s="50">
+        <v>330045</v>
+      </c>
+      <c r="D321" s="50" t="s">
+        <v>712</v>
+      </c>
+      <c r="E321" s="50">
+        <v>5</v>
+      </c>
+      <c r="F321" s="50">
+        <v>1</v>
+      </c>
+      <c r="G321" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H321" s="50" t="s">
+        <v>713</v>
+      </c>
+      <c r="I321" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J321" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K321" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N321" s="50">
+        <v>33</v>
+      </c>
+      <c r="O321" s="50">
+        <v>0</v>
+      </c>
+      <c r="P321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q321" s="50">
+        <v>0</v>
+      </c>
+      <c r="R321" s="50">
+        <v>0</v>
+      </c>
+      <c r="S321" s="50">
+        <v>0</v>
+      </c>
+      <c r="T321" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U321" s="50">
+        <v>0</v>
+      </c>
+      <c r="V321" s="50">
+        <v>0</v>
+      </c>
+      <c r="W321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y321" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z321" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA321" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="50">
+        <v>317</v>
+      </c>
+      <c r="B322" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C322" s="50">
+        <v>330046</v>
+      </c>
+      <c r="D322" s="50" t="s">
+        <v>714</v>
+      </c>
+      <c r="E322" s="50">
+        <v>16</v>
+      </c>
+      <c r="F322" s="50">
+        <v>6</v>
+      </c>
+      <c r="G322" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H322" s="50" t="s">
+        <v>715</v>
+      </c>
+      <c r="I322" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J322" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K322" s="50" t="s">
+        <v>461</v>
+      </c>
+      <c r="L322" s="50" t="s">
+        <v>716</v>
+      </c>
+      <c r="M322" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N322" s="50">
+        <v>33</v>
+      </c>
+      <c r="O322" s="50">
+        <v>0</v>
+      </c>
+      <c r="P322" s="50"/>
+      <c r="Q322" s="50">
+        <v>0</v>
+      </c>
+      <c r="R322" s="50">
+        <v>0</v>
+      </c>
+      <c r="S322" s="50">
+        <v>0</v>
+      </c>
+      <c r="T322" s="50">
+        <v>0</v>
+      </c>
+      <c r="U322" s="50">
+        <v>0</v>
+      </c>
+      <c r="V322" s="50">
+        <v>0</v>
+      </c>
+      <c r="W322" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X322" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y322" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z322" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA322" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="50">
+        <v>318</v>
+      </c>
+      <c r="B323" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C323" s="50">
+        <v>330047</v>
+      </c>
+      <c r="D323" s="50" t="s">
+        <v>717</v>
+      </c>
+      <c r="E323" s="50">
+        <v>3</v>
+      </c>
+      <c r="F323" s="50">
+        <v>6</v>
+      </c>
+      <c r="G323" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H323" s="50" t="s">
+        <v>718</v>
+      </c>
+      <c r="I323" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J323" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K323" s="50" t="s">
+        <v>465</v>
+      </c>
+      <c r="L323" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M323" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N323" s="50">
+        <v>33</v>
+      </c>
+      <c r="O323" s="50">
+        <v>0</v>
+      </c>
+      <c r="P323" s="50"/>
+      <c r="Q323" s="50">
+        <v>0</v>
+      </c>
+      <c r="R323" s="50">
+        <v>0</v>
+      </c>
+      <c r="S323" s="50">
+        <v>0</v>
+      </c>
+      <c r="T323" s="50">
+        <v>0</v>
+      </c>
+      <c r="U323" s="50">
+        <v>0</v>
+      </c>
+      <c r="V323" s="50">
+        <v>0</v>
+      </c>
+      <c r="W323" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X323" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y323" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z323" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA323" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="50">
+        <v>319</v>
+      </c>
+      <c r="B324" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C324" s="50">
+        <v>330048</v>
+      </c>
+      <c r="D324" s="50" t="s">
+        <v>719</v>
+      </c>
+      <c r="E324" s="50">
+        <v>5</v>
+      </c>
+      <c r="F324" s="50">
+        <v>1</v>
+      </c>
+      <c r="G324" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H324" s="50" t="s">
+        <v>720</v>
+      </c>
+      <c r="I324" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J324" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K324" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N324" s="50">
+        <v>33</v>
+      </c>
+      <c r="O324" s="50">
+        <v>0</v>
+      </c>
+      <c r="P324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q324" s="50">
+        <v>0</v>
+      </c>
+      <c r="R324" s="50">
+        <v>0</v>
+      </c>
+      <c r="S324" s="50">
+        <v>0</v>
+      </c>
+      <c r="T324" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U324" s="50">
+        <v>0</v>
+      </c>
+      <c r="V324" s="50">
+        <v>0</v>
+      </c>
+      <c r="W324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y324" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z324" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA324" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="50">
+        <v>320</v>
+      </c>
+      <c r="B325" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C325" s="50">
+        <v>330049</v>
+      </c>
+      <c r="D325" s="50" t="s">
+        <v>721</v>
+      </c>
+      <c r="E325" s="50">
+        <v>43</v>
+      </c>
+      <c r="F325" s="50">
+        <v>0</v>
+      </c>
+      <c r="G325" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H325" s="50" t="s">
+        <v>722</v>
+      </c>
+      <c r="I325" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J325" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K325" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="L325" s="50" t="s">
+        <v>723</v>
+      </c>
+      <c r="M325" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N325" s="50">
+        <v>33</v>
+      </c>
+      <c r="O325" s="50">
+        <v>0</v>
+      </c>
+      <c r="P325" s="50"/>
+      <c r="Q325" s="50">
+        <v>0</v>
+      </c>
+      <c r="R325" s="50">
+        <v>0</v>
+      </c>
+      <c r="S325" s="50">
+        <v>0</v>
+      </c>
+      <c r="T325" s="50">
+        <v>0</v>
+      </c>
+      <c r="U325" s="50">
+        <v>0</v>
+      </c>
+      <c r="V325" s="50">
+        <v>0</v>
+      </c>
+      <c r="W325" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X325" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y325" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z325" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA325" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="50">
+        <v>321</v>
+      </c>
+      <c r="B326" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C326" s="50">
+        <v>330050</v>
+      </c>
+      <c r="D326" s="50" t="s">
+        <v>724</v>
+      </c>
+      <c r="E326" s="50">
+        <v>44</v>
+      </c>
+      <c r="F326" s="50">
+        <v>0</v>
+      </c>
+      <c r="G326" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H326" s="50" t="s">
+        <v>725</v>
+      </c>
+      <c r="I326" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J326" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K326" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="L326" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M326" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N326" s="50">
+        <v>33</v>
+      </c>
+      <c r="O326" s="50">
+        <v>0</v>
+      </c>
+      <c r="P326" s="50"/>
+      <c r="Q326" s="50">
+        <v>0</v>
+      </c>
+      <c r="R326" s="50">
+        <v>0</v>
+      </c>
+      <c r="S326" s="50">
+        <v>0</v>
+      </c>
+      <c r="T326" s="50">
+        <v>0</v>
+      </c>
+      <c r="U326" s="50">
+        <v>0</v>
+      </c>
+      <c r="V326" s="50">
+        <v>0</v>
+      </c>
+      <c r="W326" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X326" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y326" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z326" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA326" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="50">
+        <v>322</v>
+      </c>
+      <c r="B327" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C327" s="50">
+        <v>330051</v>
+      </c>
+      <c r="D327" s="50" t="s">
+        <v>726</v>
+      </c>
+      <c r="E327" s="50">
+        <v>4</v>
+      </c>
+      <c r="F327" s="50">
+        <v>1</v>
+      </c>
+      <c r="G327" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H327" s="50" t="s">
+        <v>727</v>
+      </c>
+      <c r="I327" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J327" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K327" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N327" s="50">
+        <v>33</v>
+      </c>
+      <c r="O327" s="50">
+        <v>0</v>
+      </c>
+      <c r="P327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q327" s="50">
+        <v>0</v>
+      </c>
+      <c r="R327" s="50">
+        <v>0</v>
+      </c>
+      <c r="S327" s="50">
+        <v>0</v>
+      </c>
+      <c r="T327" s="50">
+        <v>0</v>
+      </c>
+      <c r="U327" s="50">
+        <v>0</v>
+      </c>
+      <c r="V327" s="50">
+        <v>0</v>
+      </c>
+      <c r="W327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y327" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z327" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA327" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="50">
+        <v>323</v>
+      </c>
+      <c r="B328" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C328" s="50">
+        <v>330052</v>
+      </c>
+      <c r="D328" s="50" t="s">
+        <v>728</v>
+      </c>
+      <c r="E328" s="50">
+        <v>4</v>
+      </c>
+      <c r="F328" s="50">
+        <v>2</v>
+      </c>
+      <c r="G328" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H328" s="50" t="s">
+        <v>729</v>
+      </c>
+      <c r="I328" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J328" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K328" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="L328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N328" s="50">
+        <v>33</v>
+      </c>
+      <c r="O328" s="50">
+        <v>0</v>
+      </c>
+      <c r="P328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q328" s="50">
+        <v>0</v>
+      </c>
+      <c r="R328" s="50">
+        <v>0</v>
+      </c>
+      <c r="S328" s="50">
+        <v>0</v>
+      </c>
+      <c r="T328" s="50">
+        <v>0</v>
+      </c>
+      <c r="U328" s="50">
+        <v>0</v>
+      </c>
+      <c r="V328" s="50">
+        <v>0</v>
+      </c>
+      <c r="W328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y328" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z328" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA328" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="50">
+        <v>324</v>
+      </c>
+      <c r="B329" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C329" s="50">
+        <v>330053</v>
+      </c>
+      <c r="D329" s="50" t="s">
+        <v>730</v>
+      </c>
+      <c r="E329" s="50">
+        <v>4</v>
+      </c>
+      <c r="F329" s="50">
+        <v>3</v>
+      </c>
+      <c r="G329" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H329" s="50" t="s">
+        <v>731</v>
+      </c>
+      <c r="I329" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J329" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K329" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="L329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N329" s="50">
+        <v>33</v>
+      </c>
+      <c r="O329" s="50">
+        <v>0</v>
+      </c>
+      <c r="P329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q329" s="50">
+        <v>0</v>
+      </c>
+      <c r="R329" s="50">
+        <v>0</v>
+      </c>
+      <c r="S329" s="50">
+        <v>0</v>
+      </c>
+      <c r="T329" s="50">
+        <v>0</v>
+      </c>
+      <c r="U329" s="50">
+        <v>0</v>
+      </c>
+      <c r="V329" s="50">
+        <v>0</v>
+      </c>
+      <c r="W329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y329" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z329" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA329" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="50">
+        <v>325</v>
+      </c>
+      <c r="B330" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C330" s="50">
+        <v>330054</v>
+      </c>
+      <c r="D330" s="50" t="s">
+        <v>732</v>
+      </c>
+      <c r="E330" s="50">
+        <v>5</v>
+      </c>
+      <c r="F330" s="50">
+        <v>1</v>
+      </c>
+      <c r="G330" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H330" s="50" t="s">
+        <v>733</v>
+      </c>
+      <c r="I330" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J330" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K330" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N330" s="50">
+        <v>33</v>
+      </c>
+      <c r="O330" s="50">
+        <v>0</v>
+      </c>
+      <c r="P330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q330" s="50">
+        <v>0</v>
+      </c>
+      <c r="R330" s="50">
+        <v>0</v>
+      </c>
+      <c r="S330" s="50">
+        <v>0</v>
+      </c>
+      <c r="T330" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U330" s="50">
+        <v>0</v>
+      </c>
+      <c r="V330" s="50">
+        <v>0</v>
+      </c>
+      <c r="W330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y330" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z330" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA330" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="50">
+        <v>326</v>
+      </c>
+      <c r="B331" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C331" s="50">
+        <v>330055</v>
+      </c>
+      <c r="D331" s="50" t="s">
+        <v>734</v>
+      </c>
+      <c r="E331" s="50">
+        <v>4</v>
+      </c>
+      <c r="F331" s="50">
+        <v>1</v>
+      </c>
+      <c r="G331" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H331" s="50" t="s">
+        <v>735</v>
+      </c>
+      <c r="I331" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J331" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K331" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N331" s="50">
+        <v>33</v>
+      </c>
+      <c r="O331" s="50">
+        <v>0</v>
+      </c>
+      <c r="P331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q331" s="50">
+        <v>0</v>
+      </c>
+      <c r="R331" s="50">
+        <v>0</v>
+      </c>
+      <c r="S331" s="50">
+        <v>0</v>
+      </c>
+      <c r="T331" s="50">
+        <v>0</v>
+      </c>
+      <c r="U331" s="50">
+        <v>0</v>
+      </c>
+      <c r="V331" s="50">
+        <v>0</v>
+      </c>
+      <c r="W331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y331" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z331" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA331" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="50">
+        <v>327</v>
+      </c>
+      <c r="B332" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C332" s="50">
+        <v>330056</v>
+      </c>
+      <c r="D332" s="50" t="s">
+        <v>736</v>
+      </c>
+      <c r="E332" s="50">
+        <v>54</v>
+      </c>
+      <c r="F332" s="50">
+        <v>0</v>
+      </c>
+      <c r="G332" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H332" s="50" t="s">
+        <v>737</v>
+      </c>
+      <c r="I332" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J332" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K332" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="L332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N332" s="50">
+        <v>33</v>
+      </c>
+      <c r="O332" s="50">
+        <v>0</v>
+      </c>
+      <c r="P332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q332" s="50">
+        <v>0</v>
+      </c>
+      <c r="R332" s="50">
+        <v>0</v>
+      </c>
+      <c r="S332" s="50">
+        <v>0</v>
+      </c>
+      <c r="T332" s="50">
+        <v>0</v>
+      </c>
+      <c r="U332" s="50">
+        <v>0</v>
+      </c>
+      <c r="V332" s="50">
+        <v>0</v>
+      </c>
+      <c r="W332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y332" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z332" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA332" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="50">
+        <v>328</v>
+      </c>
+      <c r="B333" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C333" s="50">
+        <v>330058</v>
+      </c>
+      <c r="D333" s="50" t="s">
+        <v>738</v>
+      </c>
+      <c r="E333" s="50">
+        <v>5</v>
+      </c>
+      <c r="F333" s="50">
+        <v>1</v>
+      </c>
+      <c r="G333" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H333" s="50" t="s">
+        <v>739</v>
+      </c>
+      <c r="I333" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J333" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K333" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N333" s="50">
+        <v>33</v>
+      </c>
+      <c r="O333" s="50">
+        <v>0</v>
+      </c>
+      <c r="P333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q333" s="50">
+        <v>0</v>
+      </c>
+      <c r="R333" s="50">
+        <v>0</v>
+      </c>
+      <c r="S333" s="50">
+        <v>0</v>
+      </c>
+      <c r="T333" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U333" s="50">
+        <v>0</v>
+      </c>
+      <c r="V333" s="50">
+        <v>0</v>
+      </c>
+      <c r="W333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y333" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z333" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA333" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="50">
+        <v>329</v>
+      </c>
+      <c r="B334" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C334" s="50">
+        <v>330061</v>
+      </c>
+      <c r="D334" s="50" t="s">
+        <v>740</v>
+      </c>
+      <c r="E334" s="50">
+        <v>39</v>
+      </c>
+      <c r="F334" s="50">
+        <v>0</v>
+      </c>
+      <c r="G334" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H334" s="50" t="s">
+        <v>741</v>
+      </c>
+      <c r="I334" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J334" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K334" s="50" t="s">
+        <v>742</v>
+      </c>
+      <c r="L334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N334" s="50">
+        <v>33</v>
+      </c>
+      <c r="O334" s="50">
+        <v>0</v>
+      </c>
+      <c r="P334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q334" s="50">
+        <v>0</v>
+      </c>
+      <c r="R334" s="50">
+        <v>0</v>
+      </c>
+      <c r="S334" s="50">
+        <v>0</v>
+      </c>
+      <c r="T334" s="50">
+        <v>0</v>
+      </c>
+      <c r="U334" s="50">
+        <v>0</v>
+      </c>
+      <c r="V334" s="50">
+        <v>0</v>
+      </c>
+      <c r="W334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y334" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z334" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA334" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="50">
+        <v>330</v>
+      </c>
+      <c r="B335" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C335" s="50">
+        <v>330062</v>
+      </c>
+      <c r="D335" s="50" t="s">
+        <v>743</v>
+      </c>
+      <c r="E335" s="50">
+        <v>40</v>
+      </c>
+      <c r="F335" s="50">
+        <v>0</v>
+      </c>
+      <c r="G335" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H335" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="I335" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J335" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K335" s="50" t="s">
+        <v>745</v>
+      </c>
+      <c r="L335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N335" s="50">
+        <v>33</v>
+      </c>
+      <c r="O335" s="50">
+        <v>0</v>
+      </c>
+      <c r="P335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q335" s="50">
+        <v>0</v>
+      </c>
+      <c r="R335" s="50">
+        <v>0</v>
+      </c>
+      <c r="S335" s="50">
+        <v>0</v>
+      </c>
+      <c r="T335" s="50">
+        <v>0</v>
+      </c>
+      <c r="U335" s="50">
+        <v>0</v>
+      </c>
+      <c r="V335" s="50">
+        <v>0</v>
+      </c>
+      <c r="W335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y335" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z335" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA335" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="50">
+        <v>331</v>
+      </c>
+      <c r="B336" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C336" s="50">
+        <v>330063</v>
+      </c>
+      <c r="D336" s="50" t="s">
+        <v>746</v>
+      </c>
+      <c r="E336" s="50">
+        <v>28</v>
+      </c>
+      <c r="F336" s="50">
+        <v>0</v>
+      </c>
+      <c r="G336" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H336" s="50" t="s">
+        <v>747</v>
+      </c>
+      <c r="I336" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J336" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K336" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L336" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N336" s="50">
+        <v>33</v>
+      </c>
+      <c r="O336" s="50">
+        <v>0</v>
+      </c>
+      <c r="P336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q336" s="50">
+        <v>0</v>
+      </c>
+      <c r="R336" s="50">
+        <v>0</v>
+      </c>
+      <c r="S336" s="50">
+        <v>0</v>
+      </c>
+      <c r="T336" s="50">
+        <v>0</v>
+      </c>
+      <c r="U336" s="50">
+        <v>0</v>
+      </c>
+      <c r="V336" s="50">
+        <v>0</v>
+      </c>
+      <c r="W336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z336" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA336" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="50">
+        <v>332</v>
+      </c>
+      <c r="B337" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C337" s="50">
+        <v>330064</v>
+      </c>
+      <c r="D337" s="50" t="s">
+        <v>748</v>
+      </c>
+      <c r="E337" s="50">
+        <v>29</v>
+      </c>
+      <c r="F337" s="50">
+        <v>0</v>
+      </c>
+      <c r="G337" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H337" s="50" t="s">
+        <v>749</v>
+      </c>
+      <c r="I337" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J337" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K337" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="L337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M337" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N337" s="50">
+        <v>33</v>
+      </c>
+      <c r="O337" s="50">
+        <v>0</v>
+      </c>
+      <c r="P337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q337" s="50">
+        <v>0</v>
+      </c>
+      <c r="R337" s="50">
+        <v>0</v>
+      </c>
+      <c r="S337" s="50">
+        <v>0</v>
+      </c>
+      <c r="T337" s="50">
+        <v>0</v>
+      </c>
+      <c r="U337" s="50">
+        <v>0</v>
+      </c>
+      <c r="V337" s="50">
+        <v>0</v>
+      </c>
+      <c r="W337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z337" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA337" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="50">
+        <v>333</v>
+      </c>
+      <c r="B338" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C338" s="50">
+        <v>330065</v>
+      </c>
+      <c r="D338" s="50" t="s">
+        <v>750</v>
+      </c>
+      <c r="E338" s="50">
+        <v>5</v>
+      </c>
+      <c r="F338" s="50">
+        <v>2</v>
+      </c>
+      <c r="G338" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H338" s="50" t="s">
+        <v>751</v>
+      </c>
+      <c r="I338" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J338" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K338" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="L338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N338" s="50">
+        <v>33</v>
+      </c>
+      <c r="O338" s="50">
+        <v>0</v>
+      </c>
+      <c r="P338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q338" s="50">
+        <v>0</v>
+      </c>
+      <c r="R338" s="50">
+        <v>0</v>
+      </c>
+      <c r="S338" s="50">
+        <v>0</v>
+      </c>
+      <c r="T338" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U338" s="50">
+        <v>0</v>
+      </c>
+      <c r="V338" s="50">
+        <v>0</v>
+      </c>
+      <c r="W338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z338" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA338" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="50">
+        <v>334</v>
+      </c>
+      <c r="B339" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C339" s="50">
+        <v>330067</v>
+      </c>
+      <c r="D339" s="50" t="s">
+        <v>752</v>
+      </c>
+      <c r="E339" s="50">
+        <v>4</v>
+      </c>
+      <c r="F339" s="50">
+        <v>1</v>
+      </c>
+      <c r="G339" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H339" s="50" t="s">
+        <v>753</v>
+      </c>
+      <c r="I339" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J339" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K339" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N339" s="50">
+        <v>33</v>
+      </c>
+      <c r="O339" s="50">
+        <v>0</v>
+      </c>
+      <c r="P339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q339" s="50">
+        <v>0</v>
+      </c>
+      <c r="R339" s="50">
+        <v>0</v>
+      </c>
+      <c r="S339" s="50">
+        <v>0</v>
+      </c>
+      <c r="T339" s="50">
+        <v>0</v>
+      </c>
+      <c r="U339" s="50">
+        <v>0</v>
+      </c>
+      <c r="V339" s="50">
+        <v>0</v>
+      </c>
+      <c r="W339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z339" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA339" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="50">
+        <v>335</v>
+      </c>
+      <c r="B340" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C340" s="50">
+        <v>330068</v>
+      </c>
+      <c r="D340" s="50" t="s">
+        <v>754</v>
+      </c>
+      <c r="E340" s="50">
+        <v>5</v>
+      </c>
+      <c r="F340" s="50">
+        <v>1</v>
+      </c>
+      <c r="G340" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H340" s="50" t="s">
+        <v>755</v>
+      </c>
+      <c r="I340" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J340" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K340" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N340" s="50">
+        <v>33</v>
+      </c>
+      <c r="O340" s="50">
+        <v>0</v>
+      </c>
+      <c r="P340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q340" s="50">
+        <v>0</v>
+      </c>
+      <c r="R340" s="50">
+        <v>0</v>
+      </c>
+      <c r="S340" s="50">
+        <v>0</v>
+      </c>
+      <c r="T340" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U340" s="50">
+        <v>0</v>
+      </c>
+      <c r="V340" s="50">
+        <v>0</v>
+      </c>
+      <c r="W340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y340" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z340" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA340" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="50">
+        <v>336</v>
+      </c>
+      <c r="B341" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C341" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D341" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="E341" s="50">
+        <v>16</v>
+      </c>
+      <c r="F341" s="50">
+        <v>1</v>
+      </c>
+      <c r="G341" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H341" s="50" t="s">
+        <v>757</v>
+      </c>
+      <c r="I341" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J341" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K341" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L341" s="50" t="s">
+        <v>758</v>
+      </c>
+      <c r="M341" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N341" s="50">
+        <v>33</v>
+      </c>
+      <c r="O341" s="50">
+        <v>0</v>
+      </c>
+      <c r="P341" s="50"/>
+      <c r="Q341" s="50">
+        <v>0</v>
+      </c>
+      <c r="R341" s="50">
+        <v>0</v>
+      </c>
+      <c r="S341" s="50">
+        <v>0</v>
+      </c>
+      <c r="T341" s="50">
+        <v>0</v>
+      </c>
+      <c r="U341" s="50">
+        <v>0</v>
+      </c>
+      <c r="V341" s="50">
+        <v>0</v>
+      </c>
+      <c r="W341" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X341" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y341" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z341" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA341" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="50">
+        <v>337</v>
+      </c>
+      <c r="B342" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C342" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D342" s="50" t="s">
+        <v>759</v>
+      </c>
+      <c r="E342" s="50">
+        <v>3</v>
+      </c>
+      <c r="F342" s="50">
+        <v>1</v>
+      </c>
+      <c r="G342" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H342" s="50" t="s">
+        <v>760</v>
+      </c>
+      <c r="I342" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J342" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K342" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L342" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M342" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N342" s="50">
+        <v>33</v>
+      </c>
+      <c r="O342" s="50">
+        <v>0</v>
+      </c>
+      <c r="P342" s="50"/>
+      <c r="Q342" s="50">
+        <v>0</v>
+      </c>
+      <c r="R342" s="50">
+        <v>0</v>
+      </c>
+      <c r="S342" s="50">
+        <v>0</v>
+      </c>
+      <c r="T342" s="50">
+        <v>0</v>
+      </c>
+      <c r="U342" s="50">
+        <v>0</v>
+      </c>
+      <c r="V342" s="50">
+        <v>0</v>
+      </c>
+      <c r="W342" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X342" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y342" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z342" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA342" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="767">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1291,19 +1291,19 @@
     <t>110,7.999978,43</t>
   </si>
   <si>
-    <t>115,9.499898,52</t>
-  </si>
-  <si>
-    <t>112.75,8,54.25_112.75,8,49.75_117.25,8,49.75_117.25,8,54.25</t>
+    <t>115,8.003199,52</t>
+  </si>
+  <si>
+    <t>112.75,8.003199,54.25_112.75,8.003199,49.75_117.25,8.003199,49.75_117.25,8.003199,54.25</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>132,7.999978,52</t>
-  </si>
-  <si>
-    <t>130.5,8,50_133.5,8,50_133.5,8,54_130.5,8,54</t>
+    <t>132,8.003199,52</t>
+  </si>
+  <si>
+    <t>130.5,8.003199,50_133.5,8.003199,50_133.5,8.003199,54_130.5,8.003199,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1312,28 +1312,28 @@
     <t>70001_0</t>
   </si>
   <si>
-    <t>117,-0.04387474,73.8584136962891</t>
-  </si>
-  <si>
-    <t>118,8,72.85841_118,8,74.85841_116,8,74.85841_116,8,72.85841</t>
+    <t>117,8.003199,73.8584136962891</t>
+  </si>
+  <si>
+    <t>118,8.003199,72.85841_118,8.003199,74.85841_116,8.003199,74.85841_116,8.003199,72.85841</t>
   </si>
   <si>
     <t>74857</t>
   </si>
   <si>
-    <t>119,-0.04387474,73.8584136962891</t>
-  </si>
-  <si>
-    <t>120,8,72.85841_120,8,74.85841_118,8,74.85841_118,8,72.85841</t>
-  </si>
-  <si>
-    <t>121,-0.04387474,73.8584136962891</t>
-  </si>
-  <si>
-    <t>122,8,72.85841_122,8,74.85841_120,8,74.85841_120,8,72.85841</t>
-  </si>
-  <si>
-    <t>129.307510375977,8.003199,60.7048797607422</t>
+    <t>119,8.003199,73.8584136962891</t>
+  </si>
+  <si>
+    <t>120,8.003199,72.85841_120,8.003199,74.85841_118,8.003199,74.85841_118,8.003199,72.85841</t>
+  </si>
+  <si>
+    <t>121,8.003199,73.8584136962891</t>
+  </si>
+  <si>
+    <t>122,8.003199,72.85841_122,8.003199,74.85841_120,8.003199,74.85841_120,8.003199,72.85841</t>
+  </si>
+  <si>
+    <t>129.307510375977,7.999978,60.7048797607422</t>
   </si>
   <si>
     <t>117.00,0.00,63.00,145.00,0.00,63.00,145.00,0.00,41.00,117.00,0.00,41.00</t>
@@ -1342,7 +1342,7 @@
     <t>97,7.999978,71</t>
   </si>
   <si>
-    <t>98.5,8,72.5_95.5,8,72.5_95.5,8,69.5_98.5,8,69.5</t>
+    <t>98.5,7.999978,72.5_95.5,7.999978,72.5_95.5,7.999978,69.5_98.5,7.999978,69.5</t>
   </si>
   <si>
     <t>74864</t>
@@ -1351,16 +1351,16 @@
     <t>74865</t>
   </si>
   <si>
-    <t>130,3.049911,74</t>
-  </si>
-  <si>
-    <t>131.5,8,75.5_128.5,8,75.5_128.5,8,72.5_131.5,8,72.5</t>
+    <t>130,7.999978,74</t>
+  </si>
+  <si>
+    <t>131.5,7.999978,75.5_128.5,7.999978,75.5_128.5,7.999978,72.5_131.5,7.999978,72.5</t>
   </si>
   <si>
     <t>104,7.999978,79</t>
   </si>
   <si>
-    <t>106,8,80_102,8,80_102,8,78_106,8,78</t>
+    <t>106,7.999978,80_102,7.999978,80_102,7.999978,78_106,7.999978,78</t>
   </si>
   <si>
     <t>74863</t>
@@ -1369,13 +1369,13 @@
     <t>70001_1</t>
   </si>
   <si>
-    <t>81,8.384579,84</t>
-  </si>
-  <si>
-    <t>82.5,8,82_82.5,8,86_79.5,8,86_79.5,8,82</t>
-  </si>
-  <si>
-    <t>87.1449661254883,7.999978,103.072158813477</t>
+    <t>81,7.999978,84</t>
+  </si>
+  <si>
+    <t>82.5,7.999978,82_82.5,7.999978,86_79.5,7.999978,86_79.5,7.999978,82</t>
+  </si>
+  <si>
+    <t>87.1449661254883,5.598887,103.072158813477</t>
   </si>
   <si>
     <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
@@ -1384,7 +1384,7 @@
     <t>58,7.999978,89</t>
   </si>
   <si>
-    <t>60.25,8,90.5_55.75,8,90.5_55.75,8,87.5_60.25,8,87.5</t>
+    <t>60.25,7.999978,90.5_55.75,7.999978,90.5_55.75,7.999978,87.5_60.25,7.999978,87.5</t>
   </si>
   <si>
     <t>70308</t>
@@ -1393,13 +1393,13 @@
     <t>57.7461738586426,7.999978,84</t>
   </si>
   <si>
-    <t>59.74617,8,85.5_55.74617,8,85.5_55.74617,8,82.5_59.74617,8,82.5</t>
-  </si>
-  <si>
-    <t>63,9.699891,70</t>
-  </si>
-  <si>
-    <t>62,8,72_62,8,68_64,8,68_64,8,72</t>
+    <t>59.74617,7.999978,85.5_55.74617,7.999978,85.5_55.74617,7.999978,82.5_59.74617,7.999978,82.5</t>
+  </si>
+  <si>
+    <t>63,7.999978,70</t>
+  </si>
+  <si>
+    <t>62,7.999978,72_62,7.999978,68_64,7.999978,68_64,7.999978,72</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1408,19 +1408,19 @@
     <t>74871</t>
   </si>
   <si>
-    <t>98,6.143705,54</t>
-  </si>
-  <si>
-    <t>99,9.000299,55_97,9.000299,55_97,9.000299,53_99,9.000299,53</t>
+    <t>98,7.999978,54</t>
+  </si>
+  <si>
+    <t>99,7.999978,55_97,7.999978,55_97,7.999978,53_99,7.999978,53</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
-    <t>91,9.999871,56</t>
-  </si>
-  <si>
-    <t>88.75,8,58.25_88.75,8,53.75_93.25,8,53.75_93.25,8,58.25</t>
+    <t>91,7.999978,56</t>
+  </si>
+  <si>
+    <t>88.75,7.999978,58.25_88.75,7.999978,53.75_93.25,7.999978,53.75_93.25,7.999978,58.25</t>
   </si>
   <si>
     <t>74876</t>
@@ -1432,16 +1432,16 @@
     <t>58,7.999978,63</t>
   </si>
   <si>
-    <t>60.25,8,65.25_55.75,8,65.25_55.75,8,60.75_60.25,8,60.75</t>
+    <t>60.25,7.999978,65.25_55.75,7.999978,65.25_55.75,7.999978,60.75_60.25,7.999978,60.75</t>
   </si>
   <si>
     <t>70302</t>
   </si>
   <si>
-    <t>109.408554077148,-0.04387474,114</t>
-  </si>
-  <si>
-    <t>114.4086,7.999999,116_107.4086,7.999999,116_107.4086,7.999999,112_114.4086,7.999999,112</t>
+    <t>109.408554077148,8.003199,114</t>
+  </si>
+  <si>
+    <t>114.4086,8.003199,116_107.4086,8.003199,116_107.4086,8.003199,112_114.4086,8.003199,112</t>
   </si>
   <si>
     <t>74875</t>
@@ -1450,19 +1450,19 @@
     <t>58,7.999978,57</t>
   </si>
   <si>
-    <t>59,8,58_57,8,58_57,8,56_59,8,56</t>
-  </si>
-  <si>
-    <t>58,0,41</t>
-  </si>
-  <si>
-    <t>59.5,8,39_59.5,8,43_56.5,8,43_56.5,8,39</t>
-  </si>
-  <si>
-    <t>137,-0.04387474,133.983917236328</t>
-  </si>
-  <si>
-    <t>138.5,8,131.4839_138.5,8,136.4839_135.5,8,136.4839_135.5,8,131.4839</t>
+    <t>59,7.999978,58_57,7.999978,58_57,7.999978,56_59,7.999978,56</t>
+  </si>
+  <si>
+    <t>58,7.999978,41</t>
+  </si>
+  <si>
+    <t>59.5,7.999978,39_59.5,7.999978,43_56.5,7.999978,43_56.5,7.999978,39</t>
+  </si>
+  <si>
+    <t>137,8.003199,133.983917236328</t>
+  </si>
+  <si>
+    <t>138.5,8.003199,131.4839_138.5,8.003199,136.4839_135.5,8.003199,136.4839_135.5,8.003199,131.4839</t>
   </si>
   <si>
     <t>74878</t>
@@ -1471,19 +1471,19 @@
     <t>88,7.999978,156</t>
   </si>
   <si>
-    <t>89,8,155_89,8,157_87,8,157_87,8,155</t>
+    <t>89,7.999978,155_89,7.999978,157_87,7.999978,157_87,7.999978,155</t>
   </si>
   <si>
     <t>99,7.999978,156</t>
   </si>
   <si>
-    <t>100.5,8.013261,153.5_100.5,8.013261,158.5_97.5,8.013261,158.5_97.5,8.013261,153.5</t>
+    <t>100.5,7.999978,153.5_100.5,7.999978,158.5_97.5,7.999978,158.5_97.5,7.999978,153.5</t>
   </si>
   <si>
     <t>102,7.999978,121</t>
   </si>
   <si>
-    <t>104,7.859674,122_100,7.859674,122_100,7.859674,120_104,7.859674,120</t>
+    <t>104,7.999978,122_100,7.999978,122_100,7.999978,120_104,7.999978,120</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_purple.prefab</t>
@@ -1504,19 +1504,19 @@
     <t>74880</t>
   </si>
   <si>
-    <t>122,-0.04387474,114</t>
-  </si>
-  <si>
-    <t>123,7.859674,115_121,7.859674,115_121,7.859674,113_123,7.859674,113</t>
+    <t>122,7.999978,114</t>
+  </si>
+  <si>
+    <t>123,7.999978,115_121,7.999978,115_121,7.999978,113_123,7.999978,113</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Purple.prefab</t>
   </si>
   <si>
-    <t>112,-0.04387474,134</t>
-  </si>
-  <si>
-    <t>110.5,7.960799,136_110.5,7.960799,132_113.5,7.960799,132_113.5,7.960799,136</t>
+    <t>112,8.003199,134</t>
+  </si>
+  <si>
+    <t>110.5,8.003199,136_110.5,8.003199,132_113.5,8.003199,132_113.5,8.003199,136</t>
   </si>
   <si>
     <t>0,74996</t>
@@ -1531,16 +1531,16 @@
     <t>74996</t>
   </si>
   <si>
-    <t>127,-0.04387474,134</t>
-  </si>
-  <si>
-    <t>129.25,8,131.75_129.25,8,136.25_124.75,8,136.25_124.75,8,131.75</t>
+    <t>127,8.003199,134</t>
+  </si>
+  <si>
+    <t>129.25,8.003199,131.75_129.25,8.003199,136.25_124.75,8.003199,136.25_124.75,8.003199,131.75</t>
   </si>
   <si>
     <t>142,7.999978,176</t>
   </si>
   <si>
-    <t>143.5,8.039689,178_140.5,8.039689,178_140.5,8.039689,174_143.5,8.039689,174</t>
+    <t>143.5,7.999978,178_140.5,7.999978,178_140.5,7.999978,174_143.5,7.999978,174</t>
   </si>
   <si>
     <t>74887</t>
@@ -1552,22 +1552,22 @@
     <t>142,7.999978,185</t>
   </si>
   <si>
-    <t>144,8.039689,187_140,8.039689,187_140,8.039689,183_144,8.039689,183</t>
+    <t>144,7.999978,187_140,7.999978,187_140,7.999978,183_144,7.999978,183</t>
   </si>
   <si>
     <t>74885</t>
   </si>
   <si>
-    <t>122,-0.04387474,134</t>
-  </si>
-  <si>
-    <t>123,8,135_121,8,135_121,8,133_123,8,133</t>
+    <t>122,8.003199,134</t>
+  </si>
+  <si>
+    <t>123,8.003199,135_121,8.003199,135_121,8.003199,133_123,8.003199,133</t>
   </si>
   <si>
     <t>119,10.00309,203</t>
   </si>
   <si>
-    <t>120,10,204.5_118,10,204.5_118,10,201.5_120,10,201.5</t>
+    <t>120,10.00309,204.5_118,10.00309,204.5_118,10.00309,201.5_120,10.00309,201.5</t>
   </si>
   <si>
     <t>74889</t>
@@ -1576,13 +1576,13 @@
     <t>112,8.003199,203</t>
   </si>
   <si>
-    <t>113.5,8,205_110.5,8,205_110.5,8,201_113.5,8,201</t>
+    <t>113.5,8.003199,205_110.5,8.003199,205_110.5,8.003199,201_113.5,8.003199,201</t>
   </si>
   <si>
     <t>74888</t>
   </si>
   <si>
-    <t>112,7.999978,207</t>
+    <t>112,8.000208,207</t>
   </si>
   <si>
     <t>0,74998</t>
@@ -1591,16 +1591,16 @@
     <t>112,7.999978,208</t>
   </si>
   <si>
-    <t>95.7563781738281,-0.04387474,203</t>
-  </si>
-  <si>
-    <t>97.75638,8.046697,204.5_93.75638,8.046697,204.5_93.75638,8.046697,201.5_97.75638,8.046697,201.5</t>
-  </si>
-  <si>
-    <t>96,-0.04387474,209</t>
-  </si>
-  <si>
-    <t>98.25,7.109542,211.25_93.75,7.109542,211.25_93.75,7.109542,206.75_98.25,7.109542,206.75</t>
+    <t>95.7563781738281,7.999978,203</t>
+  </si>
+  <si>
+    <t>97.75638,7.999978,204.5_93.75638,7.999978,204.5_93.75638,7.999978,201.5_97.75638,7.999978,201.5</t>
+  </si>
+  <si>
+    <t>96,7.999978,209</t>
+  </si>
+  <si>
+    <t>98.25,7.999978,211.25_93.75,7.999978,211.25_93.75,7.999978,206.75_98.25,7.999978,206.75</t>
   </si>
   <si>
     <t>70309</t>
@@ -1609,16 +1609,16 @@
     <t>73,7.999978,216</t>
   </si>
   <si>
-    <t>74.5,7.664845,213.75_74.5,7.664845,218.25_71.5,7.664845,218.25_71.5,7.664845,213.75</t>
+    <t>74.5,7.999978,213.75_74.5,7.999978,218.25_71.5,7.999978,218.25_71.5,7.999978,213.75</t>
   </si>
   <si>
     <t>70304</t>
   </si>
   <si>
-    <t>115,9.499898,240</t>
-  </si>
-  <si>
-    <t>116,7.859674,238_116,7.859674,242_114,7.859674,242_114,7.859674,238</t>
+    <t>115,7.999978,240</t>
+  </si>
+  <si>
+    <t>116,7.999978,238_116,7.999978,242_114,7.999978,242_114,7.999978,238</t>
   </si>
   <si>
     <t>74894</t>
@@ -1630,13 +1630,13 @@
     <t>67,7.999978,216</t>
   </si>
   <si>
-    <t>68,7.859674,217_66,7.859674,217_66,7.859674,215_68,7.859674,215</t>
+    <t>68,7.999978,217_66,7.999978,217_66,7.999978,215_68,7.999978,215</t>
   </si>
   <si>
     <t>133,7.999978,238.119369506836</t>
   </si>
   <si>
-    <t>131.5,8,240.1194_131.5,8,236.1194_134.5,8,236.1194_134.5,8,240.1194</t>
+    <t>131.5,7.999978,240.1194_131.5,7.999978,236.1194_134.5,7.999978,236.1194_134.5,7.999978,240.1194</t>
   </si>
   <si>
     <t>100.981590270996,7.999978,172.904113769531</t>
@@ -1648,7 +1648,7 @@
     <t>128,7.999978,296</t>
   </si>
   <si>
-    <t>126.5,8,294_129.5,8,294_129.5,8,298_126.5,8,298</t>
+    <t>126.5,7.999978,294_129.5,7.999978,294_129.5,7.999978,298_126.5,7.999978,298</t>
   </si>
   <si>
     <t>74898,74899,74900</t>
@@ -1657,7 +1657,7 @@
     <t>117.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>118.1416,8,273_118.1416,8,275_116.1416,8,275_116.1416,8,273</t>
+    <t>118.1416,8.003199,273_118.1416,8.003199,275_116.1416,8.003199,275_116.1416,8.003199,273</t>
   </si>
   <si>
     <t>74897</t>
@@ -1666,19 +1666,19 @@
     <t>119.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>120.1416,8,273_120.1416,8,275_118.1416,8,275_118.1416,8,273</t>
+    <t>120.1416,8.003199,273_120.1416,8.003199,275_118.1416,8.003199,275_118.1416,8.003199,273</t>
   </si>
   <si>
     <t>121.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>122.1416,8,273_122.1416,8,275_120.1416,8,275_120.1416,8,273</t>
+    <t>122.1416,8.003199,273_122.1416,8.003199,275_120.1416,8.003199,275_120.1416,8.003199,273</t>
   </si>
   <si>
     <t>135,7.999978,274</t>
   </si>
   <si>
-    <t>132.75,8,276.25_132.75,8,271.75_137.25,8,271.75_137.25,8,276.25</t>
+    <t>132.75,7.999978,276.25_132.75,7.999978,271.75_137.25,7.999978,271.75_137.25,7.999978,276.25</t>
   </si>
   <si>
     <t>70306</t>
@@ -1699,10 +1699,10 @@
     <t>74907</t>
   </si>
   <si>
-    <t>119,-0.04387474,293.976043701172</t>
-  </si>
-  <si>
-    <t>119,-0.04387474,298</t>
+    <t>119,7.999978,293.976043701172</t>
+  </si>
+  <si>
+    <t>119,7.999978,298</t>
   </si>
   <si>
     <t>74909</t>
@@ -1711,34 +1711,43 @@
     <t>113,7.999978,297.976043701172</t>
   </si>
   <si>
-    <t>74.038444519043,14.99987,232</t>
-  </si>
-  <si>
-    <t>75.78844,14,230.5_75.78844,14,233.5_71.78844,14,233.5_71.78844,14,230.5</t>
+    <t>110,7.999978,286</t>
+  </si>
+  <si>
+    <t>107.75,7.999978,283.75_112.25,7.999978,283.75_112.25,7.999978,288.25_107.75,7.999978,288.25</t>
+  </si>
+  <si>
+    <t>70305</t>
+  </si>
+  <si>
+    <t>74.038444519043,13.99992,232</t>
+  </si>
+  <si>
+    <t>75.78844,13.99992,230.5_75.78844,13.99992,233.5_71.78844,13.99992,233.5_71.78844,13.99992,230.5</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_JGfasheqi.prefab</t>
   </si>
   <si>
-    <t>88.038444519043,14.99987,232</t>
-  </si>
-  <si>
-    <t>89.53844,14,233.5_86.53844,14,233.5_86.53844,14,230.5_89.53844,14,230.5</t>
+    <t>88.038444519043,13.99992,232</t>
+  </si>
+  <si>
+    <t>89.53844,13.99992,233.5_86.53844,13.99992,233.5_86.53844,13.99992,230.5_89.53844,13.99992,230.5</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_JGjingzi.prefab</t>
   </si>
   <si>
-    <t>88.038444519043,14.99987,244</t>
-  </si>
-  <si>
-    <t>89.53844,14,245.5_86.53844,14,245.5_86.53844,14,242.5_89.53844,14,242.5</t>
-  </si>
-  <si>
-    <t>74.038444519043,14.99987,253.25</t>
-  </si>
-  <si>
-    <t>72.53844,14,251_75.53844,14,251_75.53844,14,255_72.53844,14,255</t>
+    <t>88.038444519043,13.99992,244</t>
+  </si>
+  <si>
+    <t>89.53844,13.99992,245.5_86.53844,13.99992,245.5_86.53844,13.99992,242.5_89.53844,13.99992,242.5</t>
+  </si>
+  <si>
+    <t>74.038444519043,13.99992,253.25</t>
+  </si>
+  <si>
+    <t>72.53844,13.99992,251_75.53844,13.99992,251_75.53844,13.99992,255_72.53844,13.99992,255</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_JGJieshouqi.prefab</t>
@@ -1747,22 +1756,22 @@
     <t>74983</t>
   </si>
   <si>
-    <t>78,14.99987,255</t>
-  </si>
-  <si>
-    <t>80,14,256_76,14,256_76,14,254_80,14,254</t>
+    <t>78,13.99992,255</t>
+  </si>
+  <si>
+    <t>80,13.99992,256_76,13.99992,256_76,13.99992,254_80,13.99992,254</t>
   </si>
   <si>
     <t>74981</t>
   </si>
   <si>
-    <t>74.038444519043,14.99987,244</t>
-  </si>
-  <si>
-    <t>75.53844,14,245.5_72.53844,14,245.5_72.53844,14,242.5_75.53844,14,242.5</t>
-  </si>
-  <si>
-    <t>62.2290153503418,14.99987,253.647537231445</t>
+    <t>74.038444519043,13.99992,244</t>
+  </si>
+  <si>
+    <t>75.53844,13.99992,245.5_72.53844,13.99992,245.5_72.53844,13.99992,242.5_75.53844,13.99992,242.5</t>
+  </si>
+  <si>
+    <t>62.2290153503418,13.99992,253.647537231445</t>
   </si>
   <si>
     <t>62.23,0.00,253.65,97.86,0.00,253.65,97.86,0.00,222.24,62.23,0.00,222.24</t>
@@ -1771,19 +1780,28 @@
     <t>143,7.999978,274</t>
   </si>
   <si>
-    <t>142,8,273_144,8,273_144,8,275_142,8,275</t>
+    <t>142,7.999978,273_144,7.999978,273_144,7.999978,275_142,7.999978,275</t>
   </si>
   <si>
     <t>90.9580841064453,7.999978,221</t>
   </si>
   <si>
-    <t>92.95808,8,222.5_88.95808,8,222.5_88.95808,8,219.5_92.95808,8,219.5</t>
+    <t>92.95808,7.999978,222.5_88.95808,7.999978,222.5_88.95808,7.999978,219.5_92.95808,7.999978,219.5</t>
   </si>
   <si>
     <t>74991</t>
   </si>
   <si>
-    <t>75,14.99987,266</t>
+    <t>75,13.99992,266</t>
+  </si>
+  <si>
+    <t>91,13.99992,224.229995727539</t>
+  </si>
+  <si>
+    <t>88.75,13.99992,221.98_93.25,13.99992,221.98_93.25,13.99992,226.48_88.75,13.99992,226.48</t>
+  </si>
+  <si>
+    <t>70307</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -3391,7 +3409,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA342"/>
+  <dimension ref="A1:AA344"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -22313,19 +22331,19 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>74979</v>
+        <v>74999</v>
       </c>
       <c r="D247" s="50" t="s">
         <v>564</v>
       </c>
       <c r="E247" s="50">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="F247" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H247" s="50" t="s">
         <v>565</v>
@@ -22337,7 +22355,7 @@
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>566</v>
+        <v>297</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
@@ -22351,7 +22369,9 @@
       <c r="O247" s="50">
         <v>0</v>
       </c>
-      <c r="P247" s="50"/>
+      <c r="P247" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q247" s="50">
         <v>0</v>
       </c>
@@ -22361,8 +22381,8 @@
       <c r="S247" s="50">
         <v>0</v>
       </c>
-      <c r="T247" s="50">
-        <v>0</v>
+      <c r="T247" s="50" t="s">
+        <v>566</v>
       </c>
       <c r="U247" s="50">
         <v>0</v>
@@ -22394,19 +22414,19 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>74982</v>
+        <v>74979</v>
       </c>
       <c r="D248" s="50" t="s">
         <v>567</v>
       </c>
       <c r="E248" s="50">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F248" s="50">
         <v>0</v>
       </c>
       <c r="G248" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H248" s="50" t="s">
         <v>568</v>
@@ -22475,7 +22495,7 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>74984</v>
+        <v>74982</v>
       </c>
       <c r="D249" s="50" t="s">
         <v>570</v>
@@ -22499,7 +22519,7 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22556,22 +22576,22 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>74981</v>
+        <v>74984</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E250" s="50">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F250" s="50">
         <v>0</v>
       </c>
       <c r="G250" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H250" s="50" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>78</v>
@@ -22580,13 +22600,13 @@
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M250" s="50" t="s">
-        <v>575</v>
+        <v>1</v>
       </c>
       <c r="N250" s="50">
         <v>7</v>
@@ -22637,22 +22657,22 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>74983</v>
+        <v>74981</v>
       </c>
       <c r="D251" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="E251" s="50">
+        <v>47</v>
+      </c>
+      <c r="F251" s="50">
+        <v>0</v>
+      </c>
+      <c r="G251" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H251" s="50" t="s">
         <v>576</v>
-      </c>
-      <c r="E251" s="50">
-        <v>16</v>
-      </c>
-      <c r="F251" s="50">
-        <v>7</v>
-      </c>
-      <c r="G251" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H251" s="50" t="s">
-        <v>577</v>
       </c>
       <c r="I251" s="50" t="s">
         <v>78</v>
@@ -22661,13 +22681,13 @@
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>192</v>
+        <v>577</v>
       </c>
       <c r="L251" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M251" s="50" t="s">
         <v>578</v>
-      </c>
-      <c r="M251" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N251" s="50">
         <v>7</v>
@@ -22718,16 +22738,16 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>74985</v>
+        <v>74983</v>
       </c>
       <c r="D252" s="50" t="s">
         <v>579</v>
       </c>
       <c r="E252" s="50">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F252" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G252" s="50" t="s">
         <v>60</v>
@@ -22742,10 +22762,10 @@
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>569</v>
+        <v>192</v>
       </c>
       <c r="L252" s="50" t="s">
-        <v>1</v>
+        <v>581</v>
       </c>
       <c r="M252" s="50" t="s">
         <v>1</v>
@@ -22799,47 +22819,78 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>74988</v>
+        <v>74985</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E253" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F253" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G253" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H253" s="50" t="s">
+        <v>583</v>
+      </c>
       <c r="I253" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J253" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K253" s="50"/>
-      <c r="L253" s="50"/>
-      <c r="M253" s="50"/>
+      <c r="K253" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M253" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N253" s="50">
         <v>7</v>
       </c>
-      <c r="O253" s="50"/>
-      <c r="P253" s="50" t="s">
-        <v>582</v>
-      </c>
-      <c r="Q253" s="50"/>
-      <c r="R253" s="50"/>
-      <c r="S253" s="50"/>
-      <c r="T253" s="50"/>
-      <c r="U253" s="50"/>
-      <c r="V253" s="50"/>
-      <c r="W253" s="50"/>
-      <c r="X253" s="50"/>
-      <c r="Y253" s="50"/>
-      <c r="Z253" s="52"/>
-      <c r="AA253" s="50"/>
+      <c r="O253" s="50">
+        <v>0</v>
+      </c>
+      <c r="P253" s="50"/>
+      <c r="Q253" s="50">
+        <v>0</v>
+      </c>
+      <c r="R253" s="50">
+        <v>0</v>
+      </c>
+      <c r="S253" s="50">
+        <v>0</v>
+      </c>
+      <c r="T253" s="50">
+        <v>0</v>
+      </c>
+      <c r="U253" s="50">
+        <v>0</v>
+      </c>
+      <c r="V253" s="50">
+        <v>0</v>
+      </c>
+      <c r="W253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y253" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z253" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA253" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="50">
@@ -22849,78 +22900,47 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>74991</v>
+        <v>74988</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E254" s="50">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F254" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G254" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H254" s="50" t="s">
-        <v>584</v>
+        <v>60</v>
       </c>
       <c r="I254" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J254" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K254" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="L254" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M254" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K254" s="50"/>
+      <c r="L254" s="50"/>
+      <c r="M254" s="50"/>
       <c r="N254" s="50">
         <v>7</v>
       </c>
-      <c r="O254" s="50">
-        <v>0</v>
-      </c>
-      <c r="P254" s="50"/>
-      <c r="Q254" s="50">
-        <v>0</v>
-      </c>
-      <c r="R254" s="50">
-        <v>0</v>
-      </c>
-      <c r="S254" s="50">
-        <v>0</v>
-      </c>
-      <c r="T254" s="50">
-        <v>0</v>
-      </c>
-      <c r="U254" s="50">
-        <v>0</v>
-      </c>
-      <c r="V254" s="50">
-        <v>0</v>
-      </c>
-      <c r="W254" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X254" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y254" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z254" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA254" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O254" s="50"/>
+      <c r="P254" s="50" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q254" s="50"/>
+      <c r="R254" s="50"/>
+      <c r="S254" s="50"/>
+      <c r="T254" s="50"/>
+      <c r="U254" s="50"/>
+      <c r="V254" s="50"/>
+      <c r="W254" s="50"/>
+      <c r="X254" s="50"/>
+      <c r="Y254" s="50"/>
+      <c r="Z254" s="52"/>
+      <c r="AA254" s="50"/>
     </row>
     <row r="255">
       <c r="A255" s="50">
@@ -22930,22 +22950,22 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>74990</v>
+        <v>74991</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E255" s="50">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F255" s="50">
         <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H255" s="50" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I255" s="50" t="s">
         <v>78</v>
@@ -22954,10 +22974,10 @@
         <v>62</v>
       </c>
       <c r="K255" s="50" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="L255" s="50" t="s">
-        <v>587</v>
+        <v>1</v>
       </c>
       <c r="M255" s="50" t="s">
         <v>1</v>
@@ -23011,13 +23031,13 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>74989</v>
+        <v>74990</v>
       </c>
       <c r="D256" s="50" t="s">
         <v>588</v>
       </c>
       <c r="E256" s="50">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F256" s="50">
         <v>0</v>
@@ -23025,17 +23045,20 @@
       <c r="G256" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H256" s="50" t="s">
+        <v>589</v>
+      </c>
       <c r="I256" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J256" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="L256" s="50" t="s">
-        <v>61</v>
+        <v>590</v>
       </c>
       <c r="M256" s="50" t="s">
         <v>1</v>
@@ -23046,9 +23069,7 @@
       <c r="O256" s="50">
         <v>0</v>
       </c>
-      <c r="P256" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P256" s="50"/>
       <c r="Q256" s="50">
         <v>0</v>
       </c>
@@ -23091,13 +23112,13 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>84928</v>
+        <v>74989</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E257" s="50">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
@@ -23112,16 +23133,16 @@
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L257" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M257" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N257" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O257" s="50">
         <v>0</v>
@@ -23171,22 +23192,22 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>84929</v>
+        <v>75000</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E258" s="50">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F258" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G258" s="50" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H258" s="50" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I258" s="50" t="s">
         <v>78</v>
@@ -23195,21 +23216,23 @@
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>377</v>
+        <v>222</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>592</v>
+        <v>1</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N258" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O258" s="50">
         <v>0</v>
       </c>
-      <c r="P258" s="50"/>
+      <c r="P258" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q258" s="50">
         <v>0</v>
       </c>
@@ -23219,8 +23242,8 @@
       <c r="S258" s="50">
         <v>0</v>
       </c>
-      <c r="T258" s="50">
-        <v>0</v>
+      <c r="T258" s="50" t="s">
+        <v>594</v>
       </c>
       <c r="U258" s="50">
         <v>0</v>
@@ -23252,19 +23275,19 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>84930</v>
+        <v>84928</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E259" s="50">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F259" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>61</v>
@@ -23273,13 +23296,13 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>594</v>
+        <v>1</v>
       </c>
       <c r="M259" s="50" t="s">
-        <v>595</v>
+        <v>1</v>
       </c>
       <c r="N259" s="50">
         <v>8</v>
@@ -23287,7 +23310,9 @@
       <c r="O259" s="50">
         <v>0</v>
       </c>
-      <c r="P259" s="50"/>
+      <c r="P259" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q259" s="50">
         <v>0</v>
       </c>
@@ -23330,19 +23355,19 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>84931</v>
+        <v>84929</v>
       </c>
       <c r="D260" s="50" t="s">
         <v>596</v>
       </c>
       <c r="E260" s="50">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F260" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G260" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H260" s="50" t="s">
         <v>597</v>
@@ -23354,10 +23379,10 @@
         <v>62</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>1</v>
+        <v>598</v>
       </c>
       <c r="M260" s="50" t="s">
         <v>1</v>
@@ -23411,10 +23436,10 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>84932</v>
+        <v>84930</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E261" s="50">
         <v>57</v>
@@ -23423,7 +23448,7 @@
         <v>1</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I261" s="50" t="s">
         <v>61</v>
@@ -23435,10 +23460,10 @@
         <v>388</v>
       </c>
       <c r="L261" s="50" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M261" s="50" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="N261" s="50">
         <v>8</v>
@@ -23489,10 +23514,10 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>84933</v>
+        <v>84931</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E262" s="50">
         <v>32</v>
@@ -23501,10 +23526,10 @@
         <v>1</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H262" s="50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I262" s="50" t="s">
         <v>78</v>
@@ -23570,37 +23595,34 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>84934</v>
+        <v>84932</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E263" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F263" s="50">
         <v>1</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H263" s="50" t="s">
-        <v>603</v>
+        <v>60</v>
       </c>
       <c r="I263" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J263" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>1</v>
+        <v>601</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23651,22 +23673,22 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>84935</v>
+        <v>84933</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E264" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F264" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G264" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23675,7 +23697,7 @@
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="L264" s="50" t="s">
         <v>1</v>
@@ -23732,22 +23754,22 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>84936</v>
+        <v>84934</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E265" s="50">
         <v>31</v>
       </c>
       <c r="F265" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G265" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H265" s="50" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I265" s="50" t="s">
         <v>78</v>
@@ -23756,7 +23778,7 @@
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L265" s="50" t="s">
         <v>1</v>
@@ -23787,7 +23809,7 @@
         <v>0</v>
       </c>
       <c r="V265" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W265" s="50" t="s">
         <v>1</v>
@@ -23813,22 +23835,22 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>84937</v>
+        <v>84935</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E266" s="50">
         <v>31</v>
       </c>
       <c r="F266" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G266" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H266" s="50" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I266" s="50" t="s">
         <v>78</v>
@@ -23837,7 +23859,7 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -23868,7 +23890,7 @@
         <v>0</v>
       </c>
       <c r="V266" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W266" s="50" t="s">
         <v>1</v>
@@ -23894,22 +23916,22 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>84938</v>
+        <v>84936</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E267" s="50">
         <v>31</v>
       </c>
       <c r="F267" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -23918,7 +23940,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23949,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="V267" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W267" s="50" t="s">
         <v>1</v>
@@ -23975,22 +23997,22 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>84939</v>
+        <v>84937</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E268" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F268" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G268" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -23999,7 +24021,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -24030,7 +24052,7 @@
         <v>0</v>
       </c>
       <c r="V268" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W268" s="50" t="s">
         <v>1</v>
@@ -24056,22 +24078,22 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>84940</v>
+        <v>84938</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E269" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F269" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G269" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -24080,7 +24102,7 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -24137,22 +24159,22 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>84941</v>
+        <v>84939</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E270" s="50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F270" s="50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G270" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -24161,10 +24183,10 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>192</v>
+        <v>394</v>
       </c>
       <c r="L270" s="50" t="s">
-        <v>618</v>
+        <v>1</v>
       </c>
       <c r="M270" s="50" t="s">
         <v>1</v>
@@ -24218,34 +24240,37 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>84942</v>
+        <v>84940</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E271" s="50">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F271" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G271" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H271" s="50" t="s">
+        <v>621</v>
+      </c>
       <c r="I271" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J271" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="L271" s="50" t="s">
-        <v>620</v>
+        <v>1</v>
       </c>
       <c r="M271" s="50" t="s">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="N271" s="50">
         <v>8</v>
@@ -24296,16 +24321,16 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>84943</v>
+        <v>84941</v>
       </c>
       <c r="D272" s="50" t="s">
         <v>622</v>
       </c>
       <c r="E272" s="50">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F272" s="50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G272" s="50" t="s">
         <v>60</v>
@@ -24320,10 +24345,10 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>1</v>
+        <v>624</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -24377,16 +24402,16 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>84944</v>
+        <v>84942</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E273" s="50">
         <v>52</v>
       </c>
       <c r="F273" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G273" s="50" t="s">
         <v>60</v>
@@ -24398,13 +24423,13 @@
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M273" s="50" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="N273" s="50">
         <v>8</v>
@@ -24455,22 +24480,22 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>84945</v>
+        <v>84943</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E274" s="50">
         <v>51</v>
       </c>
       <c r="F274" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G274" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24479,7 +24504,7 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L274" s="50" t="s">
         <v>1</v>
@@ -24536,16 +24561,16 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>84946</v>
+        <v>84944</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E275" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F275" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G275" s="50" t="s">
         <v>60</v>
@@ -24557,13 +24582,13 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>629</v>
+        <v>271</v>
       </c>
       <c r="L275" s="50" t="s">
-        <v>1</v>
+        <v>631</v>
       </c>
       <c r="M275" s="50" t="s">
-        <v>1</v>
+        <v>627</v>
       </c>
       <c r="N275" s="50">
         <v>8</v>
@@ -24614,28 +24639,31 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>84947</v>
+        <v>84945</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E276" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F276" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H276" s="50" t="s">
+        <v>633</v>
+      </c>
       <c r="I276" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J276" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="L276" s="50" t="s">
         <v>1</v>
@@ -24692,16 +24720,16 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>84948</v>
+        <v>84946</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E277" s="50">
         <v>56</v>
       </c>
       <c r="F277" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" s="50" t="s">
         <v>60</v>
@@ -24713,7 +24741,7 @@
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>301</v>
+        <v>635</v>
       </c>
       <c r="L277" s="50" t="s">
         <v>1</v>
@@ -24770,10 +24798,10 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>84949</v>
+        <v>84947</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E278" s="50">
         <v>56</v>
@@ -24848,10 +24876,10 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>84950</v>
+        <v>84948</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
@@ -24926,10 +24954,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>84951</v>
+        <v>84949</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25004,10 +25032,10 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>84952</v>
+        <v>84950</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25082,10 +25110,10 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>84953</v>
+        <v>84951</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25160,10 +25188,10 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>84954</v>
+        <v>84952</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25238,10 +25266,10 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>84955</v>
+        <v>84953</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25316,10 +25344,10 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>84956</v>
+        <v>84954</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25394,10 +25422,10 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>84957</v>
+        <v>84955</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25472,10 +25500,10 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>84958</v>
+        <v>84956</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25550,10 +25578,10 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>84959</v>
+        <v>84957</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25628,10 +25656,10 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>84960</v>
+        <v>84958</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E289" s="50">
         <v>56</v>
@@ -25706,10 +25734,10 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>84961</v>
+        <v>84959</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E290" s="50">
         <v>56</v>
@@ -25784,10 +25812,10 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>84962</v>
+        <v>84960</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E291" s="50">
         <v>56</v>
@@ -25862,10 +25890,10 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>84963</v>
+        <v>84961</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E292" s="50">
         <v>56</v>
@@ -25940,10 +25968,10 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>84964</v>
+        <v>84962</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E293" s="50">
         <v>56</v>
@@ -26018,10 +26046,10 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>84965</v>
+        <v>84963</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E294" s="50">
         <v>56</v>
@@ -26096,10 +26124,10 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>84966</v>
+        <v>84964</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E295" s="50">
         <v>56</v>
@@ -26174,10 +26202,10 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>84967</v>
+        <v>84965</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E296" s="50">
         <v>56</v>
@@ -26252,10 +26280,10 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>84968</v>
+        <v>84966</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E297" s="50">
         <v>56</v>
@@ -26330,31 +26358,28 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>84969</v>
+        <v>84967</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E298" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F298" s="50">
         <v>0</v>
       </c>
       <c r="G298" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H298" s="50" t="s">
-        <v>653</v>
+        <v>60</v>
       </c>
       <c r="I298" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J298" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>566</v>
+        <v>301</v>
       </c>
       <c r="L298" s="50" t="s">
         <v>1</v>
@@ -26411,31 +26436,28 @@
         <v>58</v>
       </c>
       <c r="C299" s="50">
-        <v>84970</v>
+        <v>84968</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E299" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F299" s="50">
         <v>0</v>
       </c>
       <c r="G299" s="50" t="s">
-        <v>655</v>
-      </c>
-      <c r="H299" s="50" t="s">
-        <v>656</v>
+        <v>60</v>
       </c>
       <c r="I299" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J299" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K299" s="50" t="s">
-        <v>569</v>
+        <v>301</v>
       </c>
       <c r="L299" s="50" t="s">
         <v>1</v>
@@ -26492,22 +26514,22 @@
         <v>58</v>
       </c>
       <c r="C300" s="50">
-        <v>84971</v>
+        <v>84969</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E300" s="50">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F300" s="50">
         <v>0</v>
       </c>
       <c r="G300" s="50" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H300" s="50" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I300" s="50" t="s">
         <v>78</v>
@@ -26516,13 +26538,13 @@
         <v>62</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="L300" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M300" s="50" t="s">
-        <v>659</v>
+        <v>1</v>
       </c>
       <c r="N300" s="50">
         <v>8</v>
@@ -26573,7 +26595,7 @@
         <v>58</v>
       </c>
       <c r="C301" s="50">
-        <v>84972</v>
+        <v>84970</v>
       </c>
       <c r="D301" s="50" t="s">
         <v>660</v>
@@ -26597,7 +26619,7 @@
         <v>62</v>
       </c>
       <c r="K301" s="50" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L301" s="50" t="s">
         <v>1</v>
@@ -26654,19 +26676,19 @@
         <v>58</v>
       </c>
       <c r="C302" s="50">
-        <v>84973</v>
+        <v>84971</v>
       </c>
       <c r="D302" s="50" t="s">
         <v>663</v>
       </c>
       <c r="E302" s="50">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F302" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G302" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H302" s="50" t="s">
         <v>664</v>
@@ -26678,13 +26700,13 @@
         <v>62</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>192</v>
+        <v>577</v>
       </c>
       <c r="L302" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M302" s="50" t="s">
         <v>665</v>
-      </c>
-      <c r="M302" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N302" s="50">
         <v>8</v>
@@ -26735,7 +26757,7 @@
         <v>58</v>
       </c>
       <c r="C303" s="50">
-        <v>84974</v>
+        <v>84972</v>
       </c>
       <c r="D303" s="50" t="s">
         <v>666</v>
@@ -26747,10 +26769,10 @@
         <v>0</v>
       </c>
       <c r="G303" s="50" t="s">
-        <v>60</v>
+        <v>667</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>78</v>
@@ -26759,7 +26781,7 @@
         <v>62</v>
       </c>
       <c r="K303" s="50" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L303" s="50" t="s">
         <v>1</v>
@@ -26816,47 +26838,78 @@
         <v>58</v>
       </c>
       <c r="C304" s="50">
-        <v>84976</v>
+        <v>84973</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E304" s="50">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F304" s="50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G304" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H304" s="50" t="s">
+        <v>670</v>
+      </c>
       <c r="I304" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J304" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K304" s="50"/>
-      <c r="L304" s="50"/>
-      <c r="M304" s="50"/>
+      <c r="K304" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L304" s="50" t="s">
+        <v>671</v>
+      </c>
+      <c r="M304" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N304" s="50">
         <v>8</v>
       </c>
-      <c r="O304" s="50"/>
-      <c r="P304" s="50" t="s">
-        <v>669</v>
-      </c>
-      <c r="Q304" s="50"/>
-      <c r="R304" s="50"/>
-      <c r="S304" s="50"/>
-      <c r="T304" s="50"/>
-      <c r="U304" s="50"/>
-      <c r="V304" s="50"/>
-      <c r="W304" s="50"/>
-      <c r="X304" s="50"/>
-      <c r="Y304" s="50"/>
-      <c r="Z304" s="52"/>
-      <c r="AA304" s="50"/>
+      <c r="O304" s="50">
+        <v>0</v>
+      </c>
+      <c r="P304" s="50"/>
+      <c r="Q304" s="50">
+        <v>0</v>
+      </c>
+      <c r="R304" s="50">
+        <v>0</v>
+      </c>
+      <c r="S304" s="50">
+        <v>0</v>
+      </c>
+      <c r="T304" s="50">
+        <v>0</v>
+      </c>
+      <c r="U304" s="50">
+        <v>0</v>
+      </c>
+      <c r="V304" s="50">
+        <v>0</v>
+      </c>
+      <c r="W304" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X304" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y304" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z304" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA304" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="50">
@@ -26866,47 +26919,78 @@
         <v>58</v>
       </c>
       <c r="C305" s="50">
-        <v>84977</v>
+        <v>84974</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E305" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F305" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G305" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H305" s="50" t="s">
+        <v>673</v>
+      </c>
       <c r="I305" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J305" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K305" s="50"/>
-      <c r="L305" s="50"/>
-      <c r="M305" s="50"/>
+      <c r="K305" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L305" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M305" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N305" s="50">
         <v>8</v>
       </c>
-      <c r="O305" s="50"/>
-      <c r="P305" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="Q305" s="50"/>
-      <c r="R305" s="50"/>
-      <c r="S305" s="50"/>
-      <c r="T305" s="50"/>
-      <c r="U305" s="50"/>
-      <c r="V305" s="50"/>
-      <c r="W305" s="50"/>
-      <c r="X305" s="50"/>
-      <c r="Y305" s="50"/>
-      <c r="Z305" s="52"/>
-      <c r="AA305" s="50"/>
+      <c r="O305" s="50">
+        <v>0</v>
+      </c>
+      <c r="P305" s="50"/>
+      <c r="Q305" s="50">
+        <v>0</v>
+      </c>
+      <c r="R305" s="50">
+        <v>0</v>
+      </c>
+      <c r="S305" s="50">
+        <v>0</v>
+      </c>
+      <c r="T305" s="50">
+        <v>0</v>
+      </c>
+      <c r="U305" s="50">
+        <v>0</v>
+      </c>
+      <c r="V305" s="50">
+        <v>0</v>
+      </c>
+      <c r="W305" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X305" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y305" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z305" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA305" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="50">
@@ -26916,16 +27000,16 @@
         <v>58</v>
       </c>
       <c r="C306" s="50">
-        <v>84978</v>
+        <v>84976</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E306" s="50">
         <v>2</v>
       </c>
       <c r="F306" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G306" s="50" t="s">
         <v>60</v>
@@ -26944,7 +27028,7 @@
       </c>
       <c r="O306" s="50"/>
       <c r="P306" s="50" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="Q306" s="50"/>
       <c r="R306" s="50"/>
@@ -26966,78 +27050,47 @@
         <v>58</v>
       </c>
       <c r="C307" s="50">
-        <v>84979</v>
+        <v>84977</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E307" s="50">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F307" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G307" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H307" s="50" t="s">
-        <v>675</v>
+        <v>60</v>
       </c>
       <c r="I307" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J307" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K307" s="50" t="s">
-        <v>327</v>
-      </c>
-      <c r="L307" s="50" t="s">
-        <v>676</v>
-      </c>
-      <c r="M307" s="50" t="s">
-        <v>677</v>
-      </c>
+      <c r="K307" s="50"/>
+      <c r="L307" s="50"/>
+      <c r="M307" s="50"/>
       <c r="N307" s="50">
         <v>8</v>
       </c>
-      <c r="O307" s="50">
-        <v>0</v>
-      </c>
-      <c r="P307" s="50"/>
-      <c r="Q307" s="50">
-        <v>0</v>
-      </c>
-      <c r="R307" s="50">
-        <v>0</v>
-      </c>
-      <c r="S307" s="50">
-        <v>0</v>
-      </c>
-      <c r="T307" s="50">
-        <v>0</v>
-      </c>
-      <c r="U307" s="50">
-        <v>0</v>
-      </c>
-      <c r="V307" s="50">
-        <v>0</v>
-      </c>
-      <c r="W307" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X307" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y307" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z307" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA307" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O307" s="50"/>
+      <c r="P307" s="50" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q307" s="50"/>
+      <c r="R307" s="50"/>
+      <c r="S307" s="50"/>
+      <c r="T307" s="50"/>
+      <c r="U307" s="50"/>
+      <c r="V307" s="50"/>
+      <c r="W307" s="50"/>
+      <c r="X307" s="50"/>
+      <c r="Y307" s="50"/>
+      <c r="Z307" s="52"/>
+      <c r="AA307" s="50"/>
     </row>
     <row r="308">
       <c r="A308" s="50">
@@ -27047,78 +27100,47 @@
         <v>58</v>
       </c>
       <c r="C308" s="50">
-        <v>84980</v>
+        <v>84978</v>
       </c>
       <c r="D308" s="50" t="s">
         <v>678</v>
       </c>
       <c r="E308" s="50">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="F308" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G308" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H308" s="50" t="s">
-        <v>679</v>
-      </c>
       <c r="I308" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J308" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K308" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="L308" s="50" t="s">
-        <v>680</v>
-      </c>
-      <c r="M308" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K308" s="50"/>
+      <c r="L308" s="50"/>
+      <c r="M308" s="50"/>
       <c r="N308" s="50">
         <v>8</v>
       </c>
-      <c r="O308" s="50">
-        <v>0</v>
-      </c>
-      <c r="P308" s="50"/>
-      <c r="Q308" s="50">
-        <v>0</v>
-      </c>
-      <c r="R308" s="50">
-        <v>0</v>
-      </c>
-      <c r="S308" s="50">
-        <v>0</v>
-      </c>
-      <c r="T308" s="50">
-        <v>0</v>
-      </c>
-      <c r="U308" s="50">
-        <v>0</v>
-      </c>
-      <c r="V308" s="50">
-        <v>0</v>
-      </c>
-      <c r="W308" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X308" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y308" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z308" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA308" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O308" s="50"/>
+      <c r="P308" s="50" t="s">
+        <v>679</v>
+      </c>
+      <c r="Q308" s="50"/>
+      <c r="R308" s="50"/>
+      <c r="S308" s="50"/>
+      <c r="T308" s="50"/>
+      <c r="U308" s="50"/>
+      <c r="V308" s="50"/>
+      <c r="W308" s="50"/>
+      <c r="X308" s="50"/>
+      <c r="Y308" s="50"/>
+      <c r="Z308" s="52"/>
+      <c r="AA308" s="50"/>
     </row>
     <row r="309">
       <c r="A309" s="50">
@@ -27128,22 +27150,22 @@
         <v>58</v>
       </c>
       <c r="C309" s="50">
-        <v>84981</v>
+        <v>84979</v>
       </c>
       <c r="D309" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="E309" s="50">
+        <v>48</v>
+      </c>
+      <c r="F309" s="50">
+        <v>0</v>
+      </c>
+      <c r="G309" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H309" s="50" t="s">
         <v>681</v>
-      </c>
-      <c r="E309" s="50">
-        <v>50</v>
-      </c>
-      <c r="F309" s="50">
-        <v>0</v>
-      </c>
-      <c r="G309" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H309" s="50" t="s">
-        <v>682</v>
       </c>
       <c r="I309" s="50" t="s">
         <v>78</v>
@@ -27152,13 +27174,13 @@
         <v>62</v>
       </c>
       <c r="K309" s="50" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L309" s="50" t="s">
-        <v>1</v>
+        <v>682</v>
       </c>
       <c r="M309" s="50" t="s">
-        <v>1</v>
+        <v>683</v>
       </c>
       <c r="N309" s="50">
         <v>8</v>
@@ -27209,13 +27231,13 @@
         <v>58</v>
       </c>
       <c r="C310" s="50">
-        <v>84982</v>
+        <v>84980</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E310" s="50">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F310" s="50">
         <v>0</v>
@@ -27223,20 +27245,23 @@
       <c r="G310" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H310" s="50" t="s">
+        <v>685</v>
+      </c>
       <c r="I310" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J310" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K310" s="50" t="s">
-        <v>684</v>
+        <v>324</v>
       </c>
       <c r="L310" s="50" t="s">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="M310" s="50" t="s">
-        <v>685</v>
+        <v>1</v>
       </c>
       <c r="N310" s="50">
         <v>8</v>
@@ -27244,9 +27269,7 @@
       <c r="O310" s="50">
         <v>0</v>
       </c>
-      <c r="P310" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P310" s="50"/>
       <c r="Q310" s="50">
         <v>0</v>
       </c>
@@ -27289,13 +27312,13 @@
         <v>58</v>
       </c>
       <c r="C311" s="50">
-        <v>84983</v>
+        <v>84981</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E311" s="50">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F311" s="50">
         <v>0</v>
@@ -27304,7 +27327,7 @@
         <v>60</v>
       </c>
       <c r="H311" s="50" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I311" s="50" t="s">
         <v>78</v>
@@ -27313,7 +27336,7 @@
         <v>62</v>
       </c>
       <c r="K311" s="50" t="s">
-        <v>687</v>
+        <v>331</v>
       </c>
       <c r="L311" s="50" t="s">
         <v>1</v>
@@ -27327,9 +27350,7 @@
       <c r="O311" s="50">
         <v>0</v>
       </c>
-      <c r="P311" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P311" s="50"/>
       <c r="Q311" s="50">
         <v>0</v>
       </c>
@@ -27372,13 +27393,13 @@
         <v>58</v>
       </c>
       <c r="C312" s="50">
-        <v>84984</v>
+        <v>84982</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E312" s="50">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F312" s="50">
         <v>0</v>
@@ -27386,11 +27407,8 @@
       <c r="G312" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H312" s="50" t="s">
-        <v>689</v>
-      </c>
       <c r="I312" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J312" s="50" t="s">
         <v>62</v>
@@ -27402,7 +27420,7 @@
         <v>1</v>
       </c>
       <c r="M312" s="50" t="s">
-        <v>1</v>
+        <v>691</v>
       </c>
       <c r="N312" s="50">
         <v>8</v>
@@ -27455,16 +27473,16 @@
         <v>58</v>
       </c>
       <c r="C313" s="50">
-        <v>330037</v>
+        <v>84983</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E313" s="50">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F313" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G313" s="50" t="s">
         <v>60</v>
@@ -27479,7 +27497,7 @@
         <v>62</v>
       </c>
       <c r="K313" s="50" t="s">
-        <v>96</v>
+        <v>693</v>
       </c>
       <c r="L313" s="50" t="s">
         <v>1</v>
@@ -27488,7 +27506,7 @@
         <v>1</v>
       </c>
       <c r="N313" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O313" s="50">
         <v>0</v>
@@ -27505,8 +27523,8 @@
       <c r="S313" s="50">
         <v>0</v>
       </c>
-      <c r="T313" s="50" t="s">
-        <v>61</v>
+      <c r="T313" s="50">
+        <v>0</v>
       </c>
       <c r="U313" s="50">
         <v>0</v>
@@ -27538,22 +27556,22 @@
         <v>58</v>
       </c>
       <c r="C314" s="50">
-        <v>330038</v>
+        <v>84984</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E314" s="50">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F314" s="50">
         <v>0</v>
       </c>
       <c r="G314" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H314" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I314" s="50" t="s">
         <v>78</v>
@@ -27562,21 +27580,23 @@
         <v>62</v>
       </c>
       <c r="K314" s="50" t="s">
-        <v>142</v>
+        <v>696</v>
       </c>
       <c r="L314" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M314" s="50" t="s">
-        <v>695</v>
+        <v>1</v>
       </c>
       <c r="N314" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O314" s="50">
         <v>0</v>
       </c>
-      <c r="P314" s="50"/>
+      <c r="P314" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q314" s="50">
         <v>0</v>
       </c>
@@ -27619,22 +27639,22 @@
         <v>58</v>
       </c>
       <c r="C315" s="50">
-        <v>330039</v>
+        <v>330037</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E315" s="50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F315" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H315" s="50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I315" s="50" t="s">
         <v>78</v>
@@ -27643,10 +27663,10 @@
         <v>62</v>
       </c>
       <c r="K315" s="50" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="L315" s="50" t="s">
-        <v>698</v>
+        <v>1</v>
       </c>
       <c r="M315" s="50" t="s">
         <v>1</v>
@@ -27657,7 +27677,9 @@
       <c r="O315" s="50">
         <v>0</v>
       </c>
-      <c r="P315" s="50"/>
+      <c r="P315" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q315" s="50">
         <v>0</v>
       </c>
@@ -27667,8 +27689,8 @@
       <c r="S315" s="50">
         <v>0</v>
       </c>
-      <c r="T315" s="50">
-        <v>0</v>
+      <c r="T315" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U315" s="50">
         <v>0</v>
@@ -27700,19 +27722,19 @@
         <v>58</v>
       </c>
       <c r="C316" s="50">
-        <v>330040</v>
+        <v>330038</v>
       </c>
       <c r="D316" s="50" t="s">
         <v>699</v>
       </c>
       <c r="E316" s="50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F316" s="50">
         <v>0</v>
       </c>
       <c r="G316" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H316" s="50" t="s">
         <v>700</v>
@@ -27724,13 +27746,13 @@
         <v>62</v>
       </c>
       <c r="K316" s="50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L316" s="50" t="s">
-        <v>698</v>
+        <v>1</v>
       </c>
       <c r="M316" s="50" t="s">
-        <v>1</v>
+        <v>701</v>
       </c>
       <c r="N316" s="50">
         <v>33</v>
@@ -27781,10 +27803,10 @@
         <v>58</v>
       </c>
       <c r="C317" s="50">
-        <v>330041</v>
+        <v>330039</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E317" s="50">
         <v>7</v>
@@ -27796,7 +27818,7 @@
         <v>138</v>
       </c>
       <c r="H317" s="50" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I317" s="50" t="s">
         <v>78</v>
@@ -27808,7 +27830,7 @@
         <v>147</v>
       </c>
       <c r="L317" s="50" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="M317" s="50" t="s">
         <v>1</v>
@@ -27862,22 +27884,22 @@
         <v>58</v>
       </c>
       <c r="C318" s="50">
-        <v>330042</v>
+        <v>330040</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E318" s="50">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F318" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H318" s="50" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I318" s="50" t="s">
         <v>78</v>
@@ -27886,13 +27908,13 @@
         <v>62</v>
       </c>
       <c r="K318" s="50" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="L318" s="50" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M318" s="50" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="N318" s="50">
         <v>33</v>
@@ -27943,19 +27965,19 @@
         <v>58</v>
       </c>
       <c r="C319" s="50">
-        <v>330043</v>
+        <v>330041</v>
       </c>
       <c r="D319" s="50" t="s">
         <v>707</v>
       </c>
       <c r="E319" s="50">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F319" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G319" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H319" s="50" t="s">
         <v>708</v>
@@ -27967,10 +27989,10 @@
         <v>62</v>
       </c>
       <c r="K319" s="50" t="s">
-        <v>238</v>
+        <v>147</v>
       </c>
       <c r="L319" s="50" t="s">
-        <v>1</v>
+        <v>704</v>
       </c>
       <c r="M319" s="50" t="s">
         <v>1</v>
@@ -28024,16 +28046,16 @@
         <v>58</v>
       </c>
       <c r="C320" s="50">
-        <v>330044</v>
+        <v>330042</v>
       </c>
       <c r="D320" s="50" t="s">
         <v>709</v>
       </c>
       <c r="E320" s="50">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F320" s="50">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G320" s="50" t="s">
         <v>60</v>
@@ -28048,13 +28070,13 @@
         <v>62</v>
       </c>
       <c r="K320" s="50" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L320" s="50" t="s">
         <v>711</v>
       </c>
       <c r="M320" s="50" t="s">
-        <v>1</v>
+        <v>712</v>
       </c>
       <c r="N320" s="50">
         <v>33</v>
@@ -28105,22 +28127,22 @@
         <v>58</v>
       </c>
       <c r="C321" s="50">
-        <v>330045</v>
+        <v>330043</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E321" s="50">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F321" s="50">
         <v>1</v>
       </c>
       <c r="G321" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H321" s="50" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I321" s="50" t="s">
         <v>78</v>
@@ -28129,7 +28151,7 @@
         <v>62</v>
       </c>
       <c r="K321" s="50" t="s">
-        <v>96</v>
+        <v>238</v>
       </c>
       <c r="L321" s="50" t="s">
         <v>1</v>
@@ -28143,9 +28165,7 @@
       <c r="O321" s="50">
         <v>0</v>
       </c>
-      <c r="P321" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P321" s="50"/>
       <c r="Q321" s="50">
         <v>0</v>
       </c>
@@ -28155,8 +28175,8 @@
       <c r="S321" s="50">
         <v>0</v>
       </c>
-      <c r="T321" s="50" t="s">
-        <v>61</v>
+      <c r="T321" s="50">
+        <v>0</v>
       </c>
       <c r="U321" s="50">
         <v>0</v>
@@ -28188,22 +28208,22 @@
         <v>58</v>
       </c>
       <c r="C322" s="50">
-        <v>330046</v>
+        <v>330044</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E322" s="50">
         <v>16</v>
       </c>
       <c r="F322" s="50">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G322" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H322" s="50" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I322" s="50" t="s">
         <v>78</v>
@@ -28212,10 +28232,10 @@
         <v>62</v>
       </c>
       <c r="K322" s="50" t="s">
-        <v>461</v>
+        <v>192</v>
       </c>
       <c r="L322" s="50" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M322" s="50" t="s">
         <v>1</v>
@@ -28269,22 +28289,22 @@
         <v>58</v>
       </c>
       <c r="C323" s="50">
-        <v>330047</v>
+        <v>330045</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E323" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F323" s="50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G323" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H323" s="50" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I323" s="50" t="s">
         <v>78</v>
@@ -28293,7 +28313,7 @@
         <v>62</v>
       </c>
       <c r="K323" s="50" t="s">
-        <v>465</v>
+        <v>96</v>
       </c>
       <c r="L323" s="50" t="s">
         <v>1</v>
@@ -28307,7 +28327,9 @@
       <c r="O323" s="50">
         <v>0</v>
       </c>
-      <c r="P323" s="50"/>
+      <c r="P323" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q323" s="50">
         <v>0</v>
       </c>
@@ -28317,8 +28339,8 @@
       <c r="S323" s="50">
         <v>0</v>
       </c>
-      <c r="T323" s="50">
-        <v>0</v>
+      <c r="T323" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U323" s="50">
         <v>0</v>
@@ -28350,22 +28372,22 @@
         <v>58</v>
       </c>
       <c r="C324" s="50">
-        <v>330048</v>
+        <v>330046</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E324" s="50">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F324" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G324" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H324" s="50" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I324" s="50" t="s">
         <v>78</v>
@@ -28374,10 +28396,10 @@
         <v>62</v>
       </c>
       <c r="K324" s="50" t="s">
-        <v>96</v>
+        <v>461</v>
       </c>
       <c r="L324" s="50" t="s">
-        <v>1</v>
+        <v>722</v>
       </c>
       <c r="M324" s="50" t="s">
         <v>1</v>
@@ -28388,9 +28410,7 @@
       <c r="O324" s="50">
         <v>0</v>
       </c>
-      <c r="P324" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P324" s="50"/>
       <c r="Q324" s="50">
         <v>0</v>
       </c>
@@ -28400,8 +28420,8 @@
       <c r="S324" s="50">
         <v>0</v>
       </c>
-      <c r="T324" s="50" t="s">
-        <v>61</v>
+      <c r="T324" s="50">
+        <v>0</v>
       </c>
       <c r="U324" s="50">
         <v>0</v>
@@ -28433,22 +28453,22 @@
         <v>58</v>
       </c>
       <c r="C325" s="50">
-        <v>330049</v>
+        <v>330047</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E325" s="50">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F325" s="50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G325" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H325" s="50" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I325" s="50" t="s">
         <v>78</v>
@@ -28457,10 +28477,10 @@
         <v>62</v>
       </c>
       <c r="K325" s="50" t="s">
-        <v>100</v>
+        <v>465</v>
       </c>
       <c r="L325" s="50" t="s">
-        <v>723</v>
+        <v>1</v>
       </c>
       <c r="M325" s="50" t="s">
         <v>1</v>
@@ -28514,22 +28534,22 @@
         <v>58</v>
       </c>
       <c r="C326" s="50">
-        <v>330050</v>
+        <v>330048</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E326" s="50">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F326" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G326" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H326" s="50" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I326" s="50" t="s">
         <v>78</v>
@@ -28538,7 +28558,7 @@
         <v>62</v>
       </c>
       <c r="K326" s="50" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L326" s="50" t="s">
         <v>1</v>
@@ -28552,7 +28572,9 @@
       <c r="O326" s="50">
         <v>0</v>
       </c>
-      <c r="P326" s="50"/>
+      <c r="P326" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q326" s="50">
         <v>0</v>
       </c>
@@ -28562,8 +28584,8 @@
       <c r="S326" s="50">
         <v>0</v>
       </c>
-      <c r="T326" s="50">
-        <v>0</v>
+      <c r="T326" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U326" s="50">
         <v>0</v>
@@ -28595,22 +28617,22 @@
         <v>58</v>
       </c>
       <c r="C327" s="50">
-        <v>330051</v>
+        <v>330049</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E327" s="50">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F327" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H327" s="50" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I327" s="50" t="s">
         <v>78</v>
@@ -28619,10 +28641,10 @@
         <v>62</v>
       </c>
       <c r="K327" s="50" t="s">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="L327" s="50" t="s">
-        <v>1</v>
+        <v>729</v>
       </c>
       <c r="M327" s="50" t="s">
         <v>1</v>
@@ -28633,9 +28655,7 @@
       <c r="O327" s="50">
         <v>0</v>
       </c>
-      <c r="P327" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P327" s="50"/>
       <c r="Q327" s="50">
         <v>0</v>
       </c>
@@ -28678,22 +28698,22 @@
         <v>58</v>
       </c>
       <c r="C328" s="50">
-        <v>330052</v>
+        <v>330050</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E328" s="50">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F328" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G328" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H328" s="50" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="I328" s="50" t="s">
         <v>78</v>
@@ -28702,7 +28722,7 @@
         <v>62</v>
       </c>
       <c r="K328" s="50" t="s">
-        <v>294</v>
+        <v>88</v>
       </c>
       <c r="L328" s="50" t="s">
         <v>1</v>
@@ -28716,9 +28736,7 @@
       <c r="O328" s="50">
         <v>0</v>
       </c>
-      <c r="P328" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P328" s="50"/>
       <c r="Q328" s="50">
         <v>0</v>
       </c>
@@ -28761,22 +28779,22 @@
         <v>58</v>
       </c>
       <c r="C329" s="50">
-        <v>330053</v>
+        <v>330051</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E329" s="50">
         <v>4</v>
       </c>
       <c r="F329" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G329" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H329" s="50" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I329" s="50" t="s">
         <v>78</v>
@@ -28785,7 +28803,7 @@
         <v>62</v>
       </c>
       <c r="K329" s="50" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="L329" s="50" t="s">
         <v>1</v>
@@ -28844,22 +28862,22 @@
         <v>58</v>
       </c>
       <c r="C330" s="50">
-        <v>330054</v>
+        <v>330052</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E330" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F330" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G330" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H330" s="50" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="I330" s="50" t="s">
         <v>78</v>
@@ -28868,7 +28886,7 @@
         <v>62</v>
       </c>
       <c r="K330" s="50" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="L330" s="50" t="s">
         <v>1</v>
@@ -28894,8 +28912,8 @@
       <c r="S330" s="50">
         <v>0</v>
       </c>
-      <c r="T330" s="50" t="s">
-        <v>61</v>
+      <c r="T330" s="50">
+        <v>0</v>
       </c>
       <c r="U330" s="50">
         <v>0</v>
@@ -28927,22 +28945,22 @@
         <v>58</v>
       </c>
       <c r="C331" s="50">
-        <v>330055</v>
+        <v>330053</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E331" s="50">
         <v>4</v>
       </c>
       <c r="F331" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G331" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H331" s="50" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I331" s="50" t="s">
         <v>78</v>
@@ -28951,7 +28969,7 @@
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -29010,22 +29028,22 @@
         <v>58</v>
       </c>
       <c r="C332" s="50">
-        <v>330056</v>
+        <v>330054</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E332" s="50">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F332" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H332" s="50" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I332" s="50" t="s">
         <v>78</v>
@@ -29034,7 +29052,7 @@
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
@@ -29060,8 +29078,8 @@
       <c r="S332" s="50">
         <v>0</v>
       </c>
-      <c r="T332" s="50">
-        <v>0</v>
+      <c r="T332" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U332" s="50">
         <v>0</v>
@@ -29093,22 +29111,22 @@
         <v>58</v>
       </c>
       <c r="C333" s="50">
-        <v>330058</v>
+        <v>330055</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E333" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F333" s="50">
         <v>1</v>
       </c>
       <c r="G333" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H333" s="50" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="I333" s="50" t="s">
         <v>78</v>
@@ -29117,7 +29135,7 @@
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
@@ -29143,8 +29161,8 @@
       <c r="S333" s="50">
         <v>0</v>
       </c>
-      <c r="T333" s="50" t="s">
-        <v>61</v>
+      <c r="T333" s="50">
+        <v>0</v>
       </c>
       <c r="U333" s="50">
         <v>0</v>
@@ -29176,22 +29194,22 @@
         <v>58</v>
       </c>
       <c r="C334" s="50">
-        <v>330061</v>
+        <v>330056</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E334" s="50">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F334" s="50">
         <v>0</v>
       </c>
       <c r="G334" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H334" s="50" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I334" s="50" t="s">
         <v>78</v>
@@ -29200,7 +29218,7 @@
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>742</v>
+        <v>85</v>
       </c>
       <c r="L334" s="50" t="s">
         <v>1</v>
@@ -29259,22 +29277,22 @@
         <v>58</v>
       </c>
       <c r="C335" s="50">
-        <v>330062</v>
+        <v>330058</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E335" s="50">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F335" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G335" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H335" s="50" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I335" s="50" t="s">
         <v>78</v>
@@ -29283,7 +29301,7 @@
         <v>62</v>
       </c>
       <c r="K335" s="50" t="s">
-        <v>745</v>
+        <v>96</v>
       </c>
       <c r="L335" s="50" t="s">
         <v>1</v>
@@ -29309,8 +29327,8 @@
       <c r="S335" s="50">
         <v>0</v>
       </c>
-      <c r="T335" s="50">
-        <v>0</v>
+      <c r="T335" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U335" s="50">
         <v>0</v>
@@ -29342,13 +29360,13 @@
         <v>58</v>
       </c>
       <c r="C336" s="50">
-        <v>330063</v>
+        <v>330061</v>
       </c>
       <c r="D336" s="50" t="s">
         <v>746</v>
       </c>
       <c r="E336" s="50">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F336" s="50">
         <v>0</v>
@@ -29366,10 +29384,10 @@
         <v>62</v>
       </c>
       <c r="K336" s="50" t="s">
-        <v>75</v>
+        <v>748</v>
       </c>
       <c r="L336" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M336" s="50" t="s">
         <v>1</v>
@@ -29425,22 +29443,22 @@
         <v>58</v>
       </c>
       <c r="C337" s="50">
-        <v>330064</v>
+        <v>330062</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E337" s="50">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F337" s="50">
         <v>0</v>
       </c>
       <c r="G337" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H337" s="50" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I337" s="50" t="s">
         <v>78</v>
@@ -29449,13 +29467,13 @@
         <v>62</v>
       </c>
       <c r="K337" s="50" t="s">
-        <v>180</v>
+        <v>751</v>
       </c>
       <c r="L337" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M337" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N337" s="50">
         <v>33</v>
@@ -29508,22 +29526,22 @@
         <v>58</v>
       </c>
       <c r="C338" s="50">
-        <v>330065</v>
+        <v>330063</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E338" s="50">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F338" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G338" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H338" s="50" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="I338" s="50" t="s">
         <v>78</v>
@@ -29532,10 +29550,10 @@
         <v>62</v>
       </c>
       <c r="K338" s="50" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="L338" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M338" s="50" t="s">
         <v>1</v>
@@ -29558,8 +29576,8 @@
       <c r="S338" s="50">
         <v>0</v>
       </c>
-      <c r="T338" s="50" t="s">
-        <v>61</v>
+      <c r="T338" s="50">
+        <v>0</v>
       </c>
       <c r="U338" s="50">
         <v>0</v>
@@ -29591,22 +29609,22 @@
         <v>58</v>
       </c>
       <c r="C339" s="50">
-        <v>330067</v>
+        <v>330064</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E339" s="50">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F339" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G339" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H339" s="50" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="I339" s="50" t="s">
         <v>78</v>
@@ -29615,13 +29633,13 @@
         <v>62</v>
       </c>
       <c r="K339" s="50" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="L339" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M339" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N339" s="50">
         <v>33</v>
@@ -29674,22 +29692,22 @@
         <v>58</v>
       </c>
       <c r="C340" s="50">
-        <v>330068</v>
+        <v>330065</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E340" s="50">
         <v>5</v>
       </c>
       <c r="F340" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G340" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29698,7 +29716,7 @@
         <v>62</v>
       </c>
       <c r="K340" s="50" t="s">
-        <v>96</v>
+        <v>297</v>
       </c>
       <c r="L340" s="50" t="s">
         <v>1</v>
@@ -29757,13 +29775,13 @@
         <v>58</v>
       </c>
       <c r="C341" s="50">
-        <v>330069</v>
+        <v>330067</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E341" s="50">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F341" s="50">
         <v>1</v>
@@ -29772,7 +29790,7 @@
         <v>60</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29781,10 +29799,10 @@
         <v>62</v>
       </c>
       <c r="K341" s="50" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="L341" s="50" t="s">
-        <v>758</v>
+        <v>1</v>
       </c>
       <c r="M341" s="50" t="s">
         <v>1</v>
@@ -29795,7 +29813,9 @@
       <c r="O341" s="50">
         <v>0</v>
       </c>
-      <c r="P341" s="50"/>
+      <c r="P341" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q341" s="50">
         <v>0</v>
       </c>
@@ -29838,22 +29858,22 @@
         <v>58</v>
       </c>
       <c r="C342" s="50">
-        <v>330070</v>
+        <v>330068</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E342" s="50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F342" s="50">
         <v>1</v>
       </c>
       <c r="G342" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H342" s="50" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I342" s="50" t="s">
         <v>78</v>
@@ -29862,7 +29882,7 @@
         <v>62</v>
       </c>
       <c r="K342" s="50" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="L342" s="50" t="s">
         <v>1</v>
@@ -29876,7 +29896,9 @@
       <c r="O342" s="50">
         <v>0</v>
       </c>
-      <c r="P342" s="50"/>
+      <c r="P342" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q342" s="50">
         <v>0</v>
       </c>
@@ -29886,8 +29908,8 @@
       <c r="S342" s="50">
         <v>0</v>
       </c>
-      <c r="T342" s="50">
-        <v>0</v>
+      <c r="T342" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U342" s="50">
         <v>0</v>
@@ -29908,6 +29930,168 @@
         <v>0</v>
       </c>
       <c r="AA342" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="50">
+        <v>338</v>
+      </c>
+      <c r="B343" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C343" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D343" s="50" t="s">
+        <v>762</v>
+      </c>
+      <c r="E343" s="50">
+        <v>16</v>
+      </c>
+      <c r="F343" s="50">
+        <v>1</v>
+      </c>
+      <c r="G343" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H343" s="50" t="s">
+        <v>763</v>
+      </c>
+      <c r="I343" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J343" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K343" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L343" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="M343" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N343" s="50">
+        <v>33</v>
+      </c>
+      <c r="O343" s="50">
+        <v>0</v>
+      </c>
+      <c r="P343" s="50"/>
+      <c r="Q343" s="50">
+        <v>0</v>
+      </c>
+      <c r="R343" s="50">
+        <v>0</v>
+      </c>
+      <c r="S343" s="50">
+        <v>0</v>
+      </c>
+      <c r="T343" s="50">
+        <v>0</v>
+      </c>
+      <c r="U343" s="50">
+        <v>0</v>
+      </c>
+      <c r="V343" s="50">
+        <v>0</v>
+      </c>
+      <c r="W343" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X343" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y343" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z343" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA343" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="50">
+        <v>339</v>
+      </c>
+      <c r="B344" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C344" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D344" s="50" t="s">
+        <v>765</v>
+      </c>
+      <c r="E344" s="50">
+        <v>3</v>
+      </c>
+      <c r="F344" s="50">
+        <v>1</v>
+      </c>
+      <c r="G344" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H344" s="50" t="s">
+        <v>766</v>
+      </c>
+      <c r="I344" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J344" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K344" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L344" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M344" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N344" s="50">
+        <v>33</v>
+      </c>
+      <c r="O344" s="50">
+        <v>0</v>
+      </c>
+      <c r="P344" s="50"/>
+      <c r="Q344" s="50">
+        <v>0</v>
+      </c>
+      <c r="R344" s="50">
+        <v>0</v>
+      </c>
+      <c r="S344" s="50">
+        <v>0</v>
+      </c>
+      <c r="T344" s="50">
+        <v>0</v>
+      </c>
+      <c r="U344" s="50">
+        <v>0</v>
+      </c>
+      <c r="V344" s="50">
+        <v>0</v>
+      </c>
+      <c r="W344" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X344" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y344" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z344" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA344" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="771">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1291,10 +1291,10 @@
     <t>110,7.999978,43</t>
   </si>
   <si>
-    <t>115,8.003199,52</t>
-  </si>
-  <si>
-    <t>112.75,8.003199,54.25_112.75,8.003199,49.75_117.25,8.003199,49.75_117.25,8.003199,54.25</t>
+    <t>98,7.999978,63</t>
+  </si>
+  <si>
+    <t>100.25,8.003201,65.25_95.75,8.003201,65.25_95.75,8.003201,60.75_100.25,8.003201,60.75</t>
   </si>
   <si>
     <t>70201</t>
@@ -1303,7 +1303,7 @@
     <t>132,8.003199,52</t>
   </si>
   <si>
-    <t>130.5,8.003199,50_133.5,8.003199,50_133.5,8.003199,54_130.5,8.003199,54</t>
+    <t>130.5,8.003201,50_133.5,8.003201,50_133.5,8.003201,54_130.5,8.003201,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1315,7 +1315,7 @@
     <t>117,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>118,8.003199,72.85841_118,8.003199,74.85841_116,8.003199,74.85841_116,8.003199,72.85841</t>
+    <t>118,8.003201,72.85841_118,8.003201,74.85841_116,8.003201,74.85841_116,8.003201,72.85841</t>
   </si>
   <si>
     <t>74857</t>
@@ -1324,13 +1324,13 @@
     <t>119,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>120,8.003199,72.85841_120,8.003199,74.85841_118,8.003199,74.85841_118,8.003199,72.85841</t>
+    <t>120,8.003201,72.85841_120,8.003201,74.85841_118,8.003201,74.85841_118,8.003201,72.85841</t>
   </si>
   <si>
     <t>121,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>122,8.003199,72.85841_122,8.003199,74.85841_120,8.003199,74.85841_120,8.003199,72.85841</t>
+    <t>122,8.003201,72.85841_122,8.003201,74.85841_120,8.003201,74.85841_120,8.003201,72.85841</t>
   </si>
   <si>
     <t>129.307510375977,7.999978,60.7048797607422</t>
@@ -1408,19 +1408,19 @@
     <t>74871</t>
   </si>
   <si>
-    <t>98,7.999978,54</t>
-  </si>
-  <si>
-    <t>99,7.999978,55_97,7.999978,55_97,7.999978,53_99,7.999978,53</t>
+    <t>85,7.999978,56</t>
+  </si>
+  <si>
+    <t>86,7.999978,57_84,7.999978,57_84,7.999978,55_86,7.999978,55</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
-    <t>91,7.999978,56</t>
-  </si>
-  <si>
-    <t>88.75,7.999978,58.25_88.75,7.999978,53.75_93.25,7.999978,53.75_93.25,7.999978,58.25</t>
+    <t>77,7.999978,56</t>
+  </si>
+  <si>
+    <t>74.75,7.999978,58.25_74.75,7.999978,53.75_79.25,7.999978,53.75_79.25,7.999978,58.25</t>
   </si>
   <si>
     <t>74876</t>
@@ -1441,7 +1441,7 @@
     <t>109.408554077148,8.003199,114</t>
   </si>
   <si>
-    <t>114.4086,8.003199,116_107.4086,8.003199,116_107.4086,8.003199,112_114.4086,8.003199,112</t>
+    <t>114.4086,8.003201,116_107.4086,8.003201,116_107.4086,8.003201,112_114.4086,8.003201,112</t>
   </si>
   <si>
     <t>74875</t>
@@ -1462,7 +1462,7 @@
     <t>137,8.003199,133.983917236328</t>
   </si>
   <si>
-    <t>138.5,8.003199,131.4839_138.5,8.003199,136.4839_135.5,8.003199,136.4839_135.5,8.003199,131.4839</t>
+    <t>138.5,8.003201,131.4839_138.5,8.003201,136.4839_135.5,8.003201,136.4839_135.5,8.003201,131.4839</t>
   </si>
   <si>
     <t>74878</t>
@@ -1474,10 +1474,10 @@
     <t>89,7.999978,155_89,7.999978,157_87,7.999978,157_87,7.999978,155</t>
   </si>
   <si>
-    <t>99,7.999978,156</t>
-  </si>
-  <si>
-    <t>100.5,7.999978,153.5_100.5,7.999978,158.5_97.5,7.999978,158.5_97.5,7.999978,153.5</t>
+    <t>98,7.999978,156</t>
+  </si>
+  <si>
+    <t>99.5,7.999978,153.5_99.5,7.999978,158.5_96.5,7.999978,158.5_96.5,7.999978,153.5</t>
   </si>
   <si>
     <t>102,7.999978,121</t>
@@ -1516,7 +1516,7 @@
     <t>112,8.003199,134</t>
   </si>
   <si>
-    <t>110.5,8.003199,136_110.5,8.003199,132_113.5,8.003199,132_113.5,8.003199,136</t>
+    <t>110.5,8.003201,136_110.5,8.003201,132_113.5,8.003201,132_113.5,8.003201,136</t>
   </si>
   <si>
     <t>0,74996</t>
@@ -1534,7 +1534,7 @@
     <t>127,8.003199,134</t>
   </si>
   <si>
-    <t>129.25,8.003199,131.75_129.25,8.003199,136.25_124.75,8.003199,136.25_124.75,8.003199,131.75</t>
+    <t>129.25,8.003201,131.75_129.25,8.003201,136.25_124.75,8.003201,136.25_124.75,8.003201,131.75</t>
   </si>
   <si>
     <t>142,7.999978,176</t>
@@ -1561,7 +1561,7 @@
     <t>122,8.003199,134</t>
   </si>
   <si>
-    <t>123,8.003199,135_121,8.003199,135_121,8.003199,133_123,8.003199,133</t>
+    <t>123,8.003201,135_121,8.003201,135_121,8.003201,133_123,8.003201,133</t>
   </si>
   <si>
     <t>119,10.00309,203</t>
@@ -1576,7 +1576,7 @@
     <t>112,8.003199,203</t>
   </si>
   <si>
-    <t>113.5,8.003199,205_110.5,8.003199,205_110.5,8.003199,201_113.5,8.003199,201</t>
+    <t>113.5,8.003201,205_110.5,8.003201,205_110.5,8.003201,201_113.5,8.003201,201</t>
   </si>
   <si>
     <t>74888</t>
@@ -1657,7 +1657,7 @@
     <t>117.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>118.1416,8.003199,273_118.1416,8.003199,275_116.1416,8.003199,275_116.1416,8.003199,273</t>
+    <t>118.1416,8.003201,273_118.1416,8.003201,275_116.1416,8.003201,275_116.1416,8.003201,273</t>
   </si>
   <si>
     <t>74897</t>
@@ -1666,13 +1666,13 @@
     <t>119.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>120.1416,8.003199,273_120.1416,8.003199,275_118.1416,8.003199,275_118.1416,8.003199,273</t>
+    <t>120.1416,8.003201,273_120.1416,8.003201,275_118.1416,8.003201,275_118.1416,8.003201,273</t>
   </si>
   <si>
     <t>121.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>122.1416,8.003199,273_122.1416,8.003199,275_120.1416,8.003199,275_120.1416,8.003199,273</t>
+    <t>122.1416,8.003201,273_122.1416,8.003201,275_120.1416,8.003201,275_120.1416,8.003201,273</t>
   </si>
   <si>
     <t>135,7.999978,274</t>
@@ -1802,6 +1802,18 @@
   </si>
   <si>
     <t>70307</t>
+  </si>
+  <si>
+    <t>115,9.186258,52</t>
+  </si>
+  <si>
+    <t>116,7.999978,50_116,7.999978,54_114,7.999978,54_114,7.999978,50</t>
+  </si>
+  <si>
+    <t>98,7.999978,55</t>
+  </si>
+  <si>
+    <t>99,7.999978,56_97,7.999978,56_97,7.999978,54_99,7.999978,54</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -3409,7 +3421,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA344"/>
+  <dimension ref="A1:AA346"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -18058,7 +18070,7 @@
         <v>1</v>
       </c>
       <c r="G193" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H193" s="50" t="s">
         <v>425</v>
@@ -23275,44 +23287,45 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>84928</v>
+        <v>75001</v>
       </c>
       <c r="D259" s="50" t="s">
         <v>595</v>
       </c>
       <c r="E259" s="50">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F259" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H259" s="50" t="s">
+        <v>596</v>
       </c>
       <c r="I259" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J259" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K259" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="L259" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="J259" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K259" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="L259" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M259" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N259" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O259" s="50">
         <v>0</v>
       </c>
-      <c r="P259" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P259" s="50"/>
       <c r="Q259" s="50">
         <v>0</v>
       </c>
@@ -23355,22 +23368,22 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>84929</v>
+        <v>75002</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E260" s="50">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F260" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G260" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H260" s="50" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -23379,16 +23392,16 @@
         <v>62</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>377</v>
+        <v>91</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>598</v>
+        <v>1</v>
       </c>
       <c r="M260" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N260" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O260" s="50">
         <v>0</v>
@@ -23436,19 +23449,19 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>84930</v>
+        <v>84928</v>
       </c>
       <c r="D261" s="50" t="s">
         <v>599</v>
       </c>
       <c r="E261" s="50">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F261" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="I261" s="50" t="s">
         <v>61</v>
@@ -23457,13 +23470,13 @@
         <v>62</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="L261" s="50" t="s">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="M261" s="50" t="s">
-        <v>601</v>
+        <v>1</v>
       </c>
       <c r="N261" s="50">
         <v>8</v>
@@ -23471,7 +23484,9 @@
       <c r="O261" s="50">
         <v>0</v>
       </c>
-      <c r="P261" s="50"/>
+      <c r="P261" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q261" s="50">
         <v>0</v>
       </c>
@@ -23514,22 +23529,22 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>84931</v>
+        <v>84929</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E262" s="50">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F262" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H262" s="50" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I262" s="50" t="s">
         <v>78</v>
@@ -23538,10 +23553,10 @@
         <v>62</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>1</v>
+        <v>602</v>
       </c>
       <c r="M262" s="50" t="s">
         <v>1</v>
@@ -23595,10 +23610,10 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>84932</v>
+        <v>84930</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E263" s="50">
         <v>57</v>
@@ -23607,7 +23622,7 @@
         <v>1</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I263" s="50" t="s">
         <v>61</v>
@@ -23619,10 +23634,10 @@
         <v>388</v>
       </c>
       <c r="L263" s="50" t="s">
+        <v>604</v>
+      </c>
+      <c r="M263" s="50" t="s">
         <v>605</v>
-      </c>
-      <c r="M263" s="50" t="s">
-        <v>601</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23673,7 +23688,7 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>84933</v>
+        <v>84931</v>
       </c>
       <c r="D264" s="50" t="s">
         <v>606</v>
@@ -23685,7 +23700,7 @@
         <v>1</v>
       </c>
       <c r="G264" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H264" s="50" t="s">
         <v>607</v>
@@ -23754,37 +23769,34 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>84934</v>
+        <v>84932</v>
       </c>
       <c r="D265" s="50" t="s">
         <v>608</v>
       </c>
       <c r="E265" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F265" s="50">
         <v>1</v>
       </c>
       <c r="G265" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H265" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I265" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J265" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K265" s="50" t="s">
+        <v>388</v>
+      </c>
+      <c r="L265" s="50" t="s">
         <v>609</v>
       </c>
-      <c r="I265" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J265" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K265" s="50" t="s">
-        <v>398</v>
-      </c>
-      <c r="L265" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M265" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="N265" s="50">
         <v>8</v>
@@ -23835,16 +23847,16 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>84935</v>
+        <v>84933</v>
       </c>
       <c r="D266" s="50" t="s">
         <v>610</v>
       </c>
       <c r="E266" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F266" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G266" s="50" t="s">
         <v>60</v>
@@ -23859,7 +23871,7 @@
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -23916,7 +23928,7 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>84936</v>
+        <v>84934</v>
       </c>
       <c r="D267" s="50" t="s">
         <v>612</v>
@@ -23925,10 +23937,10 @@
         <v>31</v>
       </c>
       <c r="F267" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G267" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H267" s="50" t="s">
         <v>613</v>
@@ -23940,7 +23952,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23971,7 +23983,7 @@
         <v>0</v>
       </c>
       <c r="V267" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W267" s="50" t="s">
         <v>1</v>
@@ -23997,7 +24009,7 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>84937</v>
+        <v>84935</v>
       </c>
       <c r="D268" s="50" t="s">
         <v>614</v>
@@ -24006,10 +24018,10 @@
         <v>31</v>
       </c>
       <c r="F268" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G268" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
         <v>615</v>
@@ -24021,7 +24033,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -24052,7 +24064,7 @@
         <v>0</v>
       </c>
       <c r="V268" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W268" s="50" t="s">
         <v>1</v>
@@ -24078,7 +24090,7 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>84938</v>
+        <v>84936</v>
       </c>
       <c r="D269" s="50" t="s">
         <v>616</v>
@@ -24087,7 +24099,7 @@
         <v>31</v>
       </c>
       <c r="F269" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G269" s="50" t="s">
         <v>60</v>
@@ -24102,7 +24114,7 @@
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -24133,7 +24145,7 @@
         <v>0</v>
       </c>
       <c r="V269" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W269" s="50" t="s">
         <v>1</v>
@@ -24159,19 +24171,19 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>84939</v>
+        <v>84937</v>
       </c>
       <c r="D270" s="50" t="s">
         <v>618</v>
       </c>
       <c r="E270" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F270" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H270" s="50" t="s">
         <v>619</v>
@@ -24183,7 +24195,7 @@
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
@@ -24214,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="V270" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W270" s="50" t="s">
         <v>1</v>
@@ -24240,16 +24252,16 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>84940</v>
+        <v>84938</v>
       </c>
       <c r="D271" s="50" t="s">
         <v>620</v>
       </c>
       <c r="E271" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F271" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G271" s="50" t="s">
         <v>60</v>
@@ -24264,7 +24276,7 @@
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="L271" s="50" t="s">
         <v>1</v>
@@ -24321,16 +24333,16 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>84941</v>
+        <v>84939</v>
       </c>
       <c r="D272" s="50" t="s">
         <v>622</v>
       </c>
       <c r="E272" s="50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F272" s="50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G272" s="50" t="s">
         <v>60</v>
@@ -24345,10 +24357,10 @@
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>192</v>
+        <v>394</v>
       </c>
       <c r="L272" s="50" t="s">
-        <v>624</v>
+        <v>1</v>
       </c>
       <c r="M272" s="50" t="s">
         <v>1</v>
@@ -24402,34 +24414,37 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>84942</v>
+        <v>84940</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E273" s="50">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F273" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G273" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H273" s="50" t="s">
+        <v>625</v>
+      </c>
       <c r="I273" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J273" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="L273" s="50" t="s">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="M273" s="50" t="s">
-        <v>627</v>
+        <v>1</v>
       </c>
       <c r="N273" s="50">
         <v>8</v>
@@ -24480,22 +24495,22 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>84943</v>
+        <v>84941</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E274" s="50">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F274" s="50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G274" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24504,10 +24519,10 @@
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>1</v>
+        <v>628</v>
       </c>
       <c r="M274" s="50" t="s">
         <v>1</v>
@@ -24561,16 +24576,16 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>84944</v>
+        <v>84942</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E275" s="50">
         <v>52</v>
       </c>
       <c r="F275" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G275" s="50" t="s">
         <v>60</v>
@@ -24582,13 +24597,13 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="L275" s="50" t="s">
+        <v>630</v>
+      </c>
+      <c r="M275" s="50" t="s">
         <v>631</v>
-      </c>
-      <c r="M275" s="50" t="s">
-        <v>627</v>
       </c>
       <c r="N275" s="50">
         <v>8</v>
@@ -24639,7 +24654,7 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>84945</v>
+        <v>84943</v>
       </c>
       <c r="D276" s="50" t="s">
         <v>632</v>
@@ -24648,7 +24663,7 @@
         <v>51</v>
       </c>
       <c r="F276" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
@@ -24663,7 +24678,7 @@
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L276" s="50" t="s">
         <v>1</v>
@@ -24720,16 +24735,16 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>84946</v>
+        <v>84944</v>
       </c>
       <c r="D277" s="50" t="s">
         <v>634</v>
       </c>
       <c r="E277" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F277" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G277" s="50" t="s">
         <v>60</v>
@@ -24741,13 +24756,13 @@
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L277" s="50" t="s">
         <v>635</v>
       </c>
-      <c r="L277" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M277" s="50" t="s">
-        <v>1</v>
+        <v>631</v>
       </c>
       <c r="N277" s="50">
         <v>8</v>
@@ -24798,28 +24813,31 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>84947</v>
+        <v>84945</v>
       </c>
       <c r="D278" s="50" t="s">
         <v>636</v>
       </c>
       <c r="E278" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F278" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G278" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H278" s="50" t="s">
+        <v>637</v>
+      </c>
       <c r="I278" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J278" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="L278" s="50" t="s">
         <v>1</v>
@@ -24876,16 +24894,16 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>84948</v>
+        <v>84946</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
       </c>
       <c r="F279" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G279" s="50" t="s">
         <v>60</v>
@@ -24897,7 +24915,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>301</v>
+        <v>639</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24954,10 +24972,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>84949</v>
+        <v>84947</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25032,10 +25050,10 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>84950</v>
+        <v>84948</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25110,10 +25128,10 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>84951</v>
+        <v>84949</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25188,10 +25206,10 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>84952</v>
+        <v>84950</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25266,10 +25284,10 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>84953</v>
+        <v>84951</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25344,10 +25362,10 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>84954</v>
+        <v>84952</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25422,10 +25440,10 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>84955</v>
+        <v>84953</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25500,10 +25518,10 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>84956</v>
+        <v>84954</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25578,10 +25596,10 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>84957</v>
+        <v>84955</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25656,10 +25674,10 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>84958</v>
+        <v>84956</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E289" s="50">
         <v>56</v>
@@ -25734,10 +25752,10 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>84959</v>
+        <v>84957</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E290" s="50">
         <v>56</v>
@@ -25812,10 +25830,10 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>84960</v>
+        <v>84958</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E291" s="50">
         <v>56</v>
@@ -25890,10 +25908,10 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>84961</v>
+        <v>84959</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E292" s="50">
         <v>56</v>
@@ -25968,10 +25986,10 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>84962</v>
+        <v>84960</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E293" s="50">
         <v>56</v>
@@ -26046,10 +26064,10 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>84963</v>
+        <v>84961</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E294" s="50">
         <v>56</v>
@@ -26124,10 +26142,10 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>84964</v>
+        <v>84962</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E295" s="50">
         <v>56</v>
@@ -26202,10 +26220,10 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>84965</v>
+        <v>84963</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E296" s="50">
         <v>56</v>
@@ -26280,10 +26298,10 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>84966</v>
+        <v>84964</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E297" s="50">
         <v>56</v>
@@ -26358,10 +26376,10 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>84967</v>
+        <v>84965</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E298" s="50">
         <v>56</v>
@@ -26436,10 +26454,10 @@
         <v>58</v>
       </c>
       <c r="C299" s="50">
-        <v>84968</v>
+        <v>84966</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E299" s="50">
         <v>56</v>
@@ -26514,31 +26532,28 @@
         <v>58</v>
       </c>
       <c r="C300" s="50">
-        <v>84969</v>
+        <v>84967</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E300" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F300" s="50">
         <v>0</v>
       </c>
       <c r="G300" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H300" s="50" t="s">
-        <v>659</v>
+        <v>60</v>
       </c>
       <c r="I300" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J300" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>569</v>
+        <v>301</v>
       </c>
       <c r="L300" s="50" t="s">
         <v>1</v>
@@ -26595,31 +26610,28 @@
         <v>58</v>
       </c>
       <c r="C301" s="50">
-        <v>84970</v>
+        <v>84968</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E301" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F301" s="50">
         <v>0</v>
       </c>
       <c r="G301" s="50" t="s">
-        <v>661</v>
-      </c>
-      <c r="H301" s="50" t="s">
-        <v>662</v>
+        <v>60</v>
       </c>
       <c r="I301" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J301" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K301" s="50" t="s">
-        <v>572</v>
+        <v>301</v>
       </c>
       <c r="L301" s="50" t="s">
         <v>1</v>
@@ -26676,22 +26688,22 @@
         <v>58</v>
       </c>
       <c r="C302" s="50">
-        <v>84971</v>
+        <v>84969</v>
       </c>
       <c r="D302" s="50" t="s">
+        <v>662</v>
+      </c>
+      <c r="E302" s="50">
+        <v>45</v>
+      </c>
+      <c r="F302" s="50">
+        <v>0</v>
+      </c>
+      <c r="G302" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H302" s="50" t="s">
         <v>663</v>
-      </c>
-      <c r="E302" s="50">
-        <v>47</v>
-      </c>
-      <c r="F302" s="50">
-        <v>0</v>
-      </c>
-      <c r="G302" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H302" s="50" t="s">
-        <v>664</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>78</v>
@@ -26700,13 +26712,13 @@
         <v>62</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="L302" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M302" s="50" t="s">
-        <v>665</v>
+        <v>1</v>
       </c>
       <c r="N302" s="50">
         <v>8</v>
@@ -26757,10 +26769,10 @@
         <v>58</v>
       </c>
       <c r="C303" s="50">
-        <v>84972</v>
+        <v>84970</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E303" s="50">
         <v>46</v>
@@ -26769,10 +26781,10 @@
         <v>0</v>
       </c>
       <c r="G303" s="50" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>78</v>
@@ -26838,22 +26850,22 @@
         <v>58</v>
       </c>
       <c r="C304" s="50">
-        <v>84973</v>
+        <v>84971</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E304" s="50">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F304" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G304" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H304" s="50" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I304" s="50" t="s">
         <v>78</v>
@@ -26862,13 +26874,13 @@
         <v>62</v>
       </c>
       <c r="K304" s="50" t="s">
-        <v>192</v>
+        <v>577</v>
       </c>
       <c r="L304" s="50" t="s">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -26919,10 +26931,10 @@
         <v>58</v>
       </c>
       <c r="C305" s="50">
-        <v>84974</v>
+        <v>84972</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E305" s="50">
         <v>46</v>
@@ -26931,10 +26943,10 @@
         <v>0</v>
       </c>
       <c r="G305" s="50" t="s">
-        <v>60</v>
+        <v>671</v>
       </c>
       <c r="H305" s="50" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="I305" s="50" t="s">
         <v>78</v>
@@ -27000,47 +27012,78 @@
         <v>58</v>
       </c>
       <c r="C306" s="50">
-        <v>84976</v>
+        <v>84973</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E306" s="50">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F306" s="50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G306" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H306" s="50" t="s">
+        <v>674</v>
+      </c>
       <c r="I306" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J306" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K306" s="50"/>
-      <c r="L306" s="50"/>
-      <c r="M306" s="50"/>
+      <c r="K306" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L306" s="50" t="s">
+        <v>675</v>
+      </c>
+      <c r="M306" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N306" s="50">
         <v>8</v>
       </c>
-      <c r="O306" s="50"/>
-      <c r="P306" s="50" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q306" s="50"/>
-      <c r="R306" s="50"/>
-      <c r="S306" s="50"/>
-      <c r="T306" s="50"/>
-      <c r="U306" s="50"/>
-      <c r="V306" s="50"/>
-      <c r="W306" s="50"/>
-      <c r="X306" s="50"/>
-      <c r="Y306" s="50"/>
-      <c r="Z306" s="52"/>
-      <c r="AA306" s="50"/>
+      <c r="O306" s="50">
+        <v>0</v>
+      </c>
+      <c r="P306" s="50"/>
+      <c r="Q306" s="50">
+        <v>0</v>
+      </c>
+      <c r="R306" s="50">
+        <v>0</v>
+      </c>
+      <c r="S306" s="50">
+        <v>0</v>
+      </c>
+      <c r="T306" s="50">
+        <v>0</v>
+      </c>
+      <c r="U306" s="50">
+        <v>0</v>
+      </c>
+      <c r="V306" s="50">
+        <v>0</v>
+      </c>
+      <c r="W306" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X306" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y306" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z306" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA306" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="50">
@@ -27050,47 +27093,78 @@
         <v>58</v>
       </c>
       <c r="C307" s="50">
-        <v>84977</v>
+        <v>84974</v>
       </c>
       <c r="D307" s="50" t="s">
         <v>676</v>
       </c>
       <c r="E307" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F307" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G307" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H307" s="50" t="s">
+        <v>677</v>
+      </c>
       <c r="I307" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J307" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K307" s="50"/>
-      <c r="L307" s="50"/>
-      <c r="M307" s="50"/>
+      <c r="K307" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M307" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N307" s="50">
         <v>8</v>
       </c>
-      <c r="O307" s="50"/>
-      <c r="P307" s="50" t="s">
-        <v>677</v>
-      </c>
-      <c r="Q307" s="50"/>
-      <c r="R307" s="50"/>
-      <c r="S307" s="50"/>
-      <c r="T307" s="50"/>
-      <c r="U307" s="50"/>
-      <c r="V307" s="50"/>
-      <c r="W307" s="50"/>
-      <c r="X307" s="50"/>
-      <c r="Y307" s="50"/>
-      <c r="Z307" s="52"/>
-      <c r="AA307" s="50"/>
+      <c r="O307" s="50">
+        <v>0</v>
+      </c>
+      <c r="P307" s="50"/>
+      <c r="Q307" s="50">
+        <v>0</v>
+      </c>
+      <c r="R307" s="50">
+        <v>0</v>
+      </c>
+      <c r="S307" s="50">
+        <v>0</v>
+      </c>
+      <c r="T307" s="50">
+        <v>0</v>
+      </c>
+      <c r="U307" s="50">
+        <v>0</v>
+      </c>
+      <c r="V307" s="50">
+        <v>0</v>
+      </c>
+      <c r="W307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y307" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z307" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA307" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="50">
@@ -27100,7 +27174,7 @@
         <v>58</v>
       </c>
       <c r="C308" s="50">
-        <v>84978</v>
+        <v>84976</v>
       </c>
       <c r="D308" s="50" t="s">
         <v>678</v>
@@ -27109,7 +27183,7 @@
         <v>2</v>
       </c>
       <c r="F308" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G308" s="50" t="s">
         <v>60</v>
@@ -27150,78 +27224,47 @@
         <v>58</v>
       </c>
       <c r="C309" s="50">
-        <v>84979</v>
+        <v>84977</v>
       </c>
       <c r="D309" s="50" t="s">
         <v>680</v>
       </c>
       <c r="E309" s="50">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F309" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G309" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H309" s="50" t="s">
-        <v>681</v>
+        <v>60</v>
       </c>
       <c r="I309" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J309" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K309" s="50" t="s">
-        <v>327</v>
-      </c>
-      <c r="L309" s="50" t="s">
-        <v>682</v>
-      </c>
-      <c r="M309" s="50" t="s">
-        <v>683</v>
-      </c>
+      <c r="K309" s="50"/>
+      <c r="L309" s="50"/>
+      <c r="M309" s="50"/>
       <c r="N309" s="50">
         <v>8</v>
       </c>
-      <c r="O309" s="50">
-        <v>0</v>
-      </c>
-      <c r="P309" s="50"/>
-      <c r="Q309" s="50">
-        <v>0</v>
-      </c>
-      <c r="R309" s="50">
-        <v>0</v>
-      </c>
-      <c r="S309" s="50">
-        <v>0</v>
-      </c>
-      <c r="T309" s="50">
-        <v>0</v>
-      </c>
-      <c r="U309" s="50">
-        <v>0</v>
-      </c>
-      <c r="V309" s="50">
-        <v>0</v>
-      </c>
-      <c r="W309" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X309" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y309" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z309" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA309" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O309" s="50"/>
+      <c r="P309" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q309" s="50"/>
+      <c r="R309" s="50"/>
+      <c r="S309" s="50"/>
+      <c r="T309" s="50"/>
+      <c r="U309" s="50"/>
+      <c r="V309" s="50"/>
+      <c r="W309" s="50"/>
+      <c r="X309" s="50"/>
+      <c r="Y309" s="50"/>
+      <c r="Z309" s="52"/>
+      <c r="AA309" s="50"/>
     </row>
     <row r="310">
       <c r="A310" s="50">
@@ -27231,78 +27274,47 @@
         <v>58</v>
       </c>
       <c r="C310" s="50">
-        <v>84980</v>
+        <v>84978</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E310" s="50">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="F310" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G310" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H310" s="50" t="s">
-        <v>685</v>
-      </c>
       <c r="I310" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J310" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K310" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="L310" s="50" t="s">
-        <v>686</v>
-      </c>
-      <c r="M310" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K310" s="50"/>
+      <c r="L310" s="50"/>
+      <c r="M310" s="50"/>
       <c r="N310" s="50">
         <v>8</v>
       </c>
-      <c r="O310" s="50">
-        <v>0</v>
-      </c>
-      <c r="P310" s="50"/>
-      <c r="Q310" s="50">
-        <v>0</v>
-      </c>
-      <c r="R310" s="50">
-        <v>0</v>
-      </c>
-      <c r="S310" s="50">
-        <v>0</v>
-      </c>
-      <c r="T310" s="50">
-        <v>0</v>
-      </c>
-      <c r="U310" s="50">
-        <v>0</v>
-      </c>
-      <c r="V310" s="50">
-        <v>0</v>
-      </c>
-      <c r="W310" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X310" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y310" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z310" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA310" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O310" s="50"/>
+      <c r="P310" s="50" t="s">
+        <v>683</v>
+      </c>
+      <c r="Q310" s="50"/>
+      <c r="R310" s="50"/>
+      <c r="S310" s="50"/>
+      <c r="T310" s="50"/>
+      <c r="U310" s="50"/>
+      <c r="V310" s="50"/>
+      <c r="W310" s="50"/>
+      <c r="X310" s="50"/>
+      <c r="Y310" s="50"/>
+      <c r="Z310" s="52"/>
+      <c r="AA310" s="50"/>
     </row>
     <row r="311">
       <c r="A311" s="50">
@@ -27312,22 +27324,22 @@
         <v>58</v>
       </c>
       <c r="C311" s="50">
-        <v>84981</v>
+        <v>84979</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E311" s="50">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F311" s="50">
         <v>0</v>
       </c>
       <c r="G311" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H311" s="50" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I311" s="50" t="s">
         <v>78</v>
@@ -27336,13 +27348,13 @@
         <v>62</v>
       </c>
       <c r="K311" s="50" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L311" s="50" t="s">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="M311" s="50" t="s">
-        <v>1</v>
+        <v>687</v>
       </c>
       <c r="N311" s="50">
         <v>8</v>
@@ -27393,13 +27405,13 @@
         <v>58</v>
       </c>
       <c r="C312" s="50">
-        <v>84982</v>
+        <v>84980</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E312" s="50">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F312" s="50">
         <v>0</v>
@@ -27407,20 +27419,23 @@
       <c r="G312" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H312" s="50" t="s">
+        <v>689</v>
+      </c>
       <c r="I312" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J312" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K312" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="L312" s="50" t="s">
         <v>690</v>
       </c>
-      <c r="L312" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M312" s="50" t="s">
-        <v>691</v>
+        <v>1</v>
       </c>
       <c r="N312" s="50">
         <v>8</v>
@@ -27428,9 +27443,7 @@
       <c r="O312" s="50">
         <v>0</v>
       </c>
-      <c r="P312" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P312" s="50"/>
       <c r="Q312" s="50">
         <v>0</v>
       </c>
@@ -27473,13 +27486,13 @@
         <v>58</v>
       </c>
       <c r="C313" s="50">
-        <v>84983</v>
+        <v>84981</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E313" s="50">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F313" s="50">
         <v>0</v>
@@ -27497,7 +27510,7 @@
         <v>62</v>
       </c>
       <c r="K313" s="50" t="s">
-        <v>693</v>
+        <v>331</v>
       </c>
       <c r="L313" s="50" t="s">
         <v>1</v>
@@ -27511,9 +27524,7 @@
       <c r="O313" s="50">
         <v>0</v>
       </c>
-      <c r="P313" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P313" s="50"/>
       <c r="Q313" s="50">
         <v>0</v>
       </c>
@@ -27556,13 +27567,13 @@
         <v>58</v>
       </c>
       <c r="C314" s="50">
-        <v>84984</v>
+        <v>84982</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E314" s="50">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F314" s="50">
         <v>0</v>
@@ -27570,23 +27581,20 @@
       <c r="G314" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H314" s="50" t="s">
+      <c r="I314" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J314" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K314" s="50" t="s">
+        <v>694</v>
+      </c>
+      <c r="L314" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M314" s="50" t="s">
         <v>695</v>
-      </c>
-      <c r="I314" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J314" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K314" s="50" t="s">
-        <v>696</v>
-      </c>
-      <c r="L314" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M314" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N314" s="50">
         <v>8</v>
@@ -27639,22 +27647,22 @@
         <v>58</v>
       </c>
       <c r="C315" s="50">
-        <v>330037</v>
+        <v>84983</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E315" s="50">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F315" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G315" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H315" s="50" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="I315" s="50" t="s">
         <v>78</v>
@@ -27663,7 +27671,7 @@
         <v>62</v>
       </c>
       <c r="K315" s="50" t="s">
-        <v>96</v>
+        <v>697</v>
       </c>
       <c r="L315" s="50" t="s">
         <v>1</v>
@@ -27672,7 +27680,7 @@
         <v>1</v>
       </c>
       <c r="N315" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O315" s="50">
         <v>0</v>
@@ -27689,8 +27697,8 @@
       <c r="S315" s="50">
         <v>0</v>
       </c>
-      <c r="T315" s="50" t="s">
-        <v>61</v>
+      <c r="T315" s="50">
+        <v>0</v>
       </c>
       <c r="U315" s="50">
         <v>0</v>
@@ -27722,22 +27730,22 @@
         <v>58</v>
       </c>
       <c r="C316" s="50">
-        <v>330038</v>
+        <v>84984</v>
       </c>
       <c r="D316" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="E316" s="50">
+        <v>25</v>
+      </c>
+      <c r="F316" s="50">
+        <v>0</v>
+      </c>
+      <c r="G316" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H316" s="50" t="s">
         <v>699</v>
-      </c>
-      <c r="E316" s="50">
-        <v>6</v>
-      </c>
-      <c r="F316" s="50">
-        <v>0</v>
-      </c>
-      <c r="G316" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H316" s="50" t="s">
-        <v>700</v>
       </c>
       <c r="I316" s="50" t="s">
         <v>78</v>
@@ -27746,21 +27754,23 @@
         <v>62</v>
       </c>
       <c r="K316" s="50" t="s">
-        <v>142</v>
+        <v>700</v>
       </c>
       <c r="L316" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M316" s="50" t="s">
-        <v>701</v>
+        <v>1</v>
       </c>
       <c r="N316" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O316" s="50">
         <v>0</v>
       </c>
-      <c r="P316" s="50"/>
+      <c r="P316" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q316" s="50">
         <v>0</v>
       </c>
@@ -27803,22 +27813,22 @@
         <v>58</v>
       </c>
       <c r="C317" s="50">
-        <v>330039</v>
+        <v>330037</v>
       </c>
       <c r="D317" s="50" t="s">
+        <v>701</v>
+      </c>
+      <c r="E317" s="50">
+        <v>5</v>
+      </c>
+      <c r="F317" s="50">
+        <v>1</v>
+      </c>
+      <c r="G317" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H317" s="50" t="s">
         <v>702</v>
-      </c>
-      <c r="E317" s="50">
-        <v>7</v>
-      </c>
-      <c r="F317" s="50">
-        <v>0</v>
-      </c>
-      <c r="G317" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H317" s="50" t="s">
-        <v>703</v>
       </c>
       <c r="I317" s="50" t="s">
         <v>78</v>
@@ -27827,10 +27837,10 @@
         <v>62</v>
       </c>
       <c r="K317" s="50" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="L317" s="50" t="s">
-        <v>704</v>
+        <v>1</v>
       </c>
       <c r="M317" s="50" t="s">
         <v>1</v>
@@ -27841,7 +27851,9 @@
       <c r="O317" s="50">
         <v>0</v>
       </c>
-      <c r="P317" s="50"/>
+      <c r="P317" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q317" s="50">
         <v>0</v>
       </c>
@@ -27851,8 +27863,8 @@
       <c r="S317" s="50">
         <v>0</v>
       </c>
-      <c r="T317" s="50">
-        <v>0</v>
+      <c r="T317" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U317" s="50">
         <v>0</v>
@@ -27884,22 +27896,22 @@
         <v>58</v>
       </c>
       <c r="C318" s="50">
-        <v>330040</v>
+        <v>330038</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E318" s="50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F318" s="50">
         <v>0</v>
       </c>
       <c r="G318" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H318" s="50" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I318" s="50" t="s">
         <v>78</v>
@@ -27908,13 +27920,13 @@
         <v>62</v>
       </c>
       <c r="K318" s="50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L318" s="50" t="s">
-        <v>704</v>
+        <v>1</v>
       </c>
       <c r="M318" s="50" t="s">
-        <v>1</v>
+        <v>705</v>
       </c>
       <c r="N318" s="50">
         <v>33</v>
@@ -27965,10 +27977,10 @@
         <v>58</v>
       </c>
       <c r="C319" s="50">
-        <v>330041</v>
+        <v>330039</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E319" s="50">
         <v>7</v>
@@ -27980,7 +27992,7 @@
         <v>138</v>
       </c>
       <c r="H319" s="50" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="I319" s="50" t="s">
         <v>78</v>
@@ -27992,7 +28004,7 @@
         <v>147</v>
       </c>
       <c r="L319" s="50" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M319" s="50" t="s">
         <v>1</v>
@@ -28046,19 +28058,19 @@
         <v>58</v>
       </c>
       <c r="C320" s="50">
-        <v>330042</v>
+        <v>330040</v>
       </c>
       <c r="D320" s="50" t="s">
         <v>709</v>
       </c>
       <c r="E320" s="50">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F320" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H320" s="50" t="s">
         <v>710</v>
@@ -28070,13 +28082,13 @@
         <v>62</v>
       </c>
       <c r="K320" s="50" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="L320" s="50" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="M320" s="50" t="s">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="N320" s="50">
         <v>33</v>
@@ -28127,22 +28139,22 @@
         <v>58</v>
       </c>
       <c r="C321" s="50">
-        <v>330043</v>
+        <v>330041</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E321" s="50">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F321" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G321" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H321" s="50" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="I321" s="50" t="s">
         <v>78</v>
@@ -28151,10 +28163,10 @@
         <v>62</v>
       </c>
       <c r="K321" s="50" t="s">
-        <v>238</v>
+        <v>147</v>
       </c>
       <c r="L321" s="50" t="s">
-        <v>1</v>
+        <v>708</v>
       </c>
       <c r="M321" s="50" t="s">
         <v>1</v>
@@ -28208,22 +28220,22 @@
         <v>58</v>
       </c>
       <c r="C322" s="50">
-        <v>330044</v>
+        <v>330042</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E322" s="50">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F322" s="50">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G322" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H322" s="50" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="I322" s="50" t="s">
         <v>78</v>
@@ -28232,13 +28244,13 @@
         <v>62</v>
       </c>
       <c r="K322" s="50" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="L322" s="50" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="M322" s="50" t="s">
-        <v>1</v>
+        <v>716</v>
       </c>
       <c r="N322" s="50">
         <v>33</v>
@@ -28289,22 +28301,22 @@
         <v>58</v>
       </c>
       <c r="C323" s="50">
-        <v>330045</v>
+        <v>330043</v>
       </c>
       <c r="D323" s="50" t="s">
+        <v>717</v>
+      </c>
+      <c r="E323" s="50">
+        <v>19</v>
+      </c>
+      <c r="F323" s="50">
+        <v>1</v>
+      </c>
+      <c r="G323" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H323" s="50" t="s">
         <v>718</v>
-      </c>
-      <c r="E323" s="50">
-        <v>5</v>
-      </c>
-      <c r="F323" s="50">
-        <v>1</v>
-      </c>
-      <c r="G323" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H323" s="50" t="s">
-        <v>719</v>
       </c>
       <c r="I323" s="50" t="s">
         <v>78</v>
@@ -28313,7 +28325,7 @@
         <v>62</v>
       </c>
       <c r="K323" s="50" t="s">
-        <v>96</v>
+        <v>238</v>
       </c>
       <c r="L323" s="50" t="s">
         <v>1</v>
@@ -28327,9 +28339,7 @@
       <c r="O323" s="50">
         <v>0</v>
       </c>
-      <c r="P323" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P323" s="50"/>
       <c r="Q323" s="50">
         <v>0</v>
       </c>
@@ -28339,8 +28349,8 @@
       <c r="S323" s="50">
         <v>0</v>
       </c>
-      <c r="T323" s="50" t="s">
-        <v>61</v>
+      <c r="T323" s="50">
+        <v>0</v>
       </c>
       <c r="U323" s="50">
         <v>0</v>
@@ -28372,22 +28382,22 @@
         <v>58</v>
       </c>
       <c r="C324" s="50">
-        <v>330046</v>
+        <v>330044</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E324" s="50">
         <v>16</v>
       </c>
       <c r="F324" s="50">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G324" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H324" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="I324" s="50" t="s">
         <v>78</v>
@@ -28396,10 +28406,10 @@
         <v>62</v>
       </c>
       <c r="K324" s="50" t="s">
-        <v>461</v>
+        <v>192</v>
       </c>
       <c r="L324" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="M324" s="50" t="s">
         <v>1</v>
@@ -28453,22 +28463,22 @@
         <v>58</v>
       </c>
       <c r="C325" s="50">
-        <v>330047</v>
+        <v>330045</v>
       </c>
       <c r="D325" s="50" t="s">
+        <v>722</v>
+      </c>
+      <c r="E325" s="50">
+        <v>5</v>
+      </c>
+      <c r="F325" s="50">
+        <v>1</v>
+      </c>
+      <c r="G325" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H325" s="50" t="s">
         <v>723</v>
-      </c>
-      <c r="E325" s="50">
-        <v>3</v>
-      </c>
-      <c r="F325" s="50">
-        <v>6</v>
-      </c>
-      <c r="G325" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H325" s="50" t="s">
-        <v>724</v>
       </c>
       <c r="I325" s="50" t="s">
         <v>78</v>
@@ -28477,7 +28487,7 @@
         <v>62</v>
       </c>
       <c r="K325" s="50" t="s">
-        <v>465</v>
+        <v>96</v>
       </c>
       <c r="L325" s="50" t="s">
         <v>1</v>
@@ -28491,7 +28501,9 @@
       <c r="O325" s="50">
         <v>0</v>
       </c>
-      <c r="P325" s="50"/>
+      <c r="P325" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q325" s="50">
         <v>0</v>
       </c>
@@ -28501,8 +28513,8 @@
       <c r="S325" s="50">
         <v>0</v>
       </c>
-      <c r="T325" s="50">
-        <v>0</v>
+      <c r="T325" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U325" s="50">
         <v>0</v>
@@ -28534,22 +28546,22 @@
         <v>58</v>
       </c>
       <c r="C326" s="50">
-        <v>330048</v>
+        <v>330046</v>
       </c>
       <c r="D326" s="50" t="s">
+        <v>724</v>
+      </c>
+      <c r="E326" s="50">
+        <v>16</v>
+      </c>
+      <c r="F326" s="50">
+        <v>6</v>
+      </c>
+      <c r="G326" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H326" s="50" t="s">
         <v>725</v>
-      </c>
-      <c r="E326" s="50">
-        <v>5</v>
-      </c>
-      <c r="F326" s="50">
-        <v>1</v>
-      </c>
-      <c r="G326" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H326" s="50" t="s">
-        <v>726</v>
       </c>
       <c r="I326" s="50" t="s">
         <v>78</v>
@@ -28558,10 +28570,10 @@
         <v>62</v>
       </c>
       <c r="K326" s="50" t="s">
-        <v>96</v>
+        <v>461</v>
       </c>
       <c r="L326" s="50" t="s">
-        <v>1</v>
+        <v>726</v>
       </c>
       <c r="M326" s="50" t="s">
         <v>1</v>
@@ -28572,9 +28584,7 @@
       <c r="O326" s="50">
         <v>0</v>
       </c>
-      <c r="P326" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P326" s="50"/>
       <c r="Q326" s="50">
         <v>0</v>
       </c>
@@ -28584,8 +28594,8 @@
       <c r="S326" s="50">
         <v>0</v>
       </c>
-      <c r="T326" s="50" t="s">
-        <v>61</v>
+      <c r="T326" s="50">
+        <v>0</v>
       </c>
       <c r="U326" s="50">
         <v>0</v>
@@ -28617,16 +28627,16 @@
         <v>58</v>
       </c>
       <c r="C327" s="50">
-        <v>330049</v>
+        <v>330047</v>
       </c>
       <c r="D327" s="50" t="s">
         <v>727</v>
       </c>
       <c r="E327" s="50">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F327" s="50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G327" s="50" t="s">
         <v>60</v>
@@ -28641,10 +28651,10 @@
         <v>62</v>
       </c>
       <c r="K327" s="50" t="s">
-        <v>100</v>
+        <v>465</v>
       </c>
       <c r="L327" s="50" t="s">
-        <v>729</v>
+        <v>1</v>
       </c>
       <c r="M327" s="50" t="s">
         <v>1</v>
@@ -28698,22 +28708,22 @@
         <v>58</v>
       </c>
       <c r="C328" s="50">
-        <v>330050</v>
+        <v>330048</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E328" s="50">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F328" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G328" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H328" s="50" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I328" s="50" t="s">
         <v>78</v>
@@ -28722,7 +28732,7 @@
         <v>62</v>
       </c>
       <c r="K328" s="50" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L328" s="50" t="s">
         <v>1</v>
@@ -28736,7 +28746,9 @@
       <c r="O328" s="50">
         <v>0</v>
       </c>
-      <c r="P328" s="50"/>
+      <c r="P328" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q328" s="50">
         <v>0</v>
       </c>
@@ -28746,8 +28758,8 @@
       <c r="S328" s="50">
         <v>0</v>
       </c>
-      <c r="T328" s="50">
-        <v>0</v>
+      <c r="T328" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U328" s="50">
         <v>0</v>
@@ -28779,22 +28791,22 @@
         <v>58</v>
       </c>
       <c r="C329" s="50">
-        <v>330051</v>
+        <v>330049</v>
       </c>
       <c r="D329" s="50" t="s">
+        <v>731</v>
+      </c>
+      <c r="E329" s="50">
+        <v>43</v>
+      </c>
+      <c r="F329" s="50">
+        <v>0</v>
+      </c>
+      <c r="G329" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H329" s="50" t="s">
         <v>732</v>
-      </c>
-      <c r="E329" s="50">
-        <v>4</v>
-      </c>
-      <c r="F329" s="50">
-        <v>1</v>
-      </c>
-      <c r="G329" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H329" s="50" t="s">
-        <v>733</v>
       </c>
       <c r="I329" s="50" t="s">
         <v>78</v>
@@ -28803,10 +28815,10 @@
         <v>62</v>
       </c>
       <c r="K329" s="50" t="s">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="L329" s="50" t="s">
-        <v>1</v>
+        <v>733</v>
       </c>
       <c r="M329" s="50" t="s">
         <v>1</v>
@@ -28817,9 +28829,7 @@
       <c r="O329" s="50">
         <v>0</v>
       </c>
-      <c r="P329" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P329" s="50"/>
       <c r="Q329" s="50">
         <v>0</v>
       </c>
@@ -28862,19 +28872,19 @@
         <v>58</v>
       </c>
       <c r="C330" s="50">
-        <v>330052</v>
+        <v>330050</v>
       </c>
       <c r="D330" s="50" t="s">
         <v>734</v>
       </c>
       <c r="E330" s="50">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F330" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G330" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H330" s="50" t="s">
         <v>735</v>
@@ -28886,7 +28896,7 @@
         <v>62</v>
       </c>
       <c r="K330" s="50" t="s">
-        <v>294</v>
+        <v>88</v>
       </c>
       <c r="L330" s="50" t="s">
         <v>1</v>
@@ -28900,9 +28910,7 @@
       <c r="O330" s="50">
         <v>0</v>
       </c>
-      <c r="P330" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P330" s="50"/>
       <c r="Q330" s="50">
         <v>0</v>
       </c>
@@ -28945,7 +28953,7 @@
         <v>58</v>
       </c>
       <c r="C331" s="50">
-        <v>330053</v>
+        <v>330051</v>
       </c>
       <c r="D331" s="50" t="s">
         <v>736</v>
@@ -28954,10 +28962,10 @@
         <v>4</v>
       </c>
       <c r="F331" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G331" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H331" s="50" t="s">
         <v>737</v>
@@ -28969,7 +28977,7 @@
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -29028,19 +29036,19 @@
         <v>58</v>
       </c>
       <c r="C332" s="50">
-        <v>330054</v>
+        <v>330052</v>
       </c>
       <c r="D332" s="50" t="s">
         <v>738</v>
       </c>
       <c r="E332" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F332" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H332" s="50" t="s">
         <v>739</v>
@@ -29052,7 +29060,7 @@
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
@@ -29078,8 +29086,8 @@
       <c r="S332" s="50">
         <v>0</v>
       </c>
-      <c r="T332" s="50" t="s">
-        <v>61</v>
+      <c r="T332" s="50">
+        <v>0</v>
       </c>
       <c r="U332" s="50">
         <v>0</v>
@@ -29111,7 +29119,7 @@
         <v>58</v>
       </c>
       <c r="C333" s="50">
-        <v>330055</v>
+        <v>330053</v>
       </c>
       <c r="D333" s="50" t="s">
         <v>740</v>
@@ -29120,10 +29128,10 @@
         <v>4</v>
       </c>
       <c r="F333" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G333" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H333" s="50" t="s">
         <v>741</v>
@@ -29135,7 +29143,7 @@
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
@@ -29194,19 +29202,19 @@
         <v>58</v>
       </c>
       <c r="C334" s="50">
-        <v>330056</v>
+        <v>330054</v>
       </c>
       <c r="D334" s="50" t="s">
         <v>742</v>
       </c>
       <c r="E334" s="50">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F334" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H334" s="50" t="s">
         <v>743</v>
@@ -29218,7 +29226,7 @@
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L334" s="50" t="s">
         <v>1</v>
@@ -29244,8 +29252,8 @@
       <c r="S334" s="50">
         <v>0</v>
       </c>
-      <c r="T334" s="50">
-        <v>0</v>
+      <c r="T334" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U334" s="50">
         <v>0</v>
@@ -29277,19 +29285,19 @@
         <v>58</v>
       </c>
       <c r="C335" s="50">
-        <v>330058</v>
+        <v>330055</v>
       </c>
       <c r="D335" s="50" t="s">
         <v>744</v>
       </c>
       <c r="E335" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F335" s="50">
         <v>1</v>
       </c>
       <c r="G335" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H335" s="50" t="s">
         <v>745</v>
@@ -29301,7 +29309,7 @@
         <v>62</v>
       </c>
       <c r="K335" s="50" t="s">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="L335" s="50" t="s">
         <v>1</v>
@@ -29327,8 +29335,8 @@
       <c r="S335" s="50">
         <v>0</v>
       </c>
-      <c r="T335" s="50" t="s">
-        <v>61</v>
+      <c r="T335" s="50">
+        <v>0</v>
       </c>
       <c r="U335" s="50">
         <v>0</v>
@@ -29360,19 +29368,19 @@
         <v>58</v>
       </c>
       <c r="C336" s="50">
-        <v>330061</v>
+        <v>330056</v>
       </c>
       <c r="D336" s="50" t="s">
         <v>746</v>
       </c>
       <c r="E336" s="50">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F336" s="50">
         <v>0</v>
       </c>
       <c r="G336" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H336" s="50" t="s">
         <v>747</v>
@@ -29384,7 +29392,7 @@
         <v>62</v>
       </c>
       <c r="K336" s="50" t="s">
-        <v>748</v>
+        <v>85</v>
       </c>
       <c r="L336" s="50" t="s">
         <v>1</v>
@@ -29443,22 +29451,22 @@
         <v>58</v>
       </c>
       <c r="C337" s="50">
-        <v>330062</v>
+        <v>330058</v>
       </c>
       <c r="D337" s="50" t="s">
+        <v>748</v>
+      </c>
+      <c r="E337" s="50">
+        <v>5</v>
+      </c>
+      <c r="F337" s="50">
+        <v>1</v>
+      </c>
+      <c r="G337" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H337" s="50" t="s">
         <v>749</v>
-      </c>
-      <c r="E337" s="50">
-        <v>40</v>
-      </c>
-      <c r="F337" s="50">
-        <v>0</v>
-      </c>
-      <c r="G337" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H337" s="50" t="s">
-        <v>750</v>
       </c>
       <c r="I337" s="50" t="s">
         <v>78</v>
@@ -29467,7 +29475,7 @@
         <v>62</v>
       </c>
       <c r="K337" s="50" t="s">
-        <v>751</v>
+        <v>96</v>
       </c>
       <c r="L337" s="50" t="s">
         <v>1</v>
@@ -29493,8 +29501,8 @@
       <c r="S337" s="50">
         <v>0</v>
       </c>
-      <c r="T337" s="50">
-        <v>0</v>
+      <c r="T337" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U337" s="50">
         <v>0</v>
@@ -29526,13 +29534,13 @@
         <v>58</v>
       </c>
       <c r="C338" s="50">
-        <v>330063</v>
+        <v>330061</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E338" s="50">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F338" s="50">
         <v>0</v>
@@ -29541,7 +29549,7 @@
         <v>60</v>
       </c>
       <c r="H338" s="50" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="I338" s="50" t="s">
         <v>78</v>
@@ -29550,10 +29558,10 @@
         <v>62</v>
       </c>
       <c r="K338" s="50" t="s">
-        <v>75</v>
+        <v>752</v>
       </c>
       <c r="L338" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M338" s="50" t="s">
         <v>1</v>
@@ -29609,22 +29617,22 @@
         <v>58</v>
       </c>
       <c r="C339" s="50">
-        <v>330064</v>
+        <v>330062</v>
       </c>
       <c r="D339" s="50" t="s">
+        <v>753</v>
+      </c>
+      <c r="E339" s="50">
+        <v>40</v>
+      </c>
+      <c r="F339" s="50">
+        <v>0</v>
+      </c>
+      <c r="G339" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H339" s="50" t="s">
         <v>754</v>
-      </c>
-      <c r="E339" s="50">
-        <v>29</v>
-      </c>
-      <c r="F339" s="50">
-        <v>0</v>
-      </c>
-      <c r="G339" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H339" s="50" t="s">
-        <v>755</v>
       </c>
       <c r="I339" s="50" t="s">
         <v>78</v>
@@ -29633,13 +29641,13 @@
         <v>62</v>
       </c>
       <c r="K339" s="50" t="s">
-        <v>180</v>
+        <v>755</v>
       </c>
       <c r="L339" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M339" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N339" s="50">
         <v>33</v>
@@ -29692,16 +29700,16 @@
         <v>58</v>
       </c>
       <c r="C340" s="50">
-        <v>330065</v>
+        <v>330063</v>
       </c>
       <c r="D340" s="50" t="s">
         <v>756</v>
       </c>
       <c r="E340" s="50">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F340" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G340" s="50" t="s">
         <v>60</v>
@@ -29716,10 +29724,10 @@
         <v>62</v>
       </c>
       <c r="K340" s="50" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="L340" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M340" s="50" t="s">
         <v>1</v>
@@ -29742,8 +29750,8 @@
       <c r="S340" s="50">
         <v>0</v>
       </c>
-      <c r="T340" s="50" t="s">
-        <v>61</v>
+      <c r="T340" s="50">
+        <v>0</v>
       </c>
       <c r="U340" s="50">
         <v>0</v>
@@ -29775,19 +29783,19 @@
         <v>58</v>
       </c>
       <c r="C341" s="50">
-        <v>330067</v>
+        <v>330064</v>
       </c>
       <c r="D341" s="50" t="s">
         <v>758</v>
       </c>
       <c r="E341" s="50">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F341" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H341" s="50" t="s">
         <v>759</v>
@@ -29799,13 +29807,13 @@
         <v>62</v>
       </c>
       <c r="K341" s="50" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="L341" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M341" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N341" s="50">
         <v>33</v>
@@ -29858,7 +29866,7 @@
         <v>58</v>
       </c>
       <c r="C342" s="50">
-        <v>330068</v>
+        <v>330065</v>
       </c>
       <c r="D342" s="50" t="s">
         <v>760</v>
@@ -29867,10 +29875,10 @@
         <v>5</v>
       </c>
       <c r="F342" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G342" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H342" s="50" t="s">
         <v>761</v>
@@ -29882,7 +29890,7 @@
         <v>62</v>
       </c>
       <c r="K342" s="50" t="s">
-        <v>96</v>
+        <v>297</v>
       </c>
       <c r="L342" s="50" t="s">
         <v>1</v>
@@ -29941,13 +29949,13 @@
         <v>58</v>
       </c>
       <c r="C343" s="50">
-        <v>330069</v>
+        <v>330067</v>
       </c>
       <c r="D343" s="50" t="s">
         <v>762</v>
       </c>
       <c r="E343" s="50">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F343" s="50">
         <v>1</v>
@@ -29965,10 +29973,10 @@
         <v>62</v>
       </c>
       <c r="K343" s="50" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="L343" s="50" t="s">
-        <v>764</v>
+        <v>1</v>
       </c>
       <c r="M343" s="50" t="s">
         <v>1</v>
@@ -29979,7 +29987,9 @@
       <c r="O343" s="50">
         <v>0</v>
       </c>
-      <c r="P343" s="50"/>
+      <c r="P343" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q343" s="50">
         <v>0</v>
       </c>
@@ -30022,22 +30032,22 @@
         <v>58</v>
       </c>
       <c r="C344" s="50">
-        <v>330070</v>
+        <v>330068</v>
       </c>
       <c r="D344" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="E344" s="50">
+        <v>5</v>
+      </c>
+      <c r="F344" s="50">
+        <v>1</v>
+      </c>
+      <c r="G344" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H344" s="50" t="s">
         <v>765</v>
-      </c>
-      <c r="E344" s="50">
-        <v>3</v>
-      </c>
-      <c r="F344" s="50">
-        <v>1</v>
-      </c>
-      <c r="G344" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H344" s="50" t="s">
-        <v>766</v>
       </c>
       <c r="I344" s="50" t="s">
         <v>78</v>
@@ -30046,7 +30056,7 @@
         <v>62</v>
       </c>
       <c r="K344" s="50" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="L344" s="50" t="s">
         <v>1</v>
@@ -30060,7 +30070,9 @@
       <c r="O344" s="50">
         <v>0</v>
       </c>
-      <c r="P344" s="50"/>
+      <c r="P344" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q344" s="50">
         <v>0</v>
       </c>
@@ -30070,8 +30082,8 @@
       <c r="S344" s="50">
         <v>0</v>
       </c>
-      <c r="T344" s="50">
-        <v>0</v>
+      <c r="T344" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U344" s="50">
         <v>0</v>
@@ -30092,6 +30104,168 @@
         <v>0</v>
       </c>
       <c r="AA344" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="50">
+        <v>340</v>
+      </c>
+      <c r="B345" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C345" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D345" s="50" t="s">
+        <v>766</v>
+      </c>
+      <c r="E345" s="50">
+        <v>16</v>
+      </c>
+      <c r="F345" s="50">
+        <v>1</v>
+      </c>
+      <c r="G345" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H345" s="50" t="s">
+        <v>767</v>
+      </c>
+      <c r="I345" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J345" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K345" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L345" s="50" t="s">
+        <v>768</v>
+      </c>
+      <c r="M345" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N345" s="50">
+        <v>33</v>
+      </c>
+      <c r="O345" s="50">
+        <v>0</v>
+      </c>
+      <c r="P345" s="50"/>
+      <c r="Q345" s="50">
+        <v>0</v>
+      </c>
+      <c r="R345" s="50">
+        <v>0</v>
+      </c>
+      <c r="S345" s="50">
+        <v>0</v>
+      </c>
+      <c r="T345" s="50">
+        <v>0</v>
+      </c>
+      <c r="U345" s="50">
+        <v>0</v>
+      </c>
+      <c r="V345" s="50">
+        <v>0</v>
+      </c>
+      <c r="W345" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X345" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y345" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z345" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA345" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="50">
+        <v>341</v>
+      </c>
+      <c r="B346" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C346" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D346" s="50" t="s">
+        <v>769</v>
+      </c>
+      <c r="E346" s="50">
+        <v>3</v>
+      </c>
+      <c r="F346" s="50">
+        <v>1</v>
+      </c>
+      <c r="G346" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H346" s="50" t="s">
+        <v>770</v>
+      </c>
+      <c r="I346" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J346" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K346" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L346" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M346" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N346" s="50">
+        <v>33</v>
+      </c>
+      <c r="O346" s="50">
+        <v>0</v>
+      </c>
+      <c r="P346" s="50"/>
+      <c r="Q346" s="50">
+        <v>0</v>
+      </c>
+      <c r="R346" s="50">
+        <v>0</v>
+      </c>
+      <c r="S346" s="50">
+        <v>0</v>
+      </c>
+      <c r="T346" s="50">
+        <v>0</v>
+      </c>
+      <c r="U346" s="50">
+        <v>0</v>
+      </c>
+      <c r="V346" s="50">
+        <v>0</v>
+      </c>
+      <c r="W346" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X346" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y346" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z346" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA346" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="772">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1576,7 +1576,7 @@
     <t>112,8.003199,203</t>
   </si>
   <si>
-    <t>113.5,8.003201,205_110.5,8.003201,205_110.5,8.003201,201_113.5,8.003201,201</t>
+    <t>114,8.003201,206_110,8.003201,206_110,8.003201,200_114,8.003201,200</t>
   </si>
   <si>
     <t>74888</t>
@@ -1808,6 +1808,9 @@
   </si>
   <si>
     <t>116,7.999978,50_116,7.999978,54_114,7.999978,54_114,7.999978,50</t>
+  </si>
+  <si>
+    <t>75002</t>
   </si>
   <si>
     <t>98,7.999978,55</t>
@@ -23314,7 +23317,7 @@
         <v>79</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>61</v>
+        <v>597</v>
       </c>
       <c r="M259" s="50" t="s">
         <v>1</v>
@@ -23371,7 +23374,7 @@
         <v>75002</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E260" s="50">
         <v>3</v>
@@ -23383,7 +23386,7 @@
         <v>60</v>
       </c>
       <c r="H260" s="50" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -23452,7 +23455,7 @@
         <v>84928</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E261" s="50">
         <v>12</v>
@@ -23532,7 +23535,7 @@
         <v>84929</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E262" s="50">
         <v>30</v>
@@ -23544,7 +23547,7 @@
         <v>83</v>
       </c>
       <c r="H262" s="50" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I262" s="50" t="s">
         <v>78</v>
@@ -23556,7 +23559,7 @@
         <v>377</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M262" s="50" t="s">
         <v>1</v>
@@ -23613,7 +23616,7 @@
         <v>84930</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E263" s="50">
         <v>57</v>
@@ -23634,10 +23637,10 @@
         <v>388</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N263" s="50">
         <v>8</v>
@@ -23691,7 +23694,7 @@
         <v>84931</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E264" s="50">
         <v>32</v>
@@ -23703,7 +23706,7 @@
         <v>138</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23772,7 +23775,7 @@
         <v>84932</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E265" s="50">
         <v>57</v>
@@ -23793,10 +23796,10 @@
         <v>388</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N265" s="50">
         <v>8</v>
@@ -23850,7 +23853,7 @@
         <v>84933</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E266" s="50">
         <v>32</v>
@@ -23862,7 +23865,7 @@
         <v>60</v>
       </c>
       <c r="H266" s="50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I266" s="50" t="s">
         <v>78</v>
@@ -23931,7 +23934,7 @@
         <v>84934</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E267" s="50">
         <v>31</v>
@@ -23943,7 +23946,7 @@
         <v>138</v>
       </c>
       <c r="H267" s="50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I267" s="50" t="s">
         <v>78</v>
@@ -24012,7 +24015,7 @@
         <v>84935</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E268" s="50">
         <v>31</v>
@@ -24024,7 +24027,7 @@
         <v>60</v>
       </c>
       <c r="H268" s="50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I268" s="50" t="s">
         <v>78</v>
@@ -24093,7 +24096,7 @@
         <v>84936</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E269" s="50">
         <v>31</v>
@@ -24105,7 +24108,7 @@
         <v>60</v>
       </c>
       <c r="H269" s="50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I269" s="50" t="s">
         <v>78</v>
@@ -24174,7 +24177,7 @@
         <v>84937</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E270" s="50">
         <v>31</v>
@@ -24186,7 +24189,7 @@
         <v>138</v>
       </c>
       <c r="H270" s="50" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I270" s="50" t="s">
         <v>78</v>
@@ -24255,7 +24258,7 @@
         <v>84938</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E271" s="50">
         <v>31</v>
@@ -24267,7 +24270,7 @@
         <v>60</v>
       </c>
       <c r="H271" s="50" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I271" s="50" t="s">
         <v>78</v>
@@ -24336,7 +24339,7 @@
         <v>84939</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E272" s="50">
         <v>15</v>
@@ -24348,7 +24351,7 @@
         <v>60</v>
       </c>
       <c r="H272" s="50" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I272" s="50" t="s">
         <v>78</v>
@@ -24417,7 +24420,7 @@
         <v>84940</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E273" s="50">
         <v>15</v>
@@ -24429,7 +24432,7 @@
         <v>60</v>
       </c>
       <c r="H273" s="50" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I273" s="50" t="s">
         <v>78</v>
@@ -24498,7 +24501,7 @@
         <v>84941</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E274" s="50">
         <v>16</v>
@@ -24510,7 +24513,7 @@
         <v>60</v>
       </c>
       <c r="H274" s="50" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I274" s="50" t="s">
         <v>78</v>
@@ -24522,7 +24525,7 @@
         <v>192</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M274" s="50" t="s">
         <v>1</v>
@@ -24579,7 +24582,7 @@
         <v>84942</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E275" s="50">
         <v>52</v>
@@ -24600,10 +24603,10 @@
         <v>285</v>
       </c>
       <c r="L275" s="50" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M275" s="50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N275" s="50">
         <v>8</v>
@@ -24657,7 +24660,7 @@
         <v>84943</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E276" s="50">
         <v>51</v>
@@ -24669,7 +24672,7 @@
         <v>60</v>
       </c>
       <c r="H276" s="50" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I276" s="50" t="s">
         <v>78</v>
@@ -24738,7 +24741,7 @@
         <v>84944</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E277" s="50">
         <v>52</v>
@@ -24759,10 +24762,10 @@
         <v>271</v>
       </c>
       <c r="L277" s="50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M277" s="50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N277" s="50">
         <v>8</v>
@@ -24816,7 +24819,7 @@
         <v>84945</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E278" s="50">
         <v>51</v>
@@ -24828,7 +24831,7 @@
         <v>60</v>
       </c>
       <c r="H278" s="50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I278" s="50" t="s">
         <v>78</v>
@@ -24897,7 +24900,7 @@
         <v>84946</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
@@ -24915,7 +24918,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24975,7 +24978,7 @@
         <v>84947</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25053,7 +25056,7 @@
         <v>84948</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25131,7 +25134,7 @@
         <v>84949</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25209,7 +25212,7 @@
         <v>84950</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25287,7 +25290,7 @@
         <v>84951</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25365,7 +25368,7 @@
         <v>84952</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25443,7 +25446,7 @@
         <v>84953</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25521,7 +25524,7 @@
         <v>84954</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25599,7 +25602,7 @@
         <v>84955</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25677,7 +25680,7 @@
         <v>84956</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E289" s="50">
         <v>56</v>
@@ -25755,7 +25758,7 @@
         <v>84957</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E290" s="50">
         <v>56</v>
@@ -25833,7 +25836,7 @@
         <v>84958</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E291" s="50">
         <v>56</v>
@@ -25911,7 +25914,7 @@
         <v>84959</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E292" s="50">
         <v>56</v>
@@ -25989,7 +25992,7 @@
         <v>84960</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E293" s="50">
         <v>56</v>
@@ -26067,7 +26070,7 @@
         <v>84961</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E294" s="50">
         <v>56</v>
@@ -26145,7 +26148,7 @@
         <v>84962</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E295" s="50">
         <v>56</v>
@@ -26223,7 +26226,7 @@
         <v>84963</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E296" s="50">
         <v>56</v>
@@ -26301,7 +26304,7 @@
         <v>84964</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E297" s="50">
         <v>56</v>
@@ -26379,7 +26382,7 @@
         <v>84965</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E298" s="50">
         <v>56</v>
@@ -26457,7 +26460,7 @@
         <v>84966</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E299" s="50">
         <v>56</v>
@@ -26535,7 +26538,7 @@
         <v>84967</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E300" s="50">
         <v>56</v>
@@ -26613,7 +26616,7 @@
         <v>84968</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E301" s="50">
         <v>56</v>
@@ -26691,7 +26694,7 @@
         <v>84969</v>
       </c>
       <c r="D302" s="50" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E302" s="50">
         <v>45</v>
@@ -26703,7 +26706,7 @@
         <v>83</v>
       </c>
       <c r="H302" s="50" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>78</v>
@@ -26772,7 +26775,7 @@
         <v>84970</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E303" s="50">
         <v>46</v>
@@ -26781,10 +26784,10 @@
         <v>0</v>
       </c>
       <c r="G303" s="50" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>78</v>
@@ -26853,7 +26856,7 @@
         <v>84971</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E304" s="50">
         <v>47</v>
@@ -26865,7 +26868,7 @@
         <v>94</v>
       </c>
       <c r="H304" s="50" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I304" s="50" t="s">
         <v>78</v>
@@ -26880,7 +26883,7 @@
         <v>1</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -26934,7 +26937,7 @@
         <v>84972</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E305" s="50">
         <v>46</v>
@@ -26943,10 +26946,10 @@
         <v>0</v>
       </c>
       <c r="G305" s="50" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H305" s="50" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I305" s="50" t="s">
         <v>78</v>
@@ -27015,7 +27018,7 @@
         <v>84973</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E306" s="50">
         <v>16</v>
@@ -27027,7 +27030,7 @@
         <v>60</v>
       </c>
       <c r="H306" s="50" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I306" s="50" t="s">
         <v>78</v>
@@ -27039,7 +27042,7 @@
         <v>192</v>
       </c>
       <c r="L306" s="50" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M306" s="50" t="s">
         <v>1</v>
@@ -27096,7 +27099,7 @@
         <v>84974</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E307" s="50">
         <v>46</v>
@@ -27108,7 +27111,7 @@
         <v>60</v>
       </c>
       <c r="H307" s="50" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I307" s="50" t="s">
         <v>78</v>
@@ -27177,7 +27180,7 @@
         <v>84976</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E308" s="50">
         <v>2</v>
@@ -27202,7 +27205,7 @@
       </c>
       <c r="O308" s="50"/>
       <c r="P308" s="50" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Q308" s="50"/>
       <c r="R308" s="50"/>
@@ -27227,7 +27230,7 @@
         <v>84977</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E309" s="50">
         <v>2</v>
@@ -27252,7 +27255,7 @@
       </c>
       <c r="O309" s="50"/>
       <c r="P309" s="50" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Q309" s="50"/>
       <c r="R309" s="50"/>
@@ -27277,7 +27280,7 @@
         <v>84978</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E310" s="50">
         <v>2</v>
@@ -27302,7 +27305,7 @@
       </c>
       <c r="O310" s="50"/>
       <c r="P310" s="50" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Q310" s="50"/>
       <c r="R310" s="50"/>
@@ -27327,7 +27330,7 @@
         <v>84979</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E311" s="50">
         <v>48</v>
@@ -27339,7 +27342,7 @@
         <v>83</v>
       </c>
       <c r="H311" s="50" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I311" s="50" t="s">
         <v>78</v>
@@ -27351,10 +27354,10 @@
         <v>327</v>
       </c>
       <c r="L311" s="50" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M311" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N311" s="50">
         <v>8</v>
@@ -27408,7 +27411,7 @@
         <v>84980</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E312" s="50">
         <v>49</v>
@@ -27420,7 +27423,7 @@
         <v>60</v>
       </c>
       <c r="H312" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I312" s="50" t="s">
         <v>78</v>
@@ -27432,7 +27435,7 @@
         <v>324</v>
       </c>
       <c r="L312" s="50" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M312" s="50" t="s">
         <v>1</v>
@@ -27489,7 +27492,7 @@
         <v>84981</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E313" s="50">
         <v>50</v>
@@ -27501,7 +27504,7 @@
         <v>60</v>
       </c>
       <c r="H313" s="50" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I313" s="50" t="s">
         <v>78</v>
@@ -27570,7 +27573,7 @@
         <v>84982</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E314" s="50">
         <v>23</v>
@@ -27588,13 +27591,13 @@
         <v>62</v>
       </c>
       <c r="K314" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L314" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M314" s="50" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N314" s="50">
         <v>8</v>
@@ -27650,7 +27653,7 @@
         <v>84983</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E315" s="50">
         <v>24</v>
@@ -27662,7 +27665,7 @@
         <v>60</v>
       </c>
       <c r="H315" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I315" s="50" t="s">
         <v>78</v>
@@ -27671,7 +27674,7 @@
         <v>62</v>
       </c>
       <c r="K315" s="50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L315" s="50" t="s">
         <v>1</v>
@@ -27733,7 +27736,7 @@
         <v>84984</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E316" s="50">
         <v>25</v>
@@ -27745,7 +27748,7 @@
         <v>60</v>
       </c>
       <c r="H316" s="50" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I316" s="50" t="s">
         <v>78</v>
@@ -27754,7 +27757,7 @@
         <v>62</v>
       </c>
       <c r="K316" s="50" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L316" s="50" t="s">
         <v>1</v>
@@ -27816,7 +27819,7 @@
         <v>330037</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E317" s="50">
         <v>5</v>
@@ -27828,7 +27831,7 @@
         <v>60</v>
       </c>
       <c r="H317" s="50" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I317" s="50" t="s">
         <v>78</v>
@@ -27899,7 +27902,7 @@
         <v>330038</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E318" s="50">
         <v>6</v>
@@ -27911,7 +27914,7 @@
         <v>94</v>
       </c>
       <c r="H318" s="50" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I318" s="50" t="s">
         <v>78</v>
@@ -27926,7 +27929,7 @@
         <v>1</v>
       </c>
       <c r="M318" s="50" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N318" s="50">
         <v>33</v>
@@ -27980,7 +27983,7 @@
         <v>330039</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E319" s="50">
         <v>7</v>
@@ -27992,7 +27995,7 @@
         <v>138</v>
       </c>
       <c r="H319" s="50" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I319" s="50" t="s">
         <v>78</v>
@@ -28004,7 +28007,7 @@
         <v>147</v>
       </c>
       <c r="L319" s="50" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M319" s="50" t="s">
         <v>1</v>
@@ -28061,7 +28064,7 @@
         <v>330040</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E320" s="50">
         <v>7</v>
@@ -28073,7 +28076,7 @@
         <v>138</v>
       </c>
       <c r="H320" s="50" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I320" s="50" t="s">
         <v>78</v>
@@ -28085,7 +28088,7 @@
         <v>147</v>
       </c>
       <c r="L320" s="50" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M320" s="50" t="s">
         <v>1</v>
@@ -28142,7 +28145,7 @@
         <v>330041</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E321" s="50">
         <v>7</v>
@@ -28154,7 +28157,7 @@
         <v>138</v>
       </c>
       <c r="H321" s="50" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I321" s="50" t="s">
         <v>78</v>
@@ -28166,7 +28169,7 @@
         <v>147</v>
       </c>
       <c r="L321" s="50" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M321" s="50" t="s">
         <v>1</v>
@@ -28223,7 +28226,7 @@
         <v>330042</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E322" s="50">
         <v>20</v>
@@ -28235,7 +28238,7 @@
         <v>60</v>
       </c>
       <c r="H322" s="50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I322" s="50" t="s">
         <v>78</v>
@@ -28247,10 +28250,10 @@
         <v>233</v>
       </c>
       <c r="L322" s="50" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M322" s="50" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N322" s="50">
         <v>33</v>
@@ -28304,7 +28307,7 @@
         <v>330043</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E323" s="50">
         <v>19</v>
@@ -28316,7 +28319,7 @@
         <v>60</v>
       </c>
       <c r="H323" s="50" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I323" s="50" t="s">
         <v>78</v>
@@ -28385,7 +28388,7 @@
         <v>330044</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E324" s="50">
         <v>16</v>
@@ -28397,7 +28400,7 @@
         <v>60</v>
       </c>
       <c r="H324" s="50" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I324" s="50" t="s">
         <v>78</v>
@@ -28409,7 +28412,7 @@
         <v>192</v>
       </c>
       <c r="L324" s="50" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M324" s="50" t="s">
         <v>1</v>
@@ -28466,7 +28469,7 @@
         <v>330045</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E325" s="50">
         <v>5</v>
@@ -28478,7 +28481,7 @@
         <v>83</v>
       </c>
       <c r="H325" s="50" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I325" s="50" t="s">
         <v>78</v>
@@ -28549,7 +28552,7 @@
         <v>330046</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E326" s="50">
         <v>16</v>
@@ -28561,7 +28564,7 @@
         <v>83</v>
       </c>
       <c r="H326" s="50" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I326" s="50" t="s">
         <v>78</v>
@@ -28573,7 +28576,7 @@
         <v>461</v>
       </c>
       <c r="L326" s="50" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M326" s="50" t="s">
         <v>1</v>
@@ -28630,7 +28633,7 @@
         <v>330047</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E327" s="50">
         <v>3</v>
@@ -28642,7 +28645,7 @@
         <v>60</v>
       </c>
       <c r="H327" s="50" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I327" s="50" t="s">
         <v>78</v>
@@ -28711,7 +28714,7 @@
         <v>330048</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E328" s="50">
         <v>5</v>
@@ -28723,7 +28726,7 @@
         <v>60</v>
       </c>
       <c r="H328" s="50" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I328" s="50" t="s">
         <v>78</v>
@@ -28794,7 +28797,7 @@
         <v>330049</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E329" s="50">
         <v>43</v>
@@ -28806,7 +28809,7 @@
         <v>60</v>
       </c>
       <c r="H329" s="50" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I329" s="50" t="s">
         <v>78</v>
@@ -28818,7 +28821,7 @@
         <v>100</v>
       </c>
       <c r="L329" s="50" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M329" s="50" t="s">
         <v>1</v>
@@ -28875,7 +28878,7 @@
         <v>330050</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E330" s="50">
         <v>44</v>
@@ -28887,7 +28890,7 @@
         <v>60</v>
       </c>
       <c r="H330" s="50" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I330" s="50" t="s">
         <v>78</v>
@@ -28956,7 +28959,7 @@
         <v>330051</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E331" s="50">
         <v>4</v>
@@ -28968,7 +28971,7 @@
         <v>138</v>
       </c>
       <c r="H331" s="50" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I331" s="50" t="s">
         <v>78</v>
@@ -29039,7 +29042,7 @@
         <v>330052</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E332" s="50">
         <v>4</v>
@@ -29051,7 +29054,7 @@
         <v>138</v>
       </c>
       <c r="H332" s="50" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I332" s="50" t="s">
         <v>78</v>
@@ -29122,7 +29125,7 @@
         <v>330053</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E333" s="50">
         <v>4</v>
@@ -29134,7 +29137,7 @@
         <v>60</v>
       </c>
       <c r="H333" s="50" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I333" s="50" t="s">
         <v>78</v>
@@ -29205,7 +29208,7 @@
         <v>330054</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E334" s="50">
         <v>5</v>
@@ -29217,7 +29220,7 @@
         <v>60</v>
       </c>
       <c r="H334" s="50" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I334" s="50" t="s">
         <v>78</v>
@@ -29288,7 +29291,7 @@
         <v>330055</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E335" s="50">
         <v>4</v>
@@ -29300,7 +29303,7 @@
         <v>83</v>
       </c>
       <c r="H335" s="50" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I335" s="50" t="s">
         <v>78</v>
@@ -29371,7 +29374,7 @@
         <v>330056</v>
       </c>
       <c r="D336" s="50" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E336" s="50">
         <v>54</v>
@@ -29383,7 +29386,7 @@
         <v>138</v>
       </c>
       <c r="H336" s="50" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I336" s="50" t="s">
         <v>78</v>
@@ -29454,7 +29457,7 @@
         <v>330058</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E337" s="50">
         <v>5</v>
@@ -29466,7 +29469,7 @@
         <v>138</v>
       </c>
       <c r="H337" s="50" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I337" s="50" t="s">
         <v>78</v>
@@ -29537,7 +29540,7 @@
         <v>330061</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E338" s="50">
         <v>39</v>
@@ -29549,7 +29552,7 @@
         <v>60</v>
       </c>
       <c r="H338" s="50" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I338" s="50" t="s">
         <v>78</v>
@@ -29558,7 +29561,7 @@
         <v>62</v>
       </c>
       <c r="K338" s="50" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L338" s="50" t="s">
         <v>1</v>
@@ -29620,7 +29623,7 @@
         <v>330062</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E339" s="50">
         <v>40</v>
@@ -29632,7 +29635,7 @@
         <v>60</v>
       </c>
       <c r="H339" s="50" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I339" s="50" t="s">
         <v>78</v>
@@ -29641,7 +29644,7 @@
         <v>62</v>
       </c>
       <c r="K339" s="50" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="L339" s="50" t="s">
         <v>1</v>
@@ -29703,7 +29706,7 @@
         <v>330063</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E340" s="50">
         <v>28</v>
@@ -29715,7 +29718,7 @@
         <v>60</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29786,7 +29789,7 @@
         <v>330064</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E341" s="50">
         <v>29</v>
@@ -29798,7 +29801,7 @@
         <v>138</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29869,7 +29872,7 @@
         <v>330065</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E342" s="50">
         <v>5</v>
@@ -29881,7 +29884,7 @@
         <v>60</v>
       </c>
       <c r="H342" s="50" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I342" s="50" t="s">
         <v>78</v>
@@ -29952,7 +29955,7 @@
         <v>330067</v>
       </c>
       <c r="D343" s="50" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E343" s="50">
         <v>4</v>
@@ -29964,7 +29967,7 @@
         <v>60</v>
       </c>
       <c r="H343" s="50" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I343" s="50" t="s">
         <v>78</v>
@@ -30035,7 +30038,7 @@
         <v>330068</v>
       </c>
       <c r="D344" s="50" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E344" s="50">
         <v>5</v>
@@ -30047,7 +30050,7 @@
         <v>138</v>
       </c>
       <c r="H344" s="50" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I344" s="50" t="s">
         <v>78</v>
@@ -30118,7 +30121,7 @@
         <v>330069</v>
       </c>
       <c r="D345" s="50" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E345" s="50">
         <v>16</v>
@@ -30130,7 +30133,7 @@
         <v>60</v>
       </c>
       <c r="H345" s="50" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I345" s="50" t="s">
         <v>78</v>
@@ -30142,7 +30145,7 @@
         <v>257</v>
       </c>
       <c r="L345" s="50" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M345" s="50" t="s">
         <v>1</v>
@@ -30199,7 +30202,7 @@
         <v>330070</v>
       </c>
       <c r="D346" s="50" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E346" s="50">
         <v>3</v>
@@ -30211,7 +30214,7 @@
         <v>60</v>
       </c>
       <c r="H346" s="50" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I346" s="50" t="s">
         <v>78</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="807">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1294,16 +1294,16 @@
     <t>98,7.999978,63</t>
   </si>
   <si>
-    <t>100.25,8.003201,65.25_95.75,8.003201,65.25_95.75,8.003201,60.75_100.25,8.003201,60.75</t>
+    <t>100.25,7.999978,65.25_95.75,7.999978,65.25_95.75,7.999978,60.75_100.25,7.999978,60.75</t>
   </si>
   <si>
     <t>70201</t>
   </si>
   <si>
-    <t>132,8.003199,52</t>
-  </si>
-  <si>
-    <t>130.5,8.003201,50_133.5,8.003201,50_133.5,8.003201,54_130.5,8.003201,54</t>
+    <t>132,8.001535,52</t>
+  </si>
+  <si>
+    <t>130.5,8.003199,50_133.5,8.003199,50_133.5,8.003199,54_130.5,8.003199,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1315,7 +1315,7 @@
     <t>117,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>118,8.003201,72.85841_118,8.003201,74.85841_116,8.003201,74.85841_116,8.003201,72.85841</t>
+    <t>118,8.003199,72.85841_118,8.003199,74.85841_116,8.003199,74.85841_116,8.003199,72.85841</t>
   </si>
   <si>
     <t>74857</t>
@@ -1324,13 +1324,13 @@
     <t>119,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>120,8.003201,72.85841_120,8.003201,74.85841_118,8.003201,74.85841_118,8.003201,72.85841</t>
+    <t>120,8.003199,72.85841_120,8.003199,74.85841_118,8.003199,74.85841_118,8.003199,72.85841</t>
   </si>
   <si>
     <t>121,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>122,8.003201,72.85841_122,8.003201,74.85841_120,8.003201,74.85841_120,8.003201,72.85841</t>
+    <t>122,8.003199,72.85841_122,8.003199,74.85841_120,8.003199,74.85841_120,8.003199,72.85841</t>
   </si>
   <si>
     <t>129.307510375977,7.999978,60.7048797607422</t>
@@ -1369,37 +1369,37 @@
     <t>70001_1</t>
   </si>
   <si>
-    <t>81,7.999978,84</t>
-  </si>
-  <si>
-    <t>82.5,7.999978,82_82.5,7.999978,86_79.5,7.999978,86_79.5,7.999978,82</t>
-  </si>
-  <si>
-    <t>87.1449661254883,5.598887,103.072158813477</t>
+    <t>62,7.999978,96</t>
+  </si>
+  <si>
+    <t>63.5,7.999978,94_63.5,7.999978,98_60.5,7.999978,98_60.5,7.999978,94</t>
+  </si>
+  <si>
+    <t>87.1449661254883,6.485435,103.072158813477</t>
   </si>
   <si>
     <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
   </si>
   <si>
-    <t>58,7.999978,89</t>
-  </si>
-  <si>
-    <t>60.25,7.999978,90.5_55.75,7.999978,90.5_55.75,7.999978,87.5_60.25,7.999978,87.5</t>
+    <t>62,7.999978,89</t>
+  </si>
+  <si>
+    <t>64.25,7.999978,90.5_59.75,7.999978,90.5_59.75,7.999978,87.5_64.25,7.999978,87.5</t>
   </si>
   <si>
     <t>70308</t>
   </si>
   <si>
-    <t>57.7461738586426,7.999978,84</t>
-  </si>
-  <si>
-    <t>59.74617,7.999978,85.5_55.74617,7.999978,85.5_55.74617,7.999978,82.5_59.74617,7.999978,82.5</t>
-  </si>
-  <si>
-    <t>63,7.999978,70</t>
-  </si>
-  <si>
-    <t>62,7.999978,72_62,7.999978,68_64,7.999978,68_64,7.999978,72</t>
+    <t>62,7.999978,84</t>
+  </si>
+  <si>
+    <t>64,7.999978,85.5_60,7.999978,85.5_60,7.999978,82.5_64,7.999978,82.5</t>
+  </si>
+  <si>
+    <t>67,9.038384,70</t>
+  </si>
+  <si>
+    <t>66,7.999978,72_66,7.999978,68_68,7.999978,68_68,7.999978,72</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1408,415 +1408,523 @@
     <t>74871</t>
   </si>
   <si>
-    <t>85,7.999978,56</t>
-  </si>
-  <si>
-    <t>86,7.999978,57_84,7.999978,57_84,7.999978,55_86,7.999978,55</t>
+    <t>85,7.999978,72</t>
+  </si>
+  <si>
+    <t>86,7.999978,73_84,7.999978,73_84,7.999978,71_86,7.999978,71</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/Key_Orange.prefab</t>
   </si>
   <si>
+    <t>77,7.999978,72</t>
+  </si>
+  <si>
+    <t>74.75,7.999978,74.25_74.75,7.999978,69.75_79.25,7.999978,69.75_79.25,7.999978,74.25</t>
+  </si>
+  <si>
+    <t>74876</t>
+  </si>
+  <si>
+    <t>70301</t>
+  </si>
+  <si>
+    <t>62,7.999978,63</t>
+  </si>
+  <si>
+    <t>64.25,7.999978,65.25_59.75,7.999978,65.25_59.75,7.999978,60.75_64.25,7.999978,60.75</t>
+  </si>
+  <si>
+    <t>70302</t>
+  </si>
+  <si>
+    <t>109.408554077148,8.003199,114</t>
+  </si>
+  <si>
+    <t>114.4086,8.003199,116_107.4086,8.003199,116_107.4086,8.003199,112_114.4086,8.003199,112</t>
+  </si>
+  <si>
+    <t>74875</t>
+  </si>
+  <si>
+    <t>62,7.999978,56</t>
+  </si>
+  <si>
+    <t>63,7.999978,57_61,7.999978,57_61,7.999978,55_63,7.999978,55</t>
+  </si>
+  <si>
+    <t>84,7.999978,56</t>
+  </si>
+  <si>
+    <t>85.5,7.999978,54_85.5,7.999978,58_82.5,7.999978,58_82.5,7.999978,54</t>
+  </si>
+  <si>
+    <t>137,8.003199,133.983917236328</t>
+  </si>
+  <si>
+    <t>138.5,8.003199,131.4839_138.5,8.003199,136.4839_135.5,8.003199,136.4839_135.5,8.003199,131.4839</t>
+  </si>
+  <si>
+    <t>74878</t>
+  </si>
+  <si>
+    <t>88,7.999978,156</t>
+  </si>
+  <si>
+    <t>89,7.999978,155_89,7.999978,157_87,7.999978,157_87,7.999978,155</t>
+  </si>
+  <si>
+    <t>98,7.999978,156</t>
+  </si>
+  <si>
+    <t>99.5,7.999978,153.5_99.5,7.999978,158.5_96.5,7.999978,158.5_96.5,7.999978,153.5</t>
+  </si>
+  <si>
+    <t>102,7.999978,121</t>
+  </si>
+  <si>
+    <t>104,7.999978,122_100,7.999978,122_100,7.999978,120_104,7.999978,120</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_Door_01_purple.prefab</t>
+  </si>
+  <si>
+    <t>74881</t>
+  </si>
+  <si>
+    <t>102,7.999978,122</t>
+  </si>
+  <si>
+    <t>0,74995</t>
+  </si>
+  <si>
+    <t>102,7.999978,124</t>
+  </si>
+  <si>
+    <t>74880</t>
+  </si>
+  <si>
+    <t>122,7.999978,114</t>
+  </si>
+  <si>
+    <t>123,7.999978,115_121,7.999978,115_121,7.999978,113_123,7.999978,113</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/Key_Purple.prefab</t>
+  </si>
+  <si>
+    <t>112,8.003199,134</t>
+  </si>
+  <si>
+    <t>110.5,8.003199,136_110.5,8.003199,132_113.5,8.003199,132_113.5,8.003199,136</t>
+  </si>
+  <si>
+    <t>0,74996</t>
+  </si>
+  <si>
+    <t>105,7.999978,143</t>
+  </si>
+  <si>
+    <t>70001_2</t>
+  </si>
+  <si>
+    <t>74996</t>
+  </si>
+  <si>
+    <t>127,8.003199,134</t>
+  </si>
+  <si>
+    <t>129.25,8.003199,131.75_129.25,8.003199,136.25_124.75,8.003199,136.25_124.75,8.003199,131.75</t>
+  </si>
+  <si>
+    <t>142,7.999978,176</t>
+  </si>
+  <si>
+    <t>143.5,7.999978,178_140.5,7.999978,178_140.5,7.999978,174_143.5,7.999978,174</t>
+  </si>
+  <si>
+    <t>74887</t>
+  </si>
+  <si>
+    <t>74886</t>
+  </si>
+  <si>
+    <t>142,7.999978,185</t>
+  </si>
+  <si>
+    <t>144,7.999978,187_140,7.999978,187_140,7.999978,183_144,7.999978,183</t>
+  </si>
+  <si>
+    <t>74885</t>
+  </si>
+  <si>
+    <t>122,8.003199,134</t>
+  </si>
+  <si>
+    <t>123,8.003199,135_121,8.003199,135_121,8.003199,133_123,8.003199,133</t>
+  </si>
+  <si>
+    <t>119,10.00309,203</t>
+  </si>
+  <si>
+    <t>120,10.00309,204.5_118,10.00309,204.5_118,10.00309,201.5_120,10.00309,201.5</t>
+  </si>
+  <si>
+    <t>74889</t>
+  </si>
+  <si>
+    <t>112,8.003199,203</t>
+  </si>
+  <si>
+    <t>114,8.003199,206_110,8.003199,206_110,8.003199,200_114,8.003199,200</t>
+  </si>
+  <si>
+    <t>74888</t>
+  </si>
+  <si>
+    <t>112,7.999978,207</t>
+  </si>
+  <si>
+    <t>0,74998</t>
+  </si>
+  <si>
+    <t>112,7.999978,208</t>
+  </si>
+  <si>
+    <t>95.7563781738281,7.999978,203</t>
+  </si>
+  <si>
+    <t>97.75638,7.999978,204.5_93.75638,7.999978,204.5_93.75638,7.999978,201.5_97.75638,7.999978,201.5</t>
+  </si>
+  <si>
+    <t>96,7.999978,209</t>
+  </si>
+  <si>
+    <t>98.25,7.999978,211.25_93.75,7.999978,211.25_93.75,7.999978,206.75_98.25,7.999978,206.75</t>
+  </si>
+  <si>
+    <t>70309</t>
+  </si>
+  <si>
+    <t>73,7.999978,216</t>
+  </si>
+  <si>
+    <t>74.5,7.999978,213.75_74.5,7.999978,218.25_71.5,7.999978,218.25_71.5,7.999978,213.75</t>
+  </si>
+  <si>
+    <t>70304</t>
+  </si>
+  <si>
+    <t>115,7.999978,240</t>
+  </si>
+  <si>
+    <t>116,7.999978,238_116,7.999978,242_114,7.999978,242_114,7.999978,238</t>
+  </si>
+  <si>
+    <t>74894</t>
+  </si>
+  <si>
+    <t>70001_3</t>
+  </si>
+  <si>
+    <t>67,7.999978,216</t>
+  </si>
+  <si>
+    <t>68,7.999978,217_66,7.999978,217_66,7.999978,215_68,7.999978,215</t>
+  </si>
+  <si>
+    <t>133,7.999978,238.119369506836</t>
+  </si>
+  <si>
+    <t>131.5,7.999978,240.1194_131.5,7.999978,236.1194_134.5,7.999978,236.1194_134.5,7.999978,240.1194</t>
+  </si>
+  <si>
+    <t>100.981590270996,7.999978,172.904113769531</t>
+  </si>
+  <si>
+    <t>100.98,0.00,172.90,145.17,0.00,172.90,145.17,0.00,142.53,100.98,0.00,142.53</t>
+  </si>
+  <si>
+    <t>128,7.999978,296</t>
+  </si>
+  <si>
+    <t>126.5,7.999978,294_129.5,7.999978,294_129.5,7.999978,298_126.5,7.999978,298</t>
+  </si>
+  <si>
+    <t>74898,74899,74900</t>
+  </si>
+  <si>
+    <t>117.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>118.1416,8.003199,273_118.1416,8.003199,275_116.1416,8.003199,275_116.1416,8.003199,273</t>
+  </si>
+  <si>
+    <t>74897</t>
+  </si>
+  <si>
+    <t>119.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>120.1416,8.003199,273_120.1416,8.003199,275_118.1416,8.003199,275_118.1416,8.003199,273</t>
+  </si>
+  <si>
+    <t>121.141586303711,8.003199,274</t>
+  </si>
+  <si>
+    <t>122.1416,8.003199,273_122.1416,8.003199,275_120.1416,8.003199,275_120.1416,8.003199,273</t>
+  </si>
+  <si>
+    <t>135,7.999978,274</t>
+  </si>
+  <si>
+    <t>132.75,7.999978,276.25_132.75,7.999978,271.75_137.25,7.999978,271.75_137.25,7.999978,276.25</t>
+  </si>
+  <si>
+    <t>70306</t>
+  </si>
+  <si>
+    <t>116.034126281738,7.999978,253.618927001953</t>
+  </si>
+  <si>
+    <t>116.03,0.00,253.00,149.00,0.00,253.00,149.00,0.00,223.00,116.03,0.00,223.00</t>
+  </si>
+  <si>
+    <t>113,7.999978,294</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_TanHuangBan.prefab</t>
+  </si>
+  <si>
+    <t>74907</t>
+  </si>
+  <si>
+    <t>119,7.999978,293.976043701172</t>
+  </si>
+  <si>
+    <t>119,7.999978,298</t>
+  </si>
+  <si>
+    <t>74909</t>
+  </si>
+  <si>
+    <t>113,7.999978,297.976043701172</t>
+  </si>
+  <si>
+    <t>110,7.999978,286</t>
+  </si>
+  <si>
+    <t>107.75,7.999978,283.75_112.25,7.999978,283.75_112.25,7.999978,288.25_107.75,7.999978,288.25</t>
+  </si>
+  <si>
+    <t>70305</t>
+  </si>
+  <si>
+    <t>74.038444519043,13.99992,232</t>
+  </si>
+  <si>
+    <t>75.78844,13.99992,230.5_75.78844,13.99992,233.5_71.78844,13.99992,233.5_71.78844,13.99992,230.5</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGfasheqi.prefab</t>
+  </si>
+  <si>
+    <t>88.038444519043,13.99992,232</t>
+  </si>
+  <si>
+    <t>89.53844,13.99992,233.5_86.53844,13.99992,233.5_86.53844,13.99992,230.5_89.53844,13.99992,230.5</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGjingzi.prefab</t>
+  </si>
+  <si>
+    <t>88.038444519043,13.99992,244</t>
+  </si>
+  <si>
+    <t>89.53844,13.99992,245.5_86.53844,13.99992,245.5_86.53844,13.99992,242.5_89.53844,13.99992,242.5</t>
+  </si>
+  <si>
+    <t>74.038444519043,13.99992,253.25</t>
+  </si>
+  <si>
+    <t>72.53844,13.99992,251_75.53844,13.99992,251_75.53844,13.99992,255_72.53844,13.99992,255</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_JGJieshouqi.prefab</t>
+  </si>
+  <si>
+    <t>74983</t>
+  </si>
+  <si>
+    <t>78,13.99992,255</t>
+  </si>
+  <si>
+    <t>80,13.99992,256_76,13.99992,256_76,13.99992,254_80,13.99992,254</t>
+  </si>
+  <si>
+    <t>74981</t>
+  </si>
+  <si>
+    <t>74.038444519043,13.99992,244</t>
+  </si>
+  <si>
+    <t>75.53844,13.99992,245.5_72.53844,13.99992,245.5_72.53844,13.99992,242.5_75.53844,13.99992,242.5</t>
+  </si>
+  <si>
+    <t>62.2290153503418,13.99992,253.647537231445</t>
+  </si>
+  <si>
+    <t>62.23,0.00,253.65,97.86,0.00,253.65,97.86,0.00,222.24,62.23,0.00,222.24</t>
+  </si>
+  <si>
+    <t>143,7.999978,274</t>
+  </si>
+  <si>
+    <t>142,7.999978,273_144,7.999978,273_144,7.999978,275_142,7.999978,275</t>
+  </si>
+  <si>
+    <t>90.9580841064453,7.999978,221</t>
+  </si>
+  <si>
+    <t>92.95808,7.999978,222.5_88.95808,7.999978,222.5_88.95808,7.999978,219.5_92.95808,7.999978,219.5</t>
+  </si>
+  <si>
+    <t>74991</t>
+  </si>
+  <si>
+    <t>75,13.99992,266</t>
+  </si>
+  <si>
+    <t>91,13.99992,224.229995727539</t>
+  </si>
+  <si>
+    <t>88.75,13.99992,221.98_93.25,13.99992,221.98_93.25,13.99992,226.48_88.75,13.99992,226.48</t>
+  </si>
+  <si>
+    <t>70307</t>
+  </si>
+  <si>
+    <t>115,8.001535,52</t>
+  </si>
+  <si>
+    <t>116,9.186258,50_116,9.186258,54_114,9.186258,54_114,9.186258,50</t>
+  </si>
+  <si>
+    <t>75002</t>
+  </si>
+  <si>
+    <t>98,7.999978,55</t>
+  </si>
+  <si>
+    <t>99,7.999978,56_97,7.999978,56_97,7.999978,54_99,7.999978,54</t>
+  </si>
+  <si>
     <t>77,7.999978,56</t>
   </si>
   <si>
-    <t>74.75,7.999978,58.25_74.75,7.999978,53.75_79.25,7.999978,53.75_79.25,7.999978,58.25</t>
-  </si>
-  <si>
-    <t>74876</t>
-  </si>
-  <si>
-    <t>70301</t>
-  </si>
-  <si>
-    <t>58,7.999978,63</t>
-  </si>
-  <si>
-    <t>60.25,7.999978,65.25_55.75,7.999978,65.25_55.75,7.999978,60.75_60.25,7.999978,60.75</t>
-  </si>
-  <si>
-    <t>70302</t>
-  </si>
-  <si>
-    <t>109.408554077148,8.003199,114</t>
-  </si>
-  <si>
-    <t>114.4086,8.003201,116_107.4086,8.003201,116_107.4086,8.003201,112_114.4086,8.003201,112</t>
-  </si>
-  <si>
-    <t>74875</t>
-  </si>
-  <si>
-    <t>58,7.999978,57</t>
-  </si>
-  <si>
-    <t>59,7.999978,58_57,7.999978,58_57,7.999978,56_59,7.999978,56</t>
-  </si>
-  <si>
-    <t>58,7.999978,41</t>
-  </si>
-  <si>
-    <t>59.5,7.999978,39_59.5,7.999978,43_56.5,7.999978,43_56.5,7.999978,39</t>
-  </si>
-  <si>
-    <t>137,8.003199,133.983917236328</t>
-  </si>
-  <si>
-    <t>138.5,8.003201,131.4839_138.5,8.003201,136.4839_135.5,8.003201,136.4839_135.5,8.003201,131.4839</t>
-  </si>
-  <si>
-    <t>74878</t>
-  </si>
-  <si>
-    <t>88,7.999978,156</t>
-  </si>
-  <si>
-    <t>89,7.999978,155_89,7.999978,157_87,7.999978,157_87,7.999978,155</t>
-  </si>
-  <si>
-    <t>98,7.999978,156</t>
-  </si>
-  <si>
-    <t>99.5,7.999978,153.5_99.5,7.999978,158.5_96.5,7.999978,158.5_96.5,7.999978,153.5</t>
-  </si>
-  <si>
-    <t>102,7.999978,121</t>
-  </si>
-  <si>
-    <t>104,7.999978,122_100,7.999978,122_100,7.999978,120_104,7.999978,120</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_Door_01_purple.prefab</t>
-  </si>
-  <si>
-    <t>74881</t>
-  </si>
-  <si>
-    <t>102,7.999978,122</t>
-  </si>
-  <si>
-    <t>0,74995</t>
-  </si>
-  <si>
-    <t>102,7.999978,124</t>
-  </si>
-  <si>
-    <t>74880</t>
-  </si>
-  <si>
-    <t>122,7.999978,114</t>
-  </si>
-  <si>
-    <t>123,7.999978,115_121,7.999978,115_121,7.999978,113_123,7.999978,113</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/Key_Purple.prefab</t>
-  </si>
-  <si>
-    <t>112,8.003199,134</t>
-  </si>
-  <si>
-    <t>110.5,8.003201,136_110.5,8.003201,132_113.5,8.003201,132_113.5,8.003201,136</t>
-  </si>
-  <si>
-    <t>0,74996</t>
-  </si>
-  <si>
-    <t>105,7.999978,143</t>
-  </si>
-  <si>
-    <t>70001_2</t>
-  </si>
-  <si>
-    <t>74996</t>
-  </si>
-  <si>
-    <t>127,8.003199,134</t>
-  </si>
-  <si>
-    <t>129.25,8.003201,131.75_129.25,8.003201,136.25_124.75,8.003201,136.25_124.75,8.003201,131.75</t>
-  </si>
-  <si>
-    <t>142,7.999978,176</t>
-  </si>
-  <si>
-    <t>143.5,7.999978,178_140.5,7.999978,178_140.5,7.999978,174_143.5,7.999978,174</t>
-  </si>
-  <si>
-    <t>74887</t>
-  </si>
-  <si>
-    <t>74886</t>
-  </si>
-  <si>
-    <t>142,7.999978,185</t>
-  </si>
-  <si>
-    <t>144,7.999978,187_140,7.999978,187_140,7.999978,183_144,7.999978,183</t>
-  </si>
-  <si>
-    <t>74885</t>
-  </si>
-  <si>
-    <t>122,8.003199,134</t>
-  </si>
-  <si>
-    <t>123,8.003201,135_121,8.003201,135_121,8.003201,133_123,8.003201,133</t>
-  </si>
-  <si>
-    <t>119,10.00309,203</t>
-  </si>
-  <si>
-    <t>120,10.00309,204.5_118,10.00309,204.5_118,10.00309,201.5_120,10.00309,201.5</t>
-  </si>
-  <si>
-    <t>74889</t>
-  </si>
-  <si>
-    <t>112,8.003199,203</t>
-  </si>
-  <si>
-    <t>114,8.003201,206_110,8.003201,206_110,8.003201,200_114,8.003201,200</t>
-  </si>
-  <si>
-    <t>74888</t>
-  </si>
-  <si>
-    <t>112,8.000208,207</t>
-  </si>
-  <si>
-    <t>0,74998</t>
-  </si>
-  <si>
-    <t>112,7.999978,208</t>
-  </si>
-  <si>
-    <t>95.7563781738281,7.999978,203</t>
-  </si>
-  <si>
-    <t>97.75638,7.999978,204.5_93.75638,7.999978,204.5_93.75638,7.999978,201.5_97.75638,7.999978,201.5</t>
-  </si>
-  <si>
-    <t>96,7.999978,209</t>
-  </si>
-  <si>
-    <t>98.25,7.999978,211.25_93.75,7.999978,211.25_93.75,7.999978,206.75_98.25,7.999978,206.75</t>
-  </si>
-  <si>
-    <t>70309</t>
-  </si>
-  <si>
-    <t>73,7.999978,216</t>
-  </si>
-  <si>
-    <t>74.5,7.999978,213.75_74.5,7.999978,218.25_71.5,7.999978,218.25_71.5,7.999978,213.75</t>
-  </si>
-  <si>
-    <t>70304</t>
-  </si>
-  <si>
-    <t>115,7.999978,240</t>
-  </si>
-  <si>
-    <t>116,7.999978,238_116,7.999978,242_114,7.999978,242_114,7.999978,238</t>
-  </si>
-  <si>
-    <t>74894</t>
-  </si>
-  <si>
-    <t>70001_3</t>
-  </si>
-  <si>
-    <t>67,7.999978,216</t>
-  </si>
-  <si>
-    <t>68,7.999978,217_66,7.999978,217_66,7.999978,215_68,7.999978,215</t>
-  </si>
-  <si>
-    <t>133,7.999978,238.119369506836</t>
-  </si>
-  <si>
-    <t>131.5,7.999978,240.1194_131.5,7.999978,236.1194_134.5,7.999978,236.1194_134.5,7.999978,240.1194</t>
-  </si>
-  <si>
-    <t>100.981590270996,7.999978,172.904113769531</t>
-  </si>
-  <si>
-    <t>100.98,0.00,172.90,145.17,0.00,172.90,145.17,0.00,142.53,100.98,0.00,142.53</t>
-  </si>
-  <si>
-    <t>128,7.999978,296</t>
-  </si>
-  <si>
-    <t>126.5,7.999978,294_129.5,7.999978,294_129.5,7.999978,298_126.5,7.999978,298</t>
-  </si>
-  <si>
-    <t>74898,74899,74900</t>
-  </si>
-  <si>
-    <t>117.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>118.1416,8.003201,273_118.1416,8.003201,275_116.1416,8.003201,275_116.1416,8.003201,273</t>
-  </si>
-  <si>
-    <t>74897</t>
-  </si>
-  <si>
-    <t>119.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>120.1416,8.003201,273_120.1416,8.003201,275_118.1416,8.003201,275_118.1416,8.003201,273</t>
-  </si>
-  <si>
-    <t>121.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>122.1416,8.003201,273_122.1416,8.003201,275_120.1416,8.003201,275_120.1416,8.003201,273</t>
-  </si>
-  <si>
-    <t>135,7.999978,274</t>
-  </si>
-  <si>
-    <t>132.75,7.999978,276.25_132.75,7.999978,271.75_137.25,7.999978,271.75_137.25,7.999978,276.25</t>
-  </si>
-  <si>
-    <t>70306</t>
-  </si>
-  <si>
-    <t>116.034126281738,7.999978,253.618927001953</t>
-  </si>
-  <si>
-    <t>116.03,0.00,253.00,149.00,0.00,253.00,149.00,0.00,223.00,116.03,0.00,223.00</t>
-  </si>
-  <si>
-    <t>113,7.999978,294</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_TanHuangBan.prefab</t>
-  </si>
-  <si>
-    <t>74907</t>
-  </si>
-  <si>
-    <t>119,7.999978,293.976043701172</t>
-  </si>
-  <si>
-    <t>119,7.999978,298</t>
-  </si>
-  <si>
-    <t>74909</t>
-  </si>
-  <si>
-    <t>113,7.999978,297.976043701172</t>
-  </si>
-  <si>
-    <t>110,7.999978,286</t>
-  </si>
-  <si>
-    <t>107.75,7.999978,283.75_112.25,7.999978,283.75_112.25,7.999978,288.25_107.75,7.999978,288.25</t>
-  </si>
-  <si>
-    <t>70305</t>
-  </si>
-  <si>
-    <t>74.038444519043,13.99992,232</t>
-  </si>
-  <si>
-    <t>75.78844,13.99992,230.5_75.78844,13.99992,233.5_71.78844,13.99992,233.5_71.78844,13.99992,230.5</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGfasheqi.prefab</t>
-  </si>
-  <si>
-    <t>88.038444519043,13.99992,232</t>
-  </si>
-  <si>
-    <t>89.53844,13.99992,233.5_86.53844,13.99992,233.5_86.53844,13.99992,230.5_89.53844,13.99992,230.5</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGjingzi.prefab</t>
-  </si>
-  <si>
-    <t>88.038444519043,13.99992,244</t>
-  </si>
-  <si>
-    <t>89.53844,13.99992,245.5_86.53844,13.99992,245.5_86.53844,13.99992,242.5_89.53844,13.99992,242.5</t>
-  </si>
-  <si>
-    <t>74.038444519043,13.99992,253.25</t>
-  </si>
-  <si>
-    <t>72.53844,13.99992,251_75.53844,13.99992,251_75.53844,13.99992,255_72.53844,13.99992,255</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_JGJieshouqi.prefab</t>
-  </si>
-  <si>
-    <t>74983</t>
-  </si>
-  <si>
-    <t>78,13.99992,255</t>
-  </si>
-  <si>
-    <t>80,13.99992,256_76,13.99992,256_76,13.99992,254_80,13.99992,254</t>
-  </si>
-  <si>
-    <t>74981</t>
-  </si>
-  <si>
-    <t>74.038444519043,13.99992,244</t>
-  </si>
-  <si>
-    <t>75.53844,13.99992,245.5_72.53844,13.99992,245.5_72.53844,13.99992,242.5_75.53844,13.99992,242.5</t>
-  </si>
-  <si>
-    <t>62.2290153503418,13.99992,253.647537231445</t>
-  </si>
-  <si>
-    <t>62.23,0.00,253.65,97.86,0.00,253.65,97.86,0.00,222.24,62.23,0.00,222.24</t>
-  </si>
-  <si>
-    <t>143,7.999978,274</t>
-  </si>
-  <si>
-    <t>142,7.999978,273_144,7.999978,273_144,7.999978,275_142,7.999978,275</t>
-  </si>
-  <si>
-    <t>90.9580841064453,7.999978,221</t>
-  </si>
-  <si>
-    <t>92.95808,7.999978,222.5_88.95808,7.999978,222.5_88.95808,7.999978,219.5_92.95808,7.999978,219.5</t>
-  </si>
-  <si>
-    <t>74991</t>
-  </si>
-  <si>
-    <t>75,13.99992,266</t>
-  </si>
-  <si>
-    <t>91,13.99992,224.229995727539</t>
-  </si>
-  <si>
-    <t>88.75,13.99992,221.98_93.25,13.99992,221.98_93.25,13.99992,226.48_88.75,13.99992,226.48</t>
-  </si>
-  <si>
-    <t>70307</t>
-  </si>
-  <si>
-    <t>115,9.186258,52</t>
-  </si>
-  <si>
-    <t>116,7.999978,50_116,7.999978,54_114,7.999978,54_114,7.999978,50</t>
-  </si>
-  <si>
-    <t>75002</t>
-  </si>
-  <si>
-    <t>98,7.999978,55</t>
-  </si>
-  <si>
-    <t>99,7.999978,56_97,7.999978,56_97,7.999978,54_99,7.999978,54</t>
+    <t>78,7.999978,54_78,7.999978,58_76,7.999978,58_76,7.999978,54</t>
+  </si>
+  <si>
+    <t>75004,75006</t>
+  </si>
+  <si>
+    <t>78,7.999978,41</t>
+  </si>
+  <si>
+    <t>75005</t>
+  </si>
+  <si>
+    <t>75003</t>
+  </si>
+  <si>
+    <t>70,7.999978,35</t>
+  </si>
+  <si>
+    <t>71.5,0,36.5_68.5,0,36.5_68.5,0,33.5_71.5,0,33.5</t>
+  </si>
+  <si>
+    <t>66,7.999978,33</t>
+  </si>
+  <si>
+    <t>75007</t>
+  </si>
+  <si>
+    <t>74,7.999978,39</t>
+  </si>
+  <si>
+    <t>75.5,-0.04387474,40.5_72.5,-0.04387474,40.5_72.5,-0.04387474,37.5_75.5,-0.04387474,37.5</t>
+  </si>
+  <si>
+    <t>72,7.999978,37</t>
+  </si>
+  <si>
+    <t>Prefab/PuzzleMap/Prop/P_Zhangai_b.prefab</t>
+  </si>
+  <si>
+    <t>66,7.999978,31</t>
+  </si>
+  <si>
+    <t>68,7.999978,31</t>
+  </si>
+  <si>
+    <t>70,7.999978,31</t>
+  </si>
+  <si>
+    <t>72,7.999978,31</t>
+  </si>
+  <si>
+    <t>74,7.999978,31</t>
+  </si>
+  <si>
+    <t>76,7.999978,31</t>
+  </si>
+  <si>
+    <t>78,7.999978,31</t>
+  </si>
+  <si>
+    <t>78,7.999978,33</t>
+  </si>
+  <si>
+    <t>78,7.999978,35</t>
+  </si>
+  <si>
+    <t>78,7.999978,37</t>
+  </si>
+  <si>
+    <t>78,7.999978,39</t>
+  </si>
+  <si>
+    <t>66,7.999978,35</t>
+  </si>
+  <si>
+    <t>78,7.999978,43</t>
+  </si>
+  <si>
+    <t>76,7.999978,43</t>
+  </si>
+  <si>
+    <t>74,7.999978,43</t>
+  </si>
+  <si>
+    <t>72,7.999978,43</t>
+  </si>
+  <si>
+    <t>70,7.999978,43</t>
+  </si>
+  <si>
+    <t>68,7.999978,43</t>
+  </si>
+  <si>
+    <t>66,7.999978,43</t>
+  </si>
+  <si>
+    <t>66,7.999978,41</t>
+  </si>
+  <si>
+    <t>66,7.999978,39</t>
+  </si>
+  <si>
+    <t>66,7.999978,37</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -1937,9 +2045,6 @@
   </si>
   <si>
     <t>38,-8.769137E-05,40</t>
-  </si>
-  <si>
-    <t>Prefab/PuzzleMap/Prop/P_Zhangai_b.prefab</t>
   </si>
   <si>
     <t>32,-8.769137E-05,34</t>
@@ -3424,7 +3529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA346"/>
+  <dimension ref="A1:AA374"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -23452,44 +23557,45 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>84928</v>
+        <v>75003</v>
       </c>
       <c r="D261" s="50" t="s">
         <v>600</v>
       </c>
       <c r="E261" s="50">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F261" s="50">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H261" s="50" t="s">
+        <v>601</v>
       </c>
       <c r="I261" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J261" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="L261" s="50" t="s">
-        <v>1</v>
+        <v>602</v>
       </c>
       <c r="M261" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N261" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O261" s="50">
         <v>0</v>
       </c>
-      <c r="P261" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P261" s="50"/>
       <c r="Q261" s="50">
         <v>0</v>
       </c>
@@ -23532,40 +23638,37 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>84929</v>
+        <v>75004</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E262" s="50">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F262" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H262" s="50" t="s">
-        <v>602</v>
+        <v>60</v>
       </c>
       <c r="I262" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J262" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>377</v>
+        <v>285</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M262" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="N262" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O262" s="50">
         <v>0</v>
@@ -23613,37 +23716,40 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>84930</v>
+        <v>75005</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E263" s="50">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F263" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G263" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
+      </c>
+      <c r="H263" s="50" t="s">
+        <v>607</v>
       </c>
       <c r="I263" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J263" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>388</v>
+        <v>276</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>605</v>
+        <v>1</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="N263" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O263" s="50">
         <v>0</v>
@@ -23691,40 +23797,37 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>84931</v>
+        <v>75006</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E264" s="50">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F264" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G264" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H264" s="50" t="s">
-        <v>608</v>
+        <v>60</v>
       </c>
       <c r="I264" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J264" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>392</v>
+        <v>271</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>1</v>
+        <v>609</v>
       </c>
       <c r="M264" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="N264" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O264" s="50">
         <v>0</v>
@@ -23772,37 +23875,40 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>84932</v>
+        <v>75007</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E265" s="50">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F265" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H265" s="50" t="s">
+        <v>611</v>
+      </c>
       <c r="I265" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J265" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>388</v>
+        <v>283</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>610</v>
+        <v>1</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="N265" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O265" s="50">
         <v>0</v>
@@ -23850,13 +23956,13 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>84933</v>
+        <v>75008</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E266" s="50">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F266" s="50">
         <v>1</v>
@@ -23864,17 +23970,14 @@
       <c r="G266" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H266" s="50" t="s">
-        <v>612</v>
-      </c>
       <c r="I266" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J266" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>392</v>
+        <v>613</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -23883,7 +23986,7 @@
         <v>1</v>
       </c>
       <c r="N266" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O266" s="50">
         <v>0</v>
@@ -23931,31 +24034,28 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>84934</v>
+        <v>75009</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E267" s="50">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F267" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H267" s="50" t="s">
-        <v>614</v>
+        <v>60</v>
       </c>
       <c r="I267" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J267" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>398</v>
+        <v>301</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -23964,7 +24064,7 @@
         <v>1</v>
       </c>
       <c r="N267" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O267" s="50">
         <v>0</v>
@@ -24012,31 +24112,28 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>84935</v>
+        <v>75010</v>
       </c>
       <c r="D268" s="50" t="s">
         <v>615</v>
       </c>
       <c r="E268" s="50">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F268" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G268" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H268" s="50" t="s">
-        <v>616</v>
-      </c>
       <c r="I268" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J268" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>403</v>
+        <v>301</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -24045,7 +24142,7 @@
         <v>1</v>
       </c>
       <c r="N268" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O268" s="50">
         <v>0</v>
@@ -24093,31 +24190,28 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>84936</v>
+        <v>75011</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E269" s="50">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F269" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G269" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H269" s="50" t="s">
-        <v>618</v>
-      </c>
       <c r="I269" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J269" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K269" s="50" t="s">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="L269" s="50" t="s">
         <v>1</v>
@@ -24126,7 +24220,7 @@
         <v>1</v>
       </c>
       <c r="N269" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O269" s="50">
         <v>0</v>
@@ -24148,7 +24242,7 @@
         <v>0</v>
       </c>
       <c r="V269" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W269" s="50" t="s">
         <v>1</v>
@@ -24174,31 +24268,28 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>84937</v>
+        <v>75012</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E270" s="50">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F270" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G270" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H270" s="50" t="s">
-        <v>620</v>
+        <v>60</v>
       </c>
       <c r="I270" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J270" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K270" s="50" t="s">
-        <v>396</v>
+        <v>301</v>
       </c>
       <c r="L270" s="50" t="s">
         <v>1</v>
@@ -24207,7 +24298,7 @@
         <v>1</v>
       </c>
       <c r="N270" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O270" s="50">
         <v>0</v>
@@ -24229,7 +24320,7 @@
         <v>0</v>
       </c>
       <c r="V270" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W270" s="50" t="s">
         <v>1</v>
@@ -24255,31 +24346,28 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>84938</v>
+        <v>75013</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E271" s="50">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F271" s="50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G271" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H271" s="50" t="s">
-        <v>622</v>
-      </c>
       <c r="I271" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J271" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K271" s="50" t="s">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="L271" s="50" t="s">
         <v>1</v>
@@ -24288,7 +24376,7 @@
         <v>1</v>
       </c>
       <c r="N271" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O271" s="50">
         <v>0</v>
@@ -24336,13 +24424,13 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>84939</v>
+        <v>75014</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E272" s="50">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F272" s="50">
         <v>0</v>
@@ -24350,17 +24438,14 @@
       <c r="G272" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H272" s="50" t="s">
-        <v>624</v>
-      </c>
       <c r="I272" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J272" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K272" s="50" t="s">
-        <v>394</v>
+        <v>301</v>
       </c>
       <c r="L272" s="50" t="s">
         <v>1</v>
@@ -24369,7 +24454,7 @@
         <v>1</v>
       </c>
       <c r="N272" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O272" s="50">
         <v>0</v>
@@ -24417,13 +24502,13 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>84940</v>
+        <v>75015</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="E273" s="50">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F273" s="50">
         <v>0</v>
@@ -24431,17 +24516,14 @@
       <c r="G273" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H273" s="50" t="s">
-        <v>626</v>
-      </c>
       <c r="I273" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J273" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K273" s="50" t="s">
-        <v>394</v>
+        <v>301</v>
       </c>
       <c r="L273" s="50" t="s">
         <v>1</v>
@@ -24450,7 +24532,7 @@
         <v>1</v>
       </c>
       <c r="N273" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O273" s="50">
         <v>0</v>
@@ -24498,40 +24580,37 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>84941</v>
+        <v>75016</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="E274" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F274" s="50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G274" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H274" s="50" t="s">
-        <v>628</v>
-      </c>
       <c r="I274" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J274" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K274" s="50" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="L274" s="50" t="s">
-        <v>629</v>
+        <v>1</v>
       </c>
       <c r="M274" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N274" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O274" s="50">
         <v>0</v>
@@ -24579,16 +24658,16 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>84942</v>
+        <v>75017</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E275" s="50">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F275" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G275" s="50" t="s">
         <v>60</v>
@@ -24600,16 +24679,16 @@
         <v>62</v>
       </c>
       <c r="K275" s="50" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="L275" s="50" t="s">
-        <v>631</v>
+        <v>1</v>
       </c>
       <c r="M275" s="50" t="s">
-        <v>632</v>
+        <v>1</v>
       </c>
       <c r="N275" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O275" s="50">
         <v>0</v>
@@ -24657,31 +24736,28 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>84943</v>
+        <v>75018</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="E276" s="50">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F276" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G276" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H276" s="50" t="s">
-        <v>634</v>
-      </c>
       <c r="I276" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J276" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K276" s="50" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="L276" s="50" t="s">
         <v>1</v>
@@ -24690,7 +24766,7 @@
         <v>1</v>
       </c>
       <c r="N276" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O276" s="50">
         <v>0</v>
@@ -24738,16 +24814,16 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>84944</v>
+        <v>75019</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="E277" s="50">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F277" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G277" s="50" t="s">
         <v>60</v>
@@ -24759,16 +24835,16 @@
         <v>62</v>
       </c>
       <c r="K277" s="50" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="L277" s="50" t="s">
-        <v>636</v>
+        <v>1</v>
       </c>
       <c r="M277" s="50" t="s">
-        <v>632</v>
+        <v>1</v>
       </c>
       <c r="N277" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O277" s="50">
         <v>0</v>
@@ -24816,31 +24892,28 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>84945</v>
+        <v>75020</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="E278" s="50">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F278" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G278" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H278" s="50" t="s">
-        <v>638</v>
-      </c>
       <c r="I278" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J278" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K278" s="50" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="L278" s="50" t="s">
         <v>1</v>
@@ -24849,7 +24922,7 @@
         <v>1</v>
       </c>
       <c r="N278" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O278" s="50">
         <v>0</v>
@@ -24897,16 +24970,16 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>84946</v>
+        <v>75021</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
       </c>
       <c r="F279" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G279" s="50" t="s">
         <v>60</v>
@@ -24918,7 +24991,7 @@
         <v>62</v>
       </c>
       <c r="K279" s="50" t="s">
-        <v>640</v>
+        <v>301</v>
       </c>
       <c r="L279" s="50" t="s">
         <v>1</v>
@@ -24927,7 +25000,7 @@
         <v>1</v>
       </c>
       <c r="N279" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O279" s="50">
         <v>0</v>
@@ -24975,10 +25048,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>84947</v>
+        <v>75022</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25005,7 +25078,7 @@
         <v>1</v>
       </c>
       <c r="N280" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O280" s="50">
         <v>0</v>
@@ -25053,10 +25126,10 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>84948</v>
+        <v>75023</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25083,7 +25156,7 @@
         <v>1</v>
       </c>
       <c r="N281" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O281" s="50">
         <v>0</v>
@@ -25131,10 +25204,10 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>84949</v>
+        <v>75024</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25161,7 +25234,7 @@
         <v>1</v>
       </c>
       <c r="N282" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O282" s="50">
         <v>0</v>
@@ -25209,10 +25282,10 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>84950</v>
+        <v>75025</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25239,7 +25312,7 @@
         <v>1</v>
       </c>
       <c r="N283" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O283" s="50">
         <v>0</v>
@@ -25287,10 +25360,10 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>84951</v>
+        <v>75026</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25317,7 +25390,7 @@
         <v>1</v>
       </c>
       <c r="N284" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O284" s="50">
         <v>0</v>
@@ -25365,10 +25438,10 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>84952</v>
+        <v>75027</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25395,7 +25468,7 @@
         <v>1</v>
       </c>
       <c r="N285" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O285" s="50">
         <v>0</v>
@@ -25443,10 +25516,10 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>84953</v>
+        <v>75028</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25473,7 +25546,7 @@
         <v>1</v>
       </c>
       <c r="N286" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O286" s="50">
         <v>0</v>
@@ -25521,10 +25594,10 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>84954</v>
+        <v>75029</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25551,7 +25624,7 @@
         <v>1</v>
       </c>
       <c r="N287" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O287" s="50">
         <v>0</v>
@@ -25599,10 +25672,10 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>84955</v>
+        <v>75030</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25629,7 +25702,7 @@
         <v>1</v>
       </c>
       <c r="N288" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O288" s="50">
         <v>0</v>
@@ -25677,13 +25750,13 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>84956</v>
+        <v>84928</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="E289" s="50">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="F289" s="50">
         <v>0</v>
@@ -25698,7 +25771,7 @@
         <v>62</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>301</v>
+        <v>75</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -25712,7 +25785,9 @@
       <c r="O289" s="50">
         <v>0</v>
       </c>
-      <c r="P289" s="50"/>
+      <c r="P289" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q289" s="50">
         <v>0</v>
       </c>
@@ -25755,31 +25830,34 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>84957</v>
+        <v>84929</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="E290" s="50">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F290" s="50">
         <v>0</v>
       </c>
       <c r="G290" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H290" s="50" t="s">
+        <v>638</v>
       </c>
       <c r="I290" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J290" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="L290" s="50" t="s">
-        <v>1</v>
+        <v>639</v>
       </c>
       <c r="M290" s="50" t="s">
         <v>1</v>
@@ -25833,19 +25911,19 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>84958</v>
+        <v>84930</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="E291" s="50">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F291" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G291" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>61</v>
@@ -25854,13 +25932,13 @@
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>301</v>
+        <v>388</v>
       </c>
       <c r="L291" s="50" t="s">
-        <v>1</v>
+        <v>641</v>
       </c>
       <c r="M291" s="50" t="s">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="N291" s="50">
         <v>8</v>
@@ -25911,28 +25989,31 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>84959</v>
+        <v>84931</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E292" s="50">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="F292" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G292" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H292" s="50" t="s">
+        <v>644</v>
       </c>
       <c r="I292" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J292" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K292" s="50" t="s">
-        <v>301</v>
+        <v>392</v>
       </c>
       <c r="L292" s="50" t="s">
         <v>1</v>
@@ -25989,16 +26070,16 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>84960</v>
+        <v>84932</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="E293" s="50">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F293" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" s="50" t="s">
         <v>60</v>
@@ -26010,13 +26091,13 @@
         <v>62</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>301</v>
+        <v>388</v>
       </c>
       <c r="L293" s="50" t="s">
-        <v>1</v>
+        <v>646</v>
       </c>
       <c r="M293" s="50" t="s">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="N293" s="50">
         <v>8</v>
@@ -26067,28 +26148,31 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>84961</v>
+        <v>84933</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="E294" s="50">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="F294" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G294" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H294" s="50" t="s">
+        <v>648</v>
+      </c>
       <c r="I294" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J294" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>301</v>
+        <v>392</v>
       </c>
       <c r="L294" s="50" t="s">
         <v>1</v>
@@ -26145,28 +26229,31 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>84962</v>
+        <v>84934</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E295" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F295" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H295" s="50" t="s">
+        <v>650</v>
       </c>
       <c r="I295" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J295" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K295" s="50" t="s">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="L295" s="50" t="s">
         <v>1</v>
@@ -26223,28 +26310,31 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>84963</v>
+        <v>84935</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="E296" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F296" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G296" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H296" s="50" t="s">
+        <v>652</v>
+      </c>
       <c r="I296" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J296" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>301</v>
+        <v>403</v>
       </c>
       <c r="L296" s="50" t="s">
         <v>1</v>
@@ -26301,28 +26391,31 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>84964</v>
+        <v>84936</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E297" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F297" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G297" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H297" s="50" t="s">
+        <v>654</v>
+      </c>
       <c r="I297" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J297" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="L297" s="50" t="s">
         <v>1</v>
@@ -26353,7 +26446,7 @@
         <v>0</v>
       </c>
       <c r="V297" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W297" s="50" t="s">
         <v>1</v>
@@ -26379,28 +26472,31 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>84965</v>
+        <v>84937</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E298" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F298" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G298" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H298" s="50" t="s">
+        <v>656</v>
       </c>
       <c r="I298" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J298" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>301</v>
+        <v>396</v>
       </c>
       <c r="L298" s="50" t="s">
         <v>1</v>
@@ -26431,7 +26527,7 @@
         <v>0</v>
       </c>
       <c r="V298" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W298" s="50" t="s">
         <v>1</v>
@@ -26457,28 +26553,31 @@
         <v>58</v>
       </c>
       <c r="C299" s="50">
-        <v>84966</v>
+        <v>84938</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E299" s="50">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F299" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G299" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H299" s="50" t="s">
+        <v>658</v>
+      </c>
       <c r="I299" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J299" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K299" s="50" t="s">
-        <v>301</v>
+        <v>386</v>
       </c>
       <c r="L299" s="50" t="s">
         <v>1</v>
@@ -26535,13 +26634,13 @@
         <v>58</v>
       </c>
       <c r="C300" s="50">
-        <v>84967</v>
+        <v>84939</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E300" s="50">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F300" s="50">
         <v>0</v>
@@ -26549,14 +26648,17 @@
       <c r="G300" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H300" s="50" t="s">
+        <v>660</v>
+      </c>
       <c r="I300" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J300" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="L300" s="50" t="s">
         <v>1</v>
@@ -26613,13 +26715,13 @@
         <v>58</v>
       </c>
       <c r="C301" s="50">
-        <v>84968</v>
+        <v>84940</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E301" s="50">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F301" s="50">
         <v>0</v>
@@ -26627,14 +26729,17 @@
       <c r="G301" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H301" s="50" t="s">
+        <v>662</v>
+      </c>
       <c r="I301" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J301" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K301" s="50" t="s">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="L301" s="50" t="s">
         <v>1</v>
@@ -26691,19 +26796,19 @@
         <v>58</v>
       </c>
       <c r="C302" s="50">
-        <v>84969</v>
+        <v>84941</v>
       </c>
       <c r="D302" s="50" t="s">
         <v>663</v>
       </c>
       <c r="E302" s="50">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F302" s="50">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G302" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H302" s="50" t="s">
         <v>664</v>
@@ -26715,10 +26820,10 @@
         <v>62</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>569</v>
+        <v>192</v>
       </c>
       <c r="L302" s="50" t="s">
-        <v>1</v>
+        <v>665</v>
       </c>
       <c r="M302" s="50" t="s">
         <v>1</v>
@@ -26772,37 +26877,34 @@
         <v>58</v>
       </c>
       <c r="C303" s="50">
-        <v>84970</v>
+        <v>84942</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E303" s="50">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F303" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G303" s="50" t="s">
-        <v>666</v>
-      </c>
-      <c r="H303" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I303" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J303" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K303" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="L303" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="I303" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J303" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K303" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="L303" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M303" s="50" t="s">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="N303" s="50">
         <v>8</v>
@@ -26853,22 +26955,22 @@
         <v>58</v>
       </c>
       <c r="C304" s="50">
-        <v>84971</v>
+        <v>84943</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E304" s="50">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F304" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G304" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H304" s="50" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I304" s="50" t="s">
         <v>78</v>
@@ -26877,13 +26979,13 @@
         <v>62</v>
       </c>
       <c r="K304" s="50" t="s">
-        <v>577</v>
+        <v>276</v>
       </c>
       <c r="L304" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>670</v>
+        <v>1</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -26934,37 +27036,34 @@
         <v>58</v>
       </c>
       <c r="C305" s="50">
-        <v>84972</v>
+        <v>84944</v>
       </c>
       <c r="D305" s="50" t="s">
         <v>671</v>
       </c>
       <c r="E305" s="50">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F305" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G305" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I305" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J305" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K305" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L305" s="50" t="s">
         <v>672</v>
       </c>
-      <c r="H305" s="50" t="s">
-        <v>673</v>
-      </c>
-      <c r="I305" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J305" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K305" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="L305" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M305" s="50" t="s">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="N305" s="50">
         <v>8</v>
@@ -27015,22 +27114,22 @@
         <v>58</v>
       </c>
       <c r="C306" s="50">
-        <v>84973</v>
+        <v>84945</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E306" s="50">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F306" s="50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G306" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H306" s="50" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I306" s="50" t="s">
         <v>78</v>
@@ -27039,10 +27138,10 @@
         <v>62</v>
       </c>
       <c r="K306" s="50" t="s">
-        <v>192</v>
+        <v>283</v>
       </c>
       <c r="L306" s="50" t="s">
-        <v>676</v>
+        <v>1</v>
       </c>
       <c r="M306" s="50" t="s">
         <v>1</v>
@@ -27096,31 +27195,28 @@
         <v>58</v>
       </c>
       <c r="C307" s="50">
-        <v>84974</v>
+        <v>84946</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E307" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F307" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H307" s="50" t="s">
-        <v>678</v>
-      </c>
       <c r="I307" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J307" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K307" s="50" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="L307" s="50" t="s">
         <v>1</v>
@@ -27177,16 +27273,16 @@
         <v>58</v>
       </c>
       <c r="C308" s="50">
-        <v>84976</v>
+        <v>84947</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E308" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F308" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G308" s="50" t="s">
         <v>60</v>
@@ -27197,27 +27293,55 @@
       <c r="J308" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K308" s="50"/>
-      <c r="L308" s="50"/>
-      <c r="M308" s="50"/>
+      <c r="K308" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="L308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M308" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N308" s="50">
         <v>8</v>
       </c>
-      <c r="O308" s="50"/>
-      <c r="P308" s="50" t="s">
-        <v>680</v>
-      </c>
-      <c r="Q308" s="50"/>
-      <c r="R308" s="50"/>
-      <c r="S308" s="50"/>
-      <c r="T308" s="50"/>
-      <c r="U308" s="50"/>
-      <c r="V308" s="50"/>
-      <c r="W308" s="50"/>
-      <c r="X308" s="50"/>
-      <c r="Y308" s="50"/>
-      <c r="Z308" s="52"/>
-      <c r="AA308" s="50"/>
+      <c r="O308" s="50">
+        <v>0</v>
+      </c>
+      <c r="P308" s="50"/>
+      <c r="Q308" s="50">
+        <v>0</v>
+      </c>
+      <c r="R308" s="50">
+        <v>0</v>
+      </c>
+      <c r="S308" s="50">
+        <v>0</v>
+      </c>
+      <c r="T308" s="50">
+        <v>0</v>
+      </c>
+      <c r="U308" s="50">
+        <v>0</v>
+      </c>
+      <c r="V308" s="50">
+        <v>0</v>
+      </c>
+      <c r="W308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y308" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z308" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="50">
@@ -27227,16 +27351,16 @@
         <v>58</v>
       </c>
       <c r="C309" s="50">
-        <v>84977</v>
+        <v>84948</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E309" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F309" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G309" s="50" t="s">
         <v>60</v>
@@ -27247,27 +27371,55 @@
       <c r="J309" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K309" s="50"/>
-      <c r="L309" s="50"/>
-      <c r="M309" s="50"/>
+      <c r="K309" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="L309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M309" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N309" s="50">
         <v>8</v>
       </c>
-      <c r="O309" s="50"/>
-      <c r="P309" s="50" t="s">
-        <v>682</v>
-      </c>
-      <c r="Q309" s="50"/>
-      <c r="R309" s="50"/>
-      <c r="S309" s="50"/>
-      <c r="T309" s="50"/>
-      <c r="U309" s="50"/>
-      <c r="V309" s="50"/>
-      <c r="W309" s="50"/>
-      <c r="X309" s="50"/>
-      <c r="Y309" s="50"/>
-      <c r="Z309" s="52"/>
-      <c r="AA309" s="50"/>
+      <c r="O309" s="50">
+        <v>0</v>
+      </c>
+      <c r="P309" s="50"/>
+      <c r="Q309" s="50">
+        <v>0</v>
+      </c>
+      <c r="R309" s="50">
+        <v>0</v>
+      </c>
+      <c r="S309" s="50">
+        <v>0</v>
+      </c>
+      <c r="T309" s="50">
+        <v>0</v>
+      </c>
+      <c r="U309" s="50">
+        <v>0</v>
+      </c>
+      <c r="V309" s="50">
+        <v>0</v>
+      </c>
+      <c r="W309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y309" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z309" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="50">
@@ -27277,16 +27429,16 @@
         <v>58</v>
       </c>
       <c r="C310" s="50">
-        <v>84978</v>
+        <v>84949</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E310" s="50">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F310" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G310" s="50" t="s">
         <v>60</v>
@@ -27297,27 +27449,55 @@
       <c r="J310" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K310" s="50"/>
-      <c r="L310" s="50"/>
-      <c r="M310" s="50"/>
+      <c r="K310" s="50" t="s">
+        <v>301</v>
+      </c>
+      <c r="L310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M310" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N310" s="50">
         <v>8</v>
       </c>
-      <c r="O310" s="50"/>
-      <c r="P310" s="50" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q310" s="50"/>
-      <c r="R310" s="50"/>
-      <c r="S310" s="50"/>
-      <c r="T310" s="50"/>
-      <c r="U310" s="50"/>
-      <c r="V310" s="50"/>
-      <c r="W310" s="50"/>
-      <c r="X310" s="50"/>
-      <c r="Y310" s="50"/>
-      <c r="Z310" s="52"/>
-      <c r="AA310" s="50"/>
+      <c r="O310" s="50">
+        <v>0</v>
+      </c>
+      <c r="P310" s="50"/>
+      <c r="Q310" s="50">
+        <v>0</v>
+      </c>
+      <c r="R310" s="50">
+        <v>0</v>
+      </c>
+      <c r="S310" s="50">
+        <v>0</v>
+      </c>
+      <c r="T310" s="50">
+        <v>0</v>
+      </c>
+      <c r="U310" s="50">
+        <v>0</v>
+      </c>
+      <c r="V310" s="50">
+        <v>0</v>
+      </c>
+      <c r="W310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y310" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z310" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA310" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="50">
@@ -27327,37 +27507,34 @@
         <v>58</v>
       </c>
       <c r="C311" s="50">
-        <v>84979</v>
+        <v>84950</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="E311" s="50">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F311" s="50">
         <v>0</v>
       </c>
       <c r="G311" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H311" s="50" t="s">
-        <v>686</v>
+        <v>60</v>
       </c>
       <c r="I311" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J311" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K311" s="50" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="L311" s="50" t="s">
-        <v>687</v>
+        <v>1</v>
       </c>
       <c r="M311" s="50" t="s">
-        <v>688</v>
+        <v>1</v>
       </c>
       <c r="N311" s="50">
         <v>8</v>
@@ -27408,13 +27585,13 @@
         <v>58</v>
       </c>
       <c r="C312" s="50">
-        <v>84980</v>
+        <v>84951</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="E312" s="50">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F312" s="50">
         <v>0</v>
@@ -27422,20 +27599,17 @@
       <c r="G312" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H312" s="50" t="s">
-        <v>690</v>
-      </c>
       <c r="I312" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J312" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K312" s="50" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="L312" s="50" t="s">
-        <v>691</v>
+        <v>1</v>
       </c>
       <c r="M312" s="50" t="s">
         <v>1</v>
@@ -27489,13 +27663,13 @@
         <v>58</v>
       </c>
       <c r="C313" s="50">
-        <v>84981</v>
+        <v>84952</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="E313" s="50">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F313" s="50">
         <v>0</v>
@@ -27503,17 +27677,14 @@
       <c r="G313" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H313" s="50" t="s">
-        <v>693</v>
-      </c>
       <c r="I313" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J313" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K313" s="50" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="L313" s="50" t="s">
         <v>1</v>
@@ -27570,13 +27741,13 @@
         <v>58</v>
       </c>
       <c r="C314" s="50">
-        <v>84982</v>
+        <v>84953</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="E314" s="50">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F314" s="50">
         <v>0</v>
@@ -27591,13 +27762,13 @@
         <v>62</v>
       </c>
       <c r="K314" s="50" t="s">
-        <v>695</v>
+        <v>301</v>
       </c>
       <c r="L314" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M314" s="50" t="s">
-        <v>696</v>
+        <v>1</v>
       </c>
       <c r="N314" s="50">
         <v>8</v>
@@ -27605,9 +27776,7 @@
       <c r="O314" s="50">
         <v>0</v>
       </c>
-      <c r="P314" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P314" s="50"/>
       <c r="Q314" s="50">
         <v>0</v>
       </c>
@@ -27650,13 +27819,13 @@
         <v>58</v>
       </c>
       <c r="C315" s="50">
-        <v>84983</v>
+        <v>84954</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="E315" s="50">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F315" s="50">
         <v>0</v>
@@ -27664,17 +27833,14 @@
       <c r="G315" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H315" s="50" t="s">
-        <v>697</v>
-      </c>
       <c r="I315" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J315" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K315" s="50" t="s">
-        <v>698</v>
+        <v>301</v>
       </c>
       <c r="L315" s="50" t="s">
         <v>1</v>
@@ -27688,9 +27854,7 @@
       <c r="O315" s="50">
         <v>0</v>
       </c>
-      <c r="P315" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P315" s="50"/>
       <c r="Q315" s="50">
         <v>0</v>
       </c>
@@ -27733,13 +27897,13 @@
         <v>58</v>
       </c>
       <c r="C316" s="50">
-        <v>84984</v>
+        <v>84955</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="E316" s="50">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F316" s="50">
         <v>0</v>
@@ -27747,17 +27911,14 @@
       <c r="G316" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H316" s="50" t="s">
-        <v>700</v>
-      </c>
       <c r="I316" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J316" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K316" s="50" t="s">
-        <v>701</v>
+        <v>301</v>
       </c>
       <c r="L316" s="50" t="s">
         <v>1</v>
@@ -27771,9 +27932,7 @@
       <c r="O316" s="50">
         <v>0</v>
       </c>
-      <c r="P316" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P316" s="50"/>
       <c r="Q316" s="50">
         <v>0</v>
       </c>
@@ -27816,31 +27975,28 @@
         <v>58</v>
       </c>
       <c r="C317" s="50">
-        <v>330037</v>
+        <v>84956</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="E317" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F317" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G317" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H317" s="50" t="s">
-        <v>703</v>
-      </c>
       <c r="I317" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J317" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K317" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L317" s="50" t="s">
         <v>1</v>
@@ -27849,14 +28005,12 @@
         <v>1</v>
       </c>
       <c r="N317" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O317" s="50">
         <v>0</v>
       </c>
-      <c r="P317" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P317" s="50"/>
       <c r="Q317" s="50">
         <v>0</v>
       </c>
@@ -27866,8 +28020,8 @@
       <c r="S317" s="50">
         <v>0</v>
       </c>
-      <c r="T317" s="50" t="s">
-        <v>61</v>
+      <c r="T317" s="50">
+        <v>0</v>
       </c>
       <c r="U317" s="50">
         <v>0</v>
@@ -27899,40 +28053,37 @@
         <v>58</v>
       </c>
       <c r="C318" s="50">
-        <v>330038</v>
+        <v>84957</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="E318" s="50">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="F318" s="50">
         <v>0</v>
       </c>
       <c r="G318" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H318" s="50" t="s">
-        <v>705</v>
+        <v>60</v>
       </c>
       <c r="I318" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J318" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K318" s="50" t="s">
-        <v>142</v>
+        <v>301</v>
       </c>
       <c r="L318" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M318" s="50" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="N318" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O318" s="50">
         <v>0</v>
@@ -27980,40 +28131,37 @@
         <v>58</v>
       </c>
       <c r="C319" s="50">
-        <v>330039</v>
+        <v>84958</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="E319" s="50">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F319" s="50">
         <v>0</v>
       </c>
       <c r="G319" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H319" s="50" t="s">
-        <v>708</v>
+        <v>60</v>
       </c>
       <c r="I319" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J319" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K319" s="50" t="s">
-        <v>147</v>
+        <v>301</v>
       </c>
       <c r="L319" s="50" t="s">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="M319" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N319" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O319" s="50">
         <v>0</v>
@@ -28061,40 +28209,37 @@
         <v>58</v>
       </c>
       <c r="C320" s="50">
-        <v>330040</v>
+        <v>84959</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="E320" s="50">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F320" s="50">
         <v>0</v>
       </c>
       <c r="G320" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H320" s="50" t="s">
-        <v>711</v>
+        <v>60</v>
       </c>
       <c r="I320" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J320" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K320" s="50" t="s">
-        <v>147</v>
+        <v>301</v>
       </c>
       <c r="L320" s="50" t="s">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="M320" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N320" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O320" s="50">
         <v>0</v>
@@ -28142,40 +28287,37 @@
         <v>58</v>
       </c>
       <c r="C321" s="50">
-        <v>330041</v>
+        <v>84960</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>712</v>
+        <v>689</v>
       </c>
       <c r="E321" s="50">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F321" s="50">
         <v>0</v>
       </c>
       <c r="G321" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H321" s="50" t="s">
-        <v>713</v>
+        <v>60</v>
       </c>
       <c r="I321" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J321" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K321" s="50" t="s">
-        <v>147</v>
+        <v>301</v>
       </c>
       <c r="L321" s="50" t="s">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="M321" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N321" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O321" s="50">
         <v>0</v>
@@ -28223,40 +28365,37 @@
         <v>58</v>
       </c>
       <c r="C322" s="50">
-        <v>330042</v>
+        <v>84961</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>714</v>
+        <v>690</v>
       </c>
       <c r="E322" s="50">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F322" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G322" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H322" s="50" t="s">
-        <v>715</v>
-      </c>
       <c r="I322" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J322" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K322" s="50" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="L322" s="50" t="s">
-        <v>716</v>
+        <v>1</v>
       </c>
       <c r="M322" s="50" t="s">
-        <v>717</v>
+        <v>1</v>
       </c>
       <c r="N322" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O322" s="50">
         <v>0</v>
@@ -28304,31 +28443,28 @@
         <v>58</v>
       </c>
       <c r="C323" s="50">
-        <v>330043</v>
+        <v>84962</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="E323" s="50">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F323" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G323" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H323" s="50" t="s">
-        <v>719</v>
-      </c>
       <c r="I323" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J323" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K323" s="50" t="s">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="L323" s="50" t="s">
         <v>1</v>
@@ -28337,7 +28473,7 @@
         <v>1</v>
       </c>
       <c r="N323" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O323" s="50">
         <v>0</v>
@@ -28385,40 +28521,37 @@
         <v>58</v>
       </c>
       <c r="C324" s="50">
-        <v>330044</v>
+        <v>84963</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>720</v>
+        <v>692</v>
       </c>
       <c r="E324" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F324" s="50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G324" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H324" s="50" t="s">
-        <v>721</v>
-      </c>
       <c r="I324" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J324" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K324" s="50" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="L324" s="50" t="s">
-        <v>722</v>
+        <v>1</v>
       </c>
       <c r="M324" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N324" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O324" s="50">
         <v>0</v>
@@ -28466,31 +28599,28 @@
         <v>58</v>
       </c>
       <c r="C325" s="50">
-        <v>330045</v>
+        <v>84964</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>723</v>
+        <v>693</v>
       </c>
       <c r="E325" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F325" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G325" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H325" s="50" t="s">
-        <v>724</v>
+        <v>60</v>
       </c>
       <c r="I325" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J325" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K325" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L325" s="50" t="s">
         <v>1</v>
@@ -28499,14 +28629,12 @@
         <v>1</v>
       </c>
       <c r="N325" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O325" s="50">
         <v>0</v>
       </c>
-      <c r="P325" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P325" s="50"/>
       <c r="Q325" s="50">
         <v>0</v>
       </c>
@@ -28516,8 +28644,8 @@
       <c r="S325" s="50">
         <v>0</v>
       </c>
-      <c r="T325" s="50" t="s">
-        <v>61</v>
+      <c r="T325" s="50">
+        <v>0</v>
       </c>
       <c r="U325" s="50">
         <v>0</v>
@@ -28549,40 +28677,37 @@
         <v>58</v>
       </c>
       <c r="C326" s="50">
-        <v>330046</v>
+        <v>84965</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="E326" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F326" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G326" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H326" s="50" t="s">
-        <v>726</v>
+        <v>60</v>
       </c>
       <c r="I326" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J326" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K326" s="50" t="s">
-        <v>461</v>
+        <v>301</v>
       </c>
       <c r="L326" s="50" t="s">
-        <v>727</v>
+        <v>1</v>
       </c>
       <c r="M326" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N326" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O326" s="50">
         <v>0</v>
@@ -28630,31 +28755,28 @@
         <v>58</v>
       </c>
       <c r="C327" s="50">
-        <v>330047</v>
+        <v>84966</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="E327" s="50">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F327" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G327" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H327" s="50" t="s">
-        <v>729</v>
-      </c>
       <c r="I327" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J327" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K327" s="50" t="s">
-        <v>465</v>
+        <v>301</v>
       </c>
       <c r="L327" s="50" t="s">
         <v>1</v>
@@ -28663,7 +28785,7 @@
         <v>1</v>
       </c>
       <c r="N327" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O327" s="50">
         <v>0</v>
@@ -28711,31 +28833,28 @@
         <v>58</v>
       </c>
       <c r="C328" s="50">
-        <v>330048</v>
+        <v>84967</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>730</v>
+        <v>696</v>
       </c>
       <c r="E328" s="50">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="F328" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H328" s="50" t="s">
-        <v>731</v>
-      </c>
       <c r="I328" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J328" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K328" s="50" t="s">
-        <v>96</v>
+        <v>301</v>
       </c>
       <c r="L328" s="50" t="s">
         <v>1</v>
@@ -28744,14 +28863,12 @@
         <v>1</v>
       </c>
       <c r="N328" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O328" s="50">
         <v>0</v>
       </c>
-      <c r="P328" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P328" s="50"/>
       <c r="Q328" s="50">
         <v>0</v>
       </c>
@@ -28761,8 +28878,8 @@
       <c r="S328" s="50">
         <v>0</v>
       </c>
-      <c r="T328" s="50" t="s">
-        <v>61</v>
+      <c r="T328" s="50">
+        <v>0</v>
       </c>
       <c r="U328" s="50">
         <v>0</v>
@@ -28794,13 +28911,13 @@
         <v>58</v>
       </c>
       <c r="C329" s="50">
-        <v>330049</v>
+        <v>84968</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>732</v>
+        <v>697</v>
       </c>
       <c r="E329" s="50">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F329" s="50">
         <v>0</v>
@@ -28808,26 +28925,23 @@
       <c r="G329" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H329" s="50" t="s">
-        <v>733</v>
-      </c>
       <c r="I329" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J329" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K329" s="50" t="s">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c r="L329" s="50" t="s">
-        <v>734</v>
+        <v>1</v>
       </c>
       <c r="M329" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N329" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O329" s="50">
         <v>0</v>
@@ -28875,22 +28989,22 @@
         <v>58</v>
       </c>
       <c r="C330" s="50">
-        <v>330050</v>
+        <v>84969</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>735</v>
+        <v>698</v>
       </c>
       <c r="E330" s="50">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F330" s="50">
         <v>0</v>
       </c>
       <c r="G330" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H330" s="50" t="s">
-        <v>736</v>
+        <v>699</v>
       </c>
       <c r="I330" s="50" t="s">
         <v>78</v>
@@ -28899,7 +29013,7 @@
         <v>62</v>
       </c>
       <c r="K330" s="50" t="s">
-        <v>88</v>
+        <v>569</v>
       </c>
       <c r="L330" s="50" t="s">
         <v>1</v>
@@ -28908,7 +29022,7 @@
         <v>1</v>
       </c>
       <c r="N330" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O330" s="50">
         <v>0</v>
@@ -28956,22 +29070,22 @@
         <v>58</v>
       </c>
       <c r="C331" s="50">
-        <v>330051</v>
+        <v>84970</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>737</v>
+        <v>700</v>
       </c>
       <c r="E331" s="50">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F331" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G331" s="50" t="s">
-        <v>138</v>
+        <v>701</v>
       </c>
       <c r="H331" s="50" t="s">
-        <v>738</v>
+        <v>702</v>
       </c>
       <c r="I331" s="50" t="s">
         <v>78</v>
@@ -28980,7 +29094,7 @@
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>230</v>
+        <v>572</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -28989,14 +29103,12 @@
         <v>1</v>
       </c>
       <c r="N331" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O331" s="50">
         <v>0</v>
       </c>
-      <c r="P331" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P331" s="50"/>
       <c r="Q331" s="50">
         <v>0</v>
       </c>
@@ -29039,22 +29151,22 @@
         <v>58</v>
       </c>
       <c r="C332" s="50">
-        <v>330052</v>
+        <v>84971</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="E332" s="50">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F332" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H332" s="50" t="s">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="I332" s="50" t="s">
         <v>78</v>
@@ -29063,23 +29175,21 @@
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>294</v>
+        <v>577</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M332" s="50" t="s">
-        <v>1</v>
+        <v>705</v>
       </c>
       <c r="N332" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O332" s="50">
         <v>0</v>
       </c>
-      <c r="P332" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P332" s="50"/>
       <c r="Q332" s="50">
         <v>0</v>
       </c>
@@ -29122,22 +29232,22 @@
         <v>58</v>
       </c>
       <c r="C333" s="50">
-        <v>330053</v>
+        <v>84972</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="E333" s="50">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F333" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G333" s="50" t="s">
-        <v>60</v>
+        <v>707</v>
       </c>
       <c r="H333" s="50" t="s">
-        <v>742</v>
+        <v>708</v>
       </c>
       <c r="I333" s="50" t="s">
         <v>78</v>
@@ -29146,7 +29256,7 @@
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>246</v>
+        <v>572</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
@@ -29155,14 +29265,12 @@
         <v>1</v>
       </c>
       <c r="N333" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O333" s="50">
         <v>0</v>
       </c>
-      <c r="P333" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P333" s="50"/>
       <c r="Q333" s="50">
         <v>0</v>
       </c>
@@ -29205,22 +29313,22 @@
         <v>58</v>
       </c>
       <c r="C334" s="50">
-        <v>330054</v>
+        <v>84973</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>743</v>
+        <v>709</v>
       </c>
       <c r="E334" s="50">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F334" s="50">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G334" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H334" s="50" t="s">
-        <v>744</v>
+        <v>710</v>
       </c>
       <c r="I334" s="50" t="s">
         <v>78</v>
@@ -29229,23 +29337,21 @@
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="L334" s="50" t="s">
-        <v>1</v>
+        <v>711</v>
       </c>
       <c r="M334" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N334" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O334" s="50">
         <v>0</v>
       </c>
-      <c r="P334" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P334" s="50"/>
       <c r="Q334" s="50">
         <v>0</v>
       </c>
@@ -29255,8 +29361,8 @@
       <c r="S334" s="50">
         <v>0</v>
       </c>
-      <c r="T334" s="50" t="s">
-        <v>61</v>
+      <c r="T334" s="50">
+        <v>0</v>
       </c>
       <c r="U334" s="50">
         <v>0</v>
@@ -29288,22 +29394,22 @@
         <v>58</v>
       </c>
       <c r="C335" s="50">
-        <v>330055</v>
+        <v>84974</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>745</v>
+        <v>712</v>
       </c>
       <c r="E335" s="50">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F335" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G335" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H335" s="50" t="s">
-        <v>746</v>
+        <v>713</v>
       </c>
       <c r="I335" s="50" t="s">
         <v>78</v>
@@ -29312,7 +29418,7 @@
         <v>62</v>
       </c>
       <c r="K335" s="50" t="s">
-        <v>230</v>
+        <v>572</v>
       </c>
       <c r="L335" s="50" t="s">
         <v>1</v>
@@ -29321,14 +29427,12 @@
         <v>1</v>
       </c>
       <c r="N335" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O335" s="50">
         <v>0</v>
       </c>
-      <c r="P335" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P335" s="50"/>
       <c r="Q335" s="50">
         <v>0</v>
       </c>
@@ -29371,80 +29475,47 @@
         <v>58</v>
       </c>
       <c r="C336" s="50">
-        <v>330056</v>
+        <v>84976</v>
       </c>
       <c r="D336" s="50" t="s">
-        <v>747</v>
+        <v>714</v>
       </c>
       <c r="E336" s="50">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F336" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G336" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H336" s="50" t="s">
-        <v>748</v>
+        <v>60</v>
       </c>
       <c r="I336" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J336" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K336" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="L336" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M336" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K336" s="50"/>
+      <c r="L336" s="50"/>
+      <c r="M336" s="50"/>
       <c r="N336" s="50">
-        <v>33</v>
-      </c>
-      <c r="O336" s="50">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O336" s="50"/>
       <c r="P336" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q336" s="50">
-        <v>0</v>
-      </c>
-      <c r="R336" s="50">
-        <v>0</v>
-      </c>
-      <c r="S336" s="50">
-        <v>0</v>
-      </c>
-      <c r="T336" s="50">
-        <v>0</v>
-      </c>
-      <c r="U336" s="50">
-        <v>0</v>
-      </c>
-      <c r="V336" s="50">
-        <v>0</v>
-      </c>
-      <c r="W336" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X336" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y336" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z336" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA336" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="Q336" s="50"/>
+      <c r="R336" s="50"/>
+      <c r="S336" s="50"/>
+      <c r="T336" s="50"/>
+      <c r="U336" s="50"/>
+      <c r="V336" s="50"/>
+      <c r="W336" s="50"/>
+      <c r="X336" s="50"/>
+      <c r="Y336" s="50"/>
+      <c r="Z336" s="52"/>
+      <c r="AA336" s="50"/>
     </row>
     <row r="337">
       <c r="A337" s="50">
@@ -29454,80 +29525,47 @@
         <v>58</v>
       </c>
       <c r="C337" s="50">
-        <v>330058</v>
+        <v>84977</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>749</v>
+        <v>716</v>
       </c>
       <c r="E337" s="50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F337" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G337" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H337" s="50" t="s">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="I337" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J337" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K337" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="L337" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M337" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K337" s="50"/>
+      <c r="L337" s="50"/>
+      <c r="M337" s="50"/>
       <c r="N337" s="50">
-        <v>33</v>
-      </c>
-      <c r="O337" s="50">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O337" s="50"/>
       <c r="P337" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q337" s="50">
-        <v>0</v>
-      </c>
-      <c r="R337" s="50">
-        <v>0</v>
-      </c>
-      <c r="S337" s="50">
-        <v>0</v>
-      </c>
-      <c r="T337" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="U337" s="50">
-        <v>0</v>
-      </c>
-      <c r="V337" s="50">
-        <v>0</v>
-      </c>
-      <c r="W337" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X337" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y337" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z337" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA337" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="Q337" s="50"/>
+      <c r="R337" s="50"/>
+      <c r="S337" s="50"/>
+      <c r="T337" s="50"/>
+      <c r="U337" s="50"/>
+      <c r="V337" s="50"/>
+      <c r="W337" s="50"/>
+      <c r="X337" s="50"/>
+      <c r="Y337" s="50"/>
+      <c r="Z337" s="52"/>
+      <c r="AA337" s="50"/>
     </row>
     <row r="338">
       <c r="A338" s="50">
@@ -29537,80 +29575,47 @@
         <v>58</v>
       </c>
       <c r="C338" s="50">
-        <v>330061</v>
+        <v>84978</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>751</v>
+        <v>718</v>
       </c>
       <c r="E338" s="50">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F338" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G338" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H338" s="50" t="s">
-        <v>752</v>
-      </c>
       <c r="I338" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J338" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K338" s="50" t="s">
-        <v>753</v>
-      </c>
-      <c r="L338" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M338" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K338" s="50"/>
+      <c r="L338" s="50"/>
+      <c r="M338" s="50"/>
       <c r="N338" s="50">
-        <v>33</v>
-      </c>
-      <c r="O338" s="50">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O338" s="50"/>
       <c r="P338" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q338" s="50">
-        <v>0</v>
-      </c>
-      <c r="R338" s="50">
-        <v>0</v>
-      </c>
-      <c r="S338" s="50">
-        <v>0</v>
-      </c>
-      <c r="T338" s="50">
-        <v>0</v>
-      </c>
-      <c r="U338" s="50">
-        <v>0</v>
-      </c>
-      <c r="V338" s="50">
-        <v>0</v>
-      </c>
-      <c r="W338" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X338" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y338" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z338" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA338" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="Q338" s="50"/>
+      <c r="R338" s="50"/>
+      <c r="S338" s="50"/>
+      <c r="T338" s="50"/>
+      <c r="U338" s="50"/>
+      <c r="V338" s="50"/>
+      <c r="W338" s="50"/>
+      <c r="X338" s="50"/>
+      <c r="Y338" s="50"/>
+      <c r="Z338" s="52"/>
+      <c r="AA338" s="50"/>
     </row>
     <row r="339">
       <c r="A339" s="50">
@@ -29620,22 +29625,22 @@
         <v>58</v>
       </c>
       <c r="C339" s="50">
-        <v>330062</v>
+        <v>84979</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="E339" s="50">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F339" s="50">
         <v>0</v>
       </c>
       <c r="G339" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H339" s="50" t="s">
-        <v>755</v>
+        <v>721</v>
       </c>
       <c r="I339" s="50" t="s">
         <v>78</v>
@@ -29644,23 +29649,21 @@
         <v>62</v>
       </c>
       <c r="K339" s="50" t="s">
-        <v>756</v>
+        <v>327</v>
       </c>
       <c r="L339" s="50" t="s">
-        <v>1</v>
+        <v>722</v>
       </c>
       <c r="M339" s="50" t="s">
-        <v>1</v>
+        <v>723</v>
       </c>
       <c r="N339" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O339" s="50">
         <v>0</v>
       </c>
-      <c r="P339" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P339" s="50"/>
       <c r="Q339" s="50">
         <v>0</v>
       </c>
@@ -29703,13 +29706,13 @@
         <v>58</v>
       </c>
       <c r="C340" s="50">
-        <v>330063</v>
+        <v>84980</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>757</v>
+        <v>724</v>
       </c>
       <c r="E340" s="50">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="F340" s="50">
         <v>0</v>
@@ -29718,7 +29721,7 @@
         <v>60</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29727,23 +29730,21 @@
         <v>62</v>
       </c>
       <c r="K340" s="50" t="s">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="L340" s="50" t="s">
-        <v>61</v>
+        <v>726</v>
       </c>
       <c r="M340" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N340" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O340" s="50">
         <v>0</v>
       </c>
-      <c r="P340" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P340" s="50"/>
       <c r="Q340" s="50">
         <v>0</v>
       </c>
@@ -29786,22 +29787,22 @@
         <v>58</v>
       </c>
       <c r="C341" s="50">
-        <v>330064</v>
+        <v>84981</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>759</v>
+        <v>727</v>
       </c>
       <c r="E341" s="50">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F341" s="50">
         <v>0</v>
       </c>
       <c r="G341" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>760</v>
+        <v>728</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29810,23 +29811,21 @@
         <v>62</v>
       </c>
       <c r="K341" s="50" t="s">
-        <v>180</v>
+        <v>331</v>
       </c>
       <c r="L341" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M341" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N341" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O341" s="50">
         <v>0</v>
       </c>
-      <c r="P341" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P341" s="50"/>
       <c r="Q341" s="50">
         <v>0</v>
       </c>
@@ -29869,40 +29868,37 @@
         <v>58</v>
       </c>
       <c r="C342" s="50">
-        <v>330065</v>
+        <v>84982</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>761</v>
+        <v>729</v>
       </c>
       <c r="E342" s="50">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F342" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G342" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H342" s="50" t="s">
-        <v>762</v>
-      </c>
       <c r="I342" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J342" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K342" s="50" t="s">
-        <v>297</v>
+        <v>730</v>
       </c>
       <c r="L342" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M342" s="50" t="s">
-        <v>1</v>
+        <v>731</v>
       </c>
       <c r="N342" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O342" s="50">
         <v>0</v>
@@ -29919,8 +29915,8 @@
       <c r="S342" s="50">
         <v>0</v>
       </c>
-      <c r="T342" s="50" t="s">
-        <v>61</v>
+      <c r="T342" s="50">
+        <v>0</v>
       </c>
       <c r="U342" s="50">
         <v>0</v>
@@ -29952,22 +29948,22 @@
         <v>58</v>
       </c>
       <c r="C343" s="50">
-        <v>330067</v>
+        <v>84983</v>
       </c>
       <c r="D343" s="50" t="s">
-        <v>763</v>
+        <v>729</v>
       </c>
       <c r="E343" s="50">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F343" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G343" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H343" s="50" t="s">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="I343" s="50" t="s">
         <v>78</v>
@@ -29976,7 +29972,7 @@
         <v>62</v>
       </c>
       <c r="K343" s="50" t="s">
-        <v>230</v>
+        <v>733</v>
       </c>
       <c r="L343" s="50" t="s">
         <v>1</v>
@@ -29985,7 +29981,7 @@
         <v>1</v>
       </c>
       <c r="N343" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O343" s="50">
         <v>0</v>
@@ -30035,22 +30031,22 @@
         <v>58</v>
       </c>
       <c r="C344" s="50">
-        <v>330068</v>
+        <v>84984</v>
       </c>
       <c r="D344" s="50" t="s">
-        <v>765</v>
+        <v>734</v>
       </c>
       <c r="E344" s="50">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F344" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G344" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H344" s="50" t="s">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="I344" s="50" t="s">
         <v>78</v>
@@ -30059,7 +30055,7 @@
         <v>62</v>
       </c>
       <c r="K344" s="50" t="s">
-        <v>96</v>
+        <v>736</v>
       </c>
       <c r="L344" s="50" t="s">
         <v>1</v>
@@ -30068,7 +30064,7 @@
         <v>1</v>
       </c>
       <c r="N344" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O344" s="50">
         <v>0</v>
@@ -30085,8 +30081,8 @@
       <c r="S344" s="50">
         <v>0</v>
       </c>
-      <c r="T344" s="50" t="s">
-        <v>61</v>
+      <c r="T344" s="50">
+        <v>0</v>
       </c>
       <c r="U344" s="50">
         <v>0</v>
@@ -30118,13 +30114,13 @@
         <v>58</v>
       </c>
       <c r="C345" s="50">
-        <v>330069</v>
+        <v>330037</v>
       </c>
       <c r="D345" s="50" t="s">
-        <v>767</v>
+        <v>737</v>
       </c>
       <c r="E345" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F345" s="50">
         <v>1</v>
@@ -30133,7 +30129,7 @@
         <v>60</v>
       </c>
       <c r="H345" s="50" t="s">
-        <v>768</v>
+        <v>738</v>
       </c>
       <c r="I345" s="50" t="s">
         <v>78</v>
@@ -30142,10 +30138,10 @@
         <v>62</v>
       </c>
       <c r="K345" s="50" t="s">
-        <v>257</v>
+        <v>96</v>
       </c>
       <c r="L345" s="50" t="s">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="M345" s="50" t="s">
         <v>1</v>
@@ -30156,7 +30152,9 @@
       <c r="O345" s="50">
         <v>0</v>
       </c>
-      <c r="P345" s="50"/>
+      <c r="P345" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q345" s="50">
         <v>0</v>
       </c>
@@ -30166,8 +30164,8 @@
       <c r="S345" s="50">
         <v>0</v>
       </c>
-      <c r="T345" s="50">
-        <v>0</v>
+      <c r="T345" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U345" s="50">
         <v>0</v>
@@ -30199,22 +30197,22 @@
         <v>58</v>
       </c>
       <c r="C346" s="50">
-        <v>330070</v>
+        <v>330038</v>
       </c>
       <c r="D346" s="50" t="s">
-        <v>770</v>
+        <v>739</v>
       </c>
       <c r="E346" s="50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F346" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H346" s="50" t="s">
-        <v>771</v>
+        <v>740</v>
       </c>
       <c r="I346" s="50" t="s">
         <v>78</v>
@@ -30223,13 +30221,13 @@
         <v>62</v>
       </c>
       <c r="K346" s="50" t="s">
-        <v>254</v>
+        <v>142</v>
       </c>
       <c r="L346" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M346" s="50" t="s">
-        <v>1</v>
+        <v>741</v>
       </c>
       <c r="N346" s="50">
         <v>33</v>
@@ -30269,6 +30267,2306 @@
         <v>0</v>
       </c>
       <c r="AA346" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="50">
+        <v>342</v>
+      </c>
+      <c r="B347" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C347" s="50">
+        <v>330039</v>
+      </c>
+      <c r="D347" s="50" t="s">
+        <v>742</v>
+      </c>
+      <c r="E347" s="50">
+        <v>7</v>
+      </c>
+      <c r="F347" s="50">
+        <v>0</v>
+      </c>
+      <c r="G347" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H347" s="50" t="s">
+        <v>743</v>
+      </c>
+      <c r="I347" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J347" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K347" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L347" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="M347" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N347" s="50">
+        <v>33</v>
+      </c>
+      <c r="O347" s="50">
+        <v>0</v>
+      </c>
+      <c r="P347" s="50"/>
+      <c r="Q347" s="50">
+        <v>0</v>
+      </c>
+      <c r="R347" s="50">
+        <v>0</v>
+      </c>
+      <c r="S347" s="50">
+        <v>0</v>
+      </c>
+      <c r="T347" s="50">
+        <v>0</v>
+      </c>
+      <c r="U347" s="50">
+        <v>0</v>
+      </c>
+      <c r="V347" s="50">
+        <v>0</v>
+      </c>
+      <c r="W347" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X347" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y347" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z347" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA347" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="50">
+        <v>343</v>
+      </c>
+      <c r="B348" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C348" s="50">
+        <v>330040</v>
+      </c>
+      <c r="D348" s="50" t="s">
+        <v>745</v>
+      </c>
+      <c r="E348" s="50">
+        <v>7</v>
+      </c>
+      <c r="F348" s="50">
+        <v>0</v>
+      </c>
+      <c r="G348" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H348" s="50" t="s">
+        <v>746</v>
+      </c>
+      <c r="I348" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J348" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K348" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L348" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="M348" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N348" s="50">
+        <v>33</v>
+      </c>
+      <c r="O348" s="50">
+        <v>0</v>
+      </c>
+      <c r="P348" s="50"/>
+      <c r="Q348" s="50">
+        <v>0</v>
+      </c>
+      <c r="R348" s="50">
+        <v>0</v>
+      </c>
+      <c r="S348" s="50">
+        <v>0</v>
+      </c>
+      <c r="T348" s="50">
+        <v>0</v>
+      </c>
+      <c r="U348" s="50">
+        <v>0</v>
+      </c>
+      <c r="V348" s="50">
+        <v>0</v>
+      </c>
+      <c r="W348" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X348" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y348" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z348" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA348" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="50">
+        <v>344</v>
+      </c>
+      <c r="B349" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C349" s="50">
+        <v>330041</v>
+      </c>
+      <c r="D349" s="50" t="s">
+        <v>747</v>
+      </c>
+      <c r="E349" s="50">
+        <v>7</v>
+      </c>
+      <c r="F349" s="50">
+        <v>0</v>
+      </c>
+      <c r="G349" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H349" s="50" t="s">
+        <v>748</v>
+      </c>
+      <c r="I349" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J349" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K349" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L349" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="M349" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N349" s="50">
+        <v>33</v>
+      </c>
+      <c r="O349" s="50">
+        <v>0</v>
+      </c>
+      <c r="P349" s="50"/>
+      <c r="Q349" s="50">
+        <v>0</v>
+      </c>
+      <c r="R349" s="50">
+        <v>0</v>
+      </c>
+      <c r="S349" s="50">
+        <v>0</v>
+      </c>
+      <c r="T349" s="50">
+        <v>0</v>
+      </c>
+      <c r="U349" s="50">
+        <v>0</v>
+      </c>
+      <c r="V349" s="50">
+        <v>0</v>
+      </c>
+      <c r="W349" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X349" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y349" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z349" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA349" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="50">
+        <v>345</v>
+      </c>
+      <c r="B350" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C350" s="50">
+        <v>330042</v>
+      </c>
+      <c r="D350" s="50" t="s">
+        <v>749</v>
+      </c>
+      <c r="E350" s="50">
+        <v>20</v>
+      </c>
+      <c r="F350" s="50">
+        <v>1</v>
+      </c>
+      <c r="G350" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H350" s="50" t="s">
+        <v>750</v>
+      </c>
+      <c r="I350" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J350" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K350" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="L350" s="50" t="s">
+        <v>751</v>
+      </c>
+      <c r="M350" s="50" t="s">
+        <v>752</v>
+      </c>
+      <c r="N350" s="50">
+        <v>33</v>
+      </c>
+      <c r="O350" s="50">
+        <v>0</v>
+      </c>
+      <c r="P350" s="50"/>
+      <c r="Q350" s="50">
+        <v>0</v>
+      </c>
+      <c r="R350" s="50">
+        <v>0</v>
+      </c>
+      <c r="S350" s="50">
+        <v>0</v>
+      </c>
+      <c r="T350" s="50">
+        <v>0</v>
+      </c>
+      <c r="U350" s="50">
+        <v>0</v>
+      </c>
+      <c r="V350" s="50">
+        <v>0</v>
+      </c>
+      <c r="W350" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X350" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y350" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z350" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA350" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="50">
+        <v>346</v>
+      </c>
+      <c r="B351" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C351" s="50">
+        <v>330043</v>
+      </c>
+      <c r="D351" s="50" t="s">
+        <v>753</v>
+      </c>
+      <c r="E351" s="50">
+        <v>19</v>
+      </c>
+      <c r="F351" s="50">
+        <v>1</v>
+      </c>
+      <c r="G351" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H351" s="50" t="s">
+        <v>754</v>
+      </c>
+      <c r="I351" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J351" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K351" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="L351" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M351" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N351" s="50">
+        <v>33</v>
+      </c>
+      <c r="O351" s="50">
+        <v>0</v>
+      </c>
+      <c r="P351" s="50"/>
+      <c r="Q351" s="50">
+        <v>0</v>
+      </c>
+      <c r="R351" s="50">
+        <v>0</v>
+      </c>
+      <c r="S351" s="50">
+        <v>0</v>
+      </c>
+      <c r="T351" s="50">
+        <v>0</v>
+      </c>
+      <c r="U351" s="50">
+        <v>0</v>
+      </c>
+      <c r="V351" s="50">
+        <v>0</v>
+      </c>
+      <c r="W351" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X351" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y351" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z351" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA351" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="50">
+        <v>347</v>
+      </c>
+      <c r="B352" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C352" s="50">
+        <v>330044</v>
+      </c>
+      <c r="D352" s="50" t="s">
+        <v>755</v>
+      </c>
+      <c r="E352" s="50">
+        <v>16</v>
+      </c>
+      <c r="F352" s="50">
+        <v>9</v>
+      </c>
+      <c r="G352" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H352" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="I352" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J352" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K352" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="L352" s="50" t="s">
+        <v>757</v>
+      </c>
+      <c r="M352" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N352" s="50">
+        <v>33</v>
+      </c>
+      <c r="O352" s="50">
+        <v>0</v>
+      </c>
+      <c r="P352" s="50"/>
+      <c r="Q352" s="50">
+        <v>0</v>
+      </c>
+      <c r="R352" s="50">
+        <v>0</v>
+      </c>
+      <c r="S352" s="50">
+        <v>0</v>
+      </c>
+      <c r="T352" s="50">
+        <v>0</v>
+      </c>
+      <c r="U352" s="50">
+        <v>0</v>
+      </c>
+      <c r="V352" s="50">
+        <v>0</v>
+      </c>
+      <c r="W352" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X352" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y352" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z352" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA352" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="50">
+        <v>348</v>
+      </c>
+      <c r="B353" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C353" s="50">
+        <v>330045</v>
+      </c>
+      <c r="D353" s="50" t="s">
+        <v>758</v>
+      </c>
+      <c r="E353" s="50">
+        <v>5</v>
+      </c>
+      <c r="F353" s="50">
+        <v>1</v>
+      </c>
+      <c r="G353" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H353" s="50" t="s">
+        <v>759</v>
+      </c>
+      <c r="I353" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J353" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K353" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N353" s="50">
+        <v>33</v>
+      </c>
+      <c r="O353" s="50">
+        <v>0</v>
+      </c>
+      <c r="P353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q353" s="50">
+        <v>0</v>
+      </c>
+      <c r="R353" s="50">
+        <v>0</v>
+      </c>
+      <c r="S353" s="50">
+        <v>0</v>
+      </c>
+      <c r="T353" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U353" s="50">
+        <v>0</v>
+      </c>
+      <c r="V353" s="50">
+        <v>0</v>
+      </c>
+      <c r="W353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y353" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z353" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA353" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="50">
+        <v>349</v>
+      </c>
+      <c r="B354" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C354" s="50">
+        <v>330046</v>
+      </c>
+      <c r="D354" s="50" t="s">
+        <v>760</v>
+      </c>
+      <c r="E354" s="50">
+        <v>16</v>
+      </c>
+      <c r="F354" s="50">
+        <v>6</v>
+      </c>
+      <c r="G354" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H354" s="50" t="s">
+        <v>761</v>
+      </c>
+      <c r="I354" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J354" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K354" s="50" t="s">
+        <v>461</v>
+      </c>
+      <c r="L354" s="50" t="s">
+        <v>762</v>
+      </c>
+      <c r="M354" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N354" s="50">
+        <v>33</v>
+      </c>
+      <c r="O354" s="50">
+        <v>0</v>
+      </c>
+      <c r="P354" s="50"/>
+      <c r="Q354" s="50">
+        <v>0</v>
+      </c>
+      <c r="R354" s="50">
+        <v>0</v>
+      </c>
+      <c r="S354" s="50">
+        <v>0</v>
+      </c>
+      <c r="T354" s="50">
+        <v>0</v>
+      </c>
+      <c r="U354" s="50">
+        <v>0</v>
+      </c>
+      <c r="V354" s="50">
+        <v>0</v>
+      </c>
+      <c r="W354" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X354" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y354" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z354" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA354" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="50">
+        <v>350</v>
+      </c>
+      <c r="B355" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C355" s="50">
+        <v>330047</v>
+      </c>
+      <c r="D355" s="50" t="s">
+        <v>763</v>
+      </c>
+      <c r="E355" s="50">
+        <v>3</v>
+      </c>
+      <c r="F355" s="50">
+        <v>6</v>
+      </c>
+      <c r="G355" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H355" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="I355" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J355" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K355" s="50" t="s">
+        <v>465</v>
+      </c>
+      <c r="L355" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M355" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N355" s="50">
+        <v>33</v>
+      </c>
+      <c r="O355" s="50">
+        <v>0</v>
+      </c>
+      <c r="P355" s="50"/>
+      <c r="Q355" s="50">
+        <v>0</v>
+      </c>
+      <c r="R355" s="50">
+        <v>0</v>
+      </c>
+      <c r="S355" s="50">
+        <v>0</v>
+      </c>
+      <c r="T355" s="50">
+        <v>0</v>
+      </c>
+      <c r="U355" s="50">
+        <v>0</v>
+      </c>
+      <c r="V355" s="50">
+        <v>0</v>
+      </c>
+      <c r="W355" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X355" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y355" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z355" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA355" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="50">
+        <v>351</v>
+      </c>
+      <c r="B356" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C356" s="50">
+        <v>330048</v>
+      </c>
+      <c r="D356" s="50" t="s">
+        <v>765</v>
+      </c>
+      <c r="E356" s="50">
+        <v>5</v>
+      </c>
+      <c r="F356" s="50">
+        <v>1</v>
+      </c>
+      <c r="G356" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H356" s="50" t="s">
+        <v>766</v>
+      </c>
+      <c r="I356" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J356" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K356" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N356" s="50">
+        <v>33</v>
+      </c>
+      <c r="O356" s="50">
+        <v>0</v>
+      </c>
+      <c r="P356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q356" s="50">
+        <v>0</v>
+      </c>
+      <c r="R356" s="50">
+        <v>0</v>
+      </c>
+      <c r="S356" s="50">
+        <v>0</v>
+      </c>
+      <c r="T356" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U356" s="50">
+        <v>0</v>
+      </c>
+      <c r="V356" s="50">
+        <v>0</v>
+      </c>
+      <c r="W356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y356" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z356" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA356" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="50">
+        <v>352</v>
+      </c>
+      <c r="B357" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C357" s="50">
+        <v>330049</v>
+      </c>
+      <c r="D357" s="50" t="s">
+        <v>767</v>
+      </c>
+      <c r="E357" s="50">
+        <v>43</v>
+      </c>
+      <c r="F357" s="50">
+        <v>0</v>
+      </c>
+      <c r="G357" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H357" s="50" t="s">
+        <v>768</v>
+      </c>
+      <c r="I357" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J357" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K357" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="L357" s="50" t="s">
+        <v>769</v>
+      </c>
+      <c r="M357" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N357" s="50">
+        <v>33</v>
+      </c>
+      <c r="O357" s="50">
+        <v>0</v>
+      </c>
+      <c r="P357" s="50"/>
+      <c r="Q357" s="50">
+        <v>0</v>
+      </c>
+      <c r="R357" s="50">
+        <v>0</v>
+      </c>
+      <c r="S357" s="50">
+        <v>0</v>
+      </c>
+      <c r="T357" s="50">
+        <v>0</v>
+      </c>
+      <c r="U357" s="50">
+        <v>0</v>
+      </c>
+      <c r="V357" s="50">
+        <v>0</v>
+      </c>
+      <c r="W357" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X357" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y357" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z357" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA357" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="50">
+        <v>353</v>
+      </c>
+      <c r="B358" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C358" s="50">
+        <v>330050</v>
+      </c>
+      <c r="D358" s="50" t="s">
+        <v>770</v>
+      </c>
+      <c r="E358" s="50">
+        <v>44</v>
+      </c>
+      <c r="F358" s="50">
+        <v>0</v>
+      </c>
+      <c r="G358" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H358" s="50" t="s">
+        <v>771</v>
+      </c>
+      <c r="I358" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J358" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K358" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="L358" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M358" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N358" s="50">
+        <v>33</v>
+      </c>
+      <c r="O358" s="50">
+        <v>0</v>
+      </c>
+      <c r="P358" s="50"/>
+      <c r="Q358" s="50">
+        <v>0</v>
+      </c>
+      <c r="R358" s="50">
+        <v>0</v>
+      </c>
+      <c r="S358" s="50">
+        <v>0</v>
+      </c>
+      <c r="T358" s="50">
+        <v>0</v>
+      </c>
+      <c r="U358" s="50">
+        <v>0</v>
+      </c>
+      <c r="V358" s="50">
+        <v>0</v>
+      </c>
+      <c r="W358" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X358" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y358" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z358" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA358" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="50">
+        <v>354</v>
+      </c>
+      <c r="B359" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C359" s="50">
+        <v>330051</v>
+      </c>
+      <c r="D359" s="50" t="s">
+        <v>772</v>
+      </c>
+      <c r="E359" s="50">
+        <v>4</v>
+      </c>
+      <c r="F359" s="50">
+        <v>1</v>
+      </c>
+      <c r="G359" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H359" s="50" t="s">
+        <v>773</v>
+      </c>
+      <c r="I359" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J359" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K359" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N359" s="50">
+        <v>33</v>
+      </c>
+      <c r="O359" s="50">
+        <v>0</v>
+      </c>
+      <c r="P359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q359" s="50">
+        <v>0</v>
+      </c>
+      <c r="R359" s="50">
+        <v>0</v>
+      </c>
+      <c r="S359" s="50">
+        <v>0</v>
+      </c>
+      <c r="T359" s="50">
+        <v>0</v>
+      </c>
+      <c r="U359" s="50">
+        <v>0</v>
+      </c>
+      <c r="V359" s="50">
+        <v>0</v>
+      </c>
+      <c r="W359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y359" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z359" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA359" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="50">
+        <v>355</v>
+      </c>
+      <c r="B360" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C360" s="50">
+        <v>330052</v>
+      </c>
+      <c r="D360" s="50" t="s">
+        <v>774</v>
+      </c>
+      <c r="E360" s="50">
+        <v>4</v>
+      </c>
+      <c r="F360" s="50">
+        <v>2</v>
+      </c>
+      <c r="G360" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H360" s="50" t="s">
+        <v>775</v>
+      </c>
+      <c r="I360" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J360" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K360" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="L360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N360" s="50">
+        <v>33</v>
+      </c>
+      <c r="O360" s="50">
+        <v>0</v>
+      </c>
+      <c r="P360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q360" s="50">
+        <v>0</v>
+      </c>
+      <c r="R360" s="50">
+        <v>0</v>
+      </c>
+      <c r="S360" s="50">
+        <v>0</v>
+      </c>
+      <c r="T360" s="50">
+        <v>0</v>
+      </c>
+      <c r="U360" s="50">
+        <v>0</v>
+      </c>
+      <c r="V360" s="50">
+        <v>0</v>
+      </c>
+      <c r="W360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y360" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z360" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA360" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="50">
+        <v>356</v>
+      </c>
+      <c r="B361" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C361" s="50">
+        <v>330053</v>
+      </c>
+      <c r="D361" s="50" t="s">
+        <v>776</v>
+      </c>
+      <c r="E361" s="50">
+        <v>4</v>
+      </c>
+      <c r="F361" s="50">
+        <v>3</v>
+      </c>
+      <c r="G361" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H361" s="50" t="s">
+        <v>777</v>
+      </c>
+      <c r="I361" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J361" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K361" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="L361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N361" s="50">
+        <v>33</v>
+      </c>
+      <c r="O361" s="50">
+        <v>0</v>
+      </c>
+      <c r="P361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q361" s="50">
+        <v>0</v>
+      </c>
+      <c r="R361" s="50">
+        <v>0</v>
+      </c>
+      <c r="S361" s="50">
+        <v>0</v>
+      </c>
+      <c r="T361" s="50">
+        <v>0</v>
+      </c>
+      <c r="U361" s="50">
+        <v>0</v>
+      </c>
+      <c r="V361" s="50">
+        <v>0</v>
+      </c>
+      <c r="W361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y361" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z361" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA361" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="50">
+        <v>357</v>
+      </c>
+      <c r="B362" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C362" s="50">
+        <v>330054</v>
+      </c>
+      <c r="D362" s="50" t="s">
+        <v>778</v>
+      </c>
+      <c r="E362" s="50">
+        <v>5</v>
+      </c>
+      <c r="F362" s="50">
+        <v>1</v>
+      </c>
+      <c r="G362" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H362" s="50" t="s">
+        <v>779</v>
+      </c>
+      <c r="I362" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J362" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K362" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N362" s="50">
+        <v>33</v>
+      </c>
+      <c r="O362" s="50">
+        <v>0</v>
+      </c>
+      <c r="P362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q362" s="50">
+        <v>0</v>
+      </c>
+      <c r="R362" s="50">
+        <v>0</v>
+      </c>
+      <c r="S362" s="50">
+        <v>0</v>
+      </c>
+      <c r="T362" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U362" s="50">
+        <v>0</v>
+      </c>
+      <c r="V362" s="50">
+        <v>0</v>
+      </c>
+      <c r="W362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y362" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z362" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA362" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="50">
+        <v>358</v>
+      </c>
+      <c r="B363" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C363" s="50">
+        <v>330055</v>
+      </c>
+      <c r="D363" s="50" t="s">
+        <v>780</v>
+      </c>
+      <c r="E363" s="50">
+        <v>4</v>
+      </c>
+      <c r="F363" s="50">
+        <v>1</v>
+      </c>
+      <c r="G363" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H363" s="50" t="s">
+        <v>781</v>
+      </c>
+      <c r="I363" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J363" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K363" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N363" s="50">
+        <v>33</v>
+      </c>
+      <c r="O363" s="50">
+        <v>0</v>
+      </c>
+      <c r="P363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q363" s="50">
+        <v>0</v>
+      </c>
+      <c r="R363" s="50">
+        <v>0</v>
+      </c>
+      <c r="S363" s="50">
+        <v>0</v>
+      </c>
+      <c r="T363" s="50">
+        <v>0</v>
+      </c>
+      <c r="U363" s="50">
+        <v>0</v>
+      </c>
+      <c r="V363" s="50">
+        <v>0</v>
+      </c>
+      <c r="W363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y363" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z363" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA363" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="50">
+        <v>359</v>
+      </c>
+      <c r="B364" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C364" s="50">
+        <v>330056</v>
+      </c>
+      <c r="D364" s="50" t="s">
+        <v>782</v>
+      </c>
+      <c r="E364" s="50">
+        <v>54</v>
+      </c>
+      <c r="F364" s="50">
+        <v>0</v>
+      </c>
+      <c r="G364" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H364" s="50" t="s">
+        <v>783</v>
+      </c>
+      <c r="I364" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J364" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K364" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="L364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N364" s="50">
+        <v>33</v>
+      </c>
+      <c r="O364" s="50">
+        <v>0</v>
+      </c>
+      <c r="P364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q364" s="50">
+        <v>0</v>
+      </c>
+      <c r="R364" s="50">
+        <v>0</v>
+      </c>
+      <c r="S364" s="50">
+        <v>0</v>
+      </c>
+      <c r="T364" s="50">
+        <v>0</v>
+      </c>
+      <c r="U364" s="50">
+        <v>0</v>
+      </c>
+      <c r="V364" s="50">
+        <v>0</v>
+      </c>
+      <c r="W364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y364" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z364" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA364" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="50">
+        <v>360</v>
+      </c>
+      <c r="B365" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C365" s="50">
+        <v>330058</v>
+      </c>
+      <c r="D365" s="50" t="s">
+        <v>784</v>
+      </c>
+      <c r="E365" s="50">
+        <v>5</v>
+      </c>
+      <c r="F365" s="50">
+        <v>1</v>
+      </c>
+      <c r="G365" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H365" s="50" t="s">
+        <v>785</v>
+      </c>
+      <c r="I365" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J365" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K365" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N365" s="50">
+        <v>33</v>
+      </c>
+      <c r="O365" s="50">
+        <v>0</v>
+      </c>
+      <c r="P365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q365" s="50">
+        <v>0</v>
+      </c>
+      <c r="R365" s="50">
+        <v>0</v>
+      </c>
+      <c r="S365" s="50">
+        <v>0</v>
+      </c>
+      <c r="T365" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U365" s="50">
+        <v>0</v>
+      </c>
+      <c r="V365" s="50">
+        <v>0</v>
+      </c>
+      <c r="W365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y365" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z365" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA365" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="50">
+        <v>361</v>
+      </c>
+      <c r="B366" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C366" s="50">
+        <v>330061</v>
+      </c>
+      <c r="D366" s="50" t="s">
+        <v>786</v>
+      </c>
+      <c r="E366" s="50">
+        <v>39</v>
+      </c>
+      <c r="F366" s="50">
+        <v>0</v>
+      </c>
+      <c r="G366" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H366" s="50" t="s">
+        <v>787</v>
+      </c>
+      <c r="I366" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J366" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K366" s="50" t="s">
+        <v>788</v>
+      </c>
+      <c r="L366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N366" s="50">
+        <v>33</v>
+      </c>
+      <c r="O366" s="50">
+        <v>0</v>
+      </c>
+      <c r="P366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q366" s="50">
+        <v>0</v>
+      </c>
+      <c r="R366" s="50">
+        <v>0</v>
+      </c>
+      <c r="S366" s="50">
+        <v>0</v>
+      </c>
+      <c r="T366" s="50">
+        <v>0</v>
+      </c>
+      <c r="U366" s="50">
+        <v>0</v>
+      </c>
+      <c r="V366" s="50">
+        <v>0</v>
+      </c>
+      <c r="W366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y366" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z366" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA366" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="50">
+        <v>362</v>
+      </c>
+      <c r="B367" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C367" s="50">
+        <v>330062</v>
+      </c>
+      <c r="D367" s="50" t="s">
+        <v>789</v>
+      </c>
+      <c r="E367" s="50">
+        <v>40</v>
+      </c>
+      <c r="F367" s="50">
+        <v>0</v>
+      </c>
+      <c r="G367" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H367" s="50" t="s">
+        <v>790</v>
+      </c>
+      <c r="I367" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J367" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K367" s="50" t="s">
+        <v>791</v>
+      </c>
+      <c r="L367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N367" s="50">
+        <v>33</v>
+      </c>
+      <c r="O367" s="50">
+        <v>0</v>
+      </c>
+      <c r="P367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q367" s="50">
+        <v>0</v>
+      </c>
+      <c r="R367" s="50">
+        <v>0</v>
+      </c>
+      <c r="S367" s="50">
+        <v>0</v>
+      </c>
+      <c r="T367" s="50">
+        <v>0</v>
+      </c>
+      <c r="U367" s="50">
+        <v>0</v>
+      </c>
+      <c r="V367" s="50">
+        <v>0</v>
+      </c>
+      <c r="W367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y367" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z367" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA367" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="50">
+        <v>363</v>
+      </c>
+      <c r="B368" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C368" s="50">
+        <v>330063</v>
+      </c>
+      <c r="D368" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="E368" s="50">
+        <v>28</v>
+      </c>
+      <c r="F368" s="50">
+        <v>0</v>
+      </c>
+      <c r="G368" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H368" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="I368" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J368" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K368" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="L368" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M368" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N368" s="50">
+        <v>33</v>
+      </c>
+      <c r="O368" s="50">
+        <v>0</v>
+      </c>
+      <c r="P368" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q368" s="50">
+        <v>0</v>
+      </c>
+      <c r="R368" s="50">
+        <v>0</v>
+      </c>
+      <c r="S368" s="50">
+        <v>0</v>
+      </c>
+      <c r="T368" s="50">
+        <v>0</v>
+      </c>
+      <c r="U368" s="50">
+        <v>0</v>
+      </c>
+      <c r="V368" s="50">
+        <v>0</v>
+      </c>
+      <c r="W368" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X368" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y368" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z368" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA368" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="50">
+        <v>364</v>
+      </c>
+      <c r="B369" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C369" s="50">
+        <v>330064</v>
+      </c>
+      <c r="D369" s="50" t="s">
+        <v>794</v>
+      </c>
+      <c r="E369" s="50">
+        <v>29</v>
+      </c>
+      <c r="F369" s="50">
+        <v>0</v>
+      </c>
+      <c r="G369" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H369" s="50" t="s">
+        <v>795</v>
+      </c>
+      <c r="I369" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J369" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K369" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="L369" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M369" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N369" s="50">
+        <v>33</v>
+      </c>
+      <c r="O369" s="50">
+        <v>0</v>
+      </c>
+      <c r="P369" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q369" s="50">
+        <v>0</v>
+      </c>
+      <c r="R369" s="50">
+        <v>0</v>
+      </c>
+      <c r="S369" s="50">
+        <v>0</v>
+      </c>
+      <c r="T369" s="50">
+        <v>0</v>
+      </c>
+      <c r="U369" s="50">
+        <v>0</v>
+      </c>
+      <c r="V369" s="50">
+        <v>0</v>
+      </c>
+      <c r="W369" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X369" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y369" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z369" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA369" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="50">
+        <v>365</v>
+      </c>
+      <c r="B370" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C370" s="50">
+        <v>330065</v>
+      </c>
+      <c r="D370" s="50" t="s">
+        <v>796</v>
+      </c>
+      <c r="E370" s="50">
+        <v>5</v>
+      </c>
+      <c r="F370" s="50">
+        <v>2</v>
+      </c>
+      <c r="G370" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H370" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="I370" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J370" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K370" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="L370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N370" s="50">
+        <v>33</v>
+      </c>
+      <c r="O370" s="50">
+        <v>0</v>
+      </c>
+      <c r="P370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q370" s="50">
+        <v>0</v>
+      </c>
+      <c r="R370" s="50">
+        <v>0</v>
+      </c>
+      <c r="S370" s="50">
+        <v>0</v>
+      </c>
+      <c r="T370" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U370" s="50">
+        <v>0</v>
+      </c>
+      <c r="V370" s="50">
+        <v>0</v>
+      </c>
+      <c r="W370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y370" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z370" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA370" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="50">
+        <v>366</v>
+      </c>
+      <c r="B371" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C371" s="50">
+        <v>330067</v>
+      </c>
+      <c r="D371" s="50" t="s">
+        <v>798</v>
+      </c>
+      <c r="E371" s="50">
+        <v>4</v>
+      </c>
+      <c r="F371" s="50">
+        <v>1</v>
+      </c>
+      <c r="G371" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H371" s="50" t="s">
+        <v>799</v>
+      </c>
+      <c r="I371" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J371" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K371" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N371" s="50">
+        <v>33</v>
+      </c>
+      <c r="O371" s="50">
+        <v>0</v>
+      </c>
+      <c r="P371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q371" s="50">
+        <v>0</v>
+      </c>
+      <c r="R371" s="50">
+        <v>0</v>
+      </c>
+      <c r="S371" s="50">
+        <v>0</v>
+      </c>
+      <c r="T371" s="50">
+        <v>0</v>
+      </c>
+      <c r="U371" s="50">
+        <v>0</v>
+      </c>
+      <c r="V371" s="50">
+        <v>0</v>
+      </c>
+      <c r="W371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y371" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z371" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA371" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="50">
+        <v>367</v>
+      </c>
+      <c r="B372" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C372" s="50">
+        <v>330068</v>
+      </c>
+      <c r="D372" s="50" t="s">
+        <v>800</v>
+      </c>
+      <c r="E372" s="50">
+        <v>5</v>
+      </c>
+      <c r="F372" s="50">
+        <v>1</v>
+      </c>
+      <c r="G372" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H372" s="50" t="s">
+        <v>801</v>
+      </c>
+      <c r="I372" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J372" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K372" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N372" s="50">
+        <v>33</v>
+      </c>
+      <c r="O372" s="50">
+        <v>0</v>
+      </c>
+      <c r="P372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q372" s="50">
+        <v>0</v>
+      </c>
+      <c r="R372" s="50">
+        <v>0</v>
+      </c>
+      <c r="S372" s="50">
+        <v>0</v>
+      </c>
+      <c r="T372" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U372" s="50">
+        <v>0</v>
+      </c>
+      <c r="V372" s="50">
+        <v>0</v>
+      </c>
+      <c r="W372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y372" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z372" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA372" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="50">
+        <v>368</v>
+      </c>
+      <c r="B373" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C373" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D373" s="50" t="s">
+        <v>802</v>
+      </c>
+      <c r="E373" s="50">
+        <v>16</v>
+      </c>
+      <c r="F373" s="50">
+        <v>1</v>
+      </c>
+      <c r="G373" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H373" s="50" t="s">
+        <v>803</v>
+      </c>
+      <c r="I373" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J373" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K373" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L373" s="50" t="s">
+        <v>804</v>
+      </c>
+      <c r="M373" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N373" s="50">
+        <v>33</v>
+      </c>
+      <c r="O373" s="50">
+        <v>0</v>
+      </c>
+      <c r="P373" s="50"/>
+      <c r="Q373" s="50">
+        <v>0</v>
+      </c>
+      <c r="R373" s="50">
+        <v>0</v>
+      </c>
+      <c r="S373" s="50">
+        <v>0</v>
+      </c>
+      <c r="T373" s="50">
+        <v>0</v>
+      </c>
+      <c r="U373" s="50">
+        <v>0</v>
+      </c>
+      <c r="V373" s="50">
+        <v>0</v>
+      </c>
+      <c r="W373" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X373" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y373" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z373" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA373" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="50">
+        <v>369</v>
+      </c>
+      <c r="B374" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C374" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D374" s="50" t="s">
+        <v>805</v>
+      </c>
+      <c r="E374" s="50">
+        <v>3</v>
+      </c>
+      <c r="F374" s="50">
+        <v>1</v>
+      </c>
+      <c r="G374" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H374" s="50" t="s">
+        <v>806</v>
+      </c>
+      <c r="I374" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J374" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K374" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L374" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M374" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N374" s="50">
+        <v>33</v>
+      </c>
+      <c r="O374" s="50">
+        <v>0</v>
+      </c>
+      <c r="P374" s="50"/>
+      <c r="Q374" s="50">
+        <v>0</v>
+      </c>
+      <c r="R374" s="50">
+        <v>0</v>
+      </c>
+      <c r="S374" s="50">
+        <v>0</v>
+      </c>
+      <c r="T374" s="50">
+        <v>0</v>
+      </c>
+      <c r="U374" s="50">
+        <v>0</v>
+      </c>
+      <c r="V374" s="50">
+        <v>0</v>
+      </c>
+      <c r="W374" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X374" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y374" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z374" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA374" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -1303,7 +1303,7 @@
     <t>132,8.001535,52</t>
   </si>
   <si>
-    <t>130.5,8.003199,50_133.5,8.003199,50_133.5,8.003199,54_130.5,8.003199,54</t>
+    <t>130.5,8.001535,50_133.5,8.001535,50_133.5,8.001535,54_130.5,8.001535,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1399,7 +1399,7 @@
     <t>67,9.038384,70</t>
   </si>
   <si>
-    <t>66,7.999978,72_66,7.999978,68_68,7.999978,68_68,7.999978,72</t>
+    <t>66,9.038384,72_66,9.038384,68_68,9.038384,68_68,9.038384,72</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1807,7 +1807,7 @@
     <t>115,8.001535,52</t>
   </si>
   <si>
-    <t>116,9.186258,50_116,9.186258,54_114,9.186258,54_114,9.186258,50</t>
+    <t>116,8.001535,50_116,8.001535,54_114,8.001535,54_114,8.001535,50</t>
   </si>
   <si>
     <t>75002</t>
@@ -1840,7 +1840,7 @@
     <t>70,7.999978,35</t>
   </si>
   <si>
-    <t>71.5,0,36.5_68.5,0,36.5_68.5,0,33.5_71.5,0,33.5</t>
+    <t>71.5,7.999978,36.5_68.5,7.999978,36.5_68.5,7.999978,33.5_71.5,7.999978,33.5</t>
   </si>
   <si>
     <t>66,7.999978,33</t>
@@ -1852,7 +1852,7 @@
     <t>74,7.999978,39</t>
   </si>
   <si>
-    <t>75.5,-0.04387474,40.5_72.5,-0.04387474,40.5_72.5,-0.04387474,37.5_75.5,-0.04387474,37.5</t>
+    <t>75.5,7.999978,40.5_72.5,7.999978,40.5_72.5,7.999978,37.5_75.5,7.999978,37.5</t>
   </si>
   <si>
     <t>72,7.999978,37</t>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -1303,7 +1303,7 @@
     <t>132,8.001535,52</t>
   </si>
   <si>
-    <t>130.5,8.001535,50_133.5,8.001535,50_133.5,8.001535,54_130.5,8.001535,54</t>
+    <t>130.5,8.001536,50_133.5,8.001536,50_133.5,8.001536,54_130.5,8.001536,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1315,7 +1315,7 @@
     <t>117,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>118,8.003199,72.85841_118,8.003199,74.85841_116,8.003199,74.85841_116,8.003199,72.85841</t>
+    <t>118,8.0032,72.85841_118,8.0032,74.85841_116,8.0032,74.85841_116,8.0032,72.85841</t>
   </si>
   <si>
     <t>74857</t>
@@ -1324,13 +1324,13 @@
     <t>119,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>120,8.003199,72.85841_120,8.003199,74.85841_118,8.003199,74.85841_118,8.003199,72.85841</t>
+    <t>120,8.0032,72.85841_120,8.0032,74.85841_118,8.0032,74.85841_118,8.0032,72.85841</t>
   </si>
   <si>
     <t>121,8.003199,73.8584136962891</t>
   </si>
   <si>
-    <t>122,8.003199,72.85841_122,8.003199,74.85841_120,8.003199,74.85841_120,8.003199,72.85841</t>
+    <t>122,8.0032,72.85841_122,8.0032,74.85841_120,8.0032,74.85841_120,8.0032,72.85841</t>
   </si>
   <si>
     <t>129.307510375977,7.999978,60.7048797607422</t>
@@ -1366,21 +1366,21 @@
     <t>74863</t>
   </si>
   <si>
+    <t>62,7.999978,96</t>
+  </si>
+  <si>
+    <t>63.5,7.999978,94_63.5,7.999978,98_60.5,7.999978,98_60.5,7.999978,94</t>
+  </si>
+  <si>
+    <t>87.1449661254883,6.485435,103.072158813477</t>
+  </si>
+  <si>
+    <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
+  </si>
+  <si>
     <t>70001_1</t>
   </si>
   <si>
-    <t>62,7.999978,96</t>
-  </si>
-  <si>
-    <t>63.5,7.999978,94_63.5,7.999978,98_60.5,7.999978,98_60.5,7.999978,94</t>
-  </si>
-  <si>
-    <t>87.1449661254883,6.485435,103.072158813477</t>
-  </si>
-  <si>
-    <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
-  </si>
-  <si>
     <t>62,7.999978,89</t>
   </si>
   <si>
@@ -1441,7 +1441,7 @@
     <t>109.408554077148,8.003199,114</t>
   </si>
   <si>
-    <t>114.4086,8.003199,116_107.4086,8.003199,116_107.4086,8.003199,112_114.4086,8.003199,112</t>
+    <t>114.4086,8.0032,116_107.4086,8.0032,116_107.4086,8.0032,112_114.4086,8.0032,112</t>
   </si>
   <si>
     <t>74875</t>
@@ -1462,7 +1462,7 @@
     <t>137,8.003199,133.983917236328</t>
   </si>
   <si>
-    <t>138.5,8.003199,131.4839_138.5,8.003199,136.4839_135.5,8.003199,136.4839_135.5,8.003199,131.4839</t>
+    <t>138.5,8.0032,131.4839_138.5,8.0032,136.4839_135.5,8.0032,136.4839_135.5,8.0032,131.4839</t>
   </si>
   <si>
     <t>74878</t>
@@ -1516,7 +1516,7 @@
     <t>112,8.003199,134</t>
   </si>
   <si>
-    <t>110.5,8.003199,136_110.5,8.003199,132_113.5,8.003199,132_113.5,8.003199,136</t>
+    <t>110.5,8.0032,136_110.5,8.0032,132_113.5,8.0032,132_113.5,8.0032,136</t>
   </si>
   <si>
     <t>0,74996</t>
@@ -1534,7 +1534,7 @@
     <t>127,8.003199,134</t>
   </si>
   <si>
-    <t>129.25,8.003199,131.75_129.25,8.003199,136.25_124.75,8.003199,136.25_124.75,8.003199,131.75</t>
+    <t>129.25,8.0032,131.75_129.25,8.0032,136.25_124.75,8.0032,136.25_124.75,8.0032,131.75</t>
   </si>
   <si>
     <t>142,7.999978,176</t>
@@ -1561,7 +1561,7 @@
     <t>122,8.003199,134</t>
   </si>
   <si>
-    <t>123,8.003199,135_121,8.003199,135_121,8.003199,133_123,8.003199,133</t>
+    <t>123,8.0032,135_121,8.0032,135_121,8.0032,133_123,8.0032,133</t>
   </si>
   <si>
     <t>119,10.00309,203</t>
@@ -1576,7 +1576,7 @@
     <t>112,8.003199,203</t>
   </si>
   <si>
-    <t>114,8.003199,206_110,8.003199,206_110,8.003199,200_114,8.003199,200</t>
+    <t>114,8.0032,206_110,8.0032,206_110,8.0032,200_114,8.0032,200</t>
   </si>
   <si>
     <t>74888</t>
@@ -1657,7 +1657,7 @@
     <t>117.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>118.1416,8.003199,273_118.1416,8.003199,275_116.1416,8.003199,275_116.1416,8.003199,273</t>
+    <t>118.1416,8.0032,273_118.1416,8.0032,275_116.1416,8.0032,275_116.1416,8.0032,273</t>
   </si>
   <si>
     <t>74897</t>
@@ -1666,13 +1666,13 @@
     <t>119.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>120.1416,8.003199,273_120.1416,8.003199,275_118.1416,8.003199,275_118.1416,8.003199,273</t>
+    <t>120.1416,8.0032,273_120.1416,8.0032,275_118.1416,8.0032,275_118.1416,8.0032,273</t>
   </si>
   <si>
     <t>121.141586303711,8.003199,274</t>
   </si>
   <si>
-    <t>122.1416,8.003199,273_122.1416,8.003199,275_120.1416,8.003199,275_120.1416,8.003199,273</t>
+    <t>122.1416,8.0032,273_122.1416,8.0032,275_120.1416,8.0032,275_120.1416,8.0032,273</t>
   </si>
   <si>
     <t>135,7.999978,274</t>
@@ -1807,7 +1807,7 @@
     <t>115,8.001535,52</t>
   </si>
   <si>
-    <t>116,8.001535,50_116,8.001535,54_114,8.001535,54_114,8.001535,50</t>
+    <t>116,8.001536,50_116,8.001536,54_114,8.001536,54_114,8.001536,50</t>
   </si>
   <si>
     <t>75002</t>
@@ -3529,7 +3529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA374"/>
+  <dimension ref="A1:AA375"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -18850,7 +18850,7 @@
         <v>1</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>449</v>
+        <v>1</v>
       </c>
       <c r="Y201" s="50" t="s">
         <v>1</v>
@@ -18873,7 +18873,7 @@
         <v>74866</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E202" s="50">
         <v>4</v>
@@ -18885,7 +18885,7 @@
         <v>138</v>
       </c>
       <c r="H202" s="50" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I202" s="50" t="s">
         <v>78</v>
@@ -18956,7 +18956,7 @@
         <v>74867</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E203" s="50">
         <v>2</v>
@@ -18983,7 +18983,7 @@
       </c>
       <c r="O203" s="50"/>
       <c r="P203" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q203" s="50"/>
       <c r="R203" s="50"/>
@@ -18992,7 +18992,7 @@
       <c r="U203" s="50"/>
       <c r="V203" s="50"/>
       <c r="W203" s="50" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="X203" s="50"/>
       <c r="Y203" s="50"/>
@@ -19009,80 +19009,51 @@
         <v>58</v>
       </c>
       <c r="C204" s="50">
-        <v>74868</v>
+        <v>75031</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E204" s="50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F204" s="50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G204" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H204" s="50" t="s">
-        <v>455</v>
-      </c>
       <c r="I204" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J204" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K204" s="50" t="s">
-        <v>352</v>
-      </c>
-      <c r="L204" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M204" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K204" s="50"/>
+      <c r="L204" s="50"/>
+      <c r="M204" s="50"/>
       <c r="N204" s="50">
         <v>7</v>
       </c>
-      <c r="O204" s="50">
-        <v>0</v>
-      </c>
+      <c r="O204" s="50"/>
       <c r="P204" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q204" s="50">
-        <v>0</v>
-      </c>
-      <c r="R204" s="50">
-        <v>0</v>
-      </c>
-      <c r="S204" s="50">
-        <v>0</v>
-      </c>
-      <c r="T204" s="50" t="s">
-        <v>456</v>
-      </c>
-      <c r="U204" s="50">
-        <v>1</v>
-      </c>
-      <c r="V204" s="50">
-        <v>0</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="Q204" s="50"/>
+      <c r="R204" s="50"/>
+      <c r="S204" s="50"/>
+      <c r="T204" s="50"/>
+      <c r="U204" s="50"/>
+      <c r="V204" s="50"/>
       <c r="W204" s="50" t="s">
-        <v>1</v>
+        <v>453</v>
       </c>
       <c r="X204" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y204" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z204" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA204" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="Y204" s="50"/>
+      <c r="Z204" s="52"/>
+      <c r="AA204" s="50"/>
     </row>
     <row r="205">
       <c r="A205" s="50">
@@ -19092,22 +19063,22 @@
         <v>58</v>
       </c>
       <c r="C205" s="50">
-        <v>74869</v>
+        <v>74868</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E205" s="50">
+        <v>5</v>
+      </c>
+      <c r="F205" s="50">
         <v>4</v>
-      </c>
-      <c r="F205" s="50">
-        <v>2</v>
       </c>
       <c r="G205" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H205" s="50" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="I205" s="50" t="s">
         <v>78</v>
@@ -19116,7 +19087,7 @@
         <v>62</v>
       </c>
       <c r="K205" s="50" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="L205" s="50" t="s">
         <v>1</v>
@@ -19140,13 +19111,13 @@
         <v>0</v>
       </c>
       <c r="S205" s="50">
-        <v>70004</v>
-      </c>
-      <c r="T205" s="50">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T205" s="50" t="s">
+        <v>456</v>
       </c>
       <c r="U205" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V205" s="50">
         <v>0</v>
@@ -19175,22 +19146,22 @@
         <v>58</v>
       </c>
       <c r="C206" s="50">
-        <v>74870</v>
+        <v>74869</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E206" s="50">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F206" s="50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G206" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H206" s="50" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I206" s="50" t="s">
         <v>78</v>
@@ -19199,10 +19170,10 @@
         <v>62</v>
       </c>
       <c r="K206" s="50" t="s">
-        <v>461</v>
+        <v>294</v>
       </c>
       <c r="L206" s="50" t="s">
-        <v>462</v>
+        <v>1</v>
       </c>
       <c r="M206" s="50" t="s">
         <v>1</v>
@@ -19213,7 +19184,9 @@
       <c r="O206" s="50">
         <v>0</v>
       </c>
-      <c r="P206" s="50"/>
+      <c r="P206" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q206" s="50">
         <v>0</v>
       </c>
@@ -19221,7 +19194,7 @@
         <v>0</v>
       </c>
       <c r="S206" s="50">
-        <v>0</v>
+        <v>70004</v>
       </c>
       <c r="T206" s="50">
         <v>0</v>
@@ -19256,22 +19229,22 @@
         <v>58</v>
       </c>
       <c r="C207" s="50">
-        <v>74871</v>
+        <v>74870</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E207" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F207" s="50">
         <v>6</v>
       </c>
       <c r="G207" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H207" s="50" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="I207" s="50" t="s">
         <v>78</v>
@@ -19280,10 +19253,10 @@
         <v>62</v>
       </c>
       <c r="K207" s="50" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L207" s="50" t="s">
-        <v>1</v>
+        <v>462</v>
       </c>
       <c r="M207" s="50" t="s">
         <v>1</v>
@@ -19337,22 +19310,22 @@
         <v>58</v>
       </c>
       <c r="C208" s="50">
-        <v>74872</v>
+        <v>74871</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E208" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F208" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G208" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H208" s="50" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I208" s="50" t="s">
         <v>78</v>
@@ -19361,10 +19334,10 @@
         <v>62</v>
       </c>
       <c r="K208" s="50" t="s">
-        <v>297</v>
+        <v>465</v>
       </c>
       <c r="L208" s="50" t="s">
-        <v>468</v>
+        <v>1</v>
       </c>
       <c r="M208" s="50" t="s">
         <v>1</v>
@@ -19375,9 +19348,7 @@
       <c r="O208" s="50">
         <v>0</v>
       </c>
-      <c r="P208" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P208" s="50"/>
       <c r="Q208" s="50">
         <v>0</v>
       </c>
@@ -19387,8 +19358,8 @@
       <c r="S208" s="50">
         <v>0</v>
       </c>
-      <c r="T208" s="50" t="s">
-        <v>469</v>
+      <c r="T208" s="50">
+        <v>0</v>
       </c>
       <c r="U208" s="50">
         <v>0</v>
@@ -19420,22 +19391,22 @@
         <v>58</v>
       </c>
       <c r="C209" s="50">
-        <v>74873</v>
+        <v>74872</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E209" s="50">
         <v>5</v>
       </c>
       <c r="F209" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G209" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H209" s="50" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="I209" s="50" t="s">
         <v>78</v>
@@ -19444,10 +19415,10 @@
         <v>62</v>
       </c>
       <c r="K209" s="50" t="s">
-        <v>222</v>
+        <v>297</v>
       </c>
       <c r="L209" s="50" t="s">
-        <v>1</v>
+        <v>468</v>
       </c>
       <c r="M209" s="50" t="s">
         <v>1</v>
@@ -19471,7 +19442,7 @@
         <v>0</v>
       </c>
       <c r="T209" s="50" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="U209" s="50">
         <v>0</v>
@@ -19503,22 +19474,22 @@
         <v>58</v>
       </c>
       <c r="C210" s="50">
-        <v>74874</v>
+        <v>74873</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E210" s="50">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="F210" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G210" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H210" s="50" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I210" s="50" t="s">
         <v>78</v>
@@ -19527,10 +19498,10 @@
         <v>62</v>
       </c>
       <c r="K210" s="50" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="L210" s="50" t="s">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="M210" s="50" t="s">
         <v>1</v>
@@ -19541,7 +19512,9 @@
       <c r="O210" s="50">
         <v>0</v>
       </c>
-      <c r="P210" s="50"/>
+      <c r="P210" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q210" s="50">
         <v>0</v>
       </c>
@@ -19551,8 +19524,8 @@
       <c r="S210" s="50">
         <v>0</v>
       </c>
-      <c r="T210" s="50">
-        <v>0</v>
+      <c r="T210" s="50" t="s">
+        <v>472</v>
       </c>
       <c r="U210" s="50">
         <v>0</v>
@@ -19584,13 +19557,13 @@
         <v>58</v>
       </c>
       <c r="C211" s="50">
-        <v>74875</v>
+        <v>74874</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E211" s="50">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F211" s="50">
         <v>0</v>
@@ -19599,7 +19572,7 @@
         <v>60</v>
       </c>
       <c r="H211" s="50" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="I211" s="50" t="s">
         <v>78</v>
@@ -19608,10 +19581,10 @@
         <v>62</v>
       </c>
       <c r="K211" s="50" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="L211" s="50" t="s">
-        <v>1</v>
+        <v>475</v>
       </c>
       <c r="M211" s="50" t="s">
         <v>1</v>
@@ -19665,22 +19638,22 @@
         <v>58</v>
       </c>
       <c r="C212" s="50">
-        <v>74876</v>
+        <v>74875</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E212" s="50">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F212" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G212" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H212" s="50" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I212" s="50" t="s">
         <v>78</v>
@@ -19689,7 +19662,7 @@
         <v>62</v>
       </c>
       <c r="K212" s="50" t="s">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c r="L212" s="50" t="s">
         <v>1</v>
@@ -19703,9 +19676,7 @@
       <c r="O212" s="50">
         <v>0</v>
       </c>
-      <c r="P212" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P212" s="50"/>
       <c r="Q212" s="50">
         <v>0</v>
       </c>
@@ -19713,7 +19684,7 @@
         <v>0</v>
       </c>
       <c r="S212" s="50">
-        <v>70003</v>
+        <v>0</v>
       </c>
       <c r="T212" s="50">
         <v>0</v>
@@ -19748,22 +19719,22 @@
         <v>58</v>
       </c>
       <c r="C213" s="50">
-        <v>74877</v>
+        <v>74876</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E213" s="50">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F213" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G213" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H213" s="50" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I213" s="50" t="s">
         <v>78</v>
@@ -19772,13 +19743,13 @@
         <v>62</v>
       </c>
       <c r="K213" s="50" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="L213" s="50" t="s">
-        <v>482</v>
+        <v>1</v>
       </c>
       <c r="M213" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N213" s="50">
         <v>7</v>
@@ -19786,7 +19757,9 @@
       <c r="O213" s="50">
         <v>0</v>
       </c>
-      <c r="P213" s="50"/>
+      <c r="P213" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q213" s="50">
         <v>0</v>
       </c>
@@ -19794,7 +19767,7 @@
         <v>0</v>
       </c>
       <c r="S213" s="50">
-        <v>0</v>
+        <v>70003</v>
       </c>
       <c r="T213" s="50">
         <v>0</v>
@@ -19829,13 +19802,13 @@
         <v>58</v>
       </c>
       <c r="C214" s="50">
-        <v>74878</v>
+        <v>74877</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E214" s="50">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F214" s="50">
         <v>0</v>
@@ -19844,7 +19817,7 @@
         <v>138</v>
       </c>
       <c r="H214" s="50" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I214" s="50" t="s">
         <v>78</v>
@@ -19853,13 +19826,13 @@
         <v>62</v>
       </c>
       <c r="K214" s="50" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L214" s="50" t="s">
-        <v>1</v>
+        <v>482</v>
       </c>
       <c r="M214" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N214" s="50">
         <v>7</v>
@@ -19872,7 +19845,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S214" s="50">
         <v>0</v>
@@ -19910,13 +19883,13 @@
         <v>58</v>
       </c>
       <c r="C215" s="50">
-        <v>74879</v>
+        <v>74878</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E215" s="50">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F215" s="50">
         <v>0</v>
@@ -19925,7 +19898,7 @@
         <v>138</v>
       </c>
       <c r="H215" s="50" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I215" s="50" t="s">
         <v>78</v>
@@ -19934,7 +19907,7 @@
         <v>62</v>
       </c>
       <c r="K215" s="50" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="L215" s="50" t="s">
         <v>1</v>
@@ -19948,14 +19921,12 @@
       <c r="O215" s="50">
         <v>0</v>
       </c>
-      <c r="P215" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P215" s="50"/>
       <c r="Q215" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R215" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S215" s="50">
         <v>0</v>
@@ -19993,22 +19964,22 @@
         <v>58</v>
       </c>
       <c r="C216" s="50">
-        <v>74880</v>
+        <v>74879</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E216" s="50">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F216" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G216" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H216" s="50" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I216" s="50" t="s">
         <v>78</v>
@@ -20017,10 +19988,10 @@
         <v>62</v>
       </c>
       <c r="K216" s="50" t="s">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="L216" s="50" t="s">
-        <v>490</v>
+        <v>1</v>
       </c>
       <c r="M216" s="50" t="s">
         <v>1</v>
@@ -20031,9 +20002,11 @@
       <c r="O216" s="50">
         <v>0</v>
       </c>
-      <c r="P216" s="50"/>
+      <c r="P216" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q216" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" s="50">
         <v>0</v>
@@ -20074,34 +20047,37 @@
         <v>58</v>
       </c>
       <c r="C217" s="50">
-        <v>74994</v>
+        <v>74880</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E217" s="50">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F217" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G217" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H217" s="50" t="s">
+        <v>488</v>
+      </c>
       <c r="I217" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J217" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K217" s="50" t="s">
-        <v>75</v>
+        <v>489</v>
       </c>
       <c r="L217" s="50" t="s">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="M217" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N217" s="50">
         <v>7</v>
@@ -20109,9 +20085,7 @@
       <c r="O217" s="50">
         <v>0</v>
       </c>
-      <c r="P217" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P217" s="50"/>
       <c r="Q217" s="50">
         <v>0</v>
       </c>
@@ -20143,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="AA217" s="50" t="s">
-        <v>492</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -20154,16 +20128,16 @@
         <v>58</v>
       </c>
       <c r="C218" s="50">
-        <v>74995</v>
+        <v>74994</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E218" s="50">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F218" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G218" s="50" t="s">
         <v>60</v>
@@ -20181,7 +20155,7 @@
         <v>1</v>
       </c>
       <c r="M218" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N218" s="50">
         <v>7</v>
@@ -20217,13 +20191,13 @@
         <v>1</v>
       </c>
       <c r="Y218" s="50" t="s">
-        <v>494</v>
+        <v>1</v>
       </c>
       <c r="Z218" s="52">
         <v>0</v>
       </c>
       <c r="AA218" s="50" t="s">
-        <v>1</v>
+        <v>492</v>
       </c>
     </row>
     <row r="219">
@@ -20234,31 +20208,28 @@
         <v>58</v>
       </c>
       <c r="C219" s="50">
-        <v>74881</v>
+        <v>74995</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E219" s="50">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F219" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G219" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H219" s="50" t="s">
-        <v>496</v>
-      </c>
       <c r="I219" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J219" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K219" s="50" t="s">
-        <v>497</v>
+        <v>75</v>
       </c>
       <c r="L219" s="50" t="s">
         <v>1</v>
@@ -20272,7 +20243,9 @@
       <c r="O219" s="50">
         <v>0</v>
       </c>
-      <c r="P219" s="50"/>
+      <c r="P219" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q219" s="50">
         <v>0</v>
       </c>
@@ -20298,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="Y219" s="50" t="s">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="Z219" s="52">
         <v>0</v>
@@ -20315,22 +20288,22 @@
         <v>58</v>
       </c>
       <c r="C220" s="50">
-        <v>74882</v>
+        <v>74881</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E220" s="50">
+        <v>3</v>
+      </c>
+      <c r="F220" s="50">
         <v>4</v>
       </c>
-      <c r="F220" s="50">
-        <v>1</v>
-      </c>
       <c r="G220" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H220" s="50" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I220" s="50" t="s">
         <v>78</v>
@@ -20339,7 +20312,7 @@
         <v>62</v>
       </c>
       <c r="K220" s="50" t="s">
-        <v>230</v>
+        <v>497</v>
       </c>
       <c r="L220" s="50" t="s">
         <v>1</v>
@@ -20353,9 +20326,7 @@
       <c r="O220" s="50">
         <v>0</v>
       </c>
-      <c r="P220" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P220" s="50"/>
       <c r="Q220" s="50">
         <v>0</v>
       </c>
@@ -20363,7 +20334,7 @@
         <v>0</v>
       </c>
       <c r="S220" s="50">
-        <v>70005</v>
+        <v>0</v>
       </c>
       <c r="T220" s="50">
         <v>0</v>
@@ -20387,7 +20358,7 @@
         <v>0</v>
       </c>
       <c r="AA220" s="50" t="s">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -20398,28 +20369,31 @@
         <v>58</v>
       </c>
       <c r="C221" s="50">
-        <v>74996</v>
+        <v>74882</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E221" s="50">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F221" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G221" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H221" s="50" t="s">
+        <v>499</v>
       </c>
       <c r="I221" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J221" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K221" s="50" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="L221" s="50" t="s">
         <v>1</v>
@@ -20443,7 +20417,7 @@
         <v>0</v>
       </c>
       <c r="S221" s="50">
-        <v>0</v>
+        <v>70005</v>
       </c>
       <c r="T221" s="50">
         <v>0</v>
@@ -20458,16 +20432,16 @@
         <v>1</v>
       </c>
       <c r="X221" s="50" t="s">
-        <v>502</v>
+        <v>1</v>
       </c>
       <c r="Y221" s="50" t="s">
-        <v>503</v>
+        <v>1</v>
       </c>
       <c r="Z221" s="52">
         <v>0</v>
       </c>
       <c r="AA221" s="50" t="s">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="222">
@@ -20478,31 +20452,28 @@
         <v>58</v>
       </c>
       <c r="C222" s="50">
-        <v>74884</v>
+        <v>74996</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E222" s="50">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="F222" s="50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G222" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H222" s="50" t="s">
-        <v>505</v>
+        <v>60</v>
       </c>
       <c r="I222" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J222" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K222" s="50" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="L222" s="50" t="s">
         <v>1</v>
@@ -20528,8 +20499,8 @@
       <c r="S222" s="50">
         <v>0</v>
       </c>
-      <c r="T222" s="50" t="s">
-        <v>61</v>
+      <c r="T222" s="50">
+        <v>0</v>
       </c>
       <c r="U222" s="50">
         <v>0</v>
@@ -20541,10 +20512,10 @@
         <v>1</v>
       </c>
       <c r="X222" s="50" t="s">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="Y222" s="50" t="s">
-        <v>1</v>
+        <v>503</v>
       </c>
       <c r="Z222" s="52">
         <v>0</v>
@@ -20561,22 +20532,22 @@
         <v>58</v>
       </c>
       <c r="C223" s="50">
-        <v>74885</v>
+        <v>74884</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E223" s="50">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="F223" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G223" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H223" s="50" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="I223" s="50" t="s">
         <v>78</v>
@@ -20585,13 +20556,13 @@
         <v>62</v>
       </c>
       <c r="K223" s="50" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="L223" s="50" t="s">
-        <v>508</v>
+        <v>1</v>
       </c>
       <c r="M223" s="50" t="s">
-        <v>509</v>
+        <v>1</v>
       </c>
       <c r="N223" s="50">
         <v>7</v>
@@ -20599,7 +20570,9 @@
       <c r="O223" s="50">
         <v>0</v>
       </c>
-      <c r="P223" s="50"/>
+      <c r="P223" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q223" s="50">
         <v>0</v>
       </c>
@@ -20609,8 +20582,8 @@
       <c r="S223" s="50">
         <v>0</v>
       </c>
-      <c r="T223" s="50">
-        <v>0</v>
+      <c r="T223" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U223" s="50">
         <v>0</v>
@@ -20642,13 +20615,13 @@
         <v>58</v>
       </c>
       <c r="C224" s="50">
-        <v>74886</v>
+        <v>74885</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E224" s="50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F224" s="50">
         <v>0</v>
@@ -20657,7 +20630,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20666,13 +20639,13 @@
         <v>62</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L224" s="50" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="M224" s="50" t="s">
-        <v>1</v>
+        <v>509</v>
       </c>
       <c r="N224" s="50">
         <v>7</v>
@@ -20723,13 +20696,13 @@
         <v>58</v>
       </c>
       <c r="C225" s="50">
-        <v>74887</v>
+        <v>74886</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E225" s="50">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F225" s="50">
         <v>0</v>
@@ -20738,7 +20711,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20747,10 +20720,10 @@
         <v>62</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L225" s="50" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="M225" s="50" t="s">
         <v>1</v>
@@ -20804,13 +20777,13 @@
         <v>58</v>
       </c>
       <c r="C226" s="50">
-        <v>74888</v>
+        <v>74887</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E226" s="50">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F226" s="50">
         <v>0</v>
@@ -20819,7 +20792,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20828,13 +20801,13 @@
         <v>62</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>180</v>
+        <v>331</v>
       </c>
       <c r="L226" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M226" s="50" t="s">
-        <v>517</v>
+        <v>1</v>
       </c>
       <c r="N226" s="50">
         <v>7</v>
@@ -20885,13 +20858,13 @@
         <v>58</v>
       </c>
       <c r="C227" s="50">
-        <v>74889</v>
+        <v>74888</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E227" s="50">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F227" s="50">
         <v>0</v>
@@ -20900,7 +20873,7 @@
         <v>60</v>
       </c>
       <c r="H227" s="50" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I227" s="50" t="s">
         <v>78</v>
@@ -20909,13 +20882,13 @@
         <v>62</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="L227" s="50" t="s">
-        <v>520</v>
+        <v>1</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="N227" s="50">
         <v>7</v>
@@ -20966,13 +20939,13 @@
         <v>58</v>
       </c>
       <c r="C228" s="50">
-        <v>74997</v>
+        <v>74889</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E228" s="50">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F228" s="50">
         <v>0</v>
@@ -20980,8 +20953,11 @@
       <c r="G228" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H228" s="50" t="s">
+        <v>519</v>
+      </c>
       <c r="I228" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J228" s="50" t="s">
         <v>62</v>
@@ -20990,10 +20966,10 @@
         <v>75</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="M228" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N228" s="50">
         <v>7</v>
@@ -21001,9 +20977,7 @@
       <c r="O228" s="50">
         <v>0</v>
       </c>
-      <c r="P228" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P228" s="50"/>
       <c r="Q228" s="50">
         <v>0</v>
       </c>
@@ -21035,7 +21009,7 @@
         <v>0</v>
       </c>
       <c r="AA228" s="50" t="s">
-        <v>522</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -21046,16 +21020,16 @@
         <v>58</v>
       </c>
       <c r="C229" s="50">
-        <v>74998</v>
+        <v>74997</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E229" s="50">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F229" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G229" s="50" t="s">
         <v>60</v>
@@ -21073,7 +21047,7 @@
         <v>1</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N229" s="50">
         <v>7</v>
@@ -21109,13 +21083,13 @@
         <v>1</v>
       </c>
       <c r="Y229" s="50" t="s">
-        <v>517</v>
+        <v>1</v>
       </c>
       <c r="Z229" s="52">
         <v>0</v>
       </c>
       <c r="AA229" s="50" t="s">
-        <v>1</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230">
@@ -21126,13 +21100,13 @@
         <v>58</v>
       </c>
       <c r="C230" s="50">
-        <v>74890</v>
+        <v>74998</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E230" s="50">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F230" s="50">
         <v>2</v>
@@ -21140,17 +21114,14 @@
       <c r="G230" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H230" s="50" t="s">
-        <v>525</v>
-      </c>
       <c r="I230" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J230" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K230" s="50" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="L230" s="50" t="s">
         <v>1</v>
@@ -21174,7 +21145,7 @@
         <v>0</v>
       </c>
       <c r="S230" s="50">
-        <v>70006</v>
+        <v>0</v>
       </c>
       <c r="T230" s="50">
         <v>0</v>
@@ -21192,7 +21163,7 @@
         <v>1</v>
       </c>
       <c r="Y230" s="50" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="Z230" s="52">
         <v>0</v>
@@ -21209,22 +21180,22 @@
         <v>58</v>
       </c>
       <c r="C231" s="50">
-        <v>74891</v>
+        <v>74890</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E231" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F231" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G231" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H231" s="50" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="I231" s="50" t="s">
         <v>78</v>
@@ -21233,7 +21204,7 @@
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -21257,10 +21228,10 @@
         <v>0</v>
       </c>
       <c r="S231" s="50">
-        <v>0</v>
-      </c>
-      <c r="T231" s="50" t="s">
-        <v>528</v>
+        <v>70006</v>
+      </c>
+      <c r="T231" s="50">
+        <v>0</v>
       </c>
       <c r="U231" s="50">
         <v>0</v>
@@ -21292,22 +21263,22 @@
         <v>58</v>
       </c>
       <c r="C232" s="50">
-        <v>74892</v>
+        <v>74891</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E232" s="50">
         <v>5</v>
       </c>
       <c r="F232" s="50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G232" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H232" s="50" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="I232" s="50" t="s">
         <v>78</v>
@@ -21316,7 +21287,7 @@
         <v>62</v>
       </c>
       <c r="K232" s="50" t="s">
-        <v>352</v>
+        <v>96</v>
       </c>
       <c r="L232" s="50" t="s">
         <v>1</v>
@@ -21343,7 +21314,7 @@
         <v>0</v>
       </c>
       <c r="T232" s="50" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="U232" s="50">
         <v>0</v>
@@ -21375,22 +21346,22 @@
         <v>58</v>
       </c>
       <c r="C233" s="50">
-        <v>74893</v>
+        <v>74892</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E233" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F233" s="50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G233" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H233" s="50" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I233" s="50" t="s">
         <v>78</v>
@@ -21399,10 +21370,10 @@
         <v>62</v>
       </c>
       <c r="K233" s="50" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="L233" s="50" t="s">
-        <v>534</v>
+        <v>1</v>
       </c>
       <c r="M233" s="50" t="s">
         <v>1</v>
@@ -21413,7 +21384,9 @@
       <c r="O233" s="50">
         <v>0</v>
       </c>
-      <c r="P233" s="50"/>
+      <c r="P233" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q233" s="50">
         <v>0</v>
       </c>
@@ -21423,8 +21396,8 @@
       <c r="S233" s="50">
         <v>0</v>
       </c>
-      <c r="T233" s="50">
-        <v>0</v>
+      <c r="T233" s="50" t="s">
+        <v>531</v>
       </c>
       <c r="U233" s="50">
         <v>0</v>
@@ -21436,7 +21409,7 @@
         <v>1</v>
       </c>
       <c r="X233" s="50" t="s">
-        <v>535</v>
+        <v>1</v>
       </c>
       <c r="Y233" s="50" t="s">
         <v>1</v>
@@ -21456,22 +21429,22 @@
         <v>58</v>
       </c>
       <c r="C234" s="50">
-        <v>74894</v>
+        <v>74893</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E234" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F234" s="50">
         <v>3</v>
       </c>
       <c r="G234" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H234" s="50" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I234" s="50" t="s">
         <v>78</v>
@@ -21480,10 +21453,10 @@
         <v>62</v>
       </c>
       <c r="K234" s="50" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="L234" s="50" t="s">
-        <v>1</v>
+        <v>534</v>
       </c>
       <c r="M234" s="50" t="s">
         <v>1</v>
@@ -21517,7 +21490,7 @@
         <v>1</v>
       </c>
       <c r="X234" s="50" t="s">
-        <v>1</v>
+        <v>535</v>
       </c>
       <c r="Y234" s="50" t="s">
         <v>1</v>
@@ -21537,22 +21510,22 @@
         <v>58</v>
       </c>
       <c r="C235" s="50">
-        <v>74895</v>
+        <v>74894</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E235" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F235" s="50">
         <v>3</v>
       </c>
       <c r="G235" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H235" s="50" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I235" s="50" t="s">
         <v>78</v>
@@ -21561,7 +21534,7 @@
         <v>62</v>
       </c>
       <c r="K235" s="50" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="L235" s="50" t="s">
         <v>1</v>
@@ -21575,9 +21548,7 @@
       <c r="O235" s="50">
         <v>0</v>
       </c>
-      <c r="P235" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P235" s="50"/>
       <c r="Q235" s="50">
         <v>0</v>
       </c>
@@ -21585,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="S235" s="50">
-        <v>70007</v>
+        <v>0</v>
       </c>
       <c r="T235" s="50">
         <v>0</v>
@@ -21620,52 +21591,79 @@
         <v>58</v>
       </c>
       <c r="C236" s="50">
-        <v>74896</v>
+        <v>74895</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E236" s="50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F236" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G236" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H236" s="50" t="s">
+        <v>539</v>
       </c>
       <c r="I236" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J236" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K236" s="50"/>
+      <c r="K236" s="50" t="s">
+        <v>246</v>
+      </c>
       <c r="L236" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="M236" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="M236" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N236" s="50">
         <v>7</v>
       </c>
-      <c r="O236" s="50"/>
+      <c r="O236" s="50">
+        <v>0</v>
+      </c>
       <c r="P236" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="Q236" s="50"/>
-      <c r="R236" s="50"/>
-      <c r="S236" s="50"/>
-      <c r="T236" s="50"/>
-      <c r="U236" s="50"/>
-      <c r="V236" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="Q236" s="50">
+        <v>0</v>
+      </c>
+      <c r="R236" s="50">
+        <v>0</v>
+      </c>
+      <c r="S236" s="50">
+        <v>70007</v>
+      </c>
+      <c r="T236" s="50">
+        <v>0</v>
+      </c>
+      <c r="U236" s="50">
+        <v>0</v>
+      </c>
+      <c r="V236" s="50">
+        <v>0</v>
+      </c>
       <c r="W236" s="50" t="s">
-        <v>502</v>
-      </c>
-      <c r="X236" s="50"/>
-      <c r="Y236" s="50"/>
-      <c r="Z236" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="X236" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y236" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z236" s="52">
+        <v>0</v>
+      </c>
       <c r="AA236" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -21676,77 +21674,52 @@
         <v>58</v>
       </c>
       <c r="C237" s="50">
-        <v>74897</v>
+        <v>74896</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E237" s="50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F237" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H237" s="50" t="s">
-        <v>543</v>
+        <v>60</v>
       </c>
       <c r="I237" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J237" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K237" s="50" t="s">
-        <v>142</v>
-      </c>
+      <c r="K237" s="50"/>
       <c r="L237" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M237" s="50" t="s">
-        <v>544</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M237" s="50"/>
       <c r="N237" s="50">
         <v>7</v>
       </c>
-      <c r="O237" s="50">
-        <v>0</v>
-      </c>
-      <c r="P237" s="50"/>
-      <c r="Q237" s="50">
-        <v>0</v>
-      </c>
-      <c r="R237" s="50">
-        <v>0</v>
-      </c>
-      <c r="S237" s="50">
-        <v>0</v>
-      </c>
-      <c r="T237" s="50">
-        <v>0</v>
-      </c>
-      <c r="U237" s="50">
-        <v>0</v>
-      </c>
-      <c r="V237" s="50">
-        <v>0</v>
-      </c>
+      <c r="O237" s="50"/>
+      <c r="P237" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="Q237" s="50"/>
+      <c r="R237" s="50"/>
+      <c r="S237" s="50"/>
+      <c r="T237" s="50"/>
+      <c r="U237" s="50"/>
+      <c r="V237" s="50"/>
       <c r="W237" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X237" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y237" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z237" s="52">
-        <v>0</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="X237" s="50"/>
+      <c r="Y237" s="50"/>
+      <c r="Z237" s="52"/>
       <c r="AA237" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="238">
@@ -21757,22 +21730,22 @@
         <v>58</v>
       </c>
       <c r="C238" s="50">
-        <v>74898</v>
+        <v>74897</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E238" s="50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F238" s="50">
         <v>0</v>
       </c>
       <c r="G238" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H238" s="50" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="I238" s="50" t="s">
         <v>78</v>
@@ -21781,13 +21754,13 @@
         <v>62</v>
       </c>
       <c r="K238" s="50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L238" s="50" t="s">
-        <v>547</v>
+        <v>1</v>
       </c>
       <c r="M238" s="50" t="s">
-        <v>1</v>
+        <v>544</v>
       </c>
       <c r="N238" s="50">
         <v>7</v>
@@ -21838,10 +21811,10 @@
         <v>58</v>
       </c>
       <c r="C239" s="50">
-        <v>74899</v>
+        <v>74898</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E239" s="50">
         <v>7</v>
@@ -21853,7 +21826,7 @@
         <v>138</v>
       </c>
       <c r="H239" s="50" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I239" s="50" t="s">
         <v>78</v>
@@ -21919,10 +21892,10 @@
         <v>58</v>
       </c>
       <c r="C240" s="50">
-        <v>74900</v>
+        <v>74899</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E240" s="50">
         <v>7</v>
@@ -21934,7 +21907,7 @@
         <v>138</v>
       </c>
       <c r="H240" s="50" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I240" s="50" t="s">
         <v>78</v>
@@ -22000,22 +21973,22 @@
         <v>58</v>
       </c>
       <c r="C241" s="50">
-        <v>74901</v>
+        <v>74900</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E241" s="50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F241" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G241" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H241" s="50" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I241" s="50" t="s">
         <v>78</v>
@@ -22024,10 +21997,10 @@
         <v>62</v>
       </c>
       <c r="K241" s="50" t="s">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="L241" s="50" t="s">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="M241" s="50" t="s">
         <v>1</v>
@@ -22038,9 +22011,7 @@
       <c r="O241" s="50">
         <v>0</v>
       </c>
-      <c r="P241" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P241" s="50"/>
       <c r="Q241" s="50">
         <v>0</v>
       </c>
@@ -22050,8 +22021,8 @@
       <c r="S241" s="50">
         <v>0</v>
       </c>
-      <c r="T241" s="50" t="s">
-        <v>554</v>
+      <c r="T241" s="50">
+        <v>0</v>
       </c>
       <c r="U241" s="50">
         <v>0</v>
@@ -22083,52 +22054,79 @@
         <v>58</v>
       </c>
       <c r="C242" s="50">
-        <v>74905</v>
+        <v>74901</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E242" s="50">
+        <v>5</v>
+      </c>
+      <c r="F242" s="50">
         <v>2</v>
       </c>
-      <c r="F242" s="50">
-        <v>1</v>
-      </c>
       <c r="G242" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H242" s="50" t="s">
+        <v>553</v>
       </c>
       <c r="I242" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J242" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K242" s="50"/>
+      <c r="K242" s="50" t="s">
+        <v>297</v>
+      </c>
       <c r="L242" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="M242" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="M242" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N242" s="50">
         <v>7</v>
       </c>
-      <c r="O242" s="50"/>
+      <c r="O242" s="50">
+        <v>0</v>
+      </c>
       <c r="P242" s="50" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q242" s="50"/>
-      <c r="R242" s="50"/>
-      <c r="S242" s="50"/>
-      <c r="T242" s="50"/>
-      <c r="U242" s="50"/>
-      <c r="V242" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="Q242" s="50">
+        <v>0</v>
+      </c>
+      <c r="R242" s="50">
+        <v>0</v>
+      </c>
+      <c r="S242" s="50">
+        <v>0</v>
+      </c>
+      <c r="T242" s="50" t="s">
+        <v>554</v>
+      </c>
+      <c r="U242" s="50">
+        <v>0</v>
+      </c>
+      <c r="V242" s="50">
+        <v>0</v>
+      </c>
       <c r="W242" s="50" t="s">
-        <v>535</v>
-      </c>
-      <c r="X242" s="50"/>
-      <c r="Y242" s="50"/>
-      <c r="Z242" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="X242" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y242" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z242" s="52">
+        <v>0</v>
+      </c>
       <c r="AA242" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -22139,19 +22137,19 @@
         <v>58</v>
       </c>
       <c r="C243" s="50">
-        <v>74906</v>
+        <v>74905</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E243" s="50">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F243" s="50">
         <v>1</v>
       </c>
       <c r="G243" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="I243" s="50" t="s">
         <v>61</v>
@@ -22159,54 +22157,32 @@
       <c r="J243" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K243" s="50" t="s">
-        <v>558</v>
-      </c>
+      <c r="K243" s="50"/>
       <c r="L243" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M243" s="50" t="s">
-        <v>559</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M243" s="50"/>
       <c r="N243" s="50">
         <v>7</v>
       </c>
-      <c r="O243" s="50">
-        <v>0</v>
-      </c>
-      <c r="P243" s="50"/>
-      <c r="Q243" s="50">
-        <v>0</v>
-      </c>
-      <c r="R243" s="50">
-        <v>0</v>
-      </c>
-      <c r="S243" s="50">
-        <v>0</v>
-      </c>
-      <c r="T243" s="50">
-        <v>0</v>
-      </c>
-      <c r="U243" s="50">
-        <v>0</v>
-      </c>
-      <c r="V243" s="50">
-        <v>0</v>
-      </c>
+      <c r="O243" s="50"/>
+      <c r="P243" s="50" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q243" s="50"/>
+      <c r="R243" s="50"/>
+      <c r="S243" s="50"/>
+      <c r="T243" s="50"/>
+      <c r="U243" s="50"/>
+      <c r="V243" s="50"/>
       <c r="W243" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X243" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y243" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z243" s="52">
-        <v>0</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="X243" s="50"/>
+      <c r="Y243" s="50"/>
+      <c r="Z243" s="52"/>
       <c r="AA243" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="244">
@@ -22217,19 +22193,19 @@
         <v>58</v>
       </c>
       <c r="C244" s="50">
-        <v>74907</v>
+        <v>74906</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E244" s="50">
         <v>13</v>
       </c>
       <c r="F244" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G244" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I244" s="50" t="s">
         <v>61</v>
@@ -22238,13 +22214,13 @@
         <v>62</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>75</v>
+        <v>558</v>
       </c>
       <c r="L244" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M244" s="50" t="s">
-        <v>1</v>
+        <v>559</v>
       </c>
       <c r="N244" s="50">
         <v>7</v>
@@ -22295,19 +22271,19 @@
         <v>58</v>
       </c>
       <c r="C245" s="50">
-        <v>74908</v>
+        <v>74907</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E245" s="50">
         <v>13</v>
       </c>
       <c r="F245" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G245" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="I245" s="50" t="s">
         <v>61</v>
@@ -22316,13 +22292,13 @@
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>558</v>
+        <v>75</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M245" s="50" t="s">
-        <v>562</v>
+        <v>1</v>
       </c>
       <c r="N245" s="50">
         <v>7</v>
@@ -22373,19 +22349,19 @@
         <v>58</v>
       </c>
       <c r="C246" s="50">
-        <v>74909</v>
+        <v>74908</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E246" s="50">
         <v>13</v>
       </c>
       <c r="F246" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G246" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I246" s="50" t="s">
         <v>61</v>
@@ -22394,13 +22370,13 @@
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>75</v>
+        <v>558</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M246" s="50" t="s">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="N246" s="50">
         <v>7</v>
@@ -22451,31 +22427,28 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>74999</v>
+        <v>74909</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E247" s="50">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F247" s="50">
         <v>2</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H247" s="50" t="s">
-        <v>565</v>
+        <v>60</v>
       </c>
       <c r="I247" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J247" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
@@ -22489,9 +22462,7 @@
       <c r="O247" s="50">
         <v>0</v>
       </c>
-      <c r="P247" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P247" s="50"/>
       <c r="Q247" s="50">
         <v>0</v>
       </c>
@@ -22501,8 +22472,8 @@
       <c r="S247" s="50">
         <v>0</v>
       </c>
-      <c r="T247" s="50" t="s">
-        <v>566</v>
+      <c r="T247" s="50">
+        <v>0</v>
       </c>
       <c r="U247" s="50">
         <v>0</v>
@@ -22534,22 +22505,22 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>74979</v>
+        <v>74999</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E248" s="50">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="F248" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G248" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H248" s="50" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="I248" s="50" t="s">
         <v>78</v>
@@ -22558,7 +22529,7 @@
         <v>62</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>569</v>
+        <v>297</v>
       </c>
       <c r="L248" s="50" t="s">
         <v>1</v>
@@ -22572,7 +22543,9 @@
       <c r="O248" s="50">
         <v>0</v>
       </c>
-      <c r="P248" s="50"/>
+      <c r="P248" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q248" s="50">
         <v>0</v>
       </c>
@@ -22582,8 +22555,8 @@
       <c r="S248" s="50">
         <v>0</v>
       </c>
-      <c r="T248" s="50">
-        <v>0</v>
+      <c r="T248" s="50" t="s">
+        <v>566</v>
       </c>
       <c r="U248" s="50">
         <v>0</v>
@@ -22615,22 +22588,22 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>74982</v>
+        <v>74979</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E249" s="50">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F249" s="50">
         <v>0</v>
       </c>
       <c r="G249" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H249" s="50" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="I249" s="50" t="s">
         <v>78</v>
@@ -22639,7 +22612,7 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22696,10 +22669,10 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>74984</v>
+        <v>74982</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E250" s="50">
         <v>46</v>
@@ -22711,7 +22684,7 @@
         <v>60</v>
       </c>
       <c r="H250" s="50" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>78</v>
@@ -22777,22 +22750,22 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>74981</v>
+        <v>74984</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E251" s="50">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F251" s="50">
         <v>0</v>
       </c>
       <c r="G251" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H251" s="50" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I251" s="50" t="s">
         <v>78</v>
@@ -22801,13 +22774,13 @@
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="L251" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M251" s="50" t="s">
-        <v>578</v>
+        <v>1</v>
       </c>
       <c r="N251" s="50">
         <v>7</v>
@@ -22858,22 +22831,22 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>74983</v>
+        <v>74981</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E252" s="50">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F252" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G252" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H252" s="50" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I252" s="50" t="s">
         <v>78</v>
@@ -22882,13 +22855,13 @@
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>192</v>
+        <v>577</v>
       </c>
       <c r="L252" s="50" t="s">
-        <v>581</v>
+        <v>1</v>
       </c>
       <c r="M252" s="50" t="s">
-        <v>1</v>
+        <v>578</v>
       </c>
       <c r="N252" s="50">
         <v>7</v>
@@ -22939,22 +22912,22 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>74985</v>
+        <v>74983</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E253" s="50">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F253" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G253" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H253" s="50" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I253" s="50" t="s">
         <v>78</v>
@@ -22963,10 +22936,10 @@
         <v>62</v>
       </c>
       <c r="K253" s="50" t="s">
-        <v>572</v>
+        <v>192</v>
       </c>
       <c r="L253" s="50" t="s">
-        <v>1</v>
+        <v>581</v>
       </c>
       <c r="M253" s="50" t="s">
         <v>1</v>
@@ -23020,47 +22993,78 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>74988</v>
+        <v>74985</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E254" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F254" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G254" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H254" s="50" t="s">
+        <v>583</v>
+      </c>
       <c r="I254" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J254" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K254" s="50"/>
-      <c r="L254" s="50"/>
-      <c r="M254" s="50"/>
+      <c r="K254" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L254" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M254" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N254" s="50">
         <v>7</v>
       </c>
-      <c r="O254" s="50"/>
-      <c r="P254" s="50" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q254" s="50"/>
-      <c r="R254" s="50"/>
-      <c r="S254" s="50"/>
-      <c r="T254" s="50"/>
-      <c r="U254" s="50"/>
-      <c r="V254" s="50"/>
-      <c r="W254" s="50"/>
-      <c r="X254" s="50"/>
-      <c r="Y254" s="50"/>
-      <c r="Z254" s="52"/>
-      <c r="AA254" s="50"/>
+      <c r="O254" s="50">
+        <v>0</v>
+      </c>
+      <c r="P254" s="50"/>
+      <c r="Q254" s="50">
+        <v>0</v>
+      </c>
+      <c r="R254" s="50">
+        <v>0</v>
+      </c>
+      <c r="S254" s="50">
+        <v>0</v>
+      </c>
+      <c r="T254" s="50">
+        <v>0</v>
+      </c>
+      <c r="U254" s="50">
+        <v>0</v>
+      </c>
+      <c r="V254" s="50">
+        <v>0</v>
+      </c>
+      <c r="W254" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X254" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y254" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z254" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA254" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="50">
@@ -23070,78 +23074,47 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>74991</v>
+        <v>74988</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E255" s="50">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F255" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G255" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H255" s="50" t="s">
-        <v>587</v>
+        <v>60</v>
       </c>
       <c r="I255" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J255" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K255" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="L255" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M255" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K255" s="50"/>
+      <c r="L255" s="50"/>
+      <c r="M255" s="50"/>
       <c r="N255" s="50">
         <v>7</v>
       </c>
-      <c r="O255" s="50">
-        <v>0</v>
-      </c>
-      <c r="P255" s="50"/>
-      <c r="Q255" s="50">
-        <v>0</v>
-      </c>
-      <c r="R255" s="50">
-        <v>0</v>
-      </c>
-      <c r="S255" s="50">
-        <v>0</v>
-      </c>
-      <c r="T255" s="50">
-        <v>0</v>
-      </c>
-      <c r="U255" s="50">
-        <v>0</v>
-      </c>
-      <c r="V255" s="50">
-        <v>0</v>
-      </c>
-      <c r="W255" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X255" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y255" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z255" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA255" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O255" s="50"/>
+      <c r="P255" s="50" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q255" s="50"/>
+      <c r="R255" s="50"/>
+      <c r="S255" s="50"/>
+      <c r="T255" s="50"/>
+      <c r="U255" s="50"/>
+      <c r="V255" s="50"/>
+      <c r="W255" s="50"/>
+      <c r="X255" s="50"/>
+      <c r="Y255" s="50"/>
+      <c r="Z255" s="52"/>
+      <c r="AA255" s="50"/>
     </row>
     <row r="256">
       <c r="A256" s="50">
@@ -23151,22 +23124,22 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>74990</v>
+        <v>74991</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E256" s="50">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F256" s="50">
         <v>0</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -23175,10 +23148,10 @@
         <v>62</v>
       </c>
       <c r="K256" s="50" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="L256" s="50" t="s">
-        <v>590</v>
+        <v>1</v>
       </c>
       <c r="M256" s="50" t="s">
         <v>1</v>
@@ -23232,13 +23205,13 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>74989</v>
+        <v>74990</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E257" s="50">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
@@ -23246,17 +23219,20 @@
       <c r="G257" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H257" s="50" t="s">
+        <v>589</v>
+      </c>
       <c r="I257" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J257" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="L257" s="50" t="s">
-        <v>61</v>
+        <v>590</v>
       </c>
       <c r="M257" s="50" t="s">
         <v>1</v>
@@ -23267,9 +23243,7 @@
       <c r="O257" s="50">
         <v>0</v>
       </c>
-      <c r="P257" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P257" s="50"/>
       <c r="Q257" s="50">
         <v>0</v>
       </c>
@@ -23312,34 +23286,31 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>75000</v>
+        <v>74989</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E258" s="50">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F258" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G258" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H258" s="50" t="s">
-        <v>593</v>
+        <v>60</v>
       </c>
       <c r="I258" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J258" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -23362,8 +23333,8 @@
       <c r="S258" s="50">
         <v>0</v>
       </c>
-      <c r="T258" s="50" t="s">
-        <v>594</v>
+      <c r="T258" s="50">
+        <v>0</v>
       </c>
       <c r="U258" s="50">
         <v>0</v>
@@ -23395,22 +23366,22 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>75001</v>
+        <v>75000</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E259" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F259" s="50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -23419,10 +23390,10 @@
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>597</v>
+        <v>1</v>
       </c>
       <c r="M259" s="50" t="s">
         <v>1</v>
@@ -23433,7 +23404,9 @@
       <c r="O259" s="50">
         <v>0</v>
       </c>
-      <c r="P259" s="50"/>
+      <c r="P259" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q259" s="50">
         <v>0</v>
       </c>
@@ -23443,8 +23416,8 @@
       <c r="S259" s="50">
         <v>0</v>
       </c>
-      <c r="T259" s="50">
-        <v>0</v>
+      <c r="T259" s="50" t="s">
+        <v>594</v>
       </c>
       <c r="U259" s="50">
         <v>0</v>
@@ -23476,22 +23449,22 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>75002</v>
+        <v>75001</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E260" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F260" s="50">
         <v>2</v>
       </c>
       <c r="G260" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H260" s="50" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -23500,10 +23473,10 @@
         <v>62</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>1</v>
+        <v>597</v>
       </c>
       <c r="M260" s="50" t="s">
         <v>1</v>
@@ -23557,22 +23530,22 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>75003</v>
+        <v>75002</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E261" s="50">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F261" s="50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H261" s="50" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I261" s="50" t="s">
         <v>78</v>
@@ -23581,10 +23554,10 @@
         <v>62</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="L261" s="50" t="s">
-        <v>602</v>
+        <v>1</v>
       </c>
       <c r="M261" s="50" t="s">
         <v>1</v>
@@ -23638,34 +23611,37 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>75004</v>
+        <v>75003</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E262" s="50">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F262" s="50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H262" s="50" t="s">
+        <v>601</v>
       </c>
       <c r="I262" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J262" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M262" s="50" t="s">
-        <v>605</v>
+        <v>1</v>
       </c>
       <c r="N262" s="50">
         <v>7</v>
@@ -23716,13 +23692,13 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>75005</v>
+        <v>75004</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E263" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F263" s="50">
         <v>2</v>
@@ -23730,23 +23706,20 @@
       <c r="G263" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H263" s="50" t="s">
-        <v>607</v>
-      </c>
       <c r="I263" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J263" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>1</v>
+        <v>604</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="N263" s="50">
         <v>7</v>
@@ -23797,34 +23770,37 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>75006</v>
+        <v>75005</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E264" s="50">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F264" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G264" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H264" s="50" t="s">
+        <v>607</v>
+      </c>
       <c r="I264" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J264" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K264" s="50" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L264" s="50" t="s">
-        <v>609</v>
+        <v>1</v>
       </c>
       <c r="M264" s="50" t="s">
-        <v>605</v>
+        <v>1</v>
       </c>
       <c r="N264" s="50">
         <v>7</v>
@@ -23875,13 +23851,13 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>75007</v>
+        <v>75006</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E265" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F265" s="50">
         <v>4</v>
@@ -23889,23 +23865,20 @@
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H265" s="50" t="s">
-        <v>611</v>
-      </c>
       <c r="I265" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J265" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>1</v>
+        <v>609</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>1</v>
+        <v>605</v>
       </c>
       <c r="N265" s="50">
         <v>7</v>
@@ -23956,28 +23929,31 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>75008</v>
+        <v>75007</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E266" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F266" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G266" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H266" s="50" t="s">
+        <v>611</v>
+      </c>
       <c r="I266" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J266" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K266" s="50" t="s">
-        <v>613</v>
+        <v>283</v>
       </c>
       <c r="L266" s="50" t="s">
         <v>1</v>
@@ -24034,16 +24010,16 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>75009</v>
+        <v>75008</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E267" s="50">
         <v>56</v>
       </c>
       <c r="F267" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
@@ -24055,7 +24031,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>301</v>
+        <v>613</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -24112,10 +24088,10 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>75010</v>
+        <v>75009</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E268" s="50">
         <v>56</v>
@@ -24190,10 +24166,10 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>75011</v>
+        <v>75010</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E269" s="50">
         <v>56</v>
@@ -24268,10 +24244,10 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>75012</v>
+        <v>75011</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E270" s="50">
         <v>56</v>
@@ -24346,10 +24322,10 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>75013</v>
+        <v>75012</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E271" s="50">
         <v>56</v>
@@ -24424,10 +24400,10 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>75014</v>
+        <v>75013</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E272" s="50">
         <v>56</v>
@@ -24502,10 +24478,10 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>75015</v>
+        <v>75014</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E273" s="50">
         <v>56</v>
@@ -24580,10 +24556,10 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>75016</v>
+        <v>75015</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E274" s="50">
         <v>56</v>
@@ -24658,10 +24634,10 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>75017</v>
+        <v>75016</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E275" s="50">
         <v>56</v>
@@ -24736,10 +24712,10 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>75018</v>
+        <v>75017</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E276" s="50">
         <v>56</v>
@@ -24814,10 +24790,10 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>75019</v>
+        <v>75018</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E277" s="50">
         <v>56</v>
@@ -24892,10 +24868,10 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>75020</v>
+        <v>75019</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E278" s="50">
         <v>56</v>
@@ -24970,10 +24946,10 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>75021</v>
+        <v>75020</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
@@ -25048,10 +25024,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>75022</v>
+        <v>75021</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25126,10 +25102,10 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>75023</v>
+        <v>75022</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25204,10 +25180,10 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>75024</v>
+        <v>75023</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25282,10 +25258,10 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>75025</v>
+        <v>75024</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25360,10 +25336,10 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>75026</v>
+        <v>75025</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25438,10 +25414,10 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>75027</v>
+        <v>75026</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25516,10 +25492,10 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>75028</v>
+        <v>75027</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25594,10 +25570,10 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>75029</v>
+        <v>75028</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25672,10 +25648,10 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>75030</v>
+        <v>75029</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25750,13 +25726,13 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>84928</v>
+        <v>75030</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E289" s="50">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F289" s="50">
         <v>0</v>
@@ -25771,7 +25747,7 @@
         <v>62</v>
       </c>
       <c r="K289" s="50" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="L289" s="50" t="s">
         <v>1</v>
@@ -25780,14 +25756,12 @@
         <v>1</v>
       </c>
       <c r="N289" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O289" s="50">
         <v>0</v>
       </c>
-      <c r="P289" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P289" s="50"/>
       <c r="Q289" s="50">
         <v>0</v>
       </c>
@@ -25830,34 +25804,31 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>84929</v>
+        <v>84928</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E290" s="50">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F290" s="50">
         <v>0</v>
       </c>
       <c r="G290" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H290" s="50" t="s">
-        <v>638</v>
+        <v>60</v>
       </c>
       <c r="I290" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J290" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="L290" s="50" t="s">
-        <v>639</v>
+        <v>1</v>
       </c>
       <c r="M290" s="50" t="s">
         <v>1</v>
@@ -25868,7 +25839,9 @@
       <c r="O290" s="50">
         <v>0</v>
       </c>
-      <c r="P290" s="50"/>
+      <c r="P290" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q290" s="50">
         <v>0</v>
       </c>
@@ -25911,34 +25884,37 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>84930</v>
+        <v>84929</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E291" s="50">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F291" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G291" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
+      </c>
+      <c r="H291" s="50" t="s">
+        <v>638</v>
       </c>
       <c r="I291" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J291" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="L291" s="50" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M291" s="50" t="s">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="N291" s="50">
         <v>8</v>
@@ -25989,13 +25965,13 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>84931</v>
+        <v>84930</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E292" s="50">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="F292" s="50">
         <v>1</v>
@@ -26003,23 +25979,20 @@
       <c r="G292" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="H292" s="50" t="s">
-        <v>644</v>
-      </c>
       <c r="I292" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J292" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K292" s="50" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L292" s="50" t="s">
-        <v>1</v>
+        <v>641</v>
       </c>
       <c r="M292" s="50" t="s">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="N292" s="50">
         <v>8</v>
@@ -26070,34 +26043,37 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>84932</v>
+        <v>84931</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E293" s="50">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F293" s="50">
         <v>1</v>
       </c>
       <c r="G293" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
+      </c>
+      <c r="H293" s="50" t="s">
+        <v>644</v>
       </c>
       <c r="I293" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J293" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L293" s="50" t="s">
-        <v>646</v>
+        <v>1</v>
       </c>
       <c r="M293" s="50" t="s">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="N293" s="50">
         <v>8</v>
@@ -26148,13 +26124,13 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>84933</v>
+        <v>84932</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E294" s="50">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="F294" s="50">
         <v>1</v>
@@ -26162,23 +26138,20 @@
       <c r="G294" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H294" s="50" t="s">
-        <v>648</v>
-      </c>
       <c r="I294" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J294" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L294" s="50" t="s">
-        <v>1</v>
+        <v>646</v>
       </c>
       <c r="M294" s="50" t="s">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="N294" s="50">
         <v>8</v>
@@ -26229,22 +26202,22 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>84934</v>
+        <v>84933</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E295" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F295" s="50">
         <v>1</v>
       </c>
       <c r="G295" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>78</v>
@@ -26253,7 +26226,7 @@
         <v>62</v>
       </c>
       <c r="K295" s="50" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="L295" s="50" t="s">
         <v>1</v>
@@ -26310,22 +26283,22 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>84935</v>
+        <v>84934</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E296" s="50">
         <v>31</v>
       </c>
       <c r="F296" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G296" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>78</v>
@@ -26334,7 +26307,7 @@
         <v>62</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="L296" s="50" t="s">
         <v>1</v>
@@ -26391,22 +26364,22 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>84936</v>
+        <v>84935</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E297" s="50">
         <v>31</v>
       </c>
       <c r="F297" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G297" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -26415,7 +26388,7 @@
         <v>62</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L297" s="50" t="s">
         <v>1</v>
@@ -26446,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="V297" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W297" s="50" t="s">
         <v>1</v>
@@ -26472,22 +26445,22 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>84937</v>
+        <v>84936</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E298" s="50">
         <v>31</v>
       </c>
       <c r="F298" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G298" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>
@@ -26496,7 +26469,7 @@
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="L298" s="50" t="s">
         <v>1</v>
@@ -26553,22 +26526,22 @@
         <v>58</v>
       </c>
       <c r="C299" s="50">
-        <v>84938</v>
+        <v>84937</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E299" s="50">
         <v>31</v>
       </c>
       <c r="F299" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G299" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H299" s="50" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I299" s="50" t="s">
         <v>78</v>
@@ -26577,7 +26550,7 @@
         <v>62</v>
       </c>
       <c r="K299" s="50" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L299" s="50" t="s">
         <v>1</v>
@@ -26608,7 +26581,7 @@
         <v>0</v>
       </c>
       <c r="V299" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W299" s="50" t="s">
         <v>1</v>
@@ -26634,22 +26607,22 @@
         <v>58</v>
       </c>
       <c r="C300" s="50">
-        <v>84939</v>
+        <v>84938</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E300" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F300" s="50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G300" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H300" s="50" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="I300" s="50" t="s">
         <v>78</v>
@@ -26658,7 +26631,7 @@
         <v>62</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="L300" s="50" t="s">
         <v>1</v>
@@ -26715,10 +26688,10 @@
         <v>58</v>
       </c>
       <c r="C301" s="50">
-        <v>84940</v>
+        <v>84939</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E301" s="50">
         <v>15</v>
@@ -26730,7 +26703,7 @@
         <v>60</v>
       </c>
       <c r="H301" s="50" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I301" s="50" t="s">
         <v>78</v>
@@ -26796,22 +26769,22 @@
         <v>58</v>
       </c>
       <c r="C302" s="50">
-        <v>84941</v>
+        <v>84940</v>
       </c>
       <c r="D302" s="50" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E302" s="50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F302" s="50">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G302" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H302" s="50" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>78</v>
@@ -26820,10 +26793,10 @@
         <v>62</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>192</v>
+        <v>394</v>
       </c>
       <c r="L302" s="50" t="s">
-        <v>665</v>
+        <v>1</v>
       </c>
       <c r="M302" s="50" t="s">
         <v>1</v>
@@ -26877,34 +26850,37 @@
         <v>58</v>
       </c>
       <c r="C303" s="50">
-        <v>84942</v>
+        <v>84941</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E303" s="50">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F303" s="50">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G303" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H303" s="50" t="s">
+        <v>664</v>
+      </c>
       <c r="I303" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J303" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K303" s="50" t="s">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="L303" s="50" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="M303" s="50" t="s">
-        <v>668</v>
+        <v>1</v>
       </c>
       <c r="N303" s="50">
         <v>8</v>
@@ -26955,13 +26931,13 @@
         <v>58</v>
       </c>
       <c r="C304" s="50">
-        <v>84943</v>
+        <v>84942</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E304" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F304" s="50">
         <v>2</v>
@@ -26969,23 +26945,20 @@
       <c r="G304" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H304" s="50" t="s">
-        <v>670</v>
-      </c>
       <c r="I304" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J304" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K304" s="50" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="L304" s="50" t="s">
-        <v>1</v>
+        <v>667</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -27036,34 +27009,37 @@
         <v>58</v>
       </c>
       <c r="C305" s="50">
-        <v>84944</v>
+        <v>84943</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E305" s="50">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F305" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G305" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H305" s="50" t="s">
+        <v>670</v>
+      </c>
       <c r="I305" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J305" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K305" s="50" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L305" s="50" t="s">
-        <v>672</v>
+        <v>1</v>
       </c>
       <c r="M305" s="50" t="s">
-        <v>668</v>
+        <v>1</v>
       </c>
       <c r="N305" s="50">
         <v>8</v>
@@ -27114,13 +27090,13 @@
         <v>58</v>
       </c>
       <c r="C306" s="50">
-        <v>84945</v>
+        <v>84944</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E306" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F306" s="50">
         <v>4</v>
@@ -27128,23 +27104,20 @@
       <c r="G306" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H306" s="50" t="s">
-        <v>674</v>
-      </c>
       <c r="I306" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J306" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K306" s="50" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="L306" s="50" t="s">
-        <v>1</v>
+        <v>672</v>
       </c>
       <c r="M306" s="50" t="s">
-        <v>1</v>
+        <v>668</v>
       </c>
       <c r="N306" s="50">
         <v>8</v>
@@ -27195,28 +27168,31 @@
         <v>58</v>
       </c>
       <c r="C307" s="50">
-        <v>84946</v>
+        <v>84945</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E307" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F307" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G307" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H307" s="50" t="s">
+        <v>674</v>
+      </c>
       <c r="I307" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J307" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K307" s="50" t="s">
-        <v>613</v>
+        <v>283</v>
       </c>
       <c r="L307" s="50" t="s">
         <v>1</v>
@@ -27273,16 +27249,16 @@
         <v>58</v>
       </c>
       <c r="C308" s="50">
-        <v>84947</v>
+        <v>84946</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E308" s="50">
         <v>56</v>
       </c>
       <c r="F308" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G308" s="50" t="s">
         <v>60</v>
@@ -27294,7 +27270,7 @@
         <v>62</v>
       </c>
       <c r="K308" s="50" t="s">
-        <v>301</v>
+        <v>613</v>
       </c>
       <c r="L308" s="50" t="s">
         <v>1</v>
@@ -27351,10 +27327,10 @@
         <v>58</v>
       </c>
       <c r="C309" s="50">
-        <v>84948</v>
+        <v>84947</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E309" s="50">
         <v>56</v>
@@ -27429,10 +27405,10 @@
         <v>58</v>
       </c>
       <c r="C310" s="50">
-        <v>84949</v>
+        <v>84948</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E310" s="50">
         <v>56</v>
@@ -27507,10 +27483,10 @@
         <v>58</v>
       </c>
       <c r="C311" s="50">
-        <v>84950</v>
+        <v>84949</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E311" s="50">
         <v>56</v>
@@ -27585,10 +27561,10 @@
         <v>58</v>
       </c>
       <c r="C312" s="50">
-        <v>84951</v>
+        <v>84950</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E312" s="50">
         <v>56</v>
@@ -27663,10 +27639,10 @@
         <v>58</v>
       </c>
       <c r="C313" s="50">
-        <v>84952</v>
+        <v>84951</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E313" s="50">
         <v>56</v>
@@ -27741,10 +27717,10 @@
         <v>58</v>
       </c>
       <c r="C314" s="50">
-        <v>84953</v>
+        <v>84952</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E314" s="50">
         <v>56</v>
@@ -27819,10 +27795,10 @@
         <v>58</v>
       </c>
       <c r="C315" s="50">
-        <v>84954</v>
+        <v>84953</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E315" s="50">
         <v>56</v>
@@ -27897,10 +27873,10 @@
         <v>58</v>
       </c>
       <c r="C316" s="50">
-        <v>84955</v>
+        <v>84954</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E316" s="50">
         <v>56</v>
@@ -27975,10 +27951,10 @@
         <v>58</v>
       </c>
       <c r="C317" s="50">
-        <v>84956</v>
+        <v>84955</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E317" s="50">
         <v>56</v>
@@ -28053,10 +28029,10 @@
         <v>58</v>
       </c>
       <c r="C318" s="50">
-        <v>84957</v>
+        <v>84956</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E318" s="50">
         <v>56</v>
@@ -28131,10 +28107,10 @@
         <v>58</v>
       </c>
       <c r="C319" s="50">
-        <v>84958</v>
+        <v>84957</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E319" s="50">
         <v>56</v>
@@ -28209,10 +28185,10 @@
         <v>58</v>
       </c>
       <c r="C320" s="50">
-        <v>84959</v>
+        <v>84958</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E320" s="50">
         <v>56</v>
@@ -28287,10 +28263,10 @@
         <v>58</v>
       </c>
       <c r="C321" s="50">
-        <v>84960</v>
+        <v>84959</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E321" s="50">
         <v>56</v>
@@ -28365,10 +28341,10 @@
         <v>58</v>
       </c>
       <c r="C322" s="50">
-        <v>84961</v>
+        <v>84960</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E322" s="50">
         <v>56</v>
@@ -28443,10 +28419,10 @@
         <v>58</v>
       </c>
       <c r="C323" s="50">
-        <v>84962</v>
+        <v>84961</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E323" s="50">
         <v>56</v>
@@ -28521,10 +28497,10 @@
         <v>58</v>
       </c>
       <c r="C324" s="50">
-        <v>84963</v>
+        <v>84962</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E324" s="50">
         <v>56</v>
@@ -28599,10 +28575,10 @@
         <v>58</v>
       </c>
       <c r="C325" s="50">
-        <v>84964</v>
+        <v>84963</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E325" s="50">
         <v>56</v>
@@ -28677,10 +28653,10 @@
         <v>58</v>
       </c>
       <c r="C326" s="50">
-        <v>84965</v>
+        <v>84964</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E326" s="50">
         <v>56</v>
@@ -28755,10 +28731,10 @@
         <v>58</v>
       </c>
       <c r="C327" s="50">
-        <v>84966</v>
+        <v>84965</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E327" s="50">
         <v>56</v>
@@ -28833,10 +28809,10 @@
         <v>58</v>
       </c>
       <c r="C328" s="50">
-        <v>84967</v>
+        <v>84966</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E328" s="50">
         <v>56</v>
@@ -28911,10 +28887,10 @@
         <v>58</v>
       </c>
       <c r="C329" s="50">
-        <v>84968</v>
+        <v>84967</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E329" s="50">
         <v>56</v>
@@ -28989,31 +28965,28 @@
         <v>58</v>
       </c>
       <c r="C330" s="50">
-        <v>84969</v>
+        <v>84968</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E330" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F330" s="50">
         <v>0</v>
       </c>
       <c r="G330" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H330" s="50" t="s">
-        <v>699</v>
+        <v>60</v>
       </c>
       <c r="I330" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J330" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K330" s="50" t="s">
-        <v>569</v>
+        <v>301</v>
       </c>
       <c r="L330" s="50" t="s">
         <v>1</v>
@@ -29070,22 +29043,22 @@
         <v>58</v>
       </c>
       <c r="C331" s="50">
-        <v>84970</v>
+        <v>84969</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E331" s="50">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F331" s="50">
         <v>0</v>
       </c>
       <c r="G331" s="50" t="s">
-        <v>701</v>
+        <v>83</v>
       </c>
       <c r="H331" s="50" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="I331" s="50" t="s">
         <v>78</v>
@@ -29094,7 +29067,7 @@
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -29151,22 +29124,22 @@
         <v>58</v>
       </c>
       <c r="C332" s="50">
-        <v>84971</v>
+        <v>84970</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E332" s="50">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F332" s="50">
         <v>0</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>94</v>
+        <v>701</v>
       </c>
       <c r="H332" s="50" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="I332" s="50" t="s">
         <v>78</v>
@@ -29175,13 +29148,13 @@
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M332" s="50" t="s">
-        <v>705</v>
+        <v>1</v>
       </c>
       <c r="N332" s="50">
         <v>8</v>
@@ -29232,22 +29205,22 @@
         <v>58</v>
       </c>
       <c r="C333" s="50">
-        <v>84972</v>
+        <v>84971</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E333" s="50">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F333" s="50">
         <v>0</v>
       </c>
       <c r="G333" s="50" t="s">
-        <v>707</v>
+        <v>94</v>
       </c>
       <c r="H333" s="50" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="I333" s="50" t="s">
         <v>78</v>
@@ -29256,13 +29229,13 @@
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M333" s="50" t="s">
-        <v>1</v>
+        <v>705</v>
       </c>
       <c r="N333" s="50">
         <v>8</v>
@@ -29313,22 +29286,22 @@
         <v>58</v>
       </c>
       <c r="C334" s="50">
-        <v>84973</v>
+        <v>84972</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E334" s="50">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F334" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G334" s="50" t="s">
-        <v>60</v>
+        <v>707</v>
       </c>
       <c r="H334" s="50" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I334" s="50" t="s">
         <v>78</v>
@@ -29337,10 +29310,10 @@
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>192</v>
+        <v>572</v>
       </c>
       <c r="L334" s="50" t="s">
-        <v>711</v>
+        <v>1</v>
       </c>
       <c r="M334" s="50" t="s">
         <v>1</v>
@@ -29394,22 +29367,22 @@
         <v>58</v>
       </c>
       <c r="C335" s="50">
-        <v>84974</v>
+        <v>84973</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E335" s="50">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F335" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G335" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H335" s="50" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="I335" s="50" t="s">
         <v>78</v>
@@ -29418,10 +29391,10 @@
         <v>62</v>
       </c>
       <c r="K335" s="50" t="s">
-        <v>572</v>
+        <v>192</v>
       </c>
       <c r="L335" s="50" t="s">
-        <v>1</v>
+        <v>711</v>
       </c>
       <c r="M335" s="50" t="s">
         <v>1</v>
@@ -29475,47 +29448,78 @@
         <v>58</v>
       </c>
       <c r="C336" s="50">
-        <v>84976</v>
+        <v>84974</v>
       </c>
       <c r="D336" s="50" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E336" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F336" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G336" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H336" s="50" t="s">
+        <v>713</v>
+      </c>
       <c r="I336" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J336" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K336" s="50"/>
-      <c r="L336" s="50"/>
-      <c r="M336" s="50"/>
+      <c r="K336" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M336" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N336" s="50">
         <v>8</v>
       </c>
-      <c r="O336" s="50"/>
-      <c r="P336" s="50" t="s">
-        <v>715</v>
-      </c>
-      <c r="Q336" s="50"/>
-      <c r="R336" s="50"/>
-      <c r="S336" s="50"/>
-      <c r="T336" s="50"/>
-      <c r="U336" s="50"/>
-      <c r="V336" s="50"/>
-      <c r="W336" s="50"/>
-      <c r="X336" s="50"/>
-      <c r="Y336" s="50"/>
-      <c r="Z336" s="52"/>
-      <c r="AA336" s="50"/>
+      <c r="O336" s="50">
+        <v>0</v>
+      </c>
+      <c r="P336" s="50"/>
+      <c r="Q336" s="50">
+        <v>0</v>
+      </c>
+      <c r="R336" s="50">
+        <v>0</v>
+      </c>
+      <c r="S336" s="50">
+        <v>0</v>
+      </c>
+      <c r="T336" s="50">
+        <v>0</v>
+      </c>
+      <c r="U336" s="50">
+        <v>0</v>
+      </c>
+      <c r="V336" s="50">
+        <v>0</v>
+      </c>
+      <c r="W336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y336" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z336" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA336" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="50">
@@ -29525,16 +29529,16 @@
         <v>58</v>
       </c>
       <c r="C337" s="50">
-        <v>84977</v>
+        <v>84976</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E337" s="50">
         <v>2</v>
       </c>
       <c r="F337" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G337" s="50" t="s">
         <v>60</v>
@@ -29553,7 +29557,7 @@
       </c>
       <c r="O337" s="50"/>
       <c r="P337" s="50" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="Q337" s="50"/>
       <c r="R337" s="50"/>
@@ -29575,16 +29579,16 @@
         <v>58</v>
       </c>
       <c r="C338" s="50">
-        <v>84978</v>
+        <v>84977</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E338" s="50">
         <v>2</v>
       </c>
       <c r="F338" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G338" s="50" t="s">
         <v>60</v>
@@ -29603,7 +29607,7 @@
       </c>
       <c r="O338" s="50"/>
       <c r="P338" s="50" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="Q338" s="50"/>
       <c r="R338" s="50"/>
@@ -29625,78 +29629,47 @@
         <v>58</v>
       </c>
       <c r="C339" s="50">
-        <v>84979</v>
+        <v>84978</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E339" s="50">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F339" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G339" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H339" s="50" t="s">
-        <v>721</v>
+        <v>60</v>
       </c>
       <c r="I339" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J339" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K339" s="50" t="s">
-        <v>327</v>
-      </c>
-      <c r="L339" s="50" t="s">
-        <v>722</v>
-      </c>
-      <c r="M339" s="50" t="s">
-        <v>723</v>
-      </c>
+      <c r="K339" s="50"/>
+      <c r="L339" s="50"/>
+      <c r="M339" s="50"/>
       <c r="N339" s="50">
         <v>8</v>
       </c>
-      <c r="O339" s="50">
-        <v>0</v>
-      </c>
-      <c r="P339" s="50"/>
-      <c r="Q339" s="50">
-        <v>0</v>
-      </c>
-      <c r="R339" s="50">
-        <v>0</v>
-      </c>
-      <c r="S339" s="50">
-        <v>0</v>
-      </c>
-      <c r="T339" s="50">
-        <v>0</v>
-      </c>
-      <c r="U339" s="50">
-        <v>0</v>
-      </c>
-      <c r="V339" s="50">
-        <v>0</v>
-      </c>
-      <c r="W339" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X339" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y339" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z339" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA339" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O339" s="50"/>
+      <c r="P339" s="50" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q339" s="50"/>
+      <c r="R339" s="50"/>
+      <c r="S339" s="50"/>
+      <c r="T339" s="50"/>
+      <c r="U339" s="50"/>
+      <c r="V339" s="50"/>
+      <c r="W339" s="50"/>
+      <c r="X339" s="50"/>
+      <c r="Y339" s="50"/>
+      <c r="Z339" s="52"/>
+      <c r="AA339" s="50"/>
     </row>
     <row r="340">
       <c r="A340" s="50">
@@ -29706,22 +29679,22 @@
         <v>58</v>
       </c>
       <c r="C340" s="50">
-        <v>84980</v>
+        <v>84979</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="E340" s="50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F340" s="50">
         <v>0</v>
       </c>
       <c r="G340" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29730,13 +29703,13 @@
         <v>62</v>
       </c>
       <c r="K340" s="50" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L340" s="50" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="M340" s="50" t="s">
-        <v>1</v>
+        <v>723</v>
       </c>
       <c r="N340" s="50">
         <v>8</v>
@@ -29787,13 +29760,13 @@
         <v>58</v>
       </c>
       <c r="C341" s="50">
-        <v>84981</v>
+        <v>84980</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E341" s="50">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F341" s="50">
         <v>0</v>
@@ -29802,7 +29775,7 @@
         <v>60</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29811,10 +29784,10 @@
         <v>62</v>
       </c>
       <c r="K341" s="50" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L341" s="50" t="s">
-        <v>1</v>
+        <v>726</v>
       </c>
       <c r="M341" s="50" t="s">
         <v>1</v>
@@ -29868,13 +29841,13 @@
         <v>58</v>
       </c>
       <c r="C342" s="50">
-        <v>84982</v>
+        <v>84981</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E342" s="50">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F342" s="50">
         <v>0</v>
@@ -29882,20 +29855,23 @@
       <c r="G342" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H342" s="50" t="s">
+        <v>728</v>
+      </c>
       <c r="I342" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J342" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K342" s="50" t="s">
-        <v>730</v>
+        <v>331</v>
       </c>
       <c r="L342" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M342" s="50" t="s">
-        <v>731</v>
+        <v>1</v>
       </c>
       <c r="N342" s="50">
         <v>8</v>
@@ -29903,9 +29879,7 @@
       <c r="O342" s="50">
         <v>0</v>
       </c>
-      <c r="P342" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P342" s="50"/>
       <c r="Q342" s="50">
         <v>0</v>
       </c>
@@ -29948,13 +29922,13 @@
         <v>58</v>
       </c>
       <c r="C343" s="50">
-        <v>84983</v>
+        <v>84982</v>
       </c>
       <c r="D343" s="50" t="s">
         <v>729</v>
       </c>
       <c r="E343" s="50">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F343" s="50">
         <v>0</v>
@@ -29962,23 +29936,20 @@
       <c r="G343" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H343" s="50" t="s">
-        <v>732</v>
-      </c>
       <c r="I343" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J343" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K343" s="50" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="L343" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M343" s="50" t="s">
-        <v>1</v>
+        <v>731</v>
       </c>
       <c r="N343" s="50">
         <v>8</v>
@@ -30031,13 +30002,13 @@
         <v>58</v>
       </c>
       <c r="C344" s="50">
-        <v>84984</v>
+        <v>84983</v>
       </c>
       <c r="D344" s="50" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="E344" s="50">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F344" s="50">
         <v>0</v>
@@ -30046,7 +30017,7 @@
         <v>60</v>
       </c>
       <c r="H344" s="50" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I344" s="50" t="s">
         <v>78</v>
@@ -30055,7 +30026,7 @@
         <v>62</v>
       </c>
       <c r="K344" s="50" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="L344" s="50" t="s">
         <v>1</v>
@@ -30114,22 +30085,22 @@
         <v>58</v>
       </c>
       <c r="C345" s="50">
-        <v>330037</v>
+        <v>84984</v>
       </c>
       <c r="D345" s="50" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E345" s="50">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F345" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G345" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H345" s="50" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="I345" s="50" t="s">
         <v>78</v>
@@ -30138,7 +30109,7 @@
         <v>62</v>
       </c>
       <c r="K345" s="50" t="s">
-        <v>96</v>
+        <v>736</v>
       </c>
       <c r="L345" s="50" t="s">
         <v>1</v>
@@ -30147,7 +30118,7 @@
         <v>1</v>
       </c>
       <c r="N345" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O345" s="50">
         <v>0</v>
@@ -30164,8 +30135,8 @@
       <c r="S345" s="50">
         <v>0</v>
       </c>
-      <c r="T345" s="50" t="s">
-        <v>61</v>
+      <c r="T345" s="50">
+        <v>0</v>
       </c>
       <c r="U345" s="50">
         <v>0</v>
@@ -30197,22 +30168,22 @@
         <v>58</v>
       </c>
       <c r="C346" s="50">
-        <v>330038</v>
+        <v>330037</v>
       </c>
       <c r="D346" s="50" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E346" s="50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F346" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G346" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H346" s="50" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="I346" s="50" t="s">
         <v>78</v>
@@ -30221,13 +30192,13 @@
         <v>62</v>
       </c>
       <c r="K346" s="50" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L346" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M346" s="50" t="s">
-        <v>741</v>
+        <v>1</v>
       </c>
       <c r="N346" s="50">
         <v>33</v>
@@ -30235,7 +30206,9 @@
       <c r="O346" s="50">
         <v>0</v>
       </c>
-      <c r="P346" s="50"/>
+      <c r="P346" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q346" s="50">
         <v>0</v>
       </c>
@@ -30245,8 +30218,8 @@
       <c r="S346" s="50">
         <v>0</v>
       </c>
-      <c r="T346" s="50">
-        <v>0</v>
+      <c r="T346" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U346" s="50">
         <v>0</v>
@@ -30278,22 +30251,22 @@
         <v>58</v>
       </c>
       <c r="C347" s="50">
-        <v>330039</v>
+        <v>330038</v>
       </c>
       <c r="D347" s="50" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E347" s="50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F347" s="50">
         <v>0</v>
       </c>
       <c r="G347" s="50" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="H347" s="50" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I347" s="50" t="s">
         <v>78</v>
@@ -30302,13 +30275,13 @@
         <v>62</v>
       </c>
       <c r="K347" s="50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L347" s="50" t="s">
-        <v>744</v>
+        <v>1</v>
       </c>
       <c r="M347" s="50" t="s">
-        <v>1</v>
+        <v>741</v>
       </c>
       <c r="N347" s="50">
         <v>33</v>
@@ -30359,10 +30332,10 @@
         <v>58</v>
       </c>
       <c r="C348" s="50">
-        <v>330040</v>
+        <v>330039</v>
       </c>
       <c r="D348" s="50" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E348" s="50">
         <v>7</v>
@@ -30374,7 +30347,7 @@
         <v>138</v>
       </c>
       <c r="H348" s="50" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I348" s="50" t="s">
         <v>78</v>
@@ -30440,10 +30413,10 @@
         <v>58</v>
       </c>
       <c r="C349" s="50">
-        <v>330041</v>
+        <v>330040</v>
       </c>
       <c r="D349" s="50" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E349" s="50">
         <v>7</v>
@@ -30455,7 +30428,7 @@
         <v>138</v>
       </c>
       <c r="H349" s="50" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="I349" s="50" t="s">
         <v>78</v>
@@ -30521,22 +30494,22 @@
         <v>58</v>
       </c>
       <c r="C350" s="50">
-        <v>330042</v>
+        <v>330041</v>
       </c>
       <c r="D350" s="50" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E350" s="50">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F350" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G350" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H350" s="50" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="I350" s="50" t="s">
         <v>78</v>
@@ -30545,13 +30518,13 @@
         <v>62</v>
       </c>
       <c r="K350" s="50" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="L350" s="50" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="M350" s="50" t="s">
-        <v>752</v>
+        <v>1</v>
       </c>
       <c r="N350" s="50">
         <v>33</v>
@@ -30602,13 +30575,13 @@
         <v>58</v>
       </c>
       <c r="C351" s="50">
-        <v>330043</v>
+        <v>330042</v>
       </c>
       <c r="D351" s="50" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E351" s="50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F351" s="50">
         <v>1</v>
@@ -30617,7 +30590,7 @@
         <v>60</v>
       </c>
       <c r="H351" s="50" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="I351" s="50" t="s">
         <v>78</v>
@@ -30626,13 +30599,13 @@
         <v>62</v>
       </c>
       <c r="K351" s="50" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L351" s="50" t="s">
-        <v>1</v>
+        <v>751</v>
       </c>
       <c r="M351" s="50" t="s">
-        <v>1</v>
+        <v>752</v>
       </c>
       <c r="N351" s="50">
         <v>33</v>
@@ -30683,22 +30656,22 @@
         <v>58</v>
       </c>
       <c r="C352" s="50">
-        <v>330044</v>
+        <v>330043</v>
       </c>
       <c r="D352" s="50" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E352" s="50">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F352" s="50">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G352" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H352" s="50" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="I352" s="50" t="s">
         <v>78</v>
@@ -30707,10 +30680,10 @@
         <v>62</v>
       </c>
       <c r="K352" s="50" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="L352" s="50" t="s">
-        <v>757</v>
+        <v>1</v>
       </c>
       <c r="M352" s="50" t="s">
         <v>1</v>
@@ -30764,22 +30737,22 @@
         <v>58</v>
       </c>
       <c r="C353" s="50">
-        <v>330045</v>
+        <v>330044</v>
       </c>
       <c r="D353" s="50" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E353" s="50">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F353" s="50">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G353" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H353" s="50" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="I353" s="50" t="s">
         <v>78</v>
@@ -30788,10 +30761,10 @@
         <v>62</v>
       </c>
       <c r="K353" s="50" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="L353" s="50" t="s">
-        <v>1</v>
+        <v>757</v>
       </c>
       <c r="M353" s="50" t="s">
         <v>1</v>
@@ -30802,9 +30775,7 @@
       <c r="O353" s="50">
         <v>0</v>
       </c>
-      <c r="P353" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P353" s="50"/>
       <c r="Q353" s="50">
         <v>0</v>
       </c>
@@ -30814,8 +30785,8 @@
       <c r="S353" s="50">
         <v>0</v>
       </c>
-      <c r="T353" s="50" t="s">
-        <v>61</v>
+      <c r="T353" s="50">
+        <v>0</v>
       </c>
       <c r="U353" s="50">
         <v>0</v>
@@ -30847,22 +30818,22 @@
         <v>58</v>
       </c>
       <c r="C354" s="50">
-        <v>330046</v>
+        <v>330045</v>
       </c>
       <c r="D354" s="50" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E354" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F354" s="50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G354" s="50" t="s">
         <v>83</v>
       </c>
       <c r="H354" s="50" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="I354" s="50" t="s">
         <v>78</v>
@@ -30871,10 +30842,10 @@
         <v>62</v>
       </c>
       <c r="K354" s="50" t="s">
-        <v>461</v>
+        <v>96</v>
       </c>
       <c r="L354" s="50" t="s">
-        <v>762</v>
+        <v>1</v>
       </c>
       <c r="M354" s="50" t="s">
         <v>1</v>
@@ -30885,7 +30856,9 @@
       <c r="O354" s="50">
         <v>0</v>
       </c>
-      <c r="P354" s="50"/>
+      <c r="P354" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q354" s="50">
         <v>0</v>
       </c>
@@ -30895,8 +30868,8 @@
       <c r="S354" s="50">
         <v>0</v>
       </c>
-      <c r="T354" s="50">
-        <v>0</v>
+      <c r="T354" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U354" s="50">
         <v>0</v>
@@ -30928,22 +30901,22 @@
         <v>58</v>
       </c>
       <c r="C355" s="50">
-        <v>330047</v>
+        <v>330046</v>
       </c>
       <c r="D355" s="50" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E355" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F355" s="50">
         <v>6</v>
       </c>
       <c r="G355" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H355" s="50" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="I355" s="50" t="s">
         <v>78</v>
@@ -30952,10 +30925,10 @@
         <v>62</v>
       </c>
       <c r="K355" s="50" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L355" s="50" t="s">
-        <v>1</v>
+        <v>762</v>
       </c>
       <c r="M355" s="50" t="s">
         <v>1</v>
@@ -31009,22 +30982,22 @@
         <v>58</v>
       </c>
       <c r="C356" s="50">
-        <v>330048</v>
+        <v>330047</v>
       </c>
       <c r="D356" s="50" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E356" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F356" s="50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G356" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H356" s="50" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I356" s="50" t="s">
         <v>78</v>
@@ -31033,7 +31006,7 @@
         <v>62</v>
       </c>
       <c r="K356" s="50" t="s">
-        <v>96</v>
+        <v>465</v>
       </c>
       <c r="L356" s="50" t="s">
         <v>1</v>
@@ -31047,9 +31020,7 @@
       <c r="O356" s="50">
         <v>0</v>
       </c>
-      <c r="P356" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P356" s="50"/>
       <c r="Q356" s="50">
         <v>0</v>
       </c>
@@ -31059,8 +31030,8 @@
       <c r="S356" s="50">
         <v>0</v>
       </c>
-      <c r="T356" s="50" t="s">
-        <v>61</v>
+      <c r="T356" s="50">
+        <v>0</v>
       </c>
       <c r="U356" s="50">
         <v>0</v>
@@ -31092,22 +31063,22 @@
         <v>58</v>
       </c>
       <c r="C357" s="50">
-        <v>330049</v>
+        <v>330048</v>
       </c>
       <c r="D357" s="50" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E357" s="50">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="F357" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G357" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H357" s="50" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="I357" s="50" t="s">
         <v>78</v>
@@ -31116,10 +31087,10 @@
         <v>62</v>
       </c>
       <c r="K357" s="50" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L357" s="50" t="s">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="M357" s="50" t="s">
         <v>1</v>
@@ -31130,7 +31101,9 @@
       <c r="O357" s="50">
         <v>0</v>
       </c>
-      <c r="P357" s="50"/>
+      <c r="P357" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q357" s="50">
         <v>0</v>
       </c>
@@ -31140,8 +31113,8 @@
       <c r="S357" s="50">
         <v>0</v>
       </c>
-      <c r="T357" s="50">
-        <v>0</v>
+      <c r="T357" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U357" s="50">
         <v>0</v>
@@ -31173,13 +31146,13 @@
         <v>58</v>
       </c>
       <c r="C358" s="50">
-        <v>330050</v>
+        <v>330049</v>
       </c>
       <c r="D358" s="50" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E358" s="50">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F358" s="50">
         <v>0</v>
@@ -31188,7 +31161,7 @@
         <v>60</v>
       </c>
       <c r="H358" s="50" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="I358" s="50" t="s">
         <v>78</v>
@@ -31197,10 +31170,10 @@
         <v>62</v>
       </c>
       <c r="K358" s="50" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="L358" s="50" t="s">
-        <v>1</v>
+        <v>769</v>
       </c>
       <c r="M358" s="50" t="s">
         <v>1</v>
@@ -31254,22 +31227,22 @@
         <v>58</v>
       </c>
       <c r="C359" s="50">
-        <v>330051</v>
+        <v>330050</v>
       </c>
       <c r="D359" s="50" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E359" s="50">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F359" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H359" s="50" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I359" s="50" t="s">
         <v>78</v>
@@ -31278,7 +31251,7 @@
         <v>62</v>
       </c>
       <c r="K359" s="50" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="L359" s="50" t="s">
         <v>1</v>
@@ -31292,9 +31265,7 @@
       <c r="O359" s="50">
         <v>0</v>
       </c>
-      <c r="P359" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P359" s="50"/>
       <c r="Q359" s="50">
         <v>0</v>
       </c>
@@ -31337,22 +31308,22 @@
         <v>58</v>
       </c>
       <c r="C360" s="50">
-        <v>330052</v>
+        <v>330051</v>
       </c>
       <c r="D360" s="50" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E360" s="50">
         <v>4</v>
       </c>
       <c r="F360" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G360" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H360" s="50" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="I360" s="50" t="s">
         <v>78</v>
@@ -31361,7 +31332,7 @@
         <v>62</v>
       </c>
       <c r="K360" s="50" t="s">
-        <v>294</v>
+        <v>230</v>
       </c>
       <c r="L360" s="50" t="s">
         <v>1</v>
@@ -31420,22 +31391,22 @@
         <v>58</v>
       </c>
       <c r="C361" s="50">
-        <v>330053</v>
+        <v>330052</v>
       </c>
       <c r="D361" s="50" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E361" s="50">
         <v>4</v>
       </c>
       <c r="F361" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G361" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H361" s="50" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I361" s="50" t="s">
         <v>78</v>
@@ -31444,7 +31415,7 @@
         <v>62</v>
       </c>
       <c r="K361" s="50" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="L361" s="50" t="s">
         <v>1</v>
@@ -31503,22 +31474,22 @@
         <v>58</v>
       </c>
       <c r="C362" s="50">
-        <v>330054</v>
+        <v>330053</v>
       </c>
       <c r="D362" s="50" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E362" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F362" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G362" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H362" s="50" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="I362" s="50" t="s">
         <v>78</v>
@@ -31527,7 +31498,7 @@
         <v>62</v>
       </c>
       <c r="K362" s="50" t="s">
-        <v>96</v>
+        <v>246</v>
       </c>
       <c r="L362" s="50" t="s">
         <v>1</v>
@@ -31553,8 +31524,8 @@
       <c r="S362" s="50">
         <v>0</v>
       </c>
-      <c r="T362" s="50" t="s">
-        <v>61</v>
+      <c r="T362" s="50">
+        <v>0</v>
       </c>
       <c r="U362" s="50">
         <v>0</v>
@@ -31586,22 +31557,22 @@
         <v>58</v>
       </c>
       <c r="C363" s="50">
-        <v>330055</v>
+        <v>330054</v>
       </c>
       <c r="D363" s="50" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E363" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F363" s="50">
         <v>1</v>
       </c>
       <c r="G363" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H363" s="50" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="I363" s="50" t="s">
         <v>78</v>
@@ -31610,7 +31581,7 @@
         <v>62</v>
       </c>
       <c r="K363" s="50" t="s">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="L363" s="50" t="s">
         <v>1</v>
@@ -31636,8 +31607,8 @@
       <c r="S363" s="50">
         <v>0</v>
       </c>
-      <c r="T363" s="50">
-        <v>0</v>
+      <c r="T363" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U363" s="50">
         <v>0</v>
@@ -31669,22 +31640,22 @@
         <v>58</v>
       </c>
       <c r="C364" s="50">
-        <v>330056</v>
+        <v>330055</v>
       </c>
       <c r="D364" s="50" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E364" s="50">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F364" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H364" s="50" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="I364" s="50" t="s">
         <v>78</v>
@@ -31693,7 +31664,7 @@
         <v>62</v>
       </c>
       <c r="K364" s="50" t="s">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="L364" s="50" t="s">
         <v>1</v>
@@ -31752,22 +31723,22 @@
         <v>58</v>
       </c>
       <c r="C365" s="50">
-        <v>330058</v>
+        <v>330056</v>
       </c>
       <c r="D365" s="50" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E365" s="50">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F365" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G365" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H365" s="50" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="I365" s="50" t="s">
         <v>78</v>
@@ -31776,7 +31747,7 @@
         <v>62</v>
       </c>
       <c r="K365" s="50" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L365" s="50" t="s">
         <v>1</v>
@@ -31802,8 +31773,8 @@
       <c r="S365" s="50">
         <v>0</v>
       </c>
-      <c r="T365" s="50" t="s">
-        <v>61</v>
+      <c r="T365" s="50">
+        <v>0</v>
       </c>
       <c r="U365" s="50">
         <v>0</v>
@@ -31835,22 +31806,22 @@
         <v>58</v>
       </c>
       <c r="C366" s="50">
-        <v>330061</v>
+        <v>330058</v>
       </c>
       <c r="D366" s="50" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E366" s="50">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F366" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G366" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H366" s="50" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="I366" s="50" t="s">
         <v>78</v>
@@ -31859,7 +31830,7 @@
         <v>62</v>
       </c>
       <c r="K366" s="50" t="s">
-        <v>788</v>
+        <v>96</v>
       </c>
       <c r="L366" s="50" t="s">
         <v>1</v>
@@ -31885,8 +31856,8 @@
       <c r="S366" s="50">
         <v>0</v>
       </c>
-      <c r="T366" s="50">
-        <v>0</v>
+      <c r="T366" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U366" s="50">
         <v>0</v>
@@ -31918,13 +31889,13 @@
         <v>58</v>
       </c>
       <c r="C367" s="50">
-        <v>330062</v>
+        <v>330061</v>
       </c>
       <c r="D367" s="50" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E367" s="50">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F367" s="50">
         <v>0</v>
@@ -31933,7 +31904,7 @@
         <v>60</v>
       </c>
       <c r="H367" s="50" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="I367" s="50" t="s">
         <v>78</v>
@@ -31942,7 +31913,7 @@
         <v>62</v>
       </c>
       <c r="K367" s="50" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="L367" s="50" t="s">
         <v>1</v>
@@ -32001,13 +31972,13 @@
         <v>58</v>
       </c>
       <c r="C368" s="50">
-        <v>330063</v>
+        <v>330062</v>
       </c>
       <c r="D368" s="50" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E368" s="50">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F368" s="50">
         <v>0</v>
@@ -32016,7 +31987,7 @@
         <v>60</v>
       </c>
       <c r="H368" s="50" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="I368" s="50" t="s">
         <v>78</v>
@@ -32025,10 +31996,10 @@
         <v>62</v>
       </c>
       <c r="K368" s="50" t="s">
-        <v>75</v>
+        <v>791</v>
       </c>
       <c r="L368" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M368" s="50" t="s">
         <v>1</v>
@@ -32084,22 +32055,22 @@
         <v>58</v>
       </c>
       <c r="C369" s="50">
-        <v>330064</v>
+        <v>330063</v>
       </c>
       <c r="D369" s="50" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E369" s="50">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F369" s="50">
         <v>0</v>
       </c>
       <c r="G369" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H369" s="50" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="I369" s="50" t="s">
         <v>78</v>
@@ -32108,13 +32079,13 @@
         <v>62</v>
       </c>
       <c r="K369" s="50" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="L369" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M369" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N369" s="50">
         <v>33</v>
@@ -32167,22 +32138,22 @@
         <v>58</v>
       </c>
       <c r="C370" s="50">
-        <v>330065</v>
+        <v>330064</v>
       </c>
       <c r="D370" s="50" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E370" s="50">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F370" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G370" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H370" s="50" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="I370" s="50" t="s">
         <v>78</v>
@@ -32191,13 +32162,13 @@
         <v>62</v>
       </c>
       <c r="K370" s="50" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="L370" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M370" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N370" s="50">
         <v>33</v>
@@ -32217,8 +32188,8 @@
       <c r="S370" s="50">
         <v>0</v>
       </c>
-      <c r="T370" s="50" t="s">
-        <v>61</v>
+      <c r="T370" s="50">
+        <v>0</v>
       </c>
       <c r="U370" s="50">
         <v>0</v>
@@ -32250,22 +32221,22 @@
         <v>58</v>
       </c>
       <c r="C371" s="50">
-        <v>330067</v>
+        <v>330065</v>
       </c>
       <c r="D371" s="50" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E371" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F371" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G371" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H371" s="50" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="I371" s="50" t="s">
         <v>78</v>
@@ -32274,7 +32245,7 @@
         <v>62</v>
       </c>
       <c r="K371" s="50" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
       <c r="L371" s="50" t="s">
         <v>1</v>
@@ -32300,8 +32271,8 @@
       <c r="S371" s="50">
         <v>0</v>
       </c>
-      <c r="T371" s="50">
-        <v>0</v>
+      <c r="T371" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U371" s="50">
         <v>0</v>
@@ -32333,22 +32304,22 @@
         <v>58</v>
       </c>
       <c r="C372" s="50">
-        <v>330068</v>
+        <v>330067</v>
       </c>
       <c r="D372" s="50" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E372" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F372" s="50">
         <v>1</v>
       </c>
       <c r="G372" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H372" s="50" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="I372" s="50" t="s">
         <v>78</v>
@@ -32357,7 +32328,7 @@
         <v>62</v>
       </c>
       <c r="K372" s="50" t="s">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="L372" s="50" t="s">
         <v>1</v>
@@ -32383,8 +32354,8 @@
       <c r="S372" s="50">
         <v>0</v>
       </c>
-      <c r="T372" s="50" t="s">
-        <v>61</v>
+      <c r="T372" s="50">
+        <v>0</v>
       </c>
       <c r="U372" s="50">
         <v>0</v>
@@ -32416,22 +32387,22 @@
         <v>58</v>
       </c>
       <c r="C373" s="50">
-        <v>330069</v>
+        <v>330068</v>
       </c>
       <c r="D373" s="50" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E373" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F373" s="50">
         <v>1</v>
       </c>
       <c r="G373" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H373" s="50" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="I373" s="50" t="s">
         <v>78</v>
@@ -32440,10 +32411,10 @@
         <v>62</v>
       </c>
       <c r="K373" s="50" t="s">
-        <v>257</v>
+        <v>96</v>
       </c>
       <c r="L373" s="50" t="s">
-        <v>804</v>
+        <v>1</v>
       </c>
       <c r="M373" s="50" t="s">
         <v>1</v>
@@ -32454,7 +32425,9 @@
       <c r="O373" s="50">
         <v>0</v>
       </c>
-      <c r="P373" s="50"/>
+      <c r="P373" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q373" s="50">
         <v>0</v>
       </c>
@@ -32464,8 +32437,8 @@
       <c r="S373" s="50">
         <v>0</v>
       </c>
-      <c r="T373" s="50">
-        <v>0</v>
+      <c r="T373" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U373" s="50">
         <v>0</v>
@@ -32497,13 +32470,13 @@
         <v>58</v>
       </c>
       <c r="C374" s="50">
-        <v>330070</v>
+        <v>330069</v>
       </c>
       <c r="D374" s="50" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E374" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F374" s="50">
         <v>1</v>
@@ -32512,7 +32485,7 @@
         <v>60</v>
       </c>
       <c r="H374" s="50" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="I374" s="50" t="s">
         <v>78</v>
@@ -32521,10 +32494,10 @@
         <v>62</v>
       </c>
       <c r="K374" s="50" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L374" s="50" t="s">
-        <v>1</v>
+        <v>804</v>
       </c>
       <c r="M374" s="50" t="s">
         <v>1</v>
@@ -32567,6 +32540,87 @@
         <v>0</v>
       </c>
       <c r="AA374" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="50">
+        <v>370</v>
+      </c>
+      <c r="B375" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C375" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D375" s="50" t="s">
+        <v>805</v>
+      </c>
+      <c r="E375" s="50">
+        <v>3</v>
+      </c>
+      <c r="F375" s="50">
+        <v>1</v>
+      </c>
+      <c r="G375" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H375" s="50" t="s">
+        <v>806</v>
+      </c>
+      <c r="I375" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J375" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K375" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L375" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M375" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N375" s="50">
+        <v>33</v>
+      </c>
+      <c r="O375" s="50">
+        <v>0</v>
+      </c>
+      <c r="P375" s="50"/>
+      <c r="Q375" s="50">
+        <v>0</v>
+      </c>
+      <c r="R375" s="50">
+        <v>0</v>
+      </c>
+      <c r="S375" s="50">
+        <v>0</v>
+      </c>
+      <c r="T375" s="50">
+        <v>0</v>
+      </c>
+      <c r="U375" s="50">
+        <v>0</v>
+      </c>
+      <c r="V375" s="50">
+        <v>0</v>
+      </c>
+      <c r="W375" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X375" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y375" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z375" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA375" s="50" t="s">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1535,6 +1535,9 @@
   </si>
   <si>
     <t>129.25,8.0032,131.75_129.25,8.0032,136.25_124.75,8.0032,136.25_124.75,8.0032,131.75</t>
+  </si>
+  <si>
+    <t>70303</t>
   </si>
   <si>
     <t>142,7.999978,176</t>
@@ -20583,7 +20586,7 @@
         <v>0</v>
       </c>
       <c r="T223" s="50" t="s">
-        <v>61</v>
+        <v>506</v>
       </c>
       <c r="U223" s="50">
         <v>0</v>
@@ -20618,7 +20621,7 @@
         <v>74885</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E224" s="50">
         <v>48</v>
@@ -20630,7 +20633,7 @@
         <v>60</v>
       </c>
       <c r="H224" s="50" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20642,10 +20645,10 @@
         <v>327</v>
       </c>
       <c r="L224" s="50" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M224" s="50" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N224" s="50">
         <v>7</v>
@@ -20699,7 +20702,7 @@
         <v>74886</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E225" s="50">
         <v>49</v>
@@ -20711,7 +20714,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20723,7 +20726,7 @@
         <v>324</v>
       </c>
       <c r="L225" s="50" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M225" s="50" t="s">
         <v>1</v>
@@ -20780,7 +20783,7 @@
         <v>74887</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E226" s="50">
         <v>50</v>
@@ -20792,7 +20795,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20861,7 +20864,7 @@
         <v>74888</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E227" s="50">
         <v>29</v>
@@ -20873,7 +20876,7 @@
         <v>60</v>
       </c>
       <c r="H227" s="50" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I227" s="50" t="s">
         <v>78</v>
@@ -20888,7 +20891,7 @@
         <v>1</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N227" s="50">
         <v>7</v>
@@ -20942,7 +20945,7 @@
         <v>74889</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E228" s="50">
         <v>28</v>
@@ -20954,7 +20957,7 @@
         <v>60</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>78</v>
@@ -20966,7 +20969,7 @@
         <v>75</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M228" s="50" t="s">
         <v>1</v>
@@ -21023,7 +21026,7 @@
         <v>74997</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E229" s="50">
         <v>59</v>
@@ -21089,7 +21092,7 @@
         <v>0</v>
       </c>
       <c r="AA229" s="50" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="230">
@@ -21103,7 +21106,7 @@
         <v>74998</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E230" s="50">
         <v>62</v>
@@ -21163,7 +21166,7 @@
         <v>1</v>
       </c>
       <c r="Y230" s="50" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z230" s="52">
         <v>0</v>
@@ -21183,7 +21186,7 @@
         <v>74890</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E231" s="50">
         <v>4</v>
@@ -21195,7 +21198,7 @@
         <v>60</v>
       </c>
       <c r="H231" s="50" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I231" s="50" t="s">
         <v>78</v>
@@ -21266,7 +21269,7 @@
         <v>74891</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E232" s="50">
         <v>5</v>
@@ -21278,7 +21281,7 @@
         <v>60</v>
       </c>
       <c r="H232" s="50" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I232" s="50" t="s">
         <v>78</v>
@@ -21314,7 +21317,7 @@
         <v>0</v>
       </c>
       <c r="T232" s="50" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="U232" s="50">
         <v>0</v>
@@ -21349,7 +21352,7 @@
         <v>74892</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E233" s="50">
         <v>5</v>
@@ -21361,7 +21364,7 @@
         <v>138</v>
       </c>
       <c r="H233" s="50" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I233" s="50" t="s">
         <v>78</v>
@@ -21397,7 +21400,7 @@
         <v>0</v>
       </c>
       <c r="T233" s="50" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="U233" s="50">
         <v>0</v>
@@ -21432,7 +21435,7 @@
         <v>74893</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E234" s="50">
         <v>16</v>
@@ -21444,7 +21447,7 @@
         <v>138</v>
       </c>
       <c r="H234" s="50" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I234" s="50" t="s">
         <v>78</v>
@@ -21456,7 +21459,7 @@
         <v>355</v>
       </c>
       <c r="L234" s="50" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M234" s="50" t="s">
         <v>1</v>
@@ -21490,7 +21493,7 @@
         <v>1</v>
       </c>
       <c r="X234" s="50" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Y234" s="50" t="s">
         <v>1</v>
@@ -21513,7 +21516,7 @@
         <v>74894</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E235" s="50">
         <v>3</v>
@@ -21525,7 +21528,7 @@
         <v>60</v>
       </c>
       <c r="H235" s="50" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I235" s="50" t="s">
         <v>78</v>
@@ -21594,7 +21597,7 @@
         <v>74895</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E236" s="50">
         <v>4</v>
@@ -21606,7 +21609,7 @@
         <v>83</v>
       </c>
       <c r="H236" s="50" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I236" s="50" t="s">
         <v>78</v>
@@ -21677,7 +21680,7 @@
         <v>74896</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E237" s="50">
         <v>2</v>
@@ -21704,7 +21707,7 @@
       </c>
       <c r="O237" s="50"/>
       <c r="P237" s="50" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q237" s="50"/>
       <c r="R237" s="50"/>
@@ -21733,7 +21736,7 @@
         <v>74897</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E238" s="50">
         <v>6</v>
@@ -21745,7 +21748,7 @@
         <v>94</v>
       </c>
       <c r="H238" s="50" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I238" s="50" t="s">
         <v>78</v>
@@ -21760,7 +21763,7 @@
         <v>1</v>
       </c>
       <c r="M238" s="50" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N238" s="50">
         <v>7</v>
@@ -21814,7 +21817,7 @@
         <v>74898</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E239" s="50">
         <v>7</v>
@@ -21826,7 +21829,7 @@
         <v>138</v>
       </c>
       <c r="H239" s="50" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I239" s="50" t="s">
         <v>78</v>
@@ -21838,7 +21841,7 @@
         <v>147</v>
       </c>
       <c r="L239" s="50" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M239" s="50" t="s">
         <v>1</v>
@@ -21895,7 +21898,7 @@
         <v>74899</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E240" s="50">
         <v>7</v>
@@ -21907,7 +21910,7 @@
         <v>138</v>
       </c>
       <c r="H240" s="50" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I240" s="50" t="s">
         <v>78</v>
@@ -21919,7 +21922,7 @@
         <v>147</v>
       </c>
       <c r="L240" s="50" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M240" s="50" t="s">
         <v>1</v>
@@ -21976,7 +21979,7 @@
         <v>74900</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E241" s="50">
         <v>7</v>
@@ -21988,7 +21991,7 @@
         <v>138</v>
       </c>
       <c r="H241" s="50" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I241" s="50" t="s">
         <v>78</v>
@@ -22000,7 +22003,7 @@
         <v>147</v>
       </c>
       <c r="L241" s="50" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M241" s="50" t="s">
         <v>1</v>
@@ -22057,7 +22060,7 @@
         <v>74901</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E242" s="50">
         <v>5</v>
@@ -22069,7 +22072,7 @@
         <v>83</v>
       </c>
       <c r="H242" s="50" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I242" s="50" t="s">
         <v>78</v>
@@ -22105,7 +22108,7 @@
         <v>0</v>
       </c>
       <c r="T242" s="50" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="U242" s="50">
         <v>0</v>
@@ -22140,7 +22143,7 @@
         <v>74905</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E243" s="50">
         <v>2</v>
@@ -22167,7 +22170,7 @@
       </c>
       <c r="O243" s="50"/>
       <c r="P243" s="50" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q243" s="50"/>
       <c r="R243" s="50"/>
@@ -22176,7 +22179,7 @@
       <c r="U243" s="50"/>
       <c r="V243" s="50"/>
       <c r="W243" s="50" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="X243" s="50"/>
       <c r="Y243" s="50"/>
@@ -22196,7 +22199,7 @@
         <v>74906</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E244" s="50">
         <v>13</v>
@@ -22214,13 +22217,13 @@
         <v>62</v>
       </c>
       <c r="K244" s="50" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L244" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M244" s="50" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N244" s="50">
         <v>7</v>
@@ -22274,7 +22277,7 @@
         <v>74907</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E245" s="50">
         <v>13</v>
@@ -22352,7 +22355,7 @@
         <v>74908</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E246" s="50">
         <v>13</v>
@@ -22370,13 +22373,13 @@
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M246" s="50" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N246" s="50">
         <v>7</v>
@@ -22430,7 +22433,7 @@
         <v>74909</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E247" s="50">
         <v>13</v>
@@ -22508,7 +22511,7 @@
         <v>74999</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E248" s="50">
         <v>5</v>
@@ -22520,7 +22523,7 @@
         <v>94</v>
       </c>
       <c r="H248" s="50" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I248" s="50" t="s">
         <v>78</v>
@@ -22556,7 +22559,7 @@
         <v>0</v>
       </c>
       <c r="T248" s="50" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="U248" s="50">
         <v>0</v>
@@ -22591,7 +22594,7 @@
         <v>74979</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E249" s="50">
         <v>45</v>
@@ -22603,7 +22606,7 @@
         <v>138</v>
       </c>
       <c r="H249" s="50" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I249" s="50" t="s">
         <v>78</v>
@@ -22612,7 +22615,7 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22672,7 +22675,7 @@
         <v>74982</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E250" s="50">
         <v>46</v>
@@ -22684,7 +22687,7 @@
         <v>60</v>
       </c>
       <c r="H250" s="50" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>78</v>
@@ -22693,7 +22696,7 @@
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
@@ -22753,7 +22756,7 @@
         <v>74984</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E251" s="50">
         <v>46</v>
@@ -22765,7 +22768,7 @@
         <v>60</v>
       </c>
       <c r="H251" s="50" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I251" s="50" t="s">
         <v>78</v>
@@ -22774,7 +22777,7 @@
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L251" s="50" t="s">
         <v>1</v>
@@ -22834,7 +22837,7 @@
         <v>74981</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E252" s="50">
         <v>47</v>
@@ -22846,7 +22849,7 @@
         <v>94</v>
       </c>
       <c r="H252" s="50" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I252" s="50" t="s">
         <v>78</v>
@@ -22855,13 +22858,13 @@
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L252" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M252" s="50" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N252" s="50">
         <v>7</v>
@@ -22915,7 +22918,7 @@
         <v>74983</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E253" s="50">
         <v>16</v>
@@ -22927,7 +22930,7 @@
         <v>60</v>
       </c>
       <c r="H253" s="50" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I253" s="50" t="s">
         <v>78</v>
@@ -22939,7 +22942,7 @@
         <v>192</v>
       </c>
       <c r="L253" s="50" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M253" s="50" t="s">
         <v>1</v>
@@ -22996,7 +22999,7 @@
         <v>74985</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E254" s="50">
         <v>46</v>
@@ -23008,7 +23011,7 @@
         <v>60</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -23017,7 +23020,7 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L254" s="50" t="s">
         <v>1</v>
@@ -23077,7 +23080,7 @@
         <v>74988</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E255" s="50">
         <v>2</v>
@@ -23102,7 +23105,7 @@
       </c>
       <c r="O255" s="50"/>
       <c r="P255" s="50" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q255" s="50"/>
       <c r="R255" s="50"/>
@@ -23127,7 +23130,7 @@
         <v>74991</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E256" s="50">
         <v>18</v>
@@ -23139,7 +23142,7 @@
         <v>94</v>
       </c>
       <c r="H256" s="50" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I256" s="50" t="s">
         <v>78</v>
@@ -23208,7 +23211,7 @@
         <v>74990</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E257" s="50">
         <v>17</v>
@@ -23220,7 +23223,7 @@
         <v>60</v>
       </c>
       <c r="H257" s="50" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I257" s="50" t="s">
         <v>78</v>
@@ -23232,7 +23235,7 @@
         <v>124</v>
       </c>
       <c r="L257" s="50" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M257" s="50" t="s">
         <v>1</v>
@@ -23289,7 +23292,7 @@
         <v>74989</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E258" s="50">
         <v>14</v>
@@ -23369,7 +23372,7 @@
         <v>75000</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E259" s="50">
         <v>5</v>
@@ -23381,7 +23384,7 @@
         <v>94</v>
       </c>
       <c r="H259" s="50" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I259" s="50" t="s">
         <v>78</v>
@@ -23417,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="T259" s="50" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="U259" s="50">
         <v>0</v>
@@ -23452,7 +23455,7 @@
         <v>75001</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E260" s="50">
         <v>16</v>
@@ -23464,7 +23467,7 @@
         <v>138</v>
       </c>
       <c r="H260" s="50" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -23476,7 +23479,7 @@
         <v>79</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M260" s="50" t="s">
         <v>1</v>
@@ -23533,7 +23536,7 @@
         <v>75002</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E261" s="50">
         <v>3</v>
@@ -23545,7 +23548,7 @@
         <v>60</v>
       </c>
       <c r="H261" s="50" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I261" s="50" t="s">
         <v>78</v>
@@ -23614,7 +23617,7 @@
         <v>75003</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E262" s="50">
         <v>16</v>
@@ -23626,7 +23629,7 @@
         <v>138</v>
       </c>
       <c r="H262" s="50" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I262" s="50" t="s">
         <v>78</v>
@@ -23638,7 +23641,7 @@
         <v>192</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M262" s="50" t="s">
         <v>1</v>
@@ -23695,7 +23698,7 @@
         <v>75004</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E263" s="50">
         <v>52</v>
@@ -23716,10 +23719,10 @@
         <v>285</v>
       </c>
       <c r="L263" s="50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N263" s="50">
         <v>7</v>
@@ -23773,7 +23776,7 @@
         <v>75005</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E264" s="50">
         <v>51</v>
@@ -23785,7 +23788,7 @@
         <v>60</v>
       </c>
       <c r="H264" s="50" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I264" s="50" t="s">
         <v>78</v>
@@ -23854,7 +23857,7 @@
         <v>75006</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E265" s="50">
         <v>52</v>
@@ -23875,10 +23878,10 @@
         <v>271</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N265" s="50">
         <v>7</v>
@@ -23932,7 +23935,7 @@
         <v>75007</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E266" s="50">
         <v>51</v>
@@ -23944,7 +23947,7 @@
         <v>60</v>
       </c>
       <c r="H266" s="50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I266" s="50" t="s">
         <v>78</v>
@@ -24013,7 +24016,7 @@
         <v>75008</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E267" s="50">
         <v>56</v>
@@ -24031,7 +24034,7 @@
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -24091,7 +24094,7 @@
         <v>75009</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E268" s="50">
         <v>56</v>
@@ -24169,7 +24172,7 @@
         <v>75010</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E269" s="50">
         <v>56</v>
@@ -24247,7 +24250,7 @@
         <v>75011</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E270" s="50">
         <v>56</v>
@@ -24325,7 +24328,7 @@
         <v>75012</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E271" s="50">
         <v>56</v>
@@ -24403,7 +24406,7 @@
         <v>75013</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E272" s="50">
         <v>56</v>
@@ -24481,7 +24484,7 @@
         <v>75014</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E273" s="50">
         <v>56</v>
@@ -24559,7 +24562,7 @@
         <v>75015</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E274" s="50">
         <v>56</v>
@@ -24637,7 +24640,7 @@
         <v>75016</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E275" s="50">
         <v>56</v>
@@ -24715,7 +24718,7 @@
         <v>75017</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E276" s="50">
         <v>56</v>
@@ -24793,7 +24796,7 @@
         <v>75018</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E277" s="50">
         <v>56</v>
@@ -24871,7 +24874,7 @@
         <v>75019</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E278" s="50">
         <v>56</v>
@@ -24949,7 +24952,7 @@
         <v>75020</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
@@ -25027,7 +25030,7 @@
         <v>75021</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25105,7 +25108,7 @@
         <v>75022</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25183,7 +25186,7 @@
         <v>75023</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25261,7 +25264,7 @@
         <v>75024</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25339,7 +25342,7 @@
         <v>75025</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25417,7 +25420,7 @@
         <v>75026</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25495,7 +25498,7 @@
         <v>75027</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25573,7 +25576,7 @@
         <v>75028</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25651,7 +25654,7 @@
         <v>75029</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25729,7 +25732,7 @@
         <v>75030</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E289" s="50">
         <v>56</v>
@@ -25807,7 +25810,7 @@
         <v>84928</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E290" s="50">
         <v>12</v>
@@ -25887,7 +25890,7 @@
         <v>84929</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E291" s="50">
         <v>30</v>
@@ -25899,7 +25902,7 @@
         <v>83</v>
       </c>
       <c r="H291" s="50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I291" s="50" t="s">
         <v>78</v>
@@ -25911,7 +25914,7 @@
         <v>377</v>
       </c>
       <c r="L291" s="50" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M291" s="50" t="s">
         <v>1</v>
@@ -25968,7 +25971,7 @@
         <v>84930</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E292" s="50">
         <v>57</v>
@@ -25989,10 +25992,10 @@
         <v>388</v>
       </c>
       <c r="L292" s="50" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M292" s="50" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N292" s="50">
         <v>8</v>
@@ -26046,7 +26049,7 @@
         <v>84931</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E293" s="50">
         <v>32</v>
@@ -26058,7 +26061,7 @@
         <v>138</v>
       </c>
       <c r="H293" s="50" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I293" s="50" t="s">
         <v>78</v>
@@ -26127,7 +26130,7 @@
         <v>84932</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E294" s="50">
         <v>57</v>
@@ -26148,10 +26151,10 @@
         <v>388</v>
       </c>
       <c r="L294" s="50" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M294" s="50" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N294" s="50">
         <v>8</v>
@@ -26205,7 +26208,7 @@
         <v>84933</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E295" s="50">
         <v>32</v>
@@ -26217,7 +26220,7 @@
         <v>60</v>
       </c>
       <c r="H295" s="50" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I295" s="50" t="s">
         <v>78</v>
@@ -26286,7 +26289,7 @@
         <v>84934</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E296" s="50">
         <v>31</v>
@@ -26298,7 +26301,7 @@
         <v>138</v>
       </c>
       <c r="H296" s="50" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I296" s="50" t="s">
         <v>78</v>
@@ -26367,7 +26370,7 @@
         <v>84935</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E297" s="50">
         <v>31</v>
@@ -26379,7 +26382,7 @@
         <v>60</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -26448,7 +26451,7 @@
         <v>84936</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E298" s="50">
         <v>31</v>
@@ -26460,7 +26463,7 @@
         <v>60</v>
       </c>
       <c r="H298" s="50" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I298" s="50" t="s">
         <v>78</v>
@@ -26529,7 +26532,7 @@
         <v>84937</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E299" s="50">
         <v>31</v>
@@ -26541,7 +26544,7 @@
         <v>138</v>
       </c>
       <c r="H299" s="50" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I299" s="50" t="s">
         <v>78</v>
@@ -26610,7 +26613,7 @@
         <v>84938</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E300" s="50">
         <v>31</v>
@@ -26622,7 +26625,7 @@
         <v>60</v>
       </c>
       <c r="H300" s="50" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I300" s="50" t="s">
         <v>78</v>
@@ -26691,7 +26694,7 @@
         <v>84939</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E301" s="50">
         <v>15</v>
@@ -26703,7 +26706,7 @@
         <v>60</v>
       </c>
       <c r="H301" s="50" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I301" s="50" t="s">
         <v>78</v>
@@ -26772,7 +26775,7 @@
         <v>84940</v>
       </c>
       <c r="D302" s="50" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E302" s="50">
         <v>15</v>
@@ -26784,7 +26787,7 @@
         <v>60</v>
       </c>
       <c r="H302" s="50" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>78</v>
@@ -26853,7 +26856,7 @@
         <v>84941</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E303" s="50">
         <v>16</v>
@@ -26865,7 +26868,7 @@
         <v>60</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>78</v>
@@ -26877,7 +26880,7 @@
         <v>192</v>
       </c>
       <c r="L303" s="50" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M303" s="50" t="s">
         <v>1</v>
@@ -26934,7 +26937,7 @@
         <v>84942</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E304" s="50">
         <v>52</v>
@@ -26955,10 +26958,10 @@
         <v>285</v>
       </c>
       <c r="L304" s="50" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -27012,7 +27015,7 @@
         <v>84943</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E305" s="50">
         <v>51</v>
@@ -27024,7 +27027,7 @@
         <v>60</v>
       </c>
       <c r="H305" s="50" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I305" s="50" t="s">
         <v>78</v>
@@ -27093,7 +27096,7 @@
         <v>84944</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E306" s="50">
         <v>52</v>
@@ -27114,10 +27117,10 @@
         <v>271</v>
       </c>
       <c r="L306" s="50" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M306" s="50" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N306" s="50">
         <v>8</v>
@@ -27171,7 +27174,7 @@
         <v>84945</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E307" s="50">
         <v>51</v>
@@ -27183,7 +27186,7 @@
         <v>60</v>
       </c>
       <c r="H307" s="50" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I307" s="50" t="s">
         <v>78</v>
@@ -27252,7 +27255,7 @@
         <v>84946</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E308" s="50">
         <v>56</v>
@@ -27270,7 +27273,7 @@
         <v>62</v>
       </c>
       <c r="K308" s="50" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L308" s="50" t="s">
         <v>1</v>
@@ -27330,7 +27333,7 @@
         <v>84947</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E309" s="50">
         <v>56</v>
@@ -27408,7 +27411,7 @@
         <v>84948</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E310" s="50">
         <v>56</v>
@@ -27486,7 +27489,7 @@
         <v>84949</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E311" s="50">
         <v>56</v>
@@ -27564,7 +27567,7 @@
         <v>84950</v>
       </c>
       <c r="D312" s="50" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E312" s="50">
         <v>56</v>
@@ -27642,7 +27645,7 @@
         <v>84951</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E313" s="50">
         <v>56</v>
@@ -27720,7 +27723,7 @@
         <v>84952</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E314" s="50">
         <v>56</v>
@@ -27798,7 +27801,7 @@
         <v>84953</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E315" s="50">
         <v>56</v>
@@ -27876,7 +27879,7 @@
         <v>84954</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E316" s="50">
         <v>56</v>
@@ -27954,7 +27957,7 @@
         <v>84955</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E317" s="50">
         <v>56</v>
@@ -28032,7 +28035,7 @@
         <v>84956</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E318" s="50">
         <v>56</v>
@@ -28110,7 +28113,7 @@
         <v>84957</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E319" s="50">
         <v>56</v>
@@ -28188,7 +28191,7 @@
         <v>84958</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E320" s="50">
         <v>56</v>
@@ -28266,7 +28269,7 @@
         <v>84959</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E321" s="50">
         <v>56</v>
@@ -28344,7 +28347,7 @@
         <v>84960</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E322" s="50">
         <v>56</v>
@@ -28422,7 +28425,7 @@
         <v>84961</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E323" s="50">
         <v>56</v>
@@ -28500,7 +28503,7 @@
         <v>84962</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E324" s="50">
         <v>56</v>
@@ -28578,7 +28581,7 @@
         <v>84963</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E325" s="50">
         <v>56</v>
@@ -28656,7 +28659,7 @@
         <v>84964</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E326" s="50">
         <v>56</v>
@@ -28734,7 +28737,7 @@
         <v>84965</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E327" s="50">
         <v>56</v>
@@ -28812,7 +28815,7 @@
         <v>84966</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E328" s="50">
         <v>56</v>
@@ -28890,7 +28893,7 @@
         <v>84967</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E329" s="50">
         <v>56</v>
@@ -28968,7 +28971,7 @@
         <v>84968</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E330" s="50">
         <v>56</v>
@@ -29046,7 +29049,7 @@
         <v>84969</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E331" s="50">
         <v>45</v>
@@ -29058,7 +29061,7 @@
         <v>83</v>
       </c>
       <c r="H331" s="50" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I331" s="50" t="s">
         <v>78</v>
@@ -29067,7 +29070,7 @@
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -29127,7 +29130,7 @@
         <v>84970</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E332" s="50">
         <v>46</v>
@@ -29136,10 +29139,10 @@
         <v>0</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H332" s="50" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I332" s="50" t="s">
         <v>78</v>
@@ -29148,7 +29151,7 @@
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
@@ -29208,7 +29211,7 @@
         <v>84971</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E333" s="50">
         <v>47</v>
@@ -29220,7 +29223,7 @@
         <v>94</v>
       </c>
       <c r="H333" s="50" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I333" s="50" t="s">
         <v>78</v>
@@ -29229,13 +29232,13 @@
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M333" s="50" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N333" s="50">
         <v>8</v>
@@ -29289,7 +29292,7 @@
         <v>84972</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E334" s="50">
         <v>46</v>
@@ -29298,10 +29301,10 @@
         <v>0</v>
       </c>
       <c r="G334" s="50" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H334" s="50" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I334" s="50" t="s">
         <v>78</v>
@@ -29310,7 +29313,7 @@
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L334" s="50" t="s">
         <v>1</v>
@@ -29370,7 +29373,7 @@
         <v>84973</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E335" s="50">
         <v>16</v>
@@ -29382,7 +29385,7 @@
         <v>60</v>
       </c>
       <c r="H335" s="50" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I335" s="50" t="s">
         <v>78</v>
@@ -29394,7 +29397,7 @@
         <v>192</v>
       </c>
       <c r="L335" s="50" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M335" s="50" t="s">
         <v>1</v>
@@ -29451,7 +29454,7 @@
         <v>84974</v>
       </c>
       <c r="D336" s="50" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E336" s="50">
         <v>46</v>
@@ -29463,7 +29466,7 @@
         <v>60</v>
       </c>
       <c r="H336" s="50" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I336" s="50" t="s">
         <v>78</v>
@@ -29472,7 +29475,7 @@
         <v>62</v>
       </c>
       <c r="K336" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L336" s="50" t="s">
         <v>1</v>
@@ -29532,7 +29535,7 @@
         <v>84976</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E337" s="50">
         <v>2</v>
@@ -29557,7 +29560,7 @@
       </c>
       <c r="O337" s="50"/>
       <c r="P337" s="50" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Q337" s="50"/>
       <c r="R337" s="50"/>
@@ -29582,7 +29585,7 @@
         <v>84977</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E338" s="50">
         <v>2</v>
@@ -29607,7 +29610,7 @@
       </c>
       <c r="O338" s="50"/>
       <c r="P338" s="50" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Q338" s="50"/>
       <c r="R338" s="50"/>
@@ -29632,7 +29635,7 @@
         <v>84978</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E339" s="50">
         <v>2</v>
@@ -29657,7 +29660,7 @@
       </c>
       <c r="O339" s="50"/>
       <c r="P339" s="50" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Q339" s="50"/>
       <c r="R339" s="50"/>
@@ -29682,7 +29685,7 @@
         <v>84979</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E340" s="50">
         <v>48</v>
@@ -29694,7 +29697,7 @@
         <v>83</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29706,10 +29709,10 @@
         <v>327</v>
       </c>
       <c r="L340" s="50" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M340" s="50" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N340" s="50">
         <v>8</v>
@@ -29763,7 +29766,7 @@
         <v>84980</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E341" s="50">
         <v>49</v>
@@ -29775,7 +29778,7 @@
         <v>60</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29787,7 +29790,7 @@
         <v>324</v>
       </c>
       <c r="L341" s="50" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M341" s="50" t="s">
         <v>1</v>
@@ -29844,7 +29847,7 @@
         <v>84981</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E342" s="50">
         <v>50</v>
@@ -29856,7 +29859,7 @@
         <v>60</v>
       </c>
       <c r="H342" s="50" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I342" s="50" t="s">
         <v>78</v>
@@ -29925,7 +29928,7 @@
         <v>84982</v>
       </c>
       <c r="D343" s="50" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E343" s="50">
         <v>23</v>
@@ -29943,13 +29946,13 @@
         <v>62</v>
       </c>
       <c r="K343" s="50" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L343" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M343" s="50" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N343" s="50">
         <v>8</v>
@@ -30005,7 +30008,7 @@
         <v>84983</v>
       </c>
       <c r="D344" s="50" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E344" s="50">
         <v>24</v>
@@ -30017,7 +30020,7 @@
         <v>60</v>
       </c>
       <c r="H344" s="50" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I344" s="50" t="s">
         <v>78</v>
@@ -30026,7 +30029,7 @@
         <v>62</v>
       </c>
       <c r="K344" s="50" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L344" s="50" t="s">
         <v>1</v>
@@ -30088,7 +30091,7 @@
         <v>84984</v>
       </c>
       <c r="D345" s="50" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E345" s="50">
         <v>25</v>
@@ -30100,7 +30103,7 @@
         <v>60</v>
       </c>
       <c r="H345" s="50" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I345" s="50" t="s">
         <v>78</v>
@@ -30109,7 +30112,7 @@
         <v>62</v>
       </c>
       <c r="K345" s="50" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L345" s="50" t="s">
         <v>1</v>
@@ -30171,7 +30174,7 @@
         <v>330037</v>
       </c>
       <c r="D346" s="50" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E346" s="50">
         <v>5</v>
@@ -30183,7 +30186,7 @@
         <v>60</v>
       </c>
       <c r="H346" s="50" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I346" s="50" t="s">
         <v>78</v>
@@ -30254,7 +30257,7 @@
         <v>330038</v>
       </c>
       <c r="D347" s="50" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E347" s="50">
         <v>6</v>
@@ -30266,7 +30269,7 @@
         <v>94</v>
       </c>
       <c r="H347" s="50" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I347" s="50" t="s">
         <v>78</v>
@@ -30281,7 +30284,7 @@
         <v>1</v>
       </c>
       <c r="M347" s="50" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N347" s="50">
         <v>33</v>
@@ -30335,7 +30338,7 @@
         <v>330039</v>
       </c>
       <c r="D348" s="50" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E348" s="50">
         <v>7</v>
@@ -30347,7 +30350,7 @@
         <v>138</v>
       </c>
       <c r="H348" s="50" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I348" s="50" t="s">
         <v>78</v>
@@ -30359,7 +30362,7 @@
         <v>147</v>
       </c>
       <c r="L348" s="50" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M348" s="50" t="s">
         <v>1</v>
@@ -30416,7 +30419,7 @@
         <v>330040</v>
       </c>
       <c r="D349" s="50" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E349" s="50">
         <v>7</v>
@@ -30428,7 +30431,7 @@
         <v>138</v>
       </c>
       <c r="H349" s="50" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I349" s="50" t="s">
         <v>78</v>
@@ -30440,7 +30443,7 @@
         <v>147</v>
       </c>
       <c r="L349" s="50" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M349" s="50" t="s">
         <v>1</v>
@@ -30497,7 +30500,7 @@
         <v>330041</v>
       </c>
       <c r="D350" s="50" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E350" s="50">
         <v>7</v>
@@ -30509,7 +30512,7 @@
         <v>138</v>
       </c>
       <c r="H350" s="50" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I350" s="50" t="s">
         <v>78</v>
@@ -30521,7 +30524,7 @@
         <v>147</v>
       </c>
       <c r="L350" s="50" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M350" s="50" t="s">
         <v>1</v>
@@ -30578,7 +30581,7 @@
         <v>330042</v>
       </c>
       <c r="D351" s="50" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E351" s="50">
         <v>20</v>
@@ -30590,7 +30593,7 @@
         <v>60</v>
       </c>
       <c r="H351" s="50" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I351" s="50" t="s">
         <v>78</v>
@@ -30602,10 +30605,10 @@
         <v>233</v>
       </c>
       <c r="L351" s="50" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M351" s="50" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N351" s="50">
         <v>33</v>
@@ -30659,7 +30662,7 @@
         <v>330043</v>
       </c>
       <c r="D352" s="50" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E352" s="50">
         <v>19</v>
@@ -30671,7 +30674,7 @@
         <v>60</v>
       </c>
       <c r="H352" s="50" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I352" s="50" t="s">
         <v>78</v>
@@ -30740,7 +30743,7 @@
         <v>330044</v>
       </c>
       <c r="D353" s="50" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E353" s="50">
         <v>16</v>
@@ -30752,7 +30755,7 @@
         <v>60</v>
       </c>
       <c r="H353" s="50" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I353" s="50" t="s">
         <v>78</v>
@@ -30764,7 +30767,7 @@
         <v>192</v>
       </c>
       <c r="L353" s="50" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M353" s="50" t="s">
         <v>1</v>
@@ -30821,7 +30824,7 @@
         <v>330045</v>
       </c>
       <c r="D354" s="50" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E354" s="50">
         <v>5</v>
@@ -30833,7 +30836,7 @@
         <v>83</v>
       </c>
       <c r="H354" s="50" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="I354" s="50" t="s">
         <v>78</v>
@@ -30904,7 +30907,7 @@
         <v>330046</v>
       </c>
       <c r="D355" s="50" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E355" s="50">
         <v>16</v>
@@ -30916,7 +30919,7 @@
         <v>83</v>
       </c>
       <c r="H355" s="50" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I355" s="50" t="s">
         <v>78</v>
@@ -30928,7 +30931,7 @@
         <v>461</v>
       </c>
       <c r="L355" s="50" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M355" s="50" t="s">
         <v>1</v>
@@ -30985,7 +30988,7 @@
         <v>330047</v>
       </c>
       <c r="D356" s="50" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E356" s="50">
         <v>3</v>
@@ -30997,7 +31000,7 @@
         <v>60</v>
       </c>
       <c r="H356" s="50" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I356" s="50" t="s">
         <v>78</v>
@@ -31066,7 +31069,7 @@
         <v>330048</v>
       </c>
       <c r="D357" s="50" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E357" s="50">
         <v>5</v>
@@ -31078,7 +31081,7 @@
         <v>60</v>
       </c>
       <c r="H357" s="50" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I357" s="50" t="s">
         <v>78</v>
@@ -31149,7 +31152,7 @@
         <v>330049</v>
       </c>
       <c r="D358" s="50" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E358" s="50">
         <v>43</v>
@@ -31161,7 +31164,7 @@
         <v>60</v>
       </c>
       <c r="H358" s="50" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I358" s="50" t="s">
         <v>78</v>
@@ -31173,7 +31176,7 @@
         <v>100</v>
       </c>
       <c r="L358" s="50" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M358" s="50" t="s">
         <v>1</v>
@@ -31230,7 +31233,7 @@
         <v>330050</v>
       </c>
       <c r="D359" s="50" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E359" s="50">
         <v>44</v>
@@ -31242,7 +31245,7 @@
         <v>60</v>
       </c>
       <c r="H359" s="50" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I359" s="50" t="s">
         <v>78</v>
@@ -31311,7 +31314,7 @@
         <v>330051</v>
       </c>
       <c r="D360" s="50" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E360" s="50">
         <v>4</v>
@@ -31323,7 +31326,7 @@
         <v>138</v>
       </c>
       <c r="H360" s="50" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I360" s="50" t="s">
         <v>78</v>
@@ -31394,7 +31397,7 @@
         <v>330052</v>
       </c>
       <c r="D361" s="50" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E361" s="50">
         <v>4</v>
@@ -31406,7 +31409,7 @@
         <v>138</v>
       </c>
       <c r="H361" s="50" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I361" s="50" t="s">
         <v>78</v>
@@ -31477,7 +31480,7 @@
         <v>330053</v>
       </c>
       <c r="D362" s="50" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E362" s="50">
         <v>4</v>
@@ -31489,7 +31492,7 @@
         <v>60</v>
       </c>
       <c r="H362" s="50" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I362" s="50" t="s">
         <v>78</v>
@@ -31560,7 +31563,7 @@
         <v>330054</v>
       </c>
       <c r="D363" s="50" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E363" s="50">
         <v>5</v>
@@ -31572,7 +31575,7 @@
         <v>60</v>
       </c>
       <c r="H363" s="50" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I363" s="50" t="s">
         <v>78</v>
@@ -31643,7 +31646,7 @@
         <v>330055</v>
       </c>
       <c r="D364" s="50" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E364" s="50">
         <v>4</v>
@@ -31655,7 +31658,7 @@
         <v>83</v>
       </c>
       <c r="H364" s="50" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I364" s="50" t="s">
         <v>78</v>
@@ -31726,7 +31729,7 @@
         <v>330056</v>
       </c>
       <c r="D365" s="50" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E365" s="50">
         <v>54</v>
@@ -31738,7 +31741,7 @@
         <v>138</v>
       </c>
       <c r="H365" s="50" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I365" s="50" t="s">
         <v>78</v>
@@ -31809,7 +31812,7 @@
         <v>330058</v>
       </c>
       <c r="D366" s="50" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E366" s="50">
         <v>5</v>
@@ -31821,7 +31824,7 @@
         <v>138</v>
       </c>
       <c r="H366" s="50" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I366" s="50" t="s">
         <v>78</v>
@@ -31892,7 +31895,7 @@
         <v>330061</v>
       </c>
       <c r="D367" s="50" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E367" s="50">
         <v>39</v>
@@ -31904,7 +31907,7 @@
         <v>60</v>
       </c>
       <c r="H367" s="50" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="I367" s="50" t="s">
         <v>78</v>
@@ -31913,7 +31916,7 @@
         <v>62</v>
       </c>
       <c r="K367" s="50" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L367" s="50" t="s">
         <v>1</v>
@@ -31975,7 +31978,7 @@
         <v>330062</v>
       </c>
       <c r="D368" s="50" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E368" s="50">
         <v>40</v>
@@ -31987,7 +31990,7 @@
         <v>60</v>
       </c>
       <c r="H368" s="50" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I368" s="50" t="s">
         <v>78</v>
@@ -31996,7 +31999,7 @@
         <v>62</v>
       </c>
       <c r="K368" s="50" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="L368" s="50" t="s">
         <v>1</v>
@@ -32058,7 +32061,7 @@
         <v>330063</v>
       </c>
       <c r="D369" s="50" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E369" s="50">
         <v>28</v>
@@ -32070,7 +32073,7 @@
         <v>60</v>
       </c>
       <c r="H369" s="50" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I369" s="50" t="s">
         <v>78</v>
@@ -32141,7 +32144,7 @@
         <v>330064</v>
       </c>
       <c r="D370" s="50" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E370" s="50">
         <v>29</v>
@@ -32153,7 +32156,7 @@
         <v>138</v>
       </c>
       <c r="H370" s="50" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I370" s="50" t="s">
         <v>78</v>
@@ -32224,7 +32227,7 @@
         <v>330065</v>
       </c>
       <c r="D371" s="50" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E371" s="50">
         <v>5</v>
@@ -32236,7 +32239,7 @@
         <v>60</v>
       </c>
       <c r="H371" s="50" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I371" s="50" t="s">
         <v>78</v>
@@ -32307,7 +32310,7 @@
         <v>330067</v>
       </c>
       <c r="D372" s="50" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E372" s="50">
         <v>4</v>
@@ -32319,7 +32322,7 @@
         <v>60</v>
       </c>
       <c r="H372" s="50" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="I372" s="50" t="s">
         <v>78</v>
@@ -32390,7 +32393,7 @@
         <v>330068</v>
       </c>
       <c r="D373" s="50" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E373" s="50">
         <v>5</v>
@@ -32402,7 +32405,7 @@
         <v>138</v>
       </c>
       <c r="H373" s="50" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I373" s="50" t="s">
         <v>78</v>
@@ -32473,7 +32476,7 @@
         <v>330069</v>
       </c>
       <c r="D374" s="50" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E374" s="50">
         <v>16</v>
@@ -32485,7 +32488,7 @@
         <v>60</v>
       </c>
       <c r="H374" s="50" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I374" s="50" t="s">
         <v>78</v>
@@ -32497,7 +32500,7 @@
         <v>257</v>
       </c>
       <c r="L374" s="50" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M374" s="50" t="s">
         <v>1</v>
@@ -32554,7 +32557,7 @@
         <v>330070</v>
       </c>
       <c r="D375" s="50" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E375" s="50">
         <v>3</v>
@@ -32566,7 +32569,7 @@
         <v>60</v>
       </c>
       <c r="H375" s="50" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I375" s="50" t="s">
         <v>78</v>

--- a/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/doll_map_puzzle_new_v8【人偶-地图数据-新解谜】.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="816">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1300,10 +1300,10 @@
     <t>70201</t>
   </si>
   <si>
-    <t>132,8.001535,52</t>
-  </si>
-  <si>
-    <t>130.5,8.001536,50_133.5,8.001536,50_133.5,8.001536,54_130.5,8.001536,54</t>
+    <t>132,8.003199,52</t>
+  </si>
+  <si>
+    <t>130.5,8.0032,50_133.5,8.0032,50_133.5,8.0032,54_130.5,8.0032,54</t>
   </si>
   <si>
     <t>74858,74859,74860</t>
@@ -1312,25 +1312,25 @@
     <t>70001_0</t>
   </si>
   <si>
-    <t>117,8.003199,73.8584136962891</t>
-  </si>
-  <si>
-    <t>118,8.0032,72.85841_118,8.0032,74.85841_116,8.0032,74.85841_116,8.0032,72.85841</t>
+    <t>117,8.003199,74</t>
+  </si>
+  <si>
+    <t>118,8.0032,72_118,8.0032,76_116,8.0032,76_116,8.0032,72</t>
   </si>
   <si>
     <t>74857</t>
   </si>
   <si>
-    <t>119,8.003199,73.8584136962891</t>
-  </si>
-  <si>
-    <t>120,8.0032,72.85841_120,8.0032,74.85841_118,8.0032,74.85841_118,8.0032,72.85841</t>
-  </si>
-  <si>
-    <t>121,8.003199,73.8584136962891</t>
-  </si>
-  <si>
-    <t>122,8.0032,72.85841_122,8.0032,74.85841_120,8.0032,74.85841_120,8.0032,72.85841</t>
+    <t>119,8.003199,74</t>
+  </si>
+  <si>
+    <t>120,8.0032,72_120,8.0032,76_118,8.0032,76_118,8.0032,72</t>
+  </si>
+  <si>
+    <t>121,8.003199,74</t>
+  </si>
+  <si>
+    <t>122,8.0032,72_122,8.0032,76_120,8.0032,76_120,8.0032,72</t>
   </si>
   <si>
     <t>129.307510375977,7.999978,60.7048797607422</t>
@@ -1372,7 +1372,7 @@
     <t>63.5,7.999978,94_63.5,7.999978,98_60.5,7.999978,98_60.5,7.999978,94</t>
   </si>
   <si>
-    <t>87.1449661254883,6.485435,103.072158813477</t>
+    <t>87.1449661254883,7.999978,103.072158813477</t>
   </si>
   <si>
     <t>87.14,0.00,103.07,113.00,0.00,103.07,113.00,0.00,80.93,87.14,0.00,80.93</t>
@@ -1396,10 +1396,10 @@
     <t>64,7.999978,85.5_60,7.999978,85.5_60,7.999978,82.5_64,7.999978,82.5</t>
   </si>
   <si>
-    <t>67,9.038384,70</t>
-  </si>
-  <si>
-    <t>66,9.038384,72_66,9.038384,68_68,9.038384,68_68,9.038384,72</t>
+    <t>67,7.999978,70</t>
+  </si>
+  <si>
+    <t>66,7.999978,72_66,7.999978,68_68,7.999978,68_68,7.999978,72</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Door_01_orange.prefab</t>
@@ -1525,12 +1525,18 @@
     <t>105,7.999978,143</t>
   </si>
   <si>
+    <t>74996</t>
+  </si>
+  <si>
+    <t>98.1080551147461,7.589046,173.919784545898</t>
+  </si>
+  <si>
+    <t>98.11,0.00,173.92,145.92,0.00,173.92,145.92,0.00,141.77,98.11,0.00,141.77</t>
+  </si>
+  <si>
     <t>70001_2</t>
   </si>
   <si>
-    <t>74996</t>
-  </si>
-  <si>
     <t>127,8.003199,134</t>
   </si>
   <si>
@@ -1657,25 +1663,25 @@
     <t>74898,74899,74900</t>
   </si>
   <si>
-    <t>117.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>118.1416,8.0032,273_118.1416,8.0032,275_116.1416,8.0032,275_116.1416,8.0032,273</t>
+    <t>117,8.003199,274</t>
+  </si>
+  <si>
+    <t>118,8.0032,272_118,8.0032,276_116,8.0032,276_116,8.0032,272</t>
   </si>
   <si>
     <t>74897</t>
   </si>
   <si>
-    <t>119.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>120.1416,8.0032,273_120.1416,8.0032,275_118.1416,8.0032,275_118.1416,8.0032,273</t>
-  </si>
-  <si>
-    <t>121.141586303711,8.003199,274</t>
-  </si>
-  <si>
-    <t>122.1416,8.0032,273_122.1416,8.0032,275_120.1416,8.0032,275_120.1416,8.0032,273</t>
+    <t>119,8.003199,274</t>
+  </si>
+  <si>
+    <t>120,8.0032,272_120,8.0032,276_118,8.0032,276_118,8.0032,272</t>
+  </si>
+  <si>
+    <t>121,8.003199,274</t>
+  </si>
+  <si>
+    <t>122,8.0032,272_122,8.0032,276_120,8.0032,276_120,8.0032,272</t>
   </si>
   <si>
     <t>135,7.999978,274</t>
@@ -1807,10 +1813,10 @@
     <t>70307</t>
   </si>
   <si>
-    <t>115,8.001535,52</t>
-  </si>
-  <si>
-    <t>116,8.001536,50_116,8.001536,54_114,8.001536,54_114,8.001536,50</t>
+    <t>115,8.003199,52</t>
+  </si>
+  <si>
+    <t>116,8.0032,50_116,8.0032,54_114,8.0032,54_114,8.0032,50</t>
   </si>
   <si>
     <t>75002</t>
@@ -1831,7 +1837,7 @@
     <t>75004,75006</t>
   </si>
   <si>
-    <t>78,7.999978,41</t>
+    <t>79,7.999978,41</t>
   </si>
   <si>
     <t>75005</t>
@@ -1840,94 +1846,112 @@
     <t>75003</t>
   </si>
   <si>
-    <t>70,7.999978,35</t>
-  </si>
-  <si>
-    <t>71.5,7.999978,36.5_68.5,7.999978,36.5_68.5,7.999978,33.5_71.5,7.999978,33.5</t>
-  </si>
-  <si>
-    <t>66,7.999978,33</t>
+    <t>69,7.999978,35</t>
+  </si>
+  <si>
+    <t>70.5,7.999978,36.5_67.5,7.999978,36.5_67.5,7.999978,33.5_70.5,7.999978,33.5</t>
+  </si>
+  <si>
+    <t>65,7.999978,33</t>
   </si>
   <si>
     <t>75007</t>
   </si>
   <si>
-    <t>74,7.999978,39</t>
-  </si>
-  <si>
-    <t>75.5,7.999978,40.5_72.5,7.999978,40.5_72.5,7.999978,37.5_75.5,7.999978,37.5</t>
-  </si>
-  <si>
-    <t>72,7.999978,37</t>
+    <t>75,7.999978,37</t>
+  </si>
+  <si>
+    <t>76.5,7.999978,38.5_73.5,7.999978,38.5_73.5,7.999978,35.5_76.5,7.999978,35.5</t>
+  </si>
+  <si>
+    <t>72,7.999978,36</t>
   </si>
   <si>
     <t>Prefab/PuzzleMap/Prop/P_Zhangai_b.prefab</t>
   </si>
   <si>
-    <t>66,7.999978,31</t>
-  </si>
-  <si>
-    <t>68,7.999978,31</t>
-  </si>
-  <si>
-    <t>70,7.999978,31</t>
-  </si>
-  <si>
-    <t>72,7.999978,31</t>
-  </si>
-  <si>
-    <t>74,7.999978,31</t>
-  </si>
-  <si>
-    <t>76,7.999978,31</t>
-  </si>
-  <si>
-    <t>78,7.999978,31</t>
-  </si>
-  <si>
-    <t>78,7.999978,33</t>
-  </si>
-  <si>
-    <t>78,7.999978,35</t>
-  </si>
-  <si>
-    <t>78,7.999978,37</t>
-  </si>
-  <si>
-    <t>78,7.999978,39</t>
-  </si>
-  <si>
-    <t>66,7.999978,35</t>
-  </si>
-  <si>
-    <t>78,7.999978,43</t>
-  </si>
-  <si>
-    <t>76,7.999978,43</t>
-  </si>
-  <si>
-    <t>74,7.999978,43</t>
-  </si>
-  <si>
-    <t>72,7.999978,43</t>
-  </si>
-  <si>
-    <t>70,7.999978,43</t>
-  </si>
-  <si>
-    <t>68,7.999978,43</t>
-  </si>
-  <si>
-    <t>66,7.999978,43</t>
-  </si>
-  <si>
-    <t>66,7.999978,41</t>
-  </si>
-  <si>
-    <t>66,7.999978,39</t>
-  </si>
-  <si>
-    <t>66,7.999978,37</t>
+    <t>65,7.999978,31</t>
+  </si>
+  <si>
+    <t>67,7.999978,29</t>
+  </si>
+  <si>
+    <t>69,7.999978,29</t>
+  </si>
+  <si>
+    <t>71,7.999978,29</t>
+  </si>
+  <si>
+    <t>73,7.999978,29</t>
+  </si>
+  <si>
+    <t>75,7.999978,29</t>
+  </si>
+  <si>
+    <t>77,7.999978,29</t>
+  </si>
+  <si>
+    <t>79,7.999978,33</t>
+  </si>
+  <si>
+    <t>79,7.999978,35</t>
+  </si>
+  <si>
+    <t>79,7.999978,37</t>
+  </si>
+  <si>
+    <t>79,7.999978,39</t>
+  </si>
+  <si>
+    <t>65,7.999978,35</t>
+  </si>
+  <si>
+    <t>79,7.999978,43</t>
+  </si>
+  <si>
+    <t>75,7.999978,43</t>
+  </si>
+  <si>
+    <t>73,7.999978,43</t>
+  </si>
+  <si>
+    <t>71,7.999978,43</t>
+  </si>
+  <si>
+    <t>69,7.999978,43</t>
+  </si>
+  <si>
+    <t>67,7.999978,43</t>
+  </si>
+  <si>
+    <t>65,7.999978,43</t>
+  </si>
+  <si>
+    <t>65,7.999978,41</t>
+  </si>
+  <si>
+    <t>65,7.999978,39</t>
+  </si>
+  <si>
+    <t>65,7.999978,37</t>
+  </si>
+  <si>
+    <t>65,7.999978,29</t>
+  </si>
+  <si>
+    <t>79,7.999978,29</t>
+  </si>
+  <si>
+    <t>79,7.999978,31</t>
+  </si>
+  <si>
+    <t>77,7.999978,43</t>
+  </si>
+  <si>
+    <t>64.0971832275391,7.999978,43.8487205505371</t>
+  </si>
+  <si>
+    <t>64.10,0.00,43.85,79.94,0.00,43.85,79.94,0.00,28.11,64.10,0.00,28.11</t>
   </si>
   <si>
     <t>37,-8.769137E-05,28</t>
@@ -3532,7 +3556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA375"/>
+  <dimension ref="A1:AA381"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.0178571428571" customWidth="1" style="50"/>
@@ -20464,7 +20488,7 @@
         <v>62</v>
       </c>
       <c r="F222" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G222" s="50" t="s">
         <v>60</v>
@@ -20515,10 +20539,10 @@
         <v>1</v>
       </c>
       <c r="X222" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y222" s="50" t="s">
         <v>502</v>
-      </c>
-      <c r="Y222" s="50" t="s">
-        <v>503</v>
       </c>
       <c r="Z222" s="52">
         <v>0</v>
@@ -20535,80 +20559,51 @@
         <v>58</v>
       </c>
       <c r="C223" s="50">
-        <v>74884</v>
+        <v>75032</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E223" s="50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F223" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G223" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H223" s="50" t="s">
-        <v>505</v>
+        <v>60</v>
       </c>
       <c r="I223" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J223" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K223" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="L223" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M223" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K223" s="50"/>
+      <c r="L223" s="50"/>
+      <c r="M223" s="50"/>
       <c r="N223" s="50">
         <v>7</v>
       </c>
-      <c r="O223" s="50">
-        <v>0</v>
-      </c>
+      <c r="O223" s="50"/>
       <c r="P223" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q223" s="50">
-        <v>0</v>
-      </c>
-      <c r="R223" s="50">
-        <v>0</v>
-      </c>
-      <c r="S223" s="50">
-        <v>0</v>
-      </c>
-      <c r="T223" s="50" t="s">
-        <v>506</v>
-      </c>
-      <c r="U223" s="50">
-        <v>0</v>
-      </c>
-      <c r="V223" s="50">
-        <v>0</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="Q223" s="50"/>
+      <c r="R223" s="50"/>
+      <c r="S223" s="50"/>
+      <c r="T223" s="50"/>
+      <c r="U223" s="50"/>
+      <c r="V223" s="50"/>
       <c r="W223" s="50" t="s">
-        <v>1</v>
+        <v>505</v>
       </c>
       <c r="X223" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y223" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z223" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA223" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="Y223" s="50"/>
+      <c r="Z223" s="52"/>
+      <c r="AA223" s="50"/>
     </row>
     <row r="224">
       <c r="A224" s="50">
@@ -20618,22 +20613,22 @@
         <v>58</v>
       </c>
       <c r="C224" s="50">
-        <v>74885</v>
+        <v>74884</v>
       </c>
       <c r="D224" s="50" t="s">
+        <v>506</v>
+      </c>
+      <c r="E224" s="50">
+        <v>5</v>
+      </c>
+      <c r="F224" s="50">
+        <v>2</v>
+      </c>
+      <c r="G224" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H224" s="50" t="s">
         <v>507</v>
-      </c>
-      <c r="E224" s="50">
-        <v>48</v>
-      </c>
-      <c r="F224" s="50">
-        <v>0</v>
-      </c>
-      <c r="G224" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H224" s="50" t="s">
-        <v>508</v>
       </c>
       <c r="I224" s="50" t="s">
         <v>78</v>
@@ -20642,13 +20637,13 @@
         <v>62</v>
       </c>
       <c r="K224" s="50" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="L224" s="50" t="s">
-        <v>509</v>
+        <v>1</v>
       </c>
       <c r="M224" s="50" t="s">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c r="N224" s="50">
         <v>7</v>
@@ -20656,7 +20651,9 @@
       <c r="O224" s="50">
         <v>0</v>
       </c>
-      <c r="P224" s="50"/>
+      <c r="P224" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q224" s="50">
         <v>0</v>
       </c>
@@ -20666,8 +20663,8 @@
       <c r="S224" s="50">
         <v>0</v>
       </c>
-      <c r="T224" s="50">
-        <v>0</v>
+      <c r="T224" s="50" t="s">
+        <v>508</v>
       </c>
       <c r="U224" s="50">
         <v>0</v>
@@ -20699,13 +20696,13 @@
         <v>58</v>
       </c>
       <c r="C225" s="50">
-        <v>74886</v>
+        <v>74885</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E225" s="50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F225" s="50">
         <v>0</v>
@@ -20714,7 +20711,7 @@
         <v>60</v>
       </c>
       <c r="H225" s="50" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I225" s="50" t="s">
         <v>78</v>
@@ -20723,13 +20720,13 @@
         <v>62</v>
       </c>
       <c r="K225" s="50" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L225" s="50" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M225" s="50" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="N225" s="50">
         <v>7</v>
@@ -20780,13 +20777,13 @@
         <v>58</v>
       </c>
       <c r="C226" s="50">
-        <v>74887</v>
+        <v>74886</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E226" s="50">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F226" s="50">
         <v>0</v>
@@ -20795,7 +20792,7 @@
         <v>60</v>
       </c>
       <c r="H226" s="50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I226" s="50" t="s">
         <v>78</v>
@@ -20804,10 +20801,10 @@
         <v>62</v>
       </c>
       <c r="K226" s="50" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L226" s="50" t="s">
-        <v>1</v>
+        <v>515</v>
       </c>
       <c r="M226" s="50" t="s">
         <v>1</v>
@@ -20861,13 +20858,13 @@
         <v>58</v>
       </c>
       <c r="C227" s="50">
-        <v>74888</v>
+        <v>74887</v>
       </c>
       <c r="D227" s="50" t="s">
         <v>516</v>
       </c>
       <c r="E227" s="50">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F227" s="50">
         <v>0</v>
@@ -20885,13 +20882,13 @@
         <v>62</v>
       </c>
       <c r="K227" s="50" t="s">
-        <v>180</v>
+        <v>331</v>
       </c>
       <c r="L227" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M227" s="50" t="s">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="N227" s="50">
         <v>7</v>
@@ -20942,13 +20939,13 @@
         <v>58</v>
       </c>
       <c r="C228" s="50">
-        <v>74889</v>
+        <v>74888</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E228" s="50">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F228" s="50">
         <v>0</v>
@@ -20957,7 +20954,7 @@
         <v>60</v>
       </c>
       <c r="H228" s="50" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I228" s="50" t="s">
         <v>78</v>
@@ -20966,13 +20963,13 @@
         <v>62</v>
       </c>
       <c r="K228" s="50" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="L228" s="50" t="s">
-        <v>521</v>
+        <v>1</v>
       </c>
       <c r="M228" s="50" t="s">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="N228" s="50">
         <v>7</v>
@@ -21023,13 +21020,13 @@
         <v>58</v>
       </c>
       <c r="C229" s="50">
-        <v>74997</v>
+        <v>74889</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E229" s="50">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F229" s="50">
         <v>0</v>
@@ -21037,8 +21034,11 @@
       <c r="G229" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H229" s="50" t="s">
+        <v>522</v>
+      </c>
       <c r="I229" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J229" s="50" t="s">
         <v>62</v>
@@ -21047,10 +21047,10 @@
         <v>75</v>
       </c>
       <c r="L229" s="50" t="s">
-        <v>1</v>
+        <v>523</v>
       </c>
       <c r="M229" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N229" s="50">
         <v>7</v>
@@ -21058,9 +21058,7 @@
       <c r="O229" s="50">
         <v>0</v>
       </c>
-      <c r="P229" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P229" s="50"/>
       <c r="Q229" s="50">
         <v>0</v>
       </c>
@@ -21092,7 +21090,7 @@
         <v>0</v>
       </c>
       <c r="AA229" s="50" t="s">
-        <v>523</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -21103,16 +21101,16 @@
         <v>58</v>
       </c>
       <c r="C230" s="50">
-        <v>74998</v>
+        <v>74997</v>
       </c>
       <c r="D230" s="50" t="s">
         <v>524</v>
       </c>
       <c r="E230" s="50">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F230" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G230" s="50" t="s">
         <v>60</v>
@@ -21130,7 +21128,7 @@
         <v>1</v>
       </c>
       <c r="M230" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N230" s="50">
         <v>7</v>
@@ -21166,13 +21164,13 @@
         <v>1</v>
       </c>
       <c r="Y230" s="50" t="s">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="Z230" s="52">
         <v>0</v>
       </c>
       <c r="AA230" s="50" t="s">
-        <v>1</v>
+        <v>525</v>
       </c>
     </row>
     <row r="231">
@@ -21183,13 +21181,13 @@
         <v>58</v>
       </c>
       <c r="C231" s="50">
-        <v>74890</v>
+        <v>74998</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E231" s="50">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F231" s="50">
         <v>2</v>
@@ -21197,17 +21195,14 @@
       <c r="G231" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H231" s="50" t="s">
-        <v>526</v>
-      </c>
       <c r="I231" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J231" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K231" s="50" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="L231" s="50" t="s">
         <v>1</v>
@@ -21231,7 +21226,7 @@
         <v>0</v>
       </c>
       <c r="S231" s="50">
-        <v>70006</v>
+        <v>0</v>
       </c>
       <c r="T231" s="50">
         <v>0</v>
@@ -21249,7 +21244,7 @@
         <v>1</v>
       </c>
       <c r="Y231" s="50" t="s">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="Z231" s="52">
         <v>0</v>
@@ -21266,16 +21261,16 @@
         <v>58</v>
       </c>
       <c r="C232" s="50">
-        <v>74891</v>
+        <v>74890</v>
       </c>
       <c r="D232" s="50" t="s">
         <v>527</v>
       </c>
       <c r="E232" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F232" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G232" s="50" t="s">
         <v>60</v>
@@ -21290,7 +21285,7 @@
         <v>62</v>
       </c>
       <c r="K232" s="50" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="L232" s="50" t="s">
         <v>1</v>
@@ -21314,10 +21309,10 @@
         <v>0</v>
       </c>
       <c r="S232" s="50">
-        <v>0</v>
-      </c>
-      <c r="T232" s="50" t="s">
-        <v>529</v>
+        <v>70006</v>
+      </c>
+      <c r="T232" s="50">
+        <v>0</v>
       </c>
       <c r="U232" s="50">
         <v>0</v>
@@ -21349,22 +21344,22 @@
         <v>58</v>
       </c>
       <c r="C233" s="50">
-        <v>74892</v>
+        <v>74891</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E233" s="50">
         <v>5</v>
       </c>
       <c r="F233" s="50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G233" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H233" s="50" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I233" s="50" t="s">
         <v>78</v>
@@ -21373,7 +21368,7 @@
         <v>62</v>
       </c>
       <c r="K233" s="50" t="s">
-        <v>352</v>
+        <v>96</v>
       </c>
       <c r="L233" s="50" t="s">
         <v>1</v>
@@ -21400,7 +21395,7 @@
         <v>0</v>
       </c>
       <c r="T233" s="50" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U233" s="50">
         <v>0</v>
@@ -21432,22 +21427,22 @@
         <v>58</v>
       </c>
       <c r="C234" s="50">
-        <v>74893</v>
+        <v>74892</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E234" s="50">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F234" s="50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G234" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H234" s="50" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I234" s="50" t="s">
         <v>78</v>
@@ -21456,10 +21451,10 @@
         <v>62</v>
       </c>
       <c r="K234" s="50" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="L234" s="50" t="s">
-        <v>535</v>
+        <v>1</v>
       </c>
       <c r="M234" s="50" t="s">
         <v>1</v>
@@ -21470,7 +21465,9 @@
       <c r="O234" s="50">
         <v>0</v>
       </c>
-      <c r="P234" s="50"/>
+      <c r="P234" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q234" s="50">
         <v>0</v>
       </c>
@@ -21480,8 +21477,8 @@
       <c r="S234" s="50">
         <v>0</v>
       </c>
-      <c r="T234" s="50">
-        <v>0</v>
+      <c r="T234" s="50" t="s">
+        <v>534</v>
       </c>
       <c r="U234" s="50">
         <v>0</v>
@@ -21493,7 +21490,7 @@
         <v>1</v>
       </c>
       <c r="X234" s="50" t="s">
-        <v>536</v>
+        <v>1</v>
       </c>
       <c r="Y234" s="50" t="s">
         <v>1</v>
@@ -21513,22 +21510,22 @@
         <v>58</v>
       </c>
       <c r="C235" s="50">
-        <v>74894</v>
+        <v>74893</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E235" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F235" s="50">
         <v>3</v>
       </c>
       <c r="G235" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H235" s="50" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I235" s="50" t="s">
         <v>78</v>
@@ -21537,10 +21534,10 @@
         <v>62</v>
       </c>
       <c r="K235" s="50" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="L235" s="50" t="s">
-        <v>1</v>
+        <v>537</v>
       </c>
       <c r="M235" s="50" t="s">
         <v>1</v>
@@ -21574,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="X235" s="50" t="s">
-        <v>1</v>
+        <v>538</v>
       </c>
       <c r="Y235" s="50" t="s">
         <v>1</v>
@@ -21594,19 +21591,19 @@
         <v>58</v>
       </c>
       <c r="C236" s="50">
-        <v>74895</v>
+        <v>74894</v>
       </c>
       <c r="D236" s="50" t="s">
         <v>539</v>
       </c>
       <c r="E236" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F236" s="50">
         <v>3</v>
       </c>
       <c r="G236" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H236" s="50" t="s">
         <v>540</v>
@@ -21618,7 +21615,7 @@
         <v>62</v>
       </c>
       <c r="K236" s="50" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="L236" s="50" t="s">
         <v>1</v>
@@ -21632,9 +21629,7 @@
       <c r="O236" s="50">
         <v>0</v>
       </c>
-      <c r="P236" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P236" s="50"/>
       <c r="Q236" s="50">
         <v>0</v>
       </c>
@@ -21642,7 +21637,7 @@
         <v>0</v>
       </c>
       <c r="S236" s="50">
-        <v>70007</v>
+        <v>0</v>
       </c>
       <c r="T236" s="50">
         <v>0</v>
@@ -21677,52 +21672,79 @@
         <v>58</v>
       </c>
       <c r="C237" s="50">
-        <v>74896</v>
+        <v>74895</v>
       </c>
       <c r="D237" s="50" t="s">
         <v>541</v>
       </c>
       <c r="E237" s="50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F237" s="50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G237" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H237" s="50" t="s">
+        <v>542</v>
       </c>
       <c r="I237" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J237" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K237" s="50"/>
+      <c r="K237" s="50" t="s">
+        <v>246</v>
+      </c>
       <c r="L237" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="M237" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="M237" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N237" s="50">
         <v>7</v>
       </c>
-      <c r="O237" s="50"/>
+      <c r="O237" s="50">
+        <v>0</v>
+      </c>
       <c r="P237" s="50" t="s">
-        <v>542</v>
-      </c>
-      <c r="Q237" s="50"/>
-      <c r="R237" s="50"/>
-      <c r="S237" s="50"/>
-      <c r="T237" s="50"/>
-      <c r="U237" s="50"/>
-      <c r="V237" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="Q237" s="50">
+        <v>0</v>
+      </c>
+      <c r="R237" s="50">
+        <v>0</v>
+      </c>
+      <c r="S237" s="50">
+        <v>70007</v>
+      </c>
+      <c r="T237" s="50">
+        <v>0</v>
+      </c>
+      <c r="U237" s="50">
+        <v>0</v>
+      </c>
+      <c r="V237" s="50">
+        <v>0</v>
+      </c>
       <c r="W237" s="50" t="s">
-        <v>502</v>
-      </c>
-      <c r="X237" s="50"/>
-      <c r="Y237" s="50"/>
-      <c r="Z237" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="X237" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y237" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z237" s="52">
+        <v>0</v>
+      </c>
       <c r="AA237" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -21733,77 +21755,52 @@
         <v>58</v>
       </c>
       <c r="C238" s="50">
-        <v>74897</v>
+        <v>74896</v>
       </c>
       <c r="D238" s="50" t="s">
         <v>543</v>
       </c>
       <c r="E238" s="50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F238" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H238" s="50" t="s">
-        <v>544</v>
+        <v>60</v>
       </c>
       <c r="I238" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J238" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K238" s="50" t="s">
-        <v>142</v>
-      </c>
+      <c r="K238" s="50"/>
       <c r="L238" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M238" s="50" t="s">
-        <v>545</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M238" s="50"/>
       <c r="N238" s="50">
         <v>7</v>
       </c>
-      <c r="O238" s="50">
-        <v>0</v>
-      </c>
-      <c r="P238" s="50"/>
-      <c r="Q238" s="50">
-        <v>0</v>
-      </c>
-      <c r="R238" s="50">
-        <v>0</v>
-      </c>
-      <c r="S238" s="50">
-        <v>0</v>
-      </c>
-      <c r="T238" s="50">
-        <v>0</v>
-      </c>
-      <c r="U238" s="50">
-        <v>0</v>
-      </c>
-      <c r="V238" s="50">
-        <v>0</v>
-      </c>
+      <c r="O238" s="50"/>
+      <c r="P238" s="50" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q238" s="50"/>
+      <c r="R238" s="50"/>
+      <c r="S238" s="50"/>
+      <c r="T238" s="50"/>
+      <c r="U238" s="50"/>
+      <c r="V238" s="50"/>
       <c r="W238" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X238" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y238" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z238" s="52">
-        <v>0</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="X238" s="50"/>
+      <c r="Y238" s="50"/>
+      <c r="Z238" s="52"/>
       <c r="AA238" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="239">
@@ -21814,22 +21811,22 @@
         <v>58</v>
       </c>
       <c r="C239" s="50">
-        <v>74898</v>
+        <v>74897</v>
       </c>
       <c r="D239" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="E239" s="50">
+        <v>6</v>
+      </c>
+      <c r="F239" s="50">
+        <v>0</v>
+      </c>
+      <c r="G239" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H239" s="50" t="s">
         <v>546</v>
-      </c>
-      <c r="E239" s="50">
-        <v>7</v>
-      </c>
-      <c r="F239" s="50">
-        <v>0</v>
-      </c>
-      <c r="G239" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H239" s="50" t="s">
-        <v>547</v>
       </c>
       <c r="I239" s="50" t="s">
         <v>78</v>
@@ -21838,13 +21835,13 @@
         <v>62</v>
       </c>
       <c r="K239" s="50" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L239" s="50" t="s">
-        <v>548</v>
+        <v>1</v>
       </c>
       <c r="M239" s="50" t="s">
-        <v>1</v>
+        <v>547</v>
       </c>
       <c r="N239" s="50">
         <v>7</v>
@@ -21895,10 +21892,10 @@
         <v>58</v>
       </c>
       <c r="C240" s="50">
-        <v>74899</v>
+        <v>74898</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E240" s="50">
         <v>7</v>
@@ -21910,7 +21907,7 @@
         <v>138</v>
       </c>
       <c r="H240" s="50" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I240" s="50" t="s">
         <v>78</v>
@@ -21922,7 +21919,7 @@
         <v>147</v>
       </c>
       <c r="L240" s="50" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M240" s="50" t="s">
         <v>1</v>
@@ -21976,7 +21973,7 @@
         <v>58</v>
       </c>
       <c r="C241" s="50">
-        <v>74900</v>
+        <v>74899</v>
       </c>
       <c r="D241" s="50" t="s">
         <v>551</v>
@@ -22003,7 +22000,7 @@
         <v>147</v>
       </c>
       <c r="L241" s="50" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M241" s="50" t="s">
         <v>1</v>
@@ -22057,19 +22054,19 @@
         <v>58</v>
       </c>
       <c r="C242" s="50">
-        <v>74901</v>
+        <v>74900</v>
       </c>
       <c r="D242" s="50" t="s">
         <v>553</v>
       </c>
       <c r="E242" s="50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F242" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G242" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H242" s="50" t="s">
         <v>554</v>
@@ -22081,10 +22078,10 @@
         <v>62</v>
       </c>
       <c r="K242" s="50" t="s">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="L242" s="50" t="s">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="M242" s="50" t="s">
         <v>1</v>
@@ -22095,9 +22092,7 @@
       <c r="O242" s="50">
         <v>0</v>
       </c>
-      <c r="P242" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P242" s="50"/>
       <c r="Q242" s="50">
         <v>0</v>
       </c>
@@ -22107,8 +22102,8 @@
       <c r="S242" s="50">
         <v>0</v>
       </c>
-      <c r="T242" s="50" t="s">
-        <v>555</v>
+      <c r="T242" s="50">
+        <v>0</v>
       </c>
       <c r="U242" s="50">
         <v>0</v>
@@ -22140,52 +22135,79 @@
         <v>58</v>
       </c>
       <c r="C243" s="50">
-        <v>74905</v>
+        <v>74901</v>
       </c>
       <c r="D243" s="50" t="s">
+        <v>555</v>
+      </c>
+      <c r="E243" s="50">
+        <v>5</v>
+      </c>
+      <c r="F243" s="50">
+        <v>2</v>
+      </c>
+      <c r="G243" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H243" s="50" t="s">
         <v>556</v>
       </c>
-      <c r="E243" s="50">
-        <v>2</v>
-      </c>
-      <c r="F243" s="50">
-        <v>1</v>
-      </c>
-      <c r="G243" s="50" t="s">
-        <v>60</v>
-      </c>
       <c r="I243" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J243" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K243" s="50"/>
+      <c r="K243" s="50" t="s">
+        <v>297</v>
+      </c>
       <c r="L243" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="M243" s="50"/>
+        <v>1</v>
+      </c>
+      <c r="M243" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N243" s="50">
         <v>7</v>
       </c>
-      <c r="O243" s="50"/>
+      <c r="O243" s="50">
+        <v>0</v>
+      </c>
       <c r="P243" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q243" s="50">
+        <v>0</v>
+      </c>
+      <c r="R243" s="50">
+        <v>0</v>
+      </c>
+      <c r="S243" s="50">
+        <v>0</v>
+      </c>
+      <c r="T243" s="50" t="s">
         <v>557</v>
       </c>
-      <c r="Q243" s="50"/>
-      <c r="R243" s="50"/>
-      <c r="S243" s="50"/>
-      <c r="T243" s="50"/>
-      <c r="U243" s="50"/>
-      <c r="V243" s="50"/>
+      <c r="U243" s="50">
+        <v>0</v>
+      </c>
+      <c r="V243" s="50">
+        <v>0</v>
+      </c>
       <c r="W243" s="50" t="s">
-        <v>536</v>
-      </c>
-      <c r="X243" s="50"/>
-      <c r="Y243" s="50"/>
-      <c r="Z243" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="X243" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y243" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z243" s="52">
+        <v>0</v>
+      </c>
       <c r="AA243" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -22196,19 +22218,19 @@
         <v>58</v>
       </c>
       <c r="C244" s="50">
-        <v>74906</v>
+        <v>74905</v>
       </c>
       <c r="D244" s="50" t="s">
         <v>558</v>
       </c>
       <c r="E244" s="50">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F244" s="50">
         <v>1</v>
       </c>
       <c r="G244" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="I244" s="50" t="s">
         <v>61</v>
@@ -22216,54 +22238,32 @@
       <c r="J244" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K244" s="50" t="s">
-        <v>559</v>
-      </c>
+      <c r="K244" s="50"/>
       <c r="L244" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M244" s="50" t="s">
-        <v>560</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="M244" s="50"/>
       <c r="N244" s="50">
         <v>7</v>
       </c>
-      <c r="O244" s="50">
-        <v>0</v>
-      </c>
-      <c r="P244" s="50"/>
-      <c r="Q244" s="50">
-        <v>0</v>
-      </c>
-      <c r="R244" s="50">
-        <v>0</v>
-      </c>
-      <c r="S244" s="50">
-        <v>0</v>
-      </c>
-      <c r="T244" s="50">
-        <v>0</v>
-      </c>
-      <c r="U244" s="50">
-        <v>0</v>
-      </c>
-      <c r="V244" s="50">
-        <v>0</v>
-      </c>
+      <c r="O244" s="50"/>
+      <c r="P244" s="50" t="s">
+        <v>559</v>
+      </c>
+      <c r="Q244" s="50"/>
+      <c r="R244" s="50"/>
+      <c r="S244" s="50"/>
+      <c r="T244" s="50"/>
+      <c r="U244" s="50"/>
+      <c r="V244" s="50"/>
       <c r="W244" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X244" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y244" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z244" s="52">
-        <v>0</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="X244" s="50"/>
+      <c r="Y244" s="50"/>
+      <c r="Z244" s="52"/>
       <c r="AA244" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="245">
@@ -22274,19 +22274,19 @@
         <v>58</v>
       </c>
       <c r="C245" s="50">
-        <v>74907</v>
+        <v>74906</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E245" s="50">
         <v>13</v>
       </c>
       <c r="F245" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G245" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I245" s="50" t="s">
         <v>61</v>
@@ -22295,13 +22295,13 @@
         <v>62</v>
       </c>
       <c r="K245" s="50" t="s">
-        <v>75</v>
+        <v>561</v>
       </c>
       <c r="L245" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M245" s="50" t="s">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="N245" s="50">
         <v>7</v>
@@ -22352,19 +22352,19 @@
         <v>58</v>
       </c>
       <c r="C246" s="50">
-        <v>74908</v>
+        <v>74907</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E246" s="50">
         <v>13</v>
       </c>
       <c r="F246" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G246" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="I246" s="50" t="s">
         <v>61</v>
@@ -22373,13 +22373,13 @@
         <v>62</v>
       </c>
       <c r="K246" s="50" t="s">
-        <v>559</v>
+        <v>75</v>
       </c>
       <c r="L246" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M246" s="50" t="s">
-        <v>563</v>
+        <v>1</v>
       </c>
       <c r="N246" s="50">
         <v>7</v>
@@ -22430,7 +22430,7 @@
         <v>58</v>
       </c>
       <c r="C247" s="50">
-        <v>74909</v>
+        <v>74908</v>
       </c>
       <c r="D247" s="50" t="s">
         <v>564</v>
@@ -22439,10 +22439,10 @@
         <v>13</v>
       </c>
       <c r="F247" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G247" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="I247" s="50" t="s">
         <v>61</v>
@@ -22451,13 +22451,13 @@
         <v>62</v>
       </c>
       <c r="K247" s="50" t="s">
-        <v>75</v>
+        <v>561</v>
       </c>
       <c r="L247" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M247" s="50" t="s">
-        <v>1</v>
+        <v>565</v>
       </c>
       <c r="N247" s="50">
         <v>7</v>
@@ -22508,31 +22508,28 @@
         <v>58</v>
       </c>
       <c r="C248" s="50">
-        <v>74999</v>
+        <v>74909</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E248" s="50">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F248" s="50">
         <v>2</v>
       </c>
       <c r="G248" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H248" s="50" t="s">
-        <v>566</v>
+        <v>60</v>
       </c>
       <c r="I248" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J248" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K248" s="50" t="s">
-        <v>297</v>
+        <v>75</v>
       </c>
       <c r="L248" s="50" t="s">
         <v>1</v>
@@ -22546,9 +22543,7 @@
       <c r="O248" s="50">
         <v>0</v>
       </c>
-      <c r="P248" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P248" s="50"/>
       <c r="Q248" s="50">
         <v>0</v>
       </c>
@@ -22558,8 +22553,8 @@
       <c r="S248" s="50">
         <v>0</v>
       </c>
-      <c r="T248" s="50" t="s">
-        <v>567</v>
+      <c r="T248" s="50">
+        <v>0</v>
       </c>
       <c r="U248" s="50">
         <v>0</v>
@@ -22591,22 +22586,22 @@
         <v>58</v>
       </c>
       <c r="C249" s="50">
-        <v>74979</v>
+        <v>74999</v>
       </c>
       <c r="D249" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="E249" s="50">
+        <v>5</v>
+      </c>
+      <c r="F249" s="50">
+        <v>2</v>
+      </c>
+      <c r="G249" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H249" s="50" t="s">
         <v>568</v>
-      </c>
-      <c r="E249" s="50">
-        <v>45</v>
-      </c>
-      <c r="F249" s="50">
-        <v>0</v>
-      </c>
-      <c r="G249" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H249" s="50" t="s">
-        <v>569</v>
       </c>
       <c r="I249" s="50" t="s">
         <v>78</v>
@@ -22615,7 +22610,7 @@
         <v>62</v>
       </c>
       <c r="K249" s="50" t="s">
-        <v>570</v>
+        <v>297</v>
       </c>
       <c r="L249" s="50" t="s">
         <v>1</v>
@@ -22629,7 +22624,9 @@
       <c r="O249" s="50">
         <v>0</v>
       </c>
-      <c r="P249" s="50"/>
+      <c r="P249" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q249" s="50">
         <v>0</v>
       </c>
@@ -22639,8 +22636,8 @@
       <c r="S249" s="50">
         <v>0</v>
       </c>
-      <c r="T249" s="50">
-        <v>0</v>
+      <c r="T249" s="50" t="s">
+        <v>569</v>
       </c>
       <c r="U249" s="50">
         <v>0</v>
@@ -22672,22 +22669,22 @@
         <v>58</v>
       </c>
       <c r="C250" s="50">
-        <v>74982</v>
+        <v>74979</v>
       </c>
       <c r="D250" s="50" t="s">
+        <v>570</v>
+      </c>
+      <c r="E250" s="50">
+        <v>45</v>
+      </c>
+      <c r="F250" s="50">
+        <v>0</v>
+      </c>
+      <c r="G250" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H250" s="50" t="s">
         <v>571</v>
-      </c>
-      <c r="E250" s="50">
-        <v>46</v>
-      </c>
-      <c r="F250" s="50">
-        <v>0</v>
-      </c>
-      <c r="G250" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H250" s="50" t="s">
-        <v>572</v>
       </c>
       <c r="I250" s="50" t="s">
         <v>78</v>
@@ -22696,7 +22693,7 @@
         <v>62</v>
       </c>
       <c r="K250" s="50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L250" s="50" t="s">
         <v>1</v>
@@ -22753,10 +22750,10 @@
         <v>58</v>
       </c>
       <c r="C251" s="50">
-        <v>74984</v>
+        <v>74982</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E251" s="50">
         <v>46</v>
@@ -22768,7 +22765,7 @@
         <v>60</v>
       </c>
       <c r="H251" s="50" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I251" s="50" t="s">
         <v>78</v>
@@ -22777,7 +22774,7 @@
         <v>62</v>
       </c>
       <c r="K251" s="50" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L251" s="50" t="s">
         <v>1</v>
@@ -22834,19 +22831,19 @@
         <v>58</v>
       </c>
       <c r="C252" s="50">
-        <v>74981</v>
+        <v>74984</v>
       </c>
       <c r="D252" s="50" t="s">
         <v>576</v>
       </c>
       <c r="E252" s="50">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F252" s="50">
         <v>0</v>
       </c>
       <c r="G252" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H252" s="50" t="s">
         <v>577</v>
@@ -22858,13 +22855,13 @@
         <v>62</v>
       </c>
       <c r="K252" s="50" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="L252" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M252" s="50" t="s">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="N252" s="50">
         <v>7</v>
@@ -22915,22 +22912,22 @@
         <v>58</v>
       </c>
       <c r="C253" s="50">
-        <v>74983</v>
+        <v>74981</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E253" s="50">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F253" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G253" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H253" s="50" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="I253" s="50" t="s">
         <v>78</v>
@@ -22939,13 +22936,13 @@
         <v>62</v>
       </c>
       <c r="K253" s="50" t="s">
-        <v>192</v>
+        <v>580</v>
       </c>
       <c r="L253" s="50" t="s">
-        <v>582</v>
+        <v>1</v>
       </c>
       <c r="M253" s="50" t="s">
-        <v>1</v>
+        <v>581</v>
       </c>
       <c r="N253" s="50">
         <v>7</v>
@@ -22996,22 +22993,22 @@
         <v>58</v>
       </c>
       <c r="C254" s="50">
-        <v>74985</v>
+        <v>74983</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E254" s="50">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F254" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G254" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H254" s="50" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I254" s="50" t="s">
         <v>78</v>
@@ -23020,10 +23017,10 @@
         <v>62</v>
       </c>
       <c r="K254" s="50" t="s">
-        <v>573</v>
+        <v>192</v>
       </c>
       <c r="L254" s="50" t="s">
-        <v>1</v>
+        <v>584</v>
       </c>
       <c r="M254" s="50" t="s">
         <v>1</v>
@@ -23077,47 +23074,78 @@
         <v>58</v>
       </c>
       <c r="C255" s="50">
-        <v>74988</v>
+        <v>74985</v>
       </c>
       <c r="D255" s="50" t="s">
         <v>585</v>
       </c>
       <c r="E255" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F255" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G255" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H255" s="50" t="s">
+        <v>586</v>
+      </c>
       <c r="I255" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J255" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K255" s="50"/>
-      <c r="L255" s="50"/>
-      <c r="M255" s="50"/>
+      <c r="K255" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="L255" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M255" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N255" s="50">
         <v>7</v>
       </c>
-      <c r="O255" s="50"/>
-      <c r="P255" s="50" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q255" s="50"/>
-      <c r="R255" s="50"/>
-      <c r="S255" s="50"/>
-      <c r="T255" s="50"/>
-      <c r="U255" s="50"/>
-      <c r="V255" s="50"/>
-      <c r="W255" s="50"/>
-      <c r="X255" s="50"/>
-      <c r="Y255" s="50"/>
-      <c r="Z255" s="52"/>
-      <c r="AA255" s="50"/>
+      <c r="O255" s="50">
+        <v>0</v>
+      </c>
+      <c r="P255" s="50"/>
+      <c r="Q255" s="50">
+        <v>0</v>
+      </c>
+      <c r="R255" s="50">
+        <v>0</v>
+      </c>
+      <c r="S255" s="50">
+        <v>0</v>
+      </c>
+      <c r="T255" s="50">
+        <v>0</v>
+      </c>
+      <c r="U255" s="50">
+        <v>0</v>
+      </c>
+      <c r="V255" s="50">
+        <v>0</v>
+      </c>
+      <c r="W255" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X255" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y255" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z255" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA255" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="50">
@@ -23127,78 +23155,47 @@
         <v>58</v>
       </c>
       <c r="C256" s="50">
-        <v>74991</v>
+        <v>74988</v>
       </c>
       <c r="D256" s="50" t="s">
         <v>587</v>
       </c>
       <c r="E256" s="50">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F256" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G256" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H256" s="50" t="s">
-        <v>588</v>
+        <v>60</v>
       </c>
       <c r="I256" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J256" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K256" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="L256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M256" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K256" s="50"/>
+      <c r="L256" s="50"/>
+      <c r="M256" s="50"/>
       <c r="N256" s="50">
         <v>7</v>
       </c>
-      <c r="O256" s="50">
-        <v>0</v>
-      </c>
-      <c r="P256" s="50"/>
-      <c r="Q256" s="50">
-        <v>0</v>
-      </c>
-      <c r="R256" s="50">
-        <v>0</v>
-      </c>
-      <c r="S256" s="50">
-        <v>0</v>
-      </c>
-      <c r="T256" s="50">
-        <v>0</v>
-      </c>
-      <c r="U256" s="50">
-        <v>0</v>
-      </c>
-      <c r="V256" s="50">
-        <v>0</v>
-      </c>
-      <c r="W256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y256" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z256" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA256" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="O256" s="50"/>
+      <c r="P256" s="50" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q256" s="50"/>
+      <c r="R256" s="50"/>
+      <c r="S256" s="50"/>
+      <c r="T256" s="50"/>
+      <c r="U256" s="50"/>
+      <c r="V256" s="50"/>
+      <c r="W256" s="50"/>
+      <c r="X256" s="50"/>
+      <c r="Y256" s="50"/>
+      <c r="Z256" s="52"/>
+      <c r="AA256" s="50"/>
     </row>
     <row r="257">
       <c r="A257" s="50">
@@ -23208,19 +23205,19 @@
         <v>58</v>
       </c>
       <c r="C257" s="50">
-        <v>74990</v>
+        <v>74991</v>
       </c>
       <c r="D257" s="50" t="s">
         <v>589</v>
       </c>
       <c r="E257" s="50">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F257" s="50">
         <v>0</v>
       </c>
       <c r="G257" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H257" s="50" t="s">
         <v>590</v>
@@ -23232,10 +23229,10 @@
         <v>62</v>
       </c>
       <c r="K257" s="50" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="L257" s="50" t="s">
-        <v>591</v>
+        <v>1</v>
       </c>
       <c r="M257" s="50" t="s">
         <v>1</v>
@@ -23289,13 +23286,13 @@
         <v>58</v>
       </c>
       <c r="C258" s="50">
-        <v>74989</v>
+        <v>74990</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E258" s="50">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F258" s="50">
         <v>0</v>
@@ -23303,17 +23300,20 @@
       <c r="G258" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H258" s="50" t="s">
+        <v>592</v>
+      </c>
       <c r="I258" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J258" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K258" s="50" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="L258" s="50" t="s">
-        <v>61</v>
+        <v>593</v>
       </c>
       <c r="M258" s="50" t="s">
         <v>1</v>
@@ -23324,9 +23324,7 @@
       <c r="O258" s="50">
         <v>0</v>
       </c>
-      <c r="P258" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P258" s="50"/>
       <c r="Q258" s="50">
         <v>0</v>
       </c>
@@ -23369,34 +23367,31 @@
         <v>58</v>
       </c>
       <c r="C259" s="50">
-        <v>75000</v>
+        <v>74989</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E259" s="50">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F259" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G259" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H259" s="50" t="s">
-        <v>594</v>
+        <v>60</v>
       </c>
       <c r="I259" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J259" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K259" s="50" t="s">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="L259" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M259" s="50" t="s">
         <v>1</v>
@@ -23419,8 +23414,8 @@
       <c r="S259" s="50">
         <v>0</v>
       </c>
-      <c r="T259" s="50" t="s">
-        <v>595</v>
+      <c r="T259" s="50">
+        <v>0</v>
       </c>
       <c r="U259" s="50">
         <v>0</v>
@@ -23452,22 +23447,22 @@
         <v>58</v>
       </c>
       <c r="C260" s="50">
-        <v>75001</v>
+        <v>75000</v>
       </c>
       <c r="D260" s="50" t="s">
+        <v>595</v>
+      </c>
+      <c r="E260" s="50">
+        <v>5</v>
+      </c>
+      <c r="F260" s="50">
+        <v>3</v>
+      </c>
+      <c r="G260" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H260" s="50" t="s">
         <v>596</v>
-      </c>
-      <c r="E260" s="50">
-        <v>16</v>
-      </c>
-      <c r="F260" s="50">
-        <v>2</v>
-      </c>
-      <c r="G260" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H260" s="50" t="s">
-        <v>597</v>
       </c>
       <c r="I260" s="50" t="s">
         <v>78</v>
@@ -23476,10 +23471,10 @@
         <v>62</v>
       </c>
       <c r="K260" s="50" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="L260" s="50" t="s">
-        <v>598</v>
+        <v>1</v>
       </c>
       <c r="M260" s="50" t="s">
         <v>1</v>
@@ -23490,7 +23485,9 @@
       <c r="O260" s="50">
         <v>0</v>
       </c>
-      <c r="P260" s="50"/>
+      <c r="P260" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q260" s="50">
         <v>0</v>
       </c>
@@ -23500,8 +23497,8 @@
       <c r="S260" s="50">
         <v>0</v>
       </c>
-      <c r="T260" s="50">
-        <v>0</v>
+      <c r="T260" s="50" t="s">
+        <v>597</v>
       </c>
       <c r="U260" s="50">
         <v>0</v>
@@ -23533,22 +23530,22 @@
         <v>58</v>
       </c>
       <c r="C261" s="50">
-        <v>75002</v>
+        <v>75001</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E261" s="50">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F261" s="50">
         <v>2</v>
       </c>
       <c r="G261" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H261" s="50" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I261" s="50" t="s">
         <v>78</v>
@@ -23557,10 +23554,10 @@
         <v>62</v>
       </c>
       <c r="K261" s="50" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L261" s="50" t="s">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="M261" s="50" t="s">
         <v>1</v>
@@ -23614,19 +23611,19 @@
         <v>58</v>
       </c>
       <c r="C262" s="50">
-        <v>75003</v>
+        <v>75002</v>
       </c>
       <c r="D262" s="50" t="s">
         <v>601</v>
       </c>
       <c r="E262" s="50">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F262" s="50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G262" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H262" s="50" t="s">
         <v>602</v>
@@ -23638,10 +23635,10 @@
         <v>62</v>
       </c>
       <c r="K262" s="50" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="L262" s="50" t="s">
-        <v>603</v>
+        <v>1</v>
       </c>
       <c r="M262" s="50" t="s">
         <v>1</v>
@@ -23695,34 +23692,37 @@
         <v>58</v>
       </c>
       <c r="C263" s="50">
-        <v>75004</v>
+        <v>75003</v>
       </c>
       <c r="D263" s="50" t="s">
+        <v>603</v>
+      </c>
+      <c r="E263" s="50">
+        <v>16</v>
+      </c>
+      <c r="F263" s="50">
+        <v>8</v>
+      </c>
+      <c r="G263" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H263" s="50" t="s">
         <v>604</v>
       </c>
-      <c r="E263" s="50">
-        <v>52</v>
-      </c>
-      <c r="F263" s="50">
-        <v>2</v>
-      </c>
-      <c r="G263" s="50" t="s">
-        <v>60</v>
-      </c>
       <c r="I263" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J263" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K263" s="50" t="s">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="L263" s="50" t="s">
         <v>605</v>
       </c>
       <c r="M263" s="50" t="s">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="N263" s="50">
         <v>7</v>
@@ -23773,13 +23773,13 @@
         <v>58</v>
       </c>
       <c r="C264" s="50">
-        <v>75005</v>
+        <v>75004</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E264" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F264" s="50">
         <v>2</v>
@@ -23787,23 +23787,20 @@
       <c r="G264" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H264" s="50" t="s">
+      <c r="I264" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J264" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K264" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="L264" s="50" t="s">
+        <v>607</v>
+      </c>
+      <c r="M264" s="50" t="s">
         <v>608</v>
-      </c>
-      <c r="I264" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J264" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K264" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="L264" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M264" s="50" t="s">
-        <v>1</v>
       </c>
       <c r="N264" s="50">
         <v>7</v>
@@ -23854,34 +23851,37 @@
         <v>58</v>
       </c>
       <c r="C265" s="50">
-        <v>75006</v>
+        <v>75005</v>
       </c>
       <c r="D265" s="50" t="s">
         <v>609</v>
       </c>
       <c r="E265" s="50">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F265" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G265" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H265" s="50" t="s">
+        <v>610</v>
+      </c>
       <c r="I265" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J265" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K265" s="50" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L265" s="50" t="s">
-        <v>610</v>
+        <v>1</v>
       </c>
       <c r="M265" s="50" t="s">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="N265" s="50">
         <v>7</v>
@@ -23932,13 +23932,13 @@
         <v>58</v>
       </c>
       <c r="C266" s="50">
-        <v>75007</v>
+        <v>75006</v>
       </c>
       <c r="D266" s="50" t="s">
         <v>611</v>
       </c>
       <c r="E266" s="50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F266" s="50">
         <v>4</v>
@@ -23946,23 +23946,20 @@
       <c r="G266" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H266" s="50" t="s">
+      <c r="I266" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J266" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K266" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="L266" s="50" t="s">
         <v>612</v>
       </c>
-      <c r="I266" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J266" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="K266" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="L266" s="50" t="s">
-        <v>1</v>
-      </c>
       <c r="M266" s="50" t="s">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="N266" s="50">
         <v>7</v>
@@ -24013,28 +24010,31 @@
         <v>58</v>
       </c>
       <c r="C267" s="50">
-        <v>75008</v>
+        <v>75007</v>
       </c>
       <c r="D267" s="50" t="s">
         <v>613</v>
       </c>
       <c r="E267" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F267" s="50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G267" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H267" s="50" t="s">
+        <v>614</v>
+      </c>
       <c r="I267" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J267" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K267" s="50" t="s">
-        <v>614</v>
+        <v>283</v>
       </c>
       <c r="L267" s="50" t="s">
         <v>1</v>
@@ -24091,7 +24091,7 @@
         <v>58</v>
       </c>
       <c r="C268" s="50">
-        <v>75009</v>
+        <v>75008</v>
       </c>
       <c r="D268" s="50" t="s">
         <v>615</v>
@@ -24100,7 +24100,7 @@
         <v>56</v>
       </c>
       <c r="F268" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" s="50" t="s">
         <v>60</v>
@@ -24112,7 +24112,7 @@
         <v>62</v>
       </c>
       <c r="K268" s="50" t="s">
-        <v>301</v>
+        <v>616</v>
       </c>
       <c r="L268" s="50" t="s">
         <v>1</v>
@@ -24169,10 +24169,10 @@
         <v>58</v>
       </c>
       <c r="C269" s="50">
-        <v>75010</v>
+        <v>75009</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E269" s="50">
         <v>56</v>
@@ -24247,10 +24247,10 @@
         <v>58</v>
       </c>
       <c r="C270" s="50">
-        <v>75011</v>
+        <v>75010</v>
       </c>
       <c r="D270" s="50" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E270" s="50">
         <v>56</v>
@@ -24325,10 +24325,10 @@
         <v>58</v>
       </c>
       <c r="C271" s="50">
-        <v>75012</v>
+        <v>75011</v>
       </c>
       <c r="D271" s="50" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E271" s="50">
         <v>56</v>
@@ -24403,10 +24403,10 @@
         <v>58</v>
       </c>
       <c r="C272" s="50">
-        <v>75013</v>
+        <v>75012</v>
       </c>
       <c r="D272" s="50" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E272" s="50">
         <v>56</v>
@@ -24481,10 +24481,10 @@
         <v>58</v>
       </c>
       <c r="C273" s="50">
-        <v>75014</v>
+        <v>75013</v>
       </c>
       <c r="D273" s="50" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E273" s="50">
         <v>56</v>
@@ -24559,10 +24559,10 @@
         <v>58</v>
       </c>
       <c r="C274" s="50">
-        <v>75015</v>
+        <v>75014</v>
       </c>
       <c r="D274" s="50" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E274" s="50">
         <v>56</v>
@@ -24637,10 +24637,10 @@
         <v>58</v>
       </c>
       <c r="C275" s="50">
-        <v>75016</v>
+        <v>75015</v>
       </c>
       <c r="D275" s="50" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E275" s="50">
         <v>56</v>
@@ -24715,10 +24715,10 @@
         <v>58</v>
       </c>
       <c r="C276" s="50">
-        <v>75017</v>
+        <v>75016</v>
       </c>
       <c r="D276" s="50" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E276" s="50">
         <v>56</v>
@@ -24793,10 +24793,10 @@
         <v>58</v>
       </c>
       <c r="C277" s="50">
-        <v>75018</v>
+        <v>75017</v>
       </c>
       <c r="D277" s="50" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E277" s="50">
         <v>56</v>
@@ -24871,10 +24871,10 @@
         <v>58</v>
       </c>
       <c r="C278" s="50">
-        <v>75019</v>
+        <v>75018</v>
       </c>
       <c r="D278" s="50" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E278" s="50">
         <v>56</v>
@@ -24949,10 +24949,10 @@
         <v>58</v>
       </c>
       <c r="C279" s="50">
-        <v>75020</v>
+        <v>75019</v>
       </c>
       <c r="D279" s="50" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E279" s="50">
         <v>56</v>
@@ -25027,10 +25027,10 @@
         <v>58</v>
       </c>
       <c r="C280" s="50">
-        <v>75021</v>
+        <v>75020</v>
       </c>
       <c r="D280" s="50" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E280" s="50">
         <v>56</v>
@@ -25105,10 +25105,10 @@
         <v>58</v>
       </c>
       <c r="C281" s="50">
-        <v>75022</v>
+        <v>75021</v>
       </c>
       <c r="D281" s="50" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E281" s="50">
         <v>56</v>
@@ -25183,10 +25183,10 @@
         <v>58</v>
       </c>
       <c r="C282" s="50">
-        <v>75023</v>
+        <v>75022</v>
       </c>
       <c r="D282" s="50" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E282" s="50">
         <v>56</v>
@@ -25261,10 +25261,10 @@
         <v>58</v>
       </c>
       <c r="C283" s="50">
-        <v>75024</v>
+        <v>75023</v>
       </c>
       <c r="D283" s="50" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E283" s="50">
         <v>56</v>
@@ -25339,10 +25339,10 @@
         <v>58</v>
       </c>
       <c r="C284" s="50">
-        <v>75025</v>
+        <v>75024</v>
       </c>
       <c r="D284" s="50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E284" s="50">
         <v>56</v>
@@ -25417,10 +25417,10 @@
         <v>58</v>
       </c>
       <c r="C285" s="50">
-        <v>75026</v>
+        <v>75025</v>
       </c>
       <c r="D285" s="50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E285" s="50">
         <v>56</v>
@@ -25495,10 +25495,10 @@
         <v>58</v>
       </c>
       <c r="C286" s="50">
-        <v>75027</v>
+        <v>75026</v>
       </c>
       <c r="D286" s="50" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E286" s="50">
         <v>56</v>
@@ -25573,10 +25573,10 @@
         <v>58</v>
       </c>
       <c r="C287" s="50">
-        <v>75028</v>
+        <v>75027</v>
       </c>
       <c r="D287" s="50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E287" s="50">
         <v>56</v>
@@ -25651,10 +25651,10 @@
         <v>58</v>
       </c>
       <c r="C288" s="50">
-        <v>75029</v>
+        <v>75028</v>
       </c>
       <c r="D288" s="50" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E288" s="50">
         <v>56</v>
@@ -25729,10 +25729,10 @@
         <v>58</v>
       </c>
       <c r="C289" s="50">
-        <v>75030</v>
+        <v>75029</v>
       </c>
       <c r="D289" s="50" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E289" s="50">
         <v>56</v>
@@ -25807,13 +25807,13 @@
         <v>58</v>
       </c>
       <c r="C290" s="50">
-        <v>84928</v>
+        <v>75030</v>
       </c>
       <c r="D290" s="50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E290" s="50">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F290" s="50">
         <v>0</v>
@@ -25828,7 +25828,7 @@
         <v>62</v>
       </c>
       <c r="K290" s="50" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="L290" s="50" t="s">
         <v>1</v>
@@ -25837,14 +25837,12 @@
         <v>1</v>
       </c>
       <c r="N290" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O290" s="50">
         <v>0</v>
       </c>
-      <c r="P290" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P290" s="50"/>
       <c r="Q290" s="50">
         <v>0</v>
       </c>
@@ -25887,40 +25885,37 @@
         <v>58</v>
       </c>
       <c r="C291" s="50">
-        <v>84929</v>
+        <v>75033</v>
       </c>
       <c r="D291" s="50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E291" s="50">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F291" s="50">
         <v>0</v>
       </c>
       <c r="G291" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H291" s="50" t="s">
-        <v>639</v>
+        <v>60</v>
       </c>
       <c r="I291" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J291" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K291" s="50" t="s">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="L291" s="50" t="s">
-        <v>640</v>
+        <v>1</v>
       </c>
       <c r="M291" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N291" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O291" s="50">
         <v>0</v>
@@ -25968,19 +25963,19 @@
         <v>58</v>
       </c>
       <c r="C292" s="50">
-        <v>84930</v>
+        <v>75034</v>
       </c>
       <c r="D292" s="50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E292" s="50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F292" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G292" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="I292" s="50" t="s">
         <v>61</v>
@@ -25989,16 +25984,16 @@
         <v>62</v>
       </c>
       <c r="K292" s="50" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
       <c r="L292" s="50" t="s">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="M292" s="50" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="N292" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O292" s="50">
         <v>0</v>
@@ -26046,31 +26041,28 @@
         <v>58</v>
       </c>
       <c r="C293" s="50">
-        <v>84931</v>
+        <v>75035</v>
       </c>
       <c r="D293" s="50" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E293" s="50">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F293" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H293" s="50" t="s">
-        <v>645</v>
+        <v>60</v>
       </c>
       <c r="I293" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J293" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K293" s="50" t="s">
-        <v>392</v>
+        <v>301</v>
       </c>
       <c r="L293" s="50" t="s">
         <v>1</v>
@@ -26079,7 +26071,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O293" s="50">
         <v>0</v>
@@ -26127,16 +26119,16 @@
         <v>58</v>
       </c>
       <c r="C294" s="50">
-        <v>84932</v>
+        <v>75036</v>
       </c>
       <c r="D294" s="50" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E294" s="50">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F294" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G294" s="50" t="s">
         <v>60</v>
@@ -26148,16 +26140,16 @@
         <v>62</v>
       </c>
       <c r="K294" s="50" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
       <c r="L294" s="50" t="s">
-        <v>647</v>
+        <v>1</v>
       </c>
       <c r="M294" s="50" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="N294" s="50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O294" s="50">
         <v>0</v>
@@ -26205,78 +26197,47 @@
         <v>58</v>
       </c>
       <c r="C295" s="50">
-        <v>84933</v>
+        <v>75037</v>
       </c>
       <c r="D295" s="50" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E295" s="50">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F295" s="50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G295" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H295" s="50" t="s">
-        <v>649</v>
-      </c>
       <c r="I295" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J295" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K295" s="50" t="s">
-        <v>392</v>
-      </c>
-      <c r="L295" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M295" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K295" s="50"/>
+      <c r="L295" s="50"/>
+      <c r="M295" s="50"/>
       <c r="N295" s="50">
-        <v>8</v>
-      </c>
-      <c r="O295" s="50">
-        <v>0</v>
-      </c>
-      <c r="P295" s="50"/>
-      <c r="Q295" s="50">
-        <v>0</v>
-      </c>
-      <c r="R295" s="50">
-        <v>0</v>
-      </c>
-      <c r="S295" s="50">
-        <v>0</v>
-      </c>
-      <c r="T295" s="50">
-        <v>0</v>
-      </c>
-      <c r="U295" s="50">
-        <v>0</v>
-      </c>
-      <c r="V295" s="50">
-        <v>0</v>
-      </c>
-      <c r="W295" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X295" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y295" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z295" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA295" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="O295" s="50"/>
+      <c r="P295" s="50" t="s">
+        <v>644</v>
+      </c>
+      <c r="Q295" s="50"/>
+      <c r="R295" s="50"/>
+      <c r="S295" s="50"/>
+      <c r="T295" s="50"/>
+      <c r="U295" s="50"/>
+      <c r="V295" s="50"/>
+      <c r="W295" s="50"/>
+      <c r="X295" s="50"/>
+      <c r="Y295" s="50"/>
+      <c r="Z295" s="52"/>
+      <c r="AA295" s="50"/>
     </row>
     <row r="296">
       <c r="A296" s="50">
@@ -26286,31 +26247,28 @@
         <v>58</v>
       </c>
       <c r="C296" s="50">
-        <v>84934</v>
+        <v>84928</v>
       </c>
       <c r="D296" s="50" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E296" s="50">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F296" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H296" s="50" t="s">
-        <v>651</v>
+        <v>60</v>
       </c>
       <c r="I296" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J296" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K296" s="50" t="s">
-        <v>398</v>
+        <v>75</v>
       </c>
       <c r="L296" s="50" t="s">
         <v>1</v>
@@ -26324,7 +26282,9 @@
       <c r="O296" s="50">
         <v>0</v>
       </c>
-      <c r="P296" s="50"/>
+      <c r="P296" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q296" s="50">
         <v>0</v>
       </c>
@@ -26367,22 +26327,22 @@
         <v>58</v>
       </c>
       <c r="C297" s="50">
-        <v>84935</v>
+        <v>84929</v>
       </c>
       <c r="D297" s="50" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E297" s="50">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F297" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G297" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H297" s="50" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="I297" s="50" t="s">
         <v>78</v>
@@ -26391,10 +26351,10 @@
         <v>62</v>
       </c>
       <c r="K297" s="50" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="L297" s="50" t="s">
-        <v>1</v>
+        <v>648</v>
       </c>
       <c r="M297" s="50" t="s">
         <v>1</v>
@@ -26448,37 +26408,34 @@
         <v>58</v>
       </c>
       <c r="C298" s="50">
-        <v>84936</v>
+        <v>84930</v>
       </c>
       <c r="D298" s="50" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E298" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F298" s="50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G298" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="H298" s="50" t="s">
-        <v>655</v>
+        <v>138</v>
       </c>
       <c r="I298" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J298" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="L298" s="50" t="s">
-        <v>1</v>
+        <v>650</v>
       </c>
       <c r="M298" s="50" t="s">
-        <v>1</v>
+        <v>651</v>
       </c>
       <c r="N298" s="50">
         <v>8</v>
@@ -26503,7 +26460,7 @@
         <v>0</v>
       </c>
       <c r="V298" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W298" s="50" t="s">
         <v>1</v>
@@ -26529,22 +26486,22 @@
         <v>58</v>
       </c>
       <c r="C299" s="50">
-        <v>84937</v>
+        <v>84931</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E299" s="50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F299" s="50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G299" s="50" t="s">
         <v>138</v>
       </c>
       <c r="H299" s="50" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="I299" s="50" t="s">
         <v>78</v>
@@ -26553,7 +26510,7 @@
         <v>62</v>
       </c>
       <c r="K299" s="50" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L299" s="50" t="s">
         <v>1</v>
@@ -26584,7 +26541,7 @@
         <v>0</v>
       </c>
       <c r="V299" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W299" s="50" t="s">
         <v>1</v>
@@ -26610,37 +26567,34 @@
         <v>58</v>
       </c>
       <c r="C300" s="50">
-        <v>84938</v>
+        <v>84932</v>
       </c>
       <c r="D300" s="50" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E300" s="50">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F300" s="50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G300" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H300" s="50" t="s">
-        <v>659</v>
-      </c>
       <c r="I300" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J300" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K300" s="50" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L300" s="50" t="s">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="M300" s="50" t="s">
-        <v>1</v>
+        <v>651</v>
       </c>
       <c r="N300" s="50">
         <v>8</v>
@@ -26691,22 +26645,22 @@
         <v>58</v>
       </c>
       <c r="C301" s="50">
-        <v>84939</v>
+        <v>84933</v>
       </c>
       <c r="D301" s="50" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E301" s="50">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F301" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H301" s="50" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="I301" s="50" t="s">
         <v>78</v>
@@ -26715,7 +26669,7 @@
         <v>62</v>
       </c>
       <c r="K301" s="50" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L301" s="50" t="s">
         <v>1</v>
@@ -26772,22 +26726,22 @@
         <v>58</v>
       </c>
       <c r="C302" s="50">
-        <v>84940</v>
+        <v>84934</v>
       </c>
       <c r="D302" s="50" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E302" s="50">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F302" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G302" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H302" s="50" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="I302" s="50" t="s">
         <v>78</v>
@@ -26796,7 +26750,7 @@
         <v>62</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L302" s="50" t="s">
         <v>1</v>
@@ -26853,22 +26807,22 @@
         <v>58</v>
       </c>
       <c r="C303" s="50">
-        <v>84941</v>
+        <v>84935</v>
       </c>
       <c r="D303" s="50" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E303" s="50">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F303" s="50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G303" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H303" s="50" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="I303" s="50" t="s">
         <v>78</v>
@@ -26877,10 +26831,10 @@
         <v>62</v>
       </c>
       <c r="K303" s="50" t="s">
-        <v>192</v>
+        <v>403</v>
       </c>
       <c r="L303" s="50" t="s">
-        <v>666</v>
+        <v>1</v>
       </c>
       <c r="M303" s="50" t="s">
         <v>1</v>
@@ -26934,34 +26888,37 @@
         <v>58</v>
       </c>
       <c r="C304" s="50">
-        <v>84942</v>
+        <v>84936</v>
       </c>
       <c r="D304" s="50" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="E304" s="50">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F304" s="50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G304" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H304" s="50" t="s">
+        <v>663</v>
+      </c>
       <c r="I304" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J304" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K304" s="50" t="s">
-        <v>285</v>
+        <v>400</v>
       </c>
       <c r="L304" s="50" t="s">
-        <v>668</v>
+        <v>1</v>
       </c>
       <c r="M304" s="50" t="s">
-        <v>669</v>
+        <v>1</v>
       </c>
       <c r="N304" s="50">
         <v>8</v>
@@ -26986,7 +26943,7 @@
         <v>0</v>
       </c>
       <c r="V304" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W304" s="50" t="s">
         <v>1</v>
@@ -27012,22 +26969,22 @@
         <v>58</v>
       </c>
       <c r="C305" s="50">
-        <v>84943</v>
+        <v>84937</v>
       </c>
       <c r="D305" s="50" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E305" s="50">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F305" s="50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G305" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H305" s="50" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="I305" s="50" t="s">
         <v>78</v>
@@ -27036,7 +26993,7 @@
         <v>62</v>
       </c>
       <c r="K305" s="50" t="s">
-        <v>276</v>
+        <v>396</v>
       </c>
       <c r="L305" s="50" t="s">
         <v>1</v>
@@ -27067,7 +27024,7 @@
         <v>0</v>
       </c>
       <c r="V305" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W305" s="50" t="s">
         <v>1</v>
@@ -27093,34 +27050,37 @@
         <v>58</v>
       </c>
       <c r="C306" s="50">
-        <v>84944</v>
+        <v>84938</v>
       </c>
       <c r="D306" s="50" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E306" s="50">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F306" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G306" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H306" s="50" t="s">
+        <v>667</v>
+      </c>
       <c r="I306" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J306" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K306" s="50" t="s">
-        <v>271</v>
+        <v>386</v>
       </c>
       <c r="L306" s="50" t="s">
-        <v>673</v>
+        <v>1</v>
       </c>
       <c r="M306" s="50" t="s">
-        <v>669</v>
+        <v>1</v>
       </c>
       <c r="N306" s="50">
         <v>8</v>
@@ -27171,22 +27131,22 @@
         <v>58</v>
       </c>
       <c r="C307" s="50">
-        <v>84945</v>
+        <v>84939</v>
       </c>
       <c r="D307" s="50" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E307" s="50">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="F307" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G307" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H307" s="50" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="I307" s="50" t="s">
         <v>78</v>
@@ -27195,7 +27155,7 @@
         <v>62</v>
       </c>
       <c r="K307" s="50" t="s">
-        <v>283</v>
+        <v>394</v>
       </c>
       <c r="L307" s="50" t="s">
         <v>1</v>
@@ -27252,28 +27212,31 @@
         <v>58</v>
       </c>
       <c r="C308" s="50">
-        <v>84946</v>
+        <v>84940</v>
       </c>
       <c r="D308" s="50" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E308" s="50">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F308" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G308" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H308" s="50" t="s">
+        <v>671</v>
+      </c>
       <c r="I308" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J308" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K308" s="50" t="s">
-        <v>614</v>
+        <v>394</v>
       </c>
       <c r="L308" s="50" t="s">
         <v>1</v>
@@ -27330,31 +27293,34 @@
         <v>58</v>
       </c>
       <c r="C309" s="50">
-        <v>84947</v>
+        <v>84941</v>
       </c>
       <c r="D309" s="50" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E309" s="50">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F309" s="50">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G309" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H309" s="50" t="s">
+        <v>673</v>
+      </c>
       <c r="I309" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J309" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K309" s="50" t="s">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="L309" s="50" t="s">
-        <v>1</v>
+        <v>674</v>
       </c>
       <c r="M309" s="50" t="s">
         <v>1</v>
@@ -27408,16 +27374,16 @@
         <v>58</v>
       </c>
       <c r="C310" s="50">
-        <v>84948</v>
+        <v>84942</v>
       </c>
       <c r="D310" s="50" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E310" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F310" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G310" s="50" t="s">
         <v>60</v>
@@ -27429,13 +27395,13 @@
         <v>62</v>
       </c>
       <c r="K310" s="50" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="L310" s="50" t="s">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="M310" s="50" t="s">
-        <v>1</v>
+        <v>677</v>
       </c>
       <c r="N310" s="50">
         <v>8</v>
@@ -27486,28 +27452,31 @@
         <v>58</v>
       </c>
       <c r="C311" s="50">
-        <v>84949</v>
+        <v>84943</v>
       </c>
       <c r="D311" s="50" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E311" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F311" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G311" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H311" s="50" t="s">
+        <v>679</v>
+      </c>
       <c r="I311" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J311" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K311" s="50" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="L311" s="50" t="s">
         <v>1</v>
@@ -27564,16 +27533,16 @@
         <v>58</v>
       </c>
       <c r="C312" s="50">
-        <v>84950</v>
+        <v>84944</v>
       </c>
       <c r="D312" s="50" t="s">
         <v>680</v>
       </c>
       <c r="E312" s="50">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F312" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G312" s="50" t="s">
         <v>60</v>
@@ -27585,13 +27554,13 @@
         <v>62</v>
       </c>
       <c r="K312" s="50" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="L312" s="50" t="s">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="M312" s="50" t="s">
-        <v>1</v>
+        <v>677</v>
       </c>
       <c r="N312" s="50">
         <v>8</v>
@@ -27642,28 +27611,31 @@
         <v>58</v>
       </c>
       <c r="C313" s="50">
-        <v>84951</v>
+        <v>84945</v>
       </c>
       <c r="D313" s="50" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E313" s="50">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F313" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G313" s="50" t="s">
         <v>60</v>
       </c>
+      <c r="H313" s="50" t="s">
+        <v>683</v>
+      </c>
       <c r="I313" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J313" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K313" s="50" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="L313" s="50" t="s">
         <v>1</v>
@@ -27720,16 +27692,16 @@
         <v>58</v>
       </c>
       <c r="C314" s="50">
-        <v>84952</v>
+        <v>84946</v>
       </c>
       <c r="D314" s="50" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E314" s="50">
         <v>56</v>
       </c>
       <c r="F314" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" s="50" t="s">
         <v>60</v>
@@ -27741,7 +27713,7 @@
         <v>62</v>
       </c>
       <c r="K314" s="50" t="s">
-        <v>301</v>
+        <v>616</v>
       </c>
       <c r="L314" s="50" t="s">
         <v>1</v>
@@ -27798,10 +27770,10 @@
         <v>58</v>
       </c>
       <c r="C315" s="50">
-        <v>84953</v>
+        <v>84947</v>
       </c>
       <c r="D315" s="50" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E315" s="50">
         <v>56</v>
@@ -27876,10 +27848,10 @@
         <v>58</v>
       </c>
       <c r="C316" s="50">
-        <v>84954</v>
+        <v>84948</v>
       </c>
       <c r="D316" s="50" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E316" s="50">
         <v>56</v>
@@ -27954,10 +27926,10 @@
         <v>58</v>
       </c>
       <c r="C317" s="50">
-        <v>84955</v>
+        <v>84949</v>
       </c>
       <c r="D317" s="50" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E317" s="50">
         <v>56</v>
@@ -28032,10 +28004,10 @@
         <v>58</v>
       </c>
       <c r="C318" s="50">
-        <v>84956</v>
+        <v>84950</v>
       </c>
       <c r="D318" s="50" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E318" s="50">
         <v>56</v>
@@ -28110,10 +28082,10 @@
         <v>58</v>
       </c>
       <c r="C319" s="50">
-        <v>84957</v>
+        <v>84951</v>
       </c>
       <c r="D319" s="50" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E319" s="50">
         <v>56</v>
@@ -28188,10 +28160,10 @@
         <v>58</v>
       </c>
       <c r="C320" s="50">
-        <v>84958</v>
+        <v>84952</v>
       </c>
       <c r="D320" s="50" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E320" s="50">
         <v>56</v>
@@ -28266,10 +28238,10 @@
         <v>58</v>
       </c>
       <c r="C321" s="50">
-        <v>84959</v>
+        <v>84953</v>
       </c>
       <c r="D321" s="50" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E321" s="50">
         <v>56</v>
@@ -28344,10 +28316,10 @@
         <v>58</v>
       </c>
       <c r="C322" s="50">
-        <v>84960</v>
+        <v>84954</v>
       </c>
       <c r="D322" s="50" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E322" s="50">
         <v>56</v>
@@ -28422,10 +28394,10 @@
         <v>58</v>
       </c>
       <c r="C323" s="50">
-        <v>84961</v>
+        <v>84955</v>
       </c>
       <c r="D323" s="50" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E323" s="50">
         <v>56</v>
@@ -28500,10 +28472,10 @@
         <v>58</v>
       </c>
       <c r="C324" s="50">
-        <v>84962</v>
+        <v>84956</v>
       </c>
       <c r="D324" s="50" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E324" s="50">
         <v>56</v>
@@ -28578,10 +28550,10 @@
         <v>58</v>
       </c>
       <c r="C325" s="50">
-        <v>84963</v>
+        <v>84957</v>
       </c>
       <c r="D325" s="50" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E325" s="50">
         <v>56</v>
@@ -28656,10 +28628,10 @@
         <v>58</v>
       </c>
       <c r="C326" s="50">
-        <v>84964</v>
+        <v>84958</v>
       </c>
       <c r="D326" s="50" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E326" s="50">
         <v>56</v>
@@ -28734,10 +28706,10 @@
         <v>58</v>
       </c>
       <c r="C327" s="50">
-        <v>84965</v>
+        <v>84959</v>
       </c>
       <c r="D327" s="50" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E327" s="50">
         <v>56</v>
@@ -28812,10 +28784,10 @@
         <v>58</v>
       </c>
       <c r="C328" s="50">
-        <v>84966</v>
+        <v>84960</v>
       </c>
       <c r="D328" s="50" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E328" s="50">
         <v>56</v>
@@ -28890,10 +28862,10 @@
         <v>58</v>
       </c>
       <c r="C329" s="50">
-        <v>84967</v>
+        <v>84961</v>
       </c>
       <c r="D329" s="50" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E329" s="50">
         <v>56</v>
@@ -28968,10 +28940,10 @@
         <v>58</v>
       </c>
       <c r="C330" s="50">
-        <v>84968</v>
+        <v>84962</v>
       </c>
       <c r="D330" s="50" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E330" s="50">
         <v>56</v>
@@ -29046,31 +29018,28 @@
         <v>58</v>
       </c>
       <c r="C331" s="50">
-        <v>84969</v>
+        <v>84963</v>
       </c>
       <c r="D331" s="50" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E331" s="50">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F331" s="50">
         <v>0</v>
       </c>
       <c r="G331" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="H331" s="50" t="s">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="I331" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J331" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K331" s="50" t="s">
-        <v>570</v>
+        <v>301</v>
       </c>
       <c r="L331" s="50" t="s">
         <v>1</v>
@@ -29127,31 +29096,28 @@
         <v>58</v>
       </c>
       <c r="C332" s="50">
-        <v>84970</v>
+        <v>84964</v>
       </c>
       <c r="D332" s="50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E332" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F332" s="50">
         <v>0</v>
       </c>
       <c r="G332" s="50" t="s">
-        <v>702</v>
-      </c>
-      <c r="H332" s="50" t="s">
-        <v>703</v>
+        <v>60</v>
       </c>
       <c r="I332" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J332" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K332" s="50" t="s">
-        <v>573</v>
+        <v>301</v>
       </c>
       <c r="L332" s="50" t="s">
         <v>1</v>
@@ -29208,37 +29174,34 @@
         <v>58</v>
       </c>
       <c r="C333" s="50">
-        <v>84971</v>
+        <v>84965</v>
       </c>
       <c r="D333" s="50" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E333" s="50">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F333" s="50">
         <v>0</v>
       </c>
       <c r="G333" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="H333" s="50" t="s">
-        <v>705</v>
+        <v>60</v>
       </c>
       <c r="I333" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J333" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K333" s="50" t="s">
-        <v>578</v>
+        <v>301</v>
       </c>
       <c r="L333" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M333" s="50" t="s">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="N333" s="50">
         <v>8</v>
@@ -29289,31 +29252,28 @@
         <v>58</v>
       </c>
       <c r="C334" s="50">
-        <v>84972</v>
+        <v>84966</v>
       </c>
       <c r="D334" s="50" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E334" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F334" s="50">
         <v>0</v>
       </c>
       <c r="G334" s="50" t="s">
-        <v>708</v>
-      </c>
-      <c r="H334" s="50" t="s">
-        <v>709</v>
+        <v>60</v>
       </c>
       <c r="I334" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J334" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K334" s="50" t="s">
-        <v>573</v>
+        <v>301</v>
       </c>
       <c r="L334" s="50" t="s">
         <v>1</v>
@@ -29370,34 +29330,31 @@
         <v>58</v>
       </c>
       <c r="C335" s="50">
-        <v>84973</v>
+        <v>84967</v>
       </c>
       <c r="D335" s="50" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="E335" s="50">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F335" s="50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G335" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H335" s="50" t="s">
-        <v>711</v>
-      </c>
       <c r="I335" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J335" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K335" s="50" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="L335" s="50" t="s">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="M335" s="50" t="s">
         <v>1</v>
@@ -29451,13 +29408,13 @@
         <v>58</v>
       </c>
       <c r="C336" s="50">
-        <v>84974</v>
+        <v>84968</v>
       </c>
       <c r="D336" s="50" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="E336" s="50">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F336" s="50">
         <v>0</v>
@@ -29465,17 +29422,14 @@
       <c r="G336" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H336" s="50" t="s">
-        <v>714</v>
-      </c>
       <c r="I336" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J336" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K336" s="50" t="s">
-        <v>573</v>
+        <v>301</v>
       </c>
       <c r="L336" s="50" t="s">
         <v>1</v>
@@ -29532,47 +29486,78 @@
         <v>58</v>
       </c>
       <c r="C337" s="50">
-        <v>84976</v>
+        <v>84969</v>
       </c>
       <c r="D337" s="50" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="E337" s="50">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F337" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
+      </c>
+      <c r="H337" s="50" t="s">
+        <v>708</v>
       </c>
       <c r="I337" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J337" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K337" s="50"/>
-      <c r="L337" s="50"/>
-      <c r="M337" s="50"/>
+      <c r="K337" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="L337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M337" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N337" s="50">
         <v>8</v>
       </c>
-      <c r="O337" s="50"/>
-      <c r="P337" s="50" t="s">
-        <v>716</v>
-      </c>
-      <c r="Q337" s="50"/>
-      <c r="R337" s="50"/>
-      <c r="S337" s="50"/>
-      <c r="T337" s="50"/>
-      <c r="U337" s="50"/>
-      <c r="V337" s="50"/>
-      <c r="W337" s="50"/>
-      <c r="X337" s="50"/>
-      <c r="Y337" s="50"/>
-      <c r="Z337" s="52"/>
-      <c r="AA337" s="50"/>
+      <c r="O337" s="50">
+        <v>0</v>
+      </c>
+      <c r="P337" s="50"/>
+      <c r="Q337" s="50">
+        <v>0</v>
+      </c>
+      <c r="R337" s="50">
+        <v>0</v>
+      </c>
+      <c r="S337" s="50">
+        <v>0</v>
+      </c>
+      <c r="T337" s="50">
+        <v>0</v>
+      </c>
+      <c r="U337" s="50">
+        <v>0</v>
+      </c>
+      <c r="V337" s="50">
+        <v>0</v>
+      </c>
+      <c r="W337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y337" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z337" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA337" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="50">
@@ -29582,47 +29567,78 @@
         <v>58</v>
       </c>
       <c r="C338" s="50">
-        <v>84977</v>
+        <v>84970</v>
       </c>
       <c r="D338" s="50" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="E338" s="50">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F338" s="50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G338" s="50" t="s">
-        <v>60</v>
+        <v>710</v>
+      </c>
+      <c r="H338" s="50" t="s">
+        <v>711</v>
       </c>
       <c r="I338" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J338" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K338" s="50"/>
-      <c r="L338" s="50"/>
-      <c r="M338" s="50"/>
+      <c r="K338" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="L338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M338" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="N338" s="50">
         <v>8</v>
       </c>
-      <c r="O338" s="50"/>
-      <c r="P338" s="50" t="s">
-        <v>718</v>
-      </c>
-      <c r="Q338" s="50"/>
-      <c r="R338" s="50"/>
-      <c r="S338" s="50"/>
-      <c r="T338" s="50"/>
-      <c r="U338" s="50"/>
-      <c r="V338" s="50"/>
-      <c r="W338" s="50"/>
-      <c r="X338" s="50"/>
-      <c r="Y338" s="50"/>
-      <c r="Z338" s="52"/>
-      <c r="AA338" s="50"/>
+      <c r="O338" s="50">
+        <v>0</v>
+      </c>
+      <c r="P338" s="50"/>
+      <c r="Q338" s="50">
+        <v>0</v>
+      </c>
+      <c r="R338" s="50">
+        <v>0</v>
+      </c>
+      <c r="S338" s="50">
+        <v>0</v>
+      </c>
+      <c r="T338" s="50">
+        <v>0</v>
+      </c>
+      <c r="U338" s="50">
+        <v>0</v>
+      </c>
+      <c r="V338" s="50">
+        <v>0</v>
+      </c>
+      <c r="W338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y338" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z338" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA338" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="50">
@@ -29632,47 +29648,78 @@
         <v>58</v>
       </c>
       <c r="C339" s="50">
-        <v>84978</v>
+        <v>84971</v>
       </c>
       <c r="D339" s="50" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="E339" s="50">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F339" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G339" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
+      </c>
+      <c r="H339" s="50" t="s">
+        <v>713</v>
       </c>
       <c r="I339" s="50" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J339" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K339" s="50"/>
-      <c r="L339" s="50"/>
-      <c r="M339" s="50"/>
+      <c r="K339" s="50" t="s">
+        <v>580</v>
+      </c>
+      <c r="L339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M339" s="50" t="s">
+        <v>714</v>
+      </c>
       <c r="N339" s="50">
         <v>8</v>
       </c>
-      <c r="O339" s="50"/>
-      <c r="P339" s="50" t="s">
-        <v>720</v>
-      </c>
-      <c r="Q339" s="50"/>
-      <c r="R339" s="50"/>
-      <c r="S339" s="50"/>
-      <c r="T339" s="50"/>
-      <c r="U339" s="50"/>
-      <c r="V339" s="50"/>
-      <c r="W339" s="50"/>
-      <c r="X339" s="50"/>
-      <c r="Y339" s="50"/>
-      <c r="Z339" s="52"/>
-      <c r="AA339" s="50"/>
+      <c r="O339" s="50">
+        <v>0</v>
+      </c>
+      <c r="P339" s="50"/>
+      <c r="Q339" s="50">
+        <v>0</v>
+      </c>
+      <c r="R339" s="50">
+        <v>0</v>
+      </c>
+      <c r="S339" s="50">
+        <v>0</v>
+      </c>
+      <c r="T339" s="50">
+        <v>0</v>
+      </c>
+      <c r="U339" s="50">
+        <v>0</v>
+      </c>
+      <c r="V339" s="50">
+        <v>0</v>
+      </c>
+      <c r="W339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y339" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z339" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA339" s="50" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="50">
@@ -29682,22 +29729,22 @@
         <v>58</v>
       </c>
       <c r="C340" s="50">
-        <v>84979</v>
+        <v>84972</v>
       </c>
       <c r="D340" s="50" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E340" s="50">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F340" s="50">
         <v>0</v>
       </c>
       <c r="G340" s="50" t="s">
-        <v>83</v>
+        <v>716</v>
       </c>
       <c r="H340" s="50" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="I340" s="50" t="s">
         <v>78</v>
@@ -29706,13 +29753,13 @@
         <v>62</v>
       </c>
       <c r="K340" s="50" t="s">
-        <v>327</v>
+        <v>575</v>
       </c>
       <c r="L340" s="50" t="s">
-        <v>723</v>
+        <v>1</v>
       </c>
       <c r="M340" s="50" t="s">
-        <v>724</v>
+        <v>1</v>
       </c>
       <c r="N340" s="50">
         <v>8</v>
@@ -29763,22 +29810,22 @@
         <v>58</v>
       </c>
       <c r="C341" s="50">
-        <v>84980</v>
+        <v>84973</v>
       </c>
       <c r="D341" s="50" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E341" s="50">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="F341" s="50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G341" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H341" s="50" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="I341" s="50" t="s">
         <v>78</v>
@@ -29787,10 +29834,10 @@
         <v>62</v>
       </c>
       <c r="K341" s="50" t="s">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L341" s="50" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="M341" s="50" t="s">
         <v>1</v>
@@ -29844,13 +29891,13 @@
         <v>58</v>
       </c>
       <c r="C342" s="50">
-        <v>84981</v>
+        <v>84974</v>
       </c>
       <c r="D342" s="50" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="E342" s="50">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F342" s="50">
         <v>0</v>
@@ -29859,7 +29906,7 @@
         <v>60</v>
       </c>
       <c r="H342" s="50" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="I342" s="50" t="s">
         <v>78</v>
@@ -29868,7 +29915,7 @@
         <v>62</v>
       </c>
       <c r="K342" s="50" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
       <c r="L342" s="50" t="s">
         <v>1</v>
@@ -29925,16 +29972,16 @@
         <v>58</v>
       </c>
       <c r="C343" s="50">
-        <v>84982</v>
+        <v>84976</v>
       </c>
       <c r="D343" s="50" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="E343" s="50">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F343" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G343" s="50" t="s">
         <v>60</v>
@@ -29945,57 +29992,27 @@
       <c r="J343" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K343" s="50" t="s">
-        <v>731</v>
-      </c>
-      <c r="L343" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M343" s="50" t="s">
-        <v>732</v>
-      </c>
+      <c r="K343" s="50"/>
+      <c r="L343" s="50"/>
+      <c r="M343" s="50"/>
       <c r="N343" s="50">
         <v>8</v>
       </c>
-      <c r="O343" s="50">
-        <v>0</v>
-      </c>
+      <c r="O343" s="50"/>
       <c r="P343" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q343" s="50">
-        <v>0</v>
-      </c>
-      <c r="R343" s="50">
-        <v>0</v>
-      </c>
-      <c r="S343" s="50">
-        <v>0</v>
-      </c>
-      <c r="T343" s="50">
-        <v>0</v>
-      </c>
-      <c r="U343" s="50">
-        <v>0</v>
-      </c>
-      <c r="V343" s="50">
-        <v>0</v>
-      </c>
-      <c r="W343" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X343" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y343" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z343" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA343" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>724</v>
+      </c>
+      <c r="Q343" s="50"/>
+      <c r="R343" s="50"/>
+      <c r="S343" s="50"/>
+      <c r="T343" s="50"/>
+      <c r="U343" s="50"/>
+      <c r="V343" s="50"/>
+      <c r="W343" s="50"/>
+      <c r="X343" s="50"/>
+      <c r="Y343" s="50"/>
+      <c r="Z343" s="52"/>
+      <c r="AA343" s="50"/>
     </row>
     <row r="344">
       <c r="A344" s="50">
@@ -30005,80 +30022,47 @@
         <v>58</v>
       </c>
       <c r="C344" s="50">
-        <v>84983</v>
+        <v>84977</v>
       </c>
       <c r="D344" s="50" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="E344" s="50">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F344" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G344" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H344" s="50" t="s">
-        <v>733</v>
-      </c>
       <c r="I344" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J344" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K344" s="50" t="s">
-        <v>734</v>
-      </c>
-      <c r="L344" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M344" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K344" s="50"/>
+      <c r="L344" s="50"/>
+      <c r="M344" s="50"/>
       <c r="N344" s="50">
         <v>8</v>
       </c>
-      <c r="O344" s="50">
-        <v>0</v>
-      </c>
+      <c r="O344" s="50"/>
       <c r="P344" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q344" s="50">
-        <v>0</v>
-      </c>
-      <c r="R344" s="50">
-        <v>0</v>
-      </c>
-      <c r="S344" s="50">
-        <v>0</v>
-      </c>
-      <c r="T344" s="50">
-        <v>0</v>
-      </c>
-      <c r="U344" s="50">
-        <v>0</v>
-      </c>
-      <c r="V344" s="50">
-        <v>0</v>
-      </c>
-      <c r="W344" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X344" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y344" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z344" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA344" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="Q344" s="50"/>
+      <c r="R344" s="50"/>
+      <c r="S344" s="50"/>
+      <c r="T344" s="50"/>
+      <c r="U344" s="50"/>
+      <c r="V344" s="50"/>
+      <c r="W344" s="50"/>
+      <c r="X344" s="50"/>
+      <c r="Y344" s="50"/>
+      <c r="Z344" s="52"/>
+      <c r="AA344" s="50"/>
     </row>
     <row r="345">
       <c r="A345" s="50">
@@ -30088,80 +30072,47 @@
         <v>58</v>
       </c>
       <c r="C345" s="50">
-        <v>84984</v>
+        <v>84978</v>
       </c>
       <c r="D345" s="50" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="E345" s="50">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F345" s="50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G345" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="H345" s="50" t="s">
-        <v>736</v>
-      </c>
       <c r="I345" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J345" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="K345" s="50" t="s">
-        <v>737</v>
-      </c>
-      <c r="L345" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="M345" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="K345" s="50"/>
+      <c r="L345" s="50"/>
+      <c r="M345" s="50"/>
       <c r="N345" s="50">
         <v>8</v>
       </c>
-      <c r="O345" s="50">
-        <v>0</v>
-      </c>
+      <c r="O345" s="50"/>
       <c r="P345" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q345" s="50">
-        <v>0</v>
-      </c>
-      <c r="R345" s="50">
-        <v>0</v>
-      </c>
-      <c r="S345" s="50">
-        <v>0</v>
-      </c>
-      <c r="T345" s="50">
-        <v>0</v>
-      </c>
-      <c r="U345" s="50">
-        <v>0</v>
-      </c>
-      <c r="V345" s="50">
-        <v>0</v>
-      </c>
-      <c r="W345" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X345" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y345" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z345" s="52">
-        <v>0</v>
-      </c>
-      <c r="AA345" s="50" t="s">
-        <v>1</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="Q345" s="50"/>
+      <c r="R345" s="50"/>
+      <c r="S345" s="50"/>
+      <c r="T345" s="50"/>
+      <c r="U345" s="50"/>
+      <c r="V345" s="50"/>
+      <c r="W345" s="50"/>
+      <c r="X345" s="50"/>
+      <c r="Y345" s="50"/>
+      <c r="Z345" s="52"/>
+      <c r="AA345" s="50"/>
     </row>
     <row r="346">
       <c r="A346" s="50">
@@ -30171,22 +30122,22 @@
         <v>58</v>
       </c>
       <c r="C346" s="50">
-        <v>330037</v>
+        <v>84979</v>
       </c>
       <c r="D346" s="50" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="E346" s="50">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F346" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" s="50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H346" s="50" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="I346" s="50" t="s">
         <v>78</v>
@@ -30195,23 +30146,21 @@
         <v>62</v>
       </c>
       <c r="K346" s="50" t="s">
-        <v>96</v>
+        <v>327</v>
       </c>
       <c r="L346" s="50" t="s">
-        <v>1</v>
+        <v>731</v>
       </c>
       <c r="M346" s="50" t="s">
-        <v>1</v>
+        <v>732</v>
       </c>
       <c r="N346" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O346" s="50">
         <v>0</v>
       </c>
-      <c r="P346" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P346" s="50"/>
       <c r="Q346" s="50">
         <v>0</v>
       </c>
@@ -30221,8 +30170,8 @@
       <c r="S346" s="50">
         <v>0</v>
       </c>
-      <c r="T346" s="50" t="s">
-        <v>61</v>
+      <c r="T346" s="50">
+        <v>0</v>
       </c>
       <c r="U346" s="50">
         <v>0</v>
@@ -30254,22 +30203,22 @@
         <v>58</v>
       </c>
       <c r="C347" s="50">
-        <v>330038</v>
+        <v>84980</v>
       </c>
       <c r="D347" s="50" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E347" s="50">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F347" s="50">
         <v>0</v>
       </c>
       <c r="G347" s="50" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="H347" s="50" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I347" s="50" t="s">
         <v>78</v>
@@ -30278,16 +30227,16 @@
         <v>62</v>
       </c>
       <c r="K347" s="50" t="s">
-        <v>142</v>
+        <v>324</v>
       </c>
       <c r="L347" s="50" t="s">
-        <v>1</v>
+        <v>735</v>
       </c>
       <c r="M347" s="50" t="s">
-        <v>742</v>
+        <v>1</v>
       </c>
       <c r="N347" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O347" s="50">
         <v>0</v>
@@ -30335,22 +30284,22 @@
         <v>58</v>
       </c>
       <c r="C348" s="50">
-        <v>330039</v>
+        <v>84981</v>
       </c>
       <c r="D348" s="50" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="E348" s="50">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F348" s="50">
         <v>0</v>
       </c>
       <c r="G348" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H348" s="50" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I348" s="50" t="s">
         <v>78</v>
@@ -30359,16 +30308,16 @@
         <v>62</v>
       </c>
       <c r="K348" s="50" t="s">
-        <v>147</v>
+        <v>331</v>
       </c>
       <c r="L348" s="50" t="s">
-        <v>745</v>
+        <v>1</v>
       </c>
       <c r="M348" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N348" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O348" s="50">
         <v>0</v>
@@ -30416,45 +30365,44 @@
         <v>58</v>
       </c>
       <c r="C349" s="50">
-        <v>330040</v>
+        <v>84982</v>
       </c>
       <c r="D349" s="50" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="E349" s="50">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F349" s="50">
         <v>0</v>
       </c>
       <c r="G349" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H349" s="50" t="s">
-        <v>747</v>
+        <v>60</v>
       </c>
       <c r="I349" s="50" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J349" s="50" t="s">
         <v>62</v>
       </c>
       <c r="K349" s="50" t="s">
-        <v>147</v>
+        <v>739</v>
       </c>
       <c r="L349" s="50" t="s">
-        <v>745</v>
+        <v>1</v>
       </c>
       <c r="M349" s="50" t="s">
-        <v>1</v>
+        <v>740</v>
       </c>
       <c r="N349" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O349" s="50">
         <v>0</v>
       </c>
-      <c r="P349" s="50"/>
+      <c r="P349" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q349" s="50">
         <v>0</v>
       </c>
@@ -30497,22 +30445,22 @@
         <v>58</v>
       </c>
       <c r="C350" s="50">
-        <v>330041</v>
+        <v>84983</v>
       </c>
       <c r="D350" s="50" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="E350" s="50">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F350" s="50">
         <v>0</v>
       </c>
       <c r="G350" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H350" s="50" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="I350" s="50" t="s">
         <v>78</v>
@@ -30521,21 +30469,23 @@
         <v>62</v>
       </c>
       <c r="K350" s="50" t="s">
-        <v>147</v>
+        <v>742</v>
       </c>
       <c r="L350" s="50" t="s">
-        <v>745</v>
+        <v>1</v>
       </c>
       <c r="M350" s="50" t="s">
         <v>1</v>
       </c>
       <c r="N350" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O350" s="50">
         <v>0</v>
       </c>
-      <c r="P350" s="50"/>
+      <c r="P350" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q350" s="50">
         <v>0</v>
       </c>
@@ -30578,22 +30528,22 @@
         <v>58</v>
       </c>
       <c r="C351" s="50">
-        <v>330042</v>
+        <v>84984</v>
       </c>
       <c r="D351" s="50" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="E351" s="50">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F351" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H351" s="50" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I351" s="50" t="s">
         <v>78</v>
@@ -30602,21 +30552,23 @@
         <v>62</v>
       </c>
       <c r="K351" s="50" t="s">
-        <v>233</v>
+        <v>745</v>
       </c>
       <c r="L351" s="50" t="s">
-        <v>752</v>
+        <v>1</v>
       </c>
       <c r="M351" s="50" t="s">
-        <v>753</v>
+        <v>1</v>
       </c>
       <c r="N351" s="50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O351" s="50">
         <v>0</v>
       </c>
-      <c r="P351" s="50"/>
+      <c r="P351" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q351" s="50">
         <v>0</v>
       </c>
@@ -30659,13 +30611,13 @@
         <v>58</v>
       </c>
       <c r="C352" s="50">
-        <v>330043</v>
+        <v>330037</v>
       </c>
       <c r="D352" s="50" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E352" s="50">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F352" s="50">
         <v>1</v>
@@ -30674,7 +30626,7 @@
         <v>60</v>
       </c>
       <c r="H352" s="50" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="I352" s="50" t="s">
         <v>78</v>
@@ -30683,7 +30635,7 @@
         <v>62</v>
       </c>
       <c r="K352" s="50" t="s">
-        <v>238</v>
+        <v>96</v>
       </c>
       <c r="L352" s="50" t="s">
         <v>1</v>
@@ -30697,7 +30649,9 @@
       <c r="O352" s="50">
         <v>0</v>
       </c>
-      <c r="P352" s="50"/>
+      <c r="P352" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q352" s="50">
         <v>0</v>
       </c>
@@ -30707,8 +30661,8 @@
       <c r="S352" s="50">
         <v>0</v>
       </c>
-      <c r="T352" s="50">
-        <v>0</v>
+      <c r="T352" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U352" s="50">
         <v>0</v>
@@ -30740,22 +30694,22 @@
         <v>58</v>
       </c>
       <c r="C353" s="50">
-        <v>330044</v>
+        <v>330038</v>
       </c>
       <c r="D353" s="50" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="E353" s="50">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F353" s="50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G353" s="50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="H353" s="50" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="I353" s="50" t="s">
         <v>78</v>
@@ -30764,13 +30718,13 @@
         <v>62</v>
       </c>
       <c r="K353" s="50" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="L353" s="50" t="s">
-        <v>758</v>
+        <v>1</v>
       </c>
       <c r="M353" s="50" t="s">
-        <v>1</v>
+        <v>750</v>
       </c>
       <c r="N353" s="50">
         <v>33</v>
@@ -30821,22 +30775,22 @@
         <v>58</v>
       </c>
       <c r="C354" s="50">
-        <v>330045</v>
+        <v>330039</v>
       </c>
       <c r="D354" s="50" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="E354" s="50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F354" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G354" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H354" s="50" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="I354" s="50" t="s">
         <v>78</v>
@@ -30845,10 +30799,10 @@
         <v>62</v>
       </c>
       <c r="K354" s="50" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="L354" s="50" t="s">
-        <v>1</v>
+        <v>753</v>
       </c>
       <c r="M354" s="50" t="s">
         <v>1</v>
@@ -30859,9 +30813,7 @@
       <c r="O354" s="50">
         <v>0</v>
       </c>
-      <c r="P354" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P354" s="50"/>
       <c r="Q354" s="50">
         <v>0</v>
       </c>
@@ -30871,8 +30823,8 @@
       <c r="S354" s="50">
         <v>0</v>
       </c>
-      <c r="T354" s="50" t="s">
-        <v>61</v>
+      <c r="T354" s="50">
+        <v>0</v>
       </c>
       <c r="U354" s="50">
         <v>0</v>
@@ -30904,22 +30856,22 @@
         <v>58</v>
       </c>
       <c r="C355" s="50">
-        <v>330046</v>
+        <v>330040</v>
       </c>
       <c r="D355" s="50" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="E355" s="50">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F355" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G355" s="50" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="H355" s="50" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="I355" s="50" t="s">
         <v>78</v>
@@ -30928,10 +30880,10 @@
         <v>62</v>
       </c>
       <c r="K355" s="50" t="s">
-        <v>461</v>
+        <v>147</v>
       </c>
       <c r="L355" s="50" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="M355" s="50" t="s">
         <v>1</v>
@@ -30985,22 +30937,22 @@
         <v>58</v>
       </c>
       <c r="C356" s="50">
-        <v>330047</v>
+        <v>330041</v>
       </c>
       <c r="D356" s="50" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E356" s="50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F356" s="50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G356" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H356" s="50" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="I356" s="50" t="s">
         <v>78</v>
@@ -31009,10 +30961,10 @@
         <v>62</v>
       </c>
       <c r="K356" s="50" t="s">
-        <v>465</v>
+        <v>147</v>
       </c>
       <c r="L356" s="50" t="s">
-        <v>1</v>
+        <v>753</v>
       </c>
       <c r="M356" s="50" t="s">
         <v>1</v>
@@ -31066,13 +31018,13 @@
         <v>58</v>
       </c>
       <c r="C357" s="50">
-        <v>330048</v>
+        <v>330042</v>
       </c>
       <c r="D357" s="50" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="E357" s="50">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F357" s="50">
         <v>1</v>
@@ -31081,7 +31033,7 @@
         <v>60</v>
       </c>
       <c r="H357" s="50" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="I357" s="50" t="s">
         <v>78</v>
@@ -31090,13 +31042,13 @@
         <v>62</v>
       </c>
       <c r="K357" s="50" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="L357" s="50" t="s">
-        <v>1</v>
+        <v>760</v>
       </c>
       <c r="M357" s="50" t="s">
-        <v>1</v>
+        <v>761</v>
       </c>
       <c r="N357" s="50">
         <v>33</v>
@@ -31104,9 +31056,7 @@
       <c r="O357" s="50">
         <v>0</v>
       </c>
-      <c r="P357" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P357" s="50"/>
       <c r="Q357" s="50">
         <v>0</v>
       </c>
@@ -31116,8 +31066,8 @@
       <c r="S357" s="50">
         <v>0</v>
       </c>
-      <c r="T357" s="50" t="s">
-        <v>61</v>
+      <c r="T357" s="50">
+        <v>0</v>
       </c>
       <c r="U357" s="50">
         <v>0</v>
@@ -31149,22 +31099,22 @@
         <v>58</v>
       </c>
       <c r="C358" s="50">
-        <v>330049</v>
+        <v>330043</v>
       </c>
       <c r="D358" s="50" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E358" s="50">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F358" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H358" s="50" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="I358" s="50" t="s">
         <v>78</v>
@@ -31173,10 +31123,10 @@
         <v>62</v>
       </c>
       <c r="K358" s="50" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="L358" s="50" t="s">
-        <v>770</v>
+        <v>1</v>
       </c>
       <c r="M358" s="50" t="s">
         <v>1</v>
@@ -31230,22 +31180,22 @@
         <v>58</v>
       </c>
       <c r="C359" s="50">
-        <v>330050</v>
+        <v>330044</v>
       </c>
       <c r="D359" s="50" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="E359" s="50">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F359" s="50">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G359" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H359" s="50" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="I359" s="50" t="s">
         <v>78</v>
@@ -31254,10 +31204,10 @@
         <v>62</v>
       </c>
       <c r="K359" s="50" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="L359" s="50" t="s">
-        <v>1</v>
+        <v>766</v>
       </c>
       <c r="M359" s="50" t="s">
         <v>1</v>
@@ -31311,22 +31261,22 @@
         <v>58</v>
       </c>
       <c r="C360" s="50">
-        <v>330051</v>
+        <v>330045</v>
       </c>
       <c r="D360" s="50" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="E360" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F360" s="50">
         <v>1</v>
       </c>
       <c r="G360" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H360" s="50" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="I360" s="50" t="s">
         <v>78</v>
@@ -31335,7 +31285,7 @@
         <v>62</v>
       </c>
       <c r="K360" s="50" t="s">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="L360" s="50" t="s">
         <v>1</v>
@@ -31361,8 +31311,8 @@
       <c r="S360" s="50">
         <v>0</v>
       </c>
-      <c r="T360" s="50">
-        <v>0</v>
+      <c r="T360" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U360" s="50">
         <v>0</v>
@@ -31394,22 +31344,22 @@
         <v>58</v>
       </c>
       <c r="C361" s="50">
-        <v>330052</v>
+        <v>330046</v>
       </c>
       <c r="D361" s="50" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="E361" s="50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F361" s="50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G361" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H361" s="50" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="I361" s="50" t="s">
         <v>78</v>
@@ -31418,10 +31368,10 @@
         <v>62</v>
       </c>
       <c r="K361" s="50" t="s">
-        <v>294</v>
+        <v>461</v>
       </c>
       <c r="L361" s="50" t="s">
-        <v>1</v>
+        <v>771</v>
       </c>
       <c r="M361" s="50" t="s">
         <v>1</v>
@@ -31432,9 +31382,7 @@
       <c r="O361" s="50">
         <v>0</v>
       </c>
-      <c r="P361" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P361" s="50"/>
       <c r="Q361" s="50">
         <v>0</v>
       </c>
@@ -31477,22 +31425,22 @@
         <v>58</v>
       </c>
       <c r="C362" s="50">
-        <v>330053</v>
+        <v>330047</v>
       </c>
       <c r="D362" s="50" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E362" s="50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F362" s="50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G362" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H362" s="50" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="I362" s="50" t="s">
         <v>78</v>
@@ -31501,7 +31449,7 @@
         <v>62</v>
       </c>
       <c r="K362" s="50" t="s">
-        <v>246</v>
+        <v>465</v>
       </c>
       <c r="L362" s="50" t="s">
         <v>1</v>
@@ -31515,9 +31463,7 @@
       <c r="O362" s="50">
         <v>0</v>
       </c>
-      <c r="P362" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P362" s="50"/>
       <c r="Q362" s="50">
         <v>0</v>
       </c>
@@ -31560,10 +31506,10 @@
         <v>58</v>
       </c>
       <c r="C363" s="50">
-        <v>330054</v>
+        <v>330048</v>
       </c>
       <c r="D363" s="50" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="E363" s="50">
         <v>5</v>
@@ -31575,7 +31521,7 @@
         <v>60</v>
       </c>
       <c r="H363" s="50" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="I363" s="50" t="s">
         <v>78</v>
@@ -31643,22 +31589,22 @@
         <v>58</v>
       </c>
       <c r="C364" s="50">
-        <v>330055</v>
+        <v>330049</v>
       </c>
       <c r="D364" s="50" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="E364" s="50">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F364" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" s="50" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H364" s="50" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="I364" s="50" t="s">
         <v>78</v>
@@ -31667,10 +31613,10 @@
         <v>62</v>
       </c>
       <c r="K364" s="50" t="s">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="L364" s="50" t="s">
-        <v>1</v>
+        <v>778</v>
       </c>
       <c r="M364" s="50" t="s">
         <v>1</v>
@@ -31681,9 +31627,7 @@
       <c r="O364" s="50">
         <v>0</v>
       </c>
-      <c r="P364" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P364" s="50"/>
       <c r="Q364" s="50">
         <v>0</v>
       </c>
@@ -31726,22 +31670,22 @@
         <v>58</v>
       </c>
       <c r="C365" s="50">
-        <v>330056</v>
+        <v>330050</v>
       </c>
       <c r="D365" s="50" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E365" s="50">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F365" s="50">
         <v>0</v>
       </c>
       <c r="G365" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H365" s="50" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="I365" s="50" t="s">
         <v>78</v>
@@ -31750,7 +31694,7 @@
         <v>62</v>
       </c>
       <c r="K365" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L365" s="50" t="s">
         <v>1</v>
@@ -31764,9 +31708,7 @@
       <c r="O365" s="50">
         <v>0</v>
       </c>
-      <c r="P365" s="50" t="s">
-        <v>1</v>
-      </c>
+      <c r="P365" s="50"/>
       <c r="Q365" s="50">
         <v>0</v>
       </c>
@@ -31809,13 +31751,13 @@
         <v>58</v>
       </c>
       <c r="C366" s="50">
-        <v>330058</v>
+        <v>330051</v>
       </c>
       <c r="D366" s="50" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E366" s="50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F366" s="50">
         <v>1</v>
@@ -31824,7 +31766,7 @@
         <v>138</v>
       </c>
       <c r="H366" s="50" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="I366" s="50" t="s">
         <v>78</v>
@@ -31833,7 +31775,7 @@
         <v>62</v>
       </c>
       <c r="K366" s="50" t="s">
-        <v>96</v>
+        <v>230</v>
       </c>
       <c r="L366" s="50" t="s">
         <v>1</v>
@@ -31859,8 +31801,8 @@
       <c r="S366" s="50">
         <v>0</v>
       </c>
-      <c r="T366" s="50" t="s">
-        <v>61</v>
+      <c r="T366" s="50">
+        <v>0</v>
       </c>
       <c r="U366" s="50">
         <v>0</v>
@@ -31892,22 +31834,22 @@
         <v>58</v>
       </c>
       <c r="C367" s="50">
-        <v>330061</v>
+        <v>330052</v>
       </c>
       <c r="D367" s="50" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="E367" s="50">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F367" s="50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G367" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H367" s="50" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="I367" s="50" t="s">
         <v>78</v>
@@ -31916,7 +31858,7 @@
         <v>62</v>
       </c>
       <c r="K367" s="50" t="s">
-        <v>789</v>
+        <v>294</v>
       </c>
       <c r="L367" s="50" t="s">
         <v>1</v>
@@ -31975,22 +31917,22 @@
         <v>58</v>
       </c>
       <c r="C368" s="50">
-        <v>330062</v>
+        <v>330053</v>
       </c>
       <c r="D368" s="50" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="E368" s="50">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F368" s="50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G368" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H368" s="50" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="I368" s="50" t="s">
         <v>78</v>
@@ -31999,7 +31941,7 @@
         <v>62</v>
       </c>
       <c r="K368" s="50" t="s">
-        <v>792</v>
+        <v>246</v>
       </c>
       <c r="L368" s="50" t="s">
         <v>1</v>
@@ -32058,22 +32000,22 @@
         <v>58</v>
       </c>
       <c r="C369" s="50">
-        <v>330063</v>
+        <v>330054</v>
       </c>
       <c r="D369" s="50" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="E369" s="50">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F369" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G369" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H369" s="50" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="I369" s="50" t="s">
         <v>78</v>
@@ -32082,10 +32024,10 @@
         <v>62</v>
       </c>
       <c r="K369" s="50" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="L369" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M369" s="50" t="s">
         <v>1</v>
@@ -32108,8 +32050,8 @@
       <c r="S369" s="50">
         <v>0</v>
       </c>
-      <c r="T369" s="50">
-        <v>0</v>
+      <c r="T369" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U369" s="50">
         <v>0</v>
@@ -32141,22 +32083,22 @@
         <v>58</v>
       </c>
       <c r="C370" s="50">
-        <v>330064</v>
+        <v>330055</v>
       </c>
       <c r="D370" s="50" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="E370" s="50">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F370" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G370" s="50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="H370" s="50" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="I370" s="50" t="s">
         <v>78</v>
@@ -32165,13 +32107,13 @@
         <v>62</v>
       </c>
       <c r="K370" s="50" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="L370" s="50" t="s">
         <v>1</v>
       </c>
       <c r="M370" s="50" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N370" s="50">
         <v>33</v>
@@ -32224,22 +32166,22 @@
         <v>58</v>
       </c>
       <c r="C371" s="50">
-        <v>330065</v>
+        <v>330056</v>
       </c>
       <c r="D371" s="50" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="E371" s="50">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="F371" s="50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G371" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H371" s="50" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="I371" s="50" t="s">
         <v>78</v>
@@ -32248,7 +32190,7 @@
         <v>62</v>
       </c>
       <c r="K371" s="50" t="s">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="L371" s="50" t="s">
         <v>1</v>
@@ -32274,8 +32216,8 @@
       <c r="S371" s="50">
         <v>0</v>
       </c>
-      <c r="T371" s="50" t="s">
-        <v>61</v>
+      <c r="T371" s="50">
+        <v>0</v>
       </c>
       <c r="U371" s="50">
         <v>0</v>
@@ -32307,22 +32249,22 @@
         <v>58</v>
       </c>
       <c r="C372" s="50">
-        <v>330067</v>
+        <v>330058</v>
       </c>
       <c r="D372" s="50" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="E372" s="50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F372" s="50">
         <v>1</v>
       </c>
       <c r="G372" s="50" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H372" s="50" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="I372" s="50" t="s">
         <v>78</v>
@@ -32331,7 +32273,7 @@
         <v>62</v>
       </c>
       <c r="K372" s="50" t="s">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="L372" s="50" t="s">
         <v>1</v>
@@ -32357,8 +32299,8 @@
       <c r="S372" s="50">
         <v>0</v>
       </c>
-      <c r="T372" s="50">
-        <v>0</v>
+      <c r="T372" s="50" t="s">
+        <v>61</v>
       </c>
       <c r="U372" s="50">
         <v>0</v>
@@ -32390,22 +32332,22 @@
         <v>58</v>
       </c>
       <c r="C373" s="50">
-        <v>330068</v>
+        <v>330061</v>
       </c>
       <c r="D373" s="50" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="E373" s="50">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="F373" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G373" s="50" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H373" s="50" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="I373" s="50" t="s">
         <v>78</v>
@@ -32414,7 +32356,7 @@
         <v>62</v>
       </c>
       <c r="K373" s="50" t="s">
-        <v>96</v>
+        <v>797</v>
       </c>
       <c r="L373" s="50" t="s">
         <v>1</v>
@@ -32440,8 +32382,8 @@
       <c r="S373" s="50">
         <v>0</v>
       </c>
-      <c r="T373" s="50" t="s">
-        <v>61</v>
+      <c r="T373" s="50">
+        <v>0</v>
       </c>
       <c r="U373" s="50">
         <v>0</v>
@@ -32473,22 +32415,22 @@
         <v>58</v>
       </c>
       <c r="C374" s="50">
-        <v>330069</v>
+        <v>330062</v>
       </c>
       <c r="D374" s="50" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="E374" s="50">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F374" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G374" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H374" s="50" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="I374" s="50" t="s">
         <v>78</v>
@@ -32497,10 +32439,10 @@
         <v>62</v>
       </c>
       <c r="K374" s="50" t="s">
-        <v>257</v>
+        <v>800</v>
       </c>
       <c r="L374" s="50" t="s">
-        <v>805</v>
+        <v>1</v>
       </c>
       <c r="M374" s="50" t="s">
         <v>1</v>
@@ -32511,7 +32453,9 @@
       <c r="O374" s="50">
         <v>0</v>
       </c>
-      <c r="P374" s="50"/>
+      <c r="P374" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q374" s="50">
         <v>0</v>
       </c>
@@ -32554,22 +32498,22 @@
         <v>58</v>
       </c>
       <c r="C375" s="50">
-        <v>330070</v>
+        <v>330063</v>
       </c>
       <c r="D375" s="50" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="E375" s="50">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F375" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G375" s="50" t="s">
         <v>60</v>
       </c>
       <c r="H375" s="50" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="I375" s="50" t="s">
         <v>78</v>
@@ -32578,10 +32522,10 @@
         <v>62</v>
       </c>
       <c r="K375" s="50" t="s">
-        <v>254</v>
+        <v>75</v>
       </c>
       <c r="L375" s="50" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="M375" s="50" t="s">
         <v>1</v>
@@ -32592,7 +32536,9 @@
       <c r="O375" s="50">
         <v>0</v>
       </c>
-      <c r="P375" s="50"/>
+      <c r="P375" s="50" t="s">
+        <v>1</v>
+      </c>
       <c r="Q375" s="50">
         <v>0</v>
       </c>
@@ -32624,6 +32570,500 @@
         <v>0</v>
       </c>
       <c r="AA375" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="50">
+        <v>371</v>
+      </c>
+      <c r="B376" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C376" s="50">
+        <v>330064</v>
+      </c>
+      <c r="D376" s="50" t="s">
+        <v>803</v>
+      </c>
+      <c r="E376" s="50">
+        <v>29</v>
+      </c>
+      <c r="F376" s="50">
+        <v>0</v>
+      </c>
+      <c r="G376" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H376" s="50" t="s">
+        <v>804</v>
+      </c>
+      <c r="I376" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J376" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K376" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="L376" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M376" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N376" s="50">
+        <v>33</v>
+      </c>
+      <c r="O376" s="50">
+        <v>0</v>
+      </c>
+      <c r="P376" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q376" s="50">
+        <v>0</v>
+      </c>
+      <c r="R376" s="50">
+        <v>0</v>
+      </c>
+      <c r="S376" s="50">
+        <v>0</v>
+      </c>
+      <c r="T376" s="50">
+        <v>0</v>
+      </c>
+      <c r="U376" s="50">
+        <v>0</v>
+      </c>
+      <c r="V376" s="50">
+        <v>0</v>
+      </c>
+      <c r="W376" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X376" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y376" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z376" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA376" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="50">
+        <v>372</v>
+      </c>
+      <c r="B377" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C377" s="50">
+        <v>330065</v>
+      </c>
+      <c r="D377" s="50" t="s">
+        <v>805</v>
+      </c>
+      <c r="E377" s="50">
+        <v>5</v>
+      </c>
+      <c r="F377" s="50">
+        <v>2</v>
+      </c>
+      <c r="G377" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H377" s="50" t="s">
+        <v>806</v>
+      </c>
+      <c r="I377" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J377" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K377" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="L377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N377" s="50">
+        <v>33</v>
+      </c>
+      <c r="O377" s="50">
+        <v>0</v>
+      </c>
+      <c r="P377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q377" s="50">
+        <v>0</v>
+      </c>
+      <c r="R377" s="50">
+        <v>0</v>
+      </c>
+      <c r="S377" s="50">
+        <v>0</v>
+      </c>
+      <c r="T377" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U377" s="50">
+        <v>0</v>
+      </c>
+      <c r="V377" s="50">
+        <v>0</v>
+      </c>
+      <c r="W377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y377" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z377" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA377" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="50">
+        <v>373</v>
+      </c>
+      <c r="B378" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C378" s="50">
+        <v>330067</v>
+      </c>
+      <c r="D378" s="50" t="s">
+        <v>807</v>
+      </c>
+      <c r="E378" s="50">
+        <v>4</v>
+      </c>
+      <c r="F378" s="50">
+        <v>1</v>
+      </c>
+      <c r="G378" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H378" s="50" t="s">
+        <v>808</v>
+      </c>
+      <c r="I378" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J378" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K378" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="L378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N378" s="50">
+        <v>33</v>
+      </c>
+      <c r="O378" s="50">
+        <v>0</v>
+      </c>
+      <c r="P378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q378" s="50">
+        <v>0</v>
+      </c>
+      <c r="R378" s="50">
+        <v>0</v>
+      </c>
+      <c r="S378" s="50">
+        <v>0</v>
+      </c>
+      <c r="T378" s="50">
+        <v>0</v>
+      </c>
+      <c r="U378" s="50">
+        <v>0</v>
+      </c>
+      <c r="V378" s="50">
+        <v>0</v>
+      </c>
+      <c r="W378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y378" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z378" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA378" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="50">
+        <v>374</v>
+      </c>
+      <c r="B379" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C379" s="50">
+        <v>330068</v>
+      </c>
+      <c r="D379" s="50" t="s">
+        <v>809</v>
+      </c>
+      <c r="E379" s="50">
+        <v>5</v>
+      </c>
+      <c r="F379" s="50">
+        <v>1</v>
+      </c>
+      <c r="G379" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="H379" s="50" t="s">
+        <v>810</v>
+      </c>
+      <c r="I379" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J379" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K379" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="L379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N379" s="50">
+        <v>33</v>
+      </c>
+      <c r="O379" s="50">
+        <v>0</v>
+      </c>
+      <c r="P379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q379" s="50">
+        <v>0</v>
+      </c>
+      <c r="R379" s="50">
+        <v>0</v>
+      </c>
+      <c r="S379" s="50">
+        <v>0</v>
+      </c>
+      <c r="T379" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U379" s="50">
+        <v>0</v>
+      </c>
+      <c r="V379" s="50">
+        <v>0</v>
+      </c>
+      <c r="W379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y379" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z379" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA379" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="50">
+        <v>375</v>
+      </c>
+      <c r="B380" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C380" s="50">
+        <v>330069</v>
+      </c>
+      <c r="D380" s="50" t="s">
+        <v>811</v>
+      </c>
+      <c r="E380" s="50">
+        <v>16</v>
+      </c>
+      <c r="F380" s="50">
+        <v>1</v>
+      </c>
+      <c r="G380" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H380" s="50" t="s">
+        <v>812</v>
+      </c>
+      <c r="I380" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J380" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K380" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="L380" s="50" t="s">
+        <v>813</v>
+      </c>
+      <c r="M380" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N380" s="50">
+        <v>33</v>
+      </c>
+      <c r="O380" s="50">
+        <v>0</v>
+      </c>
+      <c r="P380" s="50"/>
+      <c r="Q380" s="50">
+        <v>0</v>
+      </c>
+      <c r="R380" s="50">
+        <v>0</v>
+      </c>
+      <c r="S380" s="50">
+        <v>0</v>
+      </c>
+      <c r="T380" s="50">
+        <v>0</v>
+      </c>
+      <c r="U380" s="50">
+        <v>0</v>
+      </c>
+      <c r="V380" s="50">
+        <v>0</v>
+      </c>
+      <c r="W380" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X380" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y380" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z380" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA380" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="50">
+        <v>376</v>
+      </c>
+      <c r="B381" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C381" s="50">
+        <v>330070</v>
+      </c>
+      <c r="D381" s="50" t="s">
+        <v>814</v>
+      </c>
+      <c r="E381" s="50">
+        <v>3</v>
+      </c>
+      <c r="F381" s="50">
+        <v>1</v>
+      </c>
+      <c r="G381" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="H381" s="50" t="s">
+        <v>815</v>
+      </c>
+      <c r="I381" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J381" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K381" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L381" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="M381" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="N381" s="50">
+        <v>33</v>
+      </c>
+      <c r="O381" s="50">
+        <v>0</v>
+      </c>
+      <c r="P381" s="50"/>
+      <c r="Q381" s="50">
+        <v>0</v>
+      </c>
+      <c r="R381" s="50">
+        <v>0</v>
+      </c>
+      <c r="S381" s="50">
+        <v>0</v>
+      </c>
+      <c r="T381" s="50">
+        <v>0</v>
+      </c>
+      <c r="U381" s="50">
+        <v>0</v>
+      </c>
+      <c r="V381" s="50">
+        <v>0</v>
+      </c>
+      <c r="W381" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X381" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y381" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z381" s="52">
+        <v>0</v>
+      </c>
+      <c r="AA381" s="50" t="s">
         <v>1</v>
       </c>
     </row>
